--- a/Documents/登録機能詳細設計書.xlsx
+++ b/Documents/登録機能詳細設計書.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user47\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user47\Documents\project\taskUN\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8D0DADA-E5E2-491F-9BF5-5CDFE953A59B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{906DC782-4C3B-4A58-B69E-8814B0D9C026}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="1" r:id="rId1"/>
@@ -37,28 +37,6 @@
     </ext>
   </extLst>
 </workbook>
-</file>
-
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata">
-  <metadataTypes count="1">
-    <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLRICHVALUE" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <valueMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </valueMetadata>
-</metadata>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1650,6 +1628,27 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="29" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="45" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="46" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="45" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="45" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="47" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="47" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1677,6 +1676,114 @@
     <xf numFmtId="14" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="3" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
     </xf>
@@ -1689,9 +1796,6 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1701,111 +1805,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="3" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1869,6 +1868,99 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1884,97 +1976,94 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="4" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1983,128 +2072,17 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="29" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="45" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="46" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="45" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="45" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="47" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="47" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -2186,23 +2164,23 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>19050</xdr:colOff>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>38100</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>28575</xdr:rowOff>
+      <xdr:rowOff>38100</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>419100</xdr:colOff>
+      <xdr:colOff>781050</xdr:colOff>
       <xdr:row>32</xdr:row>
-      <xdr:rowOff>133351</xdr:rowOff>
+      <xdr:rowOff>104775</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="図 2">
+        <xdr:cNvPr id="4" name="図 3">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5E46097C-FEED-AE8D-E585-8AD09ECD1141}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5E98D49A-279E-4D96-566C-40CC9D69FB5F}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2224,8 +2202,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="361950" y="942975"/>
-          <a:ext cx="7772400" cy="4638676"/>
+          <a:off x="723900" y="952500"/>
+          <a:ext cx="7772400" cy="4600575"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2675,16 +2653,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>981075</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>76200</xdr:rowOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>66675</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>504825</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>76200</xdr:rowOff>
+      <xdr:colOff>704850</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -2699,7 +2677,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2009775" y="2952750"/>
+          <a:off x="2209800" y="2733675"/>
           <a:ext cx="638175" cy="266700"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2737,30 +2715,25 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>1076325</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>219075</xdr:rowOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>333375</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>857686</xdr:colOff>
+      <xdr:colOff>66949</xdr:colOff>
       <xdr:row>12</xdr:row>
-      <xdr:rowOff>47824</xdr:rowOff>
+      <xdr:rowOff>76375</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="3" name="図 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F7F6865B-B9C2-327A-CD9D-E6DAB1ABF927}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0B8C0DE2-ECBA-A3C7-30AF-511B767E808F}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2782,8 +2755,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2105025" y="1762125"/>
-          <a:ext cx="3124636" cy="1428949"/>
+          <a:off x="2476500" y="1962150"/>
+          <a:ext cx="1962424" cy="1257475"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2792,18 +2765,23 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>809625</xdr:colOff>
+      <xdr:colOff>828675</xdr:colOff>
       <xdr:row>10</xdr:row>
-      <xdr:rowOff>104775</xdr:rowOff>
+      <xdr:rowOff>66675</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>333375</xdr:colOff>
+      <xdr:colOff>352425</xdr:colOff>
       <xdr:row>11</xdr:row>
-      <xdr:rowOff>104775</xdr:rowOff>
+      <xdr:rowOff>66675</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -2818,7 +2796,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1838325" y="2714625"/>
+          <a:off x="1857375" y="2676525"/>
           <a:ext cx="638175" cy="266700"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2856,71 +2834,57 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>1038525</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>95444</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="9" name="図 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{849E8D9C-ED30-C6D0-7477-81AD9F9AC61C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2143125" y="1847850"/>
+          <a:ext cx="2152950" cy="1390844"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
-</file>
-
-<file path=xl/richData/rdRichValueTypes.xml><?xml version="1.0" encoding="utf-8"?>
-<rvTypesInfo xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x">
-  <global>
-    <keyFlags>
-      <key name="_Self">
-        <flag name="ExcludeFromFile" value="1"/>
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_DisplayString">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Flags">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Format">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_SubLabel">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Attribution">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Icon">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Display">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_CanonicalPropertyNames">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_ClassificationId">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-    </keyFlags>
-  </global>
-</rvTypesInfo>
-</file>
-
-<file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="1">
-  <rv s="0">
-    <v>0</v>
-    <v>5</v>
-  </rv>
-</rvData>
-</file>
-
-<file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
-<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="1">
-  <s t="_localImage">
-    <k n="_rvRel:LocalImageIdentifier" t="i"/>
-    <k n="CalcOrigin" t="i"/>
-  </s>
-</rvStructures>
-</file>
-
-<file path=xl/richData/richValueRel.xml><?xml version="1.0" encoding="utf-8"?>
-<richValueRels xmlns="http://schemas.microsoft.com/office/spreadsheetml/2022/richvaluerel" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <rel r:id="rId1"/>
-</richValueRels>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3130,85 +3094,85 @@
   <sheetData>
     <row r="1" spans="3:16" ht="30" customHeight="1"/>
     <row r="2" spans="3:16" ht="30" customHeight="1">
-      <c r="C2" s="51" t="s">
+      <c r="C2" s="58" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="52"/>
-      <c r="E2" s="52"/>
-      <c r="F2" s="52"/>
-      <c r="G2" s="52"/>
-      <c r="H2" s="52"/>
-      <c r="I2" s="52"/>
-      <c r="J2" s="52"/>
-      <c r="K2" s="52"/>
-      <c r="L2" s="52"/>
-      <c r="M2" s="52"/>
-      <c r="N2" s="52"/>
-      <c r="O2" s="52"/>
+      <c r="D2" s="59"/>
+      <c r="E2" s="59"/>
+      <c r="F2" s="59"/>
+      <c r="G2" s="59"/>
+      <c r="H2" s="59"/>
+      <c r="I2" s="59"/>
+      <c r="J2" s="59"/>
+      <c r="K2" s="59"/>
+      <c r="L2" s="59"/>
+      <c r="M2" s="59"/>
+      <c r="N2" s="59"/>
+      <c r="O2" s="59"/>
       <c r="P2" s="1"/>
     </row>
     <row r="3" spans="3:16" ht="30" customHeight="1">
-      <c r="C3" s="50"/>
-      <c r="D3" s="50"/>
-      <c r="E3" s="50"/>
-      <c r="F3" s="50"/>
-      <c r="G3" s="50"/>
-      <c r="H3" s="50"/>
-      <c r="I3" s="50"/>
-      <c r="J3" s="50"/>
-      <c r="K3" s="50"/>
-      <c r="L3" s="50"/>
-      <c r="M3" s="50"/>
-      <c r="N3" s="50"/>
-      <c r="O3" s="50"/>
+      <c r="C3" s="57"/>
+      <c r="D3" s="57"/>
+      <c r="E3" s="57"/>
+      <c r="F3" s="57"/>
+      <c r="G3" s="57"/>
+      <c r="H3" s="57"/>
+      <c r="I3" s="57"/>
+      <c r="J3" s="57"/>
+      <c r="K3" s="57"/>
+      <c r="L3" s="57"/>
+      <c r="M3" s="57"/>
+      <c r="N3" s="57"/>
+      <c r="O3" s="57"/>
       <c r="P3" s="1"/>
     </row>
     <row r="4" spans="3:16" ht="30" customHeight="1">
-      <c r="C4" s="50"/>
-      <c r="D4" s="50"/>
-      <c r="E4" s="50"/>
-      <c r="F4" s="50"/>
-      <c r="G4" s="50"/>
-      <c r="H4" s="50"/>
-      <c r="I4" s="50"/>
-      <c r="J4" s="50"/>
-      <c r="K4" s="50"/>
-      <c r="L4" s="50"/>
-      <c r="M4" s="50"/>
-      <c r="N4" s="50"/>
-      <c r="O4" s="50"/>
+      <c r="C4" s="57"/>
+      <c r="D4" s="57"/>
+      <c r="E4" s="57"/>
+      <c r="F4" s="57"/>
+      <c r="G4" s="57"/>
+      <c r="H4" s="57"/>
+      <c r="I4" s="57"/>
+      <c r="J4" s="57"/>
+      <c r="K4" s="57"/>
+      <c r="L4" s="57"/>
+      <c r="M4" s="57"/>
+      <c r="N4" s="57"/>
+      <c r="O4" s="57"/>
       <c r="P4" s="1"/>
     </row>
     <row r="5" spans="3:16" ht="30" customHeight="1">
-      <c r="C5" s="50"/>
-      <c r="D5" s="50"/>
-      <c r="E5" s="50"/>
-      <c r="F5" s="50"/>
-      <c r="G5" s="50"/>
-      <c r="H5" s="50"/>
-      <c r="I5" s="50"/>
-      <c r="J5" s="50"/>
-      <c r="K5" s="50"/>
-      <c r="L5" s="50"/>
-      <c r="M5" s="50"/>
-      <c r="N5" s="50"/>
-      <c r="O5" s="50"/>
+      <c r="C5" s="57"/>
+      <c r="D5" s="57"/>
+      <c r="E5" s="57"/>
+      <c r="F5" s="57"/>
+      <c r="G5" s="57"/>
+      <c r="H5" s="57"/>
+      <c r="I5" s="57"/>
+      <c r="J5" s="57"/>
+      <c r="K5" s="57"/>
+      <c r="L5" s="57"/>
+      <c r="M5" s="57"/>
+      <c r="N5" s="57"/>
+      <c r="O5" s="57"/>
       <c r="P5" s="1"/>
     </row>
     <row r="6" spans="3:16" ht="30" customHeight="1">
-      <c r="C6" s="50"/>
-      <c r="D6" s="50"/>
-      <c r="E6" s="50"/>
-      <c r="F6" s="50"/>
-      <c r="G6" s="50"/>
-      <c r="H6" s="50"/>
-      <c r="I6" s="50"/>
-      <c r="J6" s="50"/>
-      <c r="K6" s="50"/>
-      <c r="L6" s="50"/>
-      <c r="M6" s="50"/>
-      <c r="N6" s="50"/>
-      <c r="O6" s="50"/>
+      <c r="C6" s="57"/>
+      <c r="D6" s="57"/>
+      <c r="E6" s="57"/>
+      <c r="F6" s="57"/>
+      <c r="G6" s="57"/>
+      <c r="H6" s="57"/>
+      <c r="I6" s="57"/>
+      <c r="J6" s="57"/>
+      <c r="K6" s="57"/>
+      <c r="L6" s="57"/>
+      <c r="M6" s="57"/>
+      <c r="N6" s="57"/>
+      <c r="O6" s="57"/>
       <c r="P6" s="1"/>
     </row>
     <row r="7" spans="3:16" ht="30" customHeight="1">
@@ -3228,50 +3192,50 @@
       <c r="P7" s="1"/>
     </row>
     <row r="8" spans="3:16" ht="30" customHeight="1">
-      <c r="E8" s="53" t="s">
+      <c r="E8" s="60" t="s">
         <v>66</v>
       </c>
-      <c r="F8" s="50"/>
-      <c r="G8" s="50"/>
-      <c r="H8" s="50"/>
-      <c r="I8" s="50"/>
-      <c r="J8" s="50"/>
-      <c r="K8" s="50"/>
-      <c r="L8" s="50"/>
-      <c r="M8" s="50"/>
+      <c r="F8" s="57"/>
+      <c r="G8" s="57"/>
+      <c r="H8" s="57"/>
+      <c r="I8" s="57"/>
+      <c r="J8" s="57"/>
+      <c r="K8" s="57"/>
+      <c r="L8" s="57"/>
+      <c r="M8" s="57"/>
     </row>
     <row r="9" spans="3:16" ht="30" customHeight="1"/>
     <row r="10" spans="3:16" ht="30" customHeight="1"/>
     <row r="11" spans="3:16" ht="30" customHeight="1"/>
     <row r="12" spans="3:16" ht="30" customHeight="1"/>
     <row r="13" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G13" s="46" t="s">
+      <c r="G13" s="53" t="s">
         <v>1</v>
       </c>
-      <c r="H13" s="48"/>
-      <c r="I13" s="46" t="s">
+      <c r="H13" s="55"/>
+      <c r="I13" s="53" t="s">
         <v>2</v>
       </c>
-      <c r="J13" s="47"/>
-      <c r="K13" s="48"/>
+      <c r="J13" s="54"/>
+      <c r="K13" s="55"/>
     </row>
     <row r="14" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G14" s="46" t="s">
+      <c r="G14" s="53" t="s">
         <v>67</v>
       </c>
-      <c r="H14" s="48"/>
-      <c r="I14" s="54">
+      <c r="H14" s="55"/>
+      <c r="I14" s="61">
         <v>45805</v>
       </c>
-      <c r="J14" s="47"/>
-      <c r="K14" s="48"/>
+      <c r="J14" s="54"/>
+      <c r="K14" s="55"/>
     </row>
     <row r="15" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G15" s="46"/>
-      <c r="H15" s="48"/>
-      <c r="I15" s="46"/>
-      <c r="J15" s="47"/>
-      <c r="K15" s="48"/>
+      <c r="G15" s="53"/>
+      <c r="H15" s="55"/>
+      <c r="I15" s="53"/>
+      <c r="J15" s="54"/>
+      <c r="K15" s="55"/>
     </row>
     <row r="16" spans="3:16" ht="15.75" customHeight="1">
       <c r="G16" s="3"/>
@@ -3280,13 +3244,13 @@
       <c r="J16" s="3"/>
     </row>
     <row r="17" spans="7:11" ht="30" customHeight="1">
-      <c r="G17" s="49" t="s">
+      <c r="G17" s="56" t="s">
         <v>64</v>
       </c>
-      <c r="H17" s="50"/>
-      <c r="I17" s="50"/>
-      <c r="J17" s="50"/>
-      <c r="K17" s="50"/>
+      <c r="H17" s="57"/>
+      <c r="I17" s="57"/>
+      <c r="J17" s="57"/>
+      <c r="K17" s="57"/>
     </row>
     <row r="18" spans="7:11" ht="14.25" customHeight="1"/>
     <row r="19" spans="7:11" ht="24.75" customHeight="1"/>
@@ -4301,19 +4265,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="90" t="s">
+      <c r="A1" s="62" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="91"/>
-      <c r="C1" s="92"/>
-      <c r="D1" s="97" t="s">
+      <c r="B1" s="63"/>
+      <c r="C1" s="64"/>
+      <c r="D1" s="71" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="87"/>
-      <c r="F1" s="97" t="s">
+      <c r="E1" s="72"/>
+      <c r="F1" s="71" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="87"/>
+      <c r="G1" s="72"/>
       <c r="H1" s="34" t="s">
         <v>6</v>
       </c>
@@ -4325,192 +4289,192 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="93"/>
-      <c r="B2" s="94"/>
-      <c r="C2" s="69"/>
-      <c r="D2" s="66" t="s">
+      <c r="A2" s="65"/>
+      <c r="B2" s="66"/>
+      <c r="C2" s="67"/>
+      <c r="D2" s="73" t="s">
         <v>79</v>
       </c>
-      <c r="E2" s="67"/>
-      <c r="F2" s="66" t="s">
+      <c r="E2" s="74"/>
+      <c r="F2" s="73" t="s">
         <v>78</v>
       </c>
-      <c r="G2" s="67"/>
-      <c r="H2" s="72">
+      <c r="G2" s="74"/>
+      <c r="H2" s="77">
         <v>45806</v>
       </c>
-      <c r="I2" s="81" t="s">
+      <c r="I2" s="90" t="s">
         <v>77</v>
       </c>
-      <c r="J2" s="82"/>
+      <c r="J2" s="91"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="93"/>
-      <c r="B3" s="94"/>
-      <c r="C3" s="69"/>
-      <c r="D3" s="68"/>
-      <c r="E3" s="69"/>
-      <c r="F3" s="68"/>
-      <c r="G3" s="69"/>
-      <c r="H3" s="73"/>
-      <c r="I3" s="73"/>
-      <c r="J3" s="83"/>
+      <c r="A3" s="65"/>
+      <c r="B3" s="66"/>
+      <c r="C3" s="67"/>
+      <c r="D3" s="75"/>
+      <c r="E3" s="67"/>
+      <c r="F3" s="75"/>
+      <c r="G3" s="67"/>
+      <c r="H3" s="78"/>
+      <c r="I3" s="78"/>
+      <c r="J3" s="92"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="95"/>
-      <c r="B4" s="96"/>
-      <c r="C4" s="71"/>
-      <c r="D4" s="70"/>
-      <c r="E4" s="71"/>
-      <c r="F4" s="70"/>
-      <c r="G4" s="71"/>
-      <c r="H4" s="74"/>
-      <c r="I4" s="74"/>
-      <c r="J4" s="84"/>
+      <c r="A4" s="68"/>
+      <c r="B4" s="69"/>
+      <c r="C4" s="70"/>
+      <c r="D4" s="76"/>
+      <c r="E4" s="70"/>
+      <c r="F4" s="76"/>
+      <c r="G4" s="70"/>
+      <c r="H4" s="79"/>
+      <c r="I4" s="79"/>
+      <c r="J4" s="93"/>
     </row>
     <row r="5" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A5" s="85" t="s">
+      <c r="A5" s="94" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="86"/>
-      <c r="C5" s="87"/>
-      <c r="D5" s="88" t="s">
+      <c r="B5" s="95"/>
+      <c r="C5" s="72"/>
+      <c r="D5" s="96" t="s">
         <v>76</v>
       </c>
-      <c r="E5" s="86"/>
-      <c r="F5" s="86"/>
-      <c r="G5" s="86"/>
-      <c r="H5" s="86"/>
-      <c r="I5" s="86"/>
-      <c r="J5" s="89"/>
+      <c r="E5" s="95"/>
+      <c r="F5" s="95"/>
+      <c r="G5" s="95"/>
+      <c r="H5" s="95"/>
+      <c r="I5" s="95"/>
+      <c r="J5" s="97"/>
     </row>
     <row r="6" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A6" s="75" t="s">
+      <c r="A6" s="80" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="64"/>
-      <c r="C6" s="59"/>
-      <c r="D6" s="63" t="s">
+      <c r="B6" s="81"/>
+      <c r="C6" s="82"/>
+      <c r="D6" s="83" t="s">
         <v>75</v>
       </c>
-      <c r="E6" s="64"/>
-      <c r="F6" s="64"/>
-      <c r="G6" s="64"/>
-      <c r="H6" s="64"/>
-      <c r="I6" s="64"/>
-      <c r="J6" s="65"/>
+      <c r="E6" s="81"/>
+      <c r="F6" s="81"/>
+      <c r="G6" s="81"/>
+      <c r="H6" s="81"/>
+      <c r="I6" s="81"/>
+      <c r="J6" s="84"/>
     </row>
     <row r="7" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A7" s="75" t="s">
+      <c r="A7" s="80" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="64"/>
-      <c r="C7" s="59"/>
-      <c r="D7" s="63" t="s">
+      <c r="B7" s="81"/>
+      <c r="C7" s="82"/>
+      <c r="D7" s="83" t="s">
         <v>74</v>
       </c>
-      <c r="E7" s="64"/>
-      <c r="F7" s="64"/>
-      <c r="G7" s="64"/>
-      <c r="H7" s="64"/>
-      <c r="I7" s="64"/>
-      <c r="J7" s="65"/>
+      <c r="E7" s="81"/>
+      <c r="F7" s="81"/>
+      <c r="G7" s="81"/>
+      <c r="H7" s="81"/>
+      <c r="I7" s="81"/>
+      <c r="J7" s="84"/>
     </row>
     <row r="8" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A8" s="75" t="s">
+      <c r="A8" s="80" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="64"/>
-      <c r="C8" s="59"/>
-      <c r="D8" s="63" t="s">
+      <c r="B8" s="81"/>
+      <c r="C8" s="82"/>
+      <c r="D8" s="83" t="s">
         <v>73</v>
       </c>
-      <c r="E8" s="64"/>
-      <c r="F8" s="64"/>
-      <c r="G8" s="64"/>
-      <c r="H8" s="64"/>
-      <c r="I8" s="64"/>
-      <c r="J8" s="65"/>
+      <c r="E8" s="81"/>
+      <c r="F8" s="81"/>
+      <c r="G8" s="81"/>
+      <c r="H8" s="81"/>
+      <c r="I8" s="81"/>
+      <c r="J8" s="84"/>
     </row>
     <row r="9" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A9" s="55" t="s">
+      <c r="A9" s="98" t="s">
         <v>13</v>
       </c>
-      <c r="B9" s="58" t="s">
+      <c r="B9" s="101" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="59"/>
-      <c r="D9" s="60" t="s">
+      <c r="C9" s="82"/>
+      <c r="D9" s="102" t="s">
         <v>72</v>
       </c>
-      <c r="E9" s="61"/>
-      <c r="F9" s="61"/>
-      <c r="G9" s="61"/>
-      <c r="H9" s="61"/>
-      <c r="I9" s="61"/>
-      <c r="J9" s="62"/>
+      <c r="E9" s="103"/>
+      <c r="F9" s="103"/>
+      <c r="G9" s="103"/>
+      <c r="H9" s="103"/>
+      <c r="I9" s="103"/>
+      <c r="J9" s="104"/>
     </row>
     <row r="10" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A10" s="56"/>
-      <c r="B10" s="58" t="s">
+      <c r="A10" s="99"/>
+      <c r="B10" s="101" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="59"/>
-      <c r="D10" s="63" t="s">
+      <c r="C10" s="82"/>
+      <c r="D10" s="83" t="s">
         <v>71</v>
       </c>
-      <c r="E10" s="64"/>
-      <c r="F10" s="64"/>
-      <c r="G10" s="64"/>
-      <c r="H10" s="64"/>
-      <c r="I10" s="64"/>
-      <c r="J10" s="65"/>
+      <c r="E10" s="81"/>
+      <c r="F10" s="81"/>
+      <c r="G10" s="81"/>
+      <c r="H10" s="81"/>
+      <c r="I10" s="81"/>
+      <c r="J10" s="84"/>
     </row>
     <row r="11" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A11" s="57"/>
-      <c r="B11" s="58" t="s">
+      <c r="A11" s="100"/>
+      <c r="B11" s="101" t="s">
         <v>16</v>
       </c>
-      <c r="C11" s="59"/>
-      <c r="D11" s="63" t="s">
+      <c r="C11" s="82"/>
+      <c r="D11" s="83" t="s">
         <v>70</v>
       </c>
-      <c r="E11" s="64"/>
-      <c r="F11" s="64"/>
-      <c r="G11" s="64"/>
-      <c r="H11" s="64"/>
-      <c r="I11" s="64"/>
-      <c r="J11" s="65"/>
+      <c r="E11" s="81"/>
+      <c r="F11" s="81"/>
+      <c r="G11" s="81"/>
+      <c r="H11" s="81"/>
+      <c r="I11" s="81"/>
+      <c r="J11" s="84"/>
     </row>
     <row r="12" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A12" s="75" t="s">
+      <c r="A12" s="80" t="s">
         <v>17</v>
       </c>
-      <c r="B12" s="64"/>
-      <c r="C12" s="59"/>
-      <c r="D12" s="63" t="s">
+      <c r="B12" s="81"/>
+      <c r="C12" s="82"/>
+      <c r="D12" s="83" t="s">
         <v>69</v>
       </c>
-      <c r="E12" s="64"/>
-      <c r="F12" s="64"/>
-      <c r="G12" s="64"/>
-      <c r="H12" s="64"/>
-      <c r="I12" s="64"/>
-      <c r="J12" s="65"/>
+      <c r="E12" s="81"/>
+      <c r="F12" s="81"/>
+      <c r="G12" s="81"/>
+      <c r="H12" s="81"/>
+      <c r="I12" s="81"/>
+      <c r="J12" s="84"/>
     </row>
     <row r="13" spans="1:10" ht="26.25" customHeight="1" thickBot="1">
-      <c r="A13" s="76" t="s">
+      <c r="A13" s="85" t="s">
         <v>18</v>
       </c>
-      <c r="B13" s="77"/>
-      <c r="C13" s="78"/>
-      <c r="D13" s="79"/>
-      <c r="E13" s="77"/>
-      <c r="F13" s="77"/>
-      <c r="G13" s="77"/>
-      <c r="H13" s="77"/>
-      <c r="I13" s="77"/>
-      <c r="J13" s="80"/>
+      <c r="B13" s="86"/>
+      <c r="C13" s="87"/>
+      <c r="D13" s="88"/>
+      <c r="E13" s="86"/>
+      <c r="F13" s="86"/>
+      <c r="G13" s="86"/>
+      <c r="H13" s="86"/>
+      <c r="I13" s="86"/>
+      <c r="J13" s="89"/>
     </row>
     <row r="14" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="15" spans="1:10" ht="12.75" customHeight="1"/>
@@ -5501,11 +5465,12 @@
     <row r="1000" s="32" customFormat="1" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="A1:C4"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="D2:E4"/>
-    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="D9:J9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="D10:J10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="D11:J11"/>
     <mergeCell ref="H2:H4"/>
     <mergeCell ref="A12:C12"/>
     <mergeCell ref="D12:J12"/>
@@ -5522,12 +5487,11 @@
     <mergeCell ref="A6:C6"/>
     <mergeCell ref="D6:J6"/>
     <mergeCell ref="A9:A11"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="D9:J9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="D10:J10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="D11:J11"/>
+    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="F2:G4"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.70833333333333304" right="0.70833333333333304" top="0.74791666666666701" bottom="0.74791666666666701" header="0" footer="0"/>
@@ -5546,19 +5510,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="105" t="s">
+      <c r="A1" s="112" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="106"/>
-      <c r="C1" s="107"/>
-      <c r="D1" s="113" t="s">
+      <c r="B1" s="113"/>
+      <c r="C1" s="114"/>
+      <c r="D1" s="120" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="114"/>
-      <c r="F1" s="113" t="s">
+      <c r="E1" s="121"/>
+      <c r="F1" s="120" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="114"/>
+      <c r="G1" s="121"/>
       <c r="H1" s="4" t="s">
         <v>6</v>
       </c>
@@ -5570,46 +5534,46 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="108"/>
-      <c r="B2" s="50"/>
-      <c r="C2" s="109"/>
-      <c r="D2" s="115" t="s">
+      <c r="A2" s="115"/>
+      <c r="B2" s="57"/>
+      <c r="C2" s="116"/>
+      <c r="D2" s="122" t="s">
         <v>107</v>
       </c>
-      <c r="E2" s="116"/>
-      <c r="F2" s="115" t="s">
+      <c r="E2" s="123"/>
+      <c r="F2" s="122" t="s">
         <v>64</v>
       </c>
-      <c r="G2" s="116"/>
-      <c r="H2" s="98">
+      <c r="G2" s="123"/>
+      <c r="H2" s="105">
         <v>45806</v>
       </c>
-      <c r="I2" s="101"/>
-      <c r="J2" s="102"/>
+      <c r="I2" s="108"/>
+      <c r="J2" s="109"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="108"/>
-      <c r="B3" s="50"/>
-      <c r="C3" s="109"/>
-      <c r="D3" s="117"/>
-      <c r="E3" s="109"/>
-      <c r="F3" s="117"/>
-      <c r="G3" s="109"/>
-      <c r="H3" s="99"/>
-      <c r="I3" s="99"/>
-      <c r="J3" s="103"/>
+      <c r="A3" s="115"/>
+      <c r="B3" s="57"/>
+      <c r="C3" s="116"/>
+      <c r="D3" s="124"/>
+      <c r="E3" s="116"/>
+      <c r="F3" s="124"/>
+      <c r="G3" s="116"/>
+      <c r="H3" s="106"/>
+      <c r="I3" s="106"/>
+      <c r="J3" s="110"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="110"/>
-      <c r="B4" s="111"/>
-      <c r="C4" s="112"/>
-      <c r="D4" s="118"/>
-      <c r="E4" s="112"/>
-      <c r="F4" s="118"/>
-      <c r="G4" s="112"/>
-      <c r="H4" s="100"/>
-      <c r="I4" s="100"/>
-      <c r="J4" s="104"/>
+      <c r="A4" s="117"/>
+      <c r="B4" s="118"/>
+      <c r="C4" s="119"/>
+      <c r="D4" s="125"/>
+      <c r="E4" s="119"/>
+      <c r="F4" s="125"/>
+      <c r="G4" s="119"/>
+      <c r="H4" s="107"/>
+      <c r="I4" s="107"/>
+      <c r="J4" s="111"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="7"/>
@@ -6966,19 +6930,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="105" t="s">
+      <c r="A1" s="112" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="106"/>
-      <c r="C1" s="107"/>
-      <c r="D1" s="113" t="s">
+      <c r="B1" s="113"/>
+      <c r="C1" s="114"/>
+      <c r="D1" s="120" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="114"/>
-      <c r="F1" s="113" t="s">
+      <c r="E1" s="121"/>
+      <c r="F1" s="120" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="114"/>
+      <c r="G1" s="121"/>
       <c r="H1" s="4" t="s">
         <v>6</v>
       </c>
@@ -6990,48 +6954,48 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="108"/>
-      <c r="B2" s="50"/>
-      <c r="C2" s="109"/>
-      <c r="D2" s="115" t="s">
+      <c r="A2" s="115"/>
+      <c r="B2" s="57"/>
+      <c r="C2" s="116"/>
+      <c r="D2" s="122" t="s">
         <v>107</v>
       </c>
-      <c r="E2" s="116"/>
-      <c r="F2" s="115" t="s">
+      <c r="E2" s="123"/>
+      <c r="F2" s="122" t="s">
         <v>106</v>
       </c>
-      <c r="G2" s="116"/>
-      <c r="H2" s="98">
+      <c r="G2" s="123"/>
+      <c r="H2" s="105">
         <v>45807</v>
       </c>
-      <c r="I2" s="101" t="s">
+      <c r="I2" s="108" t="s">
         <v>105</v>
       </c>
-      <c r="J2" s="102"/>
+      <c r="J2" s="109"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="108"/>
-      <c r="B3" s="50"/>
-      <c r="C3" s="109"/>
-      <c r="D3" s="117"/>
-      <c r="E3" s="109"/>
-      <c r="F3" s="117"/>
-      <c r="G3" s="109"/>
-      <c r="H3" s="99"/>
-      <c r="I3" s="99"/>
-      <c r="J3" s="103"/>
+      <c r="A3" s="115"/>
+      <c r="B3" s="57"/>
+      <c r="C3" s="116"/>
+      <c r="D3" s="124"/>
+      <c r="E3" s="116"/>
+      <c r="F3" s="124"/>
+      <c r="G3" s="116"/>
+      <c r="H3" s="106"/>
+      <c r="I3" s="106"/>
+      <c r="J3" s="110"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="110"/>
-      <c r="B4" s="111"/>
-      <c r="C4" s="112"/>
-      <c r="D4" s="118"/>
-      <c r="E4" s="112"/>
-      <c r="F4" s="118"/>
-      <c r="G4" s="112"/>
-      <c r="H4" s="100"/>
-      <c r="I4" s="100"/>
-      <c r="J4" s="104"/>
+      <c r="A4" s="117"/>
+      <c r="B4" s="118"/>
+      <c r="C4" s="119"/>
+      <c r="D4" s="125"/>
+      <c r="E4" s="119"/>
+      <c r="F4" s="125"/>
+      <c r="G4" s="119"/>
+      <c r="H4" s="107"/>
+      <c r="I4" s="107"/>
+      <c r="J4" s="111"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="7"/>
@@ -8383,19 +8347,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="152" t="s">
+      <c r="A1" s="147" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="153"/>
-      <c r="C1" s="154"/>
-      <c r="D1" s="131" t="s">
+      <c r="B1" s="148"/>
+      <c r="C1" s="149"/>
+      <c r="D1" s="151" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="132"/>
-      <c r="F1" s="131" t="s">
+      <c r="E1" s="138"/>
+      <c r="F1" s="151" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="132"/>
+      <c r="G1" s="138"/>
       <c r="H1" s="45" t="s">
         <v>6</v>
       </c>
@@ -8407,190 +8371,190 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="149"/>
-      <c r="B2" s="150"/>
-      <c r="C2" s="136"/>
-      <c r="D2" s="133" t="s">
+      <c r="A2" s="144"/>
+      <c r="B2" s="145"/>
+      <c r="C2" s="150"/>
+      <c r="D2" s="152" t="s">
         <v>107</v>
       </c>
-      <c r="E2" s="134"/>
-      <c r="F2" s="133" t="s">
+      <c r="E2" s="153"/>
+      <c r="F2" s="152" t="s">
         <v>106</v>
       </c>
-      <c r="G2" s="134"/>
-      <c r="H2" s="137">
+      <c r="G2" s="153"/>
+      <c r="H2" s="155">
         <v>45806</v>
       </c>
-      <c r="I2" s="139" t="s">
+      <c r="I2" s="132" t="s">
         <v>105</v>
       </c>
-      <c r="J2" s="140"/>
+      <c r="J2" s="134"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="149"/>
-      <c r="B3" s="150"/>
-      <c r="C3" s="136"/>
-      <c r="D3" s="135"/>
-      <c r="E3" s="136"/>
-      <c r="F3" s="135"/>
-      <c r="G3" s="136"/>
-      <c r="H3" s="138"/>
-      <c r="I3" s="138"/>
-      <c r="J3" s="141"/>
+      <c r="A3" s="144"/>
+      <c r="B3" s="145"/>
+      <c r="C3" s="150"/>
+      <c r="D3" s="154"/>
+      <c r="E3" s="150"/>
+      <c r="F3" s="154"/>
+      <c r="G3" s="150"/>
+      <c r="H3" s="133"/>
+      <c r="I3" s="133"/>
+      <c r="J3" s="135"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="149"/>
-      <c r="B4" s="150"/>
-      <c r="C4" s="136"/>
-      <c r="D4" s="135"/>
-      <c r="E4" s="136"/>
-      <c r="F4" s="135"/>
-      <c r="G4" s="136"/>
-      <c r="H4" s="138"/>
-      <c r="I4" s="138"/>
-      <c r="J4" s="141"/>
+      <c r="A4" s="144"/>
+      <c r="B4" s="145"/>
+      <c r="C4" s="150"/>
+      <c r="D4" s="154"/>
+      <c r="E4" s="150"/>
+      <c r="F4" s="154"/>
+      <c r="G4" s="150"/>
+      <c r="H4" s="133"/>
+      <c r="I4" s="133"/>
+      <c r="J4" s="135"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="142" t="s">
+      <c r="A5" s="136" t="s">
         <v>22</v>
       </c>
-      <c r="B5" s="143"/>
-      <c r="C5" s="132"/>
-      <c r="D5" s="144" t="s">
+      <c r="B5" s="137"/>
+      <c r="C5" s="138"/>
+      <c r="D5" s="139" t="s">
         <v>104</v>
       </c>
-      <c r="E5" s="143"/>
-      <c r="F5" s="143"/>
-      <c r="G5" s="143"/>
-      <c r="H5" s="143"/>
-      <c r="I5" s="143"/>
-      <c r="J5" s="145"/>
+      <c r="E5" s="137"/>
+      <c r="F5" s="137"/>
+      <c r="G5" s="137"/>
+      <c r="H5" s="137"/>
+      <c r="I5" s="137"/>
+      <c r="J5" s="140"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="129" t="s">
+      <c r="A6" s="126" t="s">
         <v>23</v>
       </c>
-      <c r="B6" s="125"/>
-      <c r="C6" s="125"/>
-      <c r="D6" s="125"/>
-      <c r="E6" s="125"/>
-      <c r="F6" s="125"/>
-      <c r="G6" s="125"/>
-      <c r="H6" s="125"/>
-      <c r="I6" s="125"/>
-      <c r="J6" s="128"/>
+      <c r="B6" s="127"/>
+      <c r="C6" s="127"/>
+      <c r="D6" s="127"/>
+      <c r="E6" s="127"/>
+      <c r="F6" s="127"/>
+      <c r="G6" s="127"/>
+      <c r="H6" s="127"/>
+      <c r="I6" s="127"/>
+      <c r="J6" s="131"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="146"/>
-      <c r="B7" s="147"/>
-      <c r="C7" s="147"/>
-      <c r="D7" s="147"/>
-      <c r="E7" s="147"/>
-      <c r="F7" s="147"/>
-      <c r="G7" s="147"/>
-      <c r="H7" s="147"/>
-      <c r="I7" s="147"/>
-      <c r="J7" s="148"/>
+      <c r="A7" s="141"/>
+      <c r="B7" s="142"/>
+      <c r="C7" s="142"/>
+      <c r="D7" s="142"/>
+      <c r="E7" s="142"/>
+      <c r="F7" s="142"/>
+      <c r="G7" s="142"/>
+      <c r="H7" s="142"/>
+      <c r="I7" s="142"/>
+      <c r="J7" s="143"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="149"/>
-      <c r="B8" s="150"/>
-      <c r="C8" s="150"/>
-      <c r="D8" s="150"/>
-      <c r="E8" s="150"/>
-      <c r="F8" s="150"/>
-      <c r="G8" s="150"/>
-      <c r="H8" s="150"/>
-      <c r="I8" s="150"/>
-      <c r="J8" s="151"/>
+      <c r="A8" s="144"/>
+      <c r="B8" s="145"/>
+      <c r="C8" s="145"/>
+      <c r="D8" s="145"/>
+      <c r="E8" s="145"/>
+      <c r="F8" s="145"/>
+      <c r="G8" s="145"/>
+      <c r="H8" s="145"/>
+      <c r="I8" s="145"/>
+      <c r="J8" s="146"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="149"/>
-      <c r="B9" s="150"/>
-      <c r="C9" s="150"/>
-      <c r="D9" s="150"/>
-      <c r="E9" s="150"/>
-      <c r="F9" s="150"/>
-      <c r="G9" s="150"/>
-      <c r="H9" s="150"/>
-      <c r="I9" s="150"/>
-      <c r="J9" s="151"/>
+      <c r="A9" s="144"/>
+      <c r="B9" s="145"/>
+      <c r="C9" s="145"/>
+      <c r="D9" s="145"/>
+      <c r="E9" s="145"/>
+      <c r="F9" s="145"/>
+      <c r="G9" s="145"/>
+      <c r="H9" s="145"/>
+      <c r="I9" s="145"/>
+      <c r="J9" s="146"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="149"/>
-      <c r="B10" s="150"/>
-      <c r="C10" s="150"/>
-      <c r="D10" s="150"/>
-      <c r="E10" s="150"/>
-      <c r="F10" s="150"/>
-      <c r="G10" s="150"/>
-      <c r="H10" s="150"/>
-      <c r="I10" s="150"/>
-      <c r="J10" s="151"/>
+      <c r="A10" s="144"/>
+      <c r="B10" s="145"/>
+      <c r="C10" s="145"/>
+      <c r="D10" s="145"/>
+      <c r="E10" s="145"/>
+      <c r="F10" s="145"/>
+      <c r="G10" s="145"/>
+      <c r="H10" s="145"/>
+      <c r="I10" s="145"/>
+      <c r="J10" s="146"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="149"/>
-      <c r="B11" s="150"/>
-      <c r="C11" s="150"/>
-      <c r="D11" s="150"/>
-      <c r="E11" s="150"/>
-      <c r="F11" s="150"/>
-      <c r="G11" s="150"/>
-      <c r="H11" s="150"/>
-      <c r="I11" s="150"/>
-      <c r="J11" s="151"/>
+      <c r="A11" s="144"/>
+      <c r="B11" s="145"/>
+      <c r="C11" s="145"/>
+      <c r="D11" s="145"/>
+      <c r="E11" s="145"/>
+      <c r="F11" s="145"/>
+      <c r="G11" s="145"/>
+      <c r="H11" s="145"/>
+      <c r="I11" s="145"/>
+      <c r="J11" s="146"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="149"/>
-      <c r="B12" s="150"/>
-      <c r="C12" s="150"/>
-      <c r="D12" s="150"/>
-      <c r="E12" s="150"/>
-      <c r="F12" s="150"/>
-      <c r="G12" s="150"/>
-      <c r="H12" s="150"/>
-      <c r="I12" s="150"/>
-      <c r="J12" s="151"/>
+      <c r="A12" s="144"/>
+      <c r="B12" s="145"/>
+      <c r="C12" s="145"/>
+      <c r="D12" s="145"/>
+      <c r="E12" s="145"/>
+      <c r="F12" s="145"/>
+      <c r="G12" s="145"/>
+      <c r="H12" s="145"/>
+      <c r="I12" s="145"/>
+      <c r="J12" s="146"/>
     </row>
     <row r="13" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A13" s="149"/>
-      <c r="B13" s="150"/>
-      <c r="C13" s="150"/>
-      <c r="D13" s="150"/>
-      <c r="E13" s="150"/>
-      <c r="F13" s="150"/>
-      <c r="G13" s="150"/>
-      <c r="H13" s="150"/>
-      <c r="I13" s="150"/>
-      <c r="J13" s="151"/>
+      <c r="A13" s="144"/>
+      <c r="B13" s="145"/>
+      <c r="C13" s="145"/>
+      <c r="D13" s="145"/>
+      <c r="E13" s="145"/>
+      <c r="F13" s="145"/>
+      <c r="G13" s="145"/>
+      <c r="H13" s="145"/>
+      <c r="I13" s="145"/>
+      <c r="J13" s="146"/>
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A14" s="129" t="s">
+      <c r="A14" s="126" t="s">
         <v>24</v>
       </c>
-      <c r="B14" s="125"/>
-      <c r="C14" s="125"/>
-      <c r="D14" s="125"/>
-      <c r="E14" s="125"/>
-      <c r="F14" s="125"/>
-      <c r="G14" s="125"/>
-      <c r="H14" s="125"/>
-      <c r="I14" s="125"/>
-      <c r="J14" s="128"/>
+      <c r="B14" s="127"/>
+      <c r="C14" s="127"/>
+      <c r="D14" s="127"/>
+      <c r="E14" s="127"/>
+      <c r="F14" s="127"/>
+      <c r="G14" s="127"/>
+      <c r="H14" s="127"/>
+      <c r="I14" s="127"/>
+      <c r="J14" s="131"/>
     </row>
     <row r="15" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A15" s="129" t="s">
+      <c r="A15" s="126" t="s">
         <v>25</v>
       </c>
-      <c r="B15" s="125"/>
-      <c r="C15" s="126"/>
-      <c r="D15" s="127" t="s">
+      <c r="B15" s="127"/>
+      <c r="C15" s="128"/>
+      <c r="D15" s="129" t="s">
         <v>103</v>
       </c>
-      <c r="E15" s="125"/>
-      <c r="F15" s="125"/>
-      <c r="G15" s="125"/>
-      <c r="H15" s="126"/>
+      <c r="E15" s="127"/>
+      <c r="F15" s="127"/>
+      <c r="G15" s="127"/>
+      <c r="H15" s="128"/>
       <c r="I15" s="41" t="s">
         <v>26</v>
       </c>
@@ -8599,11 +8563,11 @@
       </c>
     </row>
     <row r="16" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A16" s="129" t="s">
+      <c r="A16" s="126" t="s">
         <v>27</v>
       </c>
-      <c r="B16" s="125"/>
-      <c r="C16" s="126"/>
+      <c r="B16" s="127"/>
+      <c r="C16" s="128"/>
       <c r="D16" s="41" t="s">
         <v>28</v>
       </c>
@@ -8616,18 +8580,18 @@
       <c r="G16" s="41" t="s">
         <v>31</v>
       </c>
-      <c r="H16" s="130" t="s">
+      <c r="H16" s="156" t="s">
         <v>18</v>
       </c>
-      <c r="I16" s="125"/>
-      <c r="J16" s="128"/>
+      <c r="I16" s="127"/>
+      <c r="J16" s="131"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="124">
+      <c r="A17" s="130">
         <v>1</v>
       </c>
-      <c r="B17" s="125"/>
-      <c r="C17" s="126"/>
+      <c r="B17" s="127"/>
+      <c r="C17" s="128"/>
       <c r="D17" s="40" t="s">
         <v>101</v>
       </c>
@@ -8640,18 +8604,18 @@
       <c r="G17" s="39" t="s">
         <v>91</v>
       </c>
-      <c r="H17" s="127" t="s">
+      <c r="H17" s="129" t="s">
         <v>99</v>
       </c>
-      <c r="I17" s="125"/>
-      <c r="J17" s="128"/>
+      <c r="I17" s="127"/>
+      <c r="J17" s="131"/>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A18" s="124">
+      <c r="A18" s="130">
         <v>2</v>
       </c>
-      <c r="B18" s="125"/>
-      <c r="C18" s="126"/>
+      <c r="B18" s="127"/>
+      <c r="C18" s="128"/>
       <c r="D18" s="40" t="s">
         <v>98</v>
       </c>
@@ -8664,18 +8628,18 @@
       <c r="G18" s="39" t="s">
         <v>91</v>
       </c>
-      <c r="H18" s="127" t="s">
+      <c r="H18" s="129" t="s">
         <v>95</v>
       </c>
-      <c r="I18" s="125"/>
-      <c r="J18" s="128"/>
+      <c r="I18" s="127"/>
+      <c r="J18" s="131"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="124">
+      <c r="A19" s="130">
         <v>3</v>
       </c>
-      <c r="B19" s="125"/>
-      <c r="C19" s="126"/>
+      <c r="B19" s="127"/>
+      <c r="C19" s="128"/>
       <c r="D19" s="40" t="s">
         <v>94</v>
       </c>
@@ -8688,18 +8652,18 @@
       <c r="G19" s="39" t="s">
         <v>91</v>
       </c>
-      <c r="H19" s="127" t="s">
+      <c r="H19" s="129" t="s">
         <v>90</v>
       </c>
-      <c r="I19" s="125"/>
-      <c r="J19" s="128"/>
+      <c r="I19" s="127"/>
+      <c r="J19" s="131"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="124">
+      <c r="A20" s="130">
         <v>4</v>
       </c>
-      <c r="B20" s="125"/>
-      <c r="C20" s="126"/>
+      <c r="B20" s="127"/>
+      <c r="C20" s="128"/>
       <c r="D20" s="40" t="s">
         <v>89</v>
       </c>
@@ -8712,18 +8676,18 @@
       <c r="G20" s="39" t="s">
         <v>86</v>
       </c>
-      <c r="H20" s="127" t="s">
+      <c r="H20" s="129" t="s">
         <v>85</v>
       </c>
-      <c r="I20" s="125"/>
-      <c r="J20" s="128"/>
+      <c r="I20" s="127"/>
+      <c r="J20" s="131"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="124">
+      <c r="A21" s="130">
         <v>5</v>
       </c>
-      <c r="B21" s="125"/>
-      <c r="C21" s="126"/>
+      <c r="B21" s="127"/>
+      <c r="C21" s="128"/>
       <c r="D21" s="40" t="s">
         <v>68</v>
       </c>
@@ -8736,16 +8700,16 @@
       <c r="G21" s="39" t="s">
         <v>82</v>
       </c>
-      <c r="H21" s="127"/>
-      <c r="I21" s="125"/>
-      <c r="J21" s="128"/>
+      <c r="H21" s="129"/>
+      <c r="I21" s="127"/>
+      <c r="J21" s="131"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="124">
+      <c r="A22" s="130">
         <v>6</v>
       </c>
-      <c r="B22" s="125"/>
-      <c r="C22" s="126"/>
+      <c r="B22" s="127"/>
+      <c r="C22" s="128"/>
       <c r="D22" s="40" t="s">
         <v>80</v>
       </c>
@@ -8756,21 +8720,21 @@
       <c r="G22" s="39" t="s">
         <v>80</v>
       </c>
-      <c r="H22" s="127"/>
-      <c r="I22" s="125"/>
-      <c r="J22" s="128"/>
+      <c r="H22" s="129"/>
+      <c r="I22" s="127"/>
+      <c r="J22" s="131"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A23" s="119"/>
-      <c r="B23" s="120"/>
-      <c r="C23" s="121"/>
+      <c r="A23" s="157"/>
+      <c r="B23" s="158"/>
+      <c r="C23" s="159"/>
       <c r="D23" s="38"/>
       <c r="E23" s="38"/>
       <c r="F23" s="37"/>
       <c r="G23" s="37"/>
-      <c r="H23" s="122"/>
-      <c r="I23" s="120"/>
-      <c r="J23" s="123"/>
+      <c r="H23" s="160"/>
+      <c r="I23" s="158"/>
+      <c r="J23" s="161"/>
     </row>
     <row r="24" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="25" spans="1:10" ht="12.75" customHeight="1"/>
@@ -9751,6 +9715,21 @@
     <row r="1000" s="36" customFormat="1" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="31">
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="H19:J19"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="H23:J23"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="H20:J20"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="H21:J21"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="A14:J14"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="H16:J16"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="H18:J18"/>
     <mergeCell ref="A15:C15"/>
     <mergeCell ref="D15:H15"/>
     <mergeCell ref="A17:C17"/>
@@ -9767,21 +9746,6 @@
     <mergeCell ref="D2:E4"/>
     <mergeCell ref="F2:G4"/>
     <mergeCell ref="H2:H4"/>
-    <mergeCell ref="A14:J14"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="H16:J16"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="H19:J19"/>
-    <mergeCell ref="A23:C23"/>
-    <mergeCell ref="H23:J23"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="H20:J20"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="H21:J21"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="H22:J22"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -9805,342 +9769,340 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="180" t="s">
+      <c r="A1" s="172" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="91"/>
-      <c r="C1" s="92"/>
-      <c r="D1" s="97" t="s">
+      <c r="B1" s="63"/>
+      <c r="C1" s="64"/>
+      <c r="D1" s="71" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="87"/>
-      <c r="F1" s="97" t="s">
+      <c r="E1" s="72"/>
+      <c r="F1" s="71" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="87"/>
+      <c r="G1" s="72"/>
       <c r="H1" s="35" t="s">
         <v>6</v>
       </c>
       <c r="I1" s="34" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="181" t="s">
+      <c r="J1" s="46" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="93"/>
-      <c r="B2" s="94"/>
-      <c r="C2" s="69"/>
-      <c r="D2" s="66" t="s">
+      <c r="A2" s="65"/>
+      <c r="B2" s="66"/>
+      <c r="C2" s="67"/>
+      <c r="D2" s="73" t="s">
         <v>108</v>
       </c>
-      <c r="E2" s="67"/>
-      <c r="F2" s="66" t="s">
+      <c r="E2" s="74"/>
+      <c r="F2" s="73" t="s">
         <v>106</v>
       </c>
-      <c r="G2" s="67"/>
-      <c r="H2" s="72">
+      <c r="G2" s="74"/>
+      <c r="H2" s="77">
         <v>45805</v>
       </c>
-      <c r="I2" s="81" t="s">
+      <c r="I2" s="90" t="s">
         <v>105</v>
       </c>
-      <c r="J2" s="82"/>
+      <c r="J2" s="91"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="93"/>
-      <c r="B3" s="94"/>
-      <c r="C3" s="69"/>
-      <c r="D3" s="68"/>
-      <c r="E3" s="69"/>
-      <c r="F3" s="68"/>
-      <c r="G3" s="69"/>
-      <c r="H3" s="73"/>
-      <c r="I3" s="73"/>
-      <c r="J3" s="83"/>
+      <c r="A3" s="65"/>
+      <c r="B3" s="66"/>
+      <c r="C3" s="67"/>
+      <c r="D3" s="75"/>
+      <c r="E3" s="67"/>
+      <c r="F3" s="75"/>
+      <c r="G3" s="67"/>
+      <c r="H3" s="78"/>
+      <c r="I3" s="78"/>
+      <c r="J3" s="92"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="93"/>
-      <c r="B4" s="94"/>
-      <c r="C4" s="69"/>
-      <c r="D4" s="68"/>
-      <c r="E4" s="69"/>
-      <c r="F4" s="68"/>
-      <c r="G4" s="69"/>
-      <c r="H4" s="73"/>
-      <c r="I4" s="73"/>
-      <c r="J4" s="83"/>
+      <c r="A4" s="65"/>
+      <c r="B4" s="66"/>
+      <c r="C4" s="67"/>
+      <c r="D4" s="75"/>
+      <c r="E4" s="67"/>
+      <c r="F4" s="75"/>
+      <c r="G4" s="67"/>
+      <c r="H4" s="78"/>
+      <c r="I4" s="78"/>
+      <c r="J4" s="92"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="182" t="s">
+      <c r="A5" s="166" t="s">
         <v>22</v>
       </c>
-      <c r="B5" s="86"/>
-      <c r="C5" s="87"/>
-      <c r="D5" s="183" t="s">
+      <c r="B5" s="95"/>
+      <c r="C5" s="72"/>
+      <c r="D5" s="167" t="s">
         <v>109</v>
       </c>
-      <c r="E5" s="86"/>
-      <c r="F5" s="86"/>
-      <c r="G5" s="86"/>
-      <c r="H5" s="86"/>
-      <c r="I5" s="86"/>
-      <c r="J5" s="89"/>
+      <c r="E5" s="95"/>
+      <c r="F5" s="95"/>
+      <c r="G5" s="95"/>
+      <c r="H5" s="95"/>
+      <c r="I5" s="95"/>
+      <c r="J5" s="97"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="184" t="s">
+      <c r="A6" s="164" t="s">
         <v>23</v>
       </c>
-      <c r="B6" s="64"/>
-      <c r="C6" s="64"/>
-      <c r="D6" s="64"/>
-      <c r="E6" s="64"/>
-      <c r="F6" s="64"/>
-      <c r="G6" s="64"/>
-      <c r="H6" s="64"/>
-      <c r="I6" s="64"/>
-      <c r="J6" s="65"/>
+      <c r="B6" s="81"/>
+      <c r="C6" s="81"/>
+      <c r="D6" s="81"/>
+      <c r="E6" s="81"/>
+      <c r="F6" s="81"/>
+      <c r="G6" s="81"/>
+      <c r="H6" s="81"/>
+      <c r="I6" s="81"/>
+      <c r="J6" s="84"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="185" t="e" vm="1">
-        <v>#VALUE!</v>
-      </c>
-      <c r="B7" s="186"/>
-      <c r="C7" s="186"/>
-      <c r="D7" s="186"/>
-      <c r="E7" s="186"/>
-      <c r="F7" s="186"/>
-      <c r="G7" s="186"/>
-      <c r="H7" s="186"/>
-      <c r="I7" s="186"/>
-      <c r="J7" s="187"/>
+      <c r="A7" s="168"/>
+      <c r="B7" s="169"/>
+      <c r="C7" s="169"/>
+      <c r="D7" s="169"/>
+      <c r="E7" s="169"/>
+      <c r="F7" s="169"/>
+      <c r="G7" s="169"/>
+      <c r="H7" s="169"/>
+      <c r="I7" s="169"/>
+      <c r="J7" s="170"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="93"/>
-      <c r="B8" s="94"/>
-      <c r="C8" s="94"/>
-      <c r="D8" s="94"/>
-      <c r="E8" s="94"/>
-      <c r="F8" s="94"/>
-      <c r="G8" s="94"/>
-      <c r="H8" s="94"/>
-      <c r="I8" s="94"/>
-      <c r="J8" s="188"/>
+      <c r="A8" s="65"/>
+      <c r="B8" s="66"/>
+      <c r="C8" s="66"/>
+      <c r="D8" s="66"/>
+      <c r="E8" s="66"/>
+      <c r="F8" s="66"/>
+      <c r="G8" s="66"/>
+      <c r="H8" s="66"/>
+      <c r="I8" s="66"/>
+      <c r="J8" s="171"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="93"/>
-      <c r="B9" s="94"/>
-      <c r="C9" s="94"/>
-      <c r="D9" s="94"/>
-      <c r="E9" s="94"/>
-      <c r="F9" s="94"/>
-      <c r="G9" s="94"/>
-      <c r="H9" s="94"/>
-      <c r="I9" s="94"/>
-      <c r="J9" s="188"/>
+      <c r="A9" s="65"/>
+      <c r="B9" s="66"/>
+      <c r="C9" s="66"/>
+      <c r="D9" s="66"/>
+      <c r="E9" s="66"/>
+      <c r="F9" s="66"/>
+      <c r="G9" s="66"/>
+      <c r="H9" s="66"/>
+      <c r="I9" s="66"/>
+      <c r="J9" s="171"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="93"/>
-      <c r="B10" s="94"/>
-      <c r="C10" s="94"/>
-      <c r="D10" s="94"/>
-      <c r="E10" s="94"/>
-      <c r="F10" s="94"/>
-      <c r="G10" s="94"/>
-      <c r="H10" s="94"/>
-      <c r="I10" s="94"/>
-      <c r="J10" s="188"/>
+      <c r="A10" s="65"/>
+      <c r="B10" s="66"/>
+      <c r="C10" s="66"/>
+      <c r="D10" s="66"/>
+      <c r="E10" s="66"/>
+      <c r="F10" s="66"/>
+      <c r="G10" s="66"/>
+      <c r="H10" s="66"/>
+      <c r="I10" s="66"/>
+      <c r="J10" s="171"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="93"/>
-      <c r="B11" s="94"/>
-      <c r="C11" s="94"/>
-      <c r="D11" s="94"/>
-      <c r="E11" s="94"/>
-      <c r="F11" s="94"/>
-      <c r="G11" s="94"/>
-      <c r="H11" s="94"/>
-      <c r="I11" s="94"/>
-      <c r="J11" s="188"/>
+      <c r="A11" s="65"/>
+      <c r="B11" s="66"/>
+      <c r="C11" s="66"/>
+      <c r="D11" s="66"/>
+      <c r="E11" s="66"/>
+      <c r="F11" s="66"/>
+      <c r="G11" s="66"/>
+      <c r="H11" s="66"/>
+      <c r="I11" s="66"/>
+      <c r="J11" s="171"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="93"/>
-      <c r="B12" s="94"/>
-      <c r="C12" s="94"/>
-      <c r="D12" s="94"/>
-      <c r="E12" s="94"/>
-      <c r="F12" s="94"/>
-      <c r="G12" s="94"/>
-      <c r="H12" s="94"/>
-      <c r="I12" s="94"/>
-      <c r="J12" s="188"/>
+      <c r="A12" s="65"/>
+      <c r="B12" s="66"/>
+      <c r="C12" s="66"/>
+      <c r="D12" s="66"/>
+      <c r="E12" s="66"/>
+      <c r="F12" s="66"/>
+      <c r="G12" s="66"/>
+      <c r="H12" s="66"/>
+      <c r="I12" s="66"/>
+      <c r="J12" s="171"/>
     </row>
     <row r="13" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A13" s="93"/>
-      <c r="B13" s="94"/>
-      <c r="C13" s="94"/>
-      <c r="D13" s="94"/>
-      <c r="E13" s="94"/>
-      <c r="F13" s="94"/>
-      <c r="G13" s="94"/>
-      <c r="H13" s="94"/>
-      <c r="I13" s="94"/>
-      <c r="J13" s="188"/>
+      <c r="A13" s="65"/>
+      <c r="B13" s="66"/>
+      <c r="C13" s="66"/>
+      <c r="D13" s="66"/>
+      <c r="E13" s="66"/>
+      <c r="F13" s="66"/>
+      <c r="G13" s="66"/>
+      <c r="H13" s="66"/>
+      <c r="I13" s="66"/>
+      <c r="J13" s="171"/>
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A14" s="184" t="s">
+      <c r="A14" s="164" t="s">
         <v>24</v>
       </c>
-      <c r="B14" s="64"/>
-      <c r="C14" s="64"/>
-      <c r="D14" s="64"/>
-      <c r="E14" s="64"/>
-      <c r="F14" s="64"/>
-      <c r="G14" s="64"/>
-      <c r="H14" s="64"/>
-      <c r="I14" s="64"/>
-      <c r="J14" s="65"/>
+      <c r="B14" s="81"/>
+      <c r="C14" s="81"/>
+      <c r="D14" s="81"/>
+      <c r="E14" s="81"/>
+      <c r="F14" s="81"/>
+      <c r="G14" s="81"/>
+      <c r="H14" s="81"/>
+      <c r="I14" s="81"/>
+      <c r="J14" s="84"/>
     </row>
     <row r="15" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A15" s="184" t="s">
+      <c r="A15" s="164" t="s">
         <v>25</v>
       </c>
-      <c r="B15" s="64"/>
-      <c r="C15" s="59"/>
-      <c r="D15" s="63" t="s">
+      <c r="B15" s="81"/>
+      <c r="C15" s="82"/>
+      <c r="D15" s="83" t="s">
         <v>110</v>
       </c>
-      <c r="E15" s="64"/>
-      <c r="F15" s="64"/>
-      <c r="G15" s="64"/>
-      <c r="H15" s="59"/>
-      <c r="I15" s="189" t="s">
+      <c r="E15" s="81"/>
+      <c r="F15" s="81"/>
+      <c r="G15" s="81"/>
+      <c r="H15" s="82"/>
+      <c r="I15" s="47" t="s">
         <v>26</v>
       </c>
-      <c r="J15" s="190" t="s">
+      <c r="J15" s="48" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A16" s="184" t="s">
+      <c r="A16" s="164" t="s">
         <v>27</v>
       </c>
-      <c r="B16" s="64"/>
-      <c r="C16" s="59"/>
-      <c r="D16" s="189" t="s">
+      <c r="B16" s="81"/>
+      <c r="C16" s="82"/>
+      <c r="D16" s="47" t="s">
         <v>28</v>
       </c>
-      <c r="E16" s="189" t="s">
+      <c r="E16" s="47" t="s">
         <v>29</v>
       </c>
-      <c r="F16" s="189" t="s">
+      <c r="F16" s="47" t="s">
         <v>30</v>
       </c>
-      <c r="G16" s="189" t="s">
+      <c r="G16" s="47" t="s">
         <v>31</v>
       </c>
-      <c r="H16" s="191" t="s">
+      <c r="H16" s="165" t="s">
         <v>18</v>
       </c>
-      <c r="I16" s="64"/>
-      <c r="J16" s="65"/>
+      <c r="I16" s="81"/>
+      <c r="J16" s="84"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="192">
+      <c r="A17" s="162">
         <v>1</v>
       </c>
-      <c r="B17" s="64"/>
-      <c r="C17" s="59"/>
-      <c r="D17" s="193" t="s">
+      <c r="B17" s="81"/>
+      <c r="C17" s="82"/>
+      <c r="D17" s="49" t="s">
         <v>83</v>
       </c>
-      <c r="E17" s="193" t="s">
+      <c r="E17" s="49" t="s">
         <v>84</v>
       </c>
-      <c r="F17" s="194" t="s">
+      <c r="F17" s="50" t="s">
         <v>83</v>
       </c>
-      <c r="G17" s="194" t="s">
+      <c r="G17" s="50" t="s">
         <v>112</v>
       </c>
-      <c r="H17" s="63" t="s">
+      <c r="H17" s="83" t="s">
         <v>113</v>
       </c>
-      <c r="I17" s="64"/>
-      <c r="J17" s="65"/>
+      <c r="I17" s="81"/>
+      <c r="J17" s="84"/>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A18" s="192"/>
-      <c r="B18" s="64"/>
-      <c r="C18" s="59"/>
-      <c r="D18" s="193"/>
-      <c r="E18" s="193"/>
-      <c r="F18" s="194"/>
-      <c r="G18" s="194"/>
-      <c r="H18" s="63"/>
-      <c r="I18" s="64"/>
-      <c r="J18" s="65"/>
+      <c r="A18" s="162"/>
+      <c r="B18" s="81"/>
+      <c r="C18" s="82"/>
+      <c r="D18" s="49"/>
+      <c r="E18" s="49"/>
+      <c r="F18" s="50"/>
+      <c r="G18" s="50"/>
+      <c r="H18" s="83"/>
+      <c r="I18" s="81"/>
+      <c r="J18" s="84"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="192"/>
-      <c r="B19" s="64"/>
-      <c r="C19" s="59"/>
-      <c r="D19" s="193"/>
-      <c r="E19" s="193"/>
-      <c r="F19" s="194"/>
-      <c r="G19" s="194"/>
-      <c r="H19" s="63"/>
-      <c r="I19" s="64"/>
-      <c r="J19" s="65"/>
+      <c r="A19" s="162"/>
+      <c r="B19" s="81"/>
+      <c r="C19" s="82"/>
+      <c r="D19" s="49"/>
+      <c r="E19" s="49"/>
+      <c r="F19" s="50"/>
+      <c r="G19" s="50"/>
+      <c r="H19" s="83"/>
+      <c r="I19" s="81"/>
+      <c r="J19" s="84"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="192"/>
-      <c r="B20" s="64"/>
-      <c r="C20" s="59"/>
-      <c r="D20" s="193"/>
-      <c r="E20" s="193"/>
-      <c r="F20" s="194"/>
-      <c r="G20" s="194"/>
-      <c r="H20" s="63"/>
-      <c r="I20" s="64"/>
-      <c r="J20" s="65"/>
+      <c r="A20" s="162"/>
+      <c r="B20" s="81"/>
+      <c r="C20" s="82"/>
+      <c r="D20" s="49"/>
+      <c r="E20" s="49"/>
+      <c r="F20" s="50"/>
+      <c r="G20" s="50"/>
+      <c r="H20" s="83"/>
+      <c r="I20" s="81"/>
+      <c r="J20" s="84"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="192"/>
-      <c r="B21" s="64"/>
-      <c r="C21" s="59"/>
-      <c r="D21" s="193"/>
-      <c r="E21" s="193"/>
-      <c r="F21" s="194"/>
-      <c r="G21" s="194"/>
-      <c r="H21" s="63"/>
-      <c r="I21" s="64"/>
-      <c r="J21" s="65"/>
+      <c r="A21" s="162"/>
+      <c r="B21" s="81"/>
+      <c r="C21" s="82"/>
+      <c r="D21" s="49"/>
+      <c r="E21" s="49"/>
+      <c r="F21" s="50"/>
+      <c r="G21" s="50"/>
+      <c r="H21" s="83"/>
+      <c r="I21" s="81"/>
+      <c r="J21" s="84"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="192"/>
-      <c r="B22" s="64"/>
-      <c r="C22" s="59"/>
-      <c r="D22" s="193"/>
-      <c r="E22" s="193"/>
-      <c r="F22" s="194"/>
-      <c r="G22" s="194"/>
-      <c r="H22" s="63"/>
-      <c r="I22" s="64"/>
-      <c r="J22" s="65"/>
+      <c r="A22" s="162"/>
+      <c r="B22" s="81"/>
+      <c r="C22" s="82"/>
+      <c r="D22" s="49"/>
+      <c r="E22" s="49"/>
+      <c r="F22" s="50"/>
+      <c r="G22" s="50"/>
+      <c r="H22" s="83"/>
+      <c r="I22" s="81"/>
+      <c r="J22" s="84"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A23" s="195"/>
-      <c r="B23" s="77"/>
-      <c r="C23" s="78"/>
-      <c r="D23" s="196"/>
-      <c r="E23" s="196"/>
-      <c r="F23" s="197"/>
-      <c r="G23" s="197"/>
-      <c r="H23" s="79"/>
-      <c r="I23" s="77"/>
-      <c r="J23" s="80"/>
+      <c r="A23" s="163"/>
+      <c r="B23" s="86"/>
+      <c r="C23" s="87"/>
+      <c r="D23" s="51"/>
+      <c r="E23" s="51"/>
+      <c r="F23" s="52"/>
+      <c r="G23" s="52"/>
+      <c r="H23" s="88"/>
+      <c r="I23" s="86"/>
+      <c r="J23" s="89"/>
     </row>
     <row r="24" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="25" spans="1:10" ht="12.75" customHeight="1"/>
@@ -11121,23 +11083,6 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="31">
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="H21:J21"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="H22:J22"/>
-    <mergeCell ref="A23:C23"/>
-    <mergeCell ref="H23:J23"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="H19:J19"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="H20:J20"/>
-    <mergeCell ref="A14:J14"/>
-    <mergeCell ref="A15:C15"/>
-    <mergeCell ref="D15:H15"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="H16:J16"/>
     <mergeCell ref="A17:C17"/>
     <mergeCell ref="H17:J17"/>
     <mergeCell ref="I2:I4"/>
@@ -11152,6 +11097,23 @@
     <mergeCell ref="D2:E4"/>
     <mergeCell ref="F2:G4"/>
     <mergeCell ref="H2:H4"/>
+    <mergeCell ref="A14:J14"/>
+    <mergeCell ref="A15:C15"/>
+    <mergeCell ref="D15:H15"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="H16:J16"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="H18:J18"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="H19:J19"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="H20:J20"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="H21:J21"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="H23:J23"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -11175,340 +11137,340 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="180" t="s">
+      <c r="A1" s="172" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="91"/>
-      <c r="C1" s="92"/>
-      <c r="D1" s="97" t="s">
+      <c r="B1" s="63"/>
+      <c r="C1" s="64"/>
+      <c r="D1" s="71" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="87"/>
-      <c r="F1" s="97" t="s">
+      <c r="E1" s="72"/>
+      <c r="F1" s="71" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="87"/>
+      <c r="G1" s="72"/>
       <c r="H1" s="35" t="s">
         <v>6</v>
       </c>
       <c r="I1" s="34" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="181" t="s">
+      <c r="J1" s="46" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="93"/>
-      <c r="B2" s="94"/>
-      <c r="C2" s="69"/>
-      <c r="D2" s="66" t="s">
+      <c r="A2" s="65"/>
+      <c r="B2" s="66"/>
+      <c r="C2" s="67"/>
+      <c r="D2" s="73" t="s">
         <v>107</v>
       </c>
-      <c r="E2" s="67"/>
-      <c r="F2" s="66" t="s">
+      <c r="E2" s="74"/>
+      <c r="F2" s="73" t="s">
         <v>106</v>
       </c>
-      <c r="G2" s="67"/>
-      <c r="H2" s="72">
+      <c r="G2" s="74"/>
+      <c r="H2" s="77">
         <v>45805</v>
       </c>
-      <c r="I2" s="81" t="s">
+      <c r="I2" s="90" t="s">
         <v>105</v>
       </c>
-      <c r="J2" s="82"/>
+      <c r="J2" s="91"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="93"/>
-      <c r="B3" s="94"/>
-      <c r="C3" s="69"/>
-      <c r="D3" s="68"/>
-      <c r="E3" s="69"/>
-      <c r="F3" s="68"/>
-      <c r="G3" s="69"/>
-      <c r="H3" s="73"/>
-      <c r="I3" s="73"/>
-      <c r="J3" s="83"/>
+      <c r="A3" s="65"/>
+      <c r="B3" s="66"/>
+      <c r="C3" s="67"/>
+      <c r="D3" s="75"/>
+      <c r="E3" s="67"/>
+      <c r="F3" s="75"/>
+      <c r="G3" s="67"/>
+      <c r="H3" s="78"/>
+      <c r="I3" s="78"/>
+      <c r="J3" s="92"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="93"/>
-      <c r="B4" s="94"/>
-      <c r="C4" s="69"/>
-      <c r="D4" s="68"/>
-      <c r="E4" s="69"/>
-      <c r="F4" s="68"/>
-      <c r="G4" s="69"/>
-      <c r="H4" s="73"/>
-      <c r="I4" s="73"/>
-      <c r="J4" s="83"/>
+      <c r="A4" s="65"/>
+      <c r="B4" s="66"/>
+      <c r="C4" s="67"/>
+      <c r="D4" s="75"/>
+      <c r="E4" s="67"/>
+      <c r="F4" s="75"/>
+      <c r="G4" s="67"/>
+      <c r="H4" s="78"/>
+      <c r="I4" s="78"/>
+      <c r="J4" s="92"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="182" t="s">
+      <c r="A5" s="166" t="s">
         <v>22</v>
       </c>
-      <c r="B5" s="86"/>
-      <c r="C5" s="87"/>
-      <c r="D5" s="183" t="s">
+      <c r="B5" s="95"/>
+      <c r="C5" s="72"/>
+      <c r="D5" s="167" t="s">
         <v>114</v>
       </c>
-      <c r="E5" s="86"/>
-      <c r="F5" s="86"/>
-      <c r="G5" s="86"/>
-      <c r="H5" s="86"/>
-      <c r="I5" s="86"/>
-      <c r="J5" s="89"/>
+      <c r="E5" s="95"/>
+      <c r="F5" s="95"/>
+      <c r="G5" s="95"/>
+      <c r="H5" s="95"/>
+      <c r="I5" s="95"/>
+      <c r="J5" s="97"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="184" t="s">
+      <c r="A6" s="164" t="s">
         <v>23</v>
       </c>
-      <c r="B6" s="64"/>
-      <c r="C6" s="64"/>
-      <c r="D6" s="64"/>
-      <c r="E6" s="64"/>
-      <c r="F6" s="64"/>
-      <c r="G6" s="64"/>
-      <c r="H6" s="64"/>
-      <c r="I6" s="64"/>
-      <c r="J6" s="65"/>
+      <c r="B6" s="81"/>
+      <c r="C6" s="81"/>
+      <c r="D6" s="81"/>
+      <c r="E6" s="81"/>
+      <c r="F6" s="81"/>
+      <c r="G6" s="81"/>
+      <c r="H6" s="81"/>
+      <c r="I6" s="81"/>
+      <c r="J6" s="84"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="185"/>
-      <c r="B7" s="186"/>
-      <c r="C7" s="186"/>
-      <c r="D7" s="186"/>
-      <c r="E7" s="186"/>
-      <c r="F7" s="186"/>
-      <c r="G7" s="186"/>
-      <c r="H7" s="186"/>
-      <c r="I7" s="186"/>
-      <c r="J7" s="187"/>
+      <c r="A7" s="168"/>
+      <c r="B7" s="169"/>
+      <c r="C7" s="169"/>
+      <c r="D7" s="169"/>
+      <c r="E7" s="169"/>
+      <c r="F7" s="169"/>
+      <c r="G7" s="169"/>
+      <c r="H7" s="169"/>
+      <c r="I7" s="169"/>
+      <c r="J7" s="170"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="93"/>
-      <c r="B8" s="94"/>
-      <c r="C8" s="94"/>
-      <c r="D8" s="94"/>
-      <c r="E8" s="94"/>
-      <c r="F8" s="94"/>
-      <c r="G8" s="94"/>
-      <c r="H8" s="94"/>
-      <c r="I8" s="94"/>
-      <c r="J8" s="188"/>
+      <c r="A8" s="65"/>
+      <c r="B8" s="66"/>
+      <c r="C8" s="66"/>
+      <c r="D8" s="66"/>
+      <c r="E8" s="66"/>
+      <c r="F8" s="66"/>
+      <c r="G8" s="66"/>
+      <c r="H8" s="66"/>
+      <c r="I8" s="66"/>
+      <c r="J8" s="171"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="93"/>
-      <c r="B9" s="94"/>
-      <c r="C9" s="94"/>
-      <c r="D9" s="94"/>
-      <c r="E9" s="94"/>
-      <c r="F9" s="94"/>
-      <c r="G9" s="94"/>
-      <c r="H9" s="94"/>
-      <c r="I9" s="94"/>
-      <c r="J9" s="188"/>
+      <c r="A9" s="65"/>
+      <c r="B9" s="66"/>
+      <c r="C9" s="66"/>
+      <c r="D9" s="66"/>
+      <c r="E9" s="66"/>
+      <c r="F9" s="66"/>
+      <c r="G9" s="66"/>
+      <c r="H9" s="66"/>
+      <c r="I9" s="66"/>
+      <c r="J9" s="171"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="93"/>
-      <c r="B10" s="94"/>
-      <c r="C10" s="94"/>
-      <c r="D10" s="94"/>
-      <c r="E10" s="94"/>
-      <c r="F10" s="94"/>
-      <c r="G10" s="94"/>
-      <c r="H10" s="94"/>
-      <c r="I10" s="94"/>
-      <c r="J10" s="188"/>
+      <c r="A10" s="65"/>
+      <c r="B10" s="66"/>
+      <c r="C10" s="66"/>
+      <c r="D10" s="66"/>
+      <c r="E10" s="66"/>
+      <c r="F10" s="66"/>
+      <c r="G10" s="66"/>
+      <c r="H10" s="66"/>
+      <c r="I10" s="66"/>
+      <c r="J10" s="171"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="93"/>
-      <c r="B11" s="94"/>
-      <c r="C11" s="94"/>
-      <c r="D11" s="94"/>
-      <c r="E11" s="94"/>
-      <c r="F11" s="94"/>
-      <c r="G11" s="94"/>
-      <c r="H11" s="94"/>
-      <c r="I11" s="94"/>
-      <c r="J11" s="188"/>
+      <c r="A11" s="65"/>
+      <c r="B11" s="66"/>
+      <c r="C11" s="66"/>
+      <c r="D11" s="66"/>
+      <c r="E11" s="66"/>
+      <c r="F11" s="66"/>
+      <c r="G11" s="66"/>
+      <c r="H11" s="66"/>
+      <c r="I11" s="66"/>
+      <c r="J11" s="171"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="93"/>
-      <c r="B12" s="94"/>
-      <c r="C12" s="94"/>
-      <c r="D12" s="94"/>
-      <c r="E12" s="94"/>
-      <c r="F12" s="94"/>
-      <c r="G12" s="94"/>
-      <c r="H12" s="94"/>
-      <c r="I12" s="94"/>
-      <c r="J12" s="188"/>
+      <c r="A12" s="65"/>
+      <c r="B12" s="66"/>
+      <c r="C12" s="66"/>
+      <c r="D12" s="66"/>
+      <c r="E12" s="66"/>
+      <c r="F12" s="66"/>
+      <c r="G12" s="66"/>
+      <c r="H12" s="66"/>
+      <c r="I12" s="66"/>
+      <c r="J12" s="171"/>
     </row>
     <row r="13" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A13" s="93"/>
-      <c r="B13" s="94"/>
-      <c r="C13" s="94"/>
-      <c r="D13" s="94"/>
-      <c r="E13" s="94"/>
-      <c r="F13" s="94"/>
-      <c r="G13" s="94"/>
-      <c r="H13" s="94"/>
-      <c r="I13" s="94"/>
-      <c r="J13" s="188"/>
+      <c r="A13" s="65"/>
+      <c r="B13" s="66"/>
+      <c r="C13" s="66"/>
+      <c r="D13" s="66"/>
+      <c r="E13" s="66"/>
+      <c r="F13" s="66"/>
+      <c r="G13" s="66"/>
+      <c r="H13" s="66"/>
+      <c r="I13" s="66"/>
+      <c r="J13" s="171"/>
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A14" s="184" t="s">
+      <c r="A14" s="164" t="s">
         <v>24</v>
       </c>
-      <c r="B14" s="64"/>
-      <c r="C14" s="64"/>
-      <c r="D14" s="64"/>
-      <c r="E14" s="64"/>
-      <c r="F14" s="64"/>
-      <c r="G14" s="64"/>
-      <c r="H14" s="64"/>
-      <c r="I14" s="64"/>
-      <c r="J14" s="65"/>
+      <c r="B14" s="81"/>
+      <c r="C14" s="81"/>
+      <c r="D14" s="81"/>
+      <c r="E14" s="81"/>
+      <c r="F14" s="81"/>
+      <c r="G14" s="81"/>
+      <c r="H14" s="81"/>
+      <c r="I14" s="81"/>
+      <c r="J14" s="84"/>
     </row>
     <row r="15" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A15" s="184" t="s">
+      <c r="A15" s="164" t="s">
         <v>25</v>
       </c>
-      <c r="B15" s="64"/>
-      <c r="C15" s="59"/>
-      <c r="D15" s="63" t="s">
+      <c r="B15" s="81"/>
+      <c r="C15" s="82"/>
+      <c r="D15" s="83" t="s">
         <v>110</v>
       </c>
-      <c r="E15" s="64"/>
-      <c r="F15" s="64"/>
-      <c r="G15" s="64"/>
-      <c r="H15" s="59"/>
-      <c r="I15" s="189" t="s">
+      <c r="E15" s="81"/>
+      <c r="F15" s="81"/>
+      <c r="G15" s="81"/>
+      <c r="H15" s="82"/>
+      <c r="I15" s="47" t="s">
         <v>26</v>
       </c>
-      <c r="J15" s="190" t="s">
+      <c r="J15" s="48" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A16" s="184" t="s">
+      <c r="A16" s="164" t="s">
         <v>27</v>
       </c>
-      <c r="B16" s="64"/>
-      <c r="C16" s="59"/>
-      <c r="D16" s="189" t="s">
+      <c r="B16" s="81"/>
+      <c r="C16" s="82"/>
+      <c r="D16" s="47" t="s">
         <v>28</v>
       </c>
-      <c r="E16" s="189" t="s">
+      <c r="E16" s="47" t="s">
         <v>29</v>
       </c>
-      <c r="F16" s="189" t="s">
+      <c r="F16" s="47" t="s">
         <v>30</v>
       </c>
-      <c r="G16" s="189" t="s">
+      <c r="G16" s="47" t="s">
         <v>31</v>
       </c>
-      <c r="H16" s="191" t="s">
+      <c r="H16" s="165" t="s">
         <v>18</v>
       </c>
-      <c r="I16" s="64"/>
-      <c r="J16" s="65"/>
+      <c r="I16" s="81"/>
+      <c r="J16" s="84"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="192">
+      <c r="A17" s="162">
         <v>1</v>
       </c>
-      <c r="B17" s="64"/>
-      <c r="C17" s="59"/>
-      <c r="D17" s="193" t="s">
+      <c r="B17" s="81"/>
+      <c r="C17" s="82"/>
+      <c r="D17" s="49" t="s">
         <v>83</v>
       </c>
-      <c r="E17" s="193" t="s">
+      <c r="E17" s="49" t="s">
         <v>84</v>
       </c>
-      <c r="F17" s="194" t="s">
+      <c r="F17" s="50" t="s">
         <v>83</v>
       </c>
-      <c r="G17" s="194" t="s">
+      <c r="G17" s="50" t="s">
         <v>112</v>
       </c>
-      <c r="H17" s="63" t="s">
+      <c r="H17" s="83" t="s">
         <v>113</v>
       </c>
-      <c r="I17" s="64"/>
-      <c r="J17" s="65"/>
+      <c r="I17" s="81"/>
+      <c r="J17" s="84"/>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A18" s="192"/>
-      <c r="B18" s="64"/>
-      <c r="C18" s="59"/>
-      <c r="D18" s="193"/>
-      <c r="E18" s="193"/>
-      <c r="F18" s="194"/>
-      <c r="G18" s="194"/>
-      <c r="H18" s="63"/>
-      <c r="I18" s="64"/>
-      <c r="J18" s="65"/>
+      <c r="A18" s="162"/>
+      <c r="B18" s="81"/>
+      <c r="C18" s="82"/>
+      <c r="D18" s="49"/>
+      <c r="E18" s="49"/>
+      <c r="F18" s="50"/>
+      <c r="G18" s="50"/>
+      <c r="H18" s="83"/>
+      <c r="I18" s="81"/>
+      <c r="J18" s="84"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="192"/>
-      <c r="B19" s="64"/>
-      <c r="C19" s="59"/>
-      <c r="D19" s="193"/>
-      <c r="E19" s="193"/>
-      <c r="F19" s="194"/>
-      <c r="G19" s="194"/>
-      <c r="H19" s="63"/>
-      <c r="I19" s="64"/>
-      <c r="J19" s="65"/>
+      <c r="A19" s="162"/>
+      <c r="B19" s="81"/>
+      <c r="C19" s="82"/>
+      <c r="D19" s="49"/>
+      <c r="E19" s="49"/>
+      <c r="F19" s="50"/>
+      <c r="G19" s="50"/>
+      <c r="H19" s="83"/>
+      <c r="I19" s="81"/>
+      <c r="J19" s="84"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="192"/>
-      <c r="B20" s="64"/>
-      <c r="C20" s="59"/>
-      <c r="D20" s="193"/>
-      <c r="E20" s="193"/>
-      <c r="F20" s="194"/>
-      <c r="G20" s="194"/>
-      <c r="H20" s="63"/>
-      <c r="I20" s="64"/>
-      <c r="J20" s="65"/>
+      <c r="A20" s="162"/>
+      <c r="B20" s="81"/>
+      <c r="C20" s="82"/>
+      <c r="D20" s="49"/>
+      <c r="E20" s="49"/>
+      <c r="F20" s="50"/>
+      <c r="G20" s="50"/>
+      <c r="H20" s="83"/>
+      <c r="I20" s="81"/>
+      <c r="J20" s="84"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="192"/>
-      <c r="B21" s="64"/>
-      <c r="C21" s="59"/>
-      <c r="D21" s="193"/>
-      <c r="E21" s="193"/>
-      <c r="F21" s="194"/>
-      <c r="G21" s="194"/>
-      <c r="H21" s="63"/>
-      <c r="I21" s="64"/>
-      <c r="J21" s="65"/>
+      <c r="A21" s="162"/>
+      <c r="B21" s="81"/>
+      <c r="C21" s="82"/>
+      <c r="D21" s="49"/>
+      <c r="E21" s="49"/>
+      <c r="F21" s="50"/>
+      <c r="G21" s="50"/>
+      <c r="H21" s="83"/>
+      <c r="I21" s="81"/>
+      <c r="J21" s="84"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="192"/>
-      <c r="B22" s="64"/>
-      <c r="C22" s="59"/>
-      <c r="D22" s="193"/>
-      <c r="E22" s="193"/>
-      <c r="F22" s="194"/>
-      <c r="G22" s="194"/>
-      <c r="H22" s="63"/>
-      <c r="I22" s="64"/>
-      <c r="J22" s="65"/>
+      <c r="A22" s="162"/>
+      <c r="B22" s="81"/>
+      <c r="C22" s="82"/>
+      <c r="D22" s="49"/>
+      <c r="E22" s="49"/>
+      <c r="F22" s="50"/>
+      <c r="G22" s="50"/>
+      <c r="H22" s="83"/>
+      <c r="I22" s="81"/>
+      <c r="J22" s="84"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A23" s="195"/>
-      <c r="B23" s="77"/>
-      <c r="C23" s="78"/>
-      <c r="D23" s="196"/>
-      <c r="E23" s="196"/>
-      <c r="F23" s="197"/>
-      <c r="G23" s="197"/>
-      <c r="H23" s="79"/>
-      <c r="I23" s="77"/>
-      <c r="J23" s="80"/>
+      <c r="A23" s="163"/>
+      <c r="B23" s="86"/>
+      <c r="C23" s="87"/>
+      <c r="D23" s="51"/>
+      <c r="E23" s="51"/>
+      <c r="F23" s="52"/>
+      <c r="G23" s="52"/>
+      <c r="H23" s="88"/>
+      <c r="I23" s="86"/>
+      <c r="J23" s="89"/>
     </row>
     <row r="24" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="25" spans="1:10" ht="12.75" customHeight="1"/>
@@ -12489,23 +12451,6 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="31">
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="H21:J21"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="H22:J22"/>
-    <mergeCell ref="A23:C23"/>
-    <mergeCell ref="H23:J23"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="H19:J19"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="H20:J20"/>
-    <mergeCell ref="A14:J14"/>
-    <mergeCell ref="A15:C15"/>
-    <mergeCell ref="D15:H15"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="H16:J16"/>
     <mergeCell ref="A17:C17"/>
     <mergeCell ref="H17:J17"/>
     <mergeCell ref="I2:I4"/>
@@ -12520,6 +12465,23 @@
     <mergeCell ref="D2:E4"/>
     <mergeCell ref="F2:G4"/>
     <mergeCell ref="H2:H4"/>
+    <mergeCell ref="A14:J14"/>
+    <mergeCell ref="A15:C15"/>
+    <mergeCell ref="D15:H15"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="H16:J16"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="H18:J18"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="H19:J19"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="H20:J20"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="H21:J21"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="H23:J23"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -12539,182 +12501,182 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="18" customHeight="1">
-      <c r="A1" s="178" t="s">
+      <c r="A1" s="184" t="s">
         <v>32</v>
       </c>
-      <c r="B1" s="106"/>
-      <c r="C1" s="106"/>
-      <c r="D1" s="106"/>
-      <c r="E1" s="106"/>
-      <c r="F1" s="107"/>
-      <c r="G1" s="113" t="s">
+      <c r="B1" s="113"/>
+      <c r="C1" s="113"/>
+      <c r="D1" s="113"/>
+      <c r="E1" s="113"/>
+      <c r="F1" s="114"/>
+      <c r="G1" s="120" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="164"/>
-      <c r="I1" s="164"/>
-      <c r="J1" s="114"/>
-      <c r="K1" s="113" t="s">
+      <c r="H1" s="185"/>
+      <c r="I1" s="185"/>
+      <c r="J1" s="121"/>
+      <c r="K1" s="120" t="s">
         <v>5</v>
       </c>
-      <c r="L1" s="164"/>
-      <c r="M1" s="164"/>
-      <c r="N1" s="114"/>
-      <c r="O1" s="113" t="s">
+      <c r="L1" s="185"/>
+      <c r="M1" s="185"/>
+      <c r="N1" s="121"/>
+      <c r="O1" s="120" t="s">
         <v>6</v>
       </c>
-      <c r="P1" s="114"/>
-      <c r="Q1" s="113" t="s">
+      <c r="P1" s="121"/>
+      <c r="Q1" s="120" t="s">
         <v>7</v>
       </c>
-      <c r="R1" s="114"/>
-      <c r="S1" s="113" t="s">
+      <c r="R1" s="121"/>
+      <c r="S1" s="120" t="s">
         <v>8</v>
       </c>
-      <c r="T1" s="166"/>
+      <c r="T1" s="186"/>
     </row>
     <row r="2" spans="1:26" ht="18" customHeight="1">
-      <c r="A2" s="108"/>
-      <c r="B2" s="50"/>
-      <c r="C2" s="50"/>
-      <c r="D2" s="50"/>
-      <c r="E2" s="50"/>
-      <c r="F2" s="109"/>
-      <c r="G2" s="115"/>
-      <c r="H2" s="174"/>
-      <c r="I2" s="174"/>
-      <c r="J2" s="116"/>
-      <c r="K2" s="115"/>
-      <c r="L2" s="174"/>
-      <c r="M2" s="174"/>
-      <c r="N2" s="116"/>
-      <c r="O2" s="115"/>
-      <c r="P2" s="116"/>
-      <c r="Q2" s="115"/>
-      <c r="R2" s="116"/>
-      <c r="S2" s="115"/>
-      <c r="T2" s="175"/>
+      <c r="A2" s="115"/>
+      <c r="B2" s="57"/>
+      <c r="C2" s="57"/>
+      <c r="D2" s="57"/>
+      <c r="E2" s="57"/>
+      <c r="F2" s="116"/>
+      <c r="G2" s="122"/>
+      <c r="H2" s="180"/>
+      <c r="I2" s="180"/>
+      <c r="J2" s="123"/>
+      <c r="K2" s="122"/>
+      <c r="L2" s="180"/>
+      <c r="M2" s="180"/>
+      <c r="N2" s="123"/>
+      <c r="O2" s="122"/>
+      <c r="P2" s="123"/>
+      <c r="Q2" s="122"/>
+      <c r="R2" s="123"/>
+      <c r="S2" s="122"/>
+      <c r="T2" s="181"/>
     </row>
     <row r="3" spans="1:26" ht="18" customHeight="1">
-      <c r="A3" s="108"/>
-      <c r="B3" s="50"/>
-      <c r="C3" s="50"/>
-      <c r="D3" s="50"/>
-      <c r="E3" s="50"/>
-      <c r="F3" s="109"/>
-      <c r="G3" s="117"/>
-      <c r="H3" s="50"/>
-      <c r="I3" s="50"/>
-      <c r="J3" s="109"/>
-      <c r="K3" s="117"/>
-      <c r="L3" s="50"/>
-      <c r="M3" s="50"/>
-      <c r="N3" s="109"/>
-      <c r="O3" s="117"/>
-      <c r="P3" s="109"/>
-      <c r="Q3" s="117"/>
-      <c r="R3" s="109"/>
-      <c r="S3" s="117"/>
-      <c r="T3" s="176"/>
+      <c r="A3" s="115"/>
+      <c r="B3" s="57"/>
+      <c r="C3" s="57"/>
+      <c r="D3" s="57"/>
+      <c r="E3" s="57"/>
+      <c r="F3" s="116"/>
+      <c r="G3" s="124"/>
+      <c r="H3" s="57"/>
+      <c r="I3" s="57"/>
+      <c r="J3" s="116"/>
+      <c r="K3" s="124"/>
+      <c r="L3" s="57"/>
+      <c r="M3" s="57"/>
+      <c r="N3" s="116"/>
+      <c r="O3" s="124"/>
+      <c r="P3" s="116"/>
+      <c r="Q3" s="124"/>
+      <c r="R3" s="116"/>
+      <c r="S3" s="124"/>
+      <c r="T3" s="182"/>
     </row>
     <row r="4" spans="1:26" ht="18" customHeight="1">
-      <c r="A4" s="110"/>
-      <c r="B4" s="111"/>
-      <c r="C4" s="111"/>
-      <c r="D4" s="111"/>
-      <c r="E4" s="111"/>
-      <c r="F4" s="112"/>
-      <c r="G4" s="118"/>
-      <c r="H4" s="111"/>
-      <c r="I4" s="111"/>
-      <c r="J4" s="112"/>
-      <c r="K4" s="118"/>
-      <c r="L4" s="111"/>
-      <c r="M4" s="111"/>
-      <c r="N4" s="112"/>
-      <c r="O4" s="118"/>
-      <c r="P4" s="112"/>
-      <c r="Q4" s="118"/>
-      <c r="R4" s="112"/>
-      <c r="S4" s="118"/>
-      <c r="T4" s="177"/>
+      <c r="A4" s="117"/>
+      <c r="B4" s="118"/>
+      <c r="C4" s="118"/>
+      <c r="D4" s="118"/>
+      <c r="E4" s="118"/>
+      <c r="F4" s="119"/>
+      <c r="G4" s="125"/>
+      <c r="H4" s="118"/>
+      <c r="I4" s="118"/>
+      <c r="J4" s="119"/>
+      <c r="K4" s="125"/>
+      <c r="L4" s="118"/>
+      <c r="M4" s="118"/>
+      <c r="N4" s="119"/>
+      <c r="O4" s="125"/>
+      <c r="P4" s="119"/>
+      <c r="Q4" s="125"/>
+      <c r="R4" s="119"/>
+      <c r="S4" s="125"/>
+      <c r="T4" s="183"/>
     </row>
     <row r="5" spans="1:26" ht="18" customHeight="1">
-      <c r="A5" s="163" t="s">
+      <c r="A5" s="187" t="s">
         <v>33</v>
       </c>
-      <c r="B5" s="164"/>
-      <c r="C5" s="164"/>
-      <c r="D5" s="164"/>
-      <c r="E5" s="164"/>
-      <c r="F5" s="114"/>
-      <c r="G5" s="165" t="s">
+      <c r="B5" s="185"/>
+      <c r="C5" s="185"/>
+      <c r="D5" s="185"/>
+      <c r="E5" s="185"/>
+      <c r="F5" s="121"/>
+      <c r="G5" s="188" t="s">
         <v>34</v>
       </c>
-      <c r="H5" s="164"/>
-      <c r="I5" s="164"/>
-      <c r="J5" s="164"/>
-      <c r="K5" s="164"/>
-      <c r="L5" s="164"/>
-      <c r="M5" s="164"/>
-      <c r="N5" s="164"/>
-      <c r="O5" s="164"/>
-      <c r="P5" s="164"/>
-      <c r="Q5" s="164"/>
-      <c r="R5" s="164"/>
-      <c r="S5" s="164"/>
-      <c r="T5" s="166"/>
+      <c r="H5" s="185"/>
+      <c r="I5" s="185"/>
+      <c r="J5" s="185"/>
+      <c r="K5" s="185"/>
+      <c r="L5" s="185"/>
+      <c r="M5" s="185"/>
+      <c r="N5" s="185"/>
+      <c r="O5" s="185"/>
+      <c r="P5" s="185"/>
+      <c r="Q5" s="185"/>
+      <c r="R5" s="185"/>
+      <c r="S5" s="185"/>
+      <c r="T5" s="186"/>
     </row>
     <row r="6" spans="1:26" ht="18" customHeight="1">
-      <c r="A6" s="167" t="s">
+      <c r="A6" s="189" t="s">
         <v>35</v>
       </c>
-      <c r="B6" s="47"/>
-      <c r="C6" s="47"/>
-      <c r="D6" s="47"/>
-      <c r="E6" s="47"/>
-      <c r="F6" s="48"/>
-      <c r="G6" s="168" t="s">
+      <c r="B6" s="54"/>
+      <c r="C6" s="54"/>
+      <c r="D6" s="54"/>
+      <c r="E6" s="54"/>
+      <c r="F6" s="55"/>
+      <c r="G6" s="190" t="s">
         <v>19</v>
       </c>
-      <c r="H6" s="47"/>
-      <c r="I6" s="47"/>
-      <c r="J6" s="47"/>
-      <c r="K6" s="47"/>
-      <c r="L6" s="47"/>
-      <c r="M6" s="47"/>
-      <c r="N6" s="47"/>
-      <c r="O6" s="47"/>
-      <c r="P6" s="47"/>
-      <c r="Q6" s="47"/>
-      <c r="R6" s="47"/>
-      <c r="S6" s="47"/>
-      <c r="T6" s="169"/>
+      <c r="H6" s="54"/>
+      <c r="I6" s="54"/>
+      <c r="J6" s="54"/>
+      <c r="K6" s="54"/>
+      <c r="L6" s="54"/>
+      <c r="M6" s="54"/>
+      <c r="N6" s="54"/>
+      <c r="O6" s="54"/>
+      <c r="P6" s="54"/>
+      <c r="Q6" s="54"/>
+      <c r="R6" s="54"/>
+      <c r="S6" s="54"/>
+      <c r="T6" s="191"/>
     </row>
     <row r="7" spans="1:26" ht="18" customHeight="1">
-      <c r="A7" s="167" t="s">
+      <c r="A7" s="189" t="s">
         <v>36</v>
       </c>
-      <c r="B7" s="47"/>
-      <c r="C7" s="47"/>
-      <c r="D7" s="47"/>
-      <c r="E7" s="47"/>
-      <c r="F7" s="48"/>
-      <c r="G7" s="168" t="s">
+      <c r="B7" s="54"/>
+      <c r="C7" s="54"/>
+      <c r="D7" s="54"/>
+      <c r="E7" s="54"/>
+      <c r="F7" s="55"/>
+      <c r="G7" s="190" t="s">
         <v>37</v>
       </c>
-      <c r="H7" s="47"/>
-      <c r="I7" s="47"/>
-      <c r="J7" s="47"/>
-      <c r="K7" s="47"/>
-      <c r="L7" s="47"/>
-      <c r="M7" s="47"/>
-      <c r="N7" s="47"/>
-      <c r="O7" s="47"/>
-      <c r="P7" s="47"/>
-      <c r="Q7" s="47"/>
-      <c r="R7" s="47"/>
-      <c r="S7" s="47"/>
-      <c r="T7" s="169"/>
+      <c r="H7" s="54"/>
+      <c r="I7" s="54"/>
+      <c r="J7" s="54"/>
+      <c r="K7" s="54"/>
+      <c r="L7" s="54"/>
+      <c r="M7" s="54"/>
+      <c r="N7" s="54"/>
+      <c r="O7" s="54"/>
+      <c r="P7" s="54"/>
+      <c r="Q7" s="54"/>
+      <c r="R7" s="54"/>
+      <c r="S7" s="54"/>
+      <c r="T7" s="191"/>
     </row>
     <row r="8" spans="1:26" ht="7.5" customHeight="1">
       <c r="A8" s="7"/>
@@ -12913,37 +12875,37 @@
       <c r="T14" s="9"/>
     </row>
     <row r="15" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A15" s="167" t="s">
+      <c r="A15" s="189" t="s">
         <v>44</v>
       </c>
-      <c r="B15" s="48"/>
-      <c r="C15" s="173" t="s">
+      <c r="B15" s="55"/>
+      <c r="C15" s="195" t="s">
         <v>38</v>
       </c>
-      <c r="D15" s="48"/>
-      <c r="E15" s="171" t="s">
+      <c r="D15" s="55"/>
+      <c r="E15" s="173" t="s">
         <v>45</v>
       </c>
-      <c r="F15" s="48"/>
-      <c r="G15" s="171" t="s">
+      <c r="F15" s="55"/>
+      <c r="G15" s="173" t="s">
         <v>46</v>
       </c>
-      <c r="H15" s="47"/>
-      <c r="I15" s="48"/>
-      <c r="J15" s="171" t="s">
+      <c r="H15" s="54"/>
+      <c r="I15" s="55"/>
+      <c r="J15" s="173" t="s">
         <v>47</v>
       </c>
-      <c r="K15" s="48"/>
-      <c r="L15" s="171" t="s">
+      <c r="K15" s="55"/>
+      <c r="L15" s="173" t="s">
         <v>48</v>
       </c>
-      <c r="M15" s="47"/>
-      <c r="N15" s="48"/>
-      <c r="O15" s="171" t="s">
+      <c r="M15" s="54"/>
+      <c r="N15" s="55"/>
+      <c r="O15" s="173" t="s">
         <v>49</v>
       </c>
-      <c r="P15" s="47"/>
-      <c r="Q15" s="48"/>
+      <c r="P15" s="54"/>
+      <c r="Q15" s="55"/>
       <c r="R15" s="14" t="s">
         <v>50</v>
       </c>
@@ -12955,37 +12917,37 @@
       </c>
     </row>
     <row r="16" spans="1:26" ht="48" customHeight="1">
-      <c r="A16" s="155">
+      <c r="A16" s="192">
         <v>1</v>
       </c>
-      <c r="B16" s="48"/>
-      <c r="C16" s="156" t="s">
+      <c r="B16" s="55"/>
+      <c r="C16" s="193" t="s">
         <v>53</v>
       </c>
-      <c r="D16" s="48"/>
-      <c r="E16" s="156" t="s">
+      <c r="D16" s="55"/>
+      <c r="E16" s="193" t="s">
         <v>54</v>
       </c>
-      <c r="F16" s="48"/>
-      <c r="G16" s="170" t="s">
+      <c r="F16" s="55"/>
+      <c r="G16" s="174" t="s">
         <v>55</v>
       </c>
-      <c r="H16" s="47"/>
-      <c r="I16" s="48"/>
-      <c r="J16" s="170" t="s">
+      <c r="H16" s="54"/>
+      <c r="I16" s="55"/>
+      <c r="J16" s="174" t="s">
         <v>56</v>
       </c>
-      <c r="K16" s="48"/>
-      <c r="L16" s="172" t="s">
+      <c r="K16" s="55"/>
+      <c r="L16" s="194" t="s">
         <v>65</v>
       </c>
-      <c r="M16" s="47"/>
-      <c r="N16" s="48"/>
-      <c r="O16" s="160" t="s">
+      <c r="M16" s="54"/>
+      <c r="N16" s="55"/>
+      <c r="O16" s="178" t="s">
         <v>57</v>
       </c>
-      <c r="P16" s="47"/>
-      <c r="Q16" s="48"/>
+      <c r="P16" s="54"/>
+      <c r="Q16" s="55"/>
       <c r="R16" s="27"/>
       <c r="S16" s="27"/>
       <c r="T16" s="28"/>
@@ -12997,37 +12959,37 @@
       <c r="Z16" s="29"/>
     </row>
     <row r="17" spans="1:26" ht="41.25" customHeight="1">
-      <c r="A17" s="155">
+      <c r="A17" s="192">
         <v>2</v>
       </c>
-      <c r="B17" s="48"/>
-      <c r="C17" s="156" t="s">
+      <c r="B17" s="55"/>
+      <c r="C17" s="193" t="s">
         <v>58</v>
       </c>
-      <c r="D17" s="48"/>
-      <c r="E17" s="156" t="s">
+      <c r="D17" s="55"/>
+      <c r="E17" s="193" t="s">
         <v>59</v>
       </c>
-      <c r="F17" s="48"/>
-      <c r="G17" s="170" t="s">
+      <c r="F17" s="55"/>
+      <c r="G17" s="174" t="s">
         <v>60</v>
       </c>
-      <c r="H17" s="47"/>
-      <c r="I17" s="48"/>
-      <c r="J17" s="170" t="s">
+      <c r="H17" s="54"/>
+      <c r="I17" s="55"/>
+      <c r="J17" s="174" t="s">
         <v>61</v>
       </c>
-      <c r="K17" s="48"/>
-      <c r="L17" s="160" t="s">
+      <c r="K17" s="55"/>
+      <c r="L17" s="178" t="s">
         <v>62</v>
       </c>
-      <c r="M17" s="47"/>
-      <c r="N17" s="48"/>
-      <c r="O17" s="160" t="s">
+      <c r="M17" s="54"/>
+      <c r="N17" s="55"/>
+      <c r="O17" s="178" t="s">
         <v>63</v>
       </c>
-      <c r="P17" s="47"/>
-      <c r="Q17" s="48"/>
+      <c r="P17" s="54"/>
+      <c r="Q17" s="55"/>
       <c r="R17" s="27"/>
       <c r="S17" s="27"/>
       <c r="T17" s="28"/>
@@ -13039,23 +13001,23 @@
       <c r="Z17" s="29"/>
     </row>
     <row r="18" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A18" s="155"/>
-      <c r="B18" s="48"/>
-      <c r="C18" s="156"/>
-      <c r="D18" s="48"/>
-      <c r="E18" s="156"/>
-      <c r="F18" s="48"/>
-      <c r="G18" s="170"/>
-      <c r="H18" s="47"/>
-      <c r="I18" s="48"/>
-      <c r="J18" s="170"/>
-      <c r="K18" s="48"/>
-      <c r="L18" s="160"/>
-      <c r="M18" s="47"/>
-      <c r="N18" s="48"/>
-      <c r="O18" s="160"/>
-      <c r="P18" s="47"/>
-      <c r="Q18" s="48"/>
+      <c r="A18" s="192"/>
+      <c r="B18" s="55"/>
+      <c r="C18" s="193"/>
+      <c r="D18" s="55"/>
+      <c r="E18" s="193"/>
+      <c r="F18" s="55"/>
+      <c r="G18" s="174"/>
+      <c r="H18" s="54"/>
+      <c r="I18" s="55"/>
+      <c r="J18" s="174"/>
+      <c r="K18" s="55"/>
+      <c r="L18" s="178"/>
+      <c r="M18" s="54"/>
+      <c r="N18" s="55"/>
+      <c r="O18" s="178"/>
+      <c r="P18" s="54"/>
+      <c r="Q18" s="55"/>
       <c r="R18" s="27"/>
       <c r="S18" s="27"/>
       <c r="T18" s="28"/>
@@ -13067,23 +13029,23 @@
       <c r="Z18" s="29"/>
     </row>
     <row r="19" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A19" s="155"/>
-      <c r="B19" s="48"/>
-      <c r="C19" s="156"/>
-      <c r="D19" s="48"/>
-      <c r="E19" s="156"/>
-      <c r="F19" s="48"/>
-      <c r="G19" s="170"/>
-      <c r="H19" s="47"/>
-      <c r="I19" s="48"/>
-      <c r="J19" s="170"/>
-      <c r="K19" s="48"/>
-      <c r="L19" s="160"/>
-      <c r="M19" s="47"/>
-      <c r="N19" s="48"/>
-      <c r="O19" s="160"/>
-      <c r="P19" s="47"/>
-      <c r="Q19" s="48"/>
+      <c r="A19" s="192"/>
+      <c r="B19" s="55"/>
+      <c r="C19" s="193"/>
+      <c r="D19" s="55"/>
+      <c r="E19" s="193"/>
+      <c r="F19" s="55"/>
+      <c r="G19" s="174"/>
+      <c r="H19" s="54"/>
+      <c r="I19" s="55"/>
+      <c r="J19" s="174"/>
+      <c r="K19" s="55"/>
+      <c r="L19" s="178"/>
+      <c r="M19" s="54"/>
+      <c r="N19" s="55"/>
+      <c r="O19" s="178"/>
+      <c r="P19" s="54"/>
+      <c r="Q19" s="55"/>
       <c r="R19" s="27"/>
       <c r="S19" s="27"/>
       <c r="T19" s="28"/>
@@ -13095,23 +13057,23 @@
       <c r="Z19" s="29"/>
     </row>
     <row r="20" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A20" s="155"/>
-      <c r="B20" s="48"/>
-      <c r="C20" s="156"/>
-      <c r="D20" s="48"/>
-      <c r="E20" s="156"/>
-      <c r="F20" s="48"/>
-      <c r="G20" s="170"/>
-      <c r="H20" s="47"/>
-      <c r="I20" s="48"/>
-      <c r="J20" s="170"/>
-      <c r="K20" s="48"/>
-      <c r="L20" s="160"/>
-      <c r="M20" s="47"/>
-      <c r="N20" s="48"/>
-      <c r="O20" s="160"/>
-      <c r="P20" s="47"/>
-      <c r="Q20" s="48"/>
+      <c r="A20" s="192"/>
+      <c r="B20" s="55"/>
+      <c r="C20" s="193"/>
+      <c r="D20" s="55"/>
+      <c r="E20" s="193"/>
+      <c r="F20" s="55"/>
+      <c r="G20" s="174"/>
+      <c r="H20" s="54"/>
+      <c r="I20" s="55"/>
+      <c r="J20" s="174"/>
+      <c r="K20" s="55"/>
+      <c r="L20" s="178"/>
+      <c r="M20" s="54"/>
+      <c r="N20" s="55"/>
+      <c r="O20" s="178"/>
+      <c r="P20" s="54"/>
+      <c r="Q20" s="55"/>
       <c r="R20" s="27"/>
       <c r="S20" s="27"/>
       <c r="T20" s="28"/>
@@ -13123,23 +13085,23 @@
       <c r="Z20" s="29"/>
     </row>
     <row r="21" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A21" s="155"/>
-      <c r="B21" s="48"/>
-      <c r="C21" s="156"/>
-      <c r="D21" s="48"/>
-      <c r="E21" s="156"/>
-      <c r="F21" s="48"/>
-      <c r="G21" s="170"/>
-      <c r="H21" s="47"/>
-      <c r="I21" s="48"/>
-      <c r="J21" s="170"/>
-      <c r="K21" s="48"/>
-      <c r="L21" s="160"/>
-      <c r="M21" s="47"/>
-      <c r="N21" s="48"/>
-      <c r="O21" s="160"/>
-      <c r="P21" s="47"/>
-      <c r="Q21" s="48"/>
+      <c r="A21" s="192"/>
+      <c r="B21" s="55"/>
+      <c r="C21" s="193"/>
+      <c r="D21" s="55"/>
+      <c r="E21" s="193"/>
+      <c r="F21" s="55"/>
+      <c r="G21" s="174"/>
+      <c r="H21" s="54"/>
+      <c r="I21" s="55"/>
+      <c r="J21" s="174"/>
+      <c r="K21" s="55"/>
+      <c r="L21" s="178"/>
+      <c r="M21" s="54"/>
+      <c r="N21" s="55"/>
+      <c r="O21" s="178"/>
+      <c r="P21" s="54"/>
+      <c r="Q21" s="55"/>
       <c r="R21" s="27"/>
       <c r="S21" s="27"/>
       <c r="T21" s="28"/>
@@ -13151,23 +13113,23 @@
       <c r="Z21" s="29"/>
     </row>
     <row r="22" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A22" s="155"/>
-      <c r="B22" s="48"/>
-      <c r="C22" s="156"/>
-      <c r="D22" s="48"/>
-      <c r="E22" s="156"/>
-      <c r="F22" s="48"/>
-      <c r="G22" s="170"/>
-      <c r="H22" s="47"/>
-      <c r="I22" s="48"/>
-      <c r="J22" s="170"/>
-      <c r="K22" s="48"/>
-      <c r="L22" s="160"/>
-      <c r="M22" s="47"/>
-      <c r="N22" s="48"/>
-      <c r="O22" s="160"/>
-      <c r="P22" s="47"/>
-      <c r="Q22" s="48"/>
+      <c r="A22" s="192"/>
+      <c r="B22" s="55"/>
+      <c r="C22" s="193"/>
+      <c r="D22" s="55"/>
+      <c r="E22" s="193"/>
+      <c r="F22" s="55"/>
+      <c r="G22" s="174"/>
+      <c r="H22" s="54"/>
+      <c r="I22" s="55"/>
+      <c r="J22" s="174"/>
+      <c r="K22" s="55"/>
+      <c r="L22" s="178"/>
+      <c r="M22" s="54"/>
+      <c r="N22" s="55"/>
+      <c r="O22" s="178"/>
+      <c r="P22" s="54"/>
+      <c r="Q22" s="55"/>
       <c r="R22" s="27"/>
       <c r="S22" s="27"/>
       <c r="T22" s="28"/>
@@ -13179,23 +13141,23 @@
       <c r="Z22" s="29"/>
     </row>
     <row r="23" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A23" s="155"/>
-      <c r="B23" s="48"/>
-      <c r="C23" s="156"/>
-      <c r="D23" s="48"/>
-      <c r="E23" s="156"/>
-      <c r="F23" s="48"/>
-      <c r="G23" s="170"/>
-      <c r="H23" s="47"/>
-      <c r="I23" s="48"/>
-      <c r="J23" s="170"/>
-      <c r="K23" s="48"/>
-      <c r="L23" s="160"/>
-      <c r="M23" s="47"/>
-      <c r="N23" s="48"/>
-      <c r="O23" s="160"/>
-      <c r="P23" s="47"/>
-      <c r="Q23" s="48"/>
+      <c r="A23" s="192"/>
+      <c r="B23" s="55"/>
+      <c r="C23" s="193"/>
+      <c r="D23" s="55"/>
+      <c r="E23" s="193"/>
+      <c r="F23" s="55"/>
+      <c r="G23" s="174"/>
+      <c r="H23" s="54"/>
+      <c r="I23" s="55"/>
+      <c r="J23" s="174"/>
+      <c r="K23" s="55"/>
+      <c r="L23" s="178"/>
+      <c r="M23" s="54"/>
+      <c r="N23" s="55"/>
+      <c r="O23" s="178"/>
+      <c r="P23" s="54"/>
+      <c r="Q23" s="55"/>
       <c r="R23" s="27"/>
       <c r="S23" s="27"/>
       <c r="T23" s="28"/>
@@ -13207,23 +13169,23 @@
       <c r="Z23" s="29"/>
     </row>
     <row r="24" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A24" s="155"/>
-      <c r="B24" s="48"/>
-      <c r="C24" s="156"/>
-      <c r="D24" s="48"/>
-      <c r="E24" s="156"/>
-      <c r="F24" s="48"/>
-      <c r="G24" s="170"/>
-      <c r="H24" s="47"/>
-      <c r="I24" s="48"/>
-      <c r="J24" s="170"/>
-      <c r="K24" s="48"/>
-      <c r="L24" s="160"/>
-      <c r="M24" s="47"/>
-      <c r="N24" s="48"/>
-      <c r="O24" s="160"/>
-      <c r="P24" s="47"/>
-      <c r="Q24" s="48"/>
+      <c r="A24" s="192"/>
+      <c r="B24" s="55"/>
+      <c r="C24" s="193"/>
+      <c r="D24" s="55"/>
+      <c r="E24" s="193"/>
+      <c r="F24" s="55"/>
+      <c r="G24" s="174"/>
+      <c r="H24" s="54"/>
+      <c r="I24" s="55"/>
+      <c r="J24" s="174"/>
+      <c r="K24" s="55"/>
+      <c r="L24" s="178"/>
+      <c r="M24" s="54"/>
+      <c r="N24" s="55"/>
+      <c r="O24" s="178"/>
+      <c r="P24" s="54"/>
+      <c r="Q24" s="55"/>
       <c r="R24" s="27"/>
       <c r="S24" s="27"/>
       <c r="T24" s="28"/>
@@ -13235,23 +13197,23 @@
       <c r="Z24" s="29"/>
     </row>
     <row r="25" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A25" s="155"/>
-      <c r="B25" s="48"/>
-      <c r="C25" s="156"/>
-      <c r="D25" s="48"/>
-      <c r="E25" s="156"/>
-      <c r="F25" s="48"/>
-      <c r="G25" s="170"/>
-      <c r="H25" s="47"/>
-      <c r="I25" s="48"/>
-      <c r="J25" s="170"/>
-      <c r="K25" s="48"/>
-      <c r="L25" s="160"/>
-      <c r="M25" s="47"/>
-      <c r="N25" s="48"/>
-      <c r="O25" s="160"/>
-      <c r="P25" s="47"/>
-      <c r="Q25" s="48"/>
+      <c r="A25" s="192"/>
+      <c r="B25" s="55"/>
+      <c r="C25" s="193"/>
+      <c r="D25" s="55"/>
+      <c r="E25" s="193"/>
+      <c r="F25" s="55"/>
+      <c r="G25" s="174"/>
+      <c r="H25" s="54"/>
+      <c r="I25" s="55"/>
+      <c r="J25" s="174"/>
+      <c r="K25" s="55"/>
+      <c r="L25" s="178"/>
+      <c r="M25" s="54"/>
+      <c r="N25" s="55"/>
+      <c r="O25" s="178"/>
+      <c r="P25" s="54"/>
+      <c r="Q25" s="55"/>
       <c r="R25" s="27"/>
       <c r="S25" s="27"/>
       <c r="T25" s="28"/>
@@ -13263,23 +13225,23 @@
       <c r="Z25" s="29"/>
     </row>
     <row r="26" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A26" s="155"/>
-      <c r="B26" s="48"/>
-      <c r="C26" s="156"/>
-      <c r="D26" s="48"/>
-      <c r="E26" s="156"/>
-      <c r="F26" s="48"/>
-      <c r="G26" s="170"/>
-      <c r="H26" s="47"/>
-      <c r="I26" s="48"/>
-      <c r="J26" s="170"/>
-      <c r="K26" s="48"/>
-      <c r="L26" s="160"/>
-      <c r="M26" s="47"/>
-      <c r="N26" s="48"/>
-      <c r="O26" s="160"/>
-      <c r="P26" s="47"/>
-      <c r="Q26" s="48"/>
+      <c r="A26" s="192"/>
+      <c r="B26" s="55"/>
+      <c r="C26" s="193"/>
+      <c r="D26" s="55"/>
+      <c r="E26" s="193"/>
+      <c r="F26" s="55"/>
+      <c r="G26" s="174"/>
+      <c r="H26" s="54"/>
+      <c r="I26" s="55"/>
+      <c r="J26" s="174"/>
+      <c r="K26" s="55"/>
+      <c r="L26" s="178"/>
+      <c r="M26" s="54"/>
+      <c r="N26" s="55"/>
+      <c r="O26" s="178"/>
+      <c r="P26" s="54"/>
+      <c r="Q26" s="55"/>
       <c r="R26" s="27"/>
       <c r="S26" s="27"/>
       <c r="T26" s="28"/>
@@ -13291,23 +13253,23 @@
       <c r="Z26" s="29"/>
     </row>
     <row r="27" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A27" s="155"/>
-      <c r="B27" s="48"/>
-      <c r="C27" s="156"/>
-      <c r="D27" s="48"/>
-      <c r="E27" s="156"/>
-      <c r="F27" s="48"/>
-      <c r="G27" s="170"/>
-      <c r="H27" s="47"/>
-      <c r="I27" s="48"/>
-      <c r="J27" s="170"/>
-      <c r="K27" s="48"/>
-      <c r="L27" s="160"/>
-      <c r="M27" s="47"/>
-      <c r="N27" s="48"/>
-      <c r="O27" s="160"/>
-      <c r="P27" s="47"/>
-      <c r="Q27" s="48"/>
+      <c r="A27" s="192"/>
+      <c r="B27" s="55"/>
+      <c r="C27" s="193"/>
+      <c r="D27" s="55"/>
+      <c r="E27" s="193"/>
+      <c r="F27" s="55"/>
+      <c r="G27" s="174"/>
+      <c r="H27" s="54"/>
+      <c r="I27" s="55"/>
+      <c r="J27" s="174"/>
+      <c r="K27" s="55"/>
+      <c r="L27" s="178"/>
+      <c r="M27" s="54"/>
+      <c r="N27" s="55"/>
+      <c r="O27" s="178"/>
+      <c r="P27" s="54"/>
+      <c r="Q27" s="55"/>
       <c r="R27" s="27"/>
       <c r="S27" s="27"/>
       <c r="T27" s="28"/>
@@ -13319,23 +13281,23 @@
       <c r="Z27" s="29"/>
     </row>
     <row r="28" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A28" s="155"/>
-      <c r="B28" s="48"/>
-      <c r="C28" s="156"/>
-      <c r="D28" s="48"/>
-      <c r="E28" s="156"/>
-      <c r="F28" s="48"/>
-      <c r="G28" s="170"/>
-      <c r="H28" s="47"/>
-      <c r="I28" s="48"/>
-      <c r="J28" s="170"/>
-      <c r="K28" s="48"/>
-      <c r="L28" s="160"/>
-      <c r="M28" s="47"/>
-      <c r="N28" s="48"/>
-      <c r="O28" s="160"/>
-      <c r="P28" s="47"/>
-      <c r="Q28" s="48"/>
+      <c r="A28" s="192"/>
+      <c r="B28" s="55"/>
+      <c r="C28" s="193"/>
+      <c r="D28" s="55"/>
+      <c r="E28" s="193"/>
+      <c r="F28" s="55"/>
+      <c r="G28" s="174"/>
+      <c r="H28" s="54"/>
+      <c r="I28" s="55"/>
+      <c r="J28" s="174"/>
+      <c r="K28" s="55"/>
+      <c r="L28" s="178"/>
+      <c r="M28" s="54"/>
+      <c r="N28" s="55"/>
+      <c r="O28" s="178"/>
+      <c r="P28" s="54"/>
+      <c r="Q28" s="55"/>
       <c r="R28" s="27"/>
       <c r="S28" s="27"/>
       <c r="T28" s="28"/>
@@ -13347,23 +13309,23 @@
       <c r="Z28" s="29"/>
     </row>
     <row r="29" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A29" s="155"/>
-      <c r="B29" s="48"/>
-      <c r="C29" s="156"/>
-      <c r="D29" s="48"/>
-      <c r="E29" s="156"/>
-      <c r="F29" s="48"/>
-      <c r="G29" s="170"/>
-      <c r="H29" s="47"/>
-      <c r="I29" s="48"/>
-      <c r="J29" s="170"/>
-      <c r="K29" s="48"/>
-      <c r="L29" s="160"/>
-      <c r="M29" s="47"/>
-      <c r="N29" s="48"/>
-      <c r="O29" s="160"/>
-      <c r="P29" s="47"/>
-      <c r="Q29" s="48"/>
+      <c r="A29" s="192"/>
+      <c r="B29" s="55"/>
+      <c r="C29" s="193"/>
+      <c r="D29" s="55"/>
+      <c r="E29" s="193"/>
+      <c r="F29" s="55"/>
+      <c r="G29" s="174"/>
+      <c r="H29" s="54"/>
+      <c r="I29" s="55"/>
+      <c r="J29" s="174"/>
+      <c r="K29" s="55"/>
+      <c r="L29" s="178"/>
+      <c r="M29" s="54"/>
+      <c r="N29" s="55"/>
+      <c r="O29" s="178"/>
+      <c r="P29" s="54"/>
+      <c r="Q29" s="55"/>
       <c r="R29" s="27"/>
       <c r="S29" s="27"/>
       <c r="T29" s="28"/>
@@ -13375,23 +13337,23 @@
       <c r="Z29" s="29"/>
     </row>
     <row r="30" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A30" s="155"/>
-      <c r="B30" s="48"/>
-      <c r="C30" s="156"/>
-      <c r="D30" s="48"/>
-      <c r="E30" s="156"/>
-      <c r="F30" s="48"/>
-      <c r="G30" s="170"/>
-      <c r="H30" s="47"/>
-      <c r="I30" s="48"/>
-      <c r="J30" s="170"/>
-      <c r="K30" s="48"/>
-      <c r="L30" s="160"/>
-      <c r="M30" s="47"/>
-      <c r="N30" s="48"/>
-      <c r="O30" s="160"/>
-      <c r="P30" s="47"/>
-      <c r="Q30" s="48"/>
+      <c r="A30" s="192"/>
+      <c r="B30" s="55"/>
+      <c r="C30" s="193"/>
+      <c r="D30" s="55"/>
+      <c r="E30" s="193"/>
+      <c r="F30" s="55"/>
+      <c r="G30" s="174"/>
+      <c r="H30" s="54"/>
+      <c r="I30" s="55"/>
+      <c r="J30" s="174"/>
+      <c r="K30" s="55"/>
+      <c r="L30" s="178"/>
+      <c r="M30" s="54"/>
+      <c r="N30" s="55"/>
+      <c r="O30" s="178"/>
+      <c r="P30" s="54"/>
+      <c r="Q30" s="55"/>
       <c r="R30" s="27"/>
       <c r="S30" s="27"/>
       <c r="T30" s="28"/>
@@ -13403,23 +13365,23 @@
       <c r="Z30" s="29"/>
     </row>
     <row r="31" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A31" s="157"/>
-      <c r="B31" s="158"/>
-      <c r="C31" s="159"/>
-      <c r="D31" s="158"/>
-      <c r="E31" s="159"/>
-      <c r="F31" s="158"/>
-      <c r="G31" s="179"/>
-      <c r="H31" s="162"/>
-      <c r="I31" s="158"/>
-      <c r="J31" s="179"/>
-      <c r="K31" s="158"/>
-      <c r="L31" s="161"/>
-      <c r="M31" s="162"/>
-      <c r="N31" s="158"/>
-      <c r="O31" s="161"/>
-      <c r="P31" s="162"/>
-      <c r="Q31" s="158"/>
+      <c r="A31" s="196"/>
+      <c r="B31" s="177"/>
+      <c r="C31" s="197"/>
+      <c r="D31" s="177"/>
+      <c r="E31" s="197"/>
+      <c r="F31" s="177"/>
+      <c r="G31" s="175"/>
+      <c r="H31" s="176"/>
+      <c r="I31" s="177"/>
+      <c r="J31" s="175"/>
+      <c r="K31" s="177"/>
+      <c r="L31" s="179"/>
+      <c r="M31" s="176"/>
+      <c r="N31" s="177"/>
+      <c r="O31" s="179"/>
+      <c r="P31" s="176"/>
+      <c r="Q31" s="177"/>
       <c r="R31" s="30"/>
       <c r="S31" s="30"/>
       <c r="T31" s="31"/>
@@ -14417,62 +14379,62 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="136">
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="J18:K18"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="J19:K19"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="G23:I23"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="J30:K30"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="J29:K29"/>
-    <mergeCell ref="L26:N26"/>
-    <mergeCell ref="L27:N27"/>
-    <mergeCell ref="L28:N28"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="L18:N18"/>
-    <mergeCell ref="L19:N19"/>
-    <mergeCell ref="L21:N21"/>
-    <mergeCell ref="L22:N22"/>
-    <mergeCell ref="L23:N23"/>
-    <mergeCell ref="L24:N24"/>
-    <mergeCell ref="L25:N25"/>
-    <mergeCell ref="K2:N4"/>
-    <mergeCell ref="O2:P4"/>
-    <mergeCell ref="Q2:R4"/>
-    <mergeCell ref="S2:T4"/>
-    <mergeCell ref="A1:F4"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="O1:P1"/>
-    <mergeCell ref="Q1:R1"/>
-    <mergeCell ref="S1:T1"/>
-    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="E30:F30"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="E31:F31"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="E26:F26"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="E29:F29"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="E27:F27"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="E28:F28"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="O27:Q27"/>
+    <mergeCell ref="O28:Q28"/>
+    <mergeCell ref="O29:Q29"/>
+    <mergeCell ref="O30:Q30"/>
+    <mergeCell ref="O31:Q31"/>
+    <mergeCell ref="O19:Q19"/>
+    <mergeCell ref="O21:Q21"/>
+    <mergeCell ref="O22:Q22"/>
+    <mergeCell ref="O23:Q23"/>
+    <mergeCell ref="O24:Q24"/>
+    <mergeCell ref="O25:Q25"/>
+    <mergeCell ref="O26:Q26"/>
     <mergeCell ref="A5:F5"/>
     <mergeCell ref="G5:T5"/>
     <mergeCell ref="A6:F6"/>
@@ -14497,62 +14459,62 @@
     <mergeCell ref="C15:D15"/>
     <mergeCell ref="E15:F15"/>
     <mergeCell ref="A16:B16"/>
-    <mergeCell ref="O27:Q27"/>
-    <mergeCell ref="O28:Q28"/>
-    <mergeCell ref="O29:Q29"/>
-    <mergeCell ref="O30:Q30"/>
-    <mergeCell ref="O31:Q31"/>
-    <mergeCell ref="O19:Q19"/>
-    <mergeCell ref="O21:Q21"/>
-    <mergeCell ref="O22:Q22"/>
-    <mergeCell ref="O23:Q23"/>
-    <mergeCell ref="O24:Q24"/>
-    <mergeCell ref="O25:Q25"/>
-    <mergeCell ref="O26:Q26"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="E30:F30"/>
-    <mergeCell ref="A31:B31"/>
-    <mergeCell ref="C31:D31"/>
-    <mergeCell ref="E31:F31"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="E26:F26"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="E24:F24"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="E29:F29"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="E27:F27"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="E28:F28"/>
-    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="K2:N4"/>
+    <mergeCell ref="O2:P4"/>
+    <mergeCell ref="Q2:R4"/>
+    <mergeCell ref="S2:T4"/>
+    <mergeCell ref="A1:F4"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="S1:T1"/>
+    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="L26:N26"/>
+    <mergeCell ref="L27:N27"/>
+    <mergeCell ref="L28:N28"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="L18:N18"/>
+    <mergeCell ref="L19:N19"/>
+    <mergeCell ref="L21:N21"/>
+    <mergeCell ref="L22:N22"/>
+    <mergeCell ref="L23:N23"/>
+    <mergeCell ref="L24:N24"/>
+    <mergeCell ref="L25:N25"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="J30:K30"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="J29:K29"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="J19:K19"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <hyperlinks>

--- a/Documents/登録機能詳細設計書.xlsx
+++ b/Documents/登録機能詳細設計書.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user47\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\S-47\Documents\project\taskUN\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75E45A11-1E57-4889-B2C0-D3EBA6344D4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DA7AF9D-EE18-4DFA-8926-EF9C3830F55F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="1" r:id="rId1"/>
@@ -23,24 +23,11 @@
     <sheet name="テスト仕様書兼結果報告書" sheetId="6" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="121">
   <si>
     <t>プロジェクト型演習　成果ドキュメント</t>
   </si>
@@ -750,6 +737,13 @@
       <t>センイ</t>
     </rPh>
     <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>山本(あ)</t>
+    <rPh sb="0" eb="2">
+      <t>ヤマモト</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
   </si>
 </sst>
 </file>
@@ -1732,6 +1726,93 @@
     <xf numFmtId="14" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1762,9 +1843,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1777,90 +1855,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1939,6 +1933,12 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2011,10 +2011,31 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2023,107 +2044,80 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -2150,23 +2144,23 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>247650</xdr:colOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>38100</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
+      <xdr:rowOff>66675</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>800100</xdr:colOff>
-      <xdr:row>32</xdr:row>
-      <xdr:rowOff>149925</xdr:rowOff>
+      <xdr:colOff>438150</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="図 4">
+        <xdr:cNvPr id="3" name="図 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{99AD4A46-4D34-AC3A-3039-1C89EA6897B3}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1586A722-2167-CF7B-8072-EF5F6BA006D4}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2188,8 +2182,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="247650" y="1028700"/>
-          <a:ext cx="8267700" cy="4569525"/>
+          <a:off x="381000" y="981075"/>
+          <a:ext cx="7772400" cy="4295775"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4439,19 +4433,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="60" t="s">
+      <c r="A1" s="89" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="61"/>
-      <c r="C1" s="62"/>
-      <c r="D1" s="69" t="s">
+      <c r="B1" s="90"/>
+      <c r="C1" s="91"/>
+      <c r="D1" s="98" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="70"/>
-      <c r="F1" s="69" t="s">
+      <c r="E1" s="83"/>
+      <c r="F1" s="98" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="70"/>
+      <c r="G1" s="83"/>
       <c r="H1" s="34" t="s">
         <v>6</v>
       </c>
@@ -4463,192 +4457,192 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="63"/>
-      <c r="B2" s="64"/>
-      <c r="C2" s="65"/>
-      <c r="D2" s="71" t="s">
+      <c r="A2" s="92"/>
+      <c r="B2" s="93"/>
+      <c r="C2" s="94"/>
+      <c r="D2" s="99" t="s">
         <v>72</v>
       </c>
-      <c r="E2" s="72"/>
-      <c r="F2" s="71">
+      <c r="E2" s="100"/>
+      <c r="F2" s="99">
         <v>56</v>
       </c>
-      <c r="G2" s="72"/>
-      <c r="H2" s="75">
+      <c r="G2" s="100"/>
+      <c r="H2" s="68">
         <v>45806</v>
       </c>
-      <c r="I2" s="89" t="s">
+      <c r="I2" s="77" t="s">
         <v>71</v>
       </c>
-      <c r="J2" s="90"/>
+      <c r="J2" s="78"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="63"/>
-      <c r="B3" s="64"/>
-      <c r="C3" s="65"/>
-      <c r="D3" s="73"/>
-      <c r="E3" s="65"/>
-      <c r="F3" s="73"/>
-      <c r="G3" s="65"/>
-      <c r="H3" s="76"/>
-      <c r="I3" s="76"/>
-      <c r="J3" s="91"/>
+      <c r="A3" s="92"/>
+      <c r="B3" s="93"/>
+      <c r="C3" s="94"/>
+      <c r="D3" s="101"/>
+      <c r="E3" s="94"/>
+      <c r="F3" s="101"/>
+      <c r="G3" s="94"/>
+      <c r="H3" s="69"/>
+      <c r="I3" s="69"/>
+      <c r="J3" s="79"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="66"/>
-      <c r="B4" s="67"/>
-      <c r="C4" s="68"/>
-      <c r="D4" s="74"/>
-      <c r="E4" s="68"/>
-      <c r="F4" s="74"/>
-      <c r="G4" s="68"/>
-      <c r="H4" s="77"/>
-      <c r="I4" s="77"/>
-      <c r="J4" s="92"/>
+      <c r="A4" s="95"/>
+      <c r="B4" s="96"/>
+      <c r="C4" s="97"/>
+      <c r="D4" s="102"/>
+      <c r="E4" s="97"/>
+      <c r="F4" s="102"/>
+      <c r="G4" s="97"/>
+      <c r="H4" s="70"/>
+      <c r="I4" s="70"/>
+      <c r="J4" s="80"/>
     </row>
     <row r="5" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A5" s="93" t="s">
+      <c r="A5" s="81" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="94"/>
-      <c r="C5" s="70"/>
-      <c r="D5" s="95" t="s">
+      <c r="B5" s="82"/>
+      <c r="C5" s="83"/>
+      <c r="D5" s="84" t="s">
         <v>70</v>
       </c>
-      <c r="E5" s="94"/>
-      <c r="F5" s="94"/>
-      <c r="G5" s="94"/>
-      <c r="H5" s="94"/>
-      <c r="I5" s="94"/>
-      <c r="J5" s="96"/>
+      <c r="E5" s="82"/>
+      <c r="F5" s="82"/>
+      <c r="G5" s="82"/>
+      <c r="H5" s="82"/>
+      <c r="I5" s="82"/>
+      <c r="J5" s="85"/>
     </row>
     <row r="6" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A6" s="78" t="s">
+      <c r="A6" s="71" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="79"/>
-      <c r="C6" s="80"/>
-      <c r="D6" s="88" t="s">
+      <c r="B6" s="66"/>
+      <c r="C6" s="61"/>
+      <c r="D6" s="65" t="s">
         <v>69</v>
       </c>
-      <c r="E6" s="79"/>
-      <c r="F6" s="79"/>
-      <c r="G6" s="79"/>
-      <c r="H6" s="79"/>
-      <c r="I6" s="79"/>
-      <c r="J6" s="82"/>
+      <c r="E6" s="66"/>
+      <c r="F6" s="66"/>
+      <c r="G6" s="66"/>
+      <c r="H6" s="66"/>
+      <c r="I6" s="66"/>
+      <c r="J6" s="67"/>
     </row>
     <row r="7" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A7" s="78" t="s">
+      <c r="A7" s="71" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="79"/>
-      <c r="C7" s="80"/>
-      <c r="D7" s="88" t="s">
+      <c r="B7" s="66"/>
+      <c r="C7" s="61"/>
+      <c r="D7" s="65" t="s">
         <v>68</v>
       </c>
-      <c r="E7" s="79"/>
-      <c r="F7" s="79"/>
-      <c r="G7" s="79"/>
-      <c r="H7" s="79"/>
-      <c r="I7" s="79"/>
-      <c r="J7" s="82"/>
+      <c r="E7" s="66"/>
+      <c r="F7" s="66"/>
+      <c r="G7" s="66"/>
+      <c r="H7" s="66"/>
+      <c r="I7" s="66"/>
+      <c r="J7" s="67"/>
     </row>
     <row r="8" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A8" s="78" t="s">
+      <c r="A8" s="71" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="79"/>
-      <c r="C8" s="80"/>
-      <c r="D8" s="81" t="s">
+      <c r="B8" s="66"/>
+      <c r="C8" s="61"/>
+      <c r="D8" s="62" t="s">
         <v>118</v>
       </c>
-      <c r="E8" s="79"/>
-      <c r="F8" s="79"/>
-      <c r="G8" s="79"/>
-      <c r="H8" s="79"/>
-      <c r="I8" s="79"/>
-      <c r="J8" s="82"/>
+      <c r="E8" s="66"/>
+      <c r="F8" s="66"/>
+      <c r="G8" s="66"/>
+      <c r="H8" s="66"/>
+      <c r="I8" s="66"/>
+      <c r="J8" s="67"/>
     </row>
     <row r="9" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A9" s="97" t="s">
+      <c r="A9" s="86" t="s">
         <v>13</v>
       </c>
-      <c r="B9" s="100" t="s">
+      <c r="B9" s="60" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="80"/>
-      <c r="D9" s="81" t="s">
+      <c r="C9" s="61"/>
+      <c r="D9" s="62" t="s">
         <v>116</v>
       </c>
-      <c r="E9" s="101"/>
-      <c r="F9" s="101"/>
-      <c r="G9" s="101"/>
-      <c r="H9" s="101"/>
-      <c r="I9" s="101"/>
-      <c r="J9" s="102"/>
+      <c r="E9" s="63"/>
+      <c r="F9" s="63"/>
+      <c r="G9" s="63"/>
+      <c r="H9" s="63"/>
+      <c r="I9" s="63"/>
+      <c r="J9" s="64"/>
     </row>
     <row r="10" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A10" s="98"/>
-      <c r="B10" s="100" t="s">
+      <c r="A10" s="87"/>
+      <c r="B10" s="60" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="80"/>
-      <c r="D10" s="88" t="s">
+      <c r="C10" s="61"/>
+      <c r="D10" s="65" t="s">
         <v>104</v>
       </c>
-      <c r="E10" s="79"/>
-      <c r="F10" s="79"/>
-      <c r="G10" s="79"/>
-      <c r="H10" s="79"/>
-      <c r="I10" s="79"/>
-      <c r="J10" s="82"/>
+      <c r="E10" s="66"/>
+      <c r="F10" s="66"/>
+      <c r="G10" s="66"/>
+      <c r="H10" s="66"/>
+      <c r="I10" s="66"/>
+      <c r="J10" s="67"/>
     </row>
     <row r="11" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A11" s="99"/>
-      <c r="B11" s="100" t="s">
+      <c r="A11" s="88"/>
+      <c r="B11" s="60" t="s">
         <v>16</v>
       </c>
-      <c r="C11" s="80"/>
-      <c r="D11" s="81" t="s">
+      <c r="C11" s="61"/>
+      <c r="D11" s="62" t="s">
         <v>119</v>
       </c>
-      <c r="E11" s="79"/>
-      <c r="F11" s="79"/>
-      <c r="G11" s="79"/>
-      <c r="H11" s="79"/>
-      <c r="I11" s="79"/>
-      <c r="J11" s="82"/>
+      <c r="E11" s="66"/>
+      <c r="F11" s="66"/>
+      <c r="G11" s="66"/>
+      <c r="H11" s="66"/>
+      <c r="I11" s="66"/>
+      <c r="J11" s="67"/>
     </row>
     <row r="12" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A12" s="78" t="s">
+      <c r="A12" s="71" t="s">
         <v>17</v>
       </c>
-      <c r="B12" s="79"/>
-      <c r="C12" s="80"/>
-      <c r="D12" s="81" t="s">
+      <c r="B12" s="66"/>
+      <c r="C12" s="61"/>
+      <c r="D12" s="62" t="s">
         <v>117</v>
       </c>
-      <c r="E12" s="79"/>
-      <c r="F12" s="79"/>
-      <c r="G12" s="79"/>
-      <c r="H12" s="79"/>
-      <c r="I12" s="79"/>
-      <c r="J12" s="82"/>
+      <c r="E12" s="66"/>
+      <c r="F12" s="66"/>
+      <c r="G12" s="66"/>
+      <c r="H12" s="66"/>
+      <c r="I12" s="66"/>
+      <c r="J12" s="67"/>
     </row>
     <row r="13" spans="1:10" ht="26.25" customHeight="1" thickBot="1">
-      <c r="A13" s="83" t="s">
+      <c r="A13" s="72" t="s">
         <v>18</v>
       </c>
-      <c r="B13" s="84"/>
-      <c r="C13" s="85"/>
-      <c r="D13" s="86"/>
-      <c r="E13" s="84"/>
-      <c r="F13" s="84"/>
-      <c r="G13" s="84"/>
-      <c r="H13" s="84"/>
-      <c r="I13" s="84"/>
-      <c r="J13" s="87"/>
+      <c r="B13" s="73"/>
+      <c r="C13" s="74"/>
+      <c r="D13" s="75"/>
+      <c r="E13" s="73"/>
+      <c r="F13" s="73"/>
+      <c r="G13" s="73"/>
+      <c r="H13" s="73"/>
+      <c r="I13" s="73"/>
+      <c r="J13" s="76"/>
     </row>
     <row r="14" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="15" spans="1:10" ht="12.75" customHeight="1"/>
@@ -5639,12 +5633,11 @@
     <row r="1000" s="32" customFormat="1" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="D9:J9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="D10:J10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="D11:J11"/>
+    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="F2:G4"/>
     <mergeCell ref="H2:H4"/>
     <mergeCell ref="A12:C12"/>
     <mergeCell ref="D12:J12"/>
@@ -5661,11 +5654,12 @@
     <mergeCell ref="A6:C6"/>
     <mergeCell ref="D6:J6"/>
     <mergeCell ref="A9:A11"/>
-    <mergeCell ref="A1:C4"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="D2:E4"/>
-    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="D9:J9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="D10:J10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="D11:J11"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.70833333333333304" right="0.70833333333333304" top="0.74791666666666701" bottom="0.74791666666666701" header="0" footer="0"/>
@@ -5722,7 +5716,9 @@
       <c r="H2" s="103">
         <v>45806</v>
       </c>
-      <c r="I2" s="106"/>
+      <c r="I2" s="106" t="s">
+        <v>120</v>
+      </c>
       <c r="J2" s="107"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
@@ -8521,19 +8517,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="135" t="s">
+      <c r="A1" s="137" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="136"/>
-      <c r="C1" s="137"/>
-      <c r="D1" s="139" t="s">
+      <c r="B1" s="138"/>
+      <c r="C1" s="139"/>
+      <c r="D1" s="141" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="140"/>
-      <c r="F1" s="139" t="s">
+      <c r="E1" s="142"/>
+      <c r="F1" s="141" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="140"/>
+      <c r="G1" s="142"/>
       <c r="H1" s="43" t="s">
         <v>6</v>
       </c>
@@ -8545,67 +8541,67 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="132"/>
-      <c r="B2" s="133"/>
-      <c r="C2" s="138"/>
-      <c r="D2" s="141" t="s">
+      <c r="A2" s="134"/>
+      <c r="B2" s="135"/>
+      <c r="C2" s="140"/>
+      <c r="D2" s="143" t="s">
         <v>95</v>
       </c>
-      <c r="E2" s="142"/>
-      <c r="F2" s="141">
+      <c r="E2" s="144"/>
+      <c r="F2" s="143">
         <v>56</v>
       </c>
-      <c r="G2" s="142"/>
-      <c r="H2" s="144">
+      <c r="G2" s="144"/>
+      <c r="H2" s="146">
         <v>45806</v>
       </c>
-      <c r="I2" s="146" t="s">
+      <c r="I2" s="148" t="s">
         <v>94</v>
       </c>
-      <c r="J2" s="147"/>
+      <c r="J2" s="149"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="132"/>
-      <c r="B3" s="133"/>
-      <c r="C3" s="138"/>
-      <c r="D3" s="143"/>
-      <c r="E3" s="138"/>
-      <c r="F3" s="143"/>
-      <c r="G3" s="138"/>
-      <c r="H3" s="145"/>
-      <c r="I3" s="145"/>
-      <c r="J3" s="148"/>
+      <c r="A3" s="134"/>
+      <c r="B3" s="135"/>
+      <c r="C3" s="140"/>
+      <c r="D3" s="145"/>
+      <c r="E3" s="140"/>
+      <c r="F3" s="145"/>
+      <c r="G3" s="140"/>
+      <c r="H3" s="147"/>
+      <c r="I3" s="147"/>
+      <c r="J3" s="150"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="132"/>
-      <c r="B4" s="133"/>
-      <c r="C4" s="138"/>
-      <c r="D4" s="143"/>
-      <c r="E4" s="138"/>
-      <c r="F4" s="143"/>
-      <c r="G4" s="138"/>
-      <c r="H4" s="145"/>
-      <c r="I4" s="145"/>
-      <c r="J4" s="148"/>
+      <c r="A4" s="134"/>
+      <c r="B4" s="135"/>
+      <c r="C4" s="140"/>
+      <c r="D4" s="145"/>
+      <c r="E4" s="140"/>
+      <c r="F4" s="145"/>
+      <c r="G4" s="140"/>
+      <c r="H4" s="147"/>
+      <c r="I4" s="147"/>
+      <c r="J4" s="150"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="149" t="s">
+      <c r="A5" s="151" t="s">
         <v>22</v>
       </c>
-      <c r="B5" s="150"/>
-      <c r="C5" s="140"/>
-      <c r="D5" s="151" t="s">
+      <c r="B5" s="152"/>
+      <c r="C5" s="142"/>
+      <c r="D5" s="153" t="s">
         <v>103</v>
       </c>
-      <c r="E5" s="150"/>
-      <c r="F5" s="150"/>
-      <c r="G5" s="150"/>
-      <c r="H5" s="150"/>
-      <c r="I5" s="150"/>
-      <c r="J5" s="152"/>
+      <c r="E5" s="152"/>
+      <c r="F5" s="152"/>
+      <c r="G5" s="152"/>
+      <c r="H5" s="152"/>
+      <c r="I5" s="152"/>
+      <c r="J5" s="154"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="153" t="s">
+      <c r="A6" s="130" t="s">
         <v>23</v>
       </c>
       <c r="B6" s="125"/>
@@ -8619,91 +8615,91 @@
       <c r="J6" s="128"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="129"/>
-      <c r="B7" s="130"/>
-      <c r="C7" s="130"/>
-      <c r="D7" s="130"/>
-      <c r="E7" s="130"/>
-      <c r="F7" s="130"/>
-      <c r="G7" s="130"/>
-      <c r="H7" s="130"/>
-      <c r="I7" s="130"/>
-      <c r="J7" s="131"/>
+      <c r="A7" s="131"/>
+      <c r="B7" s="132"/>
+      <c r="C7" s="132"/>
+      <c r="D7" s="132"/>
+      <c r="E7" s="132"/>
+      <c r="F7" s="132"/>
+      <c r="G7" s="132"/>
+      <c r="H7" s="132"/>
+      <c r="I7" s="132"/>
+      <c r="J7" s="133"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="132"/>
-      <c r="B8" s="133"/>
-      <c r="C8" s="133"/>
-      <c r="D8" s="133"/>
-      <c r="E8" s="133"/>
-      <c r="F8" s="133"/>
-      <c r="G8" s="133"/>
-      <c r="H8" s="133"/>
-      <c r="I8" s="133"/>
-      <c r="J8" s="134"/>
+      <c r="A8" s="134"/>
+      <c r="B8" s="135"/>
+      <c r="C8" s="135"/>
+      <c r="D8" s="135"/>
+      <c r="E8" s="135"/>
+      <c r="F8" s="135"/>
+      <c r="G8" s="135"/>
+      <c r="H8" s="135"/>
+      <c r="I8" s="135"/>
+      <c r="J8" s="136"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="132"/>
-      <c r="B9" s="133"/>
-      <c r="C9" s="133"/>
-      <c r="D9" s="133"/>
-      <c r="E9" s="133"/>
-      <c r="F9" s="133"/>
-      <c r="G9" s="133"/>
-      <c r="H9" s="133"/>
-      <c r="I9" s="133"/>
-      <c r="J9" s="134"/>
+      <c r="A9" s="134"/>
+      <c r="B9" s="135"/>
+      <c r="C9" s="135"/>
+      <c r="D9" s="135"/>
+      <c r="E9" s="135"/>
+      <c r="F9" s="135"/>
+      <c r="G9" s="135"/>
+      <c r="H9" s="135"/>
+      <c r="I9" s="135"/>
+      <c r="J9" s="136"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="132"/>
-      <c r="B10" s="133"/>
-      <c r="C10" s="133"/>
-      <c r="D10" s="133"/>
-      <c r="E10" s="133"/>
-      <c r="F10" s="133"/>
-      <c r="G10" s="133"/>
-      <c r="H10" s="133"/>
-      <c r="I10" s="133"/>
-      <c r="J10" s="134"/>
+      <c r="A10" s="134"/>
+      <c r="B10" s="135"/>
+      <c r="C10" s="135"/>
+      <c r="D10" s="135"/>
+      <c r="E10" s="135"/>
+      <c r="F10" s="135"/>
+      <c r="G10" s="135"/>
+      <c r="H10" s="135"/>
+      <c r="I10" s="135"/>
+      <c r="J10" s="136"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="132"/>
-      <c r="B11" s="133"/>
-      <c r="C11" s="133"/>
-      <c r="D11" s="133"/>
-      <c r="E11" s="133"/>
-      <c r="F11" s="133"/>
-      <c r="G11" s="133"/>
-      <c r="H11" s="133"/>
-      <c r="I11" s="133"/>
-      <c r="J11" s="134"/>
+      <c r="A11" s="134"/>
+      <c r="B11" s="135"/>
+      <c r="C11" s="135"/>
+      <c r="D11" s="135"/>
+      <c r="E11" s="135"/>
+      <c r="F11" s="135"/>
+      <c r="G11" s="135"/>
+      <c r="H11" s="135"/>
+      <c r="I11" s="135"/>
+      <c r="J11" s="136"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="132"/>
-      <c r="B12" s="133"/>
-      <c r="C12" s="133"/>
-      <c r="D12" s="133"/>
-      <c r="E12" s="133"/>
-      <c r="F12" s="133"/>
-      <c r="G12" s="133"/>
-      <c r="H12" s="133"/>
-      <c r="I12" s="133"/>
-      <c r="J12" s="134"/>
+      <c r="A12" s="134"/>
+      <c r="B12" s="135"/>
+      <c r="C12" s="135"/>
+      <c r="D12" s="135"/>
+      <c r="E12" s="135"/>
+      <c r="F12" s="135"/>
+      <c r="G12" s="135"/>
+      <c r="H12" s="135"/>
+      <c r="I12" s="135"/>
+      <c r="J12" s="136"/>
     </row>
     <row r="13" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A13" s="132"/>
-      <c r="B13" s="133"/>
-      <c r="C13" s="133"/>
-      <c r="D13" s="133"/>
-      <c r="E13" s="133"/>
-      <c r="F13" s="133"/>
-      <c r="G13" s="133"/>
-      <c r="H13" s="133"/>
-      <c r="I13" s="133"/>
-      <c r="J13" s="134"/>
+      <c r="A13" s="134"/>
+      <c r="B13" s="135"/>
+      <c r="C13" s="135"/>
+      <c r="D13" s="135"/>
+      <c r="E13" s="135"/>
+      <c r="F13" s="135"/>
+      <c r="G13" s="135"/>
+      <c r="H13" s="135"/>
+      <c r="I13" s="135"/>
+      <c r="J13" s="136"/>
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A14" s="153" t="s">
+      <c r="A14" s="130" t="s">
         <v>24</v>
       </c>
       <c r="B14" s="125"/>
@@ -8717,7 +8713,7 @@
       <c r="J14" s="128"/>
     </row>
     <row r="15" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A15" s="153" t="s">
+      <c r="A15" s="130" t="s">
         <v>25</v>
       </c>
       <c r="B15" s="125"/>
@@ -8737,7 +8733,7 @@
       </c>
     </row>
     <row r="16" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A16" s="153" t="s">
+      <c r="A16" s="130" t="s">
         <v>27</v>
       </c>
       <c r="B16" s="125"/>
@@ -8754,7 +8750,7 @@
       <c r="G16" s="39" t="s">
         <v>31</v>
       </c>
-      <c r="H16" s="154" t="s">
+      <c r="H16" s="129" t="s">
         <v>18</v>
       </c>
       <c r="I16" s="125"/>
@@ -9926,23 +9922,6 @@
     <row r="1000" s="36" customFormat="1" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="33">
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="H19:J19"/>
-    <mergeCell ref="A23:C23"/>
-    <mergeCell ref="H23:J23"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="H20:J20"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="H21:J21"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="H22:J22"/>
-    <mergeCell ref="H16:J16"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="A15:C15"/>
-    <mergeCell ref="D15:H15"/>
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="H17:J17"/>
     <mergeCell ref="A24:C24"/>
     <mergeCell ref="H24:J24"/>
     <mergeCell ref="A7:J13"/>
@@ -9959,6 +9938,23 @@
     <mergeCell ref="A6:J6"/>
     <mergeCell ref="A14:J14"/>
     <mergeCell ref="A16:C16"/>
+    <mergeCell ref="H16:J16"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="H18:J18"/>
+    <mergeCell ref="A15:C15"/>
+    <mergeCell ref="D15:H15"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="H17:J17"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="H19:J19"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="H23:J23"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="H20:J20"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="H21:J21"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="H22:J22"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -9982,19 +9978,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="163" t="s">
+      <c r="A1" s="160" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="61"/>
-      <c r="C1" s="62"/>
-      <c r="D1" s="69" t="s">
+      <c r="B1" s="90"/>
+      <c r="C1" s="91"/>
+      <c r="D1" s="98" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="70"/>
-      <c r="F1" s="69" t="s">
+      <c r="E1" s="83"/>
+      <c r="F1" s="98" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="70"/>
+      <c r="G1" s="83"/>
       <c r="H1" s="35" t="s">
         <v>6</v>
       </c>
@@ -10006,190 +10002,190 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="63"/>
-      <c r="B2" s="64"/>
-      <c r="C2" s="65"/>
-      <c r="D2" s="71" t="s">
+      <c r="A2" s="92"/>
+      <c r="B2" s="93"/>
+      <c r="C2" s="94"/>
+      <c r="D2" s="99" t="s">
         <v>96</v>
       </c>
-      <c r="E2" s="72"/>
-      <c r="F2" s="71">
+      <c r="E2" s="100"/>
+      <c r="F2" s="99">
         <v>56</v>
       </c>
-      <c r="G2" s="72"/>
-      <c r="H2" s="75">
+      <c r="G2" s="100"/>
+      <c r="H2" s="68">
         <v>45805</v>
       </c>
-      <c r="I2" s="89" t="s">
+      <c r="I2" s="77" t="s">
         <v>94</v>
       </c>
-      <c r="J2" s="90"/>
+      <c r="J2" s="78"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="63"/>
-      <c r="B3" s="64"/>
-      <c r="C3" s="65"/>
-      <c r="D3" s="73"/>
-      <c r="E3" s="65"/>
-      <c r="F3" s="73"/>
-      <c r="G3" s="65"/>
-      <c r="H3" s="76"/>
-      <c r="I3" s="76"/>
-      <c r="J3" s="91"/>
+      <c r="A3" s="92"/>
+      <c r="B3" s="93"/>
+      <c r="C3" s="94"/>
+      <c r="D3" s="101"/>
+      <c r="E3" s="94"/>
+      <c r="F3" s="101"/>
+      <c r="G3" s="94"/>
+      <c r="H3" s="69"/>
+      <c r="I3" s="69"/>
+      <c r="J3" s="79"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="63"/>
-      <c r="B4" s="64"/>
-      <c r="C4" s="65"/>
-      <c r="D4" s="73"/>
-      <c r="E4" s="65"/>
-      <c r="F4" s="73"/>
-      <c r="G4" s="65"/>
-      <c r="H4" s="76"/>
-      <c r="I4" s="76"/>
-      <c r="J4" s="91"/>
+      <c r="A4" s="92"/>
+      <c r="B4" s="93"/>
+      <c r="C4" s="94"/>
+      <c r="D4" s="101"/>
+      <c r="E4" s="94"/>
+      <c r="F4" s="101"/>
+      <c r="G4" s="94"/>
+      <c r="H4" s="69"/>
+      <c r="I4" s="69"/>
+      <c r="J4" s="79"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="164" t="s">
+      <c r="A5" s="161" t="s">
         <v>22</v>
       </c>
-      <c r="B5" s="94"/>
-      <c r="C5" s="70"/>
-      <c r="D5" s="165" t="s">
+      <c r="B5" s="82"/>
+      <c r="C5" s="83"/>
+      <c r="D5" s="162" t="s">
         <v>97</v>
       </c>
-      <c r="E5" s="94"/>
-      <c r="F5" s="94"/>
-      <c r="G5" s="94"/>
-      <c r="H5" s="94"/>
-      <c r="I5" s="94"/>
-      <c r="J5" s="96"/>
+      <c r="E5" s="82"/>
+      <c r="F5" s="82"/>
+      <c r="G5" s="82"/>
+      <c r="H5" s="82"/>
+      <c r="I5" s="82"/>
+      <c r="J5" s="85"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="157" t="s">
+      <c r="A6" s="155" t="s">
         <v>23</v>
       </c>
-      <c r="B6" s="79"/>
-      <c r="C6" s="79"/>
-      <c r="D6" s="79"/>
-      <c r="E6" s="79"/>
-      <c r="F6" s="79"/>
-      <c r="G6" s="79"/>
-      <c r="H6" s="79"/>
-      <c r="I6" s="79"/>
-      <c r="J6" s="82"/>
+      <c r="B6" s="66"/>
+      <c r="C6" s="66"/>
+      <c r="D6" s="66"/>
+      <c r="E6" s="66"/>
+      <c r="F6" s="66"/>
+      <c r="G6" s="66"/>
+      <c r="H6" s="66"/>
+      <c r="I6" s="66"/>
+      <c r="J6" s="67"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="159"/>
-      <c r="B7" s="160"/>
-      <c r="C7" s="160"/>
-      <c r="D7" s="160"/>
-      <c r="E7" s="160"/>
-      <c r="F7" s="160"/>
-      <c r="G7" s="160"/>
-      <c r="H7" s="160"/>
-      <c r="I7" s="160"/>
-      <c r="J7" s="161"/>
+      <c r="A7" s="156"/>
+      <c r="B7" s="157"/>
+      <c r="C7" s="157"/>
+      <c r="D7" s="157"/>
+      <c r="E7" s="157"/>
+      <c r="F7" s="157"/>
+      <c r="G7" s="157"/>
+      <c r="H7" s="157"/>
+      <c r="I7" s="157"/>
+      <c r="J7" s="158"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="63"/>
-      <c r="B8" s="64"/>
-      <c r="C8" s="64"/>
-      <c r="D8" s="64"/>
-      <c r="E8" s="64"/>
-      <c r="F8" s="64"/>
-      <c r="G8" s="64"/>
-      <c r="H8" s="64"/>
-      <c r="I8" s="64"/>
-      <c r="J8" s="162"/>
+      <c r="A8" s="92"/>
+      <c r="B8" s="93"/>
+      <c r="C8" s="93"/>
+      <c r="D8" s="93"/>
+      <c r="E8" s="93"/>
+      <c r="F8" s="93"/>
+      <c r="G8" s="93"/>
+      <c r="H8" s="93"/>
+      <c r="I8" s="93"/>
+      <c r="J8" s="159"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="63"/>
-      <c r="B9" s="64"/>
-      <c r="C9" s="64"/>
-      <c r="D9" s="64"/>
-      <c r="E9" s="64"/>
-      <c r="F9" s="64"/>
-      <c r="G9" s="64"/>
-      <c r="H9" s="64"/>
-      <c r="I9" s="64"/>
-      <c r="J9" s="162"/>
+      <c r="A9" s="92"/>
+      <c r="B9" s="93"/>
+      <c r="C9" s="93"/>
+      <c r="D9" s="93"/>
+      <c r="E9" s="93"/>
+      <c r="F9" s="93"/>
+      <c r="G9" s="93"/>
+      <c r="H9" s="93"/>
+      <c r="I9" s="93"/>
+      <c r="J9" s="159"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="63"/>
-      <c r="B10" s="64"/>
-      <c r="C10" s="64"/>
-      <c r="D10" s="64"/>
-      <c r="E10" s="64"/>
-      <c r="F10" s="64"/>
-      <c r="G10" s="64"/>
-      <c r="H10" s="64"/>
-      <c r="I10" s="64"/>
-      <c r="J10" s="162"/>
+      <c r="A10" s="92"/>
+      <c r="B10" s="93"/>
+      <c r="C10" s="93"/>
+      <c r="D10" s="93"/>
+      <c r="E10" s="93"/>
+      <c r="F10" s="93"/>
+      <c r="G10" s="93"/>
+      <c r="H10" s="93"/>
+      <c r="I10" s="93"/>
+      <c r="J10" s="159"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="63"/>
-      <c r="B11" s="64"/>
-      <c r="C11" s="64"/>
-      <c r="D11" s="64"/>
-      <c r="E11" s="64"/>
-      <c r="F11" s="64"/>
-      <c r="G11" s="64"/>
-      <c r="H11" s="64"/>
-      <c r="I11" s="64"/>
-      <c r="J11" s="162"/>
+      <c r="A11" s="92"/>
+      <c r="B11" s="93"/>
+      <c r="C11" s="93"/>
+      <c r="D11" s="93"/>
+      <c r="E11" s="93"/>
+      <c r="F11" s="93"/>
+      <c r="G11" s="93"/>
+      <c r="H11" s="93"/>
+      <c r="I11" s="93"/>
+      <c r="J11" s="159"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="63"/>
-      <c r="B12" s="64"/>
-      <c r="C12" s="64"/>
-      <c r="D12" s="64"/>
-      <c r="E12" s="64"/>
-      <c r="F12" s="64"/>
-      <c r="G12" s="64"/>
-      <c r="H12" s="64"/>
-      <c r="I12" s="64"/>
-      <c r="J12" s="162"/>
+      <c r="A12" s="92"/>
+      <c r="B12" s="93"/>
+      <c r="C12" s="93"/>
+      <c r="D12" s="93"/>
+      <c r="E12" s="93"/>
+      <c r="F12" s="93"/>
+      <c r="G12" s="93"/>
+      <c r="H12" s="93"/>
+      <c r="I12" s="93"/>
+      <c r="J12" s="159"/>
     </row>
     <row r="13" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A13" s="63"/>
-      <c r="B13" s="64"/>
-      <c r="C13" s="64"/>
-      <c r="D13" s="64"/>
-      <c r="E13" s="64"/>
-      <c r="F13" s="64"/>
-      <c r="G13" s="64"/>
-      <c r="H13" s="64"/>
-      <c r="I13" s="64"/>
-      <c r="J13" s="162"/>
+      <c r="A13" s="92"/>
+      <c r="B13" s="93"/>
+      <c r="C13" s="93"/>
+      <c r="D13" s="93"/>
+      <c r="E13" s="93"/>
+      <c r="F13" s="93"/>
+      <c r="G13" s="93"/>
+      <c r="H13" s="93"/>
+      <c r="I13" s="93"/>
+      <c r="J13" s="159"/>
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A14" s="157" t="s">
+      <c r="A14" s="155" t="s">
         <v>24</v>
       </c>
-      <c r="B14" s="79"/>
-      <c r="C14" s="79"/>
-      <c r="D14" s="79"/>
-      <c r="E14" s="79"/>
-      <c r="F14" s="79"/>
-      <c r="G14" s="79"/>
-      <c r="H14" s="79"/>
-      <c r="I14" s="79"/>
-      <c r="J14" s="82"/>
+      <c r="B14" s="66"/>
+      <c r="C14" s="66"/>
+      <c r="D14" s="66"/>
+      <c r="E14" s="66"/>
+      <c r="F14" s="66"/>
+      <c r="G14" s="66"/>
+      <c r="H14" s="66"/>
+      <c r="I14" s="66"/>
+      <c r="J14" s="67"/>
     </row>
     <row r="15" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A15" s="157" t="s">
+      <c r="A15" s="155" t="s">
         <v>25</v>
       </c>
-      <c r="B15" s="79"/>
-      <c r="C15" s="80"/>
-      <c r="D15" s="88" t="s">
+      <c r="B15" s="66"/>
+      <c r="C15" s="61"/>
+      <c r="D15" s="65" t="s">
         <v>98</v>
       </c>
-      <c r="E15" s="79"/>
-      <c r="F15" s="79"/>
-      <c r="G15" s="79"/>
-      <c r="H15" s="80"/>
+      <c r="E15" s="66"/>
+      <c r="F15" s="66"/>
+      <c r="G15" s="66"/>
+      <c r="H15" s="61"/>
       <c r="I15" s="45" t="s">
         <v>26</v>
       </c>
@@ -10198,11 +10194,11 @@
       </c>
     </row>
     <row r="16" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A16" s="157" t="s">
+      <c r="A16" s="155" t="s">
         <v>27</v>
       </c>
-      <c r="B16" s="79"/>
-      <c r="C16" s="80"/>
+      <c r="B16" s="66"/>
+      <c r="C16" s="61"/>
       <c r="D16" s="45" t="s">
         <v>28</v>
       </c>
@@ -10215,18 +10211,18 @@
       <c r="G16" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="H16" s="158" t="s">
+      <c r="H16" s="163" t="s">
         <v>18</v>
       </c>
-      <c r="I16" s="79"/>
-      <c r="J16" s="82"/>
+      <c r="I16" s="66"/>
+      <c r="J16" s="67"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="155">
+      <c r="A17" s="164">
         <v>1</v>
       </c>
-      <c r="B17" s="79"/>
-      <c r="C17" s="80"/>
+      <c r="B17" s="66"/>
+      <c r="C17" s="61"/>
       <c r="D17" s="47" t="s">
         <v>75</v>
       </c>
@@ -10239,83 +10235,83 @@
       <c r="G17" s="48" t="s">
         <v>100</v>
       </c>
-      <c r="H17" s="88" t="s">
+      <c r="H17" s="65" t="s">
         <v>101</v>
       </c>
-      <c r="I17" s="79"/>
-      <c r="J17" s="82"/>
+      <c r="I17" s="66"/>
+      <c r="J17" s="67"/>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A18" s="155"/>
-      <c r="B18" s="79"/>
-      <c r="C18" s="80"/>
+      <c r="A18" s="164"/>
+      <c r="B18" s="66"/>
+      <c r="C18" s="61"/>
       <c r="D18" s="47"/>
       <c r="E18" s="47"/>
       <c r="F18" s="48"/>
       <c r="G18" s="48"/>
-      <c r="H18" s="88"/>
-      <c r="I18" s="79"/>
-      <c r="J18" s="82"/>
+      <c r="H18" s="65"/>
+      <c r="I18" s="66"/>
+      <c r="J18" s="67"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="155"/>
-      <c r="B19" s="79"/>
-      <c r="C19" s="80"/>
+      <c r="A19" s="164"/>
+      <c r="B19" s="66"/>
+      <c r="C19" s="61"/>
       <c r="D19" s="47"/>
       <c r="E19" s="47"/>
       <c r="F19" s="48"/>
       <c r="G19" s="48"/>
-      <c r="H19" s="88"/>
-      <c r="I19" s="79"/>
-      <c r="J19" s="82"/>
+      <c r="H19" s="65"/>
+      <c r="I19" s="66"/>
+      <c r="J19" s="67"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="155"/>
-      <c r="B20" s="79"/>
-      <c r="C20" s="80"/>
+      <c r="A20" s="164"/>
+      <c r="B20" s="66"/>
+      <c r="C20" s="61"/>
       <c r="D20" s="47"/>
       <c r="E20" s="47"/>
       <c r="F20" s="48"/>
       <c r="G20" s="48"/>
-      <c r="H20" s="88"/>
-      <c r="I20" s="79"/>
-      <c r="J20" s="82"/>
+      <c r="H20" s="65"/>
+      <c r="I20" s="66"/>
+      <c r="J20" s="67"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="155"/>
-      <c r="B21" s="79"/>
-      <c r="C21" s="80"/>
+      <c r="A21" s="164"/>
+      <c r="B21" s="66"/>
+      <c r="C21" s="61"/>
       <c r="D21" s="47"/>
       <c r="E21" s="47"/>
       <c r="F21" s="48"/>
       <c r="G21" s="48"/>
-      <c r="H21" s="88"/>
-      <c r="I21" s="79"/>
-      <c r="J21" s="82"/>
+      <c r="H21" s="65"/>
+      <c r="I21" s="66"/>
+      <c r="J21" s="67"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="155"/>
-      <c r="B22" s="79"/>
-      <c r="C22" s="80"/>
+      <c r="A22" s="164"/>
+      <c r="B22" s="66"/>
+      <c r="C22" s="61"/>
       <c r="D22" s="47"/>
       <c r="E22" s="47"/>
       <c r="F22" s="48"/>
       <c r="G22" s="48"/>
-      <c r="H22" s="88"/>
-      <c r="I22" s="79"/>
-      <c r="J22" s="82"/>
+      <c r="H22" s="65"/>
+      <c r="I22" s="66"/>
+      <c r="J22" s="67"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A23" s="156"/>
-      <c r="B23" s="84"/>
-      <c r="C23" s="85"/>
+      <c r="A23" s="165"/>
+      <c r="B23" s="73"/>
+      <c r="C23" s="74"/>
       <c r="D23" s="49"/>
       <c r="E23" s="49"/>
       <c r="F23" s="50"/>
       <c r="G23" s="50"/>
-      <c r="H23" s="86"/>
-      <c r="I23" s="84"/>
-      <c r="J23" s="87"/>
+      <c r="H23" s="75"/>
+      <c r="I23" s="73"/>
+      <c r="J23" s="76"/>
     </row>
     <row r="24" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="25" spans="1:10" ht="12.75" customHeight="1"/>
@@ -11296,6 +11292,22 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="31">
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="H23:J23"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="H19:J19"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="H20:J20"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="H21:J21"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="H16:J16"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="H18:J18"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="H17:J17"/>
     <mergeCell ref="A14:J14"/>
     <mergeCell ref="A15:C15"/>
     <mergeCell ref="A7:J13"/>
@@ -11311,22 +11323,6 @@
     <mergeCell ref="D5:J5"/>
     <mergeCell ref="A6:J6"/>
     <mergeCell ref="D15:H15"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="H16:J16"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="H17:J17"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="H22:J22"/>
-    <mergeCell ref="A23:C23"/>
-    <mergeCell ref="H23:J23"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="H19:J19"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="H20:J20"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="H21:J21"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -11350,19 +11346,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="163" t="s">
+      <c r="A1" s="160" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="61"/>
-      <c r="C1" s="62"/>
-      <c r="D1" s="69" t="s">
+      <c r="B1" s="90"/>
+      <c r="C1" s="91"/>
+      <c r="D1" s="98" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="70"/>
-      <c r="F1" s="69" t="s">
+      <c r="E1" s="83"/>
+      <c r="F1" s="98" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="70"/>
+      <c r="G1" s="83"/>
       <c r="H1" s="35" t="s">
         <v>6</v>
       </c>
@@ -11374,190 +11370,190 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="63"/>
-      <c r="B2" s="64"/>
-      <c r="C2" s="65"/>
-      <c r="D2" s="71" t="s">
+      <c r="A2" s="92"/>
+      <c r="B2" s="93"/>
+      <c r="C2" s="94"/>
+      <c r="D2" s="99" t="s">
         <v>95</v>
       </c>
-      <c r="E2" s="72"/>
-      <c r="F2" s="71">
+      <c r="E2" s="100"/>
+      <c r="F2" s="99">
         <v>56</v>
       </c>
-      <c r="G2" s="72"/>
-      <c r="H2" s="75">
+      <c r="G2" s="100"/>
+      <c r="H2" s="68">
         <v>45805</v>
       </c>
-      <c r="I2" s="89" t="s">
+      <c r="I2" s="77" t="s">
         <v>94</v>
       </c>
-      <c r="J2" s="90"/>
+      <c r="J2" s="78"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="63"/>
-      <c r="B3" s="64"/>
-      <c r="C3" s="65"/>
-      <c r="D3" s="73"/>
-      <c r="E3" s="65"/>
-      <c r="F3" s="73"/>
-      <c r="G3" s="65"/>
-      <c r="H3" s="76"/>
-      <c r="I3" s="76"/>
-      <c r="J3" s="91"/>
+      <c r="A3" s="92"/>
+      <c r="B3" s="93"/>
+      <c r="C3" s="94"/>
+      <c r="D3" s="101"/>
+      <c r="E3" s="94"/>
+      <c r="F3" s="101"/>
+      <c r="G3" s="94"/>
+      <c r="H3" s="69"/>
+      <c r="I3" s="69"/>
+      <c r="J3" s="79"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="63"/>
-      <c r="B4" s="64"/>
-      <c r="C4" s="65"/>
-      <c r="D4" s="73"/>
-      <c r="E4" s="65"/>
-      <c r="F4" s="73"/>
-      <c r="G4" s="65"/>
-      <c r="H4" s="76"/>
-      <c r="I4" s="76"/>
-      <c r="J4" s="91"/>
+      <c r="A4" s="92"/>
+      <c r="B4" s="93"/>
+      <c r="C4" s="94"/>
+      <c r="D4" s="101"/>
+      <c r="E4" s="94"/>
+      <c r="F4" s="101"/>
+      <c r="G4" s="94"/>
+      <c r="H4" s="69"/>
+      <c r="I4" s="69"/>
+      <c r="J4" s="79"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="164" t="s">
+      <c r="A5" s="161" t="s">
         <v>22</v>
       </c>
-      <c r="B5" s="94"/>
-      <c r="C5" s="70"/>
-      <c r="D5" s="165" t="s">
+      <c r="B5" s="82"/>
+      <c r="C5" s="83"/>
+      <c r="D5" s="162" t="s">
         <v>102</v>
       </c>
-      <c r="E5" s="94"/>
-      <c r="F5" s="94"/>
-      <c r="G5" s="94"/>
-      <c r="H5" s="94"/>
-      <c r="I5" s="94"/>
-      <c r="J5" s="96"/>
+      <c r="E5" s="82"/>
+      <c r="F5" s="82"/>
+      <c r="G5" s="82"/>
+      <c r="H5" s="82"/>
+      <c r="I5" s="82"/>
+      <c r="J5" s="85"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="157" t="s">
+      <c r="A6" s="155" t="s">
         <v>23</v>
       </c>
-      <c r="B6" s="79"/>
-      <c r="C6" s="79"/>
-      <c r="D6" s="79"/>
-      <c r="E6" s="79"/>
-      <c r="F6" s="79"/>
-      <c r="G6" s="79"/>
-      <c r="H6" s="79"/>
-      <c r="I6" s="79"/>
-      <c r="J6" s="82"/>
+      <c r="B6" s="66"/>
+      <c r="C6" s="66"/>
+      <c r="D6" s="66"/>
+      <c r="E6" s="66"/>
+      <c r="F6" s="66"/>
+      <c r="G6" s="66"/>
+      <c r="H6" s="66"/>
+      <c r="I6" s="66"/>
+      <c r="J6" s="67"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="159"/>
-      <c r="B7" s="160"/>
-      <c r="C7" s="160"/>
-      <c r="D7" s="160"/>
-      <c r="E7" s="160"/>
-      <c r="F7" s="160"/>
-      <c r="G7" s="160"/>
-      <c r="H7" s="160"/>
-      <c r="I7" s="160"/>
-      <c r="J7" s="161"/>
+      <c r="A7" s="156"/>
+      <c r="B7" s="157"/>
+      <c r="C7" s="157"/>
+      <c r="D7" s="157"/>
+      <c r="E7" s="157"/>
+      <c r="F7" s="157"/>
+      <c r="G7" s="157"/>
+      <c r="H7" s="157"/>
+      <c r="I7" s="157"/>
+      <c r="J7" s="158"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="63"/>
-      <c r="B8" s="64"/>
-      <c r="C8" s="64"/>
-      <c r="D8" s="64"/>
-      <c r="E8" s="64"/>
-      <c r="F8" s="64"/>
-      <c r="G8" s="64"/>
-      <c r="H8" s="64"/>
-      <c r="I8" s="64"/>
-      <c r="J8" s="162"/>
+      <c r="A8" s="92"/>
+      <c r="B8" s="93"/>
+      <c r="C8" s="93"/>
+      <c r="D8" s="93"/>
+      <c r="E8" s="93"/>
+      <c r="F8" s="93"/>
+      <c r="G8" s="93"/>
+      <c r="H8" s="93"/>
+      <c r="I8" s="93"/>
+      <c r="J8" s="159"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="63"/>
-      <c r="B9" s="64"/>
-      <c r="C9" s="64"/>
-      <c r="D9" s="64"/>
-      <c r="E9" s="64"/>
-      <c r="F9" s="64"/>
-      <c r="G9" s="64"/>
-      <c r="H9" s="64"/>
-      <c r="I9" s="64"/>
-      <c r="J9" s="162"/>
+      <c r="A9" s="92"/>
+      <c r="B9" s="93"/>
+      <c r="C9" s="93"/>
+      <c r="D9" s="93"/>
+      <c r="E9" s="93"/>
+      <c r="F9" s="93"/>
+      <c r="G9" s="93"/>
+      <c r="H9" s="93"/>
+      <c r="I9" s="93"/>
+      <c r="J9" s="159"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="63"/>
-      <c r="B10" s="64"/>
-      <c r="C10" s="64"/>
-      <c r="D10" s="64"/>
-      <c r="E10" s="64"/>
-      <c r="F10" s="64"/>
-      <c r="G10" s="64"/>
-      <c r="H10" s="64"/>
-      <c r="I10" s="64"/>
-      <c r="J10" s="162"/>
+      <c r="A10" s="92"/>
+      <c r="B10" s="93"/>
+      <c r="C10" s="93"/>
+      <c r="D10" s="93"/>
+      <c r="E10" s="93"/>
+      <c r="F10" s="93"/>
+      <c r="G10" s="93"/>
+      <c r="H10" s="93"/>
+      <c r="I10" s="93"/>
+      <c r="J10" s="159"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="63"/>
-      <c r="B11" s="64"/>
-      <c r="C11" s="64"/>
-      <c r="D11" s="64"/>
-      <c r="E11" s="64"/>
-      <c r="F11" s="64"/>
-      <c r="G11" s="64"/>
-      <c r="H11" s="64"/>
-      <c r="I11" s="64"/>
-      <c r="J11" s="162"/>
+      <c r="A11" s="92"/>
+      <c r="B11" s="93"/>
+      <c r="C11" s="93"/>
+      <c r="D11" s="93"/>
+      <c r="E11" s="93"/>
+      <c r="F11" s="93"/>
+      <c r="G11" s="93"/>
+      <c r="H11" s="93"/>
+      <c r="I11" s="93"/>
+      <c r="J11" s="159"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="63"/>
-      <c r="B12" s="64"/>
-      <c r="C12" s="64"/>
-      <c r="D12" s="64"/>
-      <c r="E12" s="64"/>
-      <c r="F12" s="64"/>
-      <c r="G12" s="64"/>
-      <c r="H12" s="64"/>
-      <c r="I12" s="64"/>
-      <c r="J12" s="162"/>
+      <c r="A12" s="92"/>
+      <c r="B12" s="93"/>
+      <c r="C12" s="93"/>
+      <c r="D12" s="93"/>
+      <c r="E12" s="93"/>
+      <c r="F12" s="93"/>
+      <c r="G12" s="93"/>
+      <c r="H12" s="93"/>
+      <c r="I12" s="93"/>
+      <c r="J12" s="159"/>
     </row>
     <row r="13" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A13" s="63"/>
-      <c r="B13" s="64"/>
-      <c r="C13" s="64"/>
-      <c r="D13" s="64"/>
-      <c r="E13" s="64"/>
-      <c r="F13" s="64"/>
-      <c r="G13" s="64"/>
-      <c r="H13" s="64"/>
-      <c r="I13" s="64"/>
-      <c r="J13" s="162"/>
+      <c r="A13" s="92"/>
+      <c r="B13" s="93"/>
+      <c r="C13" s="93"/>
+      <c r="D13" s="93"/>
+      <c r="E13" s="93"/>
+      <c r="F13" s="93"/>
+      <c r="G13" s="93"/>
+      <c r="H13" s="93"/>
+      <c r="I13" s="93"/>
+      <c r="J13" s="159"/>
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A14" s="157" t="s">
+      <c r="A14" s="155" t="s">
         <v>24</v>
       </c>
-      <c r="B14" s="79"/>
-      <c r="C14" s="79"/>
-      <c r="D14" s="79"/>
-      <c r="E14" s="79"/>
-      <c r="F14" s="79"/>
-      <c r="G14" s="79"/>
-      <c r="H14" s="79"/>
-      <c r="I14" s="79"/>
-      <c r="J14" s="82"/>
+      <c r="B14" s="66"/>
+      <c r="C14" s="66"/>
+      <c r="D14" s="66"/>
+      <c r="E14" s="66"/>
+      <c r="F14" s="66"/>
+      <c r="G14" s="66"/>
+      <c r="H14" s="66"/>
+      <c r="I14" s="66"/>
+      <c r="J14" s="67"/>
     </row>
     <row r="15" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A15" s="157" t="s">
+      <c r="A15" s="155" t="s">
         <v>25</v>
       </c>
-      <c r="B15" s="79"/>
-      <c r="C15" s="80"/>
-      <c r="D15" s="88" t="s">
+      <c r="B15" s="66"/>
+      <c r="C15" s="61"/>
+      <c r="D15" s="65" t="s">
         <v>98</v>
       </c>
-      <c r="E15" s="79"/>
-      <c r="F15" s="79"/>
-      <c r="G15" s="79"/>
-      <c r="H15" s="80"/>
+      <c r="E15" s="66"/>
+      <c r="F15" s="66"/>
+      <c r="G15" s="66"/>
+      <c r="H15" s="61"/>
       <c r="I15" s="45" t="s">
         <v>26</v>
       </c>
@@ -11566,11 +11562,11 @@
       </c>
     </row>
     <row r="16" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A16" s="157" t="s">
+      <c r="A16" s="155" t="s">
         <v>27</v>
       </c>
-      <c r="B16" s="79"/>
-      <c r="C16" s="80"/>
+      <c r="B16" s="66"/>
+      <c r="C16" s="61"/>
       <c r="D16" s="45" t="s">
         <v>28</v>
       </c>
@@ -11583,18 +11579,18 @@
       <c r="G16" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="H16" s="158" t="s">
+      <c r="H16" s="163" t="s">
         <v>18</v>
       </c>
-      <c r="I16" s="79"/>
-      <c r="J16" s="82"/>
+      <c r="I16" s="66"/>
+      <c r="J16" s="67"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="155">
+      <c r="A17" s="164">
         <v>1</v>
       </c>
-      <c r="B17" s="79"/>
-      <c r="C17" s="80"/>
+      <c r="B17" s="66"/>
+      <c r="C17" s="61"/>
       <c r="D17" s="47" t="s">
         <v>75</v>
       </c>
@@ -11607,83 +11603,83 @@
       <c r="G17" s="48" t="s">
         <v>100</v>
       </c>
-      <c r="H17" s="88" t="s">
+      <c r="H17" s="65" t="s">
         <v>101</v>
       </c>
-      <c r="I17" s="79"/>
-      <c r="J17" s="82"/>
+      <c r="I17" s="66"/>
+      <c r="J17" s="67"/>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A18" s="155"/>
-      <c r="B18" s="79"/>
-      <c r="C18" s="80"/>
+      <c r="A18" s="164"/>
+      <c r="B18" s="66"/>
+      <c r="C18" s="61"/>
       <c r="D18" s="47"/>
       <c r="E18" s="47"/>
       <c r="F18" s="48"/>
       <c r="G18" s="48"/>
-      <c r="H18" s="88"/>
-      <c r="I18" s="79"/>
-      <c r="J18" s="82"/>
+      <c r="H18" s="65"/>
+      <c r="I18" s="66"/>
+      <c r="J18" s="67"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="155"/>
-      <c r="B19" s="79"/>
-      <c r="C19" s="80"/>
+      <c r="A19" s="164"/>
+      <c r="B19" s="66"/>
+      <c r="C19" s="61"/>
       <c r="D19" s="47"/>
       <c r="E19" s="47"/>
       <c r="F19" s="48"/>
       <c r="G19" s="48"/>
-      <c r="H19" s="88"/>
-      <c r="I19" s="79"/>
-      <c r="J19" s="82"/>
+      <c r="H19" s="65"/>
+      <c r="I19" s="66"/>
+      <c r="J19" s="67"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="155"/>
-      <c r="B20" s="79"/>
-      <c r="C20" s="80"/>
+      <c r="A20" s="164"/>
+      <c r="B20" s="66"/>
+      <c r="C20" s="61"/>
       <c r="D20" s="47"/>
       <c r="E20" s="47"/>
       <c r="F20" s="48"/>
       <c r="G20" s="48"/>
-      <c r="H20" s="88"/>
-      <c r="I20" s="79"/>
-      <c r="J20" s="82"/>
+      <c r="H20" s="65"/>
+      <c r="I20" s="66"/>
+      <c r="J20" s="67"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="155"/>
-      <c r="B21" s="79"/>
-      <c r="C21" s="80"/>
+      <c r="A21" s="164"/>
+      <c r="B21" s="66"/>
+      <c r="C21" s="61"/>
       <c r="D21" s="47"/>
       <c r="E21" s="47"/>
       <c r="F21" s="48"/>
       <c r="G21" s="48"/>
-      <c r="H21" s="88"/>
-      <c r="I21" s="79"/>
-      <c r="J21" s="82"/>
+      <c r="H21" s="65"/>
+      <c r="I21" s="66"/>
+      <c r="J21" s="67"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="155"/>
-      <c r="B22" s="79"/>
-      <c r="C22" s="80"/>
+      <c r="A22" s="164"/>
+      <c r="B22" s="66"/>
+      <c r="C22" s="61"/>
       <c r="D22" s="47"/>
       <c r="E22" s="47"/>
       <c r="F22" s="48"/>
       <c r="G22" s="48"/>
-      <c r="H22" s="88"/>
-      <c r="I22" s="79"/>
-      <c r="J22" s="82"/>
+      <c r="H22" s="65"/>
+      <c r="I22" s="66"/>
+      <c r="J22" s="67"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A23" s="156"/>
-      <c r="B23" s="84"/>
-      <c r="C23" s="85"/>
+      <c r="A23" s="165"/>
+      <c r="B23" s="73"/>
+      <c r="C23" s="74"/>
       <c r="D23" s="49"/>
       <c r="E23" s="49"/>
       <c r="F23" s="50"/>
       <c r="G23" s="50"/>
-      <c r="H23" s="86"/>
-      <c r="I23" s="84"/>
-      <c r="J23" s="87"/>
+      <c r="H23" s="75"/>
+      <c r="I23" s="73"/>
+      <c r="J23" s="76"/>
     </row>
     <row r="24" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="25" spans="1:10" ht="12.75" customHeight="1"/>
@@ -12664,6 +12660,22 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="31">
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="H23:J23"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="H19:J19"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="H20:J20"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="H21:J21"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="H16:J16"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="H18:J18"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="H17:J17"/>
     <mergeCell ref="A14:J14"/>
     <mergeCell ref="A15:C15"/>
     <mergeCell ref="A7:J13"/>
@@ -12679,22 +12691,6 @@
     <mergeCell ref="D5:J5"/>
     <mergeCell ref="A6:J6"/>
     <mergeCell ref="D15:H15"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="H16:J16"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="H17:J17"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="H22:J22"/>
-    <mergeCell ref="A23:C23"/>
-    <mergeCell ref="H23:J23"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="H19:J19"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="H20:J20"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="H21:J21"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -12714,7 +12710,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="18" customHeight="1">
-      <c r="A1" s="177" t="s">
+      <c r="A1" s="189" t="s">
         <v>32</v>
       </c>
       <c r="B1" s="111"/>
@@ -12725,14 +12721,14 @@
       <c r="G1" s="118" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="178"/>
-      <c r="I1" s="178"/>
+      <c r="H1" s="175"/>
+      <c r="I1" s="175"/>
       <c r="J1" s="119"/>
       <c r="K1" s="118" t="s">
         <v>5</v>
       </c>
-      <c r="L1" s="178"/>
-      <c r="M1" s="178"/>
+      <c r="L1" s="175"/>
+      <c r="M1" s="175"/>
       <c r="N1" s="119"/>
       <c r="O1" s="118" t="s">
         <v>6</v>
@@ -12745,7 +12741,7 @@
       <c r="S1" s="118" t="s">
         <v>8</v>
       </c>
-      <c r="T1" s="179"/>
+      <c r="T1" s="177"/>
     </row>
     <row r="2" spans="1:26" ht="18" customHeight="1">
       <c r="A2" s="113"/>
@@ -12755,19 +12751,19 @@
       <c r="E2" s="55"/>
       <c r="F2" s="114"/>
       <c r="G2" s="120"/>
-      <c r="H2" s="173"/>
-      <c r="I2" s="173"/>
+      <c r="H2" s="185"/>
+      <c r="I2" s="185"/>
       <c r="J2" s="121"/>
       <c r="K2" s="120"/>
-      <c r="L2" s="173"/>
-      <c r="M2" s="173"/>
+      <c r="L2" s="185"/>
+      <c r="M2" s="185"/>
       <c r="N2" s="121"/>
       <c r="O2" s="120"/>
       <c r="P2" s="121"/>
       <c r="Q2" s="120"/>
       <c r="R2" s="121"/>
       <c r="S2" s="120"/>
-      <c r="T2" s="174"/>
+      <c r="T2" s="186"/>
     </row>
     <row r="3" spans="1:26" ht="18" customHeight="1">
       <c r="A3" s="113"/>
@@ -12789,7 +12785,7 @@
       <c r="Q3" s="122"/>
       <c r="R3" s="114"/>
       <c r="S3" s="122"/>
-      <c r="T3" s="175"/>
+      <c r="T3" s="187"/>
     </row>
     <row r="4" spans="1:26" ht="18" customHeight="1">
       <c r="A4" s="115"/>
@@ -12811,36 +12807,36 @@
       <c r="Q4" s="123"/>
       <c r="R4" s="117"/>
       <c r="S4" s="123"/>
-      <c r="T4" s="176"/>
+      <c r="T4" s="188"/>
     </row>
     <row r="5" spans="1:26" ht="18" customHeight="1">
-      <c r="A5" s="180" t="s">
+      <c r="A5" s="174" t="s">
         <v>33</v>
       </c>
-      <c r="B5" s="178"/>
-      <c r="C5" s="178"/>
-      <c r="D5" s="178"/>
-      <c r="E5" s="178"/>
+      <c r="B5" s="175"/>
+      <c r="C5" s="175"/>
+      <c r="D5" s="175"/>
+      <c r="E5" s="175"/>
       <c r="F5" s="119"/>
-      <c r="G5" s="181" t="s">
+      <c r="G5" s="176" t="s">
         <v>34</v>
       </c>
-      <c r="H5" s="178"/>
-      <c r="I5" s="178"/>
-      <c r="J5" s="178"/>
-      <c r="K5" s="178"/>
-      <c r="L5" s="178"/>
-      <c r="M5" s="178"/>
-      <c r="N5" s="178"/>
-      <c r="O5" s="178"/>
-      <c r="P5" s="178"/>
-      <c r="Q5" s="178"/>
-      <c r="R5" s="178"/>
-      <c r="S5" s="178"/>
-      <c r="T5" s="179"/>
+      <c r="H5" s="175"/>
+      <c r="I5" s="175"/>
+      <c r="J5" s="175"/>
+      <c r="K5" s="175"/>
+      <c r="L5" s="175"/>
+      <c r="M5" s="175"/>
+      <c r="N5" s="175"/>
+      <c r="O5" s="175"/>
+      <c r="P5" s="175"/>
+      <c r="Q5" s="175"/>
+      <c r="R5" s="175"/>
+      <c r="S5" s="175"/>
+      <c r="T5" s="177"/>
     </row>
     <row r="6" spans="1:26" ht="18" customHeight="1">
-      <c r="A6" s="182" t="s">
+      <c r="A6" s="178" t="s">
         <v>35</v>
       </c>
       <c r="B6" s="52"/>
@@ -12848,7 +12844,7 @@
       <c r="D6" s="52"/>
       <c r="E6" s="52"/>
       <c r="F6" s="53"/>
-      <c r="G6" s="183" t="s">
+      <c r="G6" s="179" t="s">
         <v>19</v>
       </c>
       <c r="H6" s="52"/>
@@ -12863,10 +12859,10 @@
       <c r="Q6" s="52"/>
       <c r="R6" s="52"/>
       <c r="S6" s="52"/>
-      <c r="T6" s="184"/>
+      <c r="T6" s="180"/>
     </row>
     <row r="7" spans="1:26" ht="18" customHeight="1">
-      <c r="A7" s="182" t="s">
+      <c r="A7" s="178" t="s">
         <v>36</v>
       </c>
       <c r="B7" s="52"/>
@@ -12874,7 +12870,7 @@
       <c r="D7" s="52"/>
       <c r="E7" s="52"/>
       <c r="F7" s="53"/>
-      <c r="G7" s="183" t="s">
+      <c r="G7" s="179" t="s">
         <v>37</v>
       </c>
       <c r="H7" s="52"/>
@@ -12889,7 +12885,7 @@
       <c r="Q7" s="52"/>
       <c r="R7" s="52"/>
       <c r="S7" s="52"/>
-      <c r="T7" s="184"/>
+      <c r="T7" s="180"/>
     </row>
     <row r="8" spans="1:26" ht="7.5" customHeight="1">
       <c r="A8" s="7"/>
@@ -13088,33 +13084,33 @@
       <c r="T14" s="9"/>
     </row>
     <row r="15" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A15" s="182" t="s">
+      <c r="A15" s="178" t="s">
         <v>44</v>
       </c>
       <c r="B15" s="53"/>
-      <c r="C15" s="188" t="s">
+      <c r="C15" s="184" t="s">
         <v>38</v>
       </c>
       <c r="D15" s="53"/>
-      <c r="E15" s="166" t="s">
+      <c r="E15" s="182" t="s">
         <v>45</v>
       </c>
       <c r="F15" s="53"/>
-      <c r="G15" s="166" t="s">
+      <c r="G15" s="182" t="s">
         <v>46</v>
       </c>
       <c r="H15" s="52"/>
       <c r="I15" s="53"/>
-      <c r="J15" s="166" t="s">
+      <c r="J15" s="182" t="s">
         <v>47</v>
       </c>
       <c r="K15" s="53"/>
-      <c r="L15" s="166" t="s">
+      <c r="L15" s="182" t="s">
         <v>48</v>
       </c>
       <c r="M15" s="52"/>
       <c r="N15" s="53"/>
-      <c r="O15" s="166" t="s">
+      <c r="O15" s="182" t="s">
         <v>49</v>
       </c>
       <c r="P15" s="52"/>
@@ -13130,28 +13126,28 @@
       </c>
     </row>
     <row r="16" spans="1:26" ht="48" customHeight="1">
-      <c r="A16" s="185">
+      <c r="A16" s="166">
         <v>1</v>
       </c>
       <c r="B16" s="53"/>
-      <c r="C16" s="186" t="s">
+      <c r="C16" s="167" t="s">
         <v>53</v>
       </c>
       <c r="D16" s="53"/>
-      <c r="E16" s="186" t="s">
+      <c r="E16" s="167" t="s">
         <v>54</v>
       </c>
       <c r="F16" s="53"/>
-      <c r="G16" s="167" t="s">
+      <c r="G16" s="181" t="s">
         <v>55</v>
       </c>
       <c r="H16" s="52"/>
       <c r="I16" s="53"/>
-      <c r="J16" s="167" t="s">
+      <c r="J16" s="181" t="s">
         <v>56</v>
       </c>
       <c r="K16" s="53"/>
-      <c r="L16" s="187" t="s">
+      <c r="L16" s="183" t="s">
         <v>65</v>
       </c>
       <c r="M16" s="52"/>
@@ -13172,24 +13168,24 @@
       <c r="Z16" s="29"/>
     </row>
     <row r="17" spans="1:26" ht="41.25" customHeight="1">
-      <c r="A17" s="185">
+      <c r="A17" s="166">
         <v>2</v>
       </c>
       <c r="B17" s="53"/>
-      <c r="C17" s="186" t="s">
+      <c r="C17" s="167" t="s">
         <v>58</v>
       </c>
       <c r="D17" s="53"/>
-      <c r="E17" s="186" t="s">
+      <c r="E17" s="167" t="s">
         <v>59</v>
       </c>
       <c r="F17" s="53"/>
-      <c r="G17" s="167" t="s">
+      <c r="G17" s="181" t="s">
         <v>60</v>
       </c>
       <c r="H17" s="52"/>
       <c r="I17" s="53"/>
-      <c r="J17" s="167" t="s">
+      <c r="J17" s="181" t="s">
         <v>61</v>
       </c>
       <c r="K17" s="53"/>
@@ -13214,16 +13210,16 @@
       <c r="Z17" s="29"/>
     </row>
     <row r="18" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A18" s="185"/>
+      <c r="A18" s="166"/>
       <c r="B18" s="53"/>
-      <c r="C18" s="186"/>
+      <c r="C18" s="167"/>
       <c r="D18" s="53"/>
-      <c r="E18" s="186"/>
+      <c r="E18" s="167"/>
       <c r="F18" s="53"/>
-      <c r="G18" s="167"/>
+      <c r="G18" s="181"/>
       <c r="H18" s="52"/>
       <c r="I18" s="53"/>
-      <c r="J18" s="167"/>
+      <c r="J18" s="181"/>
       <c r="K18" s="53"/>
       <c r="L18" s="171"/>
       <c r="M18" s="52"/>
@@ -13242,16 +13238,16 @@
       <c r="Z18" s="29"/>
     </row>
     <row r="19" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A19" s="185"/>
+      <c r="A19" s="166"/>
       <c r="B19" s="53"/>
-      <c r="C19" s="186"/>
+      <c r="C19" s="167"/>
       <c r="D19" s="53"/>
-      <c r="E19" s="186"/>
+      <c r="E19" s="167"/>
       <c r="F19" s="53"/>
-      <c r="G19" s="167"/>
+      <c r="G19" s="181"/>
       <c r="H19" s="52"/>
       <c r="I19" s="53"/>
-      <c r="J19" s="167"/>
+      <c r="J19" s="181"/>
       <c r="K19" s="53"/>
       <c r="L19" s="171"/>
       <c r="M19" s="52"/>
@@ -13270,16 +13266,16 @@
       <c r="Z19" s="29"/>
     </row>
     <row r="20" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A20" s="185"/>
+      <c r="A20" s="166"/>
       <c r="B20" s="53"/>
-      <c r="C20" s="186"/>
+      <c r="C20" s="167"/>
       <c r="D20" s="53"/>
-      <c r="E20" s="186"/>
+      <c r="E20" s="167"/>
       <c r="F20" s="53"/>
-      <c r="G20" s="167"/>
+      <c r="G20" s="181"/>
       <c r="H20" s="52"/>
       <c r="I20" s="53"/>
-      <c r="J20" s="167"/>
+      <c r="J20" s="181"/>
       <c r="K20" s="53"/>
       <c r="L20" s="171"/>
       <c r="M20" s="52"/>
@@ -13298,16 +13294,16 @@
       <c r="Z20" s="29"/>
     </row>
     <row r="21" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A21" s="185"/>
+      <c r="A21" s="166"/>
       <c r="B21" s="53"/>
-      <c r="C21" s="186"/>
+      <c r="C21" s="167"/>
       <c r="D21" s="53"/>
-      <c r="E21" s="186"/>
+      <c r="E21" s="167"/>
       <c r="F21" s="53"/>
-      <c r="G21" s="167"/>
+      <c r="G21" s="181"/>
       <c r="H21" s="52"/>
       <c r="I21" s="53"/>
-      <c r="J21" s="167"/>
+      <c r="J21" s="181"/>
       <c r="K21" s="53"/>
       <c r="L21" s="171"/>
       <c r="M21" s="52"/>
@@ -13326,16 +13322,16 @@
       <c r="Z21" s="29"/>
     </row>
     <row r="22" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A22" s="185"/>
+      <c r="A22" s="166"/>
       <c r="B22" s="53"/>
-      <c r="C22" s="186"/>
+      <c r="C22" s="167"/>
       <c r="D22" s="53"/>
-      <c r="E22" s="186"/>
+      <c r="E22" s="167"/>
       <c r="F22" s="53"/>
-      <c r="G22" s="167"/>
+      <c r="G22" s="181"/>
       <c r="H22" s="52"/>
       <c r="I22" s="53"/>
-      <c r="J22" s="167"/>
+      <c r="J22" s="181"/>
       <c r="K22" s="53"/>
       <c r="L22" s="171"/>
       <c r="M22" s="52"/>
@@ -13354,16 +13350,16 @@
       <c r="Z22" s="29"/>
     </row>
     <row r="23" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A23" s="185"/>
+      <c r="A23" s="166"/>
       <c r="B23" s="53"/>
-      <c r="C23" s="186"/>
+      <c r="C23" s="167"/>
       <c r="D23" s="53"/>
-      <c r="E23" s="186"/>
+      <c r="E23" s="167"/>
       <c r="F23" s="53"/>
-      <c r="G23" s="167"/>
+      <c r="G23" s="181"/>
       <c r="H23" s="52"/>
       <c r="I23" s="53"/>
-      <c r="J23" s="167"/>
+      <c r="J23" s="181"/>
       <c r="K23" s="53"/>
       <c r="L23" s="171"/>
       <c r="M23" s="52"/>
@@ -13382,16 +13378,16 @@
       <c r="Z23" s="29"/>
     </row>
     <row r="24" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A24" s="185"/>
+      <c r="A24" s="166"/>
       <c r="B24" s="53"/>
-      <c r="C24" s="186"/>
+      <c r="C24" s="167"/>
       <c r="D24" s="53"/>
-      <c r="E24" s="186"/>
+      <c r="E24" s="167"/>
       <c r="F24" s="53"/>
-      <c r="G24" s="167"/>
+      <c r="G24" s="181"/>
       <c r="H24" s="52"/>
       <c r="I24" s="53"/>
-      <c r="J24" s="167"/>
+      <c r="J24" s="181"/>
       <c r="K24" s="53"/>
       <c r="L24" s="171"/>
       <c r="M24" s="52"/>
@@ -13410,16 +13406,16 @@
       <c r="Z24" s="29"/>
     </row>
     <row r="25" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A25" s="185"/>
+      <c r="A25" s="166"/>
       <c r="B25" s="53"/>
-      <c r="C25" s="186"/>
+      <c r="C25" s="167"/>
       <c r="D25" s="53"/>
-      <c r="E25" s="186"/>
+      <c r="E25" s="167"/>
       <c r="F25" s="53"/>
-      <c r="G25" s="167"/>
+      <c r="G25" s="181"/>
       <c r="H25" s="52"/>
       <c r="I25" s="53"/>
-      <c r="J25" s="167"/>
+      <c r="J25" s="181"/>
       <c r="K25" s="53"/>
       <c r="L25" s="171"/>
       <c r="M25" s="52"/>
@@ -13438,16 +13434,16 @@
       <c r="Z25" s="29"/>
     </row>
     <row r="26" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A26" s="185"/>
+      <c r="A26" s="166"/>
       <c r="B26" s="53"/>
-      <c r="C26" s="186"/>
+      <c r="C26" s="167"/>
       <c r="D26" s="53"/>
-      <c r="E26" s="186"/>
+      <c r="E26" s="167"/>
       <c r="F26" s="53"/>
-      <c r="G26" s="167"/>
+      <c r="G26" s="181"/>
       <c r="H26" s="52"/>
       <c r="I26" s="53"/>
-      <c r="J26" s="167"/>
+      <c r="J26" s="181"/>
       <c r="K26" s="53"/>
       <c r="L26" s="171"/>
       <c r="M26" s="52"/>
@@ -13466,16 +13462,16 @@
       <c r="Z26" s="29"/>
     </row>
     <row r="27" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A27" s="185"/>
+      <c r="A27" s="166"/>
       <c r="B27" s="53"/>
-      <c r="C27" s="186"/>
+      <c r="C27" s="167"/>
       <c r="D27" s="53"/>
-      <c r="E27" s="186"/>
+      <c r="E27" s="167"/>
       <c r="F27" s="53"/>
-      <c r="G27" s="167"/>
+      <c r="G27" s="181"/>
       <c r="H27" s="52"/>
       <c r="I27" s="53"/>
-      <c r="J27" s="167"/>
+      <c r="J27" s="181"/>
       <c r="K27" s="53"/>
       <c r="L27" s="171"/>
       <c r="M27" s="52"/>
@@ -13494,16 +13490,16 @@
       <c r="Z27" s="29"/>
     </row>
     <row r="28" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A28" s="185"/>
+      <c r="A28" s="166"/>
       <c r="B28" s="53"/>
-      <c r="C28" s="186"/>
+      <c r="C28" s="167"/>
       <c r="D28" s="53"/>
-      <c r="E28" s="186"/>
+      <c r="E28" s="167"/>
       <c r="F28" s="53"/>
-      <c r="G28" s="167"/>
+      <c r="G28" s="181"/>
       <c r="H28" s="52"/>
       <c r="I28" s="53"/>
-      <c r="J28" s="167"/>
+      <c r="J28" s="181"/>
       <c r="K28" s="53"/>
       <c r="L28" s="171"/>
       <c r="M28" s="52"/>
@@ -13522,16 +13518,16 @@
       <c r="Z28" s="29"/>
     </row>
     <row r="29" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A29" s="185"/>
+      <c r="A29" s="166"/>
       <c r="B29" s="53"/>
-      <c r="C29" s="186"/>
+      <c r="C29" s="167"/>
       <c r="D29" s="53"/>
-      <c r="E29" s="186"/>
+      <c r="E29" s="167"/>
       <c r="F29" s="53"/>
-      <c r="G29" s="167"/>
+      <c r="G29" s="181"/>
       <c r="H29" s="52"/>
       <c r="I29" s="53"/>
-      <c r="J29" s="167"/>
+      <c r="J29" s="181"/>
       <c r="K29" s="53"/>
       <c r="L29" s="171"/>
       <c r="M29" s="52"/>
@@ -13550,16 +13546,16 @@
       <c r="Z29" s="29"/>
     </row>
     <row r="30" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A30" s="185"/>
+      <c r="A30" s="166"/>
       <c r="B30" s="53"/>
-      <c r="C30" s="186"/>
+      <c r="C30" s="167"/>
       <c r="D30" s="53"/>
-      <c r="E30" s="186"/>
+      <c r="E30" s="167"/>
       <c r="F30" s="53"/>
-      <c r="G30" s="167"/>
+      <c r="G30" s="181"/>
       <c r="H30" s="52"/>
       <c r="I30" s="53"/>
-      <c r="J30" s="167"/>
+      <c r="J30" s="181"/>
       <c r="K30" s="53"/>
       <c r="L30" s="171"/>
       <c r="M30" s="52"/>
@@ -13578,23 +13574,23 @@
       <c r="Z30" s="29"/>
     </row>
     <row r="31" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A31" s="189"/>
-      <c r="B31" s="170"/>
-      <c r="C31" s="190"/>
-      <c r="D31" s="170"/>
-      <c r="E31" s="190"/>
-      <c r="F31" s="170"/>
-      <c r="G31" s="168"/>
-      <c r="H31" s="169"/>
-      <c r="I31" s="170"/>
-      <c r="J31" s="168"/>
-      <c r="K31" s="170"/>
+      <c r="A31" s="168"/>
+      <c r="B31" s="169"/>
+      <c r="C31" s="170"/>
+      <c r="D31" s="169"/>
+      <c r="E31" s="170"/>
+      <c r="F31" s="169"/>
+      <c r="G31" s="190"/>
+      <c r="H31" s="173"/>
+      <c r="I31" s="169"/>
+      <c r="J31" s="190"/>
+      <c r="K31" s="169"/>
       <c r="L31" s="172"/>
-      <c r="M31" s="169"/>
-      <c r="N31" s="170"/>
+      <c r="M31" s="173"/>
+      <c r="N31" s="169"/>
       <c r="O31" s="172"/>
-      <c r="P31" s="169"/>
-      <c r="Q31" s="170"/>
+      <c r="P31" s="173"/>
+      <c r="Q31" s="169"/>
       <c r="R31" s="30"/>
       <c r="S31" s="30"/>
       <c r="T31" s="31"/>
@@ -14592,6 +14588,118 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="136">
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="J19:K19"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="J30:K30"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="J29:K29"/>
+    <mergeCell ref="L26:N26"/>
+    <mergeCell ref="L27:N27"/>
+    <mergeCell ref="L28:N28"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="L18:N18"/>
+    <mergeCell ref="L19:N19"/>
+    <mergeCell ref="L21:N21"/>
+    <mergeCell ref="L22:N22"/>
+    <mergeCell ref="L23:N23"/>
+    <mergeCell ref="L24:N24"/>
+    <mergeCell ref="L25:N25"/>
+    <mergeCell ref="K2:N4"/>
+    <mergeCell ref="O2:P4"/>
+    <mergeCell ref="Q2:R4"/>
+    <mergeCell ref="S2:T4"/>
+    <mergeCell ref="A1:F4"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="S1:T1"/>
+    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="G5:T5"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="G6:T6"/>
+    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="G7:T7"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="G20:I20"/>
+    <mergeCell ref="J20:K20"/>
+    <mergeCell ref="L20:N20"/>
+    <mergeCell ref="O20:Q20"/>
+    <mergeCell ref="L15:N15"/>
+    <mergeCell ref="O15:Q15"/>
+    <mergeCell ref="L16:N16"/>
+    <mergeCell ref="O16:Q16"/>
+    <mergeCell ref="L17:N17"/>
+    <mergeCell ref="O17:Q17"/>
+    <mergeCell ref="O18:Q18"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="O27:Q27"/>
+    <mergeCell ref="O28:Q28"/>
+    <mergeCell ref="O29:Q29"/>
+    <mergeCell ref="O30:Q30"/>
+    <mergeCell ref="O31:Q31"/>
+    <mergeCell ref="O19:Q19"/>
+    <mergeCell ref="O21:Q21"/>
+    <mergeCell ref="O22:Q22"/>
+    <mergeCell ref="O23:Q23"/>
+    <mergeCell ref="O24:Q24"/>
+    <mergeCell ref="O25:Q25"/>
+    <mergeCell ref="O26:Q26"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="A23:B23"/>
     <mergeCell ref="A30:B30"/>
     <mergeCell ref="C30:D30"/>
     <mergeCell ref="E30:F30"/>
@@ -14616,118 +14724,6 @@
     <mergeCell ref="C28:D28"/>
     <mergeCell ref="E28:F28"/>
     <mergeCell ref="A29:B29"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="O27:Q27"/>
-    <mergeCell ref="O28:Q28"/>
-    <mergeCell ref="O29:Q29"/>
-    <mergeCell ref="O30:Q30"/>
-    <mergeCell ref="O31:Q31"/>
-    <mergeCell ref="O19:Q19"/>
-    <mergeCell ref="O21:Q21"/>
-    <mergeCell ref="O22:Q22"/>
-    <mergeCell ref="O23:Q23"/>
-    <mergeCell ref="O24:Q24"/>
-    <mergeCell ref="O25:Q25"/>
-    <mergeCell ref="O26:Q26"/>
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="G5:T5"/>
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="G6:T6"/>
-    <mergeCell ref="A7:F7"/>
-    <mergeCell ref="G7:T7"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="G20:I20"/>
-    <mergeCell ref="J20:K20"/>
-    <mergeCell ref="L20:N20"/>
-    <mergeCell ref="O20:Q20"/>
-    <mergeCell ref="L15:N15"/>
-    <mergeCell ref="O15:Q15"/>
-    <mergeCell ref="L16:N16"/>
-    <mergeCell ref="O16:Q16"/>
-    <mergeCell ref="L17:N17"/>
-    <mergeCell ref="O17:Q17"/>
-    <mergeCell ref="O18:Q18"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="K2:N4"/>
-    <mergeCell ref="O2:P4"/>
-    <mergeCell ref="Q2:R4"/>
-    <mergeCell ref="S2:T4"/>
-    <mergeCell ref="A1:F4"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="O1:P1"/>
-    <mergeCell ref="Q1:R1"/>
-    <mergeCell ref="S1:T1"/>
-    <mergeCell ref="G2:J4"/>
-    <mergeCell ref="L26:N26"/>
-    <mergeCell ref="L27:N27"/>
-    <mergeCell ref="L28:N28"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="L18:N18"/>
-    <mergeCell ref="L19:N19"/>
-    <mergeCell ref="L21:N21"/>
-    <mergeCell ref="L22:N22"/>
-    <mergeCell ref="L23:N23"/>
-    <mergeCell ref="L24:N24"/>
-    <mergeCell ref="L25:N25"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="J30:K30"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="J29:K29"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="G23:I23"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="J18:K18"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="J19:K19"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <hyperlinks>

--- a/Documents/登録機能詳細設計書.xlsx
+++ b/Documents/登録機能詳細設計書.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\S-47\Documents\project\taskUN\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DA7AF9D-EE18-4DFA-8926-EF9C3830F55F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECE2A32F-20AD-42C9-9041-DB27B370F8F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="1" r:id="rId1"/>
@@ -1726,135 +1726,135 @@
     <xf numFmtId="14" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="3" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="3" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1933,87 +1933,96 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="4" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2035,14 +2044,62 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -2050,74 +2107,17 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -2199,23 +2199,23 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>276225</xdr:colOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>319708</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>47625</xdr:rowOff>
+      <xdr:rowOff>137906</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>676275</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>142706</xdr:rowOff>
+      <xdr:colOff>380171</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>75256</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="12" name="図 11">
+        <xdr:cNvPr id="3" name="図 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{69D238B2-5C99-887A-D648-A69B560D3ADA}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E39A4CC1-4355-4FE9-EE40-FAF233C9BD23}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2237,8 +2237,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="619125" y="962025"/>
-          <a:ext cx="7772400" cy="4467056"/>
+          <a:off x="319708" y="1065558"/>
+          <a:ext cx="7788137" cy="3416046"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4433,19 +4433,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="89" t="s">
+      <c r="A1" s="60" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="90"/>
-      <c r="C1" s="91"/>
-      <c r="D1" s="98" t="s">
+      <c r="B1" s="61"/>
+      <c r="C1" s="62"/>
+      <c r="D1" s="69" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="83"/>
-      <c r="F1" s="98" t="s">
+      <c r="E1" s="70"/>
+      <c r="F1" s="69" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="83"/>
+      <c r="G1" s="70"/>
       <c r="H1" s="34" t="s">
         <v>6</v>
       </c>
@@ -4457,192 +4457,192 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="92"/>
-      <c r="B2" s="93"/>
-      <c r="C2" s="94"/>
-      <c r="D2" s="99" t="s">
+      <c r="A2" s="63"/>
+      <c r="B2" s="64"/>
+      <c r="C2" s="65"/>
+      <c r="D2" s="71" t="s">
         <v>72</v>
       </c>
-      <c r="E2" s="100"/>
-      <c r="F2" s="99">
+      <c r="E2" s="72"/>
+      <c r="F2" s="71">
         <v>56</v>
       </c>
-      <c r="G2" s="100"/>
-      <c r="H2" s="68">
+      <c r="G2" s="72"/>
+      <c r="H2" s="75">
         <v>45806</v>
       </c>
-      <c r="I2" s="77" t="s">
+      <c r="I2" s="89" t="s">
         <v>71</v>
       </c>
-      <c r="J2" s="78"/>
+      <c r="J2" s="90"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="92"/>
-      <c r="B3" s="93"/>
-      <c r="C3" s="94"/>
-      <c r="D3" s="101"/>
-      <c r="E3" s="94"/>
-      <c r="F3" s="101"/>
-      <c r="G3" s="94"/>
-      <c r="H3" s="69"/>
-      <c r="I3" s="69"/>
-      <c r="J3" s="79"/>
+      <c r="A3" s="63"/>
+      <c r="B3" s="64"/>
+      <c r="C3" s="65"/>
+      <c r="D3" s="73"/>
+      <c r="E3" s="65"/>
+      <c r="F3" s="73"/>
+      <c r="G3" s="65"/>
+      <c r="H3" s="76"/>
+      <c r="I3" s="76"/>
+      <c r="J3" s="91"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="95"/>
-      <c r="B4" s="96"/>
-      <c r="C4" s="97"/>
-      <c r="D4" s="102"/>
-      <c r="E4" s="97"/>
-      <c r="F4" s="102"/>
-      <c r="G4" s="97"/>
-      <c r="H4" s="70"/>
-      <c r="I4" s="70"/>
-      <c r="J4" s="80"/>
+      <c r="A4" s="66"/>
+      <c r="B4" s="67"/>
+      <c r="C4" s="68"/>
+      <c r="D4" s="74"/>
+      <c r="E4" s="68"/>
+      <c r="F4" s="74"/>
+      <c r="G4" s="68"/>
+      <c r="H4" s="77"/>
+      <c r="I4" s="77"/>
+      <c r="J4" s="92"/>
     </row>
     <row r="5" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A5" s="81" t="s">
+      <c r="A5" s="93" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="82"/>
-      <c r="C5" s="83"/>
-      <c r="D5" s="84" t="s">
+      <c r="B5" s="94"/>
+      <c r="C5" s="70"/>
+      <c r="D5" s="95" t="s">
         <v>70</v>
       </c>
-      <c r="E5" s="82"/>
-      <c r="F5" s="82"/>
-      <c r="G5" s="82"/>
-      <c r="H5" s="82"/>
-      <c r="I5" s="82"/>
-      <c r="J5" s="85"/>
+      <c r="E5" s="94"/>
+      <c r="F5" s="94"/>
+      <c r="G5" s="94"/>
+      <c r="H5" s="94"/>
+      <c r="I5" s="94"/>
+      <c r="J5" s="96"/>
     </row>
     <row r="6" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A6" s="71" t="s">
+      <c r="A6" s="78" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="66"/>
-      <c r="C6" s="61"/>
-      <c r="D6" s="65" t="s">
+      <c r="B6" s="79"/>
+      <c r="C6" s="80"/>
+      <c r="D6" s="88" t="s">
         <v>69</v>
       </c>
-      <c r="E6" s="66"/>
-      <c r="F6" s="66"/>
-      <c r="G6" s="66"/>
-      <c r="H6" s="66"/>
-      <c r="I6" s="66"/>
-      <c r="J6" s="67"/>
+      <c r="E6" s="79"/>
+      <c r="F6" s="79"/>
+      <c r="G6" s="79"/>
+      <c r="H6" s="79"/>
+      <c r="I6" s="79"/>
+      <c r="J6" s="82"/>
     </row>
     <row r="7" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A7" s="71" t="s">
+      <c r="A7" s="78" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="66"/>
-      <c r="C7" s="61"/>
-      <c r="D7" s="65" t="s">
+      <c r="B7" s="79"/>
+      <c r="C7" s="80"/>
+      <c r="D7" s="88" t="s">
         <v>68</v>
       </c>
-      <c r="E7" s="66"/>
-      <c r="F7" s="66"/>
-      <c r="G7" s="66"/>
-      <c r="H7" s="66"/>
-      <c r="I7" s="66"/>
-      <c r="J7" s="67"/>
+      <c r="E7" s="79"/>
+      <c r="F7" s="79"/>
+      <c r="G7" s="79"/>
+      <c r="H7" s="79"/>
+      <c r="I7" s="79"/>
+      <c r="J7" s="82"/>
     </row>
     <row r="8" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A8" s="71" t="s">
+      <c r="A8" s="78" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="66"/>
-      <c r="C8" s="61"/>
-      <c r="D8" s="62" t="s">
+      <c r="B8" s="79"/>
+      <c r="C8" s="80"/>
+      <c r="D8" s="81" t="s">
         <v>118</v>
       </c>
-      <c r="E8" s="66"/>
-      <c r="F8" s="66"/>
-      <c r="G8" s="66"/>
-      <c r="H8" s="66"/>
-      <c r="I8" s="66"/>
-      <c r="J8" s="67"/>
+      <c r="E8" s="79"/>
+      <c r="F8" s="79"/>
+      <c r="G8" s="79"/>
+      <c r="H8" s="79"/>
+      <c r="I8" s="79"/>
+      <c r="J8" s="82"/>
     </row>
     <row r="9" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A9" s="86" t="s">
+      <c r="A9" s="97" t="s">
         <v>13</v>
       </c>
-      <c r="B9" s="60" t="s">
+      <c r="B9" s="100" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="61"/>
-      <c r="D9" s="62" t="s">
+      <c r="C9" s="80"/>
+      <c r="D9" s="81" t="s">
         <v>116</v>
       </c>
-      <c r="E9" s="63"/>
-      <c r="F9" s="63"/>
-      <c r="G9" s="63"/>
-      <c r="H9" s="63"/>
-      <c r="I9" s="63"/>
-      <c r="J9" s="64"/>
+      <c r="E9" s="101"/>
+      <c r="F9" s="101"/>
+      <c r="G9" s="101"/>
+      <c r="H9" s="101"/>
+      <c r="I9" s="101"/>
+      <c r="J9" s="102"/>
     </row>
     <row r="10" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A10" s="87"/>
-      <c r="B10" s="60" t="s">
+      <c r="A10" s="98"/>
+      <c r="B10" s="100" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="61"/>
-      <c r="D10" s="65" t="s">
+      <c r="C10" s="80"/>
+      <c r="D10" s="88" t="s">
         <v>104</v>
       </c>
-      <c r="E10" s="66"/>
-      <c r="F10" s="66"/>
-      <c r="G10" s="66"/>
-      <c r="H10" s="66"/>
-      <c r="I10" s="66"/>
-      <c r="J10" s="67"/>
+      <c r="E10" s="79"/>
+      <c r="F10" s="79"/>
+      <c r="G10" s="79"/>
+      <c r="H10" s="79"/>
+      <c r="I10" s="79"/>
+      <c r="J10" s="82"/>
     </row>
     <row r="11" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A11" s="88"/>
-      <c r="B11" s="60" t="s">
+      <c r="A11" s="99"/>
+      <c r="B11" s="100" t="s">
         <v>16</v>
       </c>
-      <c r="C11" s="61"/>
-      <c r="D11" s="62" t="s">
+      <c r="C11" s="80"/>
+      <c r="D11" s="81" t="s">
         <v>119</v>
       </c>
-      <c r="E11" s="66"/>
-      <c r="F11" s="66"/>
-      <c r="G11" s="66"/>
-      <c r="H11" s="66"/>
-      <c r="I11" s="66"/>
-      <c r="J11" s="67"/>
+      <c r="E11" s="79"/>
+      <c r="F11" s="79"/>
+      <c r="G11" s="79"/>
+      <c r="H11" s="79"/>
+      <c r="I11" s="79"/>
+      <c r="J11" s="82"/>
     </row>
     <row r="12" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A12" s="71" t="s">
+      <c r="A12" s="78" t="s">
         <v>17</v>
       </c>
-      <c r="B12" s="66"/>
-      <c r="C12" s="61"/>
-      <c r="D12" s="62" t="s">
+      <c r="B12" s="79"/>
+      <c r="C12" s="80"/>
+      <c r="D12" s="81" t="s">
         <v>117</v>
       </c>
-      <c r="E12" s="66"/>
-      <c r="F12" s="66"/>
-      <c r="G12" s="66"/>
-      <c r="H12" s="66"/>
-      <c r="I12" s="66"/>
-      <c r="J12" s="67"/>
+      <c r="E12" s="79"/>
+      <c r="F12" s="79"/>
+      <c r="G12" s="79"/>
+      <c r="H12" s="79"/>
+      <c r="I12" s="79"/>
+      <c r="J12" s="82"/>
     </row>
     <row r="13" spans="1:10" ht="26.25" customHeight="1" thickBot="1">
-      <c r="A13" s="72" t="s">
+      <c r="A13" s="83" t="s">
         <v>18</v>
       </c>
-      <c r="B13" s="73"/>
-      <c r="C13" s="74"/>
-      <c r="D13" s="75"/>
-      <c r="E13" s="73"/>
-      <c r="F13" s="73"/>
-      <c r="G13" s="73"/>
-      <c r="H13" s="73"/>
-      <c r="I13" s="73"/>
-      <c r="J13" s="76"/>
+      <c r="B13" s="84"/>
+      <c r="C13" s="85"/>
+      <c r="D13" s="86"/>
+      <c r="E13" s="84"/>
+      <c r="F13" s="84"/>
+      <c r="G13" s="84"/>
+      <c r="H13" s="84"/>
+      <c r="I13" s="84"/>
+      <c r="J13" s="87"/>
     </row>
     <row r="14" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="15" spans="1:10" ht="12.75" customHeight="1"/>
@@ -5633,11 +5633,12 @@
     <row r="1000" s="32" customFormat="1" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="A1:C4"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="D2:E4"/>
-    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="D9:J9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="D10:J10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="D11:J11"/>
     <mergeCell ref="H2:H4"/>
     <mergeCell ref="A12:C12"/>
     <mergeCell ref="D12:J12"/>
@@ -5654,12 +5655,11 @@
     <mergeCell ref="A6:C6"/>
     <mergeCell ref="D6:J6"/>
     <mergeCell ref="A9:A11"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="D9:J9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="D10:J10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="D11:J11"/>
+    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="F2:G4"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.70833333333333304" right="0.70833333333333304" top="0.74791666666666701" bottom="0.74791666666666701" header="0" footer="0"/>
@@ -8517,19 +8517,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="137" t="s">
+      <c r="A1" s="135" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="138"/>
-      <c r="C1" s="139"/>
-      <c r="D1" s="141" t="s">
+      <c r="B1" s="136"/>
+      <c r="C1" s="137"/>
+      <c r="D1" s="139" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="142"/>
-      <c r="F1" s="141" t="s">
+      <c r="E1" s="140"/>
+      <c r="F1" s="139" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="142"/>
+      <c r="G1" s="140"/>
       <c r="H1" s="43" t="s">
         <v>6</v>
       </c>
@@ -8541,67 +8541,67 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="134"/>
-      <c r="B2" s="135"/>
-      <c r="C2" s="140"/>
-      <c r="D2" s="143" t="s">
+      <c r="A2" s="132"/>
+      <c r="B2" s="133"/>
+      <c r="C2" s="138"/>
+      <c r="D2" s="141" t="s">
         <v>95</v>
       </c>
-      <c r="E2" s="144"/>
-      <c r="F2" s="143">
+      <c r="E2" s="142"/>
+      <c r="F2" s="141">
         <v>56</v>
       </c>
-      <c r="G2" s="144"/>
-      <c r="H2" s="146">
+      <c r="G2" s="142"/>
+      <c r="H2" s="144">
         <v>45806</v>
       </c>
-      <c r="I2" s="148" t="s">
+      <c r="I2" s="146" t="s">
         <v>94</v>
       </c>
-      <c r="J2" s="149"/>
+      <c r="J2" s="147"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="134"/>
-      <c r="B3" s="135"/>
-      <c r="C3" s="140"/>
-      <c r="D3" s="145"/>
-      <c r="E3" s="140"/>
-      <c r="F3" s="145"/>
-      <c r="G3" s="140"/>
-      <c r="H3" s="147"/>
-      <c r="I3" s="147"/>
-      <c r="J3" s="150"/>
+      <c r="A3" s="132"/>
+      <c r="B3" s="133"/>
+      <c r="C3" s="138"/>
+      <c r="D3" s="143"/>
+      <c r="E3" s="138"/>
+      <c r="F3" s="143"/>
+      <c r="G3" s="138"/>
+      <c r="H3" s="145"/>
+      <c r="I3" s="145"/>
+      <c r="J3" s="148"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="134"/>
-      <c r="B4" s="135"/>
-      <c r="C4" s="140"/>
-      <c r="D4" s="145"/>
-      <c r="E4" s="140"/>
-      <c r="F4" s="145"/>
-      <c r="G4" s="140"/>
-      <c r="H4" s="147"/>
-      <c r="I4" s="147"/>
-      <c r="J4" s="150"/>
+      <c r="A4" s="132"/>
+      <c r="B4" s="133"/>
+      <c r="C4" s="138"/>
+      <c r="D4" s="143"/>
+      <c r="E4" s="138"/>
+      <c r="F4" s="143"/>
+      <c r="G4" s="138"/>
+      <c r="H4" s="145"/>
+      <c r="I4" s="145"/>
+      <c r="J4" s="148"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="151" t="s">
+      <c r="A5" s="149" t="s">
         <v>22</v>
       </c>
-      <c r="B5" s="152"/>
-      <c r="C5" s="142"/>
-      <c r="D5" s="153" t="s">
+      <c r="B5" s="150"/>
+      <c r="C5" s="140"/>
+      <c r="D5" s="151" t="s">
         <v>103</v>
       </c>
-      <c r="E5" s="152"/>
-      <c r="F5" s="152"/>
-      <c r="G5" s="152"/>
-      <c r="H5" s="152"/>
-      <c r="I5" s="152"/>
-      <c r="J5" s="154"/>
+      <c r="E5" s="150"/>
+      <c r="F5" s="150"/>
+      <c r="G5" s="150"/>
+      <c r="H5" s="150"/>
+      <c r="I5" s="150"/>
+      <c r="J5" s="152"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="130" t="s">
+      <c r="A6" s="153" t="s">
         <v>23</v>
       </c>
       <c r="B6" s="125"/>
@@ -8615,91 +8615,91 @@
       <c r="J6" s="128"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="131"/>
-      <c r="B7" s="132"/>
-      <c r="C7" s="132"/>
-      <c r="D7" s="132"/>
-      <c r="E7" s="132"/>
-      <c r="F7" s="132"/>
-      <c r="G7" s="132"/>
-      <c r="H7" s="132"/>
-      <c r="I7" s="132"/>
-      <c r="J7" s="133"/>
+      <c r="A7" s="129"/>
+      <c r="B7" s="130"/>
+      <c r="C7" s="130"/>
+      <c r="D7" s="130"/>
+      <c r="E7" s="130"/>
+      <c r="F7" s="130"/>
+      <c r="G7" s="130"/>
+      <c r="H7" s="130"/>
+      <c r="I7" s="130"/>
+      <c r="J7" s="131"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="134"/>
-      <c r="B8" s="135"/>
-      <c r="C8" s="135"/>
-      <c r="D8" s="135"/>
-      <c r="E8" s="135"/>
-      <c r="F8" s="135"/>
-      <c r="G8" s="135"/>
-      <c r="H8" s="135"/>
-      <c r="I8" s="135"/>
-      <c r="J8" s="136"/>
+      <c r="A8" s="132"/>
+      <c r="B8" s="133"/>
+      <c r="C8" s="133"/>
+      <c r="D8" s="133"/>
+      <c r="E8" s="133"/>
+      <c r="F8" s="133"/>
+      <c r="G8" s="133"/>
+      <c r="H8" s="133"/>
+      <c r="I8" s="133"/>
+      <c r="J8" s="134"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="134"/>
-      <c r="B9" s="135"/>
-      <c r="C9" s="135"/>
-      <c r="D9" s="135"/>
-      <c r="E9" s="135"/>
-      <c r="F9" s="135"/>
-      <c r="G9" s="135"/>
-      <c r="H9" s="135"/>
-      <c r="I9" s="135"/>
-      <c r="J9" s="136"/>
+      <c r="A9" s="132"/>
+      <c r="B9" s="133"/>
+      <c r="C9" s="133"/>
+      <c r="D9" s="133"/>
+      <c r="E9" s="133"/>
+      <c r="F9" s="133"/>
+      <c r="G9" s="133"/>
+      <c r="H9" s="133"/>
+      <c r="I9" s="133"/>
+      <c r="J9" s="134"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="134"/>
-      <c r="B10" s="135"/>
-      <c r="C10" s="135"/>
-      <c r="D10" s="135"/>
-      <c r="E10" s="135"/>
-      <c r="F10" s="135"/>
-      <c r="G10" s="135"/>
-      <c r="H10" s="135"/>
-      <c r="I10" s="135"/>
-      <c r="J10" s="136"/>
+      <c r="A10" s="132"/>
+      <c r="B10" s="133"/>
+      <c r="C10" s="133"/>
+      <c r="D10" s="133"/>
+      <c r="E10" s="133"/>
+      <c r="F10" s="133"/>
+      <c r="G10" s="133"/>
+      <c r="H10" s="133"/>
+      <c r="I10" s="133"/>
+      <c r="J10" s="134"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="134"/>
-      <c r="B11" s="135"/>
-      <c r="C11" s="135"/>
-      <c r="D11" s="135"/>
-      <c r="E11" s="135"/>
-      <c r="F11" s="135"/>
-      <c r="G11" s="135"/>
-      <c r="H11" s="135"/>
-      <c r="I11" s="135"/>
-      <c r="J11" s="136"/>
+      <c r="A11" s="132"/>
+      <c r="B11" s="133"/>
+      <c r="C11" s="133"/>
+      <c r="D11" s="133"/>
+      <c r="E11" s="133"/>
+      <c r="F11" s="133"/>
+      <c r="G11" s="133"/>
+      <c r="H11" s="133"/>
+      <c r="I11" s="133"/>
+      <c r="J11" s="134"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="134"/>
-      <c r="B12" s="135"/>
-      <c r="C12" s="135"/>
-      <c r="D12" s="135"/>
-      <c r="E12" s="135"/>
-      <c r="F12" s="135"/>
-      <c r="G12" s="135"/>
-      <c r="H12" s="135"/>
-      <c r="I12" s="135"/>
-      <c r="J12" s="136"/>
+      <c r="A12" s="132"/>
+      <c r="B12" s="133"/>
+      <c r="C12" s="133"/>
+      <c r="D12" s="133"/>
+      <c r="E12" s="133"/>
+      <c r="F12" s="133"/>
+      <c r="G12" s="133"/>
+      <c r="H12" s="133"/>
+      <c r="I12" s="133"/>
+      <c r="J12" s="134"/>
     </row>
     <row r="13" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A13" s="134"/>
-      <c r="B13" s="135"/>
-      <c r="C13" s="135"/>
-      <c r="D13" s="135"/>
-      <c r="E13" s="135"/>
-      <c r="F13" s="135"/>
-      <c r="G13" s="135"/>
-      <c r="H13" s="135"/>
-      <c r="I13" s="135"/>
-      <c r="J13" s="136"/>
+      <c r="A13" s="132"/>
+      <c r="B13" s="133"/>
+      <c r="C13" s="133"/>
+      <c r="D13" s="133"/>
+      <c r="E13" s="133"/>
+      <c r="F13" s="133"/>
+      <c r="G13" s="133"/>
+      <c r="H13" s="133"/>
+      <c r="I13" s="133"/>
+      <c r="J13" s="134"/>
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A14" s="130" t="s">
+      <c r="A14" s="153" t="s">
         <v>24</v>
       </c>
       <c r="B14" s="125"/>
@@ -8713,7 +8713,7 @@
       <c r="J14" s="128"/>
     </row>
     <row r="15" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A15" s="130" t="s">
+      <c r="A15" s="153" t="s">
         <v>25</v>
       </c>
       <c r="B15" s="125"/>
@@ -8733,7 +8733,7 @@
       </c>
     </row>
     <row r="16" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A16" s="130" t="s">
+      <c r="A16" s="153" t="s">
         <v>27</v>
       </c>
       <c r="B16" s="125"/>
@@ -8750,7 +8750,7 @@
       <c r="G16" s="39" t="s">
         <v>31</v>
       </c>
-      <c r="H16" s="129" t="s">
+      <c r="H16" s="154" t="s">
         <v>18</v>
       </c>
       <c r="I16" s="125"/>
@@ -9922,6 +9922,23 @@
     <row r="1000" s="36" customFormat="1" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="33">
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="H19:J19"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="H23:J23"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="H20:J20"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="H21:J21"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="H16:J16"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="H18:J18"/>
+    <mergeCell ref="A15:C15"/>
+    <mergeCell ref="D15:H15"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="H17:J17"/>
     <mergeCell ref="A24:C24"/>
     <mergeCell ref="H24:J24"/>
     <mergeCell ref="A7:J13"/>
@@ -9938,23 +9955,6 @@
     <mergeCell ref="A6:J6"/>
     <mergeCell ref="A14:J14"/>
     <mergeCell ref="A16:C16"/>
-    <mergeCell ref="H16:J16"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="A15:C15"/>
-    <mergeCell ref="D15:H15"/>
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="H17:J17"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="H19:J19"/>
-    <mergeCell ref="A23:C23"/>
-    <mergeCell ref="H23:J23"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="H20:J20"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="H21:J21"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="H22:J22"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -9978,19 +9978,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="160" t="s">
+      <c r="A1" s="163" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="90"/>
-      <c r="C1" s="91"/>
-      <c r="D1" s="98" t="s">
+      <c r="B1" s="61"/>
+      <c r="C1" s="62"/>
+      <c r="D1" s="69" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="83"/>
-      <c r="F1" s="98" t="s">
+      <c r="E1" s="70"/>
+      <c r="F1" s="69" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="83"/>
+      <c r="G1" s="70"/>
       <c r="H1" s="35" t="s">
         <v>6</v>
       </c>
@@ -10002,190 +10002,190 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="92"/>
-      <c r="B2" s="93"/>
-      <c r="C2" s="94"/>
-      <c r="D2" s="99" t="s">
+      <c r="A2" s="63"/>
+      <c r="B2" s="64"/>
+      <c r="C2" s="65"/>
+      <c r="D2" s="71" t="s">
         <v>96</v>
       </c>
-      <c r="E2" s="100"/>
-      <c r="F2" s="99">
+      <c r="E2" s="72"/>
+      <c r="F2" s="71">
         <v>56</v>
       </c>
-      <c r="G2" s="100"/>
-      <c r="H2" s="68">
+      <c r="G2" s="72"/>
+      <c r="H2" s="75">
         <v>45805</v>
       </c>
-      <c r="I2" s="77" t="s">
+      <c r="I2" s="89" t="s">
         <v>94</v>
       </c>
-      <c r="J2" s="78"/>
+      <c r="J2" s="90"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="92"/>
-      <c r="B3" s="93"/>
-      <c r="C3" s="94"/>
-      <c r="D3" s="101"/>
-      <c r="E3" s="94"/>
-      <c r="F3" s="101"/>
-      <c r="G3" s="94"/>
-      <c r="H3" s="69"/>
-      <c r="I3" s="69"/>
-      <c r="J3" s="79"/>
+      <c r="A3" s="63"/>
+      <c r="B3" s="64"/>
+      <c r="C3" s="65"/>
+      <c r="D3" s="73"/>
+      <c r="E3" s="65"/>
+      <c r="F3" s="73"/>
+      <c r="G3" s="65"/>
+      <c r="H3" s="76"/>
+      <c r="I3" s="76"/>
+      <c r="J3" s="91"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="92"/>
-      <c r="B4" s="93"/>
-      <c r="C4" s="94"/>
-      <c r="D4" s="101"/>
-      <c r="E4" s="94"/>
-      <c r="F4" s="101"/>
-      <c r="G4" s="94"/>
-      <c r="H4" s="69"/>
-      <c r="I4" s="69"/>
-      <c r="J4" s="79"/>
+      <c r="A4" s="63"/>
+      <c r="B4" s="64"/>
+      <c r="C4" s="65"/>
+      <c r="D4" s="73"/>
+      <c r="E4" s="65"/>
+      <c r="F4" s="73"/>
+      <c r="G4" s="65"/>
+      <c r="H4" s="76"/>
+      <c r="I4" s="76"/>
+      <c r="J4" s="91"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="161" t="s">
+      <c r="A5" s="164" t="s">
         <v>22</v>
       </c>
-      <c r="B5" s="82"/>
-      <c r="C5" s="83"/>
-      <c r="D5" s="162" t="s">
+      <c r="B5" s="94"/>
+      <c r="C5" s="70"/>
+      <c r="D5" s="165" t="s">
         <v>97</v>
       </c>
-      <c r="E5" s="82"/>
-      <c r="F5" s="82"/>
-      <c r="G5" s="82"/>
-      <c r="H5" s="82"/>
-      <c r="I5" s="82"/>
-      <c r="J5" s="85"/>
+      <c r="E5" s="94"/>
+      <c r="F5" s="94"/>
+      <c r="G5" s="94"/>
+      <c r="H5" s="94"/>
+      <c r="I5" s="94"/>
+      <c r="J5" s="96"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="155" t="s">
+      <c r="A6" s="157" t="s">
         <v>23</v>
       </c>
-      <c r="B6" s="66"/>
-      <c r="C6" s="66"/>
-      <c r="D6" s="66"/>
-      <c r="E6" s="66"/>
-      <c r="F6" s="66"/>
-      <c r="G6" s="66"/>
-      <c r="H6" s="66"/>
-      <c r="I6" s="66"/>
-      <c r="J6" s="67"/>
+      <c r="B6" s="79"/>
+      <c r="C6" s="79"/>
+      <c r="D6" s="79"/>
+      <c r="E6" s="79"/>
+      <c r="F6" s="79"/>
+      <c r="G6" s="79"/>
+      <c r="H6" s="79"/>
+      <c r="I6" s="79"/>
+      <c r="J6" s="82"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="156"/>
-      <c r="B7" s="157"/>
-      <c r="C7" s="157"/>
-      <c r="D7" s="157"/>
-      <c r="E7" s="157"/>
-      <c r="F7" s="157"/>
-      <c r="G7" s="157"/>
-      <c r="H7" s="157"/>
-      <c r="I7" s="157"/>
-      <c r="J7" s="158"/>
+      <c r="A7" s="159"/>
+      <c r="B7" s="160"/>
+      <c r="C7" s="160"/>
+      <c r="D7" s="160"/>
+      <c r="E7" s="160"/>
+      <c r="F7" s="160"/>
+      <c r="G7" s="160"/>
+      <c r="H7" s="160"/>
+      <c r="I7" s="160"/>
+      <c r="J7" s="161"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="92"/>
-      <c r="B8" s="93"/>
-      <c r="C8" s="93"/>
-      <c r="D8" s="93"/>
-      <c r="E8" s="93"/>
-      <c r="F8" s="93"/>
-      <c r="G8" s="93"/>
-      <c r="H8" s="93"/>
-      <c r="I8" s="93"/>
-      <c r="J8" s="159"/>
+      <c r="A8" s="63"/>
+      <c r="B8" s="64"/>
+      <c r="C8" s="64"/>
+      <c r="D8" s="64"/>
+      <c r="E8" s="64"/>
+      <c r="F8" s="64"/>
+      <c r="G8" s="64"/>
+      <c r="H8" s="64"/>
+      <c r="I8" s="64"/>
+      <c r="J8" s="162"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="92"/>
-      <c r="B9" s="93"/>
-      <c r="C9" s="93"/>
-      <c r="D9" s="93"/>
-      <c r="E9" s="93"/>
-      <c r="F9" s="93"/>
-      <c r="G9" s="93"/>
-      <c r="H9" s="93"/>
-      <c r="I9" s="93"/>
-      <c r="J9" s="159"/>
+      <c r="A9" s="63"/>
+      <c r="B9" s="64"/>
+      <c r="C9" s="64"/>
+      <c r="D9" s="64"/>
+      <c r="E9" s="64"/>
+      <c r="F9" s="64"/>
+      <c r="G9" s="64"/>
+      <c r="H9" s="64"/>
+      <c r="I9" s="64"/>
+      <c r="J9" s="162"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="92"/>
-      <c r="B10" s="93"/>
-      <c r="C10" s="93"/>
-      <c r="D10" s="93"/>
-      <c r="E10" s="93"/>
-      <c r="F10" s="93"/>
-      <c r="G10" s="93"/>
-      <c r="H10" s="93"/>
-      <c r="I10" s="93"/>
-      <c r="J10" s="159"/>
+      <c r="A10" s="63"/>
+      <c r="B10" s="64"/>
+      <c r="C10" s="64"/>
+      <c r="D10" s="64"/>
+      <c r="E10" s="64"/>
+      <c r="F10" s="64"/>
+      <c r="G10" s="64"/>
+      <c r="H10" s="64"/>
+      <c r="I10" s="64"/>
+      <c r="J10" s="162"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="92"/>
-      <c r="B11" s="93"/>
-      <c r="C11" s="93"/>
-      <c r="D11" s="93"/>
-      <c r="E11" s="93"/>
-      <c r="F11" s="93"/>
-      <c r="G11" s="93"/>
-      <c r="H11" s="93"/>
-      <c r="I11" s="93"/>
-      <c r="J11" s="159"/>
+      <c r="A11" s="63"/>
+      <c r="B11" s="64"/>
+      <c r="C11" s="64"/>
+      <c r="D11" s="64"/>
+      <c r="E11" s="64"/>
+      <c r="F11" s="64"/>
+      <c r="G11" s="64"/>
+      <c r="H11" s="64"/>
+      <c r="I11" s="64"/>
+      <c r="J11" s="162"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="92"/>
-      <c r="B12" s="93"/>
-      <c r="C12" s="93"/>
-      <c r="D12" s="93"/>
-      <c r="E12" s="93"/>
-      <c r="F12" s="93"/>
-      <c r="G12" s="93"/>
-      <c r="H12" s="93"/>
-      <c r="I12" s="93"/>
-      <c r="J12" s="159"/>
+      <c r="A12" s="63"/>
+      <c r="B12" s="64"/>
+      <c r="C12" s="64"/>
+      <c r="D12" s="64"/>
+      <c r="E12" s="64"/>
+      <c r="F12" s="64"/>
+      <c r="G12" s="64"/>
+      <c r="H12" s="64"/>
+      <c r="I12" s="64"/>
+      <c r="J12" s="162"/>
     </row>
     <row r="13" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A13" s="92"/>
-      <c r="B13" s="93"/>
-      <c r="C13" s="93"/>
-      <c r="D13" s="93"/>
-      <c r="E13" s="93"/>
-      <c r="F13" s="93"/>
-      <c r="G13" s="93"/>
-      <c r="H13" s="93"/>
-      <c r="I13" s="93"/>
-      <c r="J13" s="159"/>
+      <c r="A13" s="63"/>
+      <c r="B13" s="64"/>
+      <c r="C13" s="64"/>
+      <c r="D13" s="64"/>
+      <c r="E13" s="64"/>
+      <c r="F13" s="64"/>
+      <c r="G13" s="64"/>
+      <c r="H13" s="64"/>
+      <c r="I13" s="64"/>
+      <c r="J13" s="162"/>
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A14" s="155" t="s">
+      <c r="A14" s="157" t="s">
         <v>24</v>
       </c>
-      <c r="B14" s="66"/>
-      <c r="C14" s="66"/>
-      <c r="D14" s="66"/>
-      <c r="E14" s="66"/>
-      <c r="F14" s="66"/>
-      <c r="G14" s="66"/>
-      <c r="H14" s="66"/>
-      <c r="I14" s="66"/>
-      <c r="J14" s="67"/>
+      <c r="B14" s="79"/>
+      <c r="C14" s="79"/>
+      <c r="D14" s="79"/>
+      <c r="E14" s="79"/>
+      <c r="F14" s="79"/>
+      <c r="G14" s="79"/>
+      <c r="H14" s="79"/>
+      <c r="I14" s="79"/>
+      <c r="J14" s="82"/>
     </row>
     <row r="15" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A15" s="155" t="s">
+      <c r="A15" s="157" t="s">
         <v>25</v>
       </c>
-      <c r="B15" s="66"/>
-      <c r="C15" s="61"/>
-      <c r="D15" s="65" t="s">
+      <c r="B15" s="79"/>
+      <c r="C15" s="80"/>
+      <c r="D15" s="88" t="s">
         <v>98</v>
       </c>
-      <c r="E15" s="66"/>
-      <c r="F15" s="66"/>
-      <c r="G15" s="66"/>
-      <c r="H15" s="61"/>
+      <c r="E15" s="79"/>
+      <c r="F15" s="79"/>
+      <c r="G15" s="79"/>
+      <c r="H15" s="80"/>
       <c r="I15" s="45" t="s">
         <v>26</v>
       </c>
@@ -10194,11 +10194,11 @@
       </c>
     </row>
     <row r="16" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A16" s="155" t="s">
+      <c r="A16" s="157" t="s">
         <v>27</v>
       </c>
-      <c r="B16" s="66"/>
-      <c r="C16" s="61"/>
+      <c r="B16" s="79"/>
+      <c r="C16" s="80"/>
       <c r="D16" s="45" t="s">
         <v>28</v>
       </c>
@@ -10211,18 +10211,18 @@
       <c r="G16" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="H16" s="163" t="s">
+      <c r="H16" s="158" t="s">
         <v>18</v>
       </c>
-      <c r="I16" s="66"/>
-      <c r="J16" s="67"/>
+      <c r="I16" s="79"/>
+      <c r="J16" s="82"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="164">
+      <c r="A17" s="155">
         <v>1</v>
       </c>
-      <c r="B17" s="66"/>
-      <c r="C17" s="61"/>
+      <c r="B17" s="79"/>
+      <c r="C17" s="80"/>
       <c r="D17" s="47" t="s">
         <v>75</v>
       </c>
@@ -10235,83 +10235,83 @@
       <c r="G17" s="48" t="s">
         <v>100</v>
       </c>
-      <c r="H17" s="65" t="s">
+      <c r="H17" s="88" t="s">
         <v>101</v>
       </c>
-      <c r="I17" s="66"/>
-      <c r="J17" s="67"/>
+      <c r="I17" s="79"/>
+      <c r="J17" s="82"/>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A18" s="164"/>
-      <c r="B18" s="66"/>
-      <c r="C18" s="61"/>
+      <c r="A18" s="155"/>
+      <c r="B18" s="79"/>
+      <c r="C18" s="80"/>
       <c r="D18" s="47"/>
       <c r="E18" s="47"/>
       <c r="F18" s="48"/>
       <c r="G18" s="48"/>
-      <c r="H18" s="65"/>
-      <c r="I18" s="66"/>
-      <c r="J18" s="67"/>
+      <c r="H18" s="88"/>
+      <c r="I18" s="79"/>
+      <c r="J18" s="82"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="164"/>
-      <c r="B19" s="66"/>
-      <c r="C19" s="61"/>
+      <c r="A19" s="155"/>
+      <c r="B19" s="79"/>
+      <c r="C19" s="80"/>
       <c r="D19" s="47"/>
       <c r="E19" s="47"/>
       <c r="F19" s="48"/>
       <c r="G19" s="48"/>
-      <c r="H19" s="65"/>
-      <c r="I19" s="66"/>
-      <c r="J19" s="67"/>
+      <c r="H19" s="88"/>
+      <c r="I19" s="79"/>
+      <c r="J19" s="82"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="164"/>
-      <c r="B20" s="66"/>
-      <c r="C20" s="61"/>
+      <c r="A20" s="155"/>
+      <c r="B20" s="79"/>
+      <c r="C20" s="80"/>
       <c r="D20" s="47"/>
       <c r="E20" s="47"/>
       <c r="F20" s="48"/>
       <c r="G20" s="48"/>
-      <c r="H20" s="65"/>
-      <c r="I20" s="66"/>
-      <c r="J20" s="67"/>
+      <c r="H20" s="88"/>
+      <c r="I20" s="79"/>
+      <c r="J20" s="82"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="164"/>
-      <c r="B21" s="66"/>
-      <c r="C21" s="61"/>
+      <c r="A21" s="155"/>
+      <c r="B21" s="79"/>
+      <c r="C21" s="80"/>
       <c r="D21" s="47"/>
       <c r="E21" s="47"/>
       <c r="F21" s="48"/>
       <c r="G21" s="48"/>
-      <c r="H21" s="65"/>
-      <c r="I21" s="66"/>
-      <c r="J21" s="67"/>
+      <c r="H21" s="88"/>
+      <c r="I21" s="79"/>
+      <c r="J21" s="82"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="164"/>
-      <c r="B22" s="66"/>
-      <c r="C22" s="61"/>
+      <c r="A22" s="155"/>
+      <c r="B22" s="79"/>
+      <c r="C22" s="80"/>
       <c r="D22" s="47"/>
       <c r="E22" s="47"/>
       <c r="F22" s="48"/>
       <c r="G22" s="48"/>
-      <c r="H22" s="65"/>
-      <c r="I22" s="66"/>
-      <c r="J22" s="67"/>
+      <c r="H22" s="88"/>
+      <c r="I22" s="79"/>
+      <c r="J22" s="82"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A23" s="165"/>
-      <c r="B23" s="73"/>
-      <c r="C23" s="74"/>
+      <c r="A23" s="156"/>
+      <c r="B23" s="84"/>
+      <c r="C23" s="85"/>
       <c r="D23" s="49"/>
       <c r="E23" s="49"/>
       <c r="F23" s="50"/>
       <c r="G23" s="50"/>
-      <c r="H23" s="75"/>
-      <c r="I23" s="73"/>
-      <c r="J23" s="76"/>
+      <c r="H23" s="86"/>
+      <c r="I23" s="84"/>
+      <c r="J23" s="87"/>
     </row>
     <row r="24" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="25" spans="1:10" ht="12.75" customHeight="1"/>
@@ -11292,22 +11292,6 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="31">
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="H22:J22"/>
-    <mergeCell ref="A23:C23"/>
-    <mergeCell ref="H23:J23"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="H19:J19"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="H20:J20"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="H21:J21"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="H16:J16"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="H17:J17"/>
     <mergeCell ref="A14:J14"/>
     <mergeCell ref="A15:C15"/>
     <mergeCell ref="A7:J13"/>
@@ -11323,6 +11307,22 @@
     <mergeCell ref="D5:J5"/>
     <mergeCell ref="A6:J6"/>
     <mergeCell ref="D15:H15"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="H16:J16"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="H18:J18"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="H17:J17"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="H23:J23"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="H19:J19"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="H20:J20"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="H21:J21"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -11346,19 +11346,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="160" t="s">
+      <c r="A1" s="163" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="90"/>
-      <c r="C1" s="91"/>
-      <c r="D1" s="98" t="s">
+      <c r="B1" s="61"/>
+      <c r="C1" s="62"/>
+      <c r="D1" s="69" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="83"/>
-      <c r="F1" s="98" t="s">
+      <c r="E1" s="70"/>
+      <c r="F1" s="69" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="83"/>
+      <c r="G1" s="70"/>
       <c r="H1" s="35" t="s">
         <v>6</v>
       </c>
@@ -11370,190 +11370,190 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="92"/>
-      <c r="B2" s="93"/>
-      <c r="C2" s="94"/>
-      <c r="D2" s="99" t="s">
+      <c r="A2" s="63"/>
+      <c r="B2" s="64"/>
+      <c r="C2" s="65"/>
+      <c r="D2" s="71" t="s">
         <v>95</v>
       </c>
-      <c r="E2" s="100"/>
-      <c r="F2" s="99">
+      <c r="E2" s="72"/>
+      <c r="F2" s="71">
         <v>56</v>
       </c>
-      <c r="G2" s="100"/>
-      <c r="H2" s="68">
+      <c r="G2" s="72"/>
+      <c r="H2" s="75">
         <v>45805</v>
       </c>
-      <c r="I2" s="77" t="s">
+      <c r="I2" s="89" t="s">
         <v>94</v>
       </c>
-      <c r="J2" s="78"/>
+      <c r="J2" s="90"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="92"/>
-      <c r="B3" s="93"/>
-      <c r="C3" s="94"/>
-      <c r="D3" s="101"/>
-      <c r="E3" s="94"/>
-      <c r="F3" s="101"/>
-      <c r="G3" s="94"/>
-      <c r="H3" s="69"/>
-      <c r="I3" s="69"/>
-      <c r="J3" s="79"/>
+      <c r="A3" s="63"/>
+      <c r="B3" s="64"/>
+      <c r="C3" s="65"/>
+      <c r="D3" s="73"/>
+      <c r="E3" s="65"/>
+      <c r="F3" s="73"/>
+      <c r="G3" s="65"/>
+      <c r="H3" s="76"/>
+      <c r="I3" s="76"/>
+      <c r="J3" s="91"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="92"/>
-      <c r="B4" s="93"/>
-      <c r="C4" s="94"/>
-      <c r="D4" s="101"/>
-      <c r="E4" s="94"/>
-      <c r="F4" s="101"/>
-      <c r="G4" s="94"/>
-      <c r="H4" s="69"/>
-      <c r="I4" s="69"/>
-      <c r="J4" s="79"/>
+      <c r="A4" s="63"/>
+      <c r="B4" s="64"/>
+      <c r="C4" s="65"/>
+      <c r="D4" s="73"/>
+      <c r="E4" s="65"/>
+      <c r="F4" s="73"/>
+      <c r="G4" s="65"/>
+      <c r="H4" s="76"/>
+      <c r="I4" s="76"/>
+      <c r="J4" s="91"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="161" t="s">
+      <c r="A5" s="164" t="s">
         <v>22</v>
       </c>
-      <c r="B5" s="82"/>
-      <c r="C5" s="83"/>
-      <c r="D5" s="162" t="s">
+      <c r="B5" s="94"/>
+      <c r="C5" s="70"/>
+      <c r="D5" s="165" t="s">
         <v>102</v>
       </c>
-      <c r="E5" s="82"/>
-      <c r="F5" s="82"/>
-      <c r="G5" s="82"/>
-      <c r="H5" s="82"/>
-      <c r="I5" s="82"/>
-      <c r="J5" s="85"/>
+      <c r="E5" s="94"/>
+      <c r="F5" s="94"/>
+      <c r="G5" s="94"/>
+      <c r="H5" s="94"/>
+      <c r="I5" s="94"/>
+      <c r="J5" s="96"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="155" t="s">
+      <c r="A6" s="157" t="s">
         <v>23</v>
       </c>
-      <c r="B6" s="66"/>
-      <c r="C6" s="66"/>
-      <c r="D6" s="66"/>
-      <c r="E6" s="66"/>
-      <c r="F6" s="66"/>
-      <c r="G6" s="66"/>
-      <c r="H6" s="66"/>
-      <c r="I6" s="66"/>
-      <c r="J6" s="67"/>
+      <c r="B6" s="79"/>
+      <c r="C6" s="79"/>
+      <c r="D6" s="79"/>
+      <c r="E6" s="79"/>
+      <c r="F6" s="79"/>
+      <c r="G6" s="79"/>
+      <c r="H6" s="79"/>
+      <c r="I6" s="79"/>
+      <c r="J6" s="82"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="156"/>
-      <c r="B7" s="157"/>
-      <c r="C7" s="157"/>
-      <c r="D7" s="157"/>
-      <c r="E7" s="157"/>
-      <c r="F7" s="157"/>
-      <c r="G7" s="157"/>
-      <c r="H7" s="157"/>
-      <c r="I7" s="157"/>
-      <c r="J7" s="158"/>
+      <c r="A7" s="159"/>
+      <c r="B7" s="160"/>
+      <c r="C7" s="160"/>
+      <c r="D7" s="160"/>
+      <c r="E7" s="160"/>
+      <c r="F7" s="160"/>
+      <c r="G7" s="160"/>
+      <c r="H7" s="160"/>
+      <c r="I7" s="160"/>
+      <c r="J7" s="161"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="92"/>
-      <c r="B8" s="93"/>
-      <c r="C8" s="93"/>
-      <c r="D8" s="93"/>
-      <c r="E8" s="93"/>
-      <c r="F8" s="93"/>
-      <c r="G8" s="93"/>
-      <c r="H8" s="93"/>
-      <c r="I8" s="93"/>
-      <c r="J8" s="159"/>
+      <c r="A8" s="63"/>
+      <c r="B8" s="64"/>
+      <c r="C8" s="64"/>
+      <c r="D8" s="64"/>
+      <c r="E8" s="64"/>
+      <c r="F8" s="64"/>
+      <c r="G8" s="64"/>
+      <c r="H8" s="64"/>
+      <c r="I8" s="64"/>
+      <c r="J8" s="162"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="92"/>
-      <c r="B9" s="93"/>
-      <c r="C9" s="93"/>
-      <c r="D9" s="93"/>
-      <c r="E9" s="93"/>
-      <c r="F9" s="93"/>
-      <c r="G9" s="93"/>
-      <c r="H9" s="93"/>
-      <c r="I9" s="93"/>
-      <c r="J9" s="159"/>
+      <c r="A9" s="63"/>
+      <c r="B9" s="64"/>
+      <c r="C9" s="64"/>
+      <c r="D9" s="64"/>
+      <c r="E9" s="64"/>
+      <c r="F9" s="64"/>
+      <c r="G9" s="64"/>
+      <c r="H9" s="64"/>
+      <c r="I9" s="64"/>
+      <c r="J9" s="162"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="92"/>
-      <c r="B10" s="93"/>
-      <c r="C10" s="93"/>
-      <c r="D10" s="93"/>
-      <c r="E10" s="93"/>
-      <c r="F10" s="93"/>
-      <c r="G10" s="93"/>
-      <c r="H10" s="93"/>
-      <c r="I10" s="93"/>
-      <c r="J10" s="159"/>
+      <c r="A10" s="63"/>
+      <c r="B10" s="64"/>
+      <c r="C10" s="64"/>
+      <c r="D10" s="64"/>
+      <c r="E10" s="64"/>
+      <c r="F10" s="64"/>
+      <c r="G10" s="64"/>
+      <c r="H10" s="64"/>
+      <c r="I10" s="64"/>
+      <c r="J10" s="162"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="92"/>
-      <c r="B11" s="93"/>
-      <c r="C11" s="93"/>
-      <c r="D11" s="93"/>
-      <c r="E11" s="93"/>
-      <c r="F11" s="93"/>
-      <c r="G11" s="93"/>
-      <c r="H11" s="93"/>
-      <c r="I11" s="93"/>
-      <c r="J11" s="159"/>
+      <c r="A11" s="63"/>
+      <c r="B11" s="64"/>
+      <c r="C11" s="64"/>
+      <c r="D11" s="64"/>
+      <c r="E11" s="64"/>
+      <c r="F11" s="64"/>
+      <c r="G11" s="64"/>
+      <c r="H11" s="64"/>
+      <c r="I11" s="64"/>
+      <c r="J11" s="162"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="92"/>
-      <c r="B12" s="93"/>
-      <c r="C12" s="93"/>
-      <c r="D12" s="93"/>
-      <c r="E12" s="93"/>
-      <c r="F12" s="93"/>
-      <c r="G12" s="93"/>
-      <c r="H12" s="93"/>
-      <c r="I12" s="93"/>
-      <c r="J12" s="159"/>
+      <c r="A12" s="63"/>
+      <c r="B12" s="64"/>
+      <c r="C12" s="64"/>
+      <c r="D12" s="64"/>
+      <c r="E12" s="64"/>
+      <c r="F12" s="64"/>
+      <c r="G12" s="64"/>
+      <c r="H12" s="64"/>
+      <c r="I12" s="64"/>
+      <c r="J12" s="162"/>
     </row>
     <row r="13" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A13" s="92"/>
-      <c r="B13" s="93"/>
-      <c r="C13" s="93"/>
-      <c r="D13" s="93"/>
-      <c r="E13" s="93"/>
-      <c r="F13" s="93"/>
-      <c r="G13" s="93"/>
-      <c r="H13" s="93"/>
-      <c r="I13" s="93"/>
-      <c r="J13" s="159"/>
+      <c r="A13" s="63"/>
+      <c r="B13" s="64"/>
+      <c r="C13" s="64"/>
+      <c r="D13" s="64"/>
+      <c r="E13" s="64"/>
+      <c r="F13" s="64"/>
+      <c r="G13" s="64"/>
+      <c r="H13" s="64"/>
+      <c r="I13" s="64"/>
+      <c r="J13" s="162"/>
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A14" s="155" t="s">
+      <c r="A14" s="157" t="s">
         <v>24</v>
       </c>
-      <c r="B14" s="66"/>
-      <c r="C14" s="66"/>
-      <c r="D14" s="66"/>
-      <c r="E14" s="66"/>
-      <c r="F14" s="66"/>
-      <c r="G14" s="66"/>
-      <c r="H14" s="66"/>
-      <c r="I14" s="66"/>
-      <c r="J14" s="67"/>
+      <c r="B14" s="79"/>
+      <c r="C14" s="79"/>
+      <c r="D14" s="79"/>
+      <c r="E14" s="79"/>
+      <c r="F14" s="79"/>
+      <c r="G14" s="79"/>
+      <c r="H14" s="79"/>
+      <c r="I14" s="79"/>
+      <c r="J14" s="82"/>
     </row>
     <row r="15" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A15" s="155" t="s">
+      <c r="A15" s="157" t="s">
         <v>25</v>
       </c>
-      <c r="B15" s="66"/>
-      <c r="C15" s="61"/>
-      <c r="D15" s="65" t="s">
+      <c r="B15" s="79"/>
+      <c r="C15" s="80"/>
+      <c r="D15" s="88" t="s">
         <v>98</v>
       </c>
-      <c r="E15" s="66"/>
-      <c r="F15" s="66"/>
-      <c r="G15" s="66"/>
-      <c r="H15" s="61"/>
+      <c r="E15" s="79"/>
+      <c r="F15" s="79"/>
+      <c r="G15" s="79"/>
+      <c r="H15" s="80"/>
       <c r="I15" s="45" t="s">
         <v>26</v>
       </c>
@@ -11562,11 +11562,11 @@
       </c>
     </row>
     <row r="16" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A16" s="155" t="s">
+      <c r="A16" s="157" t="s">
         <v>27</v>
       </c>
-      <c r="B16" s="66"/>
-      <c r="C16" s="61"/>
+      <c r="B16" s="79"/>
+      <c r="C16" s="80"/>
       <c r="D16" s="45" t="s">
         <v>28</v>
       </c>
@@ -11579,18 +11579,18 @@
       <c r="G16" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="H16" s="163" t="s">
+      <c r="H16" s="158" t="s">
         <v>18</v>
       </c>
-      <c r="I16" s="66"/>
-      <c r="J16" s="67"/>
+      <c r="I16" s="79"/>
+      <c r="J16" s="82"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="164">
+      <c r="A17" s="155">
         <v>1</v>
       </c>
-      <c r="B17" s="66"/>
-      <c r="C17" s="61"/>
+      <c r="B17" s="79"/>
+      <c r="C17" s="80"/>
       <c r="D17" s="47" t="s">
         <v>75</v>
       </c>
@@ -11603,83 +11603,83 @@
       <c r="G17" s="48" t="s">
         <v>100</v>
       </c>
-      <c r="H17" s="65" t="s">
+      <c r="H17" s="88" t="s">
         <v>101</v>
       </c>
-      <c r="I17" s="66"/>
-      <c r="J17" s="67"/>
+      <c r="I17" s="79"/>
+      <c r="J17" s="82"/>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A18" s="164"/>
-      <c r="B18" s="66"/>
-      <c r="C18" s="61"/>
+      <c r="A18" s="155"/>
+      <c r="B18" s="79"/>
+      <c r="C18" s="80"/>
       <c r="D18" s="47"/>
       <c r="E18" s="47"/>
       <c r="F18" s="48"/>
       <c r="G18" s="48"/>
-      <c r="H18" s="65"/>
-      <c r="I18" s="66"/>
-      <c r="J18" s="67"/>
+      <c r="H18" s="88"/>
+      <c r="I18" s="79"/>
+      <c r="J18" s="82"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="164"/>
-      <c r="B19" s="66"/>
-      <c r="C19" s="61"/>
+      <c r="A19" s="155"/>
+      <c r="B19" s="79"/>
+      <c r="C19" s="80"/>
       <c r="D19" s="47"/>
       <c r="E19" s="47"/>
       <c r="F19" s="48"/>
       <c r="G19" s="48"/>
-      <c r="H19" s="65"/>
-      <c r="I19" s="66"/>
-      <c r="J19" s="67"/>
+      <c r="H19" s="88"/>
+      <c r="I19" s="79"/>
+      <c r="J19" s="82"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="164"/>
-      <c r="B20" s="66"/>
-      <c r="C20" s="61"/>
+      <c r="A20" s="155"/>
+      <c r="B20" s="79"/>
+      <c r="C20" s="80"/>
       <c r="D20" s="47"/>
       <c r="E20" s="47"/>
       <c r="F20" s="48"/>
       <c r="G20" s="48"/>
-      <c r="H20" s="65"/>
-      <c r="I20" s="66"/>
-      <c r="J20" s="67"/>
+      <c r="H20" s="88"/>
+      <c r="I20" s="79"/>
+      <c r="J20" s="82"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="164"/>
-      <c r="B21" s="66"/>
-      <c r="C21" s="61"/>
+      <c r="A21" s="155"/>
+      <c r="B21" s="79"/>
+      <c r="C21" s="80"/>
       <c r="D21" s="47"/>
       <c r="E21" s="47"/>
       <c r="F21" s="48"/>
       <c r="G21" s="48"/>
-      <c r="H21" s="65"/>
-      <c r="I21" s="66"/>
-      <c r="J21" s="67"/>
+      <c r="H21" s="88"/>
+      <c r="I21" s="79"/>
+      <c r="J21" s="82"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="164"/>
-      <c r="B22" s="66"/>
-      <c r="C22" s="61"/>
+      <c r="A22" s="155"/>
+      <c r="B22" s="79"/>
+      <c r="C22" s="80"/>
       <c r="D22" s="47"/>
       <c r="E22" s="47"/>
       <c r="F22" s="48"/>
       <c r="G22" s="48"/>
-      <c r="H22" s="65"/>
-      <c r="I22" s="66"/>
-      <c r="J22" s="67"/>
+      <c r="H22" s="88"/>
+      <c r="I22" s="79"/>
+      <c r="J22" s="82"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A23" s="165"/>
-      <c r="B23" s="73"/>
-      <c r="C23" s="74"/>
+      <c r="A23" s="156"/>
+      <c r="B23" s="84"/>
+      <c r="C23" s="85"/>
       <c r="D23" s="49"/>
       <c r="E23" s="49"/>
       <c r="F23" s="50"/>
       <c r="G23" s="50"/>
-      <c r="H23" s="75"/>
-      <c r="I23" s="73"/>
-      <c r="J23" s="76"/>
+      <c r="H23" s="86"/>
+      <c r="I23" s="84"/>
+      <c r="J23" s="87"/>
     </row>
     <row r="24" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="25" spans="1:10" ht="12.75" customHeight="1"/>
@@ -12660,22 +12660,6 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="31">
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="H22:J22"/>
-    <mergeCell ref="A23:C23"/>
-    <mergeCell ref="H23:J23"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="H19:J19"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="H20:J20"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="H21:J21"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="H16:J16"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="H17:J17"/>
     <mergeCell ref="A14:J14"/>
     <mergeCell ref="A15:C15"/>
     <mergeCell ref="A7:J13"/>
@@ -12691,6 +12675,22 @@
     <mergeCell ref="D5:J5"/>
     <mergeCell ref="A6:J6"/>
     <mergeCell ref="D15:H15"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="H16:J16"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="H18:J18"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="H17:J17"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="H23:J23"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="H19:J19"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="H20:J20"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="H21:J21"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -12710,7 +12710,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="18" customHeight="1">
-      <c r="A1" s="189" t="s">
+      <c r="A1" s="177" t="s">
         <v>32</v>
       </c>
       <c r="B1" s="111"/>
@@ -12721,14 +12721,14 @@
       <c r="G1" s="118" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="175"/>
-      <c r="I1" s="175"/>
+      <c r="H1" s="178"/>
+      <c r="I1" s="178"/>
       <c r="J1" s="119"/>
       <c r="K1" s="118" t="s">
         <v>5</v>
       </c>
-      <c r="L1" s="175"/>
-      <c r="M1" s="175"/>
+      <c r="L1" s="178"/>
+      <c r="M1" s="178"/>
       <c r="N1" s="119"/>
       <c r="O1" s="118" t="s">
         <v>6</v>
@@ -12741,7 +12741,7 @@
       <c r="S1" s="118" t="s">
         <v>8</v>
       </c>
-      <c r="T1" s="177"/>
+      <c r="T1" s="179"/>
     </row>
     <row r="2" spans="1:26" ht="18" customHeight="1">
       <c r="A2" s="113"/>
@@ -12751,19 +12751,19 @@
       <c r="E2" s="55"/>
       <c r="F2" s="114"/>
       <c r="G2" s="120"/>
-      <c r="H2" s="185"/>
-      <c r="I2" s="185"/>
+      <c r="H2" s="173"/>
+      <c r="I2" s="173"/>
       <c r="J2" s="121"/>
       <c r="K2" s="120"/>
-      <c r="L2" s="185"/>
-      <c r="M2" s="185"/>
+      <c r="L2" s="173"/>
+      <c r="M2" s="173"/>
       <c r="N2" s="121"/>
       <c r="O2" s="120"/>
       <c r="P2" s="121"/>
       <c r="Q2" s="120"/>
       <c r="R2" s="121"/>
       <c r="S2" s="120"/>
-      <c r="T2" s="186"/>
+      <c r="T2" s="174"/>
     </row>
     <row r="3" spans="1:26" ht="18" customHeight="1">
       <c r="A3" s="113"/>
@@ -12785,7 +12785,7 @@
       <c r="Q3" s="122"/>
       <c r="R3" s="114"/>
       <c r="S3" s="122"/>
-      <c r="T3" s="187"/>
+      <c r="T3" s="175"/>
     </row>
     <row r="4" spans="1:26" ht="18" customHeight="1">
       <c r="A4" s="115"/>
@@ -12807,36 +12807,36 @@
       <c r="Q4" s="123"/>
       <c r="R4" s="117"/>
       <c r="S4" s="123"/>
-      <c r="T4" s="188"/>
+      <c r="T4" s="176"/>
     </row>
     <row r="5" spans="1:26" ht="18" customHeight="1">
-      <c r="A5" s="174" t="s">
+      <c r="A5" s="180" t="s">
         <v>33</v>
       </c>
-      <c r="B5" s="175"/>
-      <c r="C5" s="175"/>
-      <c r="D5" s="175"/>
-      <c r="E5" s="175"/>
+      <c r="B5" s="178"/>
+      <c r="C5" s="178"/>
+      <c r="D5" s="178"/>
+      <c r="E5" s="178"/>
       <c r="F5" s="119"/>
-      <c r="G5" s="176" t="s">
+      <c r="G5" s="181" t="s">
         <v>34</v>
       </c>
-      <c r="H5" s="175"/>
-      <c r="I5" s="175"/>
-      <c r="J5" s="175"/>
-      <c r="K5" s="175"/>
-      <c r="L5" s="175"/>
-      <c r="M5" s="175"/>
-      <c r="N5" s="175"/>
-      <c r="O5" s="175"/>
-      <c r="P5" s="175"/>
-      <c r="Q5" s="175"/>
-      <c r="R5" s="175"/>
-      <c r="S5" s="175"/>
-      <c r="T5" s="177"/>
+      <c r="H5" s="178"/>
+      <c r="I5" s="178"/>
+      <c r="J5" s="178"/>
+      <c r="K5" s="178"/>
+      <c r="L5" s="178"/>
+      <c r="M5" s="178"/>
+      <c r="N5" s="178"/>
+      <c r="O5" s="178"/>
+      <c r="P5" s="178"/>
+      <c r="Q5" s="178"/>
+      <c r="R5" s="178"/>
+      <c r="S5" s="178"/>
+      <c r="T5" s="179"/>
     </row>
     <row r="6" spans="1:26" ht="18" customHeight="1">
-      <c r="A6" s="178" t="s">
+      <c r="A6" s="182" t="s">
         <v>35</v>
       </c>
       <c r="B6" s="52"/>
@@ -12844,7 +12844,7 @@
       <c r="D6" s="52"/>
       <c r="E6" s="52"/>
       <c r="F6" s="53"/>
-      <c r="G6" s="179" t="s">
+      <c r="G6" s="183" t="s">
         <v>19</v>
       </c>
       <c r="H6" s="52"/>
@@ -12859,10 +12859,10 @@
       <c r="Q6" s="52"/>
       <c r="R6" s="52"/>
       <c r="S6" s="52"/>
-      <c r="T6" s="180"/>
+      <c r="T6" s="184"/>
     </row>
     <row r="7" spans="1:26" ht="18" customHeight="1">
-      <c r="A7" s="178" t="s">
+      <c r="A7" s="182" t="s">
         <v>36</v>
       </c>
       <c r="B7" s="52"/>
@@ -12870,7 +12870,7 @@
       <c r="D7" s="52"/>
       <c r="E7" s="52"/>
       <c r="F7" s="53"/>
-      <c r="G7" s="179" t="s">
+      <c r="G7" s="183" t="s">
         <v>37</v>
       </c>
       <c r="H7" s="52"/>
@@ -12885,7 +12885,7 @@
       <c r="Q7" s="52"/>
       <c r="R7" s="52"/>
       <c r="S7" s="52"/>
-      <c r="T7" s="180"/>
+      <c r="T7" s="184"/>
     </row>
     <row r="8" spans="1:26" ht="7.5" customHeight="1">
       <c r="A8" s="7"/>
@@ -13084,33 +13084,33 @@
       <c r="T14" s="9"/>
     </row>
     <row r="15" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A15" s="178" t="s">
+      <c r="A15" s="182" t="s">
         <v>44</v>
       </c>
       <c r="B15" s="53"/>
-      <c r="C15" s="184" t="s">
+      <c r="C15" s="188" t="s">
         <v>38</v>
       </c>
       <c r="D15" s="53"/>
-      <c r="E15" s="182" t="s">
+      <c r="E15" s="166" t="s">
         <v>45</v>
       </c>
       <c r="F15" s="53"/>
-      <c r="G15" s="182" t="s">
+      <c r="G15" s="166" t="s">
         <v>46</v>
       </c>
       <c r="H15" s="52"/>
       <c r="I15" s="53"/>
-      <c r="J15" s="182" t="s">
+      <c r="J15" s="166" t="s">
         <v>47</v>
       </c>
       <c r="K15" s="53"/>
-      <c r="L15" s="182" t="s">
+      <c r="L15" s="166" t="s">
         <v>48</v>
       </c>
       <c r="M15" s="52"/>
       <c r="N15" s="53"/>
-      <c r="O15" s="182" t="s">
+      <c r="O15" s="166" t="s">
         <v>49</v>
       </c>
       <c r="P15" s="52"/>
@@ -13126,28 +13126,28 @@
       </c>
     </row>
     <row r="16" spans="1:26" ht="48" customHeight="1">
-      <c r="A16" s="166">
+      <c r="A16" s="185">
         <v>1</v>
       </c>
       <c r="B16" s="53"/>
-      <c r="C16" s="167" t="s">
+      <c r="C16" s="186" t="s">
         <v>53</v>
       </c>
       <c r="D16" s="53"/>
-      <c r="E16" s="167" t="s">
+      <c r="E16" s="186" t="s">
         <v>54</v>
       </c>
       <c r="F16" s="53"/>
-      <c r="G16" s="181" t="s">
+      <c r="G16" s="167" t="s">
         <v>55</v>
       </c>
       <c r="H16" s="52"/>
       <c r="I16" s="53"/>
-      <c r="J16" s="181" t="s">
+      <c r="J16" s="167" t="s">
         <v>56</v>
       </c>
       <c r="K16" s="53"/>
-      <c r="L16" s="183" t="s">
+      <c r="L16" s="187" t="s">
         <v>65</v>
       </c>
       <c r="M16" s="52"/>
@@ -13168,24 +13168,24 @@
       <c r="Z16" s="29"/>
     </row>
     <row r="17" spans="1:26" ht="41.25" customHeight="1">
-      <c r="A17" s="166">
+      <c r="A17" s="185">
         <v>2</v>
       </c>
       <c r="B17" s="53"/>
-      <c r="C17" s="167" t="s">
+      <c r="C17" s="186" t="s">
         <v>58</v>
       </c>
       <c r="D17" s="53"/>
-      <c r="E17" s="167" t="s">
+      <c r="E17" s="186" t="s">
         <v>59</v>
       </c>
       <c r="F17" s="53"/>
-      <c r="G17" s="181" t="s">
+      <c r="G17" s="167" t="s">
         <v>60</v>
       </c>
       <c r="H17" s="52"/>
       <c r="I17" s="53"/>
-      <c r="J17" s="181" t="s">
+      <c r="J17" s="167" t="s">
         <v>61</v>
       </c>
       <c r="K17" s="53"/>
@@ -13210,16 +13210,16 @@
       <c r="Z17" s="29"/>
     </row>
     <row r="18" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A18" s="166"/>
+      <c r="A18" s="185"/>
       <c r="B18" s="53"/>
-      <c r="C18" s="167"/>
+      <c r="C18" s="186"/>
       <c r="D18" s="53"/>
-      <c r="E18" s="167"/>
+      <c r="E18" s="186"/>
       <c r="F18" s="53"/>
-      <c r="G18" s="181"/>
+      <c r="G18" s="167"/>
       <c r="H18" s="52"/>
       <c r="I18" s="53"/>
-      <c r="J18" s="181"/>
+      <c r="J18" s="167"/>
       <c r="K18" s="53"/>
       <c r="L18" s="171"/>
       <c r="M18" s="52"/>
@@ -13238,16 +13238,16 @@
       <c r="Z18" s="29"/>
     </row>
     <row r="19" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A19" s="166"/>
+      <c r="A19" s="185"/>
       <c r="B19" s="53"/>
-      <c r="C19" s="167"/>
+      <c r="C19" s="186"/>
       <c r="D19" s="53"/>
-      <c r="E19" s="167"/>
+      <c r="E19" s="186"/>
       <c r="F19" s="53"/>
-      <c r="G19" s="181"/>
+      <c r="G19" s="167"/>
       <c r="H19" s="52"/>
       <c r="I19" s="53"/>
-      <c r="J19" s="181"/>
+      <c r="J19" s="167"/>
       <c r="K19" s="53"/>
       <c r="L19" s="171"/>
       <c r="M19" s="52"/>
@@ -13266,16 +13266,16 @@
       <c r="Z19" s="29"/>
     </row>
     <row r="20" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A20" s="166"/>
+      <c r="A20" s="185"/>
       <c r="B20" s="53"/>
-      <c r="C20" s="167"/>
+      <c r="C20" s="186"/>
       <c r="D20" s="53"/>
-      <c r="E20" s="167"/>
+      <c r="E20" s="186"/>
       <c r="F20" s="53"/>
-      <c r="G20" s="181"/>
+      <c r="G20" s="167"/>
       <c r="H20" s="52"/>
       <c r="I20" s="53"/>
-      <c r="J20" s="181"/>
+      <c r="J20" s="167"/>
       <c r="K20" s="53"/>
       <c r="L20" s="171"/>
       <c r="M20" s="52"/>
@@ -13294,16 +13294,16 @@
       <c r="Z20" s="29"/>
     </row>
     <row r="21" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A21" s="166"/>
+      <c r="A21" s="185"/>
       <c r="B21" s="53"/>
-      <c r="C21" s="167"/>
+      <c r="C21" s="186"/>
       <c r="D21" s="53"/>
-      <c r="E21" s="167"/>
+      <c r="E21" s="186"/>
       <c r="F21" s="53"/>
-      <c r="G21" s="181"/>
+      <c r="G21" s="167"/>
       <c r="H21" s="52"/>
       <c r="I21" s="53"/>
-      <c r="J21" s="181"/>
+      <c r="J21" s="167"/>
       <c r="K21" s="53"/>
       <c r="L21" s="171"/>
       <c r="M21" s="52"/>
@@ -13322,16 +13322,16 @@
       <c r="Z21" s="29"/>
     </row>
     <row r="22" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A22" s="166"/>
+      <c r="A22" s="185"/>
       <c r="B22" s="53"/>
-      <c r="C22" s="167"/>
+      <c r="C22" s="186"/>
       <c r="D22" s="53"/>
-      <c r="E22" s="167"/>
+      <c r="E22" s="186"/>
       <c r="F22" s="53"/>
-      <c r="G22" s="181"/>
+      <c r="G22" s="167"/>
       <c r="H22" s="52"/>
       <c r="I22" s="53"/>
-      <c r="J22" s="181"/>
+      <c r="J22" s="167"/>
       <c r="K22" s="53"/>
       <c r="L22" s="171"/>
       <c r="M22" s="52"/>
@@ -13350,16 +13350,16 @@
       <c r="Z22" s="29"/>
     </row>
     <row r="23" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A23" s="166"/>
+      <c r="A23" s="185"/>
       <c r="B23" s="53"/>
-      <c r="C23" s="167"/>
+      <c r="C23" s="186"/>
       <c r="D23" s="53"/>
-      <c r="E23" s="167"/>
+      <c r="E23" s="186"/>
       <c r="F23" s="53"/>
-      <c r="G23" s="181"/>
+      <c r="G23" s="167"/>
       <c r="H23" s="52"/>
       <c r="I23" s="53"/>
-      <c r="J23" s="181"/>
+      <c r="J23" s="167"/>
       <c r="K23" s="53"/>
       <c r="L23" s="171"/>
       <c r="M23" s="52"/>
@@ -13378,16 +13378,16 @@
       <c r="Z23" s="29"/>
     </row>
     <row r="24" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A24" s="166"/>
+      <c r="A24" s="185"/>
       <c r="B24" s="53"/>
-      <c r="C24" s="167"/>
+      <c r="C24" s="186"/>
       <c r="D24" s="53"/>
-      <c r="E24" s="167"/>
+      <c r="E24" s="186"/>
       <c r="F24" s="53"/>
-      <c r="G24" s="181"/>
+      <c r="G24" s="167"/>
       <c r="H24" s="52"/>
       <c r="I24" s="53"/>
-      <c r="J24" s="181"/>
+      <c r="J24" s="167"/>
       <c r="K24" s="53"/>
       <c r="L24" s="171"/>
       <c r="M24" s="52"/>
@@ -13406,16 +13406,16 @@
       <c r="Z24" s="29"/>
     </row>
     <row r="25" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A25" s="166"/>
+      <c r="A25" s="185"/>
       <c r="B25" s="53"/>
-      <c r="C25" s="167"/>
+      <c r="C25" s="186"/>
       <c r="D25" s="53"/>
-      <c r="E25" s="167"/>
+      <c r="E25" s="186"/>
       <c r="F25" s="53"/>
-      <c r="G25" s="181"/>
+      <c r="G25" s="167"/>
       <c r="H25" s="52"/>
       <c r="I25" s="53"/>
-      <c r="J25" s="181"/>
+      <c r="J25" s="167"/>
       <c r="K25" s="53"/>
       <c r="L25" s="171"/>
       <c r="M25" s="52"/>
@@ -13434,16 +13434,16 @@
       <c r="Z25" s="29"/>
     </row>
     <row r="26" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A26" s="166"/>
+      <c r="A26" s="185"/>
       <c r="B26" s="53"/>
-      <c r="C26" s="167"/>
+      <c r="C26" s="186"/>
       <c r="D26" s="53"/>
-      <c r="E26" s="167"/>
+      <c r="E26" s="186"/>
       <c r="F26" s="53"/>
-      <c r="G26" s="181"/>
+      <c r="G26" s="167"/>
       <c r="H26" s="52"/>
       <c r="I26" s="53"/>
-      <c r="J26" s="181"/>
+      <c r="J26" s="167"/>
       <c r="K26" s="53"/>
       <c r="L26" s="171"/>
       <c r="M26" s="52"/>
@@ -13462,16 +13462,16 @@
       <c r="Z26" s="29"/>
     </row>
     <row r="27" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A27" s="166"/>
+      <c r="A27" s="185"/>
       <c r="B27" s="53"/>
-      <c r="C27" s="167"/>
+      <c r="C27" s="186"/>
       <c r="D27" s="53"/>
-      <c r="E27" s="167"/>
+      <c r="E27" s="186"/>
       <c r="F27" s="53"/>
-      <c r="G27" s="181"/>
+      <c r="G27" s="167"/>
       <c r="H27" s="52"/>
       <c r="I27" s="53"/>
-      <c r="J27" s="181"/>
+      <c r="J27" s="167"/>
       <c r="K27" s="53"/>
       <c r="L27" s="171"/>
       <c r="M27" s="52"/>
@@ -13490,16 +13490,16 @@
       <c r="Z27" s="29"/>
     </row>
     <row r="28" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A28" s="166"/>
+      <c r="A28" s="185"/>
       <c r="B28" s="53"/>
-      <c r="C28" s="167"/>
+      <c r="C28" s="186"/>
       <c r="D28" s="53"/>
-      <c r="E28" s="167"/>
+      <c r="E28" s="186"/>
       <c r="F28" s="53"/>
-      <c r="G28" s="181"/>
+      <c r="G28" s="167"/>
       <c r="H28" s="52"/>
       <c r="I28" s="53"/>
-      <c r="J28" s="181"/>
+      <c r="J28" s="167"/>
       <c r="K28" s="53"/>
       <c r="L28" s="171"/>
       <c r="M28" s="52"/>
@@ -13518,16 +13518,16 @@
       <c r="Z28" s="29"/>
     </row>
     <row r="29" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A29" s="166"/>
+      <c r="A29" s="185"/>
       <c r="B29" s="53"/>
-      <c r="C29" s="167"/>
+      <c r="C29" s="186"/>
       <c r="D29" s="53"/>
-      <c r="E29" s="167"/>
+      <c r="E29" s="186"/>
       <c r="F29" s="53"/>
-      <c r="G29" s="181"/>
+      <c r="G29" s="167"/>
       <c r="H29" s="52"/>
       <c r="I29" s="53"/>
-      <c r="J29" s="181"/>
+      <c r="J29" s="167"/>
       <c r="K29" s="53"/>
       <c r="L29" s="171"/>
       <c r="M29" s="52"/>
@@ -13546,16 +13546,16 @@
       <c r="Z29" s="29"/>
     </row>
     <row r="30" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A30" s="166"/>
+      <c r="A30" s="185"/>
       <c r="B30" s="53"/>
-      <c r="C30" s="167"/>
+      <c r="C30" s="186"/>
       <c r="D30" s="53"/>
-      <c r="E30" s="167"/>
+      <c r="E30" s="186"/>
       <c r="F30" s="53"/>
-      <c r="G30" s="181"/>
+      <c r="G30" s="167"/>
       <c r="H30" s="52"/>
       <c r="I30" s="53"/>
-      <c r="J30" s="181"/>
+      <c r="J30" s="167"/>
       <c r="K30" s="53"/>
       <c r="L30" s="171"/>
       <c r="M30" s="52"/>
@@ -13574,23 +13574,23 @@
       <c r="Z30" s="29"/>
     </row>
     <row r="31" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A31" s="168"/>
-      <c r="B31" s="169"/>
-      <c r="C31" s="170"/>
-      <c r="D31" s="169"/>
-      <c r="E31" s="170"/>
-      <c r="F31" s="169"/>
-      <c r="G31" s="190"/>
-      <c r="H31" s="173"/>
-      <c r="I31" s="169"/>
-      <c r="J31" s="190"/>
-      <c r="K31" s="169"/>
+      <c r="A31" s="189"/>
+      <c r="B31" s="170"/>
+      <c r="C31" s="190"/>
+      <c r="D31" s="170"/>
+      <c r="E31" s="190"/>
+      <c r="F31" s="170"/>
+      <c r="G31" s="168"/>
+      <c r="H31" s="169"/>
+      <c r="I31" s="170"/>
+      <c r="J31" s="168"/>
+      <c r="K31" s="170"/>
       <c r="L31" s="172"/>
-      <c r="M31" s="173"/>
-      <c r="N31" s="169"/>
+      <c r="M31" s="169"/>
+      <c r="N31" s="170"/>
       <c r="O31" s="172"/>
-      <c r="P31" s="173"/>
-      <c r="Q31" s="169"/>
+      <c r="P31" s="169"/>
+      <c r="Q31" s="170"/>
       <c r="R31" s="30"/>
       <c r="S31" s="30"/>
       <c r="T31" s="31"/>
@@ -14588,62 +14588,62 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="136">
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="J18:K18"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="J19:K19"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="G23:I23"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="J30:K30"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="J29:K29"/>
-    <mergeCell ref="L26:N26"/>
-    <mergeCell ref="L27:N27"/>
-    <mergeCell ref="L28:N28"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="L18:N18"/>
-    <mergeCell ref="L19:N19"/>
-    <mergeCell ref="L21:N21"/>
-    <mergeCell ref="L22:N22"/>
-    <mergeCell ref="L23:N23"/>
-    <mergeCell ref="L24:N24"/>
-    <mergeCell ref="L25:N25"/>
-    <mergeCell ref="K2:N4"/>
-    <mergeCell ref="O2:P4"/>
-    <mergeCell ref="Q2:R4"/>
-    <mergeCell ref="S2:T4"/>
-    <mergeCell ref="A1:F4"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="O1:P1"/>
-    <mergeCell ref="Q1:R1"/>
-    <mergeCell ref="S1:T1"/>
-    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="E30:F30"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="E31:F31"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="E26:F26"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="E29:F29"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="E27:F27"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="E28:F28"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="O27:Q27"/>
+    <mergeCell ref="O28:Q28"/>
+    <mergeCell ref="O29:Q29"/>
+    <mergeCell ref="O30:Q30"/>
+    <mergeCell ref="O31:Q31"/>
+    <mergeCell ref="O19:Q19"/>
+    <mergeCell ref="O21:Q21"/>
+    <mergeCell ref="O22:Q22"/>
+    <mergeCell ref="O23:Q23"/>
+    <mergeCell ref="O24:Q24"/>
+    <mergeCell ref="O25:Q25"/>
+    <mergeCell ref="O26:Q26"/>
     <mergeCell ref="A5:F5"/>
     <mergeCell ref="G5:T5"/>
     <mergeCell ref="A6:F6"/>
@@ -14668,62 +14668,62 @@
     <mergeCell ref="C15:D15"/>
     <mergeCell ref="E15:F15"/>
     <mergeCell ref="A16:B16"/>
-    <mergeCell ref="O27:Q27"/>
-    <mergeCell ref="O28:Q28"/>
-    <mergeCell ref="O29:Q29"/>
-    <mergeCell ref="O30:Q30"/>
-    <mergeCell ref="O31:Q31"/>
-    <mergeCell ref="O19:Q19"/>
-    <mergeCell ref="O21:Q21"/>
-    <mergeCell ref="O22:Q22"/>
-    <mergeCell ref="O23:Q23"/>
-    <mergeCell ref="O24:Q24"/>
-    <mergeCell ref="O25:Q25"/>
-    <mergeCell ref="O26:Q26"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="E30:F30"/>
-    <mergeCell ref="A31:B31"/>
-    <mergeCell ref="C31:D31"/>
-    <mergeCell ref="E31:F31"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="E26:F26"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="E24:F24"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="E29:F29"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="E27:F27"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="E28:F28"/>
-    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="K2:N4"/>
+    <mergeCell ref="O2:P4"/>
+    <mergeCell ref="Q2:R4"/>
+    <mergeCell ref="S2:T4"/>
+    <mergeCell ref="A1:F4"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="S1:T1"/>
+    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="L26:N26"/>
+    <mergeCell ref="L27:N27"/>
+    <mergeCell ref="L28:N28"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="L18:N18"/>
+    <mergeCell ref="L19:N19"/>
+    <mergeCell ref="L21:N21"/>
+    <mergeCell ref="L22:N22"/>
+    <mergeCell ref="L23:N23"/>
+    <mergeCell ref="L24:N24"/>
+    <mergeCell ref="L25:N25"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="J30:K30"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="J29:K29"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="J19:K19"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <hyperlinks>

--- a/Documents/登録機能詳細設計書.xlsx
+++ b/Documents/登録機能詳細設計書.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\S-47\Documents\project\taskUN\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB685EA4-08F4-4E8C-96F5-63BE208464CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09690924-873F-4C22-AC9A-7DFDB2E38A57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="7" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="8" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="1" r:id="rId1"/>
@@ -23,13 +23,21 @@
     <sheet name="画面設計書-登録完了画面" sheetId="11" r:id="rId8"/>
     <sheet name="画面設計書-エラー(登録失敗)画面" sheetId="12" r:id="rId9"/>
     <sheet name="テスト仕様書兼結果報告書" sheetId="6" r:id="rId10"/>
+    <sheet name="JUnitテスト仕様書兼報告書" sheetId="15" r:id="rId11"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId12"/>
+  </externalReferences>
+  <definedNames>
+    <definedName name="範囲１" localSheetId="10">#REF!</definedName>
+    <definedName name="範囲１">#REF!</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="142">
   <si>
     <t>プロジェクト型演習　成果ドキュメント</t>
   </si>
@@ -789,10 +797,6 @@
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t>タスク名が未入力ではない、ユーザーIDが未入力ではない、メモが100文字以下、ユーザーIDが24文字以下であること</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
     <t>タスク登録成功画面が表示される</t>
     <rPh sb="3" eb="5">
       <t>トウロク</t>
@@ -804,49 +808,6 @@
       <t>ガメン</t>
     </rPh>
     <rPh sb="10" eb="12">
-      <t>ヒョウジ</t>
-    </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>タスク名が未入力、ユーザーIDが未入力、メモが100文字より多い、ユーザーIDが24文字より多い場合でタスク登録を行ったときタスク登録失敗ページが表示される</t>
-    <rPh sb="3" eb="4">
-      <t>メイ</t>
-    </rPh>
-    <rPh sb="5" eb="8">
-      <t>ミニュウリョク</t>
-    </rPh>
-    <rPh sb="16" eb="19">
-      <t>ミニュウリョク</t>
-    </rPh>
-    <rPh sb="26" eb="28">
-      <t>モジ</t>
-    </rPh>
-    <rPh sb="30" eb="31">
-      <t>オオ</t>
-    </rPh>
-    <rPh sb="42" eb="44">
-      <t>モジ</t>
-    </rPh>
-    <rPh sb="46" eb="47">
-      <t>オオ</t>
-    </rPh>
-    <rPh sb="48" eb="50">
-      <t>バアイ</t>
-    </rPh>
-    <rPh sb="54" eb="56">
-      <t>トウロク</t>
-    </rPh>
-    <rPh sb="57" eb="58">
-      <t>オコナ</t>
-    </rPh>
-    <rPh sb="65" eb="67">
-      <t>トウロク</t>
-    </rPh>
-    <rPh sb="67" eb="69">
-      <t>シッパイ</t>
-    </rPh>
-    <rPh sb="73" eb="75">
       <t>ヒョウジ</t>
     </rPh>
     <phoneticPr fontId="8"/>
@@ -878,58 +839,6 @@
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t>タスク名が未入力ではない、ユーザーIDが未入力ではない、メモが100文字以下、ユーザーIDが24文字以下の場合、指定された期限が今日より後でタスク登録を行ったときタスク登録成功ページが表示される</t>
-    <rPh sb="3" eb="4">
-      <t>メイ</t>
-    </rPh>
-    <rPh sb="5" eb="8">
-      <t>ミニュウリョク</t>
-    </rPh>
-    <rPh sb="20" eb="23">
-      <t>ミニュウリョク</t>
-    </rPh>
-    <rPh sb="34" eb="38">
-      <t>モジイカ</t>
-    </rPh>
-    <rPh sb="48" eb="50">
-      <t>モジ</t>
-    </rPh>
-    <rPh sb="50" eb="52">
-      <t>イカ</t>
-    </rPh>
-    <rPh sb="53" eb="55">
-      <t>バアイ</t>
-    </rPh>
-    <rPh sb="56" eb="58">
-      <t>シテイ</t>
-    </rPh>
-    <rPh sb="61" eb="63">
-      <t>キゲン</t>
-    </rPh>
-    <rPh sb="64" eb="66">
-      <t>キョウ</t>
-    </rPh>
-    <rPh sb="68" eb="69">
-      <t>アト</t>
-    </rPh>
-    <rPh sb="73" eb="75">
-      <t>トウロク</t>
-    </rPh>
-    <rPh sb="76" eb="77">
-      <t>オコナ</t>
-    </rPh>
-    <rPh sb="84" eb="86">
-      <t>トウロク</t>
-    </rPh>
-    <rPh sb="86" eb="88">
-      <t>セイコウ</t>
-    </rPh>
-    <rPh sb="92" eb="94">
-      <t>ヒョウジ</t>
-    </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
     <t>ログインされていませんというメッセージとログイン画面に誘導するリンクが表示される</t>
     <rPh sb="24" eb="26">
       <t>ガメン</t>
@@ -942,6 +851,185 @@
     </rPh>
     <phoneticPr fontId="8"/>
   </si>
+  <si>
+    <t>タスク名、ユーザーID、メモ、期限を入力しタスク登録を行ったときタスク登録成功ページが表示される</t>
+    <rPh sb="3" eb="4">
+      <t>メイ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>キゲン</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="27" eb="28">
+      <t>オコナ</t>
+    </rPh>
+    <rPh sb="35" eb="37">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="37" eb="39">
+      <t>セイコウ</t>
+    </rPh>
+    <rPh sb="43" eb="45">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>タスク名が未入力ではない、ユーザーIDが未入力ではない、メモが100文字以下、ユーザーIDが24文字以下、期限が今日より後であること</t>
+    <rPh sb="53" eb="55">
+      <t>キゲン</t>
+    </rPh>
+    <rPh sb="56" eb="58">
+      <t>キョウ</t>
+    </rPh>
+    <rPh sb="60" eb="61">
+      <t>アト</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>タスク名、ユーザーID、メモ、期限を入力せずタスク登録を行ったときタスク登録失敗ページが表示される</t>
+    <rPh sb="3" eb="4">
+      <t>メイ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>キゲン</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="28" eb="29">
+      <t>オコナ</t>
+    </rPh>
+    <rPh sb="36" eb="38">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="38" eb="40">
+      <t>シッパイ</t>
+    </rPh>
+    <rPh sb="44" eb="46">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>JUnitテスト仕様書兼報告書</t>
+    <rPh sb="8" eb="11">
+      <t>シヨウショ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>ケン</t>
+    </rPh>
+    <rPh sb="12" eb="15">
+      <t>ホウコクショ</t>
+    </rPh>
+    <phoneticPr fontId="16"/>
+  </si>
+  <si>
+    <t>システム名</t>
+    <rPh sb="4" eb="5">
+      <t>メイ</t>
+    </rPh>
+    <phoneticPr fontId="16"/>
+  </si>
+  <si>
+    <t>作成者</t>
+  </si>
+  <si>
+    <t>会社名</t>
+    <rPh sb="0" eb="3">
+      <t>カイシャメイ</t>
+    </rPh>
+    <phoneticPr fontId="16"/>
+  </si>
+  <si>
+    <t>コンサイズ</t>
+    <phoneticPr fontId="16"/>
+  </si>
+  <si>
+    <t>サブシステム名</t>
+    <rPh sb="6" eb="7">
+      <t>メイ</t>
+    </rPh>
+    <phoneticPr fontId="16"/>
+  </si>
+  <si>
+    <t>作成日</t>
+    <rPh sb="0" eb="3">
+      <t>サクセイビ</t>
+    </rPh>
+    <phoneticPr fontId="16"/>
+  </si>
+  <si>
+    <t>実施者</t>
+    <rPh sb="0" eb="2">
+      <t>ジッシ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>シャ</t>
+    </rPh>
+    <phoneticPr fontId="16"/>
+  </si>
+  <si>
+    <t>No</t>
+    <phoneticPr fontId="16"/>
+  </si>
+  <si>
+    <t>分類</t>
+    <rPh sb="0" eb="2">
+      <t>ブンルイ</t>
+    </rPh>
+    <phoneticPr fontId="16"/>
+  </si>
+  <si>
+    <t>テストクラス</t>
+    <phoneticPr fontId="16"/>
+  </si>
+  <si>
+    <t>検証するメソッド</t>
+    <rPh sb="0" eb="2">
+      <t>ケンショウ</t>
+    </rPh>
+    <phoneticPr fontId="16"/>
+  </si>
+  <si>
+    <t>期待する結果</t>
+    <rPh sb="0" eb="2">
+      <t>キタイ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ケッカ</t>
+    </rPh>
+    <phoneticPr fontId="16"/>
+  </si>
+  <si>
+    <t>実施日</t>
+    <rPh sb="0" eb="3">
+      <t>ジッシビ</t>
+    </rPh>
+    <phoneticPr fontId="16"/>
+  </si>
+  <si>
+    <t>備考・特記事項</t>
+    <rPh sb="0" eb="2">
+      <t>ビコウ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>トッキ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ジコウ</t>
+    </rPh>
+    <phoneticPr fontId="16"/>
+  </si>
 </sst>
 </file>
 
@@ -950,7 +1038,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="[$-411]h:mm"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -1050,8 +1138,46 @@
       <charset val="128"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="6"/>
+      <name val="明朝"/>
+      <family val="1"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1064,8 +1190,14 @@
         <bgColor rgb="FFD9D9D9"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-4.9989318521683403E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="57">
+  <borders count="71">
     <border>
       <left/>
       <right/>
@@ -1725,15 +1857,195 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="hair">
+        <color indexed="64"/>
+      </left>
+      <right style="hair">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="hair">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="hair">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="hair">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="hair">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="hair">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="hair">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="hair">
+        <color indexed="64"/>
+      </left>
+      <right style="hair">
+        <color indexed="64"/>
+      </right>
+      <top style="hair">
+        <color indexed="64"/>
+      </top>
+      <bottom style="hair">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="hair">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="hair">
+        <color indexed="64"/>
+      </top>
+      <bottom style="hair">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="hair">
+        <color indexed="64"/>
+      </top>
+      <bottom style="hair">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="hair">
+        <color indexed="64"/>
+      </right>
+      <top style="hair">
+        <color indexed="64"/>
+      </top>
+      <bottom style="hair">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="5">
+  <cellStyleXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="193">
+  <cellXfs count="236">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1914,6 +2226,93 @@
     <xf numFmtId="14" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1944,9 +2343,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1959,90 +2355,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2121,6 +2433,12 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2193,10 +2511,31 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2205,121 +2544,225 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="5" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="57" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="58" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="59" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="60" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="58" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="59" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="60" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="57" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="5" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="18" fillId="0" borderId="58" xfId="6" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="18" fillId="0" borderId="60" xfId="6" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="57" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="18" fillId="0" borderId="58" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="60" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="61" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="61" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="57" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="62" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="58" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="59" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="60" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="63" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="63" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="63" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="64" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="65" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="66" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="64" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="66" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="67" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="67" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="68" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="5" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="69" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="70" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="18" fillId="0" borderId="67" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="67" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="68" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="69" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="70" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="68" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="69" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="70" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="5" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="5">
+  <cellStyles count="7">
     <cellStyle name="ハイパーリンク" xfId="1" builtinId="8"/>
     <cellStyle name="標準" xfId="0" builtinId="0"/>
     <cellStyle name="標準 2" xfId="2" xr:uid="{34200FF7-2CB0-43CE-9E54-7B88C1A054C5}"/>
     <cellStyle name="標準 2 2" xfId="3" xr:uid="{27F598B5-3CA0-4DB2-BB0A-B46AD58157ED}"/>
     <cellStyle name="標準 3" xfId="4" xr:uid="{64517715-78F6-483F-A73E-3584FBD47293}"/>
+    <cellStyle name="標準_生産計画ED書" xfId="5" xr:uid="{DAF71B83-AD85-4492-B576-533DAD2D280C}"/>
+    <cellStyle name="標準_東京理科大DBレイアウト" xfId="6" xr:uid="{691F0CCF-F00E-45EC-8616-60155DDBDDF4}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -3247,6 +3690,24 @@
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
+</file>
+
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="JUnitテスト仕様書兼報告書"/>
+      <sheetName val="別紙"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -4626,7 +5087,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="18" customHeight="1">
-      <c r="A1" s="179" t="s">
+      <c r="A1" s="190" t="s">
         <v>32</v>
       </c>
       <c r="B1" s="111"/>
@@ -4637,14 +5098,14 @@
       <c r="G1" s="118" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="180"/>
-      <c r="I1" s="180"/>
+      <c r="H1" s="175"/>
+      <c r="I1" s="175"/>
       <c r="J1" s="119"/>
       <c r="K1" s="118" t="s">
         <v>5</v>
       </c>
-      <c r="L1" s="180"/>
-      <c r="M1" s="180"/>
+      <c r="L1" s="175"/>
+      <c r="M1" s="175"/>
       <c r="N1" s="119"/>
       <c r="O1" s="118" t="s">
         <v>6</v>
@@ -4657,7 +5118,7 @@
       <c r="S1" s="118" t="s">
         <v>8</v>
       </c>
-      <c r="T1" s="181"/>
+      <c r="T1" s="177"/>
     </row>
     <row r="2" spans="1:26" ht="18" customHeight="1">
       <c r="A2" s="113"/>
@@ -4669,16 +5130,16 @@
       <c r="G2" s="120" t="s">
         <v>84</v>
       </c>
-      <c r="H2" s="174"/>
-      <c r="I2" s="174"/>
+      <c r="H2" s="185"/>
+      <c r="I2" s="185"/>
       <c r="J2" s="121"/>
       <c r="K2" s="120" t="s">
         <v>54</v>
       </c>
-      <c r="L2" s="174"/>
-      <c r="M2" s="174"/>
+      <c r="L2" s="185"/>
+      <c r="M2" s="185"/>
       <c r="N2" s="121"/>
-      <c r="O2" s="175">
+      <c r="O2" s="186">
         <v>45821</v>
       </c>
       <c r="P2" s="121"/>
@@ -4687,7 +5148,7 @@
       </c>
       <c r="R2" s="121"/>
       <c r="S2" s="120"/>
-      <c r="T2" s="176"/>
+      <c r="T2" s="187"/>
     </row>
     <row r="3" spans="1:26" ht="18" customHeight="1">
       <c r="A3" s="113"/>
@@ -4709,7 +5170,7 @@
       <c r="Q3" s="122"/>
       <c r="R3" s="114"/>
       <c r="S3" s="122"/>
-      <c r="T3" s="177"/>
+      <c r="T3" s="188"/>
     </row>
     <row r="4" spans="1:26" ht="18" customHeight="1">
       <c r="A4" s="115"/>
@@ -4731,36 +5192,36 @@
       <c r="Q4" s="123"/>
       <c r="R4" s="117"/>
       <c r="S4" s="123"/>
-      <c r="T4" s="178"/>
+      <c r="T4" s="189"/>
     </row>
     <row r="5" spans="1:26" ht="18" customHeight="1">
-      <c r="A5" s="182" t="s">
+      <c r="A5" s="174" t="s">
         <v>33</v>
       </c>
-      <c r="B5" s="180"/>
-      <c r="C5" s="180"/>
-      <c r="D5" s="180"/>
-      <c r="E5" s="180"/>
+      <c r="B5" s="175"/>
+      <c r="C5" s="175"/>
+      <c r="D5" s="175"/>
+      <c r="E5" s="175"/>
       <c r="F5" s="119"/>
-      <c r="G5" s="183" t="s">
+      <c r="G5" s="176" t="s">
         <v>34</v>
       </c>
-      <c r="H5" s="180"/>
-      <c r="I5" s="180"/>
-      <c r="J5" s="180"/>
-      <c r="K5" s="180"/>
-      <c r="L5" s="180"/>
-      <c r="M5" s="180"/>
-      <c r="N5" s="180"/>
-      <c r="O5" s="180"/>
-      <c r="P5" s="180"/>
-      <c r="Q5" s="180"/>
-      <c r="R5" s="180"/>
-      <c r="S5" s="180"/>
-      <c r="T5" s="181"/>
+      <c r="H5" s="175"/>
+      <c r="I5" s="175"/>
+      <c r="J5" s="175"/>
+      <c r="K5" s="175"/>
+      <c r="L5" s="175"/>
+      <c r="M5" s="175"/>
+      <c r="N5" s="175"/>
+      <c r="O5" s="175"/>
+      <c r="P5" s="175"/>
+      <c r="Q5" s="175"/>
+      <c r="R5" s="175"/>
+      <c r="S5" s="175"/>
+      <c r="T5" s="177"/>
     </row>
     <row r="6" spans="1:26" ht="18" customHeight="1">
-      <c r="A6" s="184" t="s">
+      <c r="A6" s="178" t="s">
         <v>35</v>
       </c>
       <c r="B6" s="52"/>
@@ -4768,7 +5229,7 @@
       <c r="D6" s="52"/>
       <c r="E6" s="52"/>
       <c r="F6" s="53"/>
-      <c r="G6" s="185" t="s">
+      <c r="G6" s="179" t="s">
         <v>19</v>
       </c>
       <c r="H6" s="52"/>
@@ -4783,10 +5244,10 @@
       <c r="Q6" s="52"/>
       <c r="R6" s="52"/>
       <c r="S6" s="52"/>
-      <c r="T6" s="186"/>
+      <c r="T6" s="180"/>
     </row>
     <row r="7" spans="1:26" ht="18" customHeight="1">
-      <c r="A7" s="184" t="s">
+      <c r="A7" s="178" t="s">
         <v>36</v>
       </c>
       <c r="B7" s="52"/>
@@ -4794,7 +5255,7 @@
       <c r="D7" s="52"/>
       <c r="E7" s="52"/>
       <c r="F7" s="53"/>
-      <c r="G7" s="185" t="s">
+      <c r="G7" s="179" t="s">
         <v>111</v>
       </c>
       <c r="H7" s="52"/>
@@ -4809,7 +5270,7 @@
       <c r="Q7" s="52"/>
       <c r="R7" s="52"/>
       <c r="S7" s="52"/>
-      <c r="T7" s="186"/>
+      <c r="T7" s="180"/>
     </row>
     <row r="8" spans="1:26" ht="7.5" customHeight="1">
       <c r="A8" s="7"/>
@@ -5008,33 +5469,33 @@
       <c r="T14" s="9"/>
     </row>
     <row r="15" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A15" s="184" t="s">
+      <c r="A15" s="178" t="s">
         <v>43</v>
       </c>
       <c r="B15" s="53"/>
-      <c r="C15" s="190" t="s">
+      <c r="C15" s="184" t="s">
         <v>37</v>
       </c>
       <c r="D15" s="53"/>
-      <c r="E15" s="166" t="s">
+      <c r="E15" s="182" t="s">
         <v>44</v>
       </c>
       <c r="F15" s="53"/>
-      <c r="G15" s="166" t="s">
+      <c r="G15" s="182" t="s">
         <v>45</v>
       </c>
       <c r="H15" s="52"/>
       <c r="I15" s="53"/>
-      <c r="J15" s="166" t="s">
+      <c r="J15" s="182" t="s">
         <v>46</v>
       </c>
       <c r="K15" s="53"/>
-      <c r="L15" s="166" t="s">
+      <c r="L15" s="182" t="s">
         <v>47</v>
       </c>
       <c r="M15" s="52"/>
       <c r="N15" s="53"/>
-      <c r="O15" s="166" t="s">
+      <c r="O15" s="182" t="s">
         <v>48</v>
       </c>
       <c r="P15" s="52"/>
@@ -5050,33 +5511,33 @@
       </c>
     </row>
     <row r="16" spans="1:26" ht="48" customHeight="1">
-      <c r="A16" s="187">
+      <c r="A16" s="166">
         <v>1</v>
       </c>
       <c r="B16" s="53"/>
-      <c r="C16" s="188" t="s">
+      <c r="C16" s="167" t="s">
         <v>52</v>
       </c>
       <c r="D16" s="53"/>
-      <c r="E16" s="188" t="s">
+      <c r="E16" s="167" t="s">
         <v>53</v>
       </c>
       <c r="F16" s="53"/>
-      <c r="G16" s="167" t="s">
+      <c r="G16" s="181" t="s">
         <v>112</v>
       </c>
       <c r="H16" s="52"/>
       <c r="I16" s="53"/>
-      <c r="J16" s="168" t="s">
+      <c r="J16" s="192" t="s">
         <v>113</v>
       </c>
-      <c r="K16" s="80"/>
-      <c r="L16" s="172" t="s">
+      <c r="K16" s="61"/>
+      <c r="L16" s="171" t="s">
         <v>114</v>
       </c>
       <c r="M16" s="52"/>
       <c r="N16" s="53"/>
-      <c r="O16" s="172" t="s">
+      <c r="O16" s="171" t="s">
         <v>115</v>
       </c>
       <c r="P16" s="52"/>
@@ -5092,34 +5553,34 @@
       <c r="Z16" s="29"/>
     </row>
     <row r="17" spans="1:26" ht="51" customHeight="1">
-      <c r="A17" s="187">
+      <c r="A17" s="166">
         <v>2</v>
       </c>
       <c r="B17" s="53"/>
-      <c r="C17" s="188" t="s">
+      <c r="C17" s="167" t="s">
         <v>52</v>
       </c>
       <c r="D17" s="53"/>
-      <c r="E17" s="188" t="s">
+      <c r="E17" s="167" t="s">
         <v>118</v>
       </c>
       <c r="F17" s="53"/>
-      <c r="G17" s="167" t="s">
+      <c r="G17" s="181" t="s">
         <v>116</v>
       </c>
       <c r="H17" s="52"/>
       <c r="I17" s="53"/>
-      <c r="J17" s="167" t="s">
+      <c r="J17" s="181" t="s">
         <v>117</v>
       </c>
       <c r="K17" s="53"/>
-      <c r="L17" s="189" t="s">
+      <c r="L17" s="183" t="s">
         <v>119</v>
       </c>
       <c r="M17" s="52"/>
       <c r="N17" s="53"/>
-      <c r="O17" s="172" t="s">
-        <v>126</v>
+      <c r="O17" s="171" t="s">
+        <v>123</v>
       </c>
       <c r="P17" s="52"/>
       <c r="Q17" s="53"/>
@@ -5134,34 +5595,34 @@
       <c r="Z17" s="29"/>
     </row>
     <row r="18" spans="1:26" ht="99.75" customHeight="1">
-      <c r="A18" s="187">
+      <c r="A18" s="166">
         <v>3</v>
       </c>
       <c r="B18" s="53"/>
-      <c r="C18" s="188" t="s">
+      <c r="C18" s="167" t="s">
         <v>52</v>
       </c>
       <c r="D18" s="53"/>
-      <c r="E18" s="188" t="s">
+      <c r="E18" s="167" t="s">
         <v>53</v>
       </c>
       <c r="F18" s="53"/>
-      <c r="G18" s="167" t="s">
-        <v>125</v>
+      <c r="G18" s="181" t="s">
+        <v>124</v>
       </c>
       <c r="H18" s="52"/>
       <c r="I18" s="53"/>
-      <c r="J18" s="167" t="s">
-        <v>120</v>
+      <c r="J18" s="181" t="s">
+        <v>125</v>
       </c>
       <c r="K18" s="53"/>
-      <c r="L18" s="172" t="s">
+      <c r="L18" s="171" t="s">
         <v>114</v>
       </c>
       <c r="M18" s="52"/>
       <c r="N18" s="53"/>
-      <c r="O18" s="172" t="s">
-        <v>121</v>
+      <c r="O18" s="171" t="s">
+        <v>120</v>
       </c>
       <c r="P18" s="52"/>
       <c r="Q18" s="53"/>
@@ -5176,34 +5637,34 @@
       <c r="Z18" s="29"/>
     </row>
     <row r="19" spans="1:26" ht="94.5" customHeight="1">
-      <c r="A19" s="187">
+      <c r="A19" s="166">
         <v>4</v>
       </c>
       <c r="B19" s="53"/>
-      <c r="C19" s="188" t="s">
+      <c r="C19" s="167" t="s">
         <v>52</v>
       </c>
       <c r="D19" s="53"/>
-      <c r="E19" s="188" t="s">
+      <c r="E19" s="167" t="s">
         <v>118</v>
       </c>
       <c r="F19" s="53"/>
-      <c r="G19" s="167" t="s">
-        <v>122</v>
+      <c r="G19" s="181" t="s">
+        <v>126</v>
       </c>
       <c r="H19" s="52"/>
       <c r="I19" s="53"/>
-      <c r="J19" s="167" t="s">
-        <v>123</v>
+      <c r="J19" s="181" t="s">
+        <v>121</v>
       </c>
       <c r="K19" s="53"/>
-      <c r="L19" s="172" t="s">
+      <c r="L19" s="171" t="s">
         <v>114</v>
       </c>
       <c r="M19" s="52"/>
       <c r="N19" s="53"/>
-      <c r="O19" s="172" t="s">
-        <v>124</v>
+      <c r="O19" s="171" t="s">
+        <v>122</v>
       </c>
       <c r="P19" s="52"/>
       <c r="Q19" s="53"/>
@@ -5218,21 +5679,21 @@
       <c r="Z19" s="29"/>
     </row>
     <row r="20" spans="1:26" ht="61.5" customHeight="1">
-      <c r="A20" s="187"/>
+      <c r="A20" s="166"/>
       <c r="B20" s="53"/>
-      <c r="C20" s="188"/>
+      <c r="C20" s="167"/>
       <c r="D20" s="53"/>
-      <c r="E20" s="188"/>
+      <c r="E20" s="167"/>
       <c r="F20" s="53"/>
-      <c r="G20" s="167"/>
+      <c r="G20" s="181"/>
       <c r="H20" s="52"/>
       <c r="I20" s="53"/>
-      <c r="J20" s="167"/>
+      <c r="J20" s="181"/>
       <c r="K20" s="53"/>
-      <c r="L20" s="172"/>
+      <c r="L20" s="171"/>
       <c r="M20" s="52"/>
       <c r="N20" s="53"/>
-      <c r="O20" s="172"/>
+      <c r="O20" s="171"/>
       <c r="P20" s="52"/>
       <c r="Q20" s="53"/>
       <c r="R20" s="27"/>
@@ -5246,21 +5707,21 @@
       <c r="Z20" s="29"/>
     </row>
     <row r="21" spans="1:26" ht="60.75" customHeight="1">
-      <c r="A21" s="187"/>
+      <c r="A21" s="166"/>
       <c r="B21" s="53"/>
-      <c r="C21" s="188"/>
+      <c r="C21" s="167"/>
       <c r="D21" s="53"/>
-      <c r="E21" s="188"/>
+      <c r="E21" s="167"/>
       <c r="F21" s="53"/>
-      <c r="G21" s="167"/>
+      <c r="G21" s="181"/>
       <c r="H21" s="52"/>
       <c r="I21" s="53"/>
-      <c r="J21" s="167"/>
+      <c r="J21" s="181"/>
       <c r="K21" s="53"/>
-      <c r="L21" s="172"/>
+      <c r="L21" s="171"/>
       <c r="M21" s="52"/>
       <c r="N21" s="53"/>
-      <c r="O21" s="172"/>
+      <c r="O21" s="171"/>
       <c r="P21" s="52"/>
       <c r="Q21" s="53"/>
       <c r="R21" s="27"/>
@@ -5274,21 +5735,21 @@
       <c r="Z21" s="29"/>
     </row>
     <row r="22" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A22" s="187"/>
+      <c r="A22" s="166"/>
       <c r="B22" s="53"/>
-      <c r="C22" s="188"/>
+      <c r="C22" s="167"/>
       <c r="D22" s="53"/>
-      <c r="E22" s="188"/>
+      <c r="E22" s="167"/>
       <c r="F22" s="53"/>
-      <c r="G22" s="167"/>
+      <c r="G22" s="181"/>
       <c r="H22" s="52"/>
       <c r="I22" s="53"/>
-      <c r="J22" s="167"/>
+      <c r="J22" s="181"/>
       <c r="K22" s="53"/>
-      <c r="L22" s="172"/>
+      <c r="L22" s="171"/>
       <c r="M22" s="52"/>
       <c r="N22" s="53"/>
-      <c r="O22" s="172"/>
+      <c r="O22" s="171"/>
       <c r="P22" s="52"/>
       <c r="Q22" s="53"/>
       <c r="R22" s="27"/>
@@ -5302,21 +5763,21 @@
       <c r="Z22" s="29"/>
     </row>
     <row r="23" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A23" s="187"/>
+      <c r="A23" s="166"/>
       <c r="B23" s="53"/>
-      <c r="C23" s="188"/>
+      <c r="C23" s="167"/>
       <c r="D23" s="53"/>
-      <c r="E23" s="188"/>
+      <c r="E23" s="167"/>
       <c r="F23" s="53"/>
-      <c r="G23" s="167"/>
+      <c r="G23" s="181"/>
       <c r="H23" s="52"/>
       <c r="I23" s="53"/>
-      <c r="J23" s="167"/>
+      <c r="J23" s="181"/>
       <c r="K23" s="53"/>
-      <c r="L23" s="172"/>
+      <c r="L23" s="171"/>
       <c r="M23" s="52"/>
       <c r="N23" s="53"/>
-      <c r="O23" s="172"/>
+      <c r="O23" s="171"/>
       <c r="P23" s="52"/>
       <c r="Q23" s="53"/>
       <c r="R23" s="27"/>
@@ -5330,21 +5791,21 @@
       <c r="Z23" s="29"/>
     </row>
     <row r="24" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A24" s="187"/>
+      <c r="A24" s="166"/>
       <c r="B24" s="53"/>
-      <c r="C24" s="188"/>
+      <c r="C24" s="167"/>
       <c r="D24" s="53"/>
-      <c r="E24" s="188"/>
+      <c r="E24" s="167"/>
       <c r="F24" s="53"/>
-      <c r="G24" s="167"/>
+      <c r="G24" s="181"/>
       <c r="H24" s="52"/>
       <c r="I24" s="53"/>
-      <c r="J24" s="167"/>
+      <c r="J24" s="181"/>
       <c r="K24" s="53"/>
-      <c r="L24" s="172"/>
+      <c r="L24" s="171"/>
       <c r="M24" s="52"/>
       <c r="N24" s="53"/>
-      <c r="O24" s="172"/>
+      <c r="O24" s="171"/>
       <c r="P24" s="52"/>
       <c r="Q24" s="53"/>
       <c r="R24" s="27"/>
@@ -5358,21 +5819,21 @@
       <c r="Z24" s="29"/>
     </row>
     <row r="25" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A25" s="187"/>
+      <c r="A25" s="166"/>
       <c r="B25" s="53"/>
-      <c r="C25" s="188"/>
+      <c r="C25" s="167"/>
       <c r="D25" s="53"/>
-      <c r="E25" s="188"/>
+      <c r="E25" s="167"/>
       <c r="F25" s="53"/>
-      <c r="G25" s="167"/>
+      <c r="G25" s="181"/>
       <c r="H25" s="52"/>
       <c r="I25" s="53"/>
-      <c r="J25" s="167"/>
+      <c r="J25" s="181"/>
       <c r="K25" s="53"/>
-      <c r="L25" s="172"/>
+      <c r="L25" s="171"/>
       <c r="M25" s="52"/>
       <c r="N25" s="53"/>
-      <c r="O25" s="172"/>
+      <c r="O25" s="171"/>
       <c r="P25" s="52"/>
       <c r="Q25" s="53"/>
       <c r="R25" s="27"/>
@@ -5386,21 +5847,21 @@
       <c r="Z25" s="29"/>
     </row>
     <row r="26" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A26" s="187"/>
+      <c r="A26" s="166"/>
       <c r="B26" s="53"/>
-      <c r="C26" s="188"/>
+      <c r="C26" s="167"/>
       <c r="D26" s="53"/>
-      <c r="E26" s="188"/>
+      <c r="E26" s="167"/>
       <c r="F26" s="53"/>
-      <c r="G26" s="167"/>
+      <c r="G26" s="181"/>
       <c r="H26" s="52"/>
       <c r="I26" s="53"/>
-      <c r="J26" s="167"/>
+      <c r="J26" s="181"/>
       <c r="K26" s="53"/>
-      <c r="L26" s="172"/>
+      <c r="L26" s="171"/>
       <c r="M26" s="52"/>
       <c r="N26" s="53"/>
-      <c r="O26" s="172"/>
+      <c r="O26" s="171"/>
       <c r="P26" s="52"/>
       <c r="Q26" s="53"/>
       <c r="R26" s="27"/>
@@ -5414,21 +5875,21 @@
       <c r="Z26" s="29"/>
     </row>
     <row r="27" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A27" s="187"/>
+      <c r="A27" s="166"/>
       <c r="B27" s="53"/>
-      <c r="C27" s="188"/>
+      <c r="C27" s="167"/>
       <c r="D27" s="53"/>
-      <c r="E27" s="188"/>
+      <c r="E27" s="167"/>
       <c r="F27" s="53"/>
-      <c r="G27" s="167"/>
+      <c r="G27" s="181"/>
       <c r="H27" s="52"/>
       <c r="I27" s="53"/>
-      <c r="J27" s="167"/>
+      <c r="J27" s="181"/>
       <c r="K27" s="53"/>
-      <c r="L27" s="172"/>
+      <c r="L27" s="171"/>
       <c r="M27" s="52"/>
       <c r="N27" s="53"/>
-      <c r="O27" s="172"/>
+      <c r="O27" s="171"/>
       <c r="P27" s="52"/>
       <c r="Q27" s="53"/>
       <c r="R27" s="27"/>
@@ -5442,21 +5903,21 @@
       <c r="Z27" s="29"/>
     </row>
     <row r="28" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A28" s="187"/>
+      <c r="A28" s="166"/>
       <c r="B28" s="53"/>
-      <c r="C28" s="188"/>
+      <c r="C28" s="167"/>
       <c r="D28" s="53"/>
-      <c r="E28" s="188"/>
+      <c r="E28" s="167"/>
       <c r="F28" s="53"/>
-      <c r="G28" s="167"/>
+      <c r="G28" s="181"/>
       <c r="H28" s="52"/>
       <c r="I28" s="53"/>
-      <c r="J28" s="167"/>
+      <c r="J28" s="181"/>
       <c r="K28" s="53"/>
-      <c r="L28" s="172"/>
+      <c r="L28" s="171"/>
       <c r="M28" s="52"/>
       <c r="N28" s="53"/>
-      <c r="O28" s="172"/>
+      <c r="O28" s="171"/>
       <c r="P28" s="52"/>
       <c r="Q28" s="53"/>
       <c r="R28" s="27"/>
@@ -5470,21 +5931,21 @@
       <c r="Z28" s="29"/>
     </row>
     <row r="29" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A29" s="187"/>
+      <c r="A29" s="166"/>
       <c r="B29" s="53"/>
-      <c r="C29" s="188"/>
+      <c r="C29" s="167"/>
       <c r="D29" s="53"/>
-      <c r="E29" s="188"/>
+      <c r="E29" s="167"/>
       <c r="F29" s="53"/>
-      <c r="G29" s="167"/>
+      <c r="G29" s="181"/>
       <c r="H29" s="52"/>
       <c r="I29" s="53"/>
-      <c r="J29" s="167"/>
+      <c r="J29" s="181"/>
       <c r="K29" s="53"/>
-      <c r="L29" s="172"/>
+      <c r="L29" s="171"/>
       <c r="M29" s="52"/>
       <c r="N29" s="53"/>
-      <c r="O29" s="172"/>
+      <c r="O29" s="171"/>
       <c r="P29" s="52"/>
       <c r="Q29" s="53"/>
       <c r="R29" s="27"/>
@@ -5498,21 +5959,21 @@
       <c r="Z29" s="29"/>
     </row>
     <row r="30" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A30" s="187"/>
+      <c r="A30" s="166"/>
       <c r="B30" s="53"/>
-      <c r="C30" s="188"/>
+      <c r="C30" s="167"/>
       <c r="D30" s="53"/>
-      <c r="E30" s="188"/>
+      <c r="E30" s="167"/>
       <c r="F30" s="53"/>
-      <c r="G30" s="167"/>
+      <c r="G30" s="181"/>
       <c r="H30" s="52"/>
       <c r="I30" s="53"/>
-      <c r="J30" s="167"/>
+      <c r="J30" s="181"/>
       <c r="K30" s="53"/>
-      <c r="L30" s="172"/>
+      <c r="L30" s="171"/>
       <c r="M30" s="52"/>
       <c r="N30" s="53"/>
-      <c r="O30" s="172"/>
+      <c r="O30" s="171"/>
       <c r="P30" s="52"/>
       <c r="Q30" s="53"/>
       <c r="R30" s="27"/>
@@ -5526,23 +5987,23 @@
       <c r="Z30" s="29"/>
     </row>
     <row r="31" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A31" s="191"/>
-      <c r="B31" s="171"/>
-      <c r="C31" s="192"/>
-      <c r="D31" s="171"/>
-      <c r="E31" s="192"/>
-      <c r="F31" s="171"/>
-      <c r="G31" s="169"/>
-      <c r="H31" s="170"/>
-      <c r="I31" s="171"/>
-      <c r="J31" s="169"/>
-      <c r="K31" s="171"/>
-      <c r="L31" s="173"/>
-      <c r="M31" s="170"/>
-      <c r="N31" s="171"/>
-      <c r="O31" s="173"/>
-      <c r="P31" s="170"/>
-      <c r="Q31" s="171"/>
+      <c r="A31" s="168"/>
+      <c r="B31" s="169"/>
+      <c r="C31" s="170"/>
+      <c r="D31" s="169"/>
+      <c r="E31" s="170"/>
+      <c r="F31" s="169"/>
+      <c r="G31" s="191"/>
+      <c r="H31" s="173"/>
+      <c r="I31" s="169"/>
+      <c r="J31" s="191"/>
+      <c r="K31" s="169"/>
+      <c r="L31" s="172"/>
+      <c r="M31" s="173"/>
+      <c r="N31" s="169"/>
+      <c r="O31" s="172"/>
+      <c r="P31" s="173"/>
+      <c r="Q31" s="169"/>
       <c r="R31" s="30"/>
       <c r="S31" s="30"/>
       <c r="T31" s="31"/>
@@ -6540,6 +7001,118 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="136">
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="J19:K19"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="J30:K30"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="J29:K29"/>
+    <mergeCell ref="L26:N26"/>
+    <mergeCell ref="L27:N27"/>
+    <mergeCell ref="L28:N28"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="L18:N18"/>
+    <mergeCell ref="L19:N19"/>
+    <mergeCell ref="L21:N21"/>
+    <mergeCell ref="L22:N22"/>
+    <mergeCell ref="L23:N23"/>
+    <mergeCell ref="L24:N24"/>
+    <mergeCell ref="L25:N25"/>
+    <mergeCell ref="K2:N4"/>
+    <mergeCell ref="O2:P4"/>
+    <mergeCell ref="Q2:R4"/>
+    <mergeCell ref="S2:T4"/>
+    <mergeCell ref="A1:F4"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="S1:T1"/>
+    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="G5:T5"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="G6:T6"/>
+    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="G7:T7"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="G20:I20"/>
+    <mergeCell ref="J20:K20"/>
+    <mergeCell ref="L20:N20"/>
+    <mergeCell ref="O20:Q20"/>
+    <mergeCell ref="L15:N15"/>
+    <mergeCell ref="O15:Q15"/>
+    <mergeCell ref="L16:N16"/>
+    <mergeCell ref="O16:Q16"/>
+    <mergeCell ref="L17:N17"/>
+    <mergeCell ref="O17:Q17"/>
+    <mergeCell ref="O18:Q18"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="O27:Q27"/>
+    <mergeCell ref="O28:Q28"/>
+    <mergeCell ref="O29:Q29"/>
+    <mergeCell ref="O30:Q30"/>
+    <mergeCell ref="O31:Q31"/>
+    <mergeCell ref="O19:Q19"/>
+    <mergeCell ref="O21:Q21"/>
+    <mergeCell ref="O22:Q22"/>
+    <mergeCell ref="O23:Q23"/>
+    <mergeCell ref="O24:Q24"/>
+    <mergeCell ref="O25:Q25"/>
+    <mergeCell ref="O26:Q26"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="A23:B23"/>
     <mergeCell ref="A30:B30"/>
     <mergeCell ref="C30:D30"/>
     <mergeCell ref="E30:F30"/>
@@ -6564,118 +7137,6 @@
     <mergeCell ref="C28:D28"/>
     <mergeCell ref="E28:F28"/>
     <mergeCell ref="A29:B29"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="O27:Q27"/>
-    <mergeCell ref="O28:Q28"/>
-    <mergeCell ref="O29:Q29"/>
-    <mergeCell ref="O30:Q30"/>
-    <mergeCell ref="O31:Q31"/>
-    <mergeCell ref="O19:Q19"/>
-    <mergeCell ref="O21:Q21"/>
-    <mergeCell ref="O22:Q22"/>
-    <mergeCell ref="O23:Q23"/>
-    <mergeCell ref="O24:Q24"/>
-    <mergeCell ref="O25:Q25"/>
-    <mergeCell ref="O26:Q26"/>
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="G5:T5"/>
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="G6:T6"/>
-    <mergeCell ref="A7:F7"/>
-    <mergeCell ref="G7:T7"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="G20:I20"/>
-    <mergeCell ref="J20:K20"/>
-    <mergeCell ref="L20:N20"/>
-    <mergeCell ref="O20:Q20"/>
-    <mergeCell ref="L15:N15"/>
-    <mergeCell ref="O15:Q15"/>
-    <mergeCell ref="L16:N16"/>
-    <mergeCell ref="O16:Q16"/>
-    <mergeCell ref="L17:N17"/>
-    <mergeCell ref="O17:Q17"/>
-    <mergeCell ref="O18:Q18"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="K2:N4"/>
-    <mergeCell ref="O2:P4"/>
-    <mergeCell ref="Q2:R4"/>
-    <mergeCell ref="S2:T4"/>
-    <mergeCell ref="A1:F4"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="O1:P1"/>
-    <mergeCell ref="Q1:R1"/>
-    <mergeCell ref="S1:T1"/>
-    <mergeCell ref="G2:J4"/>
-    <mergeCell ref="L26:N26"/>
-    <mergeCell ref="L27:N27"/>
-    <mergeCell ref="L28:N28"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="L18:N18"/>
-    <mergeCell ref="L19:N19"/>
-    <mergeCell ref="L21:N21"/>
-    <mergeCell ref="L22:N22"/>
-    <mergeCell ref="L23:N23"/>
-    <mergeCell ref="L24:N24"/>
-    <mergeCell ref="L25:N25"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="J30:K30"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="J29:K29"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="G23:I23"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="J18:K18"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="J19:K19"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <hyperlinks>
@@ -6683,6 +7144,1359 @@
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="landscape"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94CAB32B-3B4B-457E-B790-F1ACEE03BCA0}">
+  <dimension ref="A1:S52"/>
+  <sheetFormatPr defaultColWidth="8" defaultRowHeight="11.25" customHeight="1"/>
+  <cols>
+    <col min="1" max="1" width="13.5703125" style="201" customWidth="1"/>
+    <col min="2" max="2" width="13.5703125" style="235" customWidth="1"/>
+    <col min="3" max="6" width="8.140625" style="201" customWidth="1"/>
+    <col min="7" max="7" width="8.140625" style="235" customWidth="1"/>
+    <col min="8" max="13" width="8.140625" style="201" customWidth="1"/>
+    <col min="14" max="19" width="12.140625" style="201" customWidth="1"/>
+    <col min="20" max="16384" width="8" style="201"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" ht="18.75" customHeight="1">
+      <c r="A1" s="193" t="s">
+        <v>127</v>
+      </c>
+      <c r="B1" s="193"/>
+      <c r="C1" s="194" t="s">
+        <v>128</v>
+      </c>
+      <c r="D1" s="195"/>
+      <c r="E1" s="196"/>
+      <c r="F1" s="197"/>
+      <c r="G1" s="198"/>
+      <c r="H1" s="198"/>
+      <c r="I1" s="198"/>
+      <c r="J1" s="198"/>
+      <c r="K1" s="198"/>
+      <c r="L1" s="198"/>
+      <c r="M1" s="199"/>
+      <c r="N1" s="200" t="s">
+        <v>129</v>
+      </c>
+      <c r="O1" s="197"/>
+      <c r="P1" s="199"/>
+      <c r="Q1" s="200" t="s">
+        <v>130</v>
+      </c>
+      <c r="R1" s="197" t="s">
+        <v>131</v>
+      </c>
+      <c r="S1" s="199"/>
+    </row>
+    <row r="2" spans="1:19" ht="18.75" customHeight="1">
+      <c r="A2" s="193"/>
+      <c r="B2" s="193"/>
+      <c r="C2" s="194" t="s">
+        <v>132</v>
+      </c>
+      <c r="D2" s="195"/>
+      <c r="E2" s="196"/>
+      <c r="F2" s="197"/>
+      <c r="G2" s="198"/>
+      <c r="H2" s="198"/>
+      <c r="I2" s="198"/>
+      <c r="J2" s="198"/>
+      <c r="K2" s="198"/>
+      <c r="L2" s="198"/>
+      <c r="M2" s="199"/>
+      <c r="N2" s="200" t="s">
+        <v>133</v>
+      </c>
+      <c r="O2" s="202"/>
+      <c r="P2" s="203"/>
+      <c r="Q2" s="204" t="s">
+        <v>134</v>
+      </c>
+      <c r="R2" s="205">
+        <v>44771</v>
+      </c>
+      <c r="S2" s="206"/>
+    </row>
+    <row r="3" spans="1:19" ht="11.25" customHeight="1">
+      <c r="A3" s="207"/>
+      <c r="B3" s="208"/>
+      <c r="C3" s="207"/>
+      <c r="D3" s="207"/>
+      <c r="E3" s="207"/>
+      <c r="F3" s="207"/>
+      <c r="G3" s="208"/>
+      <c r="H3" s="207"/>
+      <c r="I3" s="207"/>
+      <c r="J3" s="207"/>
+      <c r="K3" s="207"/>
+      <c r="L3" s="207"/>
+      <c r="M3" s="207"/>
+      <c r="N3" s="207"/>
+      <c r="O3" s="207"/>
+      <c r="P3" s="207"/>
+      <c r="Q3" s="207"/>
+      <c r="R3" s="207"/>
+      <c r="S3" s="207"/>
+    </row>
+    <row r="4" spans="1:19" ht="15" customHeight="1">
+      <c r="A4" s="209" t="s">
+        <v>135</v>
+      </c>
+      <c r="B4" s="210" t="s">
+        <v>136</v>
+      </c>
+      <c r="C4" s="211" t="s">
+        <v>137</v>
+      </c>
+      <c r="D4" s="212"/>
+      <c r="E4" s="212"/>
+      <c r="F4" s="212"/>
+      <c r="G4" s="213"/>
+      <c r="H4" s="211" t="s">
+        <v>138</v>
+      </c>
+      <c r="I4" s="212"/>
+      <c r="J4" s="212"/>
+      <c r="K4" s="212"/>
+      <c r="L4" s="212"/>
+      <c r="M4" s="213"/>
+      <c r="N4" s="211" t="s">
+        <v>139</v>
+      </c>
+      <c r="O4" s="212"/>
+      <c r="P4" s="213"/>
+      <c r="Q4" s="209" t="s">
+        <v>140</v>
+      </c>
+      <c r="R4" s="211" t="s">
+        <v>141</v>
+      </c>
+      <c r="S4" s="213"/>
+    </row>
+    <row r="5" spans="1:19" ht="30" customHeight="1">
+      <c r="A5" s="214"/>
+      <c r="B5" s="215"/>
+      <c r="C5" s="216"/>
+      <c r="D5" s="216"/>
+      <c r="E5" s="216"/>
+      <c r="F5" s="216"/>
+      <c r="G5" s="216"/>
+      <c r="H5" s="216"/>
+      <c r="I5" s="216"/>
+      <c r="J5" s="216"/>
+      <c r="K5" s="216"/>
+      <c r="L5" s="216"/>
+      <c r="M5" s="216"/>
+      <c r="N5" s="217"/>
+      <c r="O5" s="218"/>
+      <c r="P5" s="219"/>
+      <c r="Q5" s="214"/>
+      <c r="R5" s="220"/>
+      <c r="S5" s="221"/>
+    </row>
+    <row r="6" spans="1:19" ht="30" customHeight="1">
+      <c r="A6" s="222"/>
+      <c r="B6" s="222"/>
+      <c r="C6" s="223"/>
+      <c r="D6" s="223"/>
+      <c r="E6" s="223"/>
+      <c r="F6" s="223"/>
+      <c r="G6" s="223"/>
+      <c r="H6" s="223"/>
+      <c r="I6" s="223"/>
+      <c r="J6" s="223"/>
+      <c r="K6" s="223"/>
+      <c r="L6" s="223"/>
+      <c r="M6" s="223"/>
+      <c r="N6" s="224"/>
+      <c r="O6" s="225"/>
+      <c r="P6" s="226"/>
+      <c r="Q6" s="227"/>
+      <c r="R6" s="228"/>
+      <c r="S6" s="228"/>
+    </row>
+    <row r="7" spans="1:19" ht="30" customHeight="1">
+      <c r="A7" s="222"/>
+      <c r="B7" s="222"/>
+      <c r="C7" s="223"/>
+      <c r="D7" s="223"/>
+      <c r="E7" s="223"/>
+      <c r="F7" s="223"/>
+      <c r="G7" s="223"/>
+      <c r="H7" s="223"/>
+      <c r="I7" s="223"/>
+      <c r="J7" s="223"/>
+      <c r="K7" s="223"/>
+      <c r="L7" s="223"/>
+      <c r="M7" s="223"/>
+      <c r="N7" s="229"/>
+      <c r="O7" s="230"/>
+      <c r="P7" s="231"/>
+      <c r="Q7" s="227"/>
+      <c r="R7" s="228"/>
+      <c r="S7" s="228"/>
+    </row>
+    <row r="8" spans="1:19" ht="30" customHeight="1">
+      <c r="A8" s="222"/>
+      <c r="B8" s="222"/>
+      <c r="C8" s="223"/>
+      <c r="D8" s="223"/>
+      <c r="E8" s="223"/>
+      <c r="F8" s="223"/>
+      <c r="G8" s="223"/>
+      <c r="H8" s="223"/>
+      <c r="I8" s="223"/>
+      <c r="J8" s="223"/>
+      <c r="K8" s="223"/>
+      <c r="L8" s="223"/>
+      <c r="M8" s="223"/>
+      <c r="N8" s="229"/>
+      <c r="O8" s="230"/>
+      <c r="P8" s="231"/>
+      <c r="Q8" s="227"/>
+      <c r="R8" s="228"/>
+      <c r="S8" s="228"/>
+    </row>
+    <row r="9" spans="1:19" ht="30" customHeight="1">
+      <c r="A9" s="222"/>
+      <c r="B9" s="222"/>
+      <c r="C9" s="223"/>
+      <c r="D9" s="223"/>
+      <c r="E9" s="223"/>
+      <c r="F9" s="223"/>
+      <c r="G9" s="223"/>
+      <c r="H9" s="223"/>
+      <c r="I9" s="223"/>
+      <c r="J9" s="223"/>
+      <c r="K9" s="223"/>
+      <c r="L9" s="223"/>
+      <c r="M9" s="223"/>
+      <c r="N9" s="229"/>
+      <c r="O9" s="230"/>
+      <c r="P9" s="231"/>
+      <c r="Q9" s="222"/>
+      <c r="R9" s="228"/>
+      <c r="S9" s="228"/>
+    </row>
+    <row r="10" spans="1:19" ht="30" customHeight="1">
+      <c r="A10" s="222"/>
+      <c r="B10" s="222"/>
+      <c r="C10" s="223"/>
+      <c r="D10" s="223"/>
+      <c r="E10" s="223"/>
+      <c r="F10" s="223"/>
+      <c r="G10" s="223"/>
+      <c r="H10" s="232"/>
+      <c r="I10" s="233"/>
+      <c r="J10" s="233"/>
+      <c r="K10" s="233"/>
+      <c r="L10" s="233"/>
+      <c r="M10" s="234"/>
+      <c r="N10" s="229"/>
+      <c r="O10" s="230"/>
+      <c r="P10" s="231"/>
+      <c r="Q10" s="227"/>
+      <c r="R10" s="228"/>
+      <c r="S10" s="228"/>
+    </row>
+    <row r="11" spans="1:19" ht="30" customHeight="1">
+      <c r="A11" s="222"/>
+      <c r="B11" s="222"/>
+      <c r="C11" s="223"/>
+      <c r="D11" s="223"/>
+      <c r="E11" s="223"/>
+      <c r="F11" s="223"/>
+      <c r="G11" s="223"/>
+      <c r="H11" s="232"/>
+      <c r="I11" s="233"/>
+      <c r="J11" s="233"/>
+      <c r="K11" s="233"/>
+      <c r="L11" s="233"/>
+      <c r="M11" s="234"/>
+      <c r="N11" s="229"/>
+      <c r="O11" s="230"/>
+      <c r="P11" s="231"/>
+      <c r="Q11" s="222"/>
+      <c r="R11" s="228"/>
+      <c r="S11" s="228"/>
+    </row>
+    <row r="12" spans="1:19" ht="30" customHeight="1">
+      <c r="A12" s="222"/>
+      <c r="B12" s="222"/>
+      <c r="C12" s="223"/>
+      <c r="D12" s="223"/>
+      <c r="E12" s="223"/>
+      <c r="F12" s="223"/>
+      <c r="G12" s="223"/>
+      <c r="H12" s="232"/>
+      <c r="I12" s="233"/>
+      <c r="J12" s="233"/>
+      <c r="K12" s="233"/>
+      <c r="L12" s="233"/>
+      <c r="M12" s="234"/>
+      <c r="N12" s="229"/>
+      <c r="O12" s="230"/>
+      <c r="P12" s="231"/>
+      <c r="Q12" s="222"/>
+      <c r="R12" s="228"/>
+      <c r="S12" s="228"/>
+    </row>
+    <row r="13" spans="1:19" ht="30" customHeight="1">
+      <c r="A13" s="222"/>
+      <c r="B13" s="222"/>
+      <c r="C13" s="223"/>
+      <c r="D13" s="223"/>
+      <c r="E13" s="223"/>
+      <c r="F13" s="223"/>
+      <c r="G13" s="223"/>
+      <c r="H13" s="232"/>
+      <c r="I13" s="233"/>
+      <c r="J13" s="233"/>
+      <c r="K13" s="233"/>
+      <c r="L13" s="233"/>
+      <c r="M13" s="234"/>
+      <c r="N13" s="229"/>
+      <c r="O13" s="230"/>
+      <c r="P13" s="231"/>
+      <c r="Q13" s="222"/>
+      <c r="R13" s="228"/>
+      <c r="S13" s="228"/>
+    </row>
+    <row r="14" spans="1:19" ht="30" customHeight="1">
+      <c r="A14" s="222"/>
+      <c r="B14" s="222"/>
+      <c r="C14" s="223"/>
+      <c r="D14" s="223"/>
+      <c r="E14" s="223"/>
+      <c r="F14" s="223"/>
+      <c r="G14" s="223"/>
+      <c r="H14" s="232"/>
+      <c r="I14" s="233"/>
+      <c r="J14" s="233"/>
+      <c r="K14" s="233"/>
+      <c r="L14" s="233"/>
+      <c r="M14" s="234"/>
+      <c r="N14" s="229"/>
+      <c r="O14" s="230"/>
+      <c r="P14" s="231"/>
+      <c r="Q14" s="222"/>
+      <c r="R14" s="228"/>
+      <c r="S14" s="228"/>
+    </row>
+    <row r="15" spans="1:19" ht="30" customHeight="1">
+      <c r="A15" s="222"/>
+      <c r="B15" s="222"/>
+      <c r="C15" s="223"/>
+      <c r="D15" s="223"/>
+      <c r="E15" s="223"/>
+      <c r="F15" s="223"/>
+      <c r="G15" s="223"/>
+      <c r="H15" s="232"/>
+      <c r="I15" s="233"/>
+      <c r="J15" s="233"/>
+      <c r="K15" s="233"/>
+      <c r="L15" s="233"/>
+      <c r="M15" s="234"/>
+      <c r="N15" s="229"/>
+      <c r="O15" s="230"/>
+      <c r="P15" s="231"/>
+      <c r="Q15" s="222"/>
+      <c r="R15" s="228"/>
+      <c r="S15" s="228"/>
+    </row>
+    <row r="16" spans="1:19" ht="30" customHeight="1">
+      <c r="A16" s="222"/>
+      <c r="B16" s="222"/>
+      <c r="C16" s="223"/>
+      <c r="D16" s="223"/>
+      <c r="E16" s="223"/>
+      <c r="F16" s="223"/>
+      <c r="G16" s="223"/>
+      <c r="H16" s="232"/>
+      <c r="I16" s="233"/>
+      <c r="J16" s="233"/>
+      <c r="K16" s="233"/>
+      <c r="L16" s="233"/>
+      <c r="M16" s="234"/>
+      <c r="N16" s="229"/>
+      <c r="O16" s="230"/>
+      <c r="P16" s="231"/>
+      <c r="Q16" s="222"/>
+      <c r="R16" s="228"/>
+      <c r="S16" s="228"/>
+    </row>
+    <row r="17" spans="1:19" ht="30" customHeight="1">
+      <c r="A17" s="222"/>
+      <c r="B17" s="222"/>
+      <c r="C17" s="223"/>
+      <c r="D17" s="223"/>
+      <c r="E17" s="223"/>
+      <c r="F17" s="223"/>
+      <c r="G17" s="223"/>
+      <c r="H17" s="232"/>
+      <c r="I17" s="233"/>
+      <c r="J17" s="233"/>
+      <c r="K17" s="233"/>
+      <c r="L17" s="233"/>
+      <c r="M17" s="234"/>
+      <c r="N17" s="229"/>
+      <c r="O17" s="230"/>
+      <c r="P17" s="231"/>
+      <c r="Q17" s="222"/>
+      <c r="R17" s="228"/>
+      <c r="S17" s="228"/>
+    </row>
+    <row r="18" spans="1:19" ht="30" customHeight="1">
+      <c r="A18" s="222"/>
+      <c r="B18" s="222"/>
+      <c r="C18" s="223"/>
+      <c r="D18" s="223"/>
+      <c r="E18" s="223"/>
+      <c r="F18" s="223"/>
+      <c r="G18" s="223"/>
+      <c r="H18" s="232"/>
+      <c r="I18" s="233"/>
+      <c r="J18" s="233"/>
+      <c r="K18" s="233"/>
+      <c r="L18" s="233"/>
+      <c r="M18" s="234"/>
+      <c r="N18" s="229"/>
+      <c r="O18" s="230"/>
+      <c r="P18" s="231"/>
+      <c r="Q18" s="222"/>
+      <c r="R18" s="228"/>
+      <c r="S18" s="228"/>
+    </row>
+    <row r="19" spans="1:19" ht="30" customHeight="1">
+      <c r="A19" s="222"/>
+      <c r="B19" s="222"/>
+      <c r="C19" s="223"/>
+      <c r="D19" s="223"/>
+      <c r="E19" s="223"/>
+      <c r="F19" s="223"/>
+      <c r="G19" s="223"/>
+      <c r="H19" s="232"/>
+      <c r="I19" s="233"/>
+      <c r="J19" s="233"/>
+      <c r="K19" s="233"/>
+      <c r="L19" s="233"/>
+      <c r="M19" s="234"/>
+      <c r="N19" s="229"/>
+      <c r="O19" s="230"/>
+      <c r="P19" s="231"/>
+      <c r="Q19" s="222"/>
+      <c r="R19" s="228"/>
+      <c r="S19" s="228"/>
+    </row>
+    <row r="20" spans="1:19" ht="30" customHeight="1">
+      <c r="A20" s="222"/>
+      <c r="B20" s="222"/>
+      <c r="C20" s="223"/>
+      <c r="D20" s="223"/>
+      <c r="E20" s="223"/>
+      <c r="F20" s="223"/>
+      <c r="G20" s="223"/>
+      <c r="H20" s="232"/>
+      <c r="I20" s="233"/>
+      <c r="J20" s="233"/>
+      <c r="K20" s="233"/>
+      <c r="L20" s="233"/>
+      <c r="M20" s="234"/>
+      <c r="N20" s="229"/>
+      <c r="O20" s="230"/>
+      <c r="P20" s="231"/>
+      <c r="Q20" s="222"/>
+      <c r="R20" s="228"/>
+      <c r="S20" s="228"/>
+    </row>
+    <row r="21" spans="1:19" ht="30" customHeight="1">
+      <c r="A21" s="222"/>
+      <c r="B21" s="222"/>
+      <c r="C21" s="223"/>
+      <c r="D21" s="223"/>
+      <c r="E21" s="223"/>
+      <c r="F21" s="223"/>
+      <c r="G21" s="223"/>
+      <c r="H21" s="232"/>
+      <c r="I21" s="233"/>
+      <c r="J21" s="233"/>
+      <c r="K21" s="233"/>
+      <c r="L21" s="233"/>
+      <c r="M21" s="234"/>
+      <c r="N21" s="229"/>
+      <c r="O21" s="230"/>
+      <c r="P21" s="231"/>
+      <c r="Q21" s="222"/>
+      <c r="R21" s="228"/>
+      <c r="S21" s="228"/>
+    </row>
+    <row r="22" spans="1:19" ht="30" customHeight="1">
+      <c r="A22" s="222"/>
+      <c r="B22" s="222"/>
+      <c r="C22" s="223"/>
+      <c r="D22" s="223"/>
+      <c r="E22" s="223"/>
+      <c r="F22" s="223"/>
+      <c r="G22" s="223"/>
+      <c r="H22" s="232"/>
+      <c r="I22" s="233"/>
+      <c r="J22" s="233"/>
+      <c r="K22" s="233"/>
+      <c r="L22" s="233"/>
+      <c r="M22" s="234"/>
+      <c r="N22" s="229"/>
+      <c r="O22" s="230"/>
+      <c r="P22" s="231"/>
+      <c r="Q22" s="222"/>
+      <c r="R22" s="228"/>
+      <c r="S22" s="228"/>
+    </row>
+    <row r="23" spans="1:19" ht="30" customHeight="1">
+      <c r="A23" s="222"/>
+      <c r="B23" s="222"/>
+      <c r="C23" s="223"/>
+      <c r="D23" s="223"/>
+      <c r="E23" s="223"/>
+      <c r="F23" s="223"/>
+      <c r="G23" s="223"/>
+      <c r="H23" s="232"/>
+      <c r="I23" s="233"/>
+      <c r="J23" s="233"/>
+      <c r="K23" s="233"/>
+      <c r="L23" s="233"/>
+      <c r="M23" s="234"/>
+      <c r="N23" s="229"/>
+      <c r="O23" s="230"/>
+      <c r="P23" s="231"/>
+      <c r="Q23" s="222"/>
+      <c r="R23" s="228"/>
+      <c r="S23" s="228"/>
+    </row>
+    <row r="24" spans="1:19" ht="30" customHeight="1">
+      <c r="A24" s="222"/>
+      <c r="B24" s="222"/>
+      <c r="C24" s="223"/>
+      <c r="D24" s="223"/>
+      <c r="E24" s="223"/>
+      <c r="F24" s="223"/>
+      <c r="G24" s="223"/>
+      <c r="H24" s="232"/>
+      <c r="I24" s="233"/>
+      <c r="J24" s="233"/>
+      <c r="K24" s="233"/>
+      <c r="L24" s="233"/>
+      <c r="M24" s="234"/>
+      <c r="N24" s="229"/>
+      <c r="O24" s="230"/>
+      <c r="P24" s="231"/>
+      <c r="Q24" s="222"/>
+      <c r="R24" s="228"/>
+      <c r="S24" s="228"/>
+    </row>
+    <row r="25" spans="1:19" ht="30" customHeight="1">
+      <c r="A25" s="222"/>
+      <c r="B25" s="222"/>
+      <c r="C25" s="223"/>
+      <c r="D25" s="223"/>
+      <c r="E25" s="223"/>
+      <c r="F25" s="223"/>
+      <c r="G25" s="223"/>
+      <c r="H25" s="232"/>
+      <c r="I25" s="233"/>
+      <c r="J25" s="233"/>
+      <c r="K25" s="233"/>
+      <c r="L25" s="233"/>
+      <c r="M25" s="234"/>
+      <c r="N25" s="229"/>
+      <c r="O25" s="230"/>
+      <c r="P25" s="231"/>
+      <c r="Q25" s="222"/>
+      <c r="R25" s="228"/>
+      <c r="S25" s="228"/>
+    </row>
+    <row r="26" spans="1:19" ht="30" customHeight="1">
+      <c r="A26" s="222"/>
+      <c r="B26" s="222"/>
+      <c r="C26" s="223"/>
+      <c r="D26" s="223"/>
+      <c r="E26" s="223"/>
+      <c r="F26" s="223"/>
+      <c r="G26" s="223"/>
+      <c r="H26" s="232"/>
+      <c r="I26" s="233"/>
+      <c r="J26" s="233"/>
+      <c r="K26" s="233"/>
+      <c r="L26" s="233"/>
+      <c r="M26" s="234"/>
+      <c r="N26" s="229"/>
+      <c r="O26" s="230"/>
+      <c r="P26" s="231"/>
+      <c r="Q26" s="222"/>
+      <c r="R26" s="228"/>
+      <c r="S26" s="228"/>
+    </row>
+    <row r="27" spans="1:19" ht="30" customHeight="1">
+      <c r="A27" s="222"/>
+      <c r="B27" s="222"/>
+      <c r="C27" s="223"/>
+      <c r="D27" s="223"/>
+      <c r="E27" s="223"/>
+      <c r="F27" s="223"/>
+      <c r="G27" s="223"/>
+      <c r="H27" s="232"/>
+      <c r="I27" s="233"/>
+      <c r="J27" s="233"/>
+      <c r="K27" s="233"/>
+      <c r="L27" s="233"/>
+      <c r="M27" s="234"/>
+      <c r="N27" s="229"/>
+      <c r="O27" s="230"/>
+      <c r="P27" s="231"/>
+      <c r="Q27" s="222"/>
+      <c r="R27" s="228"/>
+      <c r="S27" s="228"/>
+    </row>
+    <row r="28" spans="1:19" ht="30" customHeight="1">
+      <c r="A28" s="222"/>
+      <c r="B28" s="222"/>
+      <c r="C28" s="223"/>
+      <c r="D28" s="223"/>
+      <c r="E28" s="223"/>
+      <c r="F28" s="223"/>
+      <c r="G28" s="223"/>
+      <c r="H28" s="232"/>
+      <c r="I28" s="233"/>
+      <c r="J28" s="233"/>
+      <c r="K28" s="233"/>
+      <c r="L28" s="233"/>
+      <c r="M28" s="234"/>
+      <c r="N28" s="229"/>
+      <c r="O28" s="230"/>
+      <c r="P28" s="231"/>
+      <c r="Q28" s="222"/>
+      <c r="R28" s="228"/>
+      <c r="S28" s="228"/>
+    </row>
+    <row r="29" spans="1:19" ht="30" customHeight="1">
+      <c r="A29" s="222"/>
+      <c r="B29" s="222"/>
+      <c r="C29" s="223"/>
+      <c r="D29" s="223"/>
+      <c r="E29" s="223"/>
+      <c r="F29" s="223"/>
+      <c r="G29" s="223"/>
+      <c r="H29" s="232"/>
+      <c r="I29" s="233"/>
+      <c r="J29" s="233"/>
+      <c r="K29" s="233"/>
+      <c r="L29" s="233"/>
+      <c r="M29" s="234"/>
+      <c r="N29" s="229"/>
+      <c r="O29" s="230"/>
+      <c r="P29" s="231"/>
+      <c r="Q29" s="222"/>
+      <c r="R29" s="228"/>
+      <c r="S29" s="228"/>
+    </row>
+    <row r="30" spans="1:19" ht="30" customHeight="1">
+      <c r="A30" s="222"/>
+      <c r="B30" s="222"/>
+      <c r="C30" s="223"/>
+      <c r="D30" s="223"/>
+      <c r="E30" s="223"/>
+      <c r="F30" s="223"/>
+      <c r="G30" s="223"/>
+      <c r="H30" s="232"/>
+      <c r="I30" s="233"/>
+      <c r="J30" s="233"/>
+      <c r="K30" s="233"/>
+      <c r="L30" s="233"/>
+      <c r="M30" s="234"/>
+      <c r="N30" s="229"/>
+      <c r="O30" s="230"/>
+      <c r="P30" s="231"/>
+      <c r="Q30" s="222"/>
+      <c r="R30" s="228"/>
+      <c r="S30" s="228"/>
+    </row>
+    <row r="31" spans="1:19" ht="30" customHeight="1">
+      <c r="A31" s="222"/>
+      <c r="B31" s="222"/>
+      <c r="C31" s="223"/>
+      <c r="D31" s="223"/>
+      <c r="E31" s="223"/>
+      <c r="F31" s="223"/>
+      <c r="G31" s="223"/>
+      <c r="H31" s="232"/>
+      <c r="I31" s="233"/>
+      <c r="J31" s="233"/>
+      <c r="K31" s="233"/>
+      <c r="L31" s="233"/>
+      <c r="M31" s="234"/>
+      <c r="N31" s="229"/>
+      <c r="O31" s="230"/>
+      <c r="P31" s="231"/>
+      <c r="Q31" s="222"/>
+      <c r="R31" s="228"/>
+      <c r="S31" s="228"/>
+    </row>
+    <row r="32" spans="1:19" ht="30" customHeight="1">
+      <c r="A32" s="222"/>
+      <c r="B32" s="222"/>
+      <c r="C32" s="223"/>
+      <c r="D32" s="223"/>
+      <c r="E32" s="223"/>
+      <c r="F32" s="223"/>
+      <c r="G32" s="223"/>
+      <c r="H32" s="232"/>
+      <c r="I32" s="233"/>
+      <c r="J32" s="233"/>
+      <c r="K32" s="233"/>
+      <c r="L32" s="233"/>
+      <c r="M32" s="234"/>
+      <c r="N32" s="229"/>
+      <c r="O32" s="230"/>
+      <c r="P32" s="231"/>
+      <c r="Q32" s="222"/>
+      <c r="R32" s="228"/>
+      <c r="S32" s="228"/>
+    </row>
+    <row r="33" spans="1:19" ht="30" customHeight="1">
+      <c r="A33" s="222"/>
+      <c r="B33" s="222"/>
+      <c r="C33" s="223"/>
+      <c r="D33" s="223"/>
+      <c r="E33" s="223"/>
+      <c r="F33" s="223"/>
+      <c r="G33" s="223"/>
+      <c r="H33" s="232"/>
+      <c r="I33" s="233"/>
+      <c r="J33" s="233"/>
+      <c r="K33" s="233"/>
+      <c r="L33" s="233"/>
+      <c r="M33" s="234"/>
+      <c r="N33" s="229"/>
+      <c r="O33" s="230"/>
+      <c r="P33" s="231"/>
+      <c r="Q33" s="222"/>
+      <c r="R33" s="228"/>
+      <c r="S33" s="228"/>
+    </row>
+    <row r="34" spans="1:19" ht="30" customHeight="1">
+      <c r="A34" s="222"/>
+      <c r="B34" s="222"/>
+      <c r="C34" s="223"/>
+      <c r="D34" s="223"/>
+      <c r="E34" s="223"/>
+      <c r="F34" s="223"/>
+      <c r="G34" s="223"/>
+      <c r="H34" s="232"/>
+      <c r="I34" s="233"/>
+      <c r="J34" s="233"/>
+      <c r="K34" s="233"/>
+      <c r="L34" s="233"/>
+      <c r="M34" s="234"/>
+      <c r="N34" s="229"/>
+      <c r="O34" s="230"/>
+      <c r="P34" s="231"/>
+      <c r="Q34" s="222"/>
+      <c r="R34" s="228"/>
+      <c r="S34" s="228"/>
+    </row>
+    <row r="35" spans="1:19" ht="30" customHeight="1">
+      <c r="A35" s="222"/>
+      <c r="B35" s="222"/>
+      <c r="C35" s="223"/>
+      <c r="D35" s="223"/>
+      <c r="E35" s="223"/>
+      <c r="F35" s="223"/>
+      <c r="G35" s="223"/>
+      <c r="H35" s="232"/>
+      <c r="I35" s="233"/>
+      <c r="J35" s="233"/>
+      <c r="K35" s="233"/>
+      <c r="L35" s="233"/>
+      <c r="M35" s="234"/>
+      <c r="N35" s="229"/>
+      <c r="O35" s="230"/>
+      <c r="P35" s="231"/>
+      <c r="Q35" s="222"/>
+      <c r="R35" s="228"/>
+      <c r="S35" s="228"/>
+    </row>
+    <row r="36" spans="1:19" ht="30" customHeight="1">
+      <c r="A36" s="222"/>
+      <c r="B36" s="222"/>
+      <c r="C36" s="223"/>
+      <c r="D36" s="223"/>
+      <c r="E36" s="223"/>
+      <c r="F36" s="223"/>
+      <c r="G36" s="223"/>
+      <c r="H36" s="232"/>
+      <c r="I36" s="233"/>
+      <c r="J36" s="233"/>
+      <c r="K36" s="233"/>
+      <c r="L36" s="233"/>
+      <c r="M36" s="234"/>
+      <c r="N36" s="229"/>
+      <c r="O36" s="230"/>
+      <c r="P36" s="231"/>
+      <c r="Q36" s="222"/>
+      <c r="R36" s="228"/>
+      <c r="S36" s="228"/>
+    </row>
+    <row r="37" spans="1:19" ht="30" customHeight="1">
+      <c r="A37" s="222"/>
+      <c r="B37" s="222"/>
+      <c r="C37" s="223"/>
+      <c r="D37" s="223"/>
+      <c r="E37" s="223"/>
+      <c r="F37" s="223"/>
+      <c r="G37" s="223"/>
+      <c r="H37" s="232"/>
+      <c r="I37" s="233"/>
+      <c r="J37" s="233"/>
+      <c r="K37" s="233"/>
+      <c r="L37" s="233"/>
+      <c r="M37" s="234"/>
+      <c r="N37" s="229"/>
+      <c r="O37" s="230"/>
+      <c r="P37" s="231"/>
+      <c r="Q37" s="222"/>
+      <c r="R37" s="228"/>
+      <c r="S37" s="228"/>
+    </row>
+    <row r="38" spans="1:19" ht="30" customHeight="1">
+      <c r="A38" s="222"/>
+      <c r="B38" s="222"/>
+      <c r="C38" s="223"/>
+      <c r="D38" s="223"/>
+      <c r="E38" s="223"/>
+      <c r="F38" s="223"/>
+      <c r="G38" s="223"/>
+      <c r="H38" s="232"/>
+      <c r="I38" s="233"/>
+      <c r="J38" s="233"/>
+      <c r="K38" s="233"/>
+      <c r="L38" s="233"/>
+      <c r="M38" s="234"/>
+      <c r="N38" s="229"/>
+      <c r="O38" s="230"/>
+      <c r="P38" s="231"/>
+      <c r="Q38" s="222"/>
+      <c r="R38" s="228"/>
+      <c r="S38" s="228"/>
+    </row>
+    <row r="39" spans="1:19" ht="30" customHeight="1">
+      <c r="A39" s="222"/>
+      <c r="B39" s="222"/>
+      <c r="C39" s="223"/>
+      <c r="D39" s="223"/>
+      <c r="E39" s="223"/>
+      <c r="F39" s="223"/>
+      <c r="G39" s="223"/>
+      <c r="H39" s="232"/>
+      <c r="I39" s="233"/>
+      <c r="J39" s="233"/>
+      <c r="K39" s="233"/>
+      <c r="L39" s="233"/>
+      <c r="M39" s="234"/>
+      <c r="N39" s="229"/>
+      <c r="O39" s="230"/>
+      <c r="P39" s="231"/>
+      <c r="Q39" s="222"/>
+      <c r="R39" s="228"/>
+      <c r="S39" s="228"/>
+    </row>
+    <row r="40" spans="1:19" ht="30" customHeight="1">
+      <c r="A40" s="222"/>
+      <c r="B40" s="222"/>
+      <c r="C40" s="223"/>
+      <c r="D40" s="223"/>
+      <c r="E40" s="223"/>
+      <c r="F40" s="223"/>
+      <c r="G40" s="223"/>
+      <c r="H40" s="232"/>
+      <c r="I40" s="233"/>
+      <c r="J40" s="233"/>
+      <c r="K40" s="233"/>
+      <c r="L40" s="233"/>
+      <c r="M40" s="234"/>
+      <c r="N40" s="229"/>
+      <c r="O40" s="230"/>
+      <c r="P40" s="231"/>
+      <c r="Q40" s="222"/>
+      <c r="R40" s="228"/>
+      <c r="S40" s="228"/>
+    </row>
+    <row r="41" spans="1:19" ht="30" customHeight="1">
+      <c r="A41" s="222"/>
+      <c r="B41" s="222"/>
+      <c r="C41" s="223"/>
+      <c r="D41" s="223"/>
+      <c r="E41" s="223"/>
+      <c r="F41" s="223"/>
+      <c r="G41" s="223"/>
+      <c r="H41" s="232"/>
+      <c r="I41" s="233"/>
+      <c r="J41" s="233"/>
+      <c r="K41" s="233"/>
+      <c r="L41" s="233"/>
+      <c r="M41" s="234"/>
+      <c r="N41" s="229"/>
+      <c r="O41" s="230"/>
+      <c r="P41" s="231"/>
+      <c r="Q41" s="222"/>
+      <c r="R41" s="228"/>
+      <c r="S41" s="228"/>
+    </row>
+    <row r="42" spans="1:19" ht="30" customHeight="1">
+      <c r="A42" s="222"/>
+      <c r="B42" s="222"/>
+      <c r="C42" s="223"/>
+      <c r="D42" s="223"/>
+      <c r="E42" s="223"/>
+      <c r="F42" s="223"/>
+      <c r="G42" s="223"/>
+      <c r="H42" s="232"/>
+      <c r="I42" s="233"/>
+      <c r="J42" s="233"/>
+      <c r="K42" s="233"/>
+      <c r="L42" s="233"/>
+      <c r="M42" s="234"/>
+      <c r="N42" s="229"/>
+      <c r="O42" s="230"/>
+      <c r="P42" s="231"/>
+      <c r="Q42" s="222"/>
+      <c r="R42" s="228"/>
+      <c r="S42" s="228"/>
+    </row>
+    <row r="43" spans="1:19" ht="30" customHeight="1">
+      <c r="A43" s="222"/>
+      <c r="B43" s="222"/>
+      <c r="C43" s="223"/>
+      <c r="D43" s="223"/>
+      <c r="E43" s="223"/>
+      <c r="F43" s="223"/>
+      <c r="G43" s="223"/>
+      <c r="H43" s="232"/>
+      <c r="I43" s="233"/>
+      <c r="J43" s="233"/>
+      <c r="K43" s="233"/>
+      <c r="L43" s="233"/>
+      <c r="M43" s="234"/>
+      <c r="N43" s="229"/>
+      <c r="O43" s="230"/>
+      <c r="P43" s="231"/>
+      <c r="Q43" s="222"/>
+      <c r="R43" s="228"/>
+      <c r="S43" s="228"/>
+    </row>
+    <row r="44" spans="1:19" ht="30" customHeight="1">
+      <c r="A44" s="222"/>
+      <c r="B44" s="222"/>
+      <c r="C44" s="223"/>
+      <c r="D44" s="223"/>
+      <c r="E44" s="223"/>
+      <c r="F44" s="223"/>
+      <c r="G44" s="223"/>
+      <c r="H44" s="232"/>
+      <c r="I44" s="233"/>
+      <c r="J44" s="233"/>
+      <c r="K44" s="233"/>
+      <c r="L44" s="233"/>
+      <c r="M44" s="234"/>
+      <c r="N44" s="229"/>
+      <c r="O44" s="230"/>
+      <c r="P44" s="231"/>
+      <c r="Q44" s="222"/>
+      <c r="R44" s="228"/>
+      <c r="S44" s="228"/>
+    </row>
+    <row r="45" spans="1:19" ht="30" customHeight="1">
+      <c r="A45" s="222"/>
+      <c r="B45" s="222"/>
+      <c r="C45" s="223"/>
+      <c r="D45" s="223"/>
+      <c r="E45" s="223"/>
+      <c r="F45" s="223"/>
+      <c r="G45" s="223"/>
+      <c r="H45" s="232"/>
+      <c r="I45" s="233"/>
+      <c r="J45" s="233"/>
+      <c r="K45" s="233"/>
+      <c r="L45" s="233"/>
+      <c r="M45" s="234"/>
+      <c r="N45" s="229"/>
+      <c r="O45" s="230"/>
+      <c r="P45" s="231"/>
+      <c r="Q45" s="222"/>
+      <c r="R45" s="228"/>
+      <c r="S45" s="228"/>
+    </row>
+    <row r="46" spans="1:19" ht="30" customHeight="1">
+      <c r="A46" s="222"/>
+      <c r="B46" s="222"/>
+      <c r="C46" s="223"/>
+      <c r="D46" s="223"/>
+      <c r="E46" s="223"/>
+      <c r="F46" s="223"/>
+      <c r="G46" s="223"/>
+      <c r="H46" s="232"/>
+      <c r="I46" s="233"/>
+      <c r="J46" s="233"/>
+      <c r="K46" s="233"/>
+      <c r="L46" s="233"/>
+      <c r="M46" s="234"/>
+      <c r="N46" s="229"/>
+      <c r="O46" s="230"/>
+      <c r="P46" s="231"/>
+      <c r="Q46" s="222"/>
+      <c r="R46" s="228"/>
+      <c r="S46" s="228"/>
+    </row>
+    <row r="47" spans="1:19" ht="30" customHeight="1">
+      <c r="A47" s="222"/>
+      <c r="B47" s="222"/>
+      <c r="C47" s="223"/>
+      <c r="D47" s="223"/>
+      <c r="E47" s="223"/>
+      <c r="F47" s="223"/>
+      <c r="G47" s="223"/>
+      <c r="H47" s="232"/>
+      <c r="I47" s="233"/>
+      <c r="J47" s="233"/>
+      <c r="K47" s="233"/>
+      <c r="L47" s="233"/>
+      <c r="M47" s="234"/>
+      <c r="N47" s="229"/>
+      <c r="O47" s="230"/>
+      <c r="P47" s="231"/>
+      <c r="Q47" s="222"/>
+      <c r="R47" s="228"/>
+      <c r="S47" s="228"/>
+    </row>
+    <row r="48" spans="1:19" ht="30" customHeight="1">
+      <c r="A48" s="222"/>
+      <c r="B48" s="222"/>
+      <c r="C48" s="223"/>
+      <c r="D48" s="223"/>
+      <c r="E48" s="223"/>
+      <c r="F48" s="223"/>
+      <c r="G48" s="223"/>
+      <c r="H48" s="232"/>
+      <c r="I48" s="233"/>
+      <c r="J48" s="233"/>
+      <c r="K48" s="233"/>
+      <c r="L48" s="233"/>
+      <c r="M48" s="234"/>
+      <c r="N48" s="229"/>
+      <c r="O48" s="230"/>
+      <c r="P48" s="231"/>
+      <c r="Q48" s="222"/>
+      <c r="R48" s="228"/>
+      <c r="S48" s="228"/>
+    </row>
+    <row r="49" spans="1:19" ht="30" customHeight="1">
+      <c r="A49" s="222"/>
+      <c r="B49" s="222"/>
+      <c r="C49" s="223"/>
+      <c r="D49" s="223"/>
+      <c r="E49" s="223"/>
+      <c r="F49" s="223"/>
+      <c r="G49" s="223"/>
+      <c r="H49" s="232"/>
+      <c r="I49" s="233"/>
+      <c r="J49" s="233"/>
+      <c r="K49" s="233"/>
+      <c r="L49" s="233"/>
+      <c r="M49" s="234"/>
+      <c r="N49" s="229"/>
+      <c r="O49" s="230"/>
+      <c r="P49" s="231"/>
+      <c r="Q49" s="222"/>
+      <c r="R49" s="228"/>
+      <c r="S49" s="228"/>
+    </row>
+    <row r="50" spans="1:19" ht="30" customHeight="1">
+      <c r="A50" s="222"/>
+      <c r="B50" s="222"/>
+      <c r="C50" s="223"/>
+      <c r="D50" s="223"/>
+      <c r="E50" s="223"/>
+      <c r="F50" s="223"/>
+      <c r="G50" s="223"/>
+      <c r="H50" s="232"/>
+      <c r="I50" s="233"/>
+      <c r="J50" s="233"/>
+      <c r="K50" s="233"/>
+      <c r="L50" s="233"/>
+      <c r="M50" s="234"/>
+      <c r="N50" s="229"/>
+      <c r="O50" s="230"/>
+      <c r="P50" s="231"/>
+      <c r="Q50" s="222"/>
+      <c r="R50" s="228"/>
+      <c r="S50" s="228"/>
+    </row>
+    <row r="51" spans="1:19" ht="30" customHeight="1">
+      <c r="A51" s="222"/>
+      <c r="B51" s="222"/>
+      <c r="C51" s="223"/>
+      <c r="D51" s="223"/>
+      <c r="E51" s="223"/>
+      <c r="F51" s="223"/>
+      <c r="G51" s="223"/>
+      <c r="H51" s="232"/>
+      <c r="I51" s="233"/>
+      <c r="J51" s="233"/>
+      <c r="K51" s="233"/>
+      <c r="L51" s="233"/>
+      <c r="M51" s="234"/>
+      <c r="N51" s="229"/>
+      <c r="O51" s="230"/>
+      <c r="P51" s="231"/>
+      <c r="Q51" s="222"/>
+      <c r="R51" s="228"/>
+      <c r="S51" s="228"/>
+    </row>
+    <row r="52" spans="1:19" ht="30" customHeight="1">
+      <c r="A52" s="222"/>
+      <c r="B52" s="222"/>
+      <c r="C52" s="223"/>
+      <c r="D52" s="223"/>
+      <c r="E52" s="223"/>
+      <c r="F52" s="223"/>
+      <c r="G52" s="223"/>
+      <c r="H52" s="232"/>
+      <c r="I52" s="233"/>
+      <c r="J52" s="233"/>
+      <c r="K52" s="233"/>
+      <c r="L52" s="233"/>
+      <c r="M52" s="234"/>
+      <c r="N52" s="229"/>
+      <c r="O52" s="230"/>
+      <c r="P52" s="231"/>
+      <c r="Q52" s="222"/>
+      <c r="R52" s="228"/>
+      <c r="S52" s="228"/>
+    </row>
+  </sheetData>
+  <mergeCells count="205">
+    <mergeCell ref="C52:G52"/>
+    <mergeCell ref="H52:M52"/>
+    <mergeCell ref="N52:P52"/>
+    <mergeCell ref="R52:S52"/>
+    <mergeCell ref="C50:G50"/>
+    <mergeCell ref="H50:M50"/>
+    <mergeCell ref="N50:P50"/>
+    <mergeCell ref="R50:S50"/>
+    <mergeCell ref="C51:G51"/>
+    <mergeCell ref="H51:M51"/>
+    <mergeCell ref="N51:P51"/>
+    <mergeCell ref="R51:S51"/>
+    <mergeCell ref="C48:G48"/>
+    <mergeCell ref="H48:M48"/>
+    <mergeCell ref="N48:P48"/>
+    <mergeCell ref="R48:S48"/>
+    <mergeCell ref="C49:G49"/>
+    <mergeCell ref="H49:M49"/>
+    <mergeCell ref="N49:P49"/>
+    <mergeCell ref="R49:S49"/>
+    <mergeCell ref="C46:G46"/>
+    <mergeCell ref="H46:M46"/>
+    <mergeCell ref="N46:P46"/>
+    <mergeCell ref="R46:S46"/>
+    <mergeCell ref="C47:G47"/>
+    <mergeCell ref="H47:M47"/>
+    <mergeCell ref="N47:P47"/>
+    <mergeCell ref="R47:S47"/>
+    <mergeCell ref="C44:G44"/>
+    <mergeCell ref="H44:M44"/>
+    <mergeCell ref="N44:P44"/>
+    <mergeCell ref="R44:S44"/>
+    <mergeCell ref="C45:G45"/>
+    <mergeCell ref="H45:M45"/>
+    <mergeCell ref="N45:P45"/>
+    <mergeCell ref="R45:S45"/>
+    <mergeCell ref="C42:G42"/>
+    <mergeCell ref="H42:M42"/>
+    <mergeCell ref="N42:P42"/>
+    <mergeCell ref="R42:S42"/>
+    <mergeCell ref="C43:G43"/>
+    <mergeCell ref="H43:M43"/>
+    <mergeCell ref="N43:P43"/>
+    <mergeCell ref="R43:S43"/>
+    <mergeCell ref="C40:G40"/>
+    <mergeCell ref="H40:M40"/>
+    <mergeCell ref="N40:P40"/>
+    <mergeCell ref="R40:S40"/>
+    <mergeCell ref="C41:G41"/>
+    <mergeCell ref="H41:M41"/>
+    <mergeCell ref="N41:P41"/>
+    <mergeCell ref="R41:S41"/>
+    <mergeCell ref="C38:G38"/>
+    <mergeCell ref="H38:M38"/>
+    <mergeCell ref="N38:P38"/>
+    <mergeCell ref="R38:S38"/>
+    <mergeCell ref="C39:G39"/>
+    <mergeCell ref="H39:M39"/>
+    <mergeCell ref="N39:P39"/>
+    <mergeCell ref="R39:S39"/>
+    <mergeCell ref="C36:G36"/>
+    <mergeCell ref="H36:M36"/>
+    <mergeCell ref="N36:P36"/>
+    <mergeCell ref="R36:S36"/>
+    <mergeCell ref="C37:G37"/>
+    <mergeCell ref="H37:M37"/>
+    <mergeCell ref="N37:P37"/>
+    <mergeCell ref="R37:S37"/>
+    <mergeCell ref="C34:G34"/>
+    <mergeCell ref="H34:M34"/>
+    <mergeCell ref="N34:P34"/>
+    <mergeCell ref="R34:S34"/>
+    <mergeCell ref="C35:G35"/>
+    <mergeCell ref="H35:M35"/>
+    <mergeCell ref="N35:P35"/>
+    <mergeCell ref="R35:S35"/>
+    <mergeCell ref="C32:G32"/>
+    <mergeCell ref="H32:M32"/>
+    <mergeCell ref="N32:P32"/>
+    <mergeCell ref="R32:S32"/>
+    <mergeCell ref="C33:G33"/>
+    <mergeCell ref="H33:M33"/>
+    <mergeCell ref="N33:P33"/>
+    <mergeCell ref="R33:S33"/>
+    <mergeCell ref="C30:G30"/>
+    <mergeCell ref="H30:M30"/>
+    <mergeCell ref="N30:P30"/>
+    <mergeCell ref="R30:S30"/>
+    <mergeCell ref="C31:G31"/>
+    <mergeCell ref="H31:M31"/>
+    <mergeCell ref="N31:P31"/>
+    <mergeCell ref="R31:S31"/>
+    <mergeCell ref="C28:G28"/>
+    <mergeCell ref="H28:M28"/>
+    <mergeCell ref="N28:P28"/>
+    <mergeCell ref="R28:S28"/>
+    <mergeCell ref="C29:G29"/>
+    <mergeCell ref="H29:M29"/>
+    <mergeCell ref="N29:P29"/>
+    <mergeCell ref="R29:S29"/>
+    <mergeCell ref="C26:G26"/>
+    <mergeCell ref="H26:M26"/>
+    <mergeCell ref="N26:P26"/>
+    <mergeCell ref="R26:S26"/>
+    <mergeCell ref="C27:G27"/>
+    <mergeCell ref="H27:M27"/>
+    <mergeCell ref="N27:P27"/>
+    <mergeCell ref="R27:S27"/>
+    <mergeCell ref="C24:G24"/>
+    <mergeCell ref="H24:M24"/>
+    <mergeCell ref="N24:P24"/>
+    <mergeCell ref="R24:S24"/>
+    <mergeCell ref="C25:G25"/>
+    <mergeCell ref="H25:M25"/>
+    <mergeCell ref="N25:P25"/>
+    <mergeCell ref="R25:S25"/>
+    <mergeCell ref="C22:G22"/>
+    <mergeCell ref="H22:M22"/>
+    <mergeCell ref="N22:P22"/>
+    <mergeCell ref="R22:S22"/>
+    <mergeCell ref="C23:G23"/>
+    <mergeCell ref="H23:M23"/>
+    <mergeCell ref="N23:P23"/>
+    <mergeCell ref="R23:S23"/>
+    <mergeCell ref="C20:G20"/>
+    <mergeCell ref="H20:M20"/>
+    <mergeCell ref="N20:P20"/>
+    <mergeCell ref="R20:S20"/>
+    <mergeCell ref="C21:G21"/>
+    <mergeCell ref="H21:M21"/>
+    <mergeCell ref="N21:P21"/>
+    <mergeCell ref="R21:S21"/>
+    <mergeCell ref="C18:G18"/>
+    <mergeCell ref="H18:M18"/>
+    <mergeCell ref="N18:P18"/>
+    <mergeCell ref="R18:S18"/>
+    <mergeCell ref="C19:G19"/>
+    <mergeCell ref="H19:M19"/>
+    <mergeCell ref="N19:P19"/>
+    <mergeCell ref="R19:S19"/>
+    <mergeCell ref="C16:G16"/>
+    <mergeCell ref="H16:M16"/>
+    <mergeCell ref="N16:P16"/>
+    <mergeCell ref="R16:S16"/>
+    <mergeCell ref="C17:G17"/>
+    <mergeCell ref="H17:M17"/>
+    <mergeCell ref="N17:P17"/>
+    <mergeCell ref="R17:S17"/>
+    <mergeCell ref="C14:G14"/>
+    <mergeCell ref="H14:M14"/>
+    <mergeCell ref="N14:P14"/>
+    <mergeCell ref="R14:S14"/>
+    <mergeCell ref="C15:G15"/>
+    <mergeCell ref="H15:M15"/>
+    <mergeCell ref="N15:P15"/>
+    <mergeCell ref="R15:S15"/>
+    <mergeCell ref="C12:G12"/>
+    <mergeCell ref="H12:M12"/>
+    <mergeCell ref="N12:P12"/>
+    <mergeCell ref="R12:S12"/>
+    <mergeCell ref="C13:G13"/>
+    <mergeCell ref="H13:M13"/>
+    <mergeCell ref="N13:P13"/>
+    <mergeCell ref="R13:S13"/>
+    <mergeCell ref="C10:G10"/>
+    <mergeCell ref="H10:M10"/>
+    <mergeCell ref="N10:P10"/>
+    <mergeCell ref="R10:S10"/>
+    <mergeCell ref="C11:G11"/>
+    <mergeCell ref="H11:M11"/>
+    <mergeCell ref="N11:P11"/>
+    <mergeCell ref="R11:S11"/>
+    <mergeCell ref="C8:G8"/>
+    <mergeCell ref="H8:M8"/>
+    <mergeCell ref="N8:P8"/>
+    <mergeCell ref="R8:S8"/>
+    <mergeCell ref="C9:G9"/>
+    <mergeCell ref="H9:M9"/>
+    <mergeCell ref="N9:P9"/>
+    <mergeCell ref="R9:S9"/>
+    <mergeCell ref="C6:G6"/>
+    <mergeCell ref="H6:M6"/>
+    <mergeCell ref="N6:P6"/>
+    <mergeCell ref="R6:S6"/>
+    <mergeCell ref="C7:G7"/>
+    <mergeCell ref="H7:M7"/>
+    <mergeCell ref="N7:P7"/>
+    <mergeCell ref="R7:S7"/>
+    <mergeCell ref="C4:G4"/>
+    <mergeCell ref="H4:M4"/>
+    <mergeCell ref="N4:P4"/>
+    <mergeCell ref="R4:S4"/>
+    <mergeCell ref="C5:G5"/>
+    <mergeCell ref="H5:M5"/>
+    <mergeCell ref="N5:P5"/>
+    <mergeCell ref="R5:S5"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="F1:M1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="R1:S1"/>
+    <mergeCell ref="C2:E2"/>
+    <mergeCell ref="F2:M2"/>
+    <mergeCell ref="O2:P2"/>
+    <mergeCell ref="R2:S2"/>
+  </mergeCells>
+  <phoneticPr fontId="8"/>
+  <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.31496062992125984" bottom="0.27559055118110237" header="0.35433070866141736" footer="0.15748031496062992"/>
+  <pageSetup paperSize="9" orientation="landscape" horizontalDpi="4294967293" r:id="rId1"/>
+  <headerFooter alignWithMargins="0"/>
 </worksheet>
 </file>
 
@@ -6698,19 +8512,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="60" t="s">
+      <c r="A1" s="89" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="61"/>
-      <c r="C1" s="62"/>
-      <c r="D1" s="69" t="s">
+      <c r="B1" s="90"/>
+      <c r="C1" s="91"/>
+      <c r="D1" s="98" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="70"/>
-      <c r="F1" s="69" t="s">
+      <c r="E1" s="83"/>
+      <c r="F1" s="98" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="70"/>
+      <c r="G1" s="83"/>
       <c r="H1" s="34" t="s">
         <v>6</v>
       </c>
@@ -6722,192 +8536,192 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="63"/>
-      <c r="B2" s="64"/>
-      <c r="C2" s="65"/>
-      <c r="D2" s="71" t="s">
+      <c r="A2" s="92"/>
+      <c r="B2" s="93"/>
+      <c r="C2" s="94"/>
+      <c r="D2" s="99" t="s">
         <v>61</v>
       </c>
-      <c r="E2" s="72"/>
-      <c r="F2" s="71">
+      <c r="E2" s="100"/>
+      <c r="F2" s="99">
         <v>56</v>
       </c>
-      <c r="G2" s="72"/>
-      <c r="H2" s="75">
+      <c r="G2" s="100"/>
+      <c r="H2" s="68">
         <v>45806</v>
       </c>
-      <c r="I2" s="89" t="s">
+      <c r="I2" s="77" t="s">
         <v>60</v>
       </c>
-      <c r="J2" s="90"/>
+      <c r="J2" s="78"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="63"/>
-      <c r="B3" s="64"/>
-      <c r="C3" s="65"/>
-      <c r="D3" s="73"/>
-      <c r="E3" s="65"/>
-      <c r="F3" s="73"/>
-      <c r="G3" s="65"/>
-      <c r="H3" s="76"/>
-      <c r="I3" s="76"/>
-      <c r="J3" s="91"/>
+      <c r="A3" s="92"/>
+      <c r="B3" s="93"/>
+      <c r="C3" s="94"/>
+      <c r="D3" s="101"/>
+      <c r="E3" s="94"/>
+      <c r="F3" s="101"/>
+      <c r="G3" s="94"/>
+      <c r="H3" s="69"/>
+      <c r="I3" s="69"/>
+      <c r="J3" s="79"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="66"/>
-      <c r="B4" s="67"/>
-      <c r="C4" s="68"/>
-      <c r="D4" s="74"/>
-      <c r="E4" s="68"/>
-      <c r="F4" s="74"/>
-      <c r="G4" s="68"/>
-      <c r="H4" s="77"/>
-      <c r="I4" s="77"/>
-      <c r="J4" s="92"/>
+      <c r="A4" s="95"/>
+      <c r="B4" s="96"/>
+      <c r="C4" s="97"/>
+      <c r="D4" s="102"/>
+      <c r="E4" s="97"/>
+      <c r="F4" s="102"/>
+      <c r="G4" s="97"/>
+      <c r="H4" s="70"/>
+      <c r="I4" s="70"/>
+      <c r="J4" s="80"/>
     </row>
     <row r="5" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A5" s="93" t="s">
+      <c r="A5" s="81" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="94"/>
-      <c r="C5" s="70"/>
-      <c r="D5" s="95" t="s">
+      <c r="B5" s="82"/>
+      <c r="C5" s="83"/>
+      <c r="D5" s="84" t="s">
         <v>59</v>
       </c>
-      <c r="E5" s="94"/>
-      <c r="F5" s="94"/>
-      <c r="G5" s="94"/>
-      <c r="H5" s="94"/>
-      <c r="I5" s="94"/>
-      <c r="J5" s="96"/>
+      <c r="E5" s="82"/>
+      <c r="F5" s="82"/>
+      <c r="G5" s="82"/>
+      <c r="H5" s="82"/>
+      <c r="I5" s="82"/>
+      <c r="J5" s="85"/>
     </row>
     <row r="6" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A6" s="78" t="s">
+      <c r="A6" s="71" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="79"/>
-      <c r="C6" s="80"/>
-      <c r="D6" s="88" t="s">
+      <c r="B6" s="66"/>
+      <c r="C6" s="61"/>
+      <c r="D6" s="65" t="s">
         <v>58</v>
       </c>
-      <c r="E6" s="79"/>
-      <c r="F6" s="79"/>
-      <c r="G6" s="79"/>
-      <c r="H6" s="79"/>
-      <c r="I6" s="79"/>
-      <c r="J6" s="82"/>
+      <c r="E6" s="66"/>
+      <c r="F6" s="66"/>
+      <c r="G6" s="66"/>
+      <c r="H6" s="66"/>
+      <c r="I6" s="66"/>
+      <c r="J6" s="67"/>
     </row>
     <row r="7" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A7" s="78" t="s">
+      <c r="A7" s="71" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="79"/>
-      <c r="C7" s="80"/>
-      <c r="D7" s="88" t="s">
+      <c r="B7" s="66"/>
+      <c r="C7" s="61"/>
+      <c r="D7" s="65" t="s">
         <v>57</v>
       </c>
-      <c r="E7" s="79"/>
-      <c r="F7" s="79"/>
-      <c r="G7" s="79"/>
-      <c r="H7" s="79"/>
-      <c r="I7" s="79"/>
-      <c r="J7" s="82"/>
+      <c r="E7" s="66"/>
+      <c r="F7" s="66"/>
+      <c r="G7" s="66"/>
+      <c r="H7" s="66"/>
+      <c r="I7" s="66"/>
+      <c r="J7" s="67"/>
     </row>
     <row r="8" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A8" s="78" t="s">
+      <c r="A8" s="71" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="79"/>
-      <c r="C8" s="80"/>
-      <c r="D8" s="81" t="s">
+      <c r="B8" s="66"/>
+      <c r="C8" s="61"/>
+      <c r="D8" s="62" t="s">
         <v>107</v>
       </c>
-      <c r="E8" s="79"/>
-      <c r="F8" s="79"/>
-      <c r="G8" s="79"/>
-      <c r="H8" s="79"/>
-      <c r="I8" s="79"/>
-      <c r="J8" s="82"/>
+      <c r="E8" s="66"/>
+      <c r="F8" s="66"/>
+      <c r="G8" s="66"/>
+      <c r="H8" s="66"/>
+      <c r="I8" s="66"/>
+      <c r="J8" s="67"/>
     </row>
     <row r="9" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A9" s="97" t="s">
+      <c r="A9" s="86" t="s">
         <v>13</v>
       </c>
-      <c r="B9" s="100" t="s">
+      <c r="B9" s="60" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="80"/>
-      <c r="D9" s="81" t="s">
+      <c r="C9" s="61"/>
+      <c r="D9" s="62" t="s">
         <v>105</v>
       </c>
-      <c r="E9" s="101"/>
-      <c r="F9" s="101"/>
-      <c r="G9" s="101"/>
-      <c r="H9" s="101"/>
-      <c r="I9" s="101"/>
-      <c r="J9" s="102"/>
+      <c r="E9" s="63"/>
+      <c r="F9" s="63"/>
+      <c r="G9" s="63"/>
+      <c r="H9" s="63"/>
+      <c r="I9" s="63"/>
+      <c r="J9" s="64"/>
     </row>
     <row r="10" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A10" s="98"/>
-      <c r="B10" s="100" t="s">
+      <c r="A10" s="87"/>
+      <c r="B10" s="60" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="80"/>
-      <c r="D10" s="88" t="s">
+      <c r="C10" s="61"/>
+      <c r="D10" s="65" t="s">
         <v>93</v>
       </c>
-      <c r="E10" s="79"/>
-      <c r="F10" s="79"/>
-      <c r="G10" s="79"/>
-      <c r="H10" s="79"/>
-      <c r="I10" s="79"/>
-      <c r="J10" s="82"/>
+      <c r="E10" s="66"/>
+      <c r="F10" s="66"/>
+      <c r="G10" s="66"/>
+      <c r="H10" s="66"/>
+      <c r="I10" s="66"/>
+      <c r="J10" s="67"/>
     </row>
     <row r="11" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A11" s="99"/>
-      <c r="B11" s="100" t="s">
+      <c r="A11" s="88"/>
+      <c r="B11" s="60" t="s">
         <v>16</v>
       </c>
-      <c r="C11" s="80"/>
-      <c r="D11" s="81" t="s">
+      <c r="C11" s="61"/>
+      <c r="D11" s="62" t="s">
         <v>108</v>
       </c>
-      <c r="E11" s="79"/>
-      <c r="F11" s="79"/>
-      <c r="G11" s="79"/>
-      <c r="H11" s="79"/>
-      <c r="I11" s="79"/>
-      <c r="J11" s="82"/>
+      <c r="E11" s="66"/>
+      <c r="F11" s="66"/>
+      <c r="G11" s="66"/>
+      <c r="H11" s="66"/>
+      <c r="I11" s="66"/>
+      <c r="J11" s="67"/>
     </row>
     <row r="12" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A12" s="78" t="s">
+      <c r="A12" s="71" t="s">
         <v>17</v>
       </c>
-      <c r="B12" s="79"/>
-      <c r="C12" s="80"/>
-      <c r="D12" s="81" t="s">
+      <c r="B12" s="66"/>
+      <c r="C12" s="61"/>
+      <c r="D12" s="62" t="s">
         <v>106</v>
       </c>
-      <c r="E12" s="79"/>
-      <c r="F12" s="79"/>
-      <c r="G12" s="79"/>
-      <c r="H12" s="79"/>
-      <c r="I12" s="79"/>
-      <c r="J12" s="82"/>
+      <c r="E12" s="66"/>
+      <c r="F12" s="66"/>
+      <c r="G12" s="66"/>
+      <c r="H12" s="66"/>
+      <c r="I12" s="66"/>
+      <c r="J12" s="67"/>
     </row>
     <row r="13" spans="1:10" ht="26.25" customHeight="1" thickBot="1">
-      <c r="A13" s="83" t="s">
+      <c r="A13" s="72" t="s">
         <v>18</v>
       </c>
-      <c r="B13" s="84"/>
-      <c r="C13" s="85"/>
-      <c r="D13" s="86"/>
-      <c r="E13" s="84"/>
-      <c r="F13" s="84"/>
-      <c r="G13" s="84"/>
-      <c r="H13" s="84"/>
-      <c r="I13" s="84"/>
-      <c r="J13" s="87"/>
+      <c r="B13" s="73"/>
+      <c r="C13" s="74"/>
+      <c r="D13" s="75"/>
+      <c r="E13" s="73"/>
+      <c r="F13" s="73"/>
+      <c r="G13" s="73"/>
+      <c r="H13" s="73"/>
+      <c r="I13" s="73"/>
+      <c r="J13" s="76"/>
     </row>
     <row r="14" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="15" spans="1:10" ht="12.75" customHeight="1"/>
@@ -7898,12 +9712,11 @@
     <row r="1000" s="32" customFormat="1" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="D9:J9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="D10:J10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="D11:J11"/>
+    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="F2:G4"/>
     <mergeCell ref="H2:H4"/>
     <mergeCell ref="A12:C12"/>
     <mergeCell ref="D12:J12"/>
@@ -7920,11 +9733,12 @@
     <mergeCell ref="A6:C6"/>
     <mergeCell ref="D6:J6"/>
     <mergeCell ref="A9:A11"/>
-    <mergeCell ref="A1:C4"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="D2:E4"/>
-    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="D9:J9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="D10:J10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="D11:J11"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.70833333333333304" right="0.70833333333333304" top="0.74791666666666701" bottom="0.74791666666666701" header="0" footer="0"/>
@@ -10802,19 +12616,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="135" t="s">
+      <c r="A1" s="137" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="136"/>
-      <c r="C1" s="137"/>
-      <c r="D1" s="139" t="s">
+      <c r="B1" s="138"/>
+      <c r="C1" s="139"/>
+      <c r="D1" s="141" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="140"/>
-      <c r="F1" s="139" t="s">
+      <c r="E1" s="142"/>
+      <c r="F1" s="141" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="140"/>
+      <c r="G1" s="142"/>
       <c r="H1" s="43" t="s">
         <v>6</v>
       </c>
@@ -10826,67 +12640,67 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="132"/>
-      <c r="B2" s="133"/>
-      <c r="C2" s="138"/>
-      <c r="D2" s="141" t="s">
+      <c r="A2" s="134"/>
+      <c r="B2" s="135"/>
+      <c r="C2" s="140"/>
+      <c r="D2" s="143" t="s">
         <v>84</v>
       </c>
-      <c r="E2" s="142"/>
-      <c r="F2" s="141">
+      <c r="E2" s="144"/>
+      <c r="F2" s="143">
         <v>56</v>
       </c>
-      <c r="G2" s="142"/>
-      <c r="H2" s="144">
+      <c r="G2" s="144"/>
+      <c r="H2" s="146">
         <v>45806</v>
       </c>
-      <c r="I2" s="146" t="s">
+      <c r="I2" s="148" t="s">
         <v>83</v>
       </c>
-      <c r="J2" s="147"/>
+      <c r="J2" s="149"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="132"/>
-      <c r="B3" s="133"/>
-      <c r="C3" s="138"/>
-      <c r="D3" s="143"/>
-      <c r="E3" s="138"/>
-      <c r="F3" s="143"/>
-      <c r="G3" s="138"/>
-      <c r="H3" s="145"/>
-      <c r="I3" s="145"/>
-      <c r="J3" s="148"/>
+      <c r="A3" s="134"/>
+      <c r="B3" s="135"/>
+      <c r="C3" s="140"/>
+      <c r="D3" s="145"/>
+      <c r="E3" s="140"/>
+      <c r="F3" s="145"/>
+      <c r="G3" s="140"/>
+      <c r="H3" s="147"/>
+      <c r="I3" s="147"/>
+      <c r="J3" s="150"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="132"/>
-      <c r="B4" s="133"/>
-      <c r="C4" s="138"/>
-      <c r="D4" s="143"/>
-      <c r="E4" s="138"/>
-      <c r="F4" s="143"/>
-      <c r="G4" s="138"/>
-      <c r="H4" s="145"/>
-      <c r="I4" s="145"/>
-      <c r="J4" s="148"/>
+      <c r="A4" s="134"/>
+      <c r="B4" s="135"/>
+      <c r="C4" s="140"/>
+      <c r="D4" s="145"/>
+      <c r="E4" s="140"/>
+      <c r="F4" s="145"/>
+      <c r="G4" s="140"/>
+      <c r="H4" s="147"/>
+      <c r="I4" s="147"/>
+      <c r="J4" s="150"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="149" t="s">
+      <c r="A5" s="151" t="s">
         <v>22</v>
       </c>
-      <c r="B5" s="150"/>
-      <c r="C5" s="140"/>
-      <c r="D5" s="151" t="s">
+      <c r="B5" s="152"/>
+      <c r="C5" s="142"/>
+      <c r="D5" s="153" t="s">
         <v>92</v>
       </c>
-      <c r="E5" s="150"/>
-      <c r="F5" s="150"/>
-      <c r="G5" s="150"/>
-      <c r="H5" s="150"/>
-      <c r="I5" s="150"/>
-      <c r="J5" s="152"/>
+      <c r="E5" s="152"/>
+      <c r="F5" s="152"/>
+      <c r="G5" s="152"/>
+      <c r="H5" s="152"/>
+      <c r="I5" s="152"/>
+      <c r="J5" s="154"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="153" t="s">
+      <c r="A6" s="130" t="s">
         <v>23</v>
       </c>
       <c r="B6" s="125"/>
@@ -10900,91 +12714,91 @@
       <c r="J6" s="128"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="129"/>
-      <c r="B7" s="130"/>
-      <c r="C7" s="130"/>
-      <c r="D7" s="130"/>
-      <c r="E7" s="130"/>
-      <c r="F7" s="130"/>
-      <c r="G7" s="130"/>
-      <c r="H7" s="130"/>
-      <c r="I7" s="130"/>
-      <c r="J7" s="131"/>
+      <c r="A7" s="131"/>
+      <c r="B7" s="132"/>
+      <c r="C7" s="132"/>
+      <c r="D7" s="132"/>
+      <c r="E7" s="132"/>
+      <c r="F7" s="132"/>
+      <c r="G7" s="132"/>
+      <c r="H7" s="132"/>
+      <c r="I7" s="132"/>
+      <c r="J7" s="133"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="132"/>
-      <c r="B8" s="133"/>
-      <c r="C8" s="133"/>
-      <c r="D8" s="133"/>
-      <c r="E8" s="133"/>
-      <c r="F8" s="133"/>
-      <c r="G8" s="133"/>
-      <c r="H8" s="133"/>
-      <c r="I8" s="133"/>
-      <c r="J8" s="134"/>
+      <c r="A8" s="134"/>
+      <c r="B8" s="135"/>
+      <c r="C8" s="135"/>
+      <c r="D8" s="135"/>
+      <c r="E8" s="135"/>
+      <c r="F8" s="135"/>
+      <c r="G8" s="135"/>
+      <c r="H8" s="135"/>
+      <c r="I8" s="135"/>
+      <c r="J8" s="136"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="132"/>
-      <c r="B9" s="133"/>
-      <c r="C9" s="133"/>
-      <c r="D9" s="133"/>
-      <c r="E9" s="133"/>
-      <c r="F9" s="133"/>
-      <c r="G9" s="133"/>
-      <c r="H9" s="133"/>
-      <c r="I9" s="133"/>
-      <c r="J9" s="134"/>
+      <c r="A9" s="134"/>
+      <c r="B9" s="135"/>
+      <c r="C9" s="135"/>
+      <c r="D9" s="135"/>
+      <c r="E9" s="135"/>
+      <c r="F9" s="135"/>
+      <c r="G9" s="135"/>
+      <c r="H9" s="135"/>
+      <c r="I9" s="135"/>
+      <c r="J9" s="136"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="132"/>
-      <c r="B10" s="133"/>
-      <c r="C10" s="133"/>
-      <c r="D10" s="133"/>
-      <c r="E10" s="133"/>
-      <c r="F10" s="133"/>
-      <c r="G10" s="133"/>
-      <c r="H10" s="133"/>
-      <c r="I10" s="133"/>
-      <c r="J10" s="134"/>
+      <c r="A10" s="134"/>
+      <c r="B10" s="135"/>
+      <c r="C10" s="135"/>
+      <c r="D10" s="135"/>
+      <c r="E10" s="135"/>
+      <c r="F10" s="135"/>
+      <c r="G10" s="135"/>
+      <c r="H10" s="135"/>
+      <c r="I10" s="135"/>
+      <c r="J10" s="136"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="132"/>
-      <c r="B11" s="133"/>
-      <c r="C11" s="133"/>
-      <c r="D11" s="133"/>
-      <c r="E11" s="133"/>
-      <c r="F11" s="133"/>
-      <c r="G11" s="133"/>
-      <c r="H11" s="133"/>
-      <c r="I11" s="133"/>
-      <c r="J11" s="134"/>
+      <c r="A11" s="134"/>
+      <c r="B11" s="135"/>
+      <c r="C11" s="135"/>
+      <c r="D11" s="135"/>
+      <c r="E11" s="135"/>
+      <c r="F11" s="135"/>
+      <c r="G11" s="135"/>
+      <c r="H11" s="135"/>
+      <c r="I11" s="135"/>
+      <c r="J11" s="136"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="132"/>
-      <c r="B12" s="133"/>
-      <c r="C12" s="133"/>
-      <c r="D12" s="133"/>
-      <c r="E12" s="133"/>
-      <c r="F12" s="133"/>
-      <c r="G12" s="133"/>
-      <c r="H12" s="133"/>
-      <c r="I12" s="133"/>
-      <c r="J12" s="134"/>
+      <c r="A12" s="134"/>
+      <c r="B12" s="135"/>
+      <c r="C12" s="135"/>
+      <c r="D12" s="135"/>
+      <c r="E12" s="135"/>
+      <c r="F12" s="135"/>
+      <c r="G12" s="135"/>
+      <c r="H12" s="135"/>
+      <c r="I12" s="135"/>
+      <c r="J12" s="136"/>
     </row>
     <row r="13" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A13" s="132"/>
-      <c r="B13" s="133"/>
-      <c r="C13" s="133"/>
-      <c r="D13" s="133"/>
-      <c r="E13" s="133"/>
-      <c r="F13" s="133"/>
-      <c r="G13" s="133"/>
-      <c r="H13" s="133"/>
-      <c r="I13" s="133"/>
-      <c r="J13" s="134"/>
+      <c r="A13" s="134"/>
+      <c r="B13" s="135"/>
+      <c r="C13" s="135"/>
+      <c r="D13" s="135"/>
+      <c r="E13" s="135"/>
+      <c r="F13" s="135"/>
+      <c r="G13" s="135"/>
+      <c r="H13" s="135"/>
+      <c r="I13" s="135"/>
+      <c r="J13" s="136"/>
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A14" s="153" t="s">
+      <c r="A14" s="130" t="s">
         <v>24</v>
       </c>
       <c r="B14" s="125"/>
@@ -10998,7 +12812,7 @@
       <c r="J14" s="128"/>
     </row>
     <row r="15" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A15" s="153" t="s">
+      <c r="A15" s="130" t="s">
         <v>25</v>
       </c>
       <c r="B15" s="125"/>
@@ -11018,7 +12832,7 @@
       </c>
     </row>
     <row r="16" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A16" s="153" t="s">
+      <c r="A16" s="130" t="s">
         <v>27</v>
       </c>
       <c r="B16" s="125"/>
@@ -11035,7 +12849,7 @@
       <c r="G16" s="39" t="s">
         <v>31</v>
       </c>
-      <c r="H16" s="154" t="s">
+      <c r="H16" s="129" t="s">
         <v>18</v>
       </c>
       <c r="I16" s="125"/>
@@ -12207,23 +14021,6 @@
     <row r="1000" s="36" customFormat="1" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="33">
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="H19:J19"/>
-    <mergeCell ref="A23:C23"/>
-    <mergeCell ref="H23:J23"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="H20:J20"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="H21:J21"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="H22:J22"/>
-    <mergeCell ref="H16:J16"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="A15:C15"/>
-    <mergeCell ref="D15:H15"/>
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="H17:J17"/>
     <mergeCell ref="A24:C24"/>
     <mergeCell ref="H24:J24"/>
     <mergeCell ref="A7:J13"/>
@@ -12240,6 +14037,23 @@
     <mergeCell ref="A6:J6"/>
     <mergeCell ref="A14:J14"/>
     <mergeCell ref="A16:C16"/>
+    <mergeCell ref="H16:J16"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="H18:J18"/>
+    <mergeCell ref="A15:C15"/>
+    <mergeCell ref="D15:H15"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="H17:J17"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="H19:J19"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="H23:J23"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="H20:J20"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="H21:J21"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="H22:J22"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -12263,19 +14077,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="163" t="s">
+      <c r="A1" s="160" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="61"/>
-      <c r="C1" s="62"/>
-      <c r="D1" s="69" t="s">
+      <c r="B1" s="90"/>
+      <c r="C1" s="91"/>
+      <c r="D1" s="98" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="70"/>
-      <c r="F1" s="69" t="s">
+      <c r="E1" s="83"/>
+      <c r="F1" s="98" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="70"/>
+      <c r="G1" s="83"/>
       <c r="H1" s="35" t="s">
         <v>6</v>
       </c>
@@ -12287,190 +14101,190 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="63"/>
-      <c r="B2" s="64"/>
-      <c r="C2" s="65"/>
-      <c r="D2" s="71" t="s">
+      <c r="A2" s="92"/>
+      <c r="B2" s="93"/>
+      <c r="C2" s="94"/>
+      <c r="D2" s="99" t="s">
         <v>85</v>
       </c>
-      <c r="E2" s="72"/>
-      <c r="F2" s="71">
+      <c r="E2" s="100"/>
+      <c r="F2" s="99">
         <v>56</v>
       </c>
-      <c r="G2" s="72"/>
-      <c r="H2" s="75">
+      <c r="G2" s="100"/>
+      <c r="H2" s="68">
         <v>45805</v>
       </c>
-      <c r="I2" s="89" t="s">
+      <c r="I2" s="77" t="s">
         <v>83</v>
       </c>
-      <c r="J2" s="90"/>
+      <c r="J2" s="78"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="63"/>
-      <c r="B3" s="64"/>
-      <c r="C3" s="65"/>
-      <c r="D3" s="73"/>
-      <c r="E3" s="65"/>
-      <c r="F3" s="73"/>
-      <c r="G3" s="65"/>
-      <c r="H3" s="76"/>
-      <c r="I3" s="76"/>
-      <c r="J3" s="91"/>
+      <c r="A3" s="92"/>
+      <c r="B3" s="93"/>
+      <c r="C3" s="94"/>
+      <c r="D3" s="101"/>
+      <c r="E3" s="94"/>
+      <c r="F3" s="101"/>
+      <c r="G3" s="94"/>
+      <c r="H3" s="69"/>
+      <c r="I3" s="69"/>
+      <c r="J3" s="79"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="63"/>
-      <c r="B4" s="64"/>
-      <c r="C4" s="65"/>
-      <c r="D4" s="73"/>
-      <c r="E4" s="65"/>
-      <c r="F4" s="73"/>
-      <c r="G4" s="65"/>
-      <c r="H4" s="76"/>
-      <c r="I4" s="76"/>
-      <c r="J4" s="91"/>
+      <c r="A4" s="92"/>
+      <c r="B4" s="93"/>
+      <c r="C4" s="94"/>
+      <c r="D4" s="101"/>
+      <c r="E4" s="94"/>
+      <c r="F4" s="101"/>
+      <c r="G4" s="94"/>
+      <c r="H4" s="69"/>
+      <c r="I4" s="69"/>
+      <c r="J4" s="79"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="164" t="s">
+      <c r="A5" s="161" t="s">
         <v>22</v>
       </c>
-      <c r="B5" s="94"/>
-      <c r="C5" s="70"/>
-      <c r="D5" s="165" t="s">
+      <c r="B5" s="82"/>
+      <c r="C5" s="83"/>
+      <c r="D5" s="162" t="s">
         <v>86</v>
       </c>
-      <c r="E5" s="94"/>
-      <c r="F5" s="94"/>
-      <c r="G5" s="94"/>
-      <c r="H5" s="94"/>
-      <c r="I5" s="94"/>
-      <c r="J5" s="96"/>
+      <c r="E5" s="82"/>
+      <c r="F5" s="82"/>
+      <c r="G5" s="82"/>
+      <c r="H5" s="82"/>
+      <c r="I5" s="82"/>
+      <c r="J5" s="85"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="157" t="s">
+      <c r="A6" s="155" t="s">
         <v>23</v>
       </c>
-      <c r="B6" s="79"/>
-      <c r="C6" s="79"/>
-      <c r="D6" s="79"/>
-      <c r="E6" s="79"/>
-      <c r="F6" s="79"/>
-      <c r="G6" s="79"/>
-      <c r="H6" s="79"/>
-      <c r="I6" s="79"/>
-      <c r="J6" s="82"/>
+      <c r="B6" s="66"/>
+      <c r="C6" s="66"/>
+      <c r="D6" s="66"/>
+      <c r="E6" s="66"/>
+      <c r="F6" s="66"/>
+      <c r="G6" s="66"/>
+      <c r="H6" s="66"/>
+      <c r="I6" s="66"/>
+      <c r="J6" s="67"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="159"/>
-      <c r="B7" s="160"/>
-      <c r="C7" s="160"/>
-      <c r="D7" s="160"/>
-      <c r="E7" s="160"/>
-      <c r="F7" s="160"/>
-      <c r="G7" s="160"/>
-      <c r="H7" s="160"/>
-      <c r="I7" s="160"/>
-      <c r="J7" s="161"/>
+      <c r="A7" s="156"/>
+      <c r="B7" s="157"/>
+      <c r="C7" s="157"/>
+      <c r="D7" s="157"/>
+      <c r="E7" s="157"/>
+      <c r="F7" s="157"/>
+      <c r="G7" s="157"/>
+      <c r="H7" s="157"/>
+      <c r="I7" s="157"/>
+      <c r="J7" s="158"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="63"/>
-      <c r="B8" s="64"/>
-      <c r="C8" s="64"/>
-      <c r="D8" s="64"/>
-      <c r="E8" s="64"/>
-      <c r="F8" s="64"/>
-      <c r="G8" s="64"/>
-      <c r="H8" s="64"/>
-      <c r="I8" s="64"/>
-      <c r="J8" s="162"/>
+      <c r="A8" s="92"/>
+      <c r="B8" s="93"/>
+      <c r="C8" s="93"/>
+      <c r="D8" s="93"/>
+      <c r="E8" s="93"/>
+      <c r="F8" s="93"/>
+      <c r="G8" s="93"/>
+      <c r="H8" s="93"/>
+      <c r="I8" s="93"/>
+      <c r="J8" s="159"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="63"/>
-      <c r="B9" s="64"/>
-      <c r="C9" s="64"/>
-      <c r="D9" s="64"/>
-      <c r="E9" s="64"/>
-      <c r="F9" s="64"/>
-      <c r="G9" s="64"/>
-      <c r="H9" s="64"/>
-      <c r="I9" s="64"/>
-      <c r="J9" s="162"/>
+      <c r="A9" s="92"/>
+      <c r="B9" s="93"/>
+      <c r="C9" s="93"/>
+      <c r="D9" s="93"/>
+      <c r="E9" s="93"/>
+      <c r="F9" s="93"/>
+      <c r="G9" s="93"/>
+      <c r="H9" s="93"/>
+      <c r="I9" s="93"/>
+      <c r="J9" s="159"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="63"/>
-      <c r="B10" s="64"/>
-      <c r="C10" s="64"/>
-      <c r="D10" s="64"/>
-      <c r="E10" s="64"/>
-      <c r="F10" s="64"/>
-      <c r="G10" s="64"/>
-      <c r="H10" s="64"/>
-      <c r="I10" s="64"/>
-      <c r="J10" s="162"/>
+      <c r="A10" s="92"/>
+      <c r="B10" s="93"/>
+      <c r="C10" s="93"/>
+      <c r="D10" s="93"/>
+      <c r="E10" s="93"/>
+      <c r="F10" s="93"/>
+      <c r="G10" s="93"/>
+      <c r="H10" s="93"/>
+      <c r="I10" s="93"/>
+      <c r="J10" s="159"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="63"/>
-      <c r="B11" s="64"/>
-      <c r="C11" s="64"/>
-      <c r="D11" s="64"/>
-      <c r="E11" s="64"/>
-      <c r="F11" s="64"/>
-      <c r="G11" s="64"/>
-      <c r="H11" s="64"/>
-      <c r="I11" s="64"/>
-      <c r="J11" s="162"/>
+      <c r="A11" s="92"/>
+      <c r="B11" s="93"/>
+      <c r="C11" s="93"/>
+      <c r="D11" s="93"/>
+      <c r="E11" s="93"/>
+      <c r="F11" s="93"/>
+      <c r="G11" s="93"/>
+      <c r="H11" s="93"/>
+      <c r="I11" s="93"/>
+      <c r="J11" s="159"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="63"/>
-      <c r="B12" s="64"/>
-      <c r="C12" s="64"/>
-      <c r="D12" s="64"/>
-      <c r="E12" s="64"/>
-      <c r="F12" s="64"/>
-      <c r="G12" s="64"/>
-      <c r="H12" s="64"/>
-      <c r="I12" s="64"/>
-      <c r="J12" s="162"/>
+      <c r="A12" s="92"/>
+      <c r="B12" s="93"/>
+      <c r="C12" s="93"/>
+      <c r="D12" s="93"/>
+      <c r="E12" s="93"/>
+      <c r="F12" s="93"/>
+      <c r="G12" s="93"/>
+      <c r="H12" s="93"/>
+      <c r="I12" s="93"/>
+      <c r="J12" s="159"/>
     </row>
     <row r="13" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A13" s="63"/>
-      <c r="B13" s="64"/>
-      <c r="C13" s="64"/>
-      <c r="D13" s="64"/>
-      <c r="E13" s="64"/>
-      <c r="F13" s="64"/>
-      <c r="G13" s="64"/>
-      <c r="H13" s="64"/>
-      <c r="I13" s="64"/>
-      <c r="J13" s="162"/>
+      <c r="A13" s="92"/>
+      <c r="B13" s="93"/>
+      <c r="C13" s="93"/>
+      <c r="D13" s="93"/>
+      <c r="E13" s="93"/>
+      <c r="F13" s="93"/>
+      <c r="G13" s="93"/>
+      <c r="H13" s="93"/>
+      <c r="I13" s="93"/>
+      <c r="J13" s="159"/>
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A14" s="157" t="s">
+      <c r="A14" s="155" t="s">
         <v>24</v>
       </c>
-      <c r="B14" s="79"/>
-      <c r="C14" s="79"/>
-      <c r="D14" s="79"/>
-      <c r="E14" s="79"/>
-      <c r="F14" s="79"/>
-      <c r="G14" s="79"/>
-      <c r="H14" s="79"/>
-      <c r="I14" s="79"/>
-      <c r="J14" s="82"/>
+      <c r="B14" s="66"/>
+      <c r="C14" s="66"/>
+      <c r="D14" s="66"/>
+      <c r="E14" s="66"/>
+      <c r="F14" s="66"/>
+      <c r="G14" s="66"/>
+      <c r="H14" s="66"/>
+      <c r="I14" s="66"/>
+      <c r="J14" s="67"/>
     </row>
     <row r="15" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A15" s="157" t="s">
+      <c r="A15" s="155" t="s">
         <v>25</v>
       </c>
-      <c r="B15" s="79"/>
-      <c r="C15" s="80"/>
-      <c r="D15" s="88" t="s">
+      <c r="B15" s="66"/>
+      <c r="C15" s="61"/>
+      <c r="D15" s="65" t="s">
         <v>87</v>
       </c>
-      <c r="E15" s="79"/>
-      <c r="F15" s="79"/>
-      <c r="G15" s="79"/>
-      <c r="H15" s="80"/>
+      <c r="E15" s="66"/>
+      <c r="F15" s="66"/>
+      <c r="G15" s="66"/>
+      <c r="H15" s="61"/>
       <c r="I15" s="45" t="s">
         <v>26</v>
       </c>
@@ -12479,11 +14293,11 @@
       </c>
     </row>
     <row r="16" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A16" s="157" t="s">
+      <c r="A16" s="155" t="s">
         <v>27</v>
       </c>
-      <c r="B16" s="79"/>
-      <c r="C16" s="80"/>
+      <c r="B16" s="66"/>
+      <c r="C16" s="61"/>
       <c r="D16" s="45" t="s">
         <v>28</v>
       </c>
@@ -12496,18 +14310,18 @@
       <c r="G16" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="H16" s="158" t="s">
+      <c r="H16" s="163" t="s">
         <v>18</v>
       </c>
-      <c r="I16" s="79"/>
-      <c r="J16" s="82"/>
+      <c r="I16" s="66"/>
+      <c r="J16" s="67"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="155">
+      <c r="A17" s="164">
         <v>1</v>
       </c>
-      <c r="B17" s="79"/>
-      <c r="C17" s="80"/>
+      <c r="B17" s="66"/>
+      <c r="C17" s="61"/>
       <c r="D17" s="47" t="s">
         <v>64</v>
       </c>
@@ -12520,83 +14334,83 @@
       <c r="G17" s="48" t="s">
         <v>89</v>
       </c>
-      <c r="H17" s="88" t="s">
+      <c r="H17" s="65" t="s">
         <v>90</v>
       </c>
-      <c r="I17" s="79"/>
-      <c r="J17" s="82"/>
+      <c r="I17" s="66"/>
+      <c r="J17" s="67"/>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A18" s="155"/>
-      <c r="B18" s="79"/>
-      <c r="C18" s="80"/>
+      <c r="A18" s="164"/>
+      <c r="B18" s="66"/>
+      <c r="C18" s="61"/>
       <c r="D18" s="47"/>
       <c r="E18" s="47"/>
       <c r="F18" s="48"/>
       <c r="G18" s="48"/>
-      <c r="H18" s="88"/>
-      <c r="I18" s="79"/>
-      <c r="J18" s="82"/>
+      <c r="H18" s="65"/>
+      <c r="I18" s="66"/>
+      <c r="J18" s="67"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="155"/>
-      <c r="B19" s="79"/>
-      <c r="C19" s="80"/>
+      <c r="A19" s="164"/>
+      <c r="B19" s="66"/>
+      <c r="C19" s="61"/>
       <c r="D19" s="47"/>
       <c r="E19" s="47"/>
       <c r="F19" s="48"/>
       <c r="G19" s="48"/>
-      <c r="H19" s="88"/>
-      <c r="I19" s="79"/>
-      <c r="J19" s="82"/>
+      <c r="H19" s="65"/>
+      <c r="I19" s="66"/>
+      <c r="J19" s="67"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="155"/>
-      <c r="B20" s="79"/>
-      <c r="C20" s="80"/>
+      <c r="A20" s="164"/>
+      <c r="B20" s="66"/>
+      <c r="C20" s="61"/>
       <c r="D20" s="47"/>
       <c r="E20" s="47"/>
       <c r="F20" s="48"/>
       <c r="G20" s="48"/>
-      <c r="H20" s="88"/>
-      <c r="I20" s="79"/>
-      <c r="J20" s="82"/>
+      <c r="H20" s="65"/>
+      <c r="I20" s="66"/>
+      <c r="J20" s="67"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="155"/>
-      <c r="B21" s="79"/>
-      <c r="C21" s="80"/>
+      <c r="A21" s="164"/>
+      <c r="B21" s="66"/>
+      <c r="C21" s="61"/>
       <c r="D21" s="47"/>
       <c r="E21" s="47"/>
       <c r="F21" s="48"/>
       <c r="G21" s="48"/>
-      <c r="H21" s="88"/>
-      <c r="I21" s="79"/>
-      <c r="J21" s="82"/>
+      <c r="H21" s="65"/>
+      <c r="I21" s="66"/>
+      <c r="J21" s="67"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="155"/>
-      <c r="B22" s="79"/>
-      <c r="C22" s="80"/>
+      <c r="A22" s="164"/>
+      <c r="B22" s="66"/>
+      <c r="C22" s="61"/>
       <c r="D22" s="47"/>
       <c r="E22" s="47"/>
       <c r="F22" s="48"/>
       <c r="G22" s="48"/>
-      <c r="H22" s="88"/>
-      <c r="I22" s="79"/>
-      <c r="J22" s="82"/>
+      <c r="H22" s="65"/>
+      <c r="I22" s="66"/>
+      <c r="J22" s="67"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A23" s="156"/>
-      <c r="B23" s="84"/>
-      <c r="C23" s="85"/>
+      <c r="A23" s="165"/>
+      <c r="B23" s="73"/>
+      <c r="C23" s="74"/>
       <c r="D23" s="49"/>
       <c r="E23" s="49"/>
       <c r="F23" s="50"/>
       <c r="G23" s="50"/>
-      <c r="H23" s="86"/>
-      <c r="I23" s="84"/>
-      <c r="J23" s="87"/>
+      <c r="H23" s="75"/>
+      <c r="I23" s="73"/>
+      <c r="J23" s="76"/>
     </row>
     <row r="24" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="25" spans="1:10" ht="12.75" customHeight="1"/>
@@ -13577,6 +15391,22 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="31">
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="H23:J23"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="H19:J19"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="H20:J20"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="H21:J21"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="H16:J16"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="H18:J18"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="H17:J17"/>
     <mergeCell ref="A14:J14"/>
     <mergeCell ref="A15:C15"/>
     <mergeCell ref="A7:J13"/>
@@ -13592,22 +15422,6 @@
     <mergeCell ref="D5:J5"/>
     <mergeCell ref="A6:J6"/>
     <mergeCell ref="D15:H15"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="H16:J16"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="H17:J17"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="H22:J22"/>
-    <mergeCell ref="A23:C23"/>
-    <mergeCell ref="H23:J23"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="H19:J19"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="H20:J20"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="H21:J21"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -13631,19 +15445,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="163" t="s">
+      <c r="A1" s="160" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="61"/>
-      <c r="C1" s="62"/>
-      <c r="D1" s="69" t="s">
+      <c r="B1" s="90"/>
+      <c r="C1" s="91"/>
+      <c r="D1" s="98" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="70"/>
-      <c r="F1" s="69" t="s">
+      <c r="E1" s="83"/>
+      <c r="F1" s="98" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="70"/>
+      <c r="G1" s="83"/>
       <c r="H1" s="35" t="s">
         <v>6</v>
       </c>
@@ -13655,190 +15469,190 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="63"/>
-      <c r="B2" s="64"/>
-      <c r="C2" s="65"/>
-      <c r="D2" s="71" t="s">
+      <c r="A2" s="92"/>
+      <c r="B2" s="93"/>
+      <c r="C2" s="94"/>
+      <c r="D2" s="99" t="s">
         <v>84</v>
       </c>
-      <c r="E2" s="72"/>
-      <c r="F2" s="71">
+      <c r="E2" s="100"/>
+      <c r="F2" s="99">
         <v>56</v>
       </c>
-      <c r="G2" s="72"/>
-      <c r="H2" s="75">
+      <c r="G2" s="100"/>
+      <c r="H2" s="68">
         <v>45805</v>
       </c>
-      <c r="I2" s="89" t="s">
+      <c r="I2" s="77" t="s">
         <v>83</v>
       </c>
-      <c r="J2" s="90"/>
+      <c r="J2" s="78"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="63"/>
-      <c r="B3" s="64"/>
-      <c r="C3" s="65"/>
-      <c r="D3" s="73"/>
-      <c r="E3" s="65"/>
-      <c r="F3" s="73"/>
-      <c r="G3" s="65"/>
-      <c r="H3" s="76"/>
-      <c r="I3" s="76"/>
-      <c r="J3" s="91"/>
+      <c r="A3" s="92"/>
+      <c r="B3" s="93"/>
+      <c r="C3" s="94"/>
+      <c r="D3" s="101"/>
+      <c r="E3" s="94"/>
+      <c r="F3" s="101"/>
+      <c r="G3" s="94"/>
+      <c r="H3" s="69"/>
+      <c r="I3" s="69"/>
+      <c r="J3" s="79"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="63"/>
-      <c r="B4" s="64"/>
-      <c r="C4" s="65"/>
-      <c r="D4" s="73"/>
-      <c r="E4" s="65"/>
-      <c r="F4" s="73"/>
-      <c r="G4" s="65"/>
-      <c r="H4" s="76"/>
-      <c r="I4" s="76"/>
-      <c r="J4" s="91"/>
+      <c r="A4" s="92"/>
+      <c r="B4" s="93"/>
+      <c r="C4" s="94"/>
+      <c r="D4" s="101"/>
+      <c r="E4" s="94"/>
+      <c r="F4" s="101"/>
+      <c r="G4" s="94"/>
+      <c r="H4" s="69"/>
+      <c r="I4" s="69"/>
+      <c r="J4" s="79"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="164" t="s">
+      <c r="A5" s="161" t="s">
         <v>22</v>
       </c>
-      <c r="B5" s="94"/>
-      <c r="C5" s="70"/>
-      <c r="D5" s="165" t="s">
+      <c r="B5" s="82"/>
+      <c r="C5" s="83"/>
+      <c r="D5" s="162" t="s">
         <v>91</v>
       </c>
-      <c r="E5" s="94"/>
-      <c r="F5" s="94"/>
-      <c r="G5" s="94"/>
-      <c r="H5" s="94"/>
-      <c r="I5" s="94"/>
-      <c r="J5" s="96"/>
+      <c r="E5" s="82"/>
+      <c r="F5" s="82"/>
+      <c r="G5" s="82"/>
+      <c r="H5" s="82"/>
+      <c r="I5" s="82"/>
+      <c r="J5" s="85"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="157" t="s">
+      <c r="A6" s="155" t="s">
         <v>23</v>
       </c>
-      <c r="B6" s="79"/>
-      <c r="C6" s="79"/>
-      <c r="D6" s="79"/>
-      <c r="E6" s="79"/>
-      <c r="F6" s="79"/>
-      <c r="G6" s="79"/>
-      <c r="H6" s="79"/>
-      <c r="I6" s="79"/>
-      <c r="J6" s="82"/>
+      <c r="B6" s="66"/>
+      <c r="C6" s="66"/>
+      <c r="D6" s="66"/>
+      <c r="E6" s="66"/>
+      <c r="F6" s="66"/>
+      <c r="G6" s="66"/>
+      <c r="H6" s="66"/>
+      <c r="I6" s="66"/>
+      <c r="J6" s="67"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="159"/>
-      <c r="B7" s="160"/>
-      <c r="C7" s="160"/>
-      <c r="D7" s="160"/>
-      <c r="E7" s="160"/>
-      <c r="F7" s="160"/>
-      <c r="G7" s="160"/>
-      <c r="H7" s="160"/>
-      <c r="I7" s="160"/>
-      <c r="J7" s="161"/>
+      <c r="A7" s="156"/>
+      <c r="B7" s="157"/>
+      <c r="C7" s="157"/>
+      <c r="D7" s="157"/>
+      <c r="E7" s="157"/>
+      <c r="F7" s="157"/>
+      <c r="G7" s="157"/>
+      <c r="H7" s="157"/>
+      <c r="I7" s="157"/>
+      <c r="J7" s="158"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="63"/>
-      <c r="B8" s="64"/>
-      <c r="C8" s="64"/>
-      <c r="D8" s="64"/>
-      <c r="E8" s="64"/>
-      <c r="F8" s="64"/>
-      <c r="G8" s="64"/>
-      <c r="H8" s="64"/>
-      <c r="I8" s="64"/>
-      <c r="J8" s="162"/>
+      <c r="A8" s="92"/>
+      <c r="B8" s="93"/>
+      <c r="C8" s="93"/>
+      <c r="D8" s="93"/>
+      <c r="E8" s="93"/>
+      <c r="F8" s="93"/>
+      <c r="G8" s="93"/>
+      <c r="H8" s="93"/>
+      <c r="I8" s="93"/>
+      <c r="J8" s="159"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="63"/>
-      <c r="B9" s="64"/>
-      <c r="C9" s="64"/>
-      <c r="D9" s="64"/>
-      <c r="E9" s="64"/>
-      <c r="F9" s="64"/>
-      <c r="G9" s="64"/>
-      <c r="H9" s="64"/>
-      <c r="I9" s="64"/>
-      <c r="J9" s="162"/>
+      <c r="A9" s="92"/>
+      <c r="B9" s="93"/>
+      <c r="C9" s="93"/>
+      <c r="D9" s="93"/>
+      <c r="E9" s="93"/>
+      <c r="F9" s="93"/>
+      <c r="G9" s="93"/>
+      <c r="H9" s="93"/>
+      <c r="I9" s="93"/>
+      <c r="J9" s="159"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="63"/>
-      <c r="B10" s="64"/>
-      <c r="C10" s="64"/>
-      <c r="D10" s="64"/>
-      <c r="E10" s="64"/>
-      <c r="F10" s="64"/>
-      <c r="G10" s="64"/>
-      <c r="H10" s="64"/>
-      <c r="I10" s="64"/>
-      <c r="J10" s="162"/>
+      <c r="A10" s="92"/>
+      <c r="B10" s="93"/>
+      <c r="C10" s="93"/>
+      <c r="D10" s="93"/>
+      <c r="E10" s="93"/>
+      <c r="F10" s="93"/>
+      <c r="G10" s="93"/>
+      <c r="H10" s="93"/>
+      <c r="I10" s="93"/>
+      <c r="J10" s="159"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="63"/>
-      <c r="B11" s="64"/>
-      <c r="C11" s="64"/>
-      <c r="D11" s="64"/>
-      <c r="E11" s="64"/>
-      <c r="F11" s="64"/>
-      <c r="G11" s="64"/>
-      <c r="H11" s="64"/>
-      <c r="I11" s="64"/>
-      <c r="J11" s="162"/>
+      <c r="A11" s="92"/>
+      <c r="B11" s="93"/>
+      <c r="C11" s="93"/>
+      <c r="D11" s="93"/>
+      <c r="E11" s="93"/>
+      <c r="F11" s="93"/>
+      <c r="G11" s="93"/>
+      <c r="H11" s="93"/>
+      <c r="I11" s="93"/>
+      <c r="J11" s="159"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="63"/>
-      <c r="B12" s="64"/>
-      <c r="C12" s="64"/>
-      <c r="D12" s="64"/>
-      <c r="E12" s="64"/>
-      <c r="F12" s="64"/>
-      <c r="G12" s="64"/>
-      <c r="H12" s="64"/>
-      <c r="I12" s="64"/>
-      <c r="J12" s="162"/>
+      <c r="A12" s="92"/>
+      <c r="B12" s="93"/>
+      <c r="C12" s="93"/>
+      <c r="D12" s="93"/>
+      <c r="E12" s="93"/>
+      <c r="F12" s="93"/>
+      <c r="G12" s="93"/>
+      <c r="H12" s="93"/>
+      <c r="I12" s="93"/>
+      <c r="J12" s="159"/>
     </row>
     <row r="13" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A13" s="63"/>
-      <c r="B13" s="64"/>
-      <c r="C13" s="64"/>
-      <c r="D13" s="64"/>
-      <c r="E13" s="64"/>
-      <c r="F13" s="64"/>
-      <c r="G13" s="64"/>
-      <c r="H13" s="64"/>
-      <c r="I13" s="64"/>
-      <c r="J13" s="162"/>
+      <c r="A13" s="92"/>
+      <c r="B13" s="93"/>
+      <c r="C13" s="93"/>
+      <c r="D13" s="93"/>
+      <c r="E13" s="93"/>
+      <c r="F13" s="93"/>
+      <c r="G13" s="93"/>
+      <c r="H13" s="93"/>
+      <c r="I13" s="93"/>
+      <c r="J13" s="159"/>
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A14" s="157" t="s">
+      <c r="A14" s="155" t="s">
         <v>24</v>
       </c>
-      <c r="B14" s="79"/>
-      <c r="C14" s="79"/>
-      <c r="D14" s="79"/>
-      <c r="E14" s="79"/>
-      <c r="F14" s="79"/>
-      <c r="G14" s="79"/>
-      <c r="H14" s="79"/>
-      <c r="I14" s="79"/>
-      <c r="J14" s="82"/>
+      <c r="B14" s="66"/>
+      <c r="C14" s="66"/>
+      <c r="D14" s="66"/>
+      <c r="E14" s="66"/>
+      <c r="F14" s="66"/>
+      <c r="G14" s="66"/>
+      <c r="H14" s="66"/>
+      <c r="I14" s="66"/>
+      <c r="J14" s="67"/>
     </row>
     <row r="15" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A15" s="157" t="s">
+      <c r="A15" s="155" t="s">
         <v>25</v>
       </c>
-      <c r="B15" s="79"/>
-      <c r="C15" s="80"/>
-      <c r="D15" s="88" t="s">
+      <c r="B15" s="66"/>
+      <c r="C15" s="61"/>
+      <c r="D15" s="65" t="s">
         <v>87</v>
       </c>
-      <c r="E15" s="79"/>
-      <c r="F15" s="79"/>
-      <c r="G15" s="79"/>
-      <c r="H15" s="80"/>
+      <c r="E15" s="66"/>
+      <c r="F15" s="66"/>
+      <c r="G15" s="66"/>
+      <c r="H15" s="61"/>
       <c r="I15" s="45" t="s">
         <v>26</v>
       </c>
@@ -13847,11 +15661,11 @@
       </c>
     </row>
     <row r="16" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A16" s="157" t="s">
+      <c r="A16" s="155" t="s">
         <v>27</v>
       </c>
-      <c r="B16" s="79"/>
-      <c r="C16" s="80"/>
+      <c r="B16" s="66"/>
+      <c r="C16" s="61"/>
       <c r="D16" s="45" t="s">
         <v>28</v>
       </c>
@@ -13864,18 +15678,18 @@
       <c r="G16" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="H16" s="158" t="s">
+      <c r="H16" s="163" t="s">
         <v>18</v>
       </c>
-      <c r="I16" s="79"/>
-      <c r="J16" s="82"/>
+      <c r="I16" s="66"/>
+      <c r="J16" s="67"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="155">
+      <c r="A17" s="164">
         <v>1</v>
       </c>
-      <c r="B17" s="79"/>
-      <c r="C17" s="80"/>
+      <c r="B17" s="66"/>
+      <c r="C17" s="61"/>
       <c r="D17" s="47" t="s">
         <v>64</v>
       </c>
@@ -13888,83 +15702,83 @@
       <c r="G17" s="48" t="s">
         <v>89</v>
       </c>
-      <c r="H17" s="88" t="s">
+      <c r="H17" s="65" t="s">
         <v>90</v>
       </c>
-      <c r="I17" s="79"/>
-      <c r="J17" s="82"/>
+      <c r="I17" s="66"/>
+      <c r="J17" s="67"/>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A18" s="155"/>
-      <c r="B18" s="79"/>
-      <c r="C18" s="80"/>
+      <c r="A18" s="164"/>
+      <c r="B18" s="66"/>
+      <c r="C18" s="61"/>
       <c r="D18" s="47"/>
       <c r="E18" s="47"/>
       <c r="F18" s="48"/>
       <c r="G18" s="48"/>
-      <c r="H18" s="88"/>
-      <c r="I18" s="79"/>
-      <c r="J18" s="82"/>
+      <c r="H18" s="65"/>
+      <c r="I18" s="66"/>
+      <c r="J18" s="67"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="155"/>
-      <c r="B19" s="79"/>
-      <c r="C19" s="80"/>
+      <c r="A19" s="164"/>
+      <c r="B19" s="66"/>
+      <c r="C19" s="61"/>
       <c r="D19" s="47"/>
       <c r="E19" s="47"/>
       <c r="F19" s="48"/>
       <c r="G19" s="48"/>
-      <c r="H19" s="88"/>
-      <c r="I19" s="79"/>
-      <c r="J19" s="82"/>
+      <c r="H19" s="65"/>
+      <c r="I19" s="66"/>
+      <c r="J19" s="67"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="155"/>
-      <c r="B20" s="79"/>
-      <c r="C20" s="80"/>
+      <c r="A20" s="164"/>
+      <c r="B20" s="66"/>
+      <c r="C20" s="61"/>
       <c r="D20" s="47"/>
       <c r="E20" s="47"/>
       <c r="F20" s="48"/>
       <c r="G20" s="48"/>
-      <c r="H20" s="88"/>
-      <c r="I20" s="79"/>
-      <c r="J20" s="82"/>
+      <c r="H20" s="65"/>
+      <c r="I20" s="66"/>
+      <c r="J20" s="67"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="155"/>
-      <c r="B21" s="79"/>
-      <c r="C21" s="80"/>
+      <c r="A21" s="164"/>
+      <c r="B21" s="66"/>
+      <c r="C21" s="61"/>
       <c r="D21" s="47"/>
       <c r="E21" s="47"/>
       <c r="F21" s="48"/>
       <c r="G21" s="48"/>
-      <c r="H21" s="88"/>
-      <c r="I21" s="79"/>
-      <c r="J21" s="82"/>
+      <c r="H21" s="65"/>
+      <c r="I21" s="66"/>
+      <c r="J21" s="67"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="155"/>
-      <c r="B22" s="79"/>
-      <c r="C22" s="80"/>
+      <c r="A22" s="164"/>
+      <c r="B22" s="66"/>
+      <c r="C22" s="61"/>
       <c r="D22" s="47"/>
       <c r="E22" s="47"/>
       <c r="F22" s="48"/>
       <c r="G22" s="48"/>
-      <c r="H22" s="88"/>
-      <c r="I22" s="79"/>
-      <c r="J22" s="82"/>
+      <c r="H22" s="65"/>
+      <c r="I22" s="66"/>
+      <c r="J22" s="67"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A23" s="156"/>
-      <c r="B23" s="84"/>
-      <c r="C23" s="85"/>
+      <c r="A23" s="165"/>
+      <c r="B23" s="73"/>
+      <c r="C23" s="74"/>
       <c r="D23" s="49"/>
       <c r="E23" s="49"/>
       <c r="F23" s="50"/>
       <c r="G23" s="50"/>
-      <c r="H23" s="86"/>
-      <c r="I23" s="84"/>
-      <c r="J23" s="87"/>
+      <c r="H23" s="75"/>
+      <c r="I23" s="73"/>
+      <c r="J23" s="76"/>
     </row>
     <row r="24" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="25" spans="1:10" ht="12.75" customHeight="1"/>
@@ -14945,6 +16759,22 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="31">
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="H23:J23"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="H19:J19"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="H20:J20"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="H21:J21"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="H16:J16"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="H18:J18"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="H17:J17"/>
     <mergeCell ref="A14:J14"/>
     <mergeCell ref="A15:C15"/>
     <mergeCell ref="A7:J13"/>
@@ -14960,22 +16790,6 @@
     <mergeCell ref="D5:J5"/>
     <mergeCell ref="A6:J6"/>
     <mergeCell ref="D15:H15"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="H16:J16"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="H17:J17"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="H22:J22"/>
-    <mergeCell ref="A23:C23"/>
-    <mergeCell ref="H23:J23"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="H19:J19"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="H20:J20"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="H21:J21"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>

--- a/Documents/登録機能詳細設計書.xlsx
+++ b/Documents/登録機能詳細設計書.xlsx
@@ -1,46 +1,43 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user47\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\S-47\Documents\project\taskUN\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75E45A11-1E57-4889-B2C0-D3EBA6344D4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09690924-873F-4C22-AC9A-7DFDB2E38A57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="8" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="1" r:id="rId1"/>
     <sheet name="ユースケース記述" sheetId="8" r:id="rId2"/>
     <sheet name="画面遷移図" sheetId="3" r:id="rId3"/>
     <sheet name="詳細クラス図" sheetId="4" r:id="rId4"/>
-    <sheet name="画面設計書-登録フォーム" sheetId="9" r:id="rId5"/>
-    <sheet name="画面設計書-登録完了画面" sheetId="11" r:id="rId6"/>
-    <sheet name="画面設計書-エラー(登録失敗)画面" sheetId="12" r:id="rId7"/>
-    <sheet name="テスト仕様書兼結果報告書" sheetId="6" r:id="rId8"/>
+    <sheet name="Sheet1" sheetId="13" r:id="rId5"/>
+    <sheet name="Sheet2" sheetId="14" r:id="rId6"/>
+    <sheet name="画面設計書-登録フォーム" sheetId="9" r:id="rId7"/>
+    <sheet name="画面設計書-登録完了画面" sheetId="11" r:id="rId8"/>
+    <sheet name="画面設計書-エラー(登録失敗)画面" sheetId="12" r:id="rId9"/>
+    <sheet name="テスト仕様書兼結果報告書" sheetId="6" r:id="rId10"/>
+    <sheet name="JUnitテスト仕様書兼報告書" sheetId="15" r:id="rId11"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId12"/>
+  </externalReferences>
+  <definedNames>
+    <definedName name="範囲１" localSheetId="10">#REF!</definedName>
+    <definedName name="範囲１">#REF!</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="142">
   <si>
     <t>プロジェクト型演習　成果ドキュメント</t>
   </si>
@@ -154,9 +151,6 @@
     <t>テスト対象</t>
   </si>
   <si>
-    <t>ログイン画面</t>
-  </si>
-  <si>
     <t>重要度</t>
   </si>
   <si>
@@ -209,57 +203,10 @@
 </t>
   </si>
   <si>
-    <t>URLアクセス</t>
-  </si>
-  <si>
-    <t>なし</t>
-  </si>
-  <si>
-    <t>ログイン画面へ遷移する</t>
-  </si>
-  <si>
-    <t>○</t>
-  </si>
-  <si>
-    <t>異常系</t>
-  </si>
-  <si>
-    <t>ユーザIDがDBに登録されていないときのログインボタン動作</t>
-  </si>
-  <si>
-    <t>・ユーザID：999999
-・パスワード：root</t>
-  </si>
-  <si>
-    <t>ログインするボタンを押下する</t>
-  </si>
-  <si>
-    <t>エラー画面へ遷移する
-エラーの原因がユーザ名が未入力である旨通知する</t>
-  </si>
-  <si>
     <t>56期</t>
     <rPh sb="2" eb="3">
       <t>キ</t>
     </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <r>
-      <t>http://localhost:8080/ans1101/login.html</t>
-    </r>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color theme="10"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <charset val="128"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>　へアクセスする</t>
-    </r>
     <phoneticPr fontId="8"/>
   </si>
   <si>
@@ -284,7 +231,7 @@
   </si>
   <si>
     <t>ユーザ</t>
-    <phoneticPr fontId="13"/>
+    <phoneticPr fontId="12"/>
   </si>
   <si>
     <t>新規のタスクを登録する</t>
@@ -294,7 +241,7 @@
     <rPh sb="7" eb="9">
       <t>トウロク</t>
     </rPh>
-    <phoneticPr fontId="13"/>
+    <phoneticPr fontId="12"/>
   </si>
   <si>
     <t>新規タスク登録</t>
@@ -304,18 +251,18 @@
     <rPh sb="5" eb="7">
       <t>トウロク</t>
     </rPh>
-    <phoneticPr fontId="13"/>
+    <phoneticPr fontId="12"/>
   </si>
   <si>
     <t>山本（あ）</t>
     <rPh sb="0" eb="2">
       <t>ヤマモト</t>
     </rPh>
-    <phoneticPr fontId="13"/>
+    <phoneticPr fontId="12"/>
   </si>
   <si>
     <t>taskUN</t>
-    <phoneticPr fontId="13"/>
+    <phoneticPr fontId="12"/>
   </si>
   <si>
     <t>クリア</t>
@@ -524,7 +471,7 @@
     <rPh sb="20" eb="22">
       <t>トウロク</t>
     </rPh>
-    <phoneticPr fontId="13"/>
+    <phoneticPr fontId="12"/>
   </si>
   <si>
     <t>担当者のユーザID</t>
@@ -647,7 +594,7 @@
     <rPh sb="136" eb="138">
       <t>センイ</t>
     </rPh>
-    <phoneticPr fontId="13"/>
+    <phoneticPr fontId="12"/>
   </si>
   <si>
     <t>基本・代替フロー：タスクテーブルに入力した情報が追加されタスク登録完了画面に遷移する。
@@ -697,7 +644,7 @@
     <rPh sb="75" eb="77">
       <t>センイ</t>
     </rPh>
-    <phoneticPr fontId="13"/>
+    <phoneticPr fontId="12"/>
   </si>
   <si>
     <t>ログイン済みであること、入力する担当者情報(ユーザID)がユーザマスタに存在していること、
@@ -726,7 +673,7 @@
     <rPh sb="87" eb="89">
       <t>ソンザイ</t>
     </rPh>
-    <phoneticPr fontId="13"/>
+    <phoneticPr fontId="12"/>
   </si>
   <si>
     <t>3.2：備考、期限以外の情報が1つでも入力されていない場合登録は失敗し、
@@ -749,7 +696,339 @@
     <rPh sb="51" eb="53">
       <t>センイ</t>
     </rPh>
-    <phoneticPr fontId="13"/>
+    <phoneticPr fontId="12"/>
+  </si>
+  <si>
+    <t>山本(あ)</t>
+    <rPh sb="0" eb="2">
+      <t>ヤマモト</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>山形</t>
+    <rPh sb="0" eb="2">
+      <t>ヤマガタ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>登録画面</t>
+    <rPh sb="0" eb="4">
+      <t>トウロクガメン</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>メニュー画面から登録画面へページ遷移</t>
+    <rPh sb="4" eb="6">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="8" eb="12">
+      <t>トウロクガメン</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>センイ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>ログイン状態かつデータベースに接続されていること</t>
+    <rPh sb="4" eb="6">
+      <t>ジョウタイ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>セツゾク</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>タスク登録ボタンを押下する</t>
+    <rPh sb="3" eb="5">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>オウカ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>タスク登録画面が表示される</t>
+    <rPh sb="3" eb="7">
+      <t>トウロクガメン</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>ログインされていない状態でタスク登録画面の表示させる</t>
+    <rPh sb="10" eb="12">
+      <t>ジョウタイ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>ログアウト状態であること</t>
+    <rPh sb="5" eb="7">
+      <t>ジョウタイ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>異常系</t>
+    <rPh sb="0" eb="3">
+      <t>イジョウケイ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>http://localhost:8080/taskUN/task-add-form.jsp</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>タスク登録成功画面が表示される</t>
+    <rPh sb="3" eb="5">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>セイコウ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>タスク名が未入力、ユーザーIDが未入力、メモが100文字より多い、ユーザーIDが24文字より多いこと</t>
+    <rPh sb="30" eb="31">
+      <t>オオ</t>
+    </rPh>
+    <rPh sb="46" eb="47">
+      <t>オオ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>タスク登録失敗画面が表示される</t>
+    <rPh sb="3" eb="5">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>シッパイ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>ログインされていませんというメッセージとログイン画面に誘導するリンクが表示される</t>
+    <rPh sb="24" eb="26">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>ユウドウ</t>
+    </rPh>
+    <rPh sb="35" eb="37">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>タスク名、ユーザーID、メモ、期限を入力しタスク登録を行ったときタスク登録成功ページが表示される</t>
+    <rPh sb="3" eb="4">
+      <t>メイ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>キゲン</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="27" eb="28">
+      <t>オコナ</t>
+    </rPh>
+    <rPh sb="35" eb="37">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="37" eb="39">
+      <t>セイコウ</t>
+    </rPh>
+    <rPh sb="43" eb="45">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>タスク名が未入力ではない、ユーザーIDが未入力ではない、メモが100文字以下、ユーザーIDが24文字以下、期限が今日より後であること</t>
+    <rPh sb="53" eb="55">
+      <t>キゲン</t>
+    </rPh>
+    <rPh sb="56" eb="58">
+      <t>キョウ</t>
+    </rPh>
+    <rPh sb="60" eb="61">
+      <t>アト</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>タスク名、ユーザーID、メモ、期限を入力せずタスク登録を行ったときタスク登録失敗ページが表示される</t>
+    <rPh sb="3" eb="4">
+      <t>メイ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>キゲン</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="28" eb="29">
+      <t>オコナ</t>
+    </rPh>
+    <rPh sb="36" eb="38">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="38" eb="40">
+      <t>シッパイ</t>
+    </rPh>
+    <rPh sb="44" eb="46">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>JUnitテスト仕様書兼報告書</t>
+    <rPh sb="8" eb="11">
+      <t>シヨウショ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>ケン</t>
+    </rPh>
+    <rPh sb="12" eb="15">
+      <t>ホウコクショ</t>
+    </rPh>
+    <phoneticPr fontId="16"/>
+  </si>
+  <si>
+    <t>システム名</t>
+    <rPh sb="4" eb="5">
+      <t>メイ</t>
+    </rPh>
+    <phoneticPr fontId="16"/>
+  </si>
+  <si>
+    <t>作成者</t>
+  </si>
+  <si>
+    <t>会社名</t>
+    <rPh sb="0" eb="3">
+      <t>カイシャメイ</t>
+    </rPh>
+    <phoneticPr fontId="16"/>
+  </si>
+  <si>
+    <t>コンサイズ</t>
+    <phoneticPr fontId="16"/>
+  </si>
+  <si>
+    <t>サブシステム名</t>
+    <rPh sb="6" eb="7">
+      <t>メイ</t>
+    </rPh>
+    <phoneticPr fontId="16"/>
+  </si>
+  <si>
+    <t>作成日</t>
+    <rPh sb="0" eb="3">
+      <t>サクセイビ</t>
+    </rPh>
+    <phoneticPr fontId="16"/>
+  </si>
+  <si>
+    <t>実施者</t>
+    <rPh sb="0" eb="2">
+      <t>ジッシ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>シャ</t>
+    </rPh>
+    <phoneticPr fontId="16"/>
+  </si>
+  <si>
+    <t>No</t>
+    <phoneticPr fontId="16"/>
+  </si>
+  <si>
+    <t>分類</t>
+    <rPh sb="0" eb="2">
+      <t>ブンルイ</t>
+    </rPh>
+    <phoneticPr fontId="16"/>
+  </si>
+  <si>
+    <t>テストクラス</t>
+    <phoneticPr fontId="16"/>
+  </si>
+  <si>
+    <t>検証するメソッド</t>
+    <rPh sb="0" eb="2">
+      <t>ケンショウ</t>
+    </rPh>
+    <phoneticPr fontId="16"/>
+  </si>
+  <si>
+    <t>期待する結果</t>
+    <rPh sb="0" eb="2">
+      <t>キタイ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ケッカ</t>
+    </rPh>
+    <phoneticPr fontId="16"/>
+  </si>
+  <si>
+    <t>実施日</t>
+    <rPh sb="0" eb="3">
+      <t>ジッシビ</t>
+    </rPh>
+    <phoneticPr fontId="16"/>
+  </si>
+  <si>
+    <t>備考・特記事項</t>
+    <rPh sb="0" eb="2">
+      <t>ビコウ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>トッキ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ジコウ</t>
+    </rPh>
+    <phoneticPr fontId="16"/>
   </si>
 </sst>
 </file>
@@ -759,7 +1038,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="[$-411]h:mm"/>
   </numFmts>
-  <fonts count="15">
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -831,15 +1110,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="10"/>
-      <name val="Calibri"/>
-      <family val="3"/>
-      <charset val="128"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -868,8 +1138,46 @@
       <charset val="128"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="6"/>
+      <name val="明朝"/>
+      <family val="1"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -882,8 +1190,14 @@
         <bgColor rgb="FFD9D9D9"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-4.9989318521683403E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="57">
+  <borders count="71">
     <border>
       <left/>
       <right/>
@@ -1543,15 +1857,195 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="hair">
+        <color indexed="64"/>
+      </left>
+      <right style="hair">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="hair">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="hair">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="hair">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="hair">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="hair">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="hair">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="hair">
+        <color indexed="64"/>
+      </left>
+      <right style="hair">
+        <color indexed="64"/>
+      </right>
+      <top style="hair">
+        <color indexed="64"/>
+      </top>
+      <bottom style="hair">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="hair">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="hair">
+        <color indexed="64"/>
+      </top>
+      <bottom style="hair">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="hair">
+        <color indexed="64"/>
+      </top>
+      <bottom style="hair">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="hair">
+        <color indexed="64"/>
+      </right>
+      <top style="hair">
+        <color indexed="64"/>
+      </top>
+      <bottom style="hair">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="5">
+  <cellStyleXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="191">
+  <cellXfs count="236">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1648,7 +2142,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="3" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="3" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1660,7 +2154,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="4" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="4" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="45" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1732,6 +2226,93 @@
     <xf numFmtId="14" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1744,7 +2325,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="3" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="3" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1762,9 +2343,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1777,90 +2355,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1939,6 +2433,12 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1951,7 +2451,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="4" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="4" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2011,10 +2511,31 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2023,115 +2544,225 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="5" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="57" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="58" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="59" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="60" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="58" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="59" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="60" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="57" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="5" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="18" fillId="0" borderId="58" xfId="6" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="18" fillId="0" borderId="60" xfId="6" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="57" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="18" fillId="0" borderId="58" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="60" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="61" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="61" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="57" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="62" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="58" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="59" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="60" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="63" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="63" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="63" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="64" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="65" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="66" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="64" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="66" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="67" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="67" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="68" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="69" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="70" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="18" fillId="0" borderId="67" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="67" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="68" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="69" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="70" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="68" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="69" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="70" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="5" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="5">
+  <cellStyles count="7">
     <cellStyle name="ハイパーリンク" xfId="1" builtinId="8"/>
     <cellStyle name="標準" xfId="0" builtinId="0"/>
     <cellStyle name="標準 2" xfId="2" xr:uid="{34200FF7-2CB0-43CE-9E54-7B88C1A054C5}"/>
     <cellStyle name="標準 2 2" xfId="3" xr:uid="{27F598B5-3CA0-4DB2-BB0A-B46AD58157ED}"/>
     <cellStyle name="標準 3" xfId="4" xr:uid="{64517715-78F6-483F-A73E-3584FBD47293}"/>
+    <cellStyle name="標準_生産計画ED書" xfId="5" xr:uid="{DAF71B83-AD85-4492-B576-533DAD2D280C}"/>
+    <cellStyle name="標準_東京理科大DBレイアウト" xfId="6" xr:uid="{691F0CCF-F00E-45EC-8616-60155DDBDDF4}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -2150,23 +2781,23 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>247650</xdr:colOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>38100</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
+      <xdr:rowOff>66675</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>800100</xdr:colOff>
-      <xdr:row>32</xdr:row>
-      <xdr:rowOff>149925</xdr:rowOff>
+      <xdr:colOff>438150</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="図 4">
+        <xdr:cNvPr id="3" name="図 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{99AD4A46-4D34-AC3A-3039-1C89EA6897B3}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1586A722-2167-CF7B-8072-EF5F6BA006D4}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2188,8 +2819,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="247650" y="1028700"/>
-          <a:ext cx="8267700" cy="4569525"/>
+          <a:off x="381000" y="981075"/>
+          <a:ext cx="7772400" cy="4295775"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2205,23 +2836,23 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>276225</xdr:colOff>
-      <xdr:row>4</xdr:row>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>104775</xdr:colOff>
+      <xdr:row>6</xdr:row>
       <xdr:rowOff>47625</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>676275</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>142706</xdr:rowOff>
+      <xdr:colOff>701951</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>34655</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="12" name="図 11">
+        <xdr:cNvPr id="8" name="図 7">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{69D238B2-5C99-887A-D648-A69B560D3ADA}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B9838CC0-B5B0-1F07-496D-861CDE794F22}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2243,8 +2874,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="619125" y="962025"/>
-          <a:ext cx="7772400" cy="4467056"/>
+          <a:off x="104775" y="1285875"/>
+          <a:ext cx="8312426" cy="3225530"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3061,6 +3692,24 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="JUnitテスト仕様書兼報告書"/>
+      <sheetName val="別紙"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
@@ -3367,7 +4016,7 @@
     </row>
     <row r="8" spans="3:16" ht="30" customHeight="1">
       <c r="E8" s="58" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="F8" s="55"/>
       <c r="G8" s="55"/>
@@ -3395,7 +4044,7 @@
     </row>
     <row r="14" spans="3:16" ht="15.75" customHeight="1">
       <c r="G14" s="51" t="s">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="H14" s="53"/>
       <c r="I14" s="59">
@@ -3419,7 +4068,7 @@
     </row>
     <row r="17" spans="7:11" ht="30" customHeight="1">
       <c r="G17" s="54" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="H17" s="55"/>
       <c r="I17" s="55"/>
@@ -4427,6 +5076,3430 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+  <dimension ref="A1:Z1000"/>
+  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
+  <cols>
+    <col min="1" max="6" width="2.85546875" customWidth="1"/>
+    <col min="7" max="20" width="8.140625" customWidth="1"/>
+    <col min="21" max="26" width="8.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:26" ht="18" customHeight="1">
+      <c r="A1" s="190" t="s">
+        <v>32</v>
+      </c>
+      <c r="B1" s="111"/>
+      <c r="C1" s="111"/>
+      <c r="D1" s="111"/>
+      <c r="E1" s="111"/>
+      <c r="F1" s="112"/>
+      <c r="G1" s="118" t="s">
+        <v>4</v>
+      </c>
+      <c r="H1" s="175"/>
+      <c r="I1" s="175"/>
+      <c r="J1" s="119"/>
+      <c r="K1" s="118" t="s">
+        <v>5</v>
+      </c>
+      <c r="L1" s="175"/>
+      <c r="M1" s="175"/>
+      <c r="N1" s="119"/>
+      <c r="O1" s="118" t="s">
+        <v>6</v>
+      </c>
+      <c r="P1" s="119"/>
+      <c r="Q1" s="118" t="s">
+        <v>7</v>
+      </c>
+      <c r="R1" s="119"/>
+      <c r="S1" s="118" t="s">
+        <v>8</v>
+      </c>
+      <c r="T1" s="177"/>
+    </row>
+    <row r="2" spans="1:26" ht="18" customHeight="1">
+      <c r="A2" s="113"/>
+      <c r="B2" s="55"/>
+      <c r="C2" s="55"/>
+      <c r="D2" s="55"/>
+      <c r="E2" s="55"/>
+      <c r="F2" s="114"/>
+      <c r="G2" s="120" t="s">
+        <v>84</v>
+      </c>
+      <c r="H2" s="185"/>
+      <c r="I2" s="185"/>
+      <c r="J2" s="121"/>
+      <c r="K2" s="120" t="s">
+        <v>54</v>
+      </c>
+      <c r="L2" s="185"/>
+      <c r="M2" s="185"/>
+      <c r="N2" s="121"/>
+      <c r="O2" s="186">
+        <v>45821</v>
+      </c>
+      <c r="P2" s="121"/>
+      <c r="Q2" s="120" t="s">
+        <v>110</v>
+      </c>
+      <c r="R2" s="121"/>
+      <c r="S2" s="120"/>
+      <c r="T2" s="187"/>
+    </row>
+    <row r="3" spans="1:26" ht="18" customHeight="1">
+      <c r="A3" s="113"/>
+      <c r="B3" s="55"/>
+      <c r="C3" s="55"/>
+      <c r="D3" s="55"/>
+      <c r="E3" s="55"/>
+      <c r="F3" s="114"/>
+      <c r="G3" s="122"/>
+      <c r="H3" s="55"/>
+      <c r="I3" s="55"/>
+      <c r="J3" s="114"/>
+      <c r="K3" s="122"/>
+      <c r="L3" s="55"/>
+      <c r="M3" s="55"/>
+      <c r="N3" s="114"/>
+      <c r="O3" s="122"/>
+      <c r="P3" s="114"/>
+      <c r="Q3" s="122"/>
+      <c r="R3" s="114"/>
+      <c r="S3" s="122"/>
+      <c r="T3" s="188"/>
+    </row>
+    <row r="4" spans="1:26" ht="18" customHeight="1">
+      <c r="A4" s="115"/>
+      <c r="B4" s="116"/>
+      <c r="C4" s="116"/>
+      <c r="D4" s="116"/>
+      <c r="E4" s="116"/>
+      <c r="F4" s="117"/>
+      <c r="G4" s="123"/>
+      <c r="H4" s="116"/>
+      <c r="I4" s="116"/>
+      <c r="J4" s="117"/>
+      <c r="K4" s="123"/>
+      <c r="L4" s="116"/>
+      <c r="M4" s="116"/>
+      <c r="N4" s="117"/>
+      <c r="O4" s="123"/>
+      <c r="P4" s="117"/>
+      <c r="Q4" s="123"/>
+      <c r="R4" s="117"/>
+      <c r="S4" s="123"/>
+      <c r="T4" s="189"/>
+    </row>
+    <row r="5" spans="1:26" ht="18" customHeight="1">
+      <c r="A5" s="174" t="s">
+        <v>33</v>
+      </c>
+      <c r="B5" s="175"/>
+      <c r="C5" s="175"/>
+      <c r="D5" s="175"/>
+      <c r="E5" s="175"/>
+      <c r="F5" s="119"/>
+      <c r="G5" s="176" t="s">
+        <v>34</v>
+      </c>
+      <c r="H5" s="175"/>
+      <c r="I5" s="175"/>
+      <c r="J5" s="175"/>
+      <c r="K5" s="175"/>
+      <c r="L5" s="175"/>
+      <c r="M5" s="175"/>
+      <c r="N5" s="175"/>
+      <c r="O5" s="175"/>
+      <c r="P5" s="175"/>
+      <c r="Q5" s="175"/>
+      <c r="R5" s="175"/>
+      <c r="S5" s="175"/>
+      <c r="T5" s="177"/>
+    </row>
+    <row r="6" spans="1:26" ht="18" customHeight="1">
+      <c r="A6" s="178" t="s">
+        <v>35</v>
+      </c>
+      <c r="B6" s="52"/>
+      <c r="C6" s="52"/>
+      <c r="D6" s="52"/>
+      <c r="E6" s="52"/>
+      <c r="F6" s="53"/>
+      <c r="G6" s="179" t="s">
+        <v>19</v>
+      </c>
+      <c r="H6" s="52"/>
+      <c r="I6" s="52"/>
+      <c r="J6" s="52"/>
+      <c r="K6" s="52"/>
+      <c r="L6" s="52"/>
+      <c r="M6" s="52"/>
+      <c r="N6" s="52"/>
+      <c r="O6" s="52"/>
+      <c r="P6" s="52"/>
+      <c r="Q6" s="52"/>
+      <c r="R6" s="52"/>
+      <c r="S6" s="52"/>
+      <c r="T6" s="180"/>
+    </row>
+    <row r="7" spans="1:26" ht="18" customHeight="1">
+      <c r="A7" s="178" t="s">
+        <v>36</v>
+      </c>
+      <c r="B7" s="52"/>
+      <c r="C7" s="52"/>
+      <c r="D7" s="52"/>
+      <c r="E7" s="52"/>
+      <c r="F7" s="53"/>
+      <c r="G7" s="179" t="s">
+        <v>111</v>
+      </c>
+      <c r="H7" s="52"/>
+      <c r="I7" s="52"/>
+      <c r="J7" s="52"/>
+      <c r="K7" s="52"/>
+      <c r="L7" s="52"/>
+      <c r="M7" s="52"/>
+      <c r="N7" s="52"/>
+      <c r="O7" s="52"/>
+      <c r="P7" s="52"/>
+      <c r="Q7" s="52"/>
+      <c r="R7" s="52"/>
+      <c r="S7" s="52"/>
+      <c r="T7" s="180"/>
+    </row>
+    <row r="8" spans="1:26" ht="7.5" customHeight="1">
+      <c r="A8" s="7"/>
+      <c r="B8" s="8"/>
+      <c r="C8" s="8"/>
+      <c r="D8" s="8"/>
+      <c r="E8" s="8"/>
+      <c r="F8" s="8"/>
+      <c r="G8" s="8"/>
+      <c r="H8" s="8"/>
+      <c r="I8" s="8"/>
+      <c r="J8" s="8"/>
+      <c r="K8" s="8"/>
+      <c r="L8" s="8"/>
+      <c r="M8" s="8"/>
+      <c r="N8" s="8"/>
+      <c r="O8" s="8"/>
+      <c r="P8" s="8"/>
+      <c r="Q8" s="8"/>
+      <c r="R8" s="8"/>
+      <c r="S8" s="8"/>
+      <c r="T8" s="9"/>
+    </row>
+    <row r="9" spans="1:26" ht="12.75" customHeight="1">
+      <c r="A9" s="15"/>
+      <c r="B9" s="16"/>
+      <c r="C9" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="D9" s="18"/>
+      <c r="E9" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="F9" s="18"/>
+      <c r="G9" s="19"/>
+      <c r="H9" s="18"/>
+      <c r="I9" s="18"/>
+      <c r="J9" s="18"/>
+      <c r="K9" s="19"/>
+      <c r="L9" s="16"/>
+      <c r="M9" s="16"/>
+      <c r="N9" s="16"/>
+      <c r="O9" s="16"/>
+      <c r="P9" s="16"/>
+      <c r="Q9" s="16"/>
+      <c r="R9" s="16"/>
+      <c r="S9" s="16"/>
+      <c r="T9" s="20"/>
+      <c r="U9" s="16"/>
+      <c r="V9" s="16"/>
+      <c r="W9" s="16"/>
+      <c r="X9" s="16"/>
+      <c r="Y9" s="16"/>
+      <c r="Z9" s="16"/>
+    </row>
+    <row r="10" spans="1:26" ht="12.75" customHeight="1">
+      <c r="A10" s="15"/>
+      <c r="B10" s="16"/>
+      <c r="C10" s="21"/>
+      <c r="D10" s="16"/>
+      <c r="E10" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="F10" s="16"/>
+      <c r="G10" s="22"/>
+      <c r="H10" s="16"/>
+      <c r="I10" s="16"/>
+      <c r="J10" s="16"/>
+      <c r="K10" s="22"/>
+      <c r="L10" s="16"/>
+      <c r="M10" s="16"/>
+      <c r="N10" s="16"/>
+      <c r="O10" s="16"/>
+      <c r="P10" s="16"/>
+      <c r="Q10" s="16"/>
+      <c r="R10" s="16"/>
+      <c r="S10" s="16"/>
+      <c r="T10" s="20"/>
+      <c r="U10" s="16"/>
+      <c r="V10" s="16"/>
+      <c r="W10" s="16"/>
+      <c r="X10" s="16"/>
+      <c r="Y10" s="16"/>
+      <c r="Z10" s="16"/>
+    </row>
+    <row r="11" spans="1:26" ht="12.75" customHeight="1">
+      <c r="A11" s="15"/>
+      <c r="B11" s="16"/>
+      <c r="C11" s="21"/>
+      <c r="D11" s="16"/>
+      <c r="E11" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="F11" s="16"/>
+      <c r="G11" s="22"/>
+      <c r="H11" s="16"/>
+      <c r="I11" s="16"/>
+      <c r="J11" s="16"/>
+      <c r="K11" s="22"/>
+      <c r="L11" s="16"/>
+      <c r="M11" s="16"/>
+      <c r="N11" s="16"/>
+      <c r="O11" s="16"/>
+      <c r="P11" s="16"/>
+      <c r="Q11" s="16"/>
+      <c r="R11" s="16"/>
+      <c r="S11" s="16"/>
+      <c r="T11" s="20"/>
+      <c r="U11" s="16"/>
+      <c r="V11" s="16"/>
+      <c r="W11" s="16"/>
+      <c r="X11" s="16"/>
+      <c r="Y11" s="16"/>
+      <c r="Z11" s="16"/>
+    </row>
+    <row r="12" spans="1:26" ht="12.75" customHeight="1">
+      <c r="A12" s="15"/>
+      <c r="B12" s="16"/>
+      <c r="C12" s="21"/>
+      <c r="D12" s="16"/>
+      <c r="E12" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="F12" s="16"/>
+      <c r="G12" s="22"/>
+      <c r="H12" s="16"/>
+      <c r="I12" s="16"/>
+      <c r="J12" s="16"/>
+      <c r="K12" s="22"/>
+      <c r="L12" s="16"/>
+      <c r="M12" s="16"/>
+      <c r="N12" s="16"/>
+      <c r="O12" s="16"/>
+      <c r="P12" s="16"/>
+      <c r="Q12" s="16"/>
+      <c r="R12" s="16"/>
+      <c r="S12" s="16"/>
+      <c r="T12" s="20"/>
+      <c r="U12" s="16"/>
+      <c r="V12" s="16"/>
+      <c r="W12" s="16"/>
+      <c r="X12" s="16"/>
+      <c r="Y12" s="16"/>
+      <c r="Z12" s="16"/>
+    </row>
+    <row r="13" spans="1:26" ht="12.75" customHeight="1">
+      <c r="A13" s="15"/>
+      <c r="B13" s="16"/>
+      <c r="C13" s="23"/>
+      <c r="D13" s="24"/>
+      <c r="E13" s="24" t="s">
+        <v>42</v>
+      </c>
+      <c r="F13" s="24"/>
+      <c r="G13" s="25"/>
+      <c r="H13" s="24"/>
+      <c r="I13" s="24"/>
+      <c r="J13" s="24"/>
+      <c r="K13" s="25"/>
+      <c r="L13" s="16"/>
+      <c r="M13" s="16"/>
+      <c r="N13" s="16"/>
+      <c r="O13" s="16"/>
+      <c r="P13" s="16"/>
+      <c r="Q13" s="16"/>
+      <c r="R13" s="16"/>
+      <c r="S13" s="16"/>
+      <c r="T13" s="20"/>
+      <c r="U13" s="16"/>
+      <c r="V13" s="16"/>
+      <c r="W13" s="16"/>
+      <c r="X13" s="16"/>
+      <c r="Y13" s="16"/>
+      <c r="Z13" s="16"/>
+    </row>
+    <row r="14" spans="1:26" ht="8.25" customHeight="1">
+      <c r="A14" s="7"/>
+      <c r="B14" s="8"/>
+      <c r="C14" s="8"/>
+      <c r="D14" s="8"/>
+      <c r="E14" s="8"/>
+      <c r="F14" s="8"/>
+      <c r="G14" s="8"/>
+      <c r="H14" s="8"/>
+      <c r="I14" s="8"/>
+      <c r="J14" s="8"/>
+      <c r="K14" s="8"/>
+      <c r="L14" s="8"/>
+      <c r="M14" s="8"/>
+      <c r="N14" s="8"/>
+      <c r="O14" s="8"/>
+      <c r="P14" s="8"/>
+      <c r="Q14" s="8"/>
+      <c r="R14" s="8"/>
+      <c r="S14" s="8"/>
+      <c r="T14" s="9"/>
+    </row>
+    <row r="15" spans="1:26" ht="18.75" customHeight="1">
+      <c r="A15" s="178" t="s">
+        <v>43</v>
+      </c>
+      <c r="B15" s="53"/>
+      <c r="C15" s="184" t="s">
+        <v>37</v>
+      </c>
+      <c r="D15" s="53"/>
+      <c r="E15" s="182" t="s">
+        <v>44</v>
+      </c>
+      <c r="F15" s="53"/>
+      <c r="G15" s="182" t="s">
+        <v>45</v>
+      </c>
+      <c r="H15" s="52"/>
+      <c r="I15" s="53"/>
+      <c r="J15" s="182" t="s">
+        <v>46</v>
+      </c>
+      <c r="K15" s="53"/>
+      <c r="L15" s="182" t="s">
+        <v>47</v>
+      </c>
+      <c r="M15" s="52"/>
+      <c r="N15" s="53"/>
+      <c r="O15" s="182" t="s">
+        <v>48</v>
+      </c>
+      <c r="P15" s="52"/>
+      <c r="Q15" s="53"/>
+      <c r="R15" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="S15" s="14" t="s">
+        <v>50</v>
+      </c>
+      <c r="T15" s="26" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" ht="48" customHeight="1">
+      <c r="A16" s="166">
+        <v>1</v>
+      </c>
+      <c r="B16" s="53"/>
+      <c r="C16" s="167" t="s">
+        <v>52</v>
+      </c>
+      <c r="D16" s="53"/>
+      <c r="E16" s="167" t="s">
+        <v>53</v>
+      </c>
+      <c r="F16" s="53"/>
+      <c r="G16" s="181" t="s">
+        <v>112</v>
+      </c>
+      <c r="H16" s="52"/>
+      <c r="I16" s="53"/>
+      <c r="J16" s="192" t="s">
+        <v>113</v>
+      </c>
+      <c r="K16" s="61"/>
+      <c r="L16" s="171" t="s">
+        <v>114</v>
+      </c>
+      <c r="M16" s="52"/>
+      <c r="N16" s="53"/>
+      <c r="O16" s="171" t="s">
+        <v>115</v>
+      </c>
+      <c r="P16" s="52"/>
+      <c r="Q16" s="53"/>
+      <c r="R16" s="27"/>
+      <c r="S16" s="27"/>
+      <c r="T16" s="28"/>
+      <c r="U16" s="29"/>
+      <c r="V16" s="29"/>
+      <c r="W16" s="29"/>
+      <c r="X16" s="29"/>
+      <c r="Y16" s="29"/>
+      <c r="Z16" s="29"/>
+    </row>
+    <row r="17" spans="1:26" ht="51" customHeight="1">
+      <c r="A17" s="166">
+        <v>2</v>
+      </c>
+      <c r="B17" s="53"/>
+      <c r="C17" s="167" t="s">
+        <v>52</v>
+      </c>
+      <c r="D17" s="53"/>
+      <c r="E17" s="167" t="s">
+        <v>118</v>
+      </c>
+      <c r="F17" s="53"/>
+      <c r="G17" s="181" t="s">
+        <v>116</v>
+      </c>
+      <c r="H17" s="52"/>
+      <c r="I17" s="53"/>
+      <c r="J17" s="181" t="s">
+        <v>117</v>
+      </c>
+      <c r="K17" s="53"/>
+      <c r="L17" s="183" t="s">
+        <v>119</v>
+      </c>
+      <c r="M17" s="52"/>
+      <c r="N17" s="53"/>
+      <c r="O17" s="171" t="s">
+        <v>123</v>
+      </c>
+      <c r="P17" s="52"/>
+      <c r="Q17" s="53"/>
+      <c r="R17" s="27"/>
+      <c r="S17" s="27"/>
+      <c r="T17" s="28"/>
+      <c r="U17" s="29"/>
+      <c r="V17" s="29"/>
+      <c r="W17" s="29"/>
+      <c r="X17" s="29"/>
+      <c r="Y17" s="29"/>
+      <c r="Z17" s="29"/>
+    </row>
+    <row r="18" spans="1:26" ht="99.75" customHeight="1">
+      <c r="A18" s="166">
+        <v>3</v>
+      </c>
+      <c r="B18" s="53"/>
+      <c r="C18" s="167" t="s">
+        <v>52</v>
+      </c>
+      <c r="D18" s="53"/>
+      <c r="E18" s="167" t="s">
+        <v>53</v>
+      </c>
+      <c r="F18" s="53"/>
+      <c r="G18" s="181" t="s">
+        <v>124</v>
+      </c>
+      <c r="H18" s="52"/>
+      <c r="I18" s="53"/>
+      <c r="J18" s="181" t="s">
+        <v>125</v>
+      </c>
+      <c r="K18" s="53"/>
+      <c r="L18" s="171" t="s">
+        <v>114</v>
+      </c>
+      <c r="M18" s="52"/>
+      <c r="N18" s="53"/>
+      <c r="O18" s="171" t="s">
+        <v>120</v>
+      </c>
+      <c r="P18" s="52"/>
+      <c r="Q18" s="53"/>
+      <c r="R18" s="27"/>
+      <c r="S18" s="27"/>
+      <c r="T18" s="28"/>
+      <c r="U18" s="29"/>
+      <c r="V18" s="29"/>
+      <c r="W18" s="29"/>
+      <c r="X18" s="29"/>
+      <c r="Y18" s="29"/>
+      <c r="Z18" s="29"/>
+    </row>
+    <row r="19" spans="1:26" ht="94.5" customHeight="1">
+      <c r="A19" s="166">
+        <v>4</v>
+      </c>
+      <c r="B19" s="53"/>
+      <c r="C19" s="167" t="s">
+        <v>52</v>
+      </c>
+      <c r="D19" s="53"/>
+      <c r="E19" s="167" t="s">
+        <v>118</v>
+      </c>
+      <c r="F19" s="53"/>
+      <c r="G19" s="181" t="s">
+        <v>126</v>
+      </c>
+      <c r="H19" s="52"/>
+      <c r="I19" s="53"/>
+      <c r="J19" s="181" t="s">
+        <v>121</v>
+      </c>
+      <c r="K19" s="53"/>
+      <c r="L19" s="171" t="s">
+        <v>114</v>
+      </c>
+      <c r="M19" s="52"/>
+      <c r="N19" s="53"/>
+      <c r="O19" s="171" t="s">
+        <v>122</v>
+      </c>
+      <c r="P19" s="52"/>
+      <c r="Q19" s="53"/>
+      <c r="R19" s="27"/>
+      <c r="S19" s="27"/>
+      <c r="T19" s="28"/>
+      <c r="U19" s="29"/>
+      <c r="V19" s="29"/>
+      <c r="W19" s="29"/>
+      <c r="X19" s="29"/>
+      <c r="Y19" s="29"/>
+      <c r="Z19" s="29"/>
+    </row>
+    <row r="20" spans="1:26" ht="61.5" customHeight="1">
+      <c r="A20" s="166"/>
+      <c r="B20" s="53"/>
+      <c r="C20" s="167"/>
+      <c r="D20" s="53"/>
+      <c r="E20" s="167"/>
+      <c r="F20" s="53"/>
+      <c r="G20" s="181"/>
+      <c r="H20" s="52"/>
+      <c r="I20" s="53"/>
+      <c r="J20" s="181"/>
+      <c r="K20" s="53"/>
+      <c r="L20" s="171"/>
+      <c r="M20" s="52"/>
+      <c r="N20" s="53"/>
+      <c r="O20" s="171"/>
+      <c r="P20" s="52"/>
+      <c r="Q20" s="53"/>
+      <c r="R20" s="27"/>
+      <c r="S20" s="27"/>
+      <c r="T20" s="28"/>
+      <c r="U20" s="29"/>
+      <c r="V20" s="29"/>
+      <c r="W20" s="29"/>
+      <c r="X20" s="29"/>
+      <c r="Y20" s="29"/>
+      <c r="Z20" s="29"/>
+    </row>
+    <row r="21" spans="1:26" ht="60.75" customHeight="1">
+      <c r="A21" s="166"/>
+      <c r="B21" s="53"/>
+      <c r="C21" s="167"/>
+      <c r="D21" s="53"/>
+      <c r="E21" s="167"/>
+      <c r="F21" s="53"/>
+      <c r="G21" s="181"/>
+      <c r="H21" s="52"/>
+      <c r="I21" s="53"/>
+      <c r="J21" s="181"/>
+      <c r="K21" s="53"/>
+      <c r="L21" s="171"/>
+      <c r="M21" s="52"/>
+      <c r="N21" s="53"/>
+      <c r="O21" s="171"/>
+      <c r="P21" s="52"/>
+      <c r="Q21" s="53"/>
+      <c r="R21" s="27"/>
+      <c r="S21" s="27"/>
+      <c r="T21" s="28"/>
+      <c r="U21" s="29"/>
+      <c r="V21" s="29"/>
+      <c r="W21" s="29"/>
+      <c r="X21" s="29"/>
+      <c r="Y21" s="29"/>
+      <c r="Z21" s="29"/>
+    </row>
+    <row r="22" spans="1:26" ht="12.75" customHeight="1">
+      <c r="A22" s="166"/>
+      <c r="B22" s="53"/>
+      <c r="C22" s="167"/>
+      <c r="D22" s="53"/>
+      <c r="E22" s="167"/>
+      <c r="F22" s="53"/>
+      <c r="G22" s="181"/>
+      <c r="H22" s="52"/>
+      <c r="I22" s="53"/>
+      <c r="J22" s="181"/>
+      <c r="K22" s="53"/>
+      <c r="L22" s="171"/>
+      <c r="M22" s="52"/>
+      <c r="N22" s="53"/>
+      <c r="O22" s="171"/>
+      <c r="P22" s="52"/>
+      <c r="Q22" s="53"/>
+      <c r="R22" s="27"/>
+      <c r="S22" s="27"/>
+      <c r="T22" s="28"/>
+      <c r="U22" s="29"/>
+      <c r="V22" s="29"/>
+      <c r="W22" s="29"/>
+      <c r="X22" s="29"/>
+      <c r="Y22" s="29"/>
+      <c r="Z22" s="29"/>
+    </row>
+    <row r="23" spans="1:26" ht="12.75" customHeight="1">
+      <c r="A23" s="166"/>
+      <c r="B23" s="53"/>
+      <c r="C23" s="167"/>
+      <c r="D23" s="53"/>
+      <c r="E23" s="167"/>
+      <c r="F23" s="53"/>
+      <c r="G23" s="181"/>
+      <c r="H23" s="52"/>
+      <c r="I23" s="53"/>
+      <c r="J23" s="181"/>
+      <c r="K23" s="53"/>
+      <c r="L23" s="171"/>
+      <c r="M23" s="52"/>
+      <c r="N23" s="53"/>
+      <c r="O23" s="171"/>
+      <c r="P23" s="52"/>
+      <c r="Q23" s="53"/>
+      <c r="R23" s="27"/>
+      <c r="S23" s="27"/>
+      <c r="T23" s="28"/>
+      <c r="U23" s="29"/>
+      <c r="V23" s="29"/>
+      <c r="W23" s="29"/>
+      <c r="X23" s="29"/>
+      <c r="Y23" s="29"/>
+      <c r="Z23" s="29"/>
+    </row>
+    <row r="24" spans="1:26" ht="12.75" customHeight="1">
+      <c r="A24" s="166"/>
+      <c r="B24" s="53"/>
+      <c r="C24" s="167"/>
+      <c r="D24" s="53"/>
+      <c r="E24" s="167"/>
+      <c r="F24" s="53"/>
+      <c r="G24" s="181"/>
+      <c r="H24" s="52"/>
+      <c r="I24" s="53"/>
+      <c r="J24" s="181"/>
+      <c r="K24" s="53"/>
+      <c r="L24" s="171"/>
+      <c r="M24" s="52"/>
+      <c r="N24" s="53"/>
+      <c r="O24" s="171"/>
+      <c r="P24" s="52"/>
+      <c r="Q24" s="53"/>
+      <c r="R24" s="27"/>
+      <c r="S24" s="27"/>
+      <c r="T24" s="28"/>
+      <c r="U24" s="29"/>
+      <c r="V24" s="29"/>
+      <c r="W24" s="29"/>
+      <c r="X24" s="29"/>
+      <c r="Y24" s="29"/>
+      <c r="Z24" s="29"/>
+    </row>
+    <row r="25" spans="1:26" ht="12.75" customHeight="1">
+      <c r="A25" s="166"/>
+      <c r="B25" s="53"/>
+      <c r="C25" s="167"/>
+      <c r="D25" s="53"/>
+      <c r="E25" s="167"/>
+      <c r="F25" s="53"/>
+      <c r="G25" s="181"/>
+      <c r="H25" s="52"/>
+      <c r="I25" s="53"/>
+      <c r="J25" s="181"/>
+      <c r="K25" s="53"/>
+      <c r="L25" s="171"/>
+      <c r="M25" s="52"/>
+      <c r="N25" s="53"/>
+      <c r="O25" s="171"/>
+      <c r="P25" s="52"/>
+      <c r="Q25" s="53"/>
+      <c r="R25" s="27"/>
+      <c r="S25" s="27"/>
+      <c r="T25" s="28"/>
+      <c r="U25" s="29"/>
+      <c r="V25" s="29"/>
+      <c r="W25" s="29"/>
+      <c r="X25" s="29"/>
+      <c r="Y25" s="29"/>
+      <c r="Z25" s="29"/>
+    </row>
+    <row r="26" spans="1:26" ht="12.75" customHeight="1">
+      <c r="A26" s="166"/>
+      <c r="B26" s="53"/>
+      <c r="C26" s="167"/>
+      <c r="D26" s="53"/>
+      <c r="E26" s="167"/>
+      <c r="F26" s="53"/>
+      <c r="G26" s="181"/>
+      <c r="H26" s="52"/>
+      <c r="I26" s="53"/>
+      <c r="J26" s="181"/>
+      <c r="K26" s="53"/>
+      <c r="L26" s="171"/>
+      <c r="M26" s="52"/>
+      <c r="N26" s="53"/>
+      <c r="O26" s="171"/>
+      <c r="P26" s="52"/>
+      <c r="Q26" s="53"/>
+      <c r="R26" s="27"/>
+      <c r="S26" s="27"/>
+      <c r="T26" s="28"/>
+      <c r="U26" s="29"/>
+      <c r="V26" s="29"/>
+      <c r="W26" s="29"/>
+      <c r="X26" s="29"/>
+      <c r="Y26" s="29"/>
+      <c r="Z26" s="29"/>
+    </row>
+    <row r="27" spans="1:26" ht="12.75" customHeight="1">
+      <c r="A27" s="166"/>
+      <c r="B27" s="53"/>
+      <c r="C27" s="167"/>
+      <c r="D27" s="53"/>
+      <c r="E27" s="167"/>
+      <c r="F27" s="53"/>
+      <c r="G27" s="181"/>
+      <c r="H27" s="52"/>
+      <c r="I27" s="53"/>
+      <c r="J27" s="181"/>
+      <c r="K27" s="53"/>
+      <c r="L27" s="171"/>
+      <c r="M27" s="52"/>
+      <c r="N27" s="53"/>
+      <c r="O27" s="171"/>
+      <c r="P27" s="52"/>
+      <c r="Q27" s="53"/>
+      <c r="R27" s="27"/>
+      <c r="S27" s="27"/>
+      <c r="T27" s="28"/>
+      <c r="U27" s="29"/>
+      <c r="V27" s="29"/>
+      <c r="W27" s="29"/>
+      <c r="X27" s="29"/>
+      <c r="Y27" s="29"/>
+      <c r="Z27" s="29"/>
+    </row>
+    <row r="28" spans="1:26" ht="12.75" customHeight="1">
+      <c r="A28" s="166"/>
+      <c r="B28" s="53"/>
+      <c r="C28" s="167"/>
+      <c r="D28" s="53"/>
+      <c r="E28" s="167"/>
+      <c r="F28" s="53"/>
+      <c r="G28" s="181"/>
+      <c r="H28" s="52"/>
+      <c r="I28" s="53"/>
+      <c r="J28" s="181"/>
+      <c r="K28" s="53"/>
+      <c r="L28" s="171"/>
+      <c r="M28" s="52"/>
+      <c r="N28" s="53"/>
+      <c r="O28" s="171"/>
+      <c r="P28" s="52"/>
+      <c r="Q28" s="53"/>
+      <c r="R28" s="27"/>
+      <c r="S28" s="27"/>
+      <c r="T28" s="28"/>
+      <c r="U28" s="29"/>
+      <c r="V28" s="29"/>
+      <c r="W28" s="29"/>
+      <c r="X28" s="29"/>
+      <c r="Y28" s="29"/>
+      <c r="Z28" s="29"/>
+    </row>
+    <row r="29" spans="1:26" ht="12.75" customHeight="1">
+      <c r="A29" s="166"/>
+      <c r="B29" s="53"/>
+      <c r="C29" s="167"/>
+      <c r="D29" s="53"/>
+      <c r="E29" s="167"/>
+      <c r="F29" s="53"/>
+      <c r="G29" s="181"/>
+      <c r="H29" s="52"/>
+      <c r="I29" s="53"/>
+      <c r="J29" s="181"/>
+      <c r="K29" s="53"/>
+      <c r="L29" s="171"/>
+      <c r="M29" s="52"/>
+      <c r="N29" s="53"/>
+      <c r="O29" s="171"/>
+      <c r="P29" s="52"/>
+      <c r="Q29" s="53"/>
+      <c r="R29" s="27"/>
+      <c r="S29" s="27"/>
+      <c r="T29" s="28"/>
+      <c r="U29" s="29"/>
+      <c r="V29" s="29"/>
+      <c r="W29" s="29"/>
+      <c r="X29" s="29"/>
+      <c r="Y29" s="29"/>
+      <c r="Z29" s="29"/>
+    </row>
+    <row r="30" spans="1:26" ht="12.75" customHeight="1">
+      <c r="A30" s="166"/>
+      <c r="B30" s="53"/>
+      <c r="C30" s="167"/>
+      <c r="D30" s="53"/>
+      <c r="E30" s="167"/>
+      <c r="F30" s="53"/>
+      <c r="G30" s="181"/>
+      <c r="H30" s="52"/>
+      <c r="I30" s="53"/>
+      <c r="J30" s="181"/>
+      <c r="K30" s="53"/>
+      <c r="L30" s="171"/>
+      <c r="M30" s="52"/>
+      <c r="N30" s="53"/>
+      <c r="O30" s="171"/>
+      <c r="P30" s="52"/>
+      <c r="Q30" s="53"/>
+      <c r="R30" s="27"/>
+      <c r="S30" s="27"/>
+      <c r="T30" s="28"/>
+      <c r="U30" s="29"/>
+      <c r="V30" s="29"/>
+      <c r="W30" s="29"/>
+      <c r="X30" s="29"/>
+      <c r="Y30" s="29"/>
+      <c r="Z30" s="29"/>
+    </row>
+    <row r="31" spans="1:26" ht="12.75" customHeight="1">
+      <c r="A31" s="168"/>
+      <c r="B31" s="169"/>
+      <c r="C31" s="170"/>
+      <c r="D31" s="169"/>
+      <c r="E31" s="170"/>
+      <c r="F31" s="169"/>
+      <c r="G31" s="191"/>
+      <c r="H31" s="173"/>
+      <c r="I31" s="169"/>
+      <c r="J31" s="191"/>
+      <c r="K31" s="169"/>
+      <c r="L31" s="172"/>
+      <c r="M31" s="173"/>
+      <c r="N31" s="169"/>
+      <c r="O31" s="172"/>
+      <c r="P31" s="173"/>
+      <c r="Q31" s="169"/>
+      <c r="R31" s="30"/>
+      <c r="S31" s="30"/>
+      <c r="T31" s="31"/>
+      <c r="U31" s="29"/>
+      <c r="V31" s="29"/>
+      <c r="W31" s="29"/>
+      <c r="X31" s="29"/>
+      <c r="Y31" s="29"/>
+      <c r="Z31" s="29"/>
+    </row>
+    <row r="32" spans="1:26" ht="12.75" customHeight="1">
+      <c r="D32" s="3"/>
+      <c r="E32" s="3"/>
+      <c r="F32" s="3"/>
+      <c r="G32" s="3"/>
+      <c r="H32" s="3"/>
+      <c r="I32" s="3"/>
+      <c r="J32" s="3"/>
+    </row>
+    <row r="33" spans="4:10" ht="12.75" customHeight="1">
+      <c r="D33" s="3"/>
+      <c r="E33" s="3"/>
+      <c r="F33" s="3"/>
+      <c r="G33" s="3"/>
+      <c r="H33" s="3"/>
+      <c r="I33" s="3"/>
+      <c r="J33" s="3"/>
+    </row>
+    <row r="34" spans="4:10" ht="12.75" customHeight="1"/>
+    <row r="35" spans="4:10" ht="12.75" customHeight="1"/>
+    <row r="36" spans="4:10" ht="12.75" customHeight="1"/>
+    <row r="37" spans="4:10" ht="12.75" customHeight="1"/>
+    <row r="38" spans="4:10" ht="12.75" customHeight="1"/>
+    <row r="39" spans="4:10" ht="12.75" customHeight="1"/>
+    <row r="40" spans="4:10" ht="12.75" customHeight="1"/>
+    <row r="41" spans="4:10" ht="12.75" customHeight="1"/>
+    <row r="42" spans="4:10" ht="12.75" customHeight="1"/>
+    <row r="43" spans="4:10" ht="12.75" customHeight="1"/>
+    <row r="44" spans="4:10" ht="12.75" customHeight="1"/>
+    <row r="45" spans="4:10" ht="12.75" customHeight="1"/>
+    <row r="46" spans="4:10" ht="12.75" customHeight="1"/>
+    <row r="47" spans="4:10" ht="12.75" customHeight="1"/>
+    <row r="48" spans="4:10" ht="12.75" customHeight="1"/>
+    <row r="49" ht="12.75" customHeight="1"/>
+    <row r="50" ht="12.75" customHeight="1"/>
+    <row r="51" ht="12.75" customHeight="1"/>
+    <row r="52" ht="12.75" customHeight="1"/>
+    <row r="53" ht="12.75" customHeight="1"/>
+    <row r="54" ht="12.75" customHeight="1"/>
+    <row r="55" ht="12.75" customHeight="1"/>
+    <row r="56" ht="12.75" customHeight="1"/>
+    <row r="57" ht="12.75" customHeight="1"/>
+    <row r="58" ht="12.75" customHeight="1"/>
+    <row r="59" ht="12.75" customHeight="1"/>
+    <row r="60" ht="12.75" customHeight="1"/>
+    <row r="61" ht="12.75" customHeight="1"/>
+    <row r="62" ht="12.75" customHeight="1"/>
+    <row r="63" ht="12.75" customHeight="1"/>
+    <row r="64" ht="12.75" customHeight="1"/>
+    <row r="65" ht="12.75" customHeight="1"/>
+    <row r="66" ht="12.75" customHeight="1"/>
+    <row r="67" ht="12.75" customHeight="1"/>
+    <row r="68" ht="12.75" customHeight="1"/>
+    <row r="69" ht="12.75" customHeight="1"/>
+    <row r="70" ht="12.75" customHeight="1"/>
+    <row r="71" ht="12.75" customHeight="1"/>
+    <row r="72" ht="12.75" customHeight="1"/>
+    <row r="73" ht="12.75" customHeight="1"/>
+    <row r="74" ht="12.75" customHeight="1"/>
+    <row r="75" ht="12.75" customHeight="1"/>
+    <row r="76" ht="12.75" customHeight="1"/>
+    <row r="77" ht="12.75" customHeight="1"/>
+    <row r="78" ht="12.75" customHeight="1"/>
+    <row r="79" ht="12.75" customHeight="1"/>
+    <row r="80" ht="12.75" customHeight="1"/>
+    <row r="81" ht="12.75" customHeight="1"/>
+    <row r="82" ht="12.75" customHeight="1"/>
+    <row r="83" ht="12.75" customHeight="1"/>
+    <row r="84" ht="12.75" customHeight="1"/>
+    <row r="85" ht="12.75" customHeight="1"/>
+    <row r="86" ht="12.75" customHeight="1"/>
+    <row r="87" ht="12.75" customHeight="1"/>
+    <row r="88" ht="12.75" customHeight="1"/>
+    <row r="89" ht="12.75" customHeight="1"/>
+    <row r="90" ht="12.75" customHeight="1"/>
+    <row r="91" ht="12.75" customHeight="1"/>
+    <row r="92" ht="12.75" customHeight="1"/>
+    <row r="93" ht="12.75" customHeight="1"/>
+    <row r="94" ht="12.75" customHeight="1"/>
+    <row r="95" ht="12.75" customHeight="1"/>
+    <row r="96" ht="12.75" customHeight="1"/>
+    <row r="97" ht="12.75" customHeight="1"/>
+    <row r="98" ht="12.75" customHeight="1"/>
+    <row r="99" ht="12.75" customHeight="1"/>
+    <row r="100" ht="12.75" customHeight="1"/>
+    <row r="101" ht="12.75" customHeight="1"/>
+    <row r="102" ht="12.75" customHeight="1"/>
+    <row r="103" ht="12.75" customHeight="1"/>
+    <row r="104" ht="12.75" customHeight="1"/>
+    <row r="105" ht="12.75" customHeight="1"/>
+    <row r="106" ht="12.75" customHeight="1"/>
+    <row r="107" ht="12.75" customHeight="1"/>
+    <row r="108" ht="12.75" customHeight="1"/>
+    <row r="109" ht="12.75" customHeight="1"/>
+    <row r="110" ht="12.75" customHeight="1"/>
+    <row r="111" ht="12.75" customHeight="1"/>
+    <row r="112" ht="12.75" customHeight="1"/>
+    <row r="113" ht="12.75" customHeight="1"/>
+    <row r="114" ht="12.75" customHeight="1"/>
+    <row r="115" ht="12.75" customHeight="1"/>
+    <row r="116" ht="12.75" customHeight="1"/>
+    <row r="117" ht="12.75" customHeight="1"/>
+    <row r="118" ht="12.75" customHeight="1"/>
+    <row r="119" ht="12.75" customHeight="1"/>
+    <row r="120" ht="12.75" customHeight="1"/>
+    <row r="121" ht="12.75" customHeight="1"/>
+    <row r="122" ht="12.75" customHeight="1"/>
+    <row r="123" ht="12.75" customHeight="1"/>
+    <row r="124" ht="12.75" customHeight="1"/>
+    <row r="125" ht="12.75" customHeight="1"/>
+    <row r="126" ht="12.75" customHeight="1"/>
+    <row r="127" ht="12.75" customHeight="1"/>
+    <row r="128" ht="12.75" customHeight="1"/>
+    <row r="129" ht="12.75" customHeight="1"/>
+    <row r="130" ht="12.75" customHeight="1"/>
+    <row r="131" ht="12.75" customHeight="1"/>
+    <row r="132" ht="12.75" customHeight="1"/>
+    <row r="133" ht="12.75" customHeight="1"/>
+    <row r="134" ht="12.75" customHeight="1"/>
+    <row r="135" ht="12.75" customHeight="1"/>
+    <row r="136" ht="12.75" customHeight="1"/>
+    <row r="137" ht="12.75" customHeight="1"/>
+    <row r="138" ht="12.75" customHeight="1"/>
+    <row r="139" ht="12.75" customHeight="1"/>
+    <row r="140" ht="12.75" customHeight="1"/>
+    <row r="141" ht="12.75" customHeight="1"/>
+    <row r="142" ht="12.75" customHeight="1"/>
+    <row r="143" ht="12.75" customHeight="1"/>
+    <row r="144" ht="12.75" customHeight="1"/>
+    <row r="145" ht="12.75" customHeight="1"/>
+    <row r="146" ht="12.75" customHeight="1"/>
+    <row r="147" ht="12.75" customHeight="1"/>
+    <row r="148" ht="12.75" customHeight="1"/>
+    <row r="149" ht="12.75" customHeight="1"/>
+    <row r="150" ht="12.75" customHeight="1"/>
+    <row r="151" ht="12.75" customHeight="1"/>
+    <row r="152" ht="12.75" customHeight="1"/>
+    <row r="153" ht="12.75" customHeight="1"/>
+    <row r="154" ht="12.75" customHeight="1"/>
+    <row r="155" ht="12.75" customHeight="1"/>
+    <row r="156" ht="12.75" customHeight="1"/>
+    <row r="157" ht="12.75" customHeight="1"/>
+    <row r="158" ht="12.75" customHeight="1"/>
+    <row r="159" ht="12.75" customHeight="1"/>
+    <row r="160" ht="12.75" customHeight="1"/>
+    <row r="161" ht="12.75" customHeight="1"/>
+    <row r="162" ht="12.75" customHeight="1"/>
+    <row r="163" ht="12.75" customHeight="1"/>
+    <row r="164" ht="12.75" customHeight="1"/>
+    <row r="165" ht="12.75" customHeight="1"/>
+    <row r="166" ht="12.75" customHeight="1"/>
+    <row r="167" ht="12.75" customHeight="1"/>
+    <row r="168" ht="12.75" customHeight="1"/>
+    <row r="169" ht="12.75" customHeight="1"/>
+    <row r="170" ht="12.75" customHeight="1"/>
+    <row r="171" ht="12.75" customHeight="1"/>
+    <row r="172" ht="12.75" customHeight="1"/>
+    <row r="173" ht="12.75" customHeight="1"/>
+    <row r="174" ht="12.75" customHeight="1"/>
+    <row r="175" ht="12.75" customHeight="1"/>
+    <row r="176" ht="12.75" customHeight="1"/>
+    <row r="177" ht="12.75" customHeight="1"/>
+    <row r="178" ht="12.75" customHeight="1"/>
+    <row r="179" ht="12.75" customHeight="1"/>
+    <row r="180" ht="12.75" customHeight="1"/>
+    <row r="181" ht="12.75" customHeight="1"/>
+    <row r="182" ht="12.75" customHeight="1"/>
+    <row r="183" ht="12.75" customHeight="1"/>
+    <row r="184" ht="12.75" customHeight="1"/>
+    <row r="185" ht="12.75" customHeight="1"/>
+    <row r="186" ht="12.75" customHeight="1"/>
+    <row r="187" ht="12.75" customHeight="1"/>
+    <row r="188" ht="12.75" customHeight="1"/>
+    <row r="189" ht="12.75" customHeight="1"/>
+    <row r="190" ht="12.75" customHeight="1"/>
+    <row r="191" ht="12.75" customHeight="1"/>
+    <row r="192" ht="12.75" customHeight="1"/>
+    <row r="193" ht="12.75" customHeight="1"/>
+    <row r="194" ht="12.75" customHeight="1"/>
+    <row r="195" ht="12.75" customHeight="1"/>
+    <row r="196" ht="12.75" customHeight="1"/>
+    <row r="197" ht="12.75" customHeight="1"/>
+    <row r="198" ht="12.75" customHeight="1"/>
+    <row r="199" ht="12.75" customHeight="1"/>
+    <row r="200" ht="12.75" customHeight="1"/>
+    <row r="201" ht="12.75" customHeight="1"/>
+    <row r="202" ht="12.75" customHeight="1"/>
+    <row r="203" ht="12.75" customHeight="1"/>
+    <row r="204" ht="12.75" customHeight="1"/>
+    <row r="205" ht="12.75" customHeight="1"/>
+    <row r="206" ht="12.75" customHeight="1"/>
+    <row r="207" ht="12.75" customHeight="1"/>
+    <row r="208" ht="12.75" customHeight="1"/>
+    <row r="209" ht="12.75" customHeight="1"/>
+    <row r="210" ht="12.75" customHeight="1"/>
+    <row r="211" ht="12.75" customHeight="1"/>
+    <row r="212" ht="12.75" customHeight="1"/>
+    <row r="213" ht="12.75" customHeight="1"/>
+    <row r="214" ht="12.75" customHeight="1"/>
+    <row r="215" ht="12.75" customHeight="1"/>
+    <row r="216" ht="12.75" customHeight="1"/>
+    <row r="217" ht="12.75" customHeight="1"/>
+    <row r="218" ht="12.75" customHeight="1"/>
+    <row r="219" ht="12.75" customHeight="1"/>
+    <row r="220" ht="12.75" customHeight="1"/>
+    <row r="221" ht="12.75" customHeight="1"/>
+    <row r="222" ht="12.75" customHeight="1"/>
+    <row r="223" ht="12.75" customHeight="1"/>
+    <row r="224" ht="12.75" customHeight="1"/>
+    <row r="225" ht="12.75" customHeight="1"/>
+    <row r="226" ht="12.75" customHeight="1"/>
+    <row r="227" ht="12.75" customHeight="1"/>
+    <row r="228" ht="12.75" customHeight="1"/>
+    <row r="229" ht="12.75" customHeight="1"/>
+    <row r="230" ht="12.75" customHeight="1"/>
+    <row r="231" ht="12.75" customHeight="1"/>
+    <row r="232" ht="12.75" customHeight="1"/>
+    <row r="233" ht="12.75" customHeight="1"/>
+    <row r="234" ht="12.75" customHeight="1"/>
+    <row r="235" ht="12.75" customHeight="1"/>
+    <row r="236" ht="12.75" customHeight="1"/>
+    <row r="237" ht="12.75" customHeight="1"/>
+    <row r="238" ht="12.75" customHeight="1"/>
+    <row r="239" ht="12.75" customHeight="1"/>
+    <row r="240" ht="12.75" customHeight="1"/>
+    <row r="241" ht="12.75" customHeight="1"/>
+    <row r="242" ht="12.75" customHeight="1"/>
+    <row r="243" ht="12.75" customHeight="1"/>
+    <row r="244" ht="12.75" customHeight="1"/>
+    <row r="245" ht="12.75" customHeight="1"/>
+    <row r="246" ht="12.75" customHeight="1"/>
+    <row r="247" ht="12.75" customHeight="1"/>
+    <row r="248" ht="12.75" customHeight="1"/>
+    <row r="249" ht="12.75" customHeight="1"/>
+    <row r="250" ht="12.75" customHeight="1"/>
+    <row r="251" ht="12.75" customHeight="1"/>
+    <row r="252" ht="12.75" customHeight="1"/>
+    <row r="253" ht="12.75" customHeight="1"/>
+    <row r="254" ht="12.75" customHeight="1"/>
+    <row r="255" ht="12.75" customHeight="1"/>
+    <row r="256" ht="12.75" customHeight="1"/>
+    <row r="257" ht="12.75" customHeight="1"/>
+    <row r="258" ht="12.75" customHeight="1"/>
+    <row r="259" ht="12.75" customHeight="1"/>
+    <row r="260" ht="12.75" customHeight="1"/>
+    <row r="261" ht="12.75" customHeight="1"/>
+    <row r="262" ht="12.75" customHeight="1"/>
+    <row r="263" ht="12.75" customHeight="1"/>
+    <row r="264" ht="12.75" customHeight="1"/>
+    <row r="265" ht="12.75" customHeight="1"/>
+    <row r="266" ht="12.75" customHeight="1"/>
+    <row r="267" ht="12.75" customHeight="1"/>
+    <row r="268" ht="12.75" customHeight="1"/>
+    <row r="269" ht="12.75" customHeight="1"/>
+    <row r="270" ht="12.75" customHeight="1"/>
+    <row r="271" ht="12.75" customHeight="1"/>
+    <row r="272" ht="12.75" customHeight="1"/>
+    <row r="273" ht="12.75" customHeight="1"/>
+    <row r="274" ht="12.75" customHeight="1"/>
+    <row r="275" ht="12.75" customHeight="1"/>
+    <row r="276" ht="12.75" customHeight="1"/>
+    <row r="277" ht="12.75" customHeight="1"/>
+    <row r="278" ht="12.75" customHeight="1"/>
+    <row r="279" ht="12.75" customHeight="1"/>
+    <row r="280" ht="12.75" customHeight="1"/>
+    <row r="281" ht="12.75" customHeight="1"/>
+    <row r="282" ht="12.75" customHeight="1"/>
+    <row r="283" ht="12.75" customHeight="1"/>
+    <row r="284" ht="12.75" customHeight="1"/>
+    <row r="285" ht="12.75" customHeight="1"/>
+    <row r="286" ht="12.75" customHeight="1"/>
+    <row r="287" ht="12.75" customHeight="1"/>
+    <row r="288" ht="12.75" customHeight="1"/>
+    <row r="289" ht="12.75" customHeight="1"/>
+    <row r="290" ht="12.75" customHeight="1"/>
+    <row r="291" ht="12.75" customHeight="1"/>
+    <row r="292" ht="12.75" customHeight="1"/>
+    <row r="293" ht="12.75" customHeight="1"/>
+    <row r="294" ht="12.75" customHeight="1"/>
+    <row r="295" ht="12.75" customHeight="1"/>
+    <row r="296" ht="12.75" customHeight="1"/>
+    <row r="297" ht="12.75" customHeight="1"/>
+    <row r="298" ht="12.75" customHeight="1"/>
+    <row r="299" ht="12.75" customHeight="1"/>
+    <row r="300" ht="12.75" customHeight="1"/>
+    <row r="301" ht="12.75" customHeight="1"/>
+    <row r="302" ht="12.75" customHeight="1"/>
+    <row r="303" ht="12.75" customHeight="1"/>
+    <row r="304" ht="12.75" customHeight="1"/>
+    <row r="305" ht="12.75" customHeight="1"/>
+    <row r="306" ht="12.75" customHeight="1"/>
+    <row r="307" ht="12.75" customHeight="1"/>
+    <row r="308" ht="12.75" customHeight="1"/>
+    <row r="309" ht="12.75" customHeight="1"/>
+    <row r="310" ht="12.75" customHeight="1"/>
+    <row r="311" ht="12.75" customHeight="1"/>
+    <row r="312" ht="12.75" customHeight="1"/>
+    <row r="313" ht="12.75" customHeight="1"/>
+    <row r="314" ht="12.75" customHeight="1"/>
+    <row r="315" ht="12.75" customHeight="1"/>
+    <row r="316" ht="12.75" customHeight="1"/>
+    <row r="317" ht="12.75" customHeight="1"/>
+    <row r="318" ht="12.75" customHeight="1"/>
+    <row r="319" ht="12.75" customHeight="1"/>
+    <row r="320" ht="12.75" customHeight="1"/>
+    <row r="321" ht="12.75" customHeight="1"/>
+    <row r="322" ht="12.75" customHeight="1"/>
+    <row r="323" ht="12.75" customHeight="1"/>
+    <row r="324" ht="12.75" customHeight="1"/>
+    <row r="325" ht="12.75" customHeight="1"/>
+    <row r="326" ht="12.75" customHeight="1"/>
+    <row r="327" ht="12.75" customHeight="1"/>
+    <row r="328" ht="12.75" customHeight="1"/>
+    <row r="329" ht="12.75" customHeight="1"/>
+    <row r="330" ht="12.75" customHeight="1"/>
+    <row r="331" ht="12.75" customHeight="1"/>
+    <row r="332" ht="12.75" customHeight="1"/>
+    <row r="333" ht="12.75" customHeight="1"/>
+    <row r="334" ht="12.75" customHeight="1"/>
+    <row r="335" ht="12.75" customHeight="1"/>
+    <row r="336" ht="12.75" customHeight="1"/>
+    <row r="337" ht="12.75" customHeight="1"/>
+    <row r="338" ht="12.75" customHeight="1"/>
+    <row r="339" ht="12.75" customHeight="1"/>
+    <row r="340" ht="12.75" customHeight="1"/>
+    <row r="341" ht="12.75" customHeight="1"/>
+    <row r="342" ht="12.75" customHeight="1"/>
+    <row r="343" ht="12.75" customHeight="1"/>
+    <row r="344" ht="12.75" customHeight="1"/>
+    <row r="345" ht="12.75" customHeight="1"/>
+    <row r="346" ht="12.75" customHeight="1"/>
+    <row r="347" ht="12.75" customHeight="1"/>
+    <row r="348" ht="12.75" customHeight="1"/>
+    <row r="349" ht="12.75" customHeight="1"/>
+    <row r="350" ht="12.75" customHeight="1"/>
+    <row r="351" ht="12.75" customHeight="1"/>
+    <row r="352" ht="12.75" customHeight="1"/>
+    <row r="353" ht="12.75" customHeight="1"/>
+    <row r="354" ht="12.75" customHeight="1"/>
+    <row r="355" ht="12.75" customHeight="1"/>
+    <row r="356" ht="12.75" customHeight="1"/>
+    <row r="357" ht="12.75" customHeight="1"/>
+    <row r="358" ht="12.75" customHeight="1"/>
+    <row r="359" ht="12.75" customHeight="1"/>
+    <row r="360" ht="12.75" customHeight="1"/>
+    <row r="361" ht="12.75" customHeight="1"/>
+    <row r="362" ht="12.75" customHeight="1"/>
+    <row r="363" ht="12.75" customHeight="1"/>
+    <row r="364" ht="12.75" customHeight="1"/>
+    <row r="365" ht="12.75" customHeight="1"/>
+    <row r="366" ht="12.75" customHeight="1"/>
+    <row r="367" ht="12.75" customHeight="1"/>
+    <row r="368" ht="12.75" customHeight="1"/>
+    <row r="369" ht="12.75" customHeight="1"/>
+    <row r="370" ht="12.75" customHeight="1"/>
+    <row r="371" ht="12.75" customHeight="1"/>
+    <row r="372" ht="12.75" customHeight="1"/>
+    <row r="373" ht="12.75" customHeight="1"/>
+    <row r="374" ht="12.75" customHeight="1"/>
+    <row r="375" ht="12.75" customHeight="1"/>
+    <row r="376" ht="12.75" customHeight="1"/>
+    <row r="377" ht="12.75" customHeight="1"/>
+    <row r="378" ht="12.75" customHeight="1"/>
+    <row r="379" ht="12.75" customHeight="1"/>
+    <row r="380" ht="12.75" customHeight="1"/>
+    <row r="381" ht="12.75" customHeight="1"/>
+    <row r="382" ht="12.75" customHeight="1"/>
+    <row r="383" ht="12.75" customHeight="1"/>
+    <row r="384" ht="12.75" customHeight="1"/>
+    <row r="385" ht="12.75" customHeight="1"/>
+    <row r="386" ht="12.75" customHeight="1"/>
+    <row r="387" ht="12.75" customHeight="1"/>
+    <row r="388" ht="12.75" customHeight="1"/>
+    <row r="389" ht="12.75" customHeight="1"/>
+    <row r="390" ht="12.75" customHeight="1"/>
+    <row r="391" ht="12.75" customHeight="1"/>
+    <row r="392" ht="12.75" customHeight="1"/>
+    <row r="393" ht="12.75" customHeight="1"/>
+    <row r="394" ht="12.75" customHeight="1"/>
+    <row r="395" ht="12.75" customHeight="1"/>
+    <row r="396" ht="12.75" customHeight="1"/>
+    <row r="397" ht="12.75" customHeight="1"/>
+    <row r="398" ht="12.75" customHeight="1"/>
+    <row r="399" ht="12.75" customHeight="1"/>
+    <row r="400" ht="12.75" customHeight="1"/>
+    <row r="401" ht="12.75" customHeight="1"/>
+    <row r="402" ht="12.75" customHeight="1"/>
+    <row r="403" ht="12.75" customHeight="1"/>
+    <row r="404" ht="12.75" customHeight="1"/>
+    <row r="405" ht="12.75" customHeight="1"/>
+    <row r="406" ht="12.75" customHeight="1"/>
+    <row r="407" ht="12.75" customHeight="1"/>
+    <row r="408" ht="12.75" customHeight="1"/>
+    <row r="409" ht="12.75" customHeight="1"/>
+    <row r="410" ht="12.75" customHeight="1"/>
+    <row r="411" ht="12.75" customHeight="1"/>
+    <row r="412" ht="12.75" customHeight="1"/>
+    <row r="413" ht="12.75" customHeight="1"/>
+    <row r="414" ht="12.75" customHeight="1"/>
+    <row r="415" ht="12.75" customHeight="1"/>
+    <row r="416" ht="12.75" customHeight="1"/>
+    <row r="417" ht="12.75" customHeight="1"/>
+    <row r="418" ht="12.75" customHeight="1"/>
+    <row r="419" ht="12.75" customHeight="1"/>
+    <row r="420" ht="12.75" customHeight="1"/>
+    <row r="421" ht="12.75" customHeight="1"/>
+    <row r="422" ht="12.75" customHeight="1"/>
+    <row r="423" ht="12.75" customHeight="1"/>
+    <row r="424" ht="12.75" customHeight="1"/>
+    <row r="425" ht="12.75" customHeight="1"/>
+    <row r="426" ht="12.75" customHeight="1"/>
+    <row r="427" ht="12.75" customHeight="1"/>
+    <row r="428" ht="12.75" customHeight="1"/>
+    <row r="429" ht="12.75" customHeight="1"/>
+    <row r="430" ht="12.75" customHeight="1"/>
+    <row r="431" ht="12.75" customHeight="1"/>
+    <row r="432" ht="12.75" customHeight="1"/>
+    <row r="433" ht="12.75" customHeight="1"/>
+    <row r="434" ht="12.75" customHeight="1"/>
+    <row r="435" ht="12.75" customHeight="1"/>
+    <row r="436" ht="12.75" customHeight="1"/>
+    <row r="437" ht="12.75" customHeight="1"/>
+    <row r="438" ht="12.75" customHeight="1"/>
+    <row r="439" ht="12.75" customHeight="1"/>
+    <row r="440" ht="12.75" customHeight="1"/>
+    <row r="441" ht="12.75" customHeight="1"/>
+    <row r="442" ht="12.75" customHeight="1"/>
+    <row r="443" ht="12.75" customHeight="1"/>
+    <row r="444" ht="12.75" customHeight="1"/>
+    <row r="445" ht="12.75" customHeight="1"/>
+    <row r="446" ht="12.75" customHeight="1"/>
+    <row r="447" ht="12.75" customHeight="1"/>
+    <row r="448" ht="12.75" customHeight="1"/>
+    <row r="449" ht="12.75" customHeight="1"/>
+    <row r="450" ht="12.75" customHeight="1"/>
+    <row r="451" ht="12.75" customHeight="1"/>
+    <row r="452" ht="12.75" customHeight="1"/>
+    <row r="453" ht="12.75" customHeight="1"/>
+    <row r="454" ht="12.75" customHeight="1"/>
+    <row r="455" ht="12.75" customHeight="1"/>
+    <row r="456" ht="12.75" customHeight="1"/>
+    <row r="457" ht="12.75" customHeight="1"/>
+    <row r="458" ht="12.75" customHeight="1"/>
+    <row r="459" ht="12.75" customHeight="1"/>
+    <row r="460" ht="12.75" customHeight="1"/>
+    <row r="461" ht="12.75" customHeight="1"/>
+    <row r="462" ht="12.75" customHeight="1"/>
+    <row r="463" ht="12.75" customHeight="1"/>
+    <row r="464" ht="12.75" customHeight="1"/>
+    <row r="465" ht="12.75" customHeight="1"/>
+    <row r="466" ht="12.75" customHeight="1"/>
+    <row r="467" ht="12.75" customHeight="1"/>
+    <row r="468" ht="12.75" customHeight="1"/>
+    <row r="469" ht="12.75" customHeight="1"/>
+    <row r="470" ht="12.75" customHeight="1"/>
+    <row r="471" ht="12.75" customHeight="1"/>
+    <row r="472" ht="12.75" customHeight="1"/>
+    <row r="473" ht="12.75" customHeight="1"/>
+    <row r="474" ht="12.75" customHeight="1"/>
+    <row r="475" ht="12.75" customHeight="1"/>
+    <row r="476" ht="12.75" customHeight="1"/>
+    <row r="477" ht="12.75" customHeight="1"/>
+    <row r="478" ht="12.75" customHeight="1"/>
+    <row r="479" ht="12.75" customHeight="1"/>
+    <row r="480" ht="12.75" customHeight="1"/>
+    <row r="481" ht="12.75" customHeight="1"/>
+    <row r="482" ht="12.75" customHeight="1"/>
+    <row r="483" ht="12.75" customHeight="1"/>
+    <row r="484" ht="12.75" customHeight="1"/>
+    <row r="485" ht="12.75" customHeight="1"/>
+    <row r="486" ht="12.75" customHeight="1"/>
+    <row r="487" ht="12.75" customHeight="1"/>
+    <row r="488" ht="12.75" customHeight="1"/>
+    <row r="489" ht="12.75" customHeight="1"/>
+    <row r="490" ht="12.75" customHeight="1"/>
+    <row r="491" ht="12.75" customHeight="1"/>
+    <row r="492" ht="12.75" customHeight="1"/>
+    <row r="493" ht="12.75" customHeight="1"/>
+    <row r="494" ht="12.75" customHeight="1"/>
+    <row r="495" ht="12.75" customHeight="1"/>
+    <row r="496" ht="12.75" customHeight="1"/>
+    <row r="497" ht="12.75" customHeight="1"/>
+    <row r="498" ht="12.75" customHeight="1"/>
+    <row r="499" ht="12.75" customHeight="1"/>
+    <row r="500" ht="12.75" customHeight="1"/>
+    <row r="501" ht="12.75" customHeight="1"/>
+    <row r="502" ht="12.75" customHeight="1"/>
+    <row r="503" ht="12.75" customHeight="1"/>
+    <row r="504" ht="12.75" customHeight="1"/>
+    <row r="505" ht="12.75" customHeight="1"/>
+    <row r="506" ht="12.75" customHeight="1"/>
+    <row r="507" ht="12.75" customHeight="1"/>
+    <row r="508" ht="12.75" customHeight="1"/>
+    <row r="509" ht="12.75" customHeight="1"/>
+    <row r="510" ht="12.75" customHeight="1"/>
+    <row r="511" ht="12.75" customHeight="1"/>
+    <row r="512" ht="12.75" customHeight="1"/>
+    <row r="513" ht="12.75" customHeight="1"/>
+    <row r="514" ht="12.75" customHeight="1"/>
+    <row r="515" ht="12.75" customHeight="1"/>
+    <row r="516" ht="12.75" customHeight="1"/>
+    <row r="517" ht="12.75" customHeight="1"/>
+    <row r="518" ht="12.75" customHeight="1"/>
+    <row r="519" ht="12.75" customHeight="1"/>
+    <row r="520" ht="12.75" customHeight="1"/>
+    <row r="521" ht="12.75" customHeight="1"/>
+    <row r="522" ht="12.75" customHeight="1"/>
+    <row r="523" ht="12.75" customHeight="1"/>
+    <row r="524" ht="12.75" customHeight="1"/>
+    <row r="525" ht="12.75" customHeight="1"/>
+    <row r="526" ht="12.75" customHeight="1"/>
+    <row r="527" ht="12.75" customHeight="1"/>
+    <row r="528" ht="12.75" customHeight="1"/>
+    <row r="529" ht="12.75" customHeight="1"/>
+    <row r="530" ht="12.75" customHeight="1"/>
+    <row r="531" ht="12.75" customHeight="1"/>
+    <row r="532" ht="12.75" customHeight="1"/>
+    <row r="533" ht="12.75" customHeight="1"/>
+    <row r="534" ht="12.75" customHeight="1"/>
+    <row r="535" ht="12.75" customHeight="1"/>
+    <row r="536" ht="12.75" customHeight="1"/>
+    <row r="537" ht="12.75" customHeight="1"/>
+    <row r="538" ht="12.75" customHeight="1"/>
+    <row r="539" ht="12.75" customHeight="1"/>
+    <row r="540" ht="12.75" customHeight="1"/>
+    <row r="541" ht="12.75" customHeight="1"/>
+    <row r="542" ht="12.75" customHeight="1"/>
+    <row r="543" ht="12.75" customHeight="1"/>
+    <row r="544" ht="12.75" customHeight="1"/>
+    <row r="545" ht="12.75" customHeight="1"/>
+    <row r="546" ht="12.75" customHeight="1"/>
+    <row r="547" ht="12.75" customHeight="1"/>
+    <row r="548" ht="12.75" customHeight="1"/>
+    <row r="549" ht="12.75" customHeight="1"/>
+    <row r="550" ht="12.75" customHeight="1"/>
+    <row r="551" ht="12.75" customHeight="1"/>
+    <row r="552" ht="12.75" customHeight="1"/>
+    <row r="553" ht="12.75" customHeight="1"/>
+    <row r="554" ht="12.75" customHeight="1"/>
+    <row r="555" ht="12.75" customHeight="1"/>
+    <row r="556" ht="12.75" customHeight="1"/>
+    <row r="557" ht="12.75" customHeight="1"/>
+    <row r="558" ht="12.75" customHeight="1"/>
+    <row r="559" ht="12.75" customHeight="1"/>
+    <row r="560" ht="12.75" customHeight="1"/>
+    <row r="561" ht="12.75" customHeight="1"/>
+    <row r="562" ht="12.75" customHeight="1"/>
+    <row r="563" ht="12.75" customHeight="1"/>
+    <row r="564" ht="12.75" customHeight="1"/>
+    <row r="565" ht="12.75" customHeight="1"/>
+    <row r="566" ht="12.75" customHeight="1"/>
+    <row r="567" ht="12.75" customHeight="1"/>
+    <row r="568" ht="12.75" customHeight="1"/>
+    <row r="569" ht="12.75" customHeight="1"/>
+    <row r="570" ht="12.75" customHeight="1"/>
+    <row r="571" ht="12.75" customHeight="1"/>
+    <row r="572" ht="12.75" customHeight="1"/>
+    <row r="573" ht="12.75" customHeight="1"/>
+    <row r="574" ht="12.75" customHeight="1"/>
+    <row r="575" ht="12.75" customHeight="1"/>
+    <row r="576" ht="12.75" customHeight="1"/>
+    <row r="577" ht="12.75" customHeight="1"/>
+    <row r="578" ht="12.75" customHeight="1"/>
+    <row r="579" ht="12.75" customHeight="1"/>
+    <row r="580" ht="12.75" customHeight="1"/>
+    <row r="581" ht="12.75" customHeight="1"/>
+    <row r="582" ht="12.75" customHeight="1"/>
+    <row r="583" ht="12.75" customHeight="1"/>
+    <row r="584" ht="12.75" customHeight="1"/>
+    <row r="585" ht="12.75" customHeight="1"/>
+    <row r="586" ht="12.75" customHeight="1"/>
+    <row r="587" ht="12.75" customHeight="1"/>
+    <row r="588" ht="12.75" customHeight="1"/>
+    <row r="589" ht="12.75" customHeight="1"/>
+    <row r="590" ht="12.75" customHeight="1"/>
+    <row r="591" ht="12.75" customHeight="1"/>
+    <row r="592" ht="12.75" customHeight="1"/>
+    <row r="593" ht="12.75" customHeight="1"/>
+    <row r="594" ht="12.75" customHeight="1"/>
+    <row r="595" ht="12.75" customHeight="1"/>
+    <row r="596" ht="12.75" customHeight="1"/>
+    <row r="597" ht="12.75" customHeight="1"/>
+    <row r="598" ht="12.75" customHeight="1"/>
+    <row r="599" ht="12.75" customHeight="1"/>
+    <row r="600" ht="12.75" customHeight="1"/>
+    <row r="601" ht="12.75" customHeight="1"/>
+    <row r="602" ht="12.75" customHeight="1"/>
+    <row r="603" ht="12.75" customHeight="1"/>
+    <row r="604" ht="12.75" customHeight="1"/>
+    <row r="605" ht="12.75" customHeight="1"/>
+    <row r="606" ht="12.75" customHeight="1"/>
+    <row r="607" ht="12.75" customHeight="1"/>
+    <row r="608" ht="12.75" customHeight="1"/>
+    <row r="609" ht="12.75" customHeight="1"/>
+    <row r="610" ht="12.75" customHeight="1"/>
+    <row r="611" ht="12.75" customHeight="1"/>
+    <row r="612" ht="12.75" customHeight="1"/>
+    <row r="613" ht="12.75" customHeight="1"/>
+    <row r="614" ht="12.75" customHeight="1"/>
+    <row r="615" ht="12.75" customHeight="1"/>
+    <row r="616" ht="12.75" customHeight="1"/>
+    <row r="617" ht="12.75" customHeight="1"/>
+    <row r="618" ht="12.75" customHeight="1"/>
+    <row r="619" ht="12.75" customHeight="1"/>
+    <row r="620" ht="12.75" customHeight="1"/>
+    <row r="621" ht="12.75" customHeight="1"/>
+    <row r="622" ht="12.75" customHeight="1"/>
+    <row r="623" ht="12.75" customHeight="1"/>
+    <row r="624" ht="12.75" customHeight="1"/>
+    <row r="625" ht="12.75" customHeight="1"/>
+    <row r="626" ht="12.75" customHeight="1"/>
+    <row r="627" ht="12.75" customHeight="1"/>
+    <row r="628" ht="12.75" customHeight="1"/>
+    <row r="629" ht="12.75" customHeight="1"/>
+    <row r="630" ht="12.75" customHeight="1"/>
+    <row r="631" ht="12.75" customHeight="1"/>
+    <row r="632" ht="12.75" customHeight="1"/>
+    <row r="633" ht="12.75" customHeight="1"/>
+    <row r="634" ht="12.75" customHeight="1"/>
+    <row r="635" ht="12.75" customHeight="1"/>
+    <row r="636" ht="12.75" customHeight="1"/>
+    <row r="637" ht="12.75" customHeight="1"/>
+    <row r="638" ht="12.75" customHeight="1"/>
+    <row r="639" ht="12.75" customHeight="1"/>
+    <row r="640" ht="12.75" customHeight="1"/>
+    <row r="641" ht="12.75" customHeight="1"/>
+    <row r="642" ht="12.75" customHeight="1"/>
+    <row r="643" ht="12.75" customHeight="1"/>
+    <row r="644" ht="12.75" customHeight="1"/>
+    <row r="645" ht="12.75" customHeight="1"/>
+    <row r="646" ht="12.75" customHeight="1"/>
+    <row r="647" ht="12.75" customHeight="1"/>
+    <row r="648" ht="12.75" customHeight="1"/>
+    <row r="649" ht="12.75" customHeight="1"/>
+    <row r="650" ht="12.75" customHeight="1"/>
+    <row r="651" ht="12.75" customHeight="1"/>
+    <row r="652" ht="12.75" customHeight="1"/>
+    <row r="653" ht="12.75" customHeight="1"/>
+    <row r="654" ht="12.75" customHeight="1"/>
+    <row r="655" ht="12.75" customHeight="1"/>
+    <row r="656" ht="12.75" customHeight="1"/>
+    <row r="657" ht="12.75" customHeight="1"/>
+    <row r="658" ht="12.75" customHeight="1"/>
+    <row r="659" ht="12.75" customHeight="1"/>
+    <row r="660" ht="12.75" customHeight="1"/>
+    <row r="661" ht="12.75" customHeight="1"/>
+    <row r="662" ht="12.75" customHeight="1"/>
+    <row r="663" ht="12.75" customHeight="1"/>
+    <row r="664" ht="12.75" customHeight="1"/>
+    <row r="665" ht="12.75" customHeight="1"/>
+    <row r="666" ht="12.75" customHeight="1"/>
+    <row r="667" ht="12.75" customHeight="1"/>
+    <row r="668" ht="12.75" customHeight="1"/>
+    <row r="669" ht="12.75" customHeight="1"/>
+    <row r="670" ht="12.75" customHeight="1"/>
+    <row r="671" ht="12.75" customHeight="1"/>
+    <row r="672" ht="12.75" customHeight="1"/>
+    <row r="673" ht="12.75" customHeight="1"/>
+    <row r="674" ht="12.75" customHeight="1"/>
+    <row r="675" ht="12.75" customHeight="1"/>
+    <row r="676" ht="12.75" customHeight="1"/>
+    <row r="677" ht="12.75" customHeight="1"/>
+    <row r="678" ht="12.75" customHeight="1"/>
+    <row r="679" ht="12.75" customHeight="1"/>
+    <row r="680" ht="12.75" customHeight="1"/>
+    <row r="681" ht="12.75" customHeight="1"/>
+    <row r="682" ht="12.75" customHeight="1"/>
+    <row r="683" ht="12.75" customHeight="1"/>
+    <row r="684" ht="12.75" customHeight="1"/>
+    <row r="685" ht="12.75" customHeight="1"/>
+    <row r="686" ht="12.75" customHeight="1"/>
+    <row r="687" ht="12.75" customHeight="1"/>
+    <row r="688" ht="12.75" customHeight="1"/>
+    <row r="689" ht="12.75" customHeight="1"/>
+    <row r="690" ht="12.75" customHeight="1"/>
+    <row r="691" ht="12.75" customHeight="1"/>
+    <row r="692" ht="12.75" customHeight="1"/>
+    <row r="693" ht="12.75" customHeight="1"/>
+    <row r="694" ht="12.75" customHeight="1"/>
+    <row r="695" ht="12.75" customHeight="1"/>
+    <row r="696" ht="12.75" customHeight="1"/>
+    <row r="697" ht="12.75" customHeight="1"/>
+    <row r="698" ht="12.75" customHeight="1"/>
+    <row r="699" ht="12.75" customHeight="1"/>
+    <row r="700" ht="12.75" customHeight="1"/>
+    <row r="701" ht="12.75" customHeight="1"/>
+    <row r="702" ht="12.75" customHeight="1"/>
+    <row r="703" ht="12.75" customHeight="1"/>
+    <row r="704" ht="12.75" customHeight="1"/>
+    <row r="705" ht="12.75" customHeight="1"/>
+    <row r="706" ht="12.75" customHeight="1"/>
+    <row r="707" ht="12.75" customHeight="1"/>
+    <row r="708" ht="12.75" customHeight="1"/>
+    <row r="709" ht="12.75" customHeight="1"/>
+    <row r="710" ht="12.75" customHeight="1"/>
+    <row r="711" ht="12.75" customHeight="1"/>
+    <row r="712" ht="12.75" customHeight="1"/>
+    <row r="713" ht="12.75" customHeight="1"/>
+    <row r="714" ht="12.75" customHeight="1"/>
+    <row r="715" ht="12.75" customHeight="1"/>
+    <row r="716" ht="12.75" customHeight="1"/>
+    <row r="717" ht="12.75" customHeight="1"/>
+    <row r="718" ht="12.75" customHeight="1"/>
+    <row r="719" ht="12.75" customHeight="1"/>
+    <row r="720" ht="12.75" customHeight="1"/>
+    <row r="721" ht="12.75" customHeight="1"/>
+    <row r="722" ht="12.75" customHeight="1"/>
+    <row r="723" ht="12.75" customHeight="1"/>
+    <row r="724" ht="12.75" customHeight="1"/>
+    <row r="725" ht="12.75" customHeight="1"/>
+    <row r="726" ht="12.75" customHeight="1"/>
+    <row r="727" ht="12.75" customHeight="1"/>
+    <row r="728" ht="12.75" customHeight="1"/>
+    <row r="729" ht="12.75" customHeight="1"/>
+    <row r="730" ht="12.75" customHeight="1"/>
+    <row r="731" ht="12.75" customHeight="1"/>
+    <row r="732" ht="12.75" customHeight="1"/>
+    <row r="733" ht="12.75" customHeight="1"/>
+    <row r="734" ht="12.75" customHeight="1"/>
+    <row r="735" ht="12.75" customHeight="1"/>
+    <row r="736" ht="12.75" customHeight="1"/>
+    <row r="737" ht="12.75" customHeight="1"/>
+    <row r="738" ht="12.75" customHeight="1"/>
+    <row r="739" ht="12.75" customHeight="1"/>
+    <row r="740" ht="12.75" customHeight="1"/>
+    <row r="741" ht="12.75" customHeight="1"/>
+    <row r="742" ht="12.75" customHeight="1"/>
+    <row r="743" ht="12.75" customHeight="1"/>
+    <row r="744" ht="12.75" customHeight="1"/>
+    <row r="745" ht="12.75" customHeight="1"/>
+    <row r="746" ht="12.75" customHeight="1"/>
+    <row r="747" ht="12.75" customHeight="1"/>
+    <row r="748" ht="12.75" customHeight="1"/>
+    <row r="749" ht="12.75" customHeight="1"/>
+    <row r="750" ht="12.75" customHeight="1"/>
+    <row r="751" ht="12.75" customHeight="1"/>
+    <row r="752" ht="12.75" customHeight="1"/>
+    <row r="753" ht="12.75" customHeight="1"/>
+    <row r="754" ht="12.75" customHeight="1"/>
+    <row r="755" ht="12.75" customHeight="1"/>
+    <row r="756" ht="12.75" customHeight="1"/>
+    <row r="757" ht="12.75" customHeight="1"/>
+    <row r="758" ht="12.75" customHeight="1"/>
+    <row r="759" ht="12.75" customHeight="1"/>
+    <row r="760" ht="12.75" customHeight="1"/>
+    <row r="761" ht="12.75" customHeight="1"/>
+    <row r="762" ht="12.75" customHeight="1"/>
+    <row r="763" ht="12.75" customHeight="1"/>
+    <row r="764" ht="12.75" customHeight="1"/>
+    <row r="765" ht="12.75" customHeight="1"/>
+    <row r="766" ht="12.75" customHeight="1"/>
+    <row r="767" ht="12.75" customHeight="1"/>
+    <row r="768" ht="12.75" customHeight="1"/>
+    <row r="769" ht="12.75" customHeight="1"/>
+    <row r="770" ht="12.75" customHeight="1"/>
+    <row r="771" ht="12.75" customHeight="1"/>
+    <row r="772" ht="12.75" customHeight="1"/>
+    <row r="773" ht="12.75" customHeight="1"/>
+    <row r="774" ht="12.75" customHeight="1"/>
+    <row r="775" ht="12.75" customHeight="1"/>
+    <row r="776" ht="12.75" customHeight="1"/>
+    <row r="777" ht="12.75" customHeight="1"/>
+    <row r="778" ht="12.75" customHeight="1"/>
+    <row r="779" ht="12.75" customHeight="1"/>
+    <row r="780" ht="12.75" customHeight="1"/>
+    <row r="781" ht="12.75" customHeight="1"/>
+    <row r="782" ht="12.75" customHeight="1"/>
+    <row r="783" ht="12.75" customHeight="1"/>
+    <row r="784" ht="12.75" customHeight="1"/>
+    <row r="785" ht="12.75" customHeight="1"/>
+    <row r="786" ht="12.75" customHeight="1"/>
+    <row r="787" ht="12.75" customHeight="1"/>
+    <row r="788" ht="12.75" customHeight="1"/>
+    <row r="789" ht="12.75" customHeight="1"/>
+    <row r="790" ht="12.75" customHeight="1"/>
+    <row r="791" ht="12.75" customHeight="1"/>
+    <row r="792" ht="12.75" customHeight="1"/>
+    <row r="793" ht="12.75" customHeight="1"/>
+    <row r="794" ht="12.75" customHeight="1"/>
+    <row r="795" ht="12.75" customHeight="1"/>
+    <row r="796" ht="12.75" customHeight="1"/>
+    <row r="797" ht="12.75" customHeight="1"/>
+    <row r="798" ht="12.75" customHeight="1"/>
+    <row r="799" ht="12.75" customHeight="1"/>
+    <row r="800" ht="12.75" customHeight="1"/>
+    <row r="801" ht="12.75" customHeight="1"/>
+    <row r="802" ht="12.75" customHeight="1"/>
+    <row r="803" ht="12.75" customHeight="1"/>
+    <row r="804" ht="12.75" customHeight="1"/>
+    <row r="805" ht="12.75" customHeight="1"/>
+    <row r="806" ht="12.75" customHeight="1"/>
+    <row r="807" ht="12.75" customHeight="1"/>
+    <row r="808" ht="12.75" customHeight="1"/>
+    <row r="809" ht="12.75" customHeight="1"/>
+    <row r="810" ht="12.75" customHeight="1"/>
+    <row r="811" ht="12.75" customHeight="1"/>
+    <row r="812" ht="12.75" customHeight="1"/>
+    <row r="813" ht="12.75" customHeight="1"/>
+    <row r="814" ht="12.75" customHeight="1"/>
+    <row r="815" ht="12.75" customHeight="1"/>
+    <row r="816" ht="12.75" customHeight="1"/>
+    <row r="817" ht="12.75" customHeight="1"/>
+    <row r="818" ht="12.75" customHeight="1"/>
+    <row r="819" ht="12.75" customHeight="1"/>
+    <row r="820" ht="12.75" customHeight="1"/>
+    <row r="821" ht="12.75" customHeight="1"/>
+    <row r="822" ht="12.75" customHeight="1"/>
+    <row r="823" ht="12.75" customHeight="1"/>
+    <row r="824" ht="12.75" customHeight="1"/>
+    <row r="825" ht="12.75" customHeight="1"/>
+    <row r="826" ht="12.75" customHeight="1"/>
+    <row r="827" ht="12.75" customHeight="1"/>
+    <row r="828" ht="12.75" customHeight="1"/>
+    <row r="829" ht="12.75" customHeight="1"/>
+    <row r="830" ht="12.75" customHeight="1"/>
+    <row r="831" ht="12.75" customHeight="1"/>
+    <row r="832" ht="12.75" customHeight="1"/>
+    <row r="833" ht="12.75" customHeight="1"/>
+    <row r="834" ht="12.75" customHeight="1"/>
+    <row r="835" ht="12.75" customHeight="1"/>
+    <row r="836" ht="12.75" customHeight="1"/>
+    <row r="837" ht="12.75" customHeight="1"/>
+    <row r="838" ht="12.75" customHeight="1"/>
+    <row r="839" ht="12.75" customHeight="1"/>
+    <row r="840" ht="12.75" customHeight="1"/>
+    <row r="841" ht="12.75" customHeight="1"/>
+    <row r="842" ht="12.75" customHeight="1"/>
+    <row r="843" ht="12.75" customHeight="1"/>
+    <row r="844" ht="12.75" customHeight="1"/>
+    <row r="845" ht="12.75" customHeight="1"/>
+    <row r="846" ht="12.75" customHeight="1"/>
+    <row r="847" ht="12.75" customHeight="1"/>
+    <row r="848" ht="12.75" customHeight="1"/>
+    <row r="849" ht="12.75" customHeight="1"/>
+    <row r="850" ht="12.75" customHeight="1"/>
+    <row r="851" ht="12.75" customHeight="1"/>
+    <row r="852" ht="12.75" customHeight="1"/>
+    <row r="853" ht="12.75" customHeight="1"/>
+    <row r="854" ht="12.75" customHeight="1"/>
+    <row r="855" ht="12.75" customHeight="1"/>
+    <row r="856" ht="12.75" customHeight="1"/>
+    <row r="857" ht="12.75" customHeight="1"/>
+    <row r="858" ht="12.75" customHeight="1"/>
+    <row r="859" ht="12.75" customHeight="1"/>
+    <row r="860" ht="12.75" customHeight="1"/>
+    <row r="861" ht="12.75" customHeight="1"/>
+    <row r="862" ht="12.75" customHeight="1"/>
+    <row r="863" ht="12.75" customHeight="1"/>
+    <row r="864" ht="12.75" customHeight="1"/>
+    <row r="865" ht="12.75" customHeight="1"/>
+    <row r="866" ht="12.75" customHeight="1"/>
+    <row r="867" ht="12.75" customHeight="1"/>
+    <row r="868" ht="12.75" customHeight="1"/>
+    <row r="869" ht="12.75" customHeight="1"/>
+    <row r="870" ht="12.75" customHeight="1"/>
+    <row r="871" ht="12.75" customHeight="1"/>
+    <row r="872" ht="12.75" customHeight="1"/>
+    <row r="873" ht="12.75" customHeight="1"/>
+    <row r="874" ht="12.75" customHeight="1"/>
+    <row r="875" ht="12.75" customHeight="1"/>
+    <row r="876" ht="12.75" customHeight="1"/>
+    <row r="877" ht="12.75" customHeight="1"/>
+    <row r="878" ht="12.75" customHeight="1"/>
+    <row r="879" ht="12.75" customHeight="1"/>
+    <row r="880" ht="12.75" customHeight="1"/>
+    <row r="881" ht="12.75" customHeight="1"/>
+    <row r="882" ht="12.75" customHeight="1"/>
+    <row r="883" ht="12.75" customHeight="1"/>
+    <row r="884" ht="12.75" customHeight="1"/>
+    <row r="885" ht="12.75" customHeight="1"/>
+    <row r="886" ht="12.75" customHeight="1"/>
+    <row r="887" ht="12.75" customHeight="1"/>
+    <row r="888" ht="12.75" customHeight="1"/>
+    <row r="889" ht="12.75" customHeight="1"/>
+    <row r="890" ht="12.75" customHeight="1"/>
+    <row r="891" ht="12.75" customHeight="1"/>
+    <row r="892" ht="12.75" customHeight="1"/>
+    <row r="893" ht="12.75" customHeight="1"/>
+    <row r="894" ht="12.75" customHeight="1"/>
+    <row r="895" ht="12.75" customHeight="1"/>
+    <row r="896" ht="12.75" customHeight="1"/>
+    <row r="897" ht="12.75" customHeight="1"/>
+    <row r="898" ht="12.75" customHeight="1"/>
+    <row r="899" ht="12.75" customHeight="1"/>
+    <row r="900" ht="12.75" customHeight="1"/>
+    <row r="901" ht="12.75" customHeight="1"/>
+    <row r="902" ht="12.75" customHeight="1"/>
+    <row r="903" ht="12.75" customHeight="1"/>
+    <row r="904" ht="12.75" customHeight="1"/>
+    <row r="905" ht="12.75" customHeight="1"/>
+    <row r="906" ht="12.75" customHeight="1"/>
+    <row r="907" ht="12.75" customHeight="1"/>
+    <row r="908" ht="12.75" customHeight="1"/>
+    <row r="909" ht="12.75" customHeight="1"/>
+    <row r="910" ht="12.75" customHeight="1"/>
+    <row r="911" ht="12.75" customHeight="1"/>
+    <row r="912" ht="12.75" customHeight="1"/>
+    <row r="913" ht="12.75" customHeight="1"/>
+    <row r="914" ht="12.75" customHeight="1"/>
+    <row r="915" ht="12.75" customHeight="1"/>
+    <row r="916" ht="12.75" customHeight="1"/>
+    <row r="917" ht="12.75" customHeight="1"/>
+    <row r="918" ht="12.75" customHeight="1"/>
+    <row r="919" ht="12.75" customHeight="1"/>
+    <row r="920" ht="12.75" customHeight="1"/>
+    <row r="921" ht="12.75" customHeight="1"/>
+    <row r="922" ht="12.75" customHeight="1"/>
+    <row r="923" ht="12.75" customHeight="1"/>
+    <row r="924" ht="12.75" customHeight="1"/>
+    <row r="925" ht="12.75" customHeight="1"/>
+    <row r="926" ht="12.75" customHeight="1"/>
+    <row r="927" ht="12.75" customHeight="1"/>
+    <row r="928" ht="12.75" customHeight="1"/>
+    <row r="929" ht="12.75" customHeight="1"/>
+    <row r="930" ht="12.75" customHeight="1"/>
+    <row r="931" ht="12.75" customHeight="1"/>
+    <row r="932" ht="12.75" customHeight="1"/>
+    <row r="933" ht="12.75" customHeight="1"/>
+    <row r="934" ht="12.75" customHeight="1"/>
+    <row r="935" ht="12.75" customHeight="1"/>
+    <row r="936" ht="12.75" customHeight="1"/>
+    <row r="937" ht="12.75" customHeight="1"/>
+    <row r="938" ht="12.75" customHeight="1"/>
+    <row r="939" ht="12.75" customHeight="1"/>
+    <row r="940" ht="12.75" customHeight="1"/>
+    <row r="941" ht="12.75" customHeight="1"/>
+    <row r="942" ht="12.75" customHeight="1"/>
+    <row r="943" ht="12.75" customHeight="1"/>
+    <row r="944" ht="12.75" customHeight="1"/>
+    <row r="945" ht="12.75" customHeight="1"/>
+    <row r="946" ht="12.75" customHeight="1"/>
+    <row r="947" ht="12.75" customHeight="1"/>
+    <row r="948" ht="12.75" customHeight="1"/>
+    <row r="949" ht="12.75" customHeight="1"/>
+    <row r="950" ht="12.75" customHeight="1"/>
+    <row r="951" ht="12.75" customHeight="1"/>
+    <row r="952" ht="12.75" customHeight="1"/>
+    <row r="953" ht="12.75" customHeight="1"/>
+    <row r="954" ht="12.75" customHeight="1"/>
+    <row r="955" ht="12.75" customHeight="1"/>
+    <row r="956" ht="12.75" customHeight="1"/>
+    <row r="957" ht="12.75" customHeight="1"/>
+    <row r="958" ht="12.75" customHeight="1"/>
+    <row r="959" ht="12.75" customHeight="1"/>
+    <row r="960" ht="12.75" customHeight="1"/>
+    <row r="961" ht="12.75" customHeight="1"/>
+    <row r="962" ht="12.75" customHeight="1"/>
+    <row r="963" ht="12.75" customHeight="1"/>
+    <row r="964" ht="12.75" customHeight="1"/>
+    <row r="965" ht="12.75" customHeight="1"/>
+    <row r="966" ht="12.75" customHeight="1"/>
+    <row r="967" ht="12.75" customHeight="1"/>
+    <row r="968" ht="12.75" customHeight="1"/>
+    <row r="969" ht="12.75" customHeight="1"/>
+    <row r="970" ht="12.75" customHeight="1"/>
+    <row r="971" ht="12.75" customHeight="1"/>
+    <row r="972" ht="12.75" customHeight="1"/>
+    <row r="973" ht="12.75" customHeight="1"/>
+    <row r="974" ht="12.75" customHeight="1"/>
+    <row r="975" ht="12.75" customHeight="1"/>
+    <row r="976" ht="12.75" customHeight="1"/>
+    <row r="977" ht="12.75" customHeight="1"/>
+    <row r="978" ht="12.75" customHeight="1"/>
+    <row r="979" ht="12.75" customHeight="1"/>
+    <row r="980" ht="12.75" customHeight="1"/>
+    <row r="981" ht="12.75" customHeight="1"/>
+    <row r="982" ht="12.75" customHeight="1"/>
+    <row r="983" ht="12.75" customHeight="1"/>
+    <row r="984" ht="12.75" customHeight="1"/>
+    <row r="985" ht="12.75" customHeight="1"/>
+    <row r="986" ht="12.75" customHeight="1"/>
+    <row r="987" ht="12.75" customHeight="1"/>
+    <row r="988" ht="12.75" customHeight="1"/>
+    <row r="989" ht="12.75" customHeight="1"/>
+    <row r="990" ht="12.75" customHeight="1"/>
+    <row r="991" ht="12.75" customHeight="1"/>
+    <row r="992" ht="12.75" customHeight="1"/>
+    <row r="993" ht="12.75" customHeight="1"/>
+    <row r="994" ht="12.75" customHeight="1"/>
+    <row r="995" ht="12.75" customHeight="1"/>
+    <row r="996" ht="12.75" customHeight="1"/>
+    <row r="997" ht="12.75" customHeight="1"/>
+    <row r="998" ht="12.75" customHeight="1"/>
+    <row r="999" ht="12.75" customHeight="1"/>
+    <row r="1000" ht="12.75" customHeight="1"/>
+  </sheetData>
+  <mergeCells count="136">
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="J19:K19"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="J30:K30"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="J29:K29"/>
+    <mergeCell ref="L26:N26"/>
+    <mergeCell ref="L27:N27"/>
+    <mergeCell ref="L28:N28"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="L18:N18"/>
+    <mergeCell ref="L19:N19"/>
+    <mergeCell ref="L21:N21"/>
+    <mergeCell ref="L22:N22"/>
+    <mergeCell ref="L23:N23"/>
+    <mergeCell ref="L24:N24"/>
+    <mergeCell ref="L25:N25"/>
+    <mergeCell ref="K2:N4"/>
+    <mergeCell ref="O2:P4"/>
+    <mergeCell ref="Q2:R4"/>
+    <mergeCell ref="S2:T4"/>
+    <mergeCell ref="A1:F4"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="S1:T1"/>
+    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="G5:T5"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="G6:T6"/>
+    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="G7:T7"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="G20:I20"/>
+    <mergeCell ref="J20:K20"/>
+    <mergeCell ref="L20:N20"/>
+    <mergeCell ref="O20:Q20"/>
+    <mergeCell ref="L15:N15"/>
+    <mergeCell ref="O15:Q15"/>
+    <mergeCell ref="L16:N16"/>
+    <mergeCell ref="O16:Q16"/>
+    <mergeCell ref="L17:N17"/>
+    <mergeCell ref="O17:Q17"/>
+    <mergeCell ref="O18:Q18"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="O27:Q27"/>
+    <mergeCell ref="O28:Q28"/>
+    <mergeCell ref="O29:Q29"/>
+    <mergeCell ref="O30:Q30"/>
+    <mergeCell ref="O31:Q31"/>
+    <mergeCell ref="O19:Q19"/>
+    <mergeCell ref="O21:Q21"/>
+    <mergeCell ref="O22:Q22"/>
+    <mergeCell ref="O23:Q23"/>
+    <mergeCell ref="O24:Q24"/>
+    <mergeCell ref="O25:Q25"/>
+    <mergeCell ref="O26:Q26"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="E30:F30"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="E31:F31"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="E26:F26"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="E29:F29"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="E27:F27"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="E28:F28"/>
+    <mergeCell ref="A29:B29"/>
+  </mergeCells>
+  <phoneticPr fontId="8"/>
+  <hyperlinks>
+    <hyperlink ref="L17" r:id="rId1" xr:uid="{9C856B3A-5628-4A84-AEB9-83C42CAD3F20}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
+  <pageSetup paperSize="9" orientation="landscape"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94CAB32B-3B4B-457E-B790-F1ACEE03BCA0}">
+  <dimension ref="A1:S52"/>
+  <sheetFormatPr defaultColWidth="8" defaultRowHeight="11.25" customHeight="1"/>
+  <cols>
+    <col min="1" max="1" width="13.5703125" style="201" customWidth="1"/>
+    <col min="2" max="2" width="13.5703125" style="235" customWidth="1"/>
+    <col min="3" max="6" width="8.140625" style="201" customWidth="1"/>
+    <col min="7" max="7" width="8.140625" style="235" customWidth="1"/>
+    <col min="8" max="13" width="8.140625" style="201" customWidth="1"/>
+    <col min="14" max="19" width="12.140625" style="201" customWidth="1"/>
+    <col min="20" max="16384" width="8" style="201"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" ht="18.75" customHeight="1">
+      <c r="A1" s="193" t="s">
+        <v>127</v>
+      </c>
+      <c r="B1" s="193"/>
+      <c r="C1" s="194" t="s">
+        <v>128</v>
+      </c>
+      <c r="D1" s="195"/>
+      <c r="E1" s="196"/>
+      <c r="F1" s="197"/>
+      <c r="G1" s="198"/>
+      <c r="H1" s="198"/>
+      <c r="I1" s="198"/>
+      <c r="J1" s="198"/>
+      <c r="K1" s="198"/>
+      <c r="L1" s="198"/>
+      <c r="M1" s="199"/>
+      <c r="N1" s="200" t="s">
+        <v>129</v>
+      </c>
+      <c r="O1" s="197"/>
+      <c r="P1" s="199"/>
+      <c r="Q1" s="200" t="s">
+        <v>130</v>
+      </c>
+      <c r="R1" s="197" t="s">
+        <v>131</v>
+      </c>
+      <c r="S1" s="199"/>
+    </row>
+    <row r="2" spans="1:19" ht="18.75" customHeight="1">
+      <c r="A2" s="193"/>
+      <c r="B2" s="193"/>
+      <c r="C2" s="194" t="s">
+        <v>132</v>
+      </c>
+      <c r="D2" s="195"/>
+      <c r="E2" s="196"/>
+      <c r="F2" s="197"/>
+      <c r="G2" s="198"/>
+      <c r="H2" s="198"/>
+      <c r="I2" s="198"/>
+      <c r="J2" s="198"/>
+      <c r="K2" s="198"/>
+      <c r="L2" s="198"/>
+      <c r="M2" s="199"/>
+      <c r="N2" s="200" t="s">
+        <v>133</v>
+      </c>
+      <c r="O2" s="202"/>
+      <c r="P2" s="203"/>
+      <c r="Q2" s="204" t="s">
+        <v>134</v>
+      </c>
+      <c r="R2" s="205">
+        <v>44771</v>
+      </c>
+      <c r="S2" s="206"/>
+    </row>
+    <row r="3" spans="1:19" ht="11.25" customHeight="1">
+      <c r="A3" s="207"/>
+      <c r="B3" s="208"/>
+      <c r="C3" s="207"/>
+      <c r="D3" s="207"/>
+      <c r="E3" s="207"/>
+      <c r="F3" s="207"/>
+      <c r="G3" s="208"/>
+      <c r="H3" s="207"/>
+      <c r="I3" s="207"/>
+      <c r="J3" s="207"/>
+      <c r="K3" s="207"/>
+      <c r="L3" s="207"/>
+      <c r="M3" s="207"/>
+      <c r="N3" s="207"/>
+      <c r="O3" s="207"/>
+      <c r="P3" s="207"/>
+      <c r="Q3" s="207"/>
+      <c r="R3" s="207"/>
+      <c r="S3" s="207"/>
+    </row>
+    <row r="4" spans="1:19" ht="15" customHeight="1">
+      <c r="A4" s="209" t="s">
+        <v>135</v>
+      </c>
+      <c r="B4" s="210" t="s">
+        <v>136</v>
+      </c>
+      <c r="C4" s="211" t="s">
+        <v>137</v>
+      </c>
+      <c r="D4" s="212"/>
+      <c r="E4" s="212"/>
+      <c r="F4" s="212"/>
+      <c r="G4" s="213"/>
+      <c r="H4" s="211" t="s">
+        <v>138</v>
+      </c>
+      <c r="I4" s="212"/>
+      <c r="J4" s="212"/>
+      <c r="K4" s="212"/>
+      <c r="L4" s="212"/>
+      <c r="M4" s="213"/>
+      <c r="N4" s="211" t="s">
+        <v>139</v>
+      </c>
+      <c r="O4" s="212"/>
+      <c r="P4" s="213"/>
+      <c r="Q4" s="209" t="s">
+        <v>140</v>
+      </c>
+      <c r="R4" s="211" t="s">
+        <v>141</v>
+      </c>
+      <c r="S4" s="213"/>
+    </row>
+    <row r="5" spans="1:19" ht="30" customHeight="1">
+      <c r="A5" s="214"/>
+      <c r="B5" s="215"/>
+      <c r="C5" s="216"/>
+      <c r="D5" s="216"/>
+      <c r="E5" s="216"/>
+      <c r="F5" s="216"/>
+      <c r="G5" s="216"/>
+      <c r="H5" s="216"/>
+      <c r="I5" s="216"/>
+      <c r="J5" s="216"/>
+      <c r="K5" s="216"/>
+      <c r="L5" s="216"/>
+      <c r="M5" s="216"/>
+      <c r="N5" s="217"/>
+      <c r="O5" s="218"/>
+      <c r="P5" s="219"/>
+      <c r="Q5" s="214"/>
+      <c r="R5" s="220"/>
+      <c r="S5" s="221"/>
+    </row>
+    <row r="6" spans="1:19" ht="30" customHeight="1">
+      <c r="A6" s="222"/>
+      <c r="B6" s="222"/>
+      <c r="C6" s="223"/>
+      <c r="D6" s="223"/>
+      <c r="E6" s="223"/>
+      <c r="F6" s="223"/>
+      <c r="G6" s="223"/>
+      <c r="H6" s="223"/>
+      <c r="I6" s="223"/>
+      <c r="J6" s="223"/>
+      <c r="K6" s="223"/>
+      <c r="L6" s="223"/>
+      <c r="M6" s="223"/>
+      <c r="N6" s="224"/>
+      <c r="O6" s="225"/>
+      <c r="P6" s="226"/>
+      <c r="Q6" s="227"/>
+      <c r="R6" s="228"/>
+      <c r="S6" s="228"/>
+    </row>
+    <row r="7" spans="1:19" ht="30" customHeight="1">
+      <c r="A7" s="222"/>
+      <c r="B7" s="222"/>
+      <c r="C7" s="223"/>
+      <c r="D7" s="223"/>
+      <c r="E7" s="223"/>
+      <c r="F7" s="223"/>
+      <c r="G7" s="223"/>
+      <c r="H7" s="223"/>
+      <c r="I7" s="223"/>
+      <c r="J7" s="223"/>
+      <c r="K7" s="223"/>
+      <c r="L7" s="223"/>
+      <c r="M7" s="223"/>
+      <c r="N7" s="229"/>
+      <c r="O7" s="230"/>
+      <c r="P7" s="231"/>
+      <c r="Q7" s="227"/>
+      <c r="R7" s="228"/>
+      <c r="S7" s="228"/>
+    </row>
+    <row r="8" spans="1:19" ht="30" customHeight="1">
+      <c r="A8" s="222"/>
+      <c r="B8" s="222"/>
+      <c r="C8" s="223"/>
+      <c r="D8" s="223"/>
+      <c r="E8" s="223"/>
+      <c r="F8" s="223"/>
+      <c r="G8" s="223"/>
+      <c r="H8" s="223"/>
+      <c r="I8" s="223"/>
+      <c r="J8" s="223"/>
+      <c r="K8" s="223"/>
+      <c r="L8" s="223"/>
+      <c r="M8" s="223"/>
+      <c r="N8" s="229"/>
+      <c r="O8" s="230"/>
+      <c r="P8" s="231"/>
+      <c r="Q8" s="227"/>
+      <c r="R8" s="228"/>
+      <c r="S8" s="228"/>
+    </row>
+    <row r="9" spans="1:19" ht="30" customHeight="1">
+      <c r="A9" s="222"/>
+      <c r="B9" s="222"/>
+      <c r="C9" s="223"/>
+      <c r="D9" s="223"/>
+      <c r="E9" s="223"/>
+      <c r="F9" s="223"/>
+      <c r="G9" s="223"/>
+      <c r="H9" s="223"/>
+      <c r="I9" s="223"/>
+      <c r="J9" s="223"/>
+      <c r="K9" s="223"/>
+      <c r="L9" s="223"/>
+      <c r="M9" s="223"/>
+      <c r="N9" s="229"/>
+      <c r="O9" s="230"/>
+      <c r="P9" s="231"/>
+      <c r="Q9" s="222"/>
+      <c r="R9" s="228"/>
+      <c r="S9" s="228"/>
+    </row>
+    <row r="10" spans="1:19" ht="30" customHeight="1">
+      <c r="A10" s="222"/>
+      <c r="B10" s="222"/>
+      <c r="C10" s="223"/>
+      <c r="D10" s="223"/>
+      <c r="E10" s="223"/>
+      <c r="F10" s="223"/>
+      <c r="G10" s="223"/>
+      <c r="H10" s="232"/>
+      <c r="I10" s="233"/>
+      <c r="J10" s="233"/>
+      <c r="K10" s="233"/>
+      <c r="L10" s="233"/>
+      <c r="M10" s="234"/>
+      <c r="N10" s="229"/>
+      <c r="O10" s="230"/>
+      <c r="P10" s="231"/>
+      <c r="Q10" s="227"/>
+      <c r="R10" s="228"/>
+      <c r="S10" s="228"/>
+    </row>
+    <row r="11" spans="1:19" ht="30" customHeight="1">
+      <c r="A11" s="222"/>
+      <c r="B11" s="222"/>
+      <c r="C11" s="223"/>
+      <c r="D11" s="223"/>
+      <c r="E11" s="223"/>
+      <c r="F11" s="223"/>
+      <c r="G11" s="223"/>
+      <c r="H11" s="232"/>
+      <c r="I11" s="233"/>
+      <c r="J11" s="233"/>
+      <c r="K11" s="233"/>
+      <c r="L11" s="233"/>
+      <c r="M11" s="234"/>
+      <c r="N11" s="229"/>
+      <c r="O11" s="230"/>
+      <c r="P11" s="231"/>
+      <c r="Q11" s="222"/>
+      <c r="R11" s="228"/>
+      <c r="S11" s="228"/>
+    </row>
+    <row r="12" spans="1:19" ht="30" customHeight="1">
+      <c r="A12" s="222"/>
+      <c r="B12" s="222"/>
+      <c r="C12" s="223"/>
+      <c r="D12" s="223"/>
+      <c r="E12" s="223"/>
+      <c r="F12" s="223"/>
+      <c r="G12" s="223"/>
+      <c r="H12" s="232"/>
+      <c r="I12" s="233"/>
+      <c r="J12" s="233"/>
+      <c r="K12" s="233"/>
+      <c r="L12" s="233"/>
+      <c r="M12" s="234"/>
+      <c r="N12" s="229"/>
+      <c r="O12" s="230"/>
+      <c r="P12" s="231"/>
+      <c r="Q12" s="222"/>
+      <c r="R12" s="228"/>
+      <c r="S12" s="228"/>
+    </row>
+    <row r="13" spans="1:19" ht="30" customHeight="1">
+      <c r="A13" s="222"/>
+      <c r="B13" s="222"/>
+      <c r="C13" s="223"/>
+      <c r="D13" s="223"/>
+      <c r="E13" s="223"/>
+      <c r="F13" s="223"/>
+      <c r="G13" s="223"/>
+      <c r="H13" s="232"/>
+      <c r="I13" s="233"/>
+      <c r="J13" s="233"/>
+      <c r="K13" s="233"/>
+      <c r="L13" s="233"/>
+      <c r="M13" s="234"/>
+      <c r="N13" s="229"/>
+      <c r="O13" s="230"/>
+      <c r="P13" s="231"/>
+      <c r="Q13" s="222"/>
+      <c r="R13" s="228"/>
+      <c r="S13" s="228"/>
+    </row>
+    <row r="14" spans="1:19" ht="30" customHeight="1">
+      <c r="A14" s="222"/>
+      <c r="B14" s="222"/>
+      <c r="C14" s="223"/>
+      <c r="D14" s="223"/>
+      <c r="E14" s="223"/>
+      <c r="F14" s="223"/>
+      <c r="G14" s="223"/>
+      <c r="H14" s="232"/>
+      <c r="I14" s="233"/>
+      <c r="J14" s="233"/>
+      <c r="K14" s="233"/>
+      <c r="L14" s="233"/>
+      <c r="M14" s="234"/>
+      <c r="N14" s="229"/>
+      <c r="O14" s="230"/>
+      <c r="P14" s="231"/>
+      <c r="Q14" s="222"/>
+      <c r="R14" s="228"/>
+      <c r="S14" s="228"/>
+    </row>
+    <row r="15" spans="1:19" ht="30" customHeight="1">
+      <c r="A15" s="222"/>
+      <c r="B15" s="222"/>
+      <c r="C15" s="223"/>
+      <c r="D15" s="223"/>
+      <c r="E15" s="223"/>
+      <c r="F15" s="223"/>
+      <c r="G15" s="223"/>
+      <c r="H15" s="232"/>
+      <c r="I15" s="233"/>
+      <c r="J15" s="233"/>
+      <c r="K15" s="233"/>
+      <c r="L15" s="233"/>
+      <c r="M15" s="234"/>
+      <c r="N15" s="229"/>
+      <c r="O15" s="230"/>
+      <c r="P15" s="231"/>
+      <c r="Q15" s="222"/>
+      <c r="R15" s="228"/>
+      <c r="S15" s="228"/>
+    </row>
+    <row r="16" spans="1:19" ht="30" customHeight="1">
+      <c r="A16" s="222"/>
+      <c r="B16" s="222"/>
+      <c r="C16" s="223"/>
+      <c r="D16" s="223"/>
+      <c r="E16" s="223"/>
+      <c r="F16" s="223"/>
+      <c r="G16" s="223"/>
+      <c r="H16" s="232"/>
+      <c r="I16" s="233"/>
+      <c r="J16" s="233"/>
+      <c r="K16" s="233"/>
+      <c r="L16" s="233"/>
+      <c r="M16" s="234"/>
+      <c r="N16" s="229"/>
+      <c r="O16" s="230"/>
+      <c r="P16" s="231"/>
+      <c r="Q16" s="222"/>
+      <c r="R16" s="228"/>
+      <c r="S16" s="228"/>
+    </row>
+    <row r="17" spans="1:19" ht="30" customHeight="1">
+      <c r="A17" s="222"/>
+      <c r="B17" s="222"/>
+      <c r="C17" s="223"/>
+      <c r="D17" s="223"/>
+      <c r="E17" s="223"/>
+      <c r="F17" s="223"/>
+      <c r="G17" s="223"/>
+      <c r="H17" s="232"/>
+      <c r="I17" s="233"/>
+      <c r="J17" s="233"/>
+      <c r="K17" s="233"/>
+      <c r="L17" s="233"/>
+      <c r="M17" s="234"/>
+      <c r="N17" s="229"/>
+      <c r="O17" s="230"/>
+      <c r="P17" s="231"/>
+      <c r="Q17" s="222"/>
+      <c r="R17" s="228"/>
+      <c r="S17" s="228"/>
+    </row>
+    <row r="18" spans="1:19" ht="30" customHeight="1">
+      <c r="A18" s="222"/>
+      <c r="B18" s="222"/>
+      <c r="C18" s="223"/>
+      <c r="D18" s="223"/>
+      <c r="E18" s="223"/>
+      <c r="F18" s="223"/>
+      <c r="G18" s="223"/>
+      <c r="H18" s="232"/>
+      <c r="I18" s="233"/>
+      <c r="J18" s="233"/>
+      <c r="K18" s="233"/>
+      <c r="L18" s="233"/>
+      <c r="M18" s="234"/>
+      <c r="N18" s="229"/>
+      <c r="O18" s="230"/>
+      <c r="P18" s="231"/>
+      <c r="Q18" s="222"/>
+      <c r="R18" s="228"/>
+      <c r="S18" s="228"/>
+    </row>
+    <row r="19" spans="1:19" ht="30" customHeight="1">
+      <c r="A19" s="222"/>
+      <c r="B19" s="222"/>
+      <c r="C19" s="223"/>
+      <c r="D19" s="223"/>
+      <c r="E19" s="223"/>
+      <c r="F19" s="223"/>
+      <c r="G19" s="223"/>
+      <c r="H19" s="232"/>
+      <c r="I19" s="233"/>
+      <c r="J19" s="233"/>
+      <c r="K19" s="233"/>
+      <c r="L19" s="233"/>
+      <c r="M19" s="234"/>
+      <c r="N19" s="229"/>
+      <c r="O19" s="230"/>
+      <c r="P19" s="231"/>
+      <c r="Q19" s="222"/>
+      <c r="R19" s="228"/>
+      <c r="S19" s="228"/>
+    </row>
+    <row r="20" spans="1:19" ht="30" customHeight="1">
+      <c r="A20" s="222"/>
+      <c r="B20" s="222"/>
+      <c r="C20" s="223"/>
+      <c r="D20" s="223"/>
+      <c r="E20" s="223"/>
+      <c r="F20" s="223"/>
+      <c r="G20" s="223"/>
+      <c r="H20" s="232"/>
+      <c r="I20" s="233"/>
+      <c r="J20" s="233"/>
+      <c r="K20" s="233"/>
+      <c r="L20" s="233"/>
+      <c r="M20" s="234"/>
+      <c r="N20" s="229"/>
+      <c r="O20" s="230"/>
+      <c r="P20" s="231"/>
+      <c r="Q20" s="222"/>
+      <c r="R20" s="228"/>
+      <c r="S20" s="228"/>
+    </row>
+    <row r="21" spans="1:19" ht="30" customHeight="1">
+      <c r="A21" s="222"/>
+      <c r="B21" s="222"/>
+      <c r="C21" s="223"/>
+      <c r="D21" s="223"/>
+      <c r="E21" s="223"/>
+      <c r="F21" s="223"/>
+      <c r="G21" s="223"/>
+      <c r="H21" s="232"/>
+      <c r="I21" s="233"/>
+      <c r="J21" s="233"/>
+      <c r="K21" s="233"/>
+      <c r="L21" s="233"/>
+      <c r="M21" s="234"/>
+      <c r="N21" s="229"/>
+      <c r="O21" s="230"/>
+      <c r="P21" s="231"/>
+      <c r="Q21" s="222"/>
+      <c r="R21" s="228"/>
+      <c r="S21" s="228"/>
+    </row>
+    <row r="22" spans="1:19" ht="30" customHeight="1">
+      <c r="A22" s="222"/>
+      <c r="B22" s="222"/>
+      <c r="C22" s="223"/>
+      <c r="D22" s="223"/>
+      <c r="E22" s="223"/>
+      <c r="F22" s="223"/>
+      <c r="G22" s="223"/>
+      <c r="H22" s="232"/>
+      <c r="I22" s="233"/>
+      <c r="J22" s="233"/>
+      <c r="K22" s="233"/>
+      <c r="L22" s="233"/>
+      <c r="M22" s="234"/>
+      <c r="N22" s="229"/>
+      <c r="O22" s="230"/>
+      <c r="P22" s="231"/>
+      <c r="Q22" s="222"/>
+      <c r="R22" s="228"/>
+      <c r="S22" s="228"/>
+    </row>
+    <row r="23" spans="1:19" ht="30" customHeight="1">
+      <c r="A23" s="222"/>
+      <c r="B23" s="222"/>
+      <c r="C23" s="223"/>
+      <c r="D23" s="223"/>
+      <c r="E23" s="223"/>
+      <c r="F23" s="223"/>
+      <c r="G23" s="223"/>
+      <c r="H23" s="232"/>
+      <c r="I23" s="233"/>
+      <c r="J23" s="233"/>
+      <c r="K23" s="233"/>
+      <c r="L23" s="233"/>
+      <c r="M23" s="234"/>
+      <c r="N23" s="229"/>
+      <c r="O23" s="230"/>
+      <c r="P23" s="231"/>
+      <c r="Q23" s="222"/>
+      <c r="R23" s="228"/>
+      <c r="S23" s="228"/>
+    </row>
+    <row r="24" spans="1:19" ht="30" customHeight="1">
+      <c r="A24" s="222"/>
+      <c r="B24" s="222"/>
+      <c r="C24" s="223"/>
+      <c r="D24" s="223"/>
+      <c r="E24" s="223"/>
+      <c r="F24" s="223"/>
+      <c r="G24" s="223"/>
+      <c r="H24" s="232"/>
+      <c r="I24" s="233"/>
+      <c r="J24" s="233"/>
+      <c r="K24" s="233"/>
+      <c r="L24" s="233"/>
+      <c r="M24" s="234"/>
+      <c r="N24" s="229"/>
+      <c r="O24" s="230"/>
+      <c r="P24" s="231"/>
+      <c r="Q24" s="222"/>
+      <c r="R24" s="228"/>
+      <c r="S24" s="228"/>
+    </row>
+    <row r="25" spans="1:19" ht="30" customHeight="1">
+      <c r="A25" s="222"/>
+      <c r="B25" s="222"/>
+      <c r="C25" s="223"/>
+      <c r="D25" s="223"/>
+      <c r="E25" s="223"/>
+      <c r="F25" s="223"/>
+      <c r="G25" s="223"/>
+      <c r="H25" s="232"/>
+      <c r="I25" s="233"/>
+      <c r="J25" s="233"/>
+      <c r="K25" s="233"/>
+      <c r="L25" s="233"/>
+      <c r="M25" s="234"/>
+      <c r="N25" s="229"/>
+      <c r="O25" s="230"/>
+      <c r="P25" s="231"/>
+      <c r="Q25" s="222"/>
+      <c r="R25" s="228"/>
+      <c r="S25" s="228"/>
+    </row>
+    <row r="26" spans="1:19" ht="30" customHeight="1">
+      <c r="A26" s="222"/>
+      <c r="B26" s="222"/>
+      <c r="C26" s="223"/>
+      <c r="D26" s="223"/>
+      <c r="E26" s="223"/>
+      <c r="F26" s="223"/>
+      <c r="G26" s="223"/>
+      <c r="H26" s="232"/>
+      <c r="I26" s="233"/>
+      <c r="J26" s="233"/>
+      <c r="K26" s="233"/>
+      <c r="L26" s="233"/>
+      <c r="M26" s="234"/>
+      <c r="N26" s="229"/>
+      <c r="O26" s="230"/>
+      <c r="P26" s="231"/>
+      <c r="Q26" s="222"/>
+      <c r="R26" s="228"/>
+      <c r="S26" s="228"/>
+    </row>
+    <row r="27" spans="1:19" ht="30" customHeight="1">
+      <c r="A27" s="222"/>
+      <c r="B27" s="222"/>
+      <c r="C27" s="223"/>
+      <c r="D27" s="223"/>
+      <c r="E27" s="223"/>
+      <c r="F27" s="223"/>
+      <c r="G27" s="223"/>
+      <c r="H27" s="232"/>
+      <c r="I27" s="233"/>
+      <c r="J27" s="233"/>
+      <c r="K27" s="233"/>
+      <c r="L27" s="233"/>
+      <c r="M27" s="234"/>
+      <c r="N27" s="229"/>
+      <c r="O27" s="230"/>
+      <c r="P27" s="231"/>
+      <c r="Q27" s="222"/>
+      <c r="R27" s="228"/>
+      <c r="S27" s="228"/>
+    </row>
+    <row r="28" spans="1:19" ht="30" customHeight="1">
+      <c r="A28" s="222"/>
+      <c r="B28" s="222"/>
+      <c r="C28" s="223"/>
+      <c r="D28" s="223"/>
+      <c r="E28" s="223"/>
+      <c r="F28" s="223"/>
+      <c r="G28" s="223"/>
+      <c r="H28" s="232"/>
+      <c r="I28" s="233"/>
+      <c r="J28" s="233"/>
+      <c r="K28" s="233"/>
+      <c r="L28" s="233"/>
+      <c r="M28" s="234"/>
+      <c r="N28" s="229"/>
+      <c r="O28" s="230"/>
+      <c r="P28" s="231"/>
+      <c r="Q28" s="222"/>
+      <c r="R28" s="228"/>
+      <c r="S28" s="228"/>
+    </row>
+    <row r="29" spans="1:19" ht="30" customHeight="1">
+      <c r="A29" s="222"/>
+      <c r="B29" s="222"/>
+      <c r="C29" s="223"/>
+      <c r="D29" s="223"/>
+      <c r="E29" s="223"/>
+      <c r="F29" s="223"/>
+      <c r="G29" s="223"/>
+      <c r="H29" s="232"/>
+      <c r="I29" s="233"/>
+      <c r="J29" s="233"/>
+      <c r="K29" s="233"/>
+      <c r="L29" s="233"/>
+      <c r="M29" s="234"/>
+      <c r="N29" s="229"/>
+      <c r="O29" s="230"/>
+      <c r="P29" s="231"/>
+      <c r="Q29" s="222"/>
+      <c r="R29" s="228"/>
+      <c r="S29" s="228"/>
+    </row>
+    <row r="30" spans="1:19" ht="30" customHeight="1">
+      <c r="A30" s="222"/>
+      <c r="B30" s="222"/>
+      <c r="C30" s="223"/>
+      <c r="D30" s="223"/>
+      <c r="E30" s="223"/>
+      <c r="F30" s="223"/>
+      <c r="G30" s="223"/>
+      <c r="H30" s="232"/>
+      <c r="I30" s="233"/>
+      <c r="J30" s="233"/>
+      <c r="K30" s="233"/>
+      <c r="L30" s="233"/>
+      <c r="M30" s="234"/>
+      <c r="N30" s="229"/>
+      <c r="O30" s="230"/>
+      <c r="P30" s="231"/>
+      <c r="Q30" s="222"/>
+      <c r="R30" s="228"/>
+      <c r="S30" s="228"/>
+    </row>
+    <row r="31" spans="1:19" ht="30" customHeight="1">
+      <c r="A31" s="222"/>
+      <c r="B31" s="222"/>
+      <c r="C31" s="223"/>
+      <c r="D31" s="223"/>
+      <c r="E31" s="223"/>
+      <c r="F31" s="223"/>
+      <c r="G31" s="223"/>
+      <c r="H31" s="232"/>
+      <c r="I31" s="233"/>
+      <c r="J31" s="233"/>
+      <c r="K31" s="233"/>
+      <c r="L31" s="233"/>
+      <c r="M31" s="234"/>
+      <c r="N31" s="229"/>
+      <c r="O31" s="230"/>
+      <c r="P31" s="231"/>
+      <c r="Q31" s="222"/>
+      <c r="R31" s="228"/>
+      <c r="S31" s="228"/>
+    </row>
+    <row r="32" spans="1:19" ht="30" customHeight="1">
+      <c r="A32" s="222"/>
+      <c r="B32" s="222"/>
+      <c r="C32" s="223"/>
+      <c r="D32" s="223"/>
+      <c r="E32" s="223"/>
+      <c r="F32" s="223"/>
+      <c r="G32" s="223"/>
+      <c r="H32" s="232"/>
+      <c r="I32" s="233"/>
+      <c r="J32" s="233"/>
+      <c r="K32" s="233"/>
+      <c r="L32" s="233"/>
+      <c r="M32" s="234"/>
+      <c r="N32" s="229"/>
+      <c r="O32" s="230"/>
+      <c r="P32" s="231"/>
+      <c r="Q32" s="222"/>
+      <c r="R32" s="228"/>
+      <c r="S32" s="228"/>
+    </row>
+    <row r="33" spans="1:19" ht="30" customHeight="1">
+      <c r="A33" s="222"/>
+      <c r="B33" s="222"/>
+      <c r="C33" s="223"/>
+      <c r="D33" s="223"/>
+      <c r="E33" s="223"/>
+      <c r="F33" s="223"/>
+      <c r="G33" s="223"/>
+      <c r="H33" s="232"/>
+      <c r="I33" s="233"/>
+      <c r="J33" s="233"/>
+      <c r="K33" s="233"/>
+      <c r="L33" s="233"/>
+      <c r="M33" s="234"/>
+      <c r="N33" s="229"/>
+      <c r="O33" s="230"/>
+      <c r="P33" s="231"/>
+      <c r="Q33" s="222"/>
+      <c r="R33" s="228"/>
+      <c r="S33" s="228"/>
+    </row>
+    <row r="34" spans="1:19" ht="30" customHeight="1">
+      <c r="A34" s="222"/>
+      <c r="B34" s="222"/>
+      <c r="C34" s="223"/>
+      <c r="D34" s="223"/>
+      <c r="E34" s="223"/>
+      <c r="F34" s="223"/>
+      <c r="G34" s="223"/>
+      <c r="H34" s="232"/>
+      <c r="I34" s="233"/>
+      <c r="J34" s="233"/>
+      <c r="K34" s="233"/>
+      <c r="L34" s="233"/>
+      <c r="M34" s="234"/>
+      <c r="N34" s="229"/>
+      <c r="O34" s="230"/>
+      <c r="P34" s="231"/>
+      <c r="Q34" s="222"/>
+      <c r="R34" s="228"/>
+      <c r="S34" s="228"/>
+    </row>
+    <row r="35" spans="1:19" ht="30" customHeight="1">
+      <c r="A35" s="222"/>
+      <c r="B35" s="222"/>
+      <c r="C35" s="223"/>
+      <c r="D35" s="223"/>
+      <c r="E35" s="223"/>
+      <c r="F35" s="223"/>
+      <c r="G35" s="223"/>
+      <c r="H35" s="232"/>
+      <c r="I35" s="233"/>
+      <c r="J35" s="233"/>
+      <c r="K35" s="233"/>
+      <c r="L35" s="233"/>
+      <c r="M35" s="234"/>
+      <c r="N35" s="229"/>
+      <c r="O35" s="230"/>
+      <c r="P35" s="231"/>
+      <c r="Q35" s="222"/>
+      <c r="R35" s="228"/>
+      <c r="S35" s="228"/>
+    </row>
+    <row r="36" spans="1:19" ht="30" customHeight="1">
+      <c r="A36" s="222"/>
+      <c r="B36" s="222"/>
+      <c r="C36" s="223"/>
+      <c r="D36" s="223"/>
+      <c r="E36" s="223"/>
+      <c r="F36" s="223"/>
+      <c r="G36" s="223"/>
+      <c r="H36" s="232"/>
+      <c r="I36" s="233"/>
+      <c r="J36" s="233"/>
+      <c r="K36" s="233"/>
+      <c r="L36" s="233"/>
+      <c r="M36" s="234"/>
+      <c r="N36" s="229"/>
+      <c r="O36" s="230"/>
+      <c r="P36" s="231"/>
+      <c r="Q36" s="222"/>
+      <c r="R36" s="228"/>
+      <c r="S36" s="228"/>
+    </row>
+    <row r="37" spans="1:19" ht="30" customHeight="1">
+      <c r="A37" s="222"/>
+      <c r="B37" s="222"/>
+      <c r="C37" s="223"/>
+      <c r="D37" s="223"/>
+      <c r="E37" s="223"/>
+      <c r="F37" s="223"/>
+      <c r="G37" s="223"/>
+      <c r="H37" s="232"/>
+      <c r="I37" s="233"/>
+      <c r="J37" s="233"/>
+      <c r="K37" s="233"/>
+      <c r="L37" s="233"/>
+      <c r="M37" s="234"/>
+      <c r="N37" s="229"/>
+      <c r="O37" s="230"/>
+      <c r="P37" s="231"/>
+      <c r="Q37" s="222"/>
+      <c r="R37" s="228"/>
+      <c r="S37" s="228"/>
+    </row>
+    <row r="38" spans="1:19" ht="30" customHeight="1">
+      <c r="A38" s="222"/>
+      <c r="B38" s="222"/>
+      <c r="C38" s="223"/>
+      <c r="D38" s="223"/>
+      <c r="E38" s="223"/>
+      <c r="F38" s="223"/>
+      <c r="G38" s="223"/>
+      <c r="H38" s="232"/>
+      <c r="I38" s="233"/>
+      <c r="J38" s="233"/>
+      <c r="K38" s="233"/>
+      <c r="L38" s="233"/>
+      <c r="M38" s="234"/>
+      <c r="N38" s="229"/>
+      <c r="O38" s="230"/>
+      <c r="P38" s="231"/>
+      <c r="Q38" s="222"/>
+      <c r="R38" s="228"/>
+      <c r="S38" s="228"/>
+    </row>
+    <row r="39" spans="1:19" ht="30" customHeight="1">
+      <c r="A39" s="222"/>
+      <c r="B39" s="222"/>
+      <c r="C39" s="223"/>
+      <c r="D39" s="223"/>
+      <c r="E39" s="223"/>
+      <c r="F39" s="223"/>
+      <c r="G39" s="223"/>
+      <c r="H39" s="232"/>
+      <c r="I39" s="233"/>
+      <c r="J39" s="233"/>
+      <c r="K39" s="233"/>
+      <c r="L39" s="233"/>
+      <c r="M39" s="234"/>
+      <c r="N39" s="229"/>
+      <c r="O39" s="230"/>
+      <c r="P39" s="231"/>
+      <c r="Q39" s="222"/>
+      <c r="R39" s="228"/>
+      <c r="S39" s="228"/>
+    </row>
+    <row r="40" spans="1:19" ht="30" customHeight="1">
+      <c r="A40" s="222"/>
+      <c r="B40" s="222"/>
+      <c r="C40" s="223"/>
+      <c r="D40" s="223"/>
+      <c r="E40" s="223"/>
+      <c r="F40" s="223"/>
+      <c r="G40" s="223"/>
+      <c r="H40" s="232"/>
+      <c r="I40" s="233"/>
+      <c r="J40" s="233"/>
+      <c r="K40" s="233"/>
+      <c r="L40" s="233"/>
+      <c r="M40" s="234"/>
+      <c r="N40" s="229"/>
+      <c r="O40" s="230"/>
+      <c r="P40" s="231"/>
+      <c r="Q40" s="222"/>
+      <c r="R40" s="228"/>
+      <c r="S40" s="228"/>
+    </row>
+    <row r="41" spans="1:19" ht="30" customHeight="1">
+      <c r="A41" s="222"/>
+      <c r="B41" s="222"/>
+      <c r="C41" s="223"/>
+      <c r="D41" s="223"/>
+      <c r="E41" s="223"/>
+      <c r="F41" s="223"/>
+      <c r="G41" s="223"/>
+      <c r="H41" s="232"/>
+      <c r="I41" s="233"/>
+      <c r="J41" s="233"/>
+      <c r="K41" s="233"/>
+      <c r="L41" s="233"/>
+      <c r="M41" s="234"/>
+      <c r="N41" s="229"/>
+      <c r="O41" s="230"/>
+      <c r="P41" s="231"/>
+      <c r="Q41" s="222"/>
+      <c r="R41" s="228"/>
+      <c r="S41" s="228"/>
+    </row>
+    <row r="42" spans="1:19" ht="30" customHeight="1">
+      <c r="A42" s="222"/>
+      <c r="B42" s="222"/>
+      <c r="C42" s="223"/>
+      <c r="D42" s="223"/>
+      <c r="E42" s="223"/>
+      <c r="F42" s="223"/>
+      <c r="G42" s="223"/>
+      <c r="H42" s="232"/>
+      <c r="I42" s="233"/>
+      <c r="J42" s="233"/>
+      <c r="K42" s="233"/>
+      <c r="L42" s="233"/>
+      <c r="M42" s="234"/>
+      <c r="N42" s="229"/>
+      <c r="O42" s="230"/>
+      <c r="P42" s="231"/>
+      <c r="Q42" s="222"/>
+      <c r="R42" s="228"/>
+      <c r="S42" s="228"/>
+    </row>
+    <row r="43" spans="1:19" ht="30" customHeight="1">
+      <c r="A43" s="222"/>
+      <c r="B43" s="222"/>
+      <c r="C43" s="223"/>
+      <c r="D43" s="223"/>
+      <c r="E43" s="223"/>
+      <c r="F43" s="223"/>
+      <c r="G43" s="223"/>
+      <c r="H43" s="232"/>
+      <c r="I43" s="233"/>
+      <c r="J43" s="233"/>
+      <c r="K43" s="233"/>
+      <c r="L43" s="233"/>
+      <c r="M43" s="234"/>
+      <c r="N43" s="229"/>
+      <c r="O43" s="230"/>
+      <c r="P43" s="231"/>
+      <c r="Q43" s="222"/>
+      <c r="R43" s="228"/>
+      <c r="S43" s="228"/>
+    </row>
+    <row r="44" spans="1:19" ht="30" customHeight="1">
+      <c r="A44" s="222"/>
+      <c r="B44" s="222"/>
+      <c r="C44" s="223"/>
+      <c r="D44" s="223"/>
+      <c r="E44" s="223"/>
+      <c r="F44" s="223"/>
+      <c r="G44" s="223"/>
+      <c r="H44" s="232"/>
+      <c r="I44" s="233"/>
+      <c r="J44" s="233"/>
+      <c r="K44" s="233"/>
+      <c r="L44" s="233"/>
+      <c r="M44" s="234"/>
+      <c r="N44" s="229"/>
+      <c r="O44" s="230"/>
+      <c r="P44" s="231"/>
+      <c r="Q44" s="222"/>
+      <c r="R44" s="228"/>
+      <c r="S44" s="228"/>
+    </row>
+    <row r="45" spans="1:19" ht="30" customHeight="1">
+      <c r="A45" s="222"/>
+      <c r="B45" s="222"/>
+      <c r="C45" s="223"/>
+      <c r="D45" s="223"/>
+      <c r="E45" s="223"/>
+      <c r="F45" s="223"/>
+      <c r="G45" s="223"/>
+      <c r="H45" s="232"/>
+      <c r="I45" s="233"/>
+      <c r="J45" s="233"/>
+      <c r="K45" s="233"/>
+      <c r="L45" s="233"/>
+      <c r="M45" s="234"/>
+      <c r="N45" s="229"/>
+      <c r="O45" s="230"/>
+      <c r="P45" s="231"/>
+      <c r="Q45" s="222"/>
+      <c r="R45" s="228"/>
+      <c r="S45" s="228"/>
+    </row>
+    <row r="46" spans="1:19" ht="30" customHeight="1">
+      <c r="A46" s="222"/>
+      <c r="B46" s="222"/>
+      <c r="C46" s="223"/>
+      <c r="D46" s="223"/>
+      <c r="E46" s="223"/>
+      <c r="F46" s="223"/>
+      <c r="G46" s="223"/>
+      <c r="H46" s="232"/>
+      <c r="I46" s="233"/>
+      <c r="J46" s="233"/>
+      <c r="K46" s="233"/>
+      <c r="L46" s="233"/>
+      <c r="M46" s="234"/>
+      <c r="N46" s="229"/>
+      <c r="O46" s="230"/>
+      <c r="P46" s="231"/>
+      <c r="Q46" s="222"/>
+      <c r="R46" s="228"/>
+      <c r="S46" s="228"/>
+    </row>
+    <row r="47" spans="1:19" ht="30" customHeight="1">
+      <c r="A47" s="222"/>
+      <c r="B47" s="222"/>
+      <c r="C47" s="223"/>
+      <c r="D47" s="223"/>
+      <c r="E47" s="223"/>
+      <c r="F47" s="223"/>
+      <c r="G47" s="223"/>
+      <c r="H47" s="232"/>
+      <c r="I47" s="233"/>
+      <c r="J47" s="233"/>
+      <c r="K47" s="233"/>
+      <c r="L47" s="233"/>
+      <c r="M47" s="234"/>
+      <c r="N47" s="229"/>
+      <c r="O47" s="230"/>
+      <c r="P47" s="231"/>
+      <c r="Q47" s="222"/>
+      <c r="R47" s="228"/>
+      <c r="S47" s="228"/>
+    </row>
+    <row r="48" spans="1:19" ht="30" customHeight="1">
+      <c r="A48" s="222"/>
+      <c r="B48" s="222"/>
+      <c r="C48" s="223"/>
+      <c r="D48" s="223"/>
+      <c r="E48" s="223"/>
+      <c r="F48" s="223"/>
+      <c r="G48" s="223"/>
+      <c r="H48" s="232"/>
+      <c r="I48" s="233"/>
+      <c r="J48" s="233"/>
+      <c r="K48" s="233"/>
+      <c r="L48" s="233"/>
+      <c r="M48" s="234"/>
+      <c r="N48" s="229"/>
+      <c r="O48" s="230"/>
+      <c r="P48" s="231"/>
+      <c r="Q48" s="222"/>
+      <c r="R48" s="228"/>
+      <c r="S48" s="228"/>
+    </row>
+    <row r="49" spans="1:19" ht="30" customHeight="1">
+      <c r="A49" s="222"/>
+      <c r="B49" s="222"/>
+      <c r="C49" s="223"/>
+      <c r="D49" s="223"/>
+      <c r="E49" s="223"/>
+      <c r="F49" s="223"/>
+      <c r="G49" s="223"/>
+      <c r="H49" s="232"/>
+      <c r="I49" s="233"/>
+      <c r="J49" s="233"/>
+      <c r="K49" s="233"/>
+      <c r="L49" s="233"/>
+      <c r="M49" s="234"/>
+      <c r="N49" s="229"/>
+      <c r="O49" s="230"/>
+      <c r="P49" s="231"/>
+      <c r="Q49" s="222"/>
+      <c r="R49" s="228"/>
+      <c r="S49" s="228"/>
+    </row>
+    <row r="50" spans="1:19" ht="30" customHeight="1">
+      <c r="A50" s="222"/>
+      <c r="B50" s="222"/>
+      <c r="C50" s="223"/>
+      <c r="D50" s="223"/>
+      <c r="E50" s="223"/>
+      <c r="F50" s="223"/>
+      <c r="G50" s="223"/>
+      <c r="H50" s="232"/>
+      <c r="I50" s="233"/>
+      <c r="J50" s="233"/>
+      <c r="K50" s="233"/>
+      <c r="L50" s="233"/>
+      <c r="M50" s="234"/>
+      <c r="N50" s="229"/>
+      <c r="O50" s="230"/>
+      <c r="P50" s="231"/>
+      <c r="Q50" s="222"/>
+      <c r="R50" s="228"/>
+      <c r="S50" s="228"/>
+    </row>
+    <row r="51" spans="1:19" ht="30" customHeight="1">
+      <c r="A51" s="222"/>
+      <c r="B51" s="222"/>
+      <c r="C51" s="223"/>
+      <c r="D51" s="223"/>
+      <c r="E51" s="223"/>
+      <c r="F51" s="223"/>
+      <c r="G51" s="223"/>
+      <c r="H51" s="232"/>
+      <c r="I51" s="233"/>
+      <c r="J51" s="233"/>
+      <c r="K51" s="233"/>
+      <c r="L51" s="233"/>
+      <c r="M51" s="234"/>
+      <c r="N51" s="229"/>
+      <c r="O51" s="230"/>
+      <c r="P51" s="231"/>
+      <c r="Q51" s="222"/>
+      <c r="R51" s="228"/>
+      <c r="S51" s="228"/>
+    </row>
+    <row r="52" spans="1:19" ht="30" customHeight="1">
+      <c r="A52" s="222"/>
+      <c r="B52" s="222"/>
+      <c r="C52" s="223"/>
+      <c r="D52" s="223"/>
+      <c r="E52" s="223"/>
+      <c r="F52" s="223"/>
+      <c r="G52" s="223"/>
+      <c r="H52" s="232"/>
+      <c r="I52" s="233"/>
+      <c r="J52" s="233"/>
+      <c r="K52" s="233"/>
+      <c r="L52" s="233"/>
+      <c r="M52" s="234"/>
+      <c r="N52" s="229"/>
+      <c r="O52" s="230"/>
+      <c r="P52" s="231"/>
+      <c r="Q52" s="222"/>
+      <c r="R52" s="228"/>
+      <c r="S52" s="228"/>
+    </row>
+  </sheetData>
+  <mergeCells count="205">
+    <mergeCell ref="C52:G52"/>
+    <mergeCell ref="H52:M52"/>
+    <mergeCell ref="N52:P52"/>
+    <mergeCell ref="R52:S52"/>
+    <mergeCell ref="C50:G50"/>
+    <mergeCell ref="H50:M50"/>
+    <mergeCell ref="N50:P50"/>
+    <mergeCell ref="R50:S50"/>
+    <mergeCell ref="C51:G51"/>
+    <mergeCell ref="H51:M51"/>
+    <mergeCell ref="N51:P51"/>
+    <mergeCell ref="R51:S51"/>
+    <mergeCell ref="C48:G48"/>
+    <mergeCell ref="H48:M48"/>
+    <mergeCell ref="N48:P48"/>
+    <mergeCell ref="R48:S48"/>
+    <mergeCell ref="C49:G49"/>
+    <mergeCell ref="H49:M49"/>
+    <mergeCell ref="N49:P49"/>
+    <mergeCell ref="R49:S49"/>
+    <mergeCell ref="C46:G46"/>
+    <mergeCell ref="H46:M46"/>
+    <mergeCell ref="N46:P46"/>
+    <mergeCell ref="R46:S46"/>
+    <mergeCell ref="C47:G47"/>
+    <mergeCell ref="H47:M47"/>
+    <mergeCell ref="N47:P47"/>
+    <mergeCell ref="R47:S47"/>
+    <mergeCell ref="C44:G44"/>
+    <mergeCell ref="H44:M44"/>
+    <mergeCell ref="N44:P44"/>
+    <mergeCell ref="R44:S44"/>
+    <mergeCell ref="C45:G45"/>
+    <mergeCell ref="H45:M45"/>
+    <mergeCell ref="N45:P45"/>
+    <mergeCell ref="R45:S45"/>
+    <mergeCell ref="C42:G42"/>
+    <mergeCell ref="H42:M42"/>
+    <mergeCell ref="N42:P42"/>
+    <mergeCell ref="R42:S42"/>
+    <mergeCell ref="C43:G43"/>
+    <mergeCell ref="H43:M43"/>
+    <mergeCell ref="N43:P43"/>
+    <mergeCell ref="R43:S43"/>
+    <mergeCell ref="C40:G40"/>
+    <mergeCell ref="H40:M40"/>
+    <mergeCell ref="N40:P40"/>
+    <mergeCell ref="R40:S40"/>
+    <mergeCell ref="C41:G41"/>
+    <mergeCell ref="H41:M41"/>
+    <mergeCell ref="N41:P41"/>
+    <mergeCell ref="R41:S41"/>
+    <mergeCell ref="C38:G38"/>
+    <mergeCell ref="H38:M38"/>
+    <mergeCell ref="N38:P38"/>
+    <mergeCell ref="R38:S38"/>
+    <mergeCell ref="C39:G39"/>
+    <mergeCell ref="H39:M39"/>
+    <mergeCell ref="N39:P39"/>
+    <mergeCell ref="R39:S39"/>
+    <mergeCell ref="C36:G36"/>
+    <mergeCell ref="H36:M36"/>
+    <mergeCell ref="N36:P36"/>
+    <mergeCell ref="R36:S36"/>
+    <mergeCell ref="C37:G37"/>
+    <mergeCell ref="H37:M37"/>
+    <mergeCell ref="N37:P37"/>
+    <mergeCell ref="R37:S37"/>
+    <mergeCell ref="C34:G34"/>
+    <mergeCell ref="H34:M34"/>
+    <mergeCell ref="N34:P34"/>
+    <mergeCell ref="R34:S34"/>
+    <mergeCell ref="C35:G35"/>
+    <mergeCell ref="H35:M35"/>
+    <mergeCell ref="N35:P35"/>
+    <mergeCell ref="R35:S35"/>
+    <mergeCell ref="C32:G32"/>
+    <mergeCell ref="H32:M32"/>
+    <mergeCell ref="N32:P32"/>
+    <mergeCell ref="R32:S32"/>
+    <mergeCell ref="C33:G33"/>
+    <mergeCell ref="H33:M33"/>
+    <mergeCell ref="N33:P33"/>
+    <mergeCell ref="R33:S33"/>
+    <mergeCell ref="C30:G30"/>
+    <mergeCell ref="H30:M30"/>
+    <mergeCell ref="N30:P30"/>
+    <mergeCell ref="R30:S30"/>
+    <mergeCell ref="C31:G31"/>
+    <mergeCell ref="H31:M31"/>
+    <mergeCell ref="N31:P31"/>
+    <mergeCell ref="R31:S31"/>
+    <mergeCell ref="C28:G28"/>
+    <mergeCell ref="H28:M28"/>
+    <mergeCell ref="N28:P28"/>
+    <mergeCell ref="R28:S28"/>
+    <mergeCell ref="C29:G29"/>
+    <mergeCell ref="H29:M29"/>
+    <mergeCell ref="N29:P29"/>
+    <mergeCell ref="R29:S29"/>
+    <mergeCell ref="C26:G26"/>
+    <mergeCell ref="H26:M26"/>
+    <mergeCell ref="N26:P26"/>
+    <mergeCell ref="R26:S26"/>
+    <mergeCell ref="C27:G27"/>
+    <mergeCell ref="H27:M27"/>
+    <mergeCell ref="N27:P27"/>
+    <mergeCell ref="R27:S27"/>
+    <mergeCell ref="C24:G24"/>
+    <mergeCell ref="H24:M24"/>
+    <mergeCell ref="N24:P24"/>
+    <mergeCell ref="R24:S24"/>
+    <mergeCell ref="C25:G25"/>
+    <mergeCell ref="H25:M25"/>
+    <mergeCell ref="N25:P25"/>
+    <mergeCell ref="R25:S25"/>
+    <mergeCell ref="C22:G22"/>
+    <mergeCell ref="H22:M22"/>
+    <mergeCell ref="N22:P22"/>
+    <mergeCell ref="R22:S22"/>
+    <mergeCell ref="C23:G23"/>
+    <mergeCell ref="H23:M23"/>
+    <mergeCell ref="N23:P23"/>
+    <mergeCell ref="R23:S23"/>
+    <mergeCell ref="C20:G20"/>
+    <mergeCell ref="H20:M20"/>
+    <mergeCell ref="N20:P20"/>
+    <mergeCell ref="R20:S20"/>
+    <mergeCell ref="C21:G21"/>
+    <mergeCell ref="H21:M21"/>
+    <mergeCell ref="N21:P21"/>
+    <mergeCell ref="R21:S21"/>
+    <mergeCell ref="C18:G18"/>
+    <mergeCell ref="H18:M18"/>
+    <mergeCell ref="N18:P18"/>
+    <mergeCell ref="R18:S18"/>
+    <mergeCell ref="C19:G19"/>
+    <mergeCell ref="H19:M19"/>
+    <mergeCell ref="N19:P19"/>
+    <mergeCell ref="R19:S19"/>
+    <mergeCell ref="C16:G16"/>
+    <mergeCell ref="H16:M16"/>
+    <mergeCell ref="N16:P16"/>
+    <mergeCell ref="R16:S16"/>
+    <mergeCell ref="C17:G17"/>
+    <mergeCell ref="H17:M17"/>
+    <mergeCell ref="N17:P17"/>
+    <mergeCell ref="R17:S17"/>
+    <mergeCell ref="C14:G14"/>
+    <mergeCell ref="H14:M14"/>
+    <mergeCell ref="N14:P14"/>
+    <mergeCell ref="R14:S14"/>
+    <mergeCell ref="C15:G15"/>
+    <mergeCell ref="H15:M15"/>
+    <mergeCell ref="N15:P15"/>
+    <mergeCell ref="R15:S15"/>
+    <mergeCell ref="C12:G12"/>
+    <mergeCell ref="H12:M12"/>
+    <mergeCell ref="N12:P12"/>
+    <mergeCell ref="R12:S12"/>
+    <mergeCell ref="C13:G13"/>
+    <mergeCell ref="H13:M13"/>
+    <mergeCell ref="N13:P13"/>
+    <mergeCell ref="R13:S13"/>
+    <mergeCell ref="C10:G10"/>
+    <mergeCell ref="H10:M10"/>
+    <mergeCell ref="N10:P10"/>
+    <mergeCell ref="R10:S10"/>
+    <mergeCell ref="C11:G11"/>
+    <mergeCell ref="H11:M11"/>
+    <mergeCell ref="N11:P11"/>
+    <mergeCell ref="R11:S11"/>
+    <mergeCell ref="C8:G8"/>
+    <mergeCell ref="H8:M8"/>
+    <mergeCell ref="N8:P8"/>
+    <mergeCell ref="R8:S8"/>
+    <mergeCell ref="C9:G9"/>
+    <mergeCell ref="H9:M9"/>
+    <mergeCell ref="N9:P9"/>
+    <mergeCell ref="R9:S9"/>
+    <mergeCell ref="C6:G6"/>
+    <mergeCell ref="H6:M6"/>
+    <mergeCell ref="N6:P6"/>
+    <mergeCell ref="R6:S6"/>
+    <mergeCell ref="C7:G7"/>
+    <mergeCell ref="H7:M7"/>
+    <mergeCell ref="N7:P7"/>
+    <mergeCell ref="R7:S7"/>
+    <mergeCell ref="C4:G4"/>
+    <mergeCell ref="H4:M4"/>
+    <mergeCell ref="N4:P4"/>
+    <mergeCell ref="R4:S4"/>
+    <mergeCell ref="C5:G5"/>
+    <mergeCell ref="H5:M5"/>
+    <mergeCell ref="N5:P5"/>
+    <mergeCell ref="R5:S5"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="F1:M1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="R1:S1"/>
+    <mergeCell ref="C2:E2"/>
+    <mergeCell ref="F2:M2"/>
+    <mergeCell ref="O2:P2"/>
+    <mergeCell ref="R2:S2"/>
+  </mergeCells>
+  <phoneticPr fontId="8"/>
+  <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.31496062992125984" bottom="0.27559055118110237" header="0.35433070866141736" footer="0.15748031496062992"/>
+  <pageSetup paperSize="9" orientation="landscape" horizontalDpi="4294967293" r:id="rId1"/>
+  <headerFooter alignWithMargins="0"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E9AF3C1D-3E84-4C0E-A4B6-DFCB3FB52326}">
   <dimension ref="A1:J1000"/>
@@ -4439,19 +8512,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="60" t="s">
+      <c r="A1" s="89" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="61"/>
-      <c r="C1" s="62"/>
-      <c r="D1" s="69" t="s">
+      <c r="B1" s="90"/>
+      <c r="C1" s="91"/>
+      <c r="D1" s="98" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="70"/>
-      <c r="F1" s="69" t="s">
+      <c r="E1" s="83"/>
+      <c r="F1" s="98" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="70"/>
+      <c r="G1" s="83"/>
       <c r="H1" s="34" t="s">
         <v>6</v>
       </c>
@@ -4463,192 +8536,192 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="63"/>
-      <c r="B2" s="64"/>
-      <c r="C2" s="65"/>
-      <c r="D2" s="71" t="s">
-        <v>72</v>
-      </c>
-      <c r="E2" s="72"/>
-      <c r="F2" s="71">
+      <c r="A2" s="92"/>
+      <c r="B2" s="93"/>
+      <c r="C2" s="94"/>
+      <c r="D2" s="99" t="s">
+        <v>61</v>
+      </c>
+      <c r="E2" s="100"/>
+      <c r="F2" s="99">
         <v>56</v>
       </c>
-      <c r="G2" s="72"/>
-      <c r="H2" s="75">
+      <c r="G2" s="100"/>
+      <c r="H2" s="68">
         <v>45806</v>
       </c>
-      <c r="I2" s="89" t="s">
-        <v>71</v>
-      </c>
-      <c r="J2" s="90"/>
+      <c r="I2" s="77" t="s">
+        <v>60</v>
+      </c>
+      <c r="J2" s="78"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="63"/>
-      <c r="B3" s="64"/>
-      <c r="C3" s="65"/>
-      <c r="D3" s="73"/>
-      <c r="E3" s="65"/>
-      <c r="F3" s="73"/>
-      <c r="G3" s="65"/>
-      <c r="H3" s="76"/>
-      <c r="I3" s="76"/>
-      <c r="J3" s="91"/>
+      <c r="A3" s="92"/>
+      <c r="B3" s="93"/>
+      <c r="C3" s="94"/>
+      <c r="D3" s="101"/>
+      <c r="E3" s="94"/>
+      <c r="F3" s="101"/>
+      <c r="G3" s="94"/>
+      <c r="H3" s="69"/>
+      <c r="I3" s="69"/>
+      <c r="J3" s="79"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="66"/>
-      <c r="B4" s="67"/>
-      <c r="C4" s="68"/>
-      <c r="D4" s="74"/>
-      <c r="E4" s="68"/>
-      <c r="F4" s="74"/>
-      <c r="G4" s="68"/>
-      <c r="H4" s="77"/>
-      <c r="I4" s="77"/>
-      <c r="J4" s="92"/>
+      <c r="A4" s="95"/>
+      <c r="B4" s="96"/>
+      <c r="C4" s="97"/>
+      <c r="D4" s="102"/>
+      <c r="E4" s="97"/>
+      <c r="F4" s="102"/>
+      <c r="G4" s="97"/>
+      <c r="H4" s="70"/>
+      <c r="I4" s="70"/>
+      <c r="J4" s="80"/>
     </row>
     <row r="5" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A5" s="93" t="s">
+      <c r="A5" s="81" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="94"/>
-      <c r="C5" s="70"/>
-      <c r="D5" s="95" t="s">
-        <v>70</v>
-      </c>
-      <c r="E5" s="94"/>
-      <c r="F5" s="94"/>
-      <c r="G5" s="94"/>
-      <c r="H5" s="94"/>
-      <c r="I5" s="94"/>
-      <c r="J5" s="96"/>
+      <c r="B5" s="82"/>
+      <c r="C5" s="83"/>
+      <c r="D5" s="84" t="s">
+        <v>59</v>
+      </c>
+      <c r="E5" s="82"/>
+      <c r="F5" s="82"/>
+      <c r="G5" s="82"/>
+      <c r="H5" s="82"/>
+      <c r="I5" s="82"/>
+      <c r="J5" s="85"/>
     </row>
     <row r="6" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A6" s="78" t="s">
+      <c r="A6" s="71" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="79"/>
-      <c r="C6" s="80"/>
-      <c r="D6" s="88" t="s">
-        <v>69</v>
-      </c>
-      <c r="E6" s="79"/>
-      <c r="F6" s="79"/>
-      <c r="G6" s="79"/>
-      <c r="H6" s="79"/>
-      <c r="I6" s="79"/>
-      <c r="J6" s="82"/>
+      <c r="B6" s="66"/>
+      <c r="C6" s="61"/>
+      <c r="D6" s="65" t="s">
+        <v>58</v>
+      </c>
+      <c r="E6" s="66"/>
+      <c r="F6" s="66"/>
+      <c r="G6" s="66"/>
+      <c r="H6" s="66"/>
+      <c r="I6" s="66"/>
+      <c r="J6" s="67"/>
     </row>
     <row r="7" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A7" s="78" t="s">
+      <c r="A7" s="71" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="79"/>
-      <c r="C7" s="80"/>
-      <c r="D7" s="88" t="s">
-        <v>68</v>
-      </c>
-      <c r="E7" s="79"/>
-      <c r="F7" s="79"/>
-      <c r="G7" s="79"/>
-      <c r="H7" s="79"/>
-      <c r="I7" s="79"/>
-      <c r="J7" s="82"/>
+      <c r="B7" s="66"/>
+      <c r="C7" s="61"/>
+      <c r="D7" s="65" t="s">
+        <v>57</v>
+      </c>
+      <c r="E7" s="66"/>
+      <c r="F7" s="66"/>
+      <c r="G7" s="66"/>
+      <c r="H7" s="66"/>
+      <c r="I7" s="66"/>
+      <c r="J7" s="67"/>
     </row>
     <row r="8" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A8" s="78" t="s">
+      <c r="A8" s="71" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="79"/>
-      <c r="C8" s="80"/>
-      <c r="D8" s="81" t="s">
-        <v>118</v>
-      </c>
-      <c r="E8" s="79"/>
-      <c r="F8" s="79"/>
-      <c r="G8" s="79"/>
-      <c r="H8" s="79"/>
-      <c r="I8" s="79"/>
-      <c r="J8" s="82"/>
+      <c r="B8" s="66"/>
+      <c r="C8" s="61"/>
+      <c r="D8" s="62" t="s">
+        <v>107</v>
+      </c>
+      <c r="E8" s="66"/>
+      <c r="F8" s="66"/>
+      <c r="G8" s="66"/>
+      <c r="H8" s="66"/>
+      <c r="I8" s="66"/>
+      <c r="J8" s="67"/>
     </row>
     <row r="9" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A9" s="97" t="s">
+      <c r="A9" s="86" t="s">
         <v>13</v>
       </c>
-      <c r="B9" s="100" t="s">
+      <c r="B9" s="60" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="80"/>
-      <c r="D9" s="81" t="s">
-        <v>116</v>
-      </c>
-      <c r="E9" s="101"/>
-      <c r="F9" s="101"/>
-      <c r="G9" s="101"/>
-      <c r="H9" s="101"/>
-      <c r="I9" s="101"/>
-      <c r="J9" s="102"/>
+      <c r="C9" s="61"/>
+      <c r="D9" s="62" t="s">
+        <v>105</v>
+      </c>
+      <c r="E9" s="63"/>
+      <c r="F9" s="63"/>
+      <c r="G9" s="63"/>
+      <c r="H9" s="63"/>
+      <c r="I9" s="63"/>
+      <c r="J9" s="64"/>
     </row>
     <row r="10" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A10" s="98"/>
-      <c r="B10" s="100" t="s">
+      <c r="A10" s="87"/>
+      <c r="B10" s="60" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="80"/>
-      <c r="D10" s="88" t="s">
-        <v>104</v>
-      </c>
-      <c r="E10" s="79"/>
-      <c r="F10" s="79"/>
-      <c r="G10" s="79"/>
-      <c r="H10" s="79"/>
-      <c r="I10" s="79"/>
-      <c r="J10" s="82"/>
+      <c r="C10" s="61"/>
+      <c r="D10" s="65" t="s">
+        <v>93</v>
+      </c>
+      <c r="E10" s="66"/>
+      <c r="F10" s="66"/>
+      <c r="G10" s="66"/>
+      <c r="H10" s="66"/>
+      <c r="I10" s="66"/>
+      <c r="J10" s="67"/>
     </row>
     <row r="11" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A11" s="99"/>
-      <c r="B11" s="100" t="s">
+      <c r="A11" s="88"/>
+      <c r="B11" s="60" t="s">
         <v>16</v>
       </c>
-      <c r="C11" s="80"/>
-      <c r="D11" s="81" t="s">
-        <v>119</v>
-      </c>
-      <c r="E11" s="79"/>
-      <c r="F11" s="79"/>
-      <c r="G11" s="79"/>
-      <c r="H11" s="79"/>
-      <c r="I11" s="79"/>
-      <c r="J11" s="82"/>
+      <c r="C11" s="61"/>
+      <c r="D11" s="62" t="s">
+        <v>108</v>
+      </c>
+      <c r="E11" s="66"/>
+      <c r="F11" s="66"/>
+      <c r="G11" s="66"/>
+      <c r="H11" s="66"/>
+      <c r="I11" s="66"/>
+      <c r="J11" s="67"/>
     </row>
     <row r="12" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A12" s="78" t="s">
+      <c r="A12" s="71" t="s">
         <v>17</v>
       </c>
-      <c r="B12" s="79"/>
-      <c r="C12" s="80"/>
-      <c r="D12" s="81" t="s">
-        <v>117</v>
-      </c>
-      <c r="E12" s="79"/>
-      <c r="F12" s="79"/>
-      <c r="G12" s="79"/>
-      <c r="H12" s="79"/>
-      <c r="I12" s="79"/>
-      <c r="J12" s="82"/>
+      <c r="B12" s="66"/>
+      <c r="C12" s="61"/>
+      <c r="D12" s="62" t="s">
+        <v>106</v>
+      </c>
+      <c r="E12" s="66"/>
+      <c r="F12" s="66"/>
+      <c r="G12" s="66"/>
+      <c r="H12" s="66"/>
+      <c r="I12" s="66"/>
+      <c r="J12" s="67"/>
     </row>
     <row r="13" spans="1:10" ht="26.25" customHeight="1" thickBot="1">
-      <c r="A13" s="83" t="s">
+      <c r="A13" s="72" t="s">
         <v>18</v>
       </c>
-      <c r="B13" s="84"/>
-      <c r="C13" s="85"/>
-      <c r="D13" s="86"/>
-      <c r="E13" s="84"/>
-      <c r="F13" s="84"/>
-      <c r="G13" s="84"/>
-      <c r="H13" s="84"/>
-      <c r="I13" s="84"/>
-      <c r="J13" s="87"/>
+      <c r="B13" s="73"/>
+      <c r="C13" s="74"/>
+      <c r="D13" s="75"/>
+      <c r="E13" s="73"/>
+      <c r="F13" s="73"/>
+      <c r="G13" s="73"/>
+      <c r="H13" s="73"/>
+      <c r="I13" s="73"/>
+      <c r="J13" s="76"/>
     </row>
     <row r="14" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="15" spans="1:10" ht="12.75" customHeight="1"/>
@@ -5639,12 +9712,11 @@
     <row r="1000" s="32" customFormat="1" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="D9:J9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="D10:J10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="D11:J11"/>
+    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="F2:G4"/>
     <mergeCell ref="H2:H4"/>
     <mergeCell ref="A12:C12"/>
     <mergeCell ref="D12:J12"/>
@@ -5661,11 +9733,12 @@
     <mergeCell ref="A6:C6"/>
     <mergeCell ref="D6:J6"/>
     <mergeCell ref="A9:A11"/>
-    <mergeCell ref="A1:C4"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="D2:E4"/>
-    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="D9:J9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="D10:J10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="D11:J11"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.70833333333333304" right="0.70833333333333304" top="0.74791666666666701" bottom="0.74791666666666701" header="0" footer="0"/>
@@ -5712,17 +9785,19 @@
       <c r="B2" s="55"/>
       <c r="C2" s="114"/>
       <c r="D2" s="120" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="E2" s="121"/>
       <c r="F2" s="120" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="G2" s="121"/>
       <c r="H2" s="103">
         <v>45806</v>
       </c>
-      <c r="I2" s="106"/>
+      <c r="I2" s="106" t="s">
+        <v>109</v>
+      </c>
       <c r="J2" s="107"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
@@ -7132,7 +11207,7 @@
       <c r="B2" s="55"/>
       <c r="C2" s="114"/>
       <c r="D2" s="120" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="E2" s="121"/>
       <c r="F2" s="120">
@@ -7143,7 +11218,7 @@
         <v>45807</v>
       </c>
       <c r="I2" s="106" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="J2" s="107"/>
     </row>
@@ -8507,6 +12582,26 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F14BB6B-9FD4-43AC-874B-69CE8D52F69D}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData/>
+  <phoneticPr fontId="8"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4384AD6B-A867-4C22-AAAC-AE2176C4193B}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData/>
+  <phoneticPr fontId="8"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4822FDF5-2D4B-40C6-8317-DC586EFBF498}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -8521,19 +12616,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="135" t="s">
+      <c r="A1" s="137" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="136"/>
-      <c r="C1" s="137"/>
-      <c r="D1" s="139" t="s">
+      <c r="B1" s="138"/>
+      <c r="C1" s="139"/>
+      <c r="D1" s="141" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="140"/>
-      <c r="F1" s="139" t="s">
+      <c r="E1" s="142"/>
+      <c r="F1" s="141" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="140"/>
+      <c r="G1" s="142"/>
       <c r="H1" s="43" t="s">
         <v>6</v>
       </c>
@@ -8545,67 +12640,67 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="132"/>
-      <c r="B2" s="133"/>
-      <c r="C2" s="138"/>
-      <c r="D2" s="141" t="s">
-        <v>95</v>
-      </c>
-      <c r="E2" s="142"/>
-      <c r="F2" s="141">
+      <c r="A2" s="134"/>
+      <c r="B2" s="135"/>
+      <c r="C2" s="140"/>
+      <c r="D2" s="143" t="s">
+        <v>84</v>
+      </c>
+      <c r="E2" s="144"/>
+      <c r="F2" s="143">
         <v>56</v>
       </c>
-      <c r="G2" s="142"/>
-      <c r="H2" s="144">
+      <c r="G2" s="144"/>
+      <c r="H2" s="146">
         <v>45806</v>
       </c>
-      <c r="I2" s="146" t="s">
-        <v>94</v>
-      </c>
-      <c r="J2" s="147"/>
+      <c r="I2" s="148" t="s">
+        <v>83</v>
+      </c>
+      <c r="J2" s="149"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="132"/>
-      <c r="B3" s="133"/>
-      <c r="C3" s="138"/>
-      <c r="D3" s="143"/>
-      <c r="E3" s="138"/>
-      <c r="F3" s="143"/>
-      <c r="G3" s="138"/>
-      <c r="H3" s="145"/>
-      <c r="I3" s="145"/>
-      <c r="J3" s="148"/>
+      <c r="A3" s="134"/>
+      <c r="B3" s="135"/>
+      <c r="C3" s="140"/>
+      <c r="D3" s="145"/>
+      <c r="E3" s="140"/>
+      <c r="F3" s="145"/>
+      <c r="G3" s="140"/>
+      <c r="H3" s="147"/>
+      <c r="I3" s="147"/>
+      <c r="J3" s="150"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="132"/>
-      <c r="B4" s="133"/>
-      <c r="C4" s="138"/>
-      <c r="D4" s="143"/>
-      <c r="E4" s="138"/>
-      <c r="F4" s="143"/>
-      <c r="G4" s="138"/>
-      <c r="H4" s="145"/>
-      <c r="I4" s="145"/>
-      <c r="J4" s="148"/>
+      <c r="A4" s="134"/>
+      <c r="B4" s="135"/>
+      <c r="C4" s="140"/>
+      <c r="D4" s="145"/>
+      <c r="E4" s="140"/>
+      <c r="F4" s="145"/>
+      <c r="G4" s="140"/>
+      <c r="H4" s="147"/>
+      <c r="I4" s="147"/>
+      <c r="J4" s="150"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="149" t="s">
+      <c r="A5" s="151" t="s">
         <v>22</v>
       </c>
-      <c r="B5" s="150"/>
-      <c r="C5" s="140"/>
-      <c r="D5" s="151" t="s">
-        <v>103</v>
-      </c>
-      <c r="E5" s="150"/>
-      <c r="F5" s="150"/>
-      <c r="G5" s="150"/>
-      <c r="H5" s="150"/>
-      <c r="I5" s="150"/>
-      <c r="J5" s="152"/>
+      <c r="B5" s="152"/>
+      <c r="C5" s="142"/>
+      <c r="D5" s="153" t="s">
+        <v>92</v>
+      </c>
+      <c r="E5" s="152"/>
+      <c r="F5" s="152"/>
+      <c r="G5" s="152"/>
+      <c r="H5" s="152"/>
+      <c r="I5" s="152"/>
+      <c r="J5" s="154"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="153" t="s">
+      <c r="A6" s="130" t="s">
         <v>23</v>
       </c>
       <c r="B6" s="125"/>
@@ -8619,91 +12714,91 @@
       <c r="J6" s="128"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="129"/>
-      <c r="B7" s="130"/>
-      <c r="C7" s="130"/>
-      <c r="D7" s="130"/>
-      <c r="E7" s="130"/>
-      <c r="F7" s="130"/>
-      <c r="G7" s="130"/>
-      <c r="H7" s="130"/>
-      <c r="I7" s="130"/>
-      <c r="J7" s="131"/>
+      <c r="A7" s="131"/>
+      <c r="B7" s="132"/>
+      <c r="C7" s="132"/>
+      <c r="D7" s="132"/>
+      <c r="E7" s="132"/>
+      <c r="F7" s="132"/>
+      <c r="G7" s="132"/>
+      <c r="H7" s="132"/>
+      <c r="I7" s="132"/>
+      <c r="J7" s="133"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="132"/>
-      <c r="B8" s="133"/>
-      <c r="C8" s="133"/>
-      <c r="D8" s="133"/>
-      <c r="E8" s="133"/>
-      <c r="F8" s="133"/>
-      <c r="G8" s="133"/>
-      <c r="H8" s="133"/>
-      <c r="I8" s="133"/>
-      <c r="J8" s="134"/>
+      <c r="A8" s="134"/>
+      <c r="B8" s="135"/>
+      <c r="C8" s="135"/>
+      <c r="D8" s="135"/>
+      <c r="E8" s="135"/>
+      <c r="F8" s="135"/>
+      <c r="G8" s="135"/>
+      <c r="H8" s="135"/>
+      <c r="I8" s="135"/>
+      <c r="J8" s="136"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="132"/>
-      <c r="B9" s="133"/>
-      <c r="C9" s="133"/>
-      <c r="D9" s="133"/>
-      <c r="E9" s="133"/>
-      <c r="F9" s="133"/>
-      <c r="G9" s="133"/>
-      <c r="H9" s="133"/>
-      <c r="I9" s="133"/>
-      <c r="J9" s="134"/>
+      <c r="A9" s="134"/>
+      <c r="B9" s="135"/>
+      <c r="C9" s="135"/>
+      <c r="D9" s="135"/>
+      <c r="E9" s="135"/>
+      <c r="F9" s="135"/>
+      <c r="G9" s="135"/>
+      <c r="H9" s="135"/>
+      <c r="I9" s="135"/>
+      <c r="J9" s="136"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="132"/>
-      <c r="B10" s="133"/>
-      <c r="C10" s="133"/>
-      <c r="D10" s="133"/>
-      <c r="E10" s="133"/>
-      <c r="F10" s="133"/>
-      <c r="G10" s="133"/>
-      <c r="H10" s="133"/>
-      <c r="I10" s="133"/>
-      <c r="J10" s="134"/>
+      <c r="A10" s="134"/>
+      <c r="B10" s="135"/>
+      <c r="C10" s="135"/>
+      <c r="D10" s="135"/>
+      <c r="E10" s="135"/>
+      <c r="F10" s="135"/>
+      <c r="G10" s="135"/>
+      <c r="H10" s="135"/>
+      <c r="I10" s="135"/>
+      <c r="J10" s="136"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="132"/>
-      <c r="B11" s="133"/>
-      <c r="C11" s="133"/>
-      <c r="D11" s="133"/>
-      <c r="E11" s="133"/>
-      <c r="F11" s="133"/>
-      <c r="G11" s="133"/>
-      <c r="H11" s="133"/>
-      <c r="I11" s="133"/>
-      <c r="J11" s="134"/>
+      <c r="A11" s="134"/>
+      <c r="B11" s="135"/>
+      <c r="C11" s="135"/>
+      <c r="D11" s="135"/>
+      <c r="E11" s="135"/>
+      <c r="F11" s="135"/>
+      <c r="G11" s="135"/>
+      <c r="H11" s="135"/>
+      <c r="I11" s="135"/>
+      <c r="J11" s="136"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="132"/>
-      <c r="B12" s="133"/>
-      <c r="C12" s="133"/>
-      <c r="D12" s="133"/>
-      <c r="E12" s="133"/>
-      <c r="F12" s="133"/>
-      <c r="G12" s="133"/>
-      <c r="H12" s="133"/>
-      <c r="I12" s="133"/>
-      <c r="J12" s="134"/>
+      <c r="A12" s="134"/>
+      <c r="B12" s="135"/>
+      <c r="C12" s="135"/>
+      <c r="D12" s="135"/>
+      <c r="E12" s="135"/>
+      <c r="F12" s="135"/>
+      <c r="G12" s="135"/>
+      <c r="H12" s="135"/>
+      <c r="I12" s="135"/>
+      <c r="J12" s="136"/>
     </row>
     <row r="13" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A13" s="132"/>
-      <c r="B13" s="133"/>
-      <c r="C13" s="133"/>
-      <c r="D13" s="133"/>
-      <c r="E13" s="133"/>
-      <c r="F13" s="133"/>
-      <c r="G13" s="133"/>
-      <c r="H13" s="133"/>
-      <c r="I13" s="133"/>
-      <c r="J13" s="134"/>
+      <c r="A13" s="134"/>
+      <c r="B13" s="135"/>
+      <c r="C13" s="135"/>
+      <c r="D13" s="135"/>
+      <c r="E13" s="135"/>
+      <c r="F13" s="135"/>
+      <c r="G13" s="135"/>
+      <c r="H13" s="135"/>
+      <c r="I13" s="135"/>
+      <c r="J13" s="136"/>
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A14" s="153" t="s">
+      <c r="A14" s="130" t="s">
         <v>24</v>
       </c>
       <c r="B14" s="125"/>
@@ -8717,13 +12812,13 @@
       <c r="J14" s="128"/>
     </row>
     <row r="15" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A15" s="153" t="s">
+      <c r="A15" s="130" t="s">
         <v>25</v>
       </c>
       <c r="B15" s="125"/>
       <c r="C15" s="126"/>
       <c r="D15" s="127" t="s">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="E15" s="125"/>
       <c r="F15" s="125"/>
@@ -8733,11 +12828,11 @@
         <v>26</v>
       </c>
       <c r="J15" s="40" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A16" s="153" t="s">
+      <c r="A16" s="130" t="s">
         <v>27</v>
       </c>
       <c r="B16" s="125"/>
@@ -8754,7 +12849,7 @@
       <c r="G16" s="39" t="s">
         <v>31</v>
       </c>
-      <c r="H16" s="154" t="s">
+      <c r="H16" s="129" t="s">
         <v>18</v>
       </c>
       <c r="I16" s="125"/>
@@ -8767,19 +12862,19 @@
       <c r="B17" s="125"/>
       <c r="C17" s="126"/>
       <c r="D17" s="38" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="E17" s="38" t="s">
-        <v>84</v>
+        <v>73</v>
       </c>
       <c r="F17" s="37" t="s">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="G17" s="37" t="s">
-        <v>82</v>
+        <v>71</v>
       </c>
       <c r="H17" s="127" t="s">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="I17" s="125"/>
       <c r="J17" s="128"/>
@@ -8791,19 +12886,19 @@
       <c r="B18" s="125"/>
       <c r="C18" s="126"/>
       <c r="D18" s="38" t="s">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="E18" s="38" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="F18" s="37" t="s">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="G18" s="37" t="s">
-        <v>78</v>
+        <v>67</v>
       </c>
       <c r="H18" s="127" t="s">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="I18" s="125"/>
       <c r="J18" s="128"/>
@@ -8815,19 +12910,19 @@
       <c r="B19" s="125"/>
       <c r="C19" s="126"/>
       <c r="D19" s="38" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="E19" s="38" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="F19" s="37" t="s">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="G19" s="37" t="s">
-        <v>82</v>
+        <v>71</v>
       </c>
       <c r="H19" s="127" t="s">
-        <v>113</v>
+        <v>102</v>
       </c>
       <c r="I19" s="125"/>
       <c r="J19" s="128"/>
@@ -8839,19 +12934,19 @@
       <c r="B20" s="125"/>
       <c r="C20" s="126"/>
       <c r="D20" s="38" t="s">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="E20" s="38" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="F20" s="37" t="s">
-        <v>111</v>
+        <v>100</v>
       </c>
       <c r="G20" s="37" t="s">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="H20" s="127" t="s">
-        <v>110</v>
+        <v>99</v>
       </c>
       <c r="I20" s="125"/>
       <c r="J20" s="128"/>
@@ -8863,19 +12958,19 @@
       <c r="B21" s="125"/>
       <c r="C21" s="126"/>
       <c r="D21" s="38" t="s">
-        <v>105</v>
+        <v>94</v>
       </c>
       <c r="E21" s="38" t="s">
-        <v>84</v>
+        <v>73</v>
       </c>
       <c r="F21" s="37" t="s">
-        <v>106</v>
+        <v>95</v>
       </c>
       <c r="G21" s="37" t="s">
-        <v>107</v>
+        <v>96</v>
       </c>
       <c r="H21" s="127" t="s">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="I21" s="125"/>
       <c r="J21" s="128"/>
@@ -8887,19 +12982,19 @@
       <c r="B22" s="125"/>
       <c r="C22" s="126"/>
       <c r="D22" s="38" t="s">
-        <v>85</v>
+        <v>74</v>
       </c>
       <c r="E22" s="38" t="s">
-        <v>84</v>
+        <v>73</v>
       </c>
       <c r="F22" s="37" t="s">
-        <v>83</v>
+        <v>72</v>
       </c>
       <c r="G22" s="37" t="s">
-        <v>82</v>
+        <v>71</v>
       </c>
       <c r="H22" s="127" t="s">
-        <v>114</v>
+        <v>103</v>
       </c>
       <c r="I22" s="125"/>
       <c r="J22" s="128"/>
@@ -8911,16 +13006,16 @@
       <c r="B23" s="125"/>
       <c r="C23" s="126"/>
       <c r="D23" s="38" t="s">
-        <v>75</v>
+        <v>64</v>
       </c>
       <c r="E23" s="38" t="s">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="F23" s="37" t="s">
-        <v>75</v>
+        <v>64</v>
       </c>
       <c r="G23" s="37" t="s">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="H23" s="127"/>
       <c r="I23" s="125"/>
@@ -8933,16 +13028,16 @@
       <c r="B24" s="125"/>
       <c r="C24" s="126"/>
       <c r="D24" s="38" t="s">
-        <v>75</v>
+        <v>64</v>
       </c>
       <c r="E24" s="38" t="s">
-        <v>74</v>
+        <v>63</v>
       </c>
       <c r="F24" s="37" t="s">
-        <v>75</v>
+        <v>64</v>
       </c>
       <c r="G24" s="37" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
       <c r="H24" s="127"/>
       <c r="I24" s="125"/>
@@ -9926,23 +14021,6 @@
     <row r="1000" s="36" customFormat="1" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="33">
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="H19:J19"/>
-    <mergeCell ref="A23:C23"/>
-    <mergeCell ref="H23:J23"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="H20:J20"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="H21:J21"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="H22:J22"/>
-    <mergeCell ref="H16:J16"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="A15:C15"/>
-    <mergeCell ref="D15:H15"/>
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="H17:J17"/>
     <mergeCell ref="A24:C24"/>
     <mergeCell ref="H24:J24"/>
     <mergeCell ref="A7:J13"/>
@@ -9959,6 +14037,23 @@
     <mergeCell ref="A6:J6"/>
     <mergeCell ref="A14:J14"/>
     <mergeCell ref="A16:C16"/>
+    <mergeCell ref="H16:J16"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="H18:J18"/>
+    <mergeCell ref="A15:C15"/>
+    <mergeCell ref="D15:H15"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="H17:J17"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="H19:J19"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="H23:J23"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="H20:J20"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="H21:J21"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="H22:J22"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -9967,7 +14062,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3CC152AA-591E-41F9-9F27-ABB4D9BD279C}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -9982,19 +14077,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="163" t="s">
+      <c r="A1" s="160" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="61"/>
-      <c r="C1" s="62"/>
-      <c r="D1" s="69" t="s">
+      <c r="B1" s="90"/>
+      <c r="C1" s="91"/>
+      <c r="D1" s="98" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="70"/>
-      <c r="F1" s="69" t="s">
+      <c r="E1" s="83"/>
+      <c r="F1" s="98" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="70"/>
+      <c r="G1" s="83"/>
       <c r="H1" s="35" t="s">
         <v>6</v>
       </c>
@@ -10006,203 +14101,203 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="63"/>
-      <c r="B2" s="64"/>
-      <c r="C2" s="65"/>
-      <c r="D2" s="71" t="s">
-        <v>96</v>
-      </c>
-      <c r="E2" s="72"/>
-      <c r="F2" s="71">
+      <c r="A2" s="92"/>
+      <c r="B2" s="93"/>
+      <c r="C2" s="94"/>
+      <c r="D2" s="99" t="s">
+        <v>85</v>
+      </c>
+      <c r="E2" s="100"/>
+      <c r="F2" s="99">
         <v>56</v>
       </c>
-      <c r="G2" s="72"/>
-      <c r="H2" s="75">
+      <c r="G2" s="100"/>
+      <c r="H2" s="68">
         <v>45805</v>
       </c>
-      <c r="I2" s="89" t="s">
-        <v>94</v>
-      </c>
-      <c r="J2" s="90"/>
+      <c r="I2" s="77" t="s">
+        <v>83</v>
+      </c>
+      <c r="J2" s="78"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="63"/>
-      <c r="B3" s="64"/>
-      <c r="C3" s="65"/>
-      <c r="D3" s="73"/>
-      <c r="E3" s="65"/>
-      <c r="F3" s="73"/>
-      <c r="G3" s="65"/>
-      <c r="H3" s="76"/>
-      <c r="I3" s="76"/>
-      <c r="J3" s="91"/>
+      <c r="A3" s="92"/>
+      <c r="B3" s="93"/>
+      <c r="C3" s="94"/>
+      <c r="D3" s="101"/>
+      <c r="E3" s="94"/>
+      <c r="F3" s="101"/>
+      <c r="G3" s="94"/>
+      <c r="H3" s="69"/>
+      <c r="I3" s="69"/>
+      <c r="J3" s="79"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="63"/>
-      <c r="B4" s="64"/>
-      <c r="C4" s="65"/>
-      <c r="D4" s="73"/>
-      <c r="E4" s="65"/>
-      <c r="F4" s="73"/>
-      <c r="G4" s="65"/>
-      <c r="H4" s="76"/>
-      <c r="I4" s="76"/>
-      <c r="J4" s="91"/>
+      <c r="A4" s="92"/>
+      <c r="B4" s="93"/>
+      <c r="C4" s="94"/>
+      <c r="D4" s="101"/>
+      <c r="E4" s="94"/>
+      <c r="F4" s="101"/>
+      <c r="G4" s="94"/>
+      <c r="H4" s="69"/>
+      <c r="I4" s="69"/>
+      <c r="J4" s="79"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="164" t="s">
+      <c r="A5" s="161" t="s">
         <v>22</v>
       </c>
-      <c r="B5" s="94"/>
-      <c r="C5" s="70"/>
-      <c r="D5" s="165" t="s">
-        <v>97</v>
-      </c>
-      <c r="E5" s="94"/>
-      <c r="F5" s="94"/>
-      <c r="G5" s="94"/>
-      <c r="H5" s="94"/>
-      <c r="I5" s="94"/>
-      <c r="J5" s="96"/>
+      <c r="B5" s="82"/>
+      <c r="C5" s="83"/>
+      <c r="D5" s="162" t="s">
+        <v>86</v>
+      </c>
+      <c r="E5" s="82"/>
+      <c r="F5" s="82"/>
+      <c r="G5" s="82"/>
+      <c r="H5" s="82"/>
+      <c r="I5" s="82"/>
+      <c r="J5" s="85"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="157" t="s">
+      <c r="A6" s="155" t="s">
         <v>23</v>
       </c>
-      <c r="B6" s="79"/>
-      <c r="C6" s="79"/>
-      <c r="D6" s="79"/>
-      <c r="E6" s="79"/>
-      <c r="F6" s="79"/>
-      <c r="G6" s="79"/>
-      <c r="H6" s="79"/>
-      <c r="I6" s="79"/>
-      <c r="J6" s="82"/>
+      <c r="B6" s="66"/>
+      <c r="C6" s="66"/>
+      <c r="D6" s="66"/>
+      <c r="E6" s="66"/>
+      <c r="F6" s="66"/>
+      <c r="G6" s="66"/>
+      <c r="H6" s="66"/>
+      <c r="I6" s="66"/>
+      <c r="J6" s="67"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="159"/>
-      <c r="B7" s="160"/>
-      <c r="C7" s="160"/>
-      <c r="D7" s="160"/>
-      <c r="E7" s="160"/>
-      <c r="F7" s="160"/>
-      <c r="G7" s="160"/>
-      <c r="H7" s="160"/>
-      <c r="I7" s="160"/>
-      <c r="J7" s="161"/>
+      <c r="A7" s="156"/>
+      <c r="B7" s="157"/>
+      <c r="C7" s="157"/>
+      <c r="D7" s="157"/>
+      <c r="E7" s="157"/>
+      <c r="F7" s="157"/>
+      <c r="G7" s="157"/>
+      <c r="H7" s="157"/>
+      <c r="I7" s="157"/>
+      <c r="J7" s="158"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="63"/>
-      <c r="B8" s="64"/>
-      <c r="C8" s="64"/>
-      <c r="D8" s="64"/>
-      <c r="E8" s="64"/>
-      <c r="F8" s="64"/>
-      <c r="G8" s="64"/>
-      <c r="H8" s="64"/>
-      <c r="I8" s="64"/>
-      <c r="J8" s="162"/>
+      <c r="A8" s="92"/>
+      <c r="B8" s="93"/>
+      <c r="C8" s="93"/>
+      <c r="D8" s="93"/>
+      <c r="E8" s="93"/>
+      <c r="F8" s="93"/>
+      <c r="G8" s="93"/>
+      <c r="H8" s="93"/>
+      <c r="I8" s="93"/>
+      <c r="J8" s="159"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="63"/>
-      <c r="B9" s="64"/>
-      <c r="C9" s="64"/>
-      <c r="D9" s="64"/>
-      <c r="E9" s="64"/>
-      <c r="F9" s="64"/>
-      <c r="G9" s="64"/>
-      <c r="H9" s="64"/>
-      <c r="I9" s="64"/>
-      <c r="J9" s="162"/>
+      <c r="A9" s="92"/>
+      <c r="B9" s="93"/>
+      <c r="C9" s="93"/>
+      <c r="D9" s="93"/>
+      <c r="E9" s="93"/>
+      <c r="F9" s="93"/>
+      <c r="G9" s="93"/>
+      <c r="H9" s="93"/>
+      <c r="I9" s="93"/>
+      <c r="J9" s="159"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="63"/>
-      <c r="B10" s="64"/>
-      <c r="C10" s="64"/>
-      <c r="D10" s="64"/>
-      <c r="E10" s="64"/>
-      <c r="F10" s="64"/>
-      <c r="G10" s="64"/>
-      <c r="H10" s="64"/>
-      <c r="I10" s="64"/>
-      <c r="J10" s="162"/>
+      <c r="A10" s="92"/>
+      <c r="B10" s="93"/>
+      <c r="C10" s="93"/>
+      <c r="D10" s="93"/>
+      <c r="E10" s="93"/>
+      <c r="F10" s="93"/>
+      <c r="G10" s="93"/>
+      <c r="H10" s="93"/>
+      <c r="I10" s="93"/>
+      <c r="J10" s="159"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="63"/>
-      <c r="B11" s="64"/>
-      <c r="C11" s="64"/>
-      <c r="D11" s="64"/>
-      <c r="E11" s="64"/>
-      <c r="F11" s="64"/>
-      <c r="G11" s="64"/>
-      <c r="H11" s="64"/>
-      <c r="I11" s="64"/>
-      <c r="J11" s="162"/>
+      <c r="A11" s="92"/>
+      <c r="B11" s="93"/>
+      <c r="C11" s="93"/>
+      <c r="D11" s="93"/>
+      <c r="E11" s="93"/>
+      <c r="F11" s="93"/>
+      <c r="G11" s="93"/>
+      <c r="H11" s="93"/>
+      <c r="I11" s="93"/>
+      <c r="J11" s="159"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="63"/>
-      <c r="B12" s="64"/>
-      <c r="C12" s="64"/>
-      <c r="D12" s="64"/>
-      <c r="E12" s="64"/>
-      <c r="F12" s="64"/>
-      <c r="G12" s="64"/>
-      <c r="H12" s="64"/>
-      <c r="I12" s="64"/>
-      <c r="J12" s="162"/>
+      <c r="A12" s="92"/>
+      <c r="B12" s="93"/>
+      <c r="C12" s="93"/>
+      <c r="D12" s="93"/>
+      <c r="E12" s="93"/>
+      <c r="F12" s="93"/>
+      <c r="G12" s="93"/>
+      <c r="H12" s="93"/>
+      <c r="I12" s="93"/>
+      <c r="J12" s="159"/>
     </row>
     <row r="13" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A13" s="63"/>
-      <c r="B13" s="64"/>
-      <c r="C13" s="64"/>
-      <c r="D13" s="64"/>
-      <c r="E13" s="64"/>
-      <c r="F13" s="64"/>
-      <c r="G13" s="64"/>
-      <c r="H13" s="64"/>
-      <c r="I13" s="64"/>
-      <c r="J13" s="162"/>
+      <c r="A13" s="92"/>
+      <c r="B13" s="93"/>
+      <c r="C13" s="93"/>
+      <c r="D13" s="93"/>
+      <c r="E13" s="93"/>
+      <c r="F13" s="93"/>
+      <c r="G13" s="93"/>
+      <c r="H13" s="93"/>
+      <c r="I13" s="93"/>
+      <c r="J13" s="159"/>
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A14" s="157" t="s">
+      <c r="A14" s="155" t="s">
         <v>24</v>
       </c>
-      <c r="B14" s="79"/>
-      <c r="C14" s="79"/>
-      <c r="D14" s="79"/>
-      <c r="E14" s="79"/>
-      <c r="F14" s="79"/>
-      <c r="G14" s="79"/>
-      <c r="H14" s="79"/>
-      <c r="I14" s="79"/>
-      <c r="J14" s="82"/>
+      <c r="B14" s="66"/>
+      <c r="C14" s="66"/>
+      <c r="D14" s="66"/>
+      <c r="E14" s="66"/>
+      <c r="F14" s="66"/>
+      <c r="G14" s="66"/>
+      <c r="H14" s="66"/>
+      <c r="I14" s="66"/>
+      <c r="J14" s="67"/>
     </row>
     <row r="15" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A15" s="157" t="s">
+      <c r="A15" s="155" t="s">
         <v>25</v>
       </c>
-      <c r="B15" s="79"/>
-      <c r="C15" s="80"/>
-      <c r="D15" s="88" t="s">
-        <v>98</v>
-      </c>
-      <c r="E15" s="79"/>
-      <c r="F15" s="79"/>
-      <c r="G15" s="79"/>
-      <c r="H15" s="80"/>
+      <c r="B15" s="66"/>
+      <c r="C15" s="61"/>
+      <c r="D15" s="65" t="s">
+        <v>87</v>
+      </c>
+      <c r="E15" s="66"/>
+      <c r="F15" s="66"/>
+      <c r="G15" s="66"/>
+      <c r="H15" s="61"/>
       <c r="I15" s="45" t="s">
         <v>26</v>
       </c>
       <c r="J15" s="46" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A16" s="157" t="s">
+      <c r="A16" s="155" t="s">
         <v>27</v>
       </c>
-      <c r="B16" s="79"/>
-      <c r="C16" s="80"/>
+      <c r="B16" s="66"/>
+      <c r="C16" s="61"/>
       <c r="D16" s="45" t="s">
         <v>28</v>
       </c>
@@ -10215,107 +14310,107 @@
       <c r="G16" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="H16" s="158" t="s">
+      <c r="H16" s="163" t="s">
         <v>18</v>
       </c>
-      <c r="I16" s="79"/>
-      <c r="J16" s="82"/>
+      <c r="I16" s="66"/>
+      <c r="J16" s="67"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="155">
+      <c r="A17" s="164">
         <v>1</v>
       </c>
-      <c r="B17" s="79"/>
-      <c r="C17" s="80"/>
+      <c r="B17" s="66"/>
+      <c r="C17" s="61"/>
       <c r="D17" s="47" t="s">
-        <v>75</v>
+        <v>64</v>
       </c>
       <c r="E17" s="47" t="s">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="F17" s="48" t="s">
-        <v>75</v>
+        <v>64</v>
       </c>
       <c r="G17" s="48" t="s">
-        <v>100</v>
-      </c>
-      <c r="H17" s="88" t="s">
-        <v>101</v>
-      </c>
-      <c r="I17" s="79"/>
-      <c r="J17" s="82"/>
+        <v>89</v>
+      </c>
+      <c r="H17" s="65" t="s">
+        <v>90</v>
+      </c>
+      <c r="I17" s="66"/>
+      <c r="J17" s="67"/>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A18" s="155"/>
-      <c r="B18" s="79"/>
-      <c r="C18" s="80"/>
+      <c r="A18" s="164"/>
+      <c r="B18" s="66"/>
+      <c r="C18" s="61"/>
       <c r="D18" s="47"/>
       <c r="E18" s="47"/>
       <c r="F18" s="48"/>
       <c r="G18" s="48"/>
-      <c r="H18" s="88"/>
-      <c r="I18" s="79"/>
-      <c r="J18" s="82"/>
+      <c r="H18" s="65"/>
+      <c r="I18" s="66"/>
+      <c r="J18" s="67"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="155"/>
-      <c r="B19" s="79"/>
-      <c r="C19" s="80"/>
+      <c r="A19" s="164"/>
+      <c r="B19" s="66"/>
+      <c r="C19" s="61"/>
       <c r="D19" s="47"/>
       <c r="E19" s="47"/>
       <c r="F19" s="48"/>
       <c r="G19" s="48"/>
-      <c r="H19" s="88"/>
-      <c r="I19" s="79"/>
-      <c r="J19" s="82"/>
+      <c r="H19" s="65"/>
+      <c r="I19" s="66"/>
+      <c r="J19" s="67"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="155"/>
-      <c r="B20" s="79"/>
-      <c r="C20" s="80"/>
+      <c r="A20" s="164"/>
+      <c r="B20" s="66"/>
+      <c r="C20" s="61"/>
       <c r="D20" s="47"/>
       <c r="E20" s="47"/>
       <c r="F20" s="48"/>
       <c r="G20" s="48"/>
-      <c r="H20" s="88"/>
-      <c r="I20" s="79"/>
-      <c r="J20" s="82"/>
+      <c r="H20" s="65"/>
+      <c r="I20" s="66"/>
+      <c r="J20" s="67"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="155"/>
-      <c r="B21" s="79"/>
-      <c r="C21" s="80"/>
+      <c r="A21" s="164"/>
+      <c r="B21" s="66"/>
+      <c r="C21" s="61"/>
       <c r="D21" s="47"/>
       <c r="E21" s="47"/>
       <c r="F21" s="48"/>
       <c r="G21" s="48"/>
-      <c r="H21" s="88"/>
-      <c r="I21" s="79"/>
-      <c r="J21" s="82"/>
+      <c r="H21" s="65"/>
+      <c r="I21" s="66"/>
+      <c r="J21" s="67"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="155"/>
-      <c r="B22" s="79"/>
-      <c r="C22" s="80"/>
+      <c r="A22" s="164"/>
+      <c r="B22" s="66"/>
+      <c r="C22" s="61"/>
       <c r="D22" s="47"/>
       <c r="E22" s="47"/>
       <c r="F22" s="48"/>
       <c r="G22" s="48"/>
-      <c r="H22" s="88"/>
-      <c r="I22" s="79"/>
-      <c r="J22" s="82"/>
+      <c r="H22" s="65"/>
+      <c r="I22" s="66"/>
+      <c r="J22" s="67"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A23" s="156"/>
-      <c r="B23" s="84"/>
-      <c r="C23" s="85"/>
+      <c r="A23" s="165"/>
+      <c r="B23" s="73"/>
+      <c r="C23" s="74"/>
       <c r="D23" s="49"/>
       <c r="E23" s="49"/>
       <c r="F23" s="50"/>
       <c r="G23" s="50"/>
-      <c r="H23" s="86"/>
-      <c r="I23" s="84"/>
-      <c r="J23" s="87"/>
+      <c r="H23" s="75"/>
+      <c r="I23" s="73"/>
+      <c r="J23" s="76"/>
     </row>
     <row r="24" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="25" spans="1:10" ht="12.75" customHeight="1"/>
@@ -11296,6 +15391,22 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="31">
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="H23:J23"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="H19:J19"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="H20:J20"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="H21:J21"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="H16:J16"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="H18:J18"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="H17:J17"/>
     <mergeCell ref="A14:J14"/>
     <mergeCell ref="A15:C15"/>
     <mergeCell ref="A7:J13"/>
@@ -11311,22 +15422,6 @@
     <mergeCell ref="D5:J5"/>
     <mergeCell ref="A6:J6"/>
     <mergeCell ref="D15:H15"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="H16:J16"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="H17:J17"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="H22:J22"/>
-    <mergeCell ref="A23:C23"/>
-    <mergeCell ref="H23:J23"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="H19:J19"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="H20:J20"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="H21:J21"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -11335,7 +15430,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{993E2276-6C27-4BB1-8304-61A18B54CE82}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -11350,19 +15445,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="163" t="s">
+      <c r="A1" s="160" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="61"/>
-      <c r="C1" s="62"/>
-      <c r="D1" s="69" t="s">
+      <c r="B1" s="90"/>
+      <c r="C1" s="91"/>
+      <c r="D1" s="98" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="70"/>
-      <c r="F1" s="69" t="s">
+      <c r="E1" s="83"/>
+      <c r="F1" s="98" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="70"/>
+      <c r="G1" s="83"/>
       <c r="H1" s="35" t="s">
         <v>6</v>
       </c>
@@ -11374,203 +15469,203 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="63"/>
-      <c r="B2" s="64"/>
-      <c r="C2" s="65"/>
-      <c r="D2" s="71" t="s">
-        <v>95</v>
-      </c>
-      <c r="E2" s="72"/>
-      <c r="F2" s="71">
+      <c r="A2" s="92"/>
+      <c r="B2" s="93"/>
+      <c r="C2" s="94"/>
+      <c r="D2" s="99" t="s">
+        <v>84</v>
+      </c>
+      <c r="E2" s="100"/>
+      <c r="F2" s="99">
         <v>56</v>
       </c>
-      <c r="G2" s="72"/>
-      <c r="H2" s="75">
+      <c r="G2" s="100"/>
+      <c r="H2" s="68">
         <v>45805</v>
       </c>
-      <c r="I2" s="89" t="s">
-        <v>94</v>
-      </c>
-      <c r="J2" s="90"/>
+      <c r="I2" s="77" t="s">
+        <v>83</v>
+      </c>
+      <c r="J2" s="78"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="63"/>
-      <c r="B3" s="64"/>
-      <c r="C3" s="65"/>
-      <c r="D3" s="73"/>
-      <c r="E3" s="65"/>
-      <c r="F3" s="73"/>
-      <c r="G3" s="65"/>
-      <c r="H3" s="76"/>
-      <c r="I3" s="76"/>
-      <c r="J3" s="91"/>
+      <c r="A3" s="92"/>
+      <c r="B3" s="93"/>
+      <c r="C3" s="94"/>
+      <c r="D3" s="101"/>
+      <c r="E3" s="94"/>
+      <c r="F3" s="101"/>
+      <c r="G3" s="94"/>
+      <c r="H3" s="69"/>
+      <c r="I3" s="69"/>
+      <c r="J3" s="79"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="63"/>
-      <c r="B4" s="64"/>
-      <c r="C4" s="65"/>
-      <c r="D4" s="73"/>
-      <c r="E4" s="65"/>
-      <c r="F4" s="73"/>
-      <c r="G4" s="65"/>
-      <c r="H4" s="76"/>
-      <c r="I4" s="76"/>
-      <c r="J4" s="91"/>
+      <c r="A4" s="92"/>
+      <c r="B4" s="93"/>
+      <c r="C4" s="94"/>
+      <c r="D4" s="101"/>
+      <c r="E4" s="94"/>
+      <c r="F4" s="101"/>
+      <c r="G4" s="94"/>
+      <c r="H4" s="69"/>
+      <c r="I4" s="69"/>
+      <c r="J4" s="79"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="164" t="s">
+      <c r="A5" s="161" t="s">
         <v>22</v>
       </c>
-      <c r="B5" s="94"/>
-      <c r="C5" s="70"/>
-      <c r="D5" s="165" t="s">
-        <v>102</v>
-      </c>
-      <c r="E5" s="94"/>
-      <c r="F5" s="94"/>
-      <c r="G5" s="94"/>
-      <c r="H5" s="94"/>
-      <c r="I5" s="94"/>
-      <c r="J5" s="96"/>
+      <c r="B5" s="82"/>
+      <c r="C5" s="83"/>
+      <c r="D5" s="162" t="s">
+        <v>91</v>
+      </c>
+      <c r="E5" s="82"/>
+      <c r="F5" s="82"/>
+      <c r="G5" s="82"/>
+      <c r="H5" s="82"/>
+      <c r="I5" s="82"/>
+      <c r="J5" s="85"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="157" t="s">
+      <c r="A6" s="155" t="s">
         <v>23</v>
       </c>
-      <c r="B6" s="79"/>
-      <c r="C6" s="79"/>
-      <c r="D6" s="79"/>
-      <c r="E6" s="79"/>
-      <c r="F6" s="79"/>
-      <c r="G6" s="79"/>
-      <c r="H6" s="79"/>
-      <c r="I6" s="79"/>
-      <c r="J6" s="82"/>
+      <c r="B6" s="66"/>
+      <c r="C6" s="66"/>
+      <c r="D6" s="66"/>
+      <c r="E6" s="66"/>
+      <c r="F6" s="66"/>
+      <c r="G6" s="66"/>
+      <c r="H6" s="66"/>
+      <c r="I6" s="66"/>
+      <c r="J6" s="67"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="159"/>
-      <c r="B7" s="160"/>
-      <c r="C7" s="160"/>
-      <c r="D7" s="160"/>
-      <c r="E7" s="160"/>
-      <c r="F7" s="160"/>
-      <c r="G7" s="160"/>
-      <c r="H7" s="160"/>
-      <c r="I7" s="160"/>
-      <c r="J7" s="161"/>
+      <c r="A7" s="156"/>
+      <c r="B7" s="157"/>
+      <c r="C7" s="157"/>
+      <c r="D7" s="157"/>
+      <c r="E7" s="157"/>
+      <c r="F7" s="157"/>
+      <c r="G7" s="157"/>
+      <c r="H7" s="157"/>
+      <c r="I7" s="157"/>
+      <c r="J7" s="158"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="63"/>
-      <c r="B8" s="64"/>
-      <c r="C8" s="64"/>
-      <c r="D8" s="64"/>
-      <c r="E8" s="64"/>
-      <c r="F8" s="64"/>
-      <c r="G8" s="64"/>
-      <c r="H8" s="64"/>
-      <c r="I8" s="64"/>
-      <c r="J8" s="162"/>
+      <c r="A8" s="92"/>
+      <c r="B8" s="93"/>
+      <c r="C8" s="93"/>
+      <c r="D8" s="93"/>
+      <c r="E8" s="93"/>
+      <c r="F8" s="93"/>
+      <c r="G8" s="93"/>
+      <c r="H8" s="93"/>
+      <c r="I8" s="93"/>
+      <c r="J8" s="159"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="63"/>
-      <c r="B9" s="64"/>
-      <c r="C9" s="64"/>
-      <c r="D9" s="64"/>
-      <c r="E9" s="64"/>
-      <c r="F9" s="64"/>
-      <c r="G9" s="64"/>
-      <c r="H9" s="64"/>
-      <c r="I9" s="64"/>
-      <c r="J9" s="162"/>
+      <c r="A9" s="92"/>
+      <c r="B9" s="93"/>
+      <c r="C9" s="93"/>
+      <c r="D9" s="93"/>
+      <c r="E9" s="93"/>
+      <c r="F9" s="93"/>
+      <c r="G9" s="93"/>
+      <c r="H9" s="93"/>
+      <c r="I9" s="93"/>
+      <c r="J9" s="159"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="63"/>
-      <c r="B10" s="64"/>
-      <c r="C10" s="64"/>
-      <c r="D10" s="64"/>
-      <c r="E10" s="64"/>
-      <c r="F10" s="64"/>
-      <c r="G10" s="64"/>
-      <c r="H10" s="64"/>
-      <c r="I10" s="64"/>
-      <c r="J10" s="162"/>
+      <c r="A10" s="92"/>
+      <c r="B10" s="93"/>
+      <c r="C10" s="93"/>
+      <c r="D10" s="93"/>
+      <c r="E10" s="93"/>
+      <c r="F10" s="93"/>
+      <c r="G10" s="93"/>
+      <c r="H10" s="93"/>
+      <c r="I10" s="93"/>
+      <c r="J10" s="159"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="63"/>
-      <c r="B11" s="64"/>
-      <c r="C11" s="64"/>
-      <c r="D11" s="64"/>
-      <c r="E11" s="64"/>
-      <c r="F11" s="64"/>
-      <c r="G11" s="64"/>
-      <c r="H11" s="64"/>
-      <c r="I11" s="64"/>
-      <c r="J11" s="162"/>
+      <c r="A11" s="92"/>
+      <c r="B11" s="93"/>
+      <c r="C11" s="93"/>
+      <c r="D11" s="93"/>
+      <c r="E11" s="93"/>
+      <c r="F11" s="93"/>
+      <c r="G11" s="93"/>
+      <c r="H11" s="93"/>
+      <c r="I11" s="93"/>
+      <c r="J11" s="159"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="63"/>
-      <c r="B12" s="64"/>
-      <c r="C12" s="64"/>
-      <c r="D12" s="64"/>
-      <c r="E12" s="64"/>
-      <c r="F12" s="64"/>
-      <c r="G12" s="64"/>
-      <c r="H12" s="64"/>
-      <c r="I12" s="64"/>
-      <c r="J12" s="162"/>
+      <c r="A12" s="92"/>
+      <c r="B12" s="93"/>
+      <c r="C12" s="93"/>
+      <c r="D12" s="93"/>
+      <c r="E12" s="93"/>
+      <c r="F12" s="93"/>
+      <c r="G12" s="93"/>
+      <c r="H12" s="93"/>
+      <c r="I12" s="93"/>
+      <c r="J12" s="159"/>
     </row>
     <row r="13" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A13" s="63"/>
-      <c r="B13" s="64"/>
-      <c r="C13" s="64"/>
-      <c r="D13" s="64"/>
-      <c r="E13" s="64"/>
-      <c r="F13" s="64"/>
-      <c r="G13" s="64"/>
-      <c r="H13" s="64"/>
-      <c r="I13" s="64"/>
-      <c r="J13" s="162"/>
+      <c r="A13" s="92"/>
+      <c r="B13" s="93"/>
+      <c r="C13" s="93"/>
+      <c r="D13" s="93"/>
+      <c r="E13" s="93"/>
+      <c r="F13" s="93"/>
+      <c r="G13" s="93"/>
+      <c r="H13" s="93"/>
+      <c r="I13" s="93"/>
+      <c r="J13" s="159"/>
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A14" s="157" t="s">
+      <c r="A14" s="155" t="s">
         <v>24</v>
       </c>
-      <c r="B14" s="79"/>
-      <c r="C14" s="79"/>
-      <c r="D14" s="79"/>
-      <c r="E14" s="79"/>
-      <c r="F14" s="79"/>
-      <c r="G14" s="79"/>
-      <c r="H14" s="79"/>
-      <c r="I14" s="79"/>
-      <c r="J14" s="82"/>
+      <c r="B14" s="66"/>
+      <c r="C14" s="66"/>
+      <c r="D14" s="66"/>
+      <c r="E14" s="66"/>
+      <c r="F14" s="66"/>
+      <c r="G14" s="66"/>
+      <c r="H14" s="66"/>
+      <c r="I14" s="66"/>
+      <c r="J14" s="67"/>
     </row>
     <row r="15" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A15" s="157" t="s">
+      <c r="A15" s="155" t="s">
         <v>25</v>
       </c>
-      <c r="B15" s="79"/>
-      <c r="C15" s="80"/>
-      <c r="D15" s="88" t="s">
-        <v>98</v>
-      </c>
-      <c r="E15" s="79"/>
-      <c r="F15" s="79"/>
-      <c r="G15" s="79"/>
-      <c r="H15" s="80"/>
+      <c r="B15" s="66"/>
+      <c r="C15" s="61"/>
+      <c r="D15" s="65" t="s">
+        <v>87</v>
+      </c>
+      <c r="E15" s="66"/>
+      <c r="F15" s="66"/>
+      <c r="G15" s="66"/>
+      <c r="H15" s="61"/>
       <c r="I15" s="45" t="s">
         <v>26</v>
       </c>
       <c r="J15" s="46" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A16" s="157" t="s">
+      <c r="A16" s="155" t="s">
         <v>27</v>
       </c>
-      <c r="B16" s="79"/>
-      <c r="C16" s="80"/>
+      <c r="B16" s="66"/>
+      <c r="C16" s="61"/>
       <c r="D16" s="45" t="s">
         <v>28</v>
       </c>
@@ -11583,107 +15678,107 @@
       <c r="G16" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="H16" s="158" t="s">
+      <c r="H16" s="163" t="s">
         <v>18</v>
       </c>
-      <c r="I16" s="79"/>
-      <c r="J16" s="82"/>
+      <c r="I16" s="66"/>
+      <c r="J16" s="67"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="155">
+      <c r="A17" s="164">
         <v>1</v>
       </c>
-      <c r="B17" s="79"/>
-      <c r="C17" s="80"/>
+      <c r="B17" s="66"/>
+      <c r="C17" s="61"/>
       <c r="D17" s="47" t="s">
-        <v>75</v>
+        <v>64</v>
       </c>
       <c r="E17" s="47" t="s">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="F17" s="48" t="s">
-        <v>75</v>
+        <v>64</v>
       </c>
       <c r="G17" s="48" t="s">
-        <v>100</v>
-      </c>
-      <c r="H17" s="88" t="s">
-        <v>101</v>
-      </c>
-      <c r="I17" s="79"/>
-      <c r="J17" s="82"/>
+        <v>89</v>
+      </c>
+      <c r="H17" s="65" t="s">
+        <v>90</v>
+      </c>
+      <c r="I17" s="66"/>
+      <c r="J17" s="67"/>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A18" s="155"/>
-      <c r="B18" s="79"/>
-      <c r="C18" s="80"/>
+      <c r="A18" s="164"/>
+      <c r="B18" s="66"/>
+      <c r="C18" s="61"/>
       <c r="D18" s="47"/>
       <c r="E18" s="47"/>
       <c r="F18" s="48"/>
       <c r="G18" s="48"/>
-      <c r="H18" s="88"/>
-      <c r="I18" s="79"/>
-      <c r="J18" s="82"/>
+      <c r="H18" s="65"/>
+      <c r="I18" s="66"/>
+      <c r="J18" s="67"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="155"/>
-      <c r="B19" s="79"/>
-      <c r="C19" s="80"/>
+      <c r="A19" s="164"/>
+      <c r="B19" s="66"/>
+      <c r="C19" s="61"/>
       <c r="D19" s="47"/>
       <c r="E19" s="47"/>
       <c r="F19" s="48"/>
       <c r="G19" s="48"/>
-      <c r="H19" s="88"/>
-      <c r="I19" s="79"/>
-      <c r="J19" s="82"/>
+      <c r="H19" s="65"/>
+      <c r="I19" s="66"/>
+      <c r="J19" s="67"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="155"/>
-      <c r="B20" s="79"/>
-      <c r="C20" s="80"/>
+      <c r="A20" s="164"/>
+      <c r="B20" s="66"/>
+      <c r="C20" s="61"/>
       <c r="D20" s="47"/>
       <c r="E20" s="47"/>
       <c r="F20" s="48"/>
       <c r="G20" s="48"/>
-      <c r="H20" s="88"/>
-      <c r="I20" s="79"/>
-      <c r="J20" s="82"/>
+      <c r="H20" s="65"/>
+      <c r="I20" s="66"/>
+      <c r="J20" s="67"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="155"/>
-      <c r="B21" s="79"/>
-      <c r="C21" s="80"/>
+      <c r="A21" s="164"/>
+      <c r="B21" s="66"/>
+      <c r="C21" s="61"/>
       <c r="D21" s="47"/>
       <c r="E21" s="47"/>
       <c r="F21" s="48"/>
       <c r="G21" s="48"/>
-      <c r="H21" s="88"/>
-      <c r="I21" s="79"/>
-      <c r="J21" s="82"/>
+      <c r="H21" s="65"/>
+      <c r="I21" s="66"/>
+      <c r="J21" s="67"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="155"/>
-      <c r="B22" s="79"/>
-      <c r="C22" s="80"/>
+      <c r="A22" s="164"/>
+      <c r="B22" s="66"/>
+      <c r="C22" s="61"/>
       <c r="D22" s="47"/>
       <c r="E22" s="47"/>
       <c r="F22" s="48"/>
       <c r="G22" s="48"/>
-      <c r="H22" s="88"/>
-      <c r="I22" s="79"/>
-      <c r="J22" s="82"/>
+      <c r="H22" s="65"/>
+      <c r="I22" s="66"/>
+      <c r="J22" s="67"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A23" s="156"/>
-      <c r="B23" s="84"/>
-      <c r="C23" s="85"/>
+      <c r="A23" s="165"/>
+      <c r="B23" s="73"/>
+      <c r="C23" s="74"/>
       <c r="D23" s="49"/>
       <c r="E23" s="49"/>
       <c r="F23" s="50"/>
       <c r="G23" s="50"/>
-      <c r="H23" s="86"/>
-      <c r="I23" s="84"/>
-      <c r="J23" s="87"/>
+      <c r="H23" s="75"/>
+      <c r="I23" s="73"/>
+      <c r="J23" s="76"/>
     </row>
     <row r="24" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="25" spans="1:10" ht="12.75" customHeight="1"/>
@@ -12664,6 +16759,22 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="31">
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="H23:J23"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="H19:J19"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="H20:J20"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="H21:J21"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="H16:J16"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="H18:J18"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="H17:J17"/>
     <mergeCell ref="A14:J14"/>
     <mergeCell ref="A15:C15"/>
     <mergeCell ref="A7:J13"/>
@@ -12679,2061 +16790,10 @@
     <mergeCell ref="D5:J5"/>
     <mergeCell ref="A6:J6"/>
     <mergeCell ref="D15:H15"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="H16:J16"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="H17:J17"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="H22:J22"/>
-    <mergeCell ref="A23:C23"/>
-    <mergeCell ref="H23:J23"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="H19:J19"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="H20:J20"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="H21:J21"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="landscape"/>
   <drawing r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:Z1000"/>
-  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
-  <cols>
-    <col min="1" max="6" width="2.85546875" customWidth="1"/>
-    <col min="7" max="20" width="8.140625" customWidth="1"/>
-    <col min="21" max="26" width="8.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:26" ht="18" customHeight="1">
-      <c r="A1" s="177" t="s">
-        <v>32</v>
-      </c>
-      <c r="B1" s="111"/>
-      <c r="C1" s="111"/>
-      <c r="D1" s="111"/>
-      <c r="E1" s="111"/>
-      <c r="F1" s="112"/>
-      <c r="G1" s="118" t="s">
-        <v>4</v>
-      </c>
-      <c r="H1" s="178"/>
-      <c r="I1" s="178"/>
-      <c r="J1" s="119"/>
-      <c r="K1" s="118" t="s">
-        <v>5</v>
-      </c>
-      <c r="L1" s="178"/>
-      <c r="M1" s="178"/>
-      <c r="N1" s="119"/>
-      <c r="O1" s="118" t="s">
-        <v>6</v>
-      </c>
-      <c r="P1" s="119"/>
-      <c r="Q1" s="118" t="s">
-        <v>7</v>
-      </c>
-      <c r="R1" s="119"/>
-      <c r="S1" s="118" t="s">
-        <v>8</v>
-      </c>
-      <c r="T1" s="179"/>
-    </row>
-    <row r="2" spans="1:26" ht="18" customHeight="1">
-      <c r="A2" s="113"/>
-      <c r="B2" s="55"/>
-      <c r="C2" s="55"/>
-      <c r="D2" s="55"/>
-      <c r="E2" s="55"/>
-      <c r="F2" s="114"/>
-      <c r="G2" s="120"/>
-      <c r="H2" s="173"/>
-      <c r="I2" s="173"/>
-      <c r="J2" s="121"/>
-      <c r="K2" s="120"/>
-      <c r="L2" s="173"/>
-      <c r="M2" s="173"/>
-      <c r="N2" s="121"/>
-      <c r="O2" s="120"/>
-      <c r="P2" s="121"/>
-      <c r="Q2" s="120"/>
-      <c r="R2" s="121"/>
-      <c r="S2" s="120"/>
-      <c r="T2" s="174"/>
-    </row>
-    <row r="3" spans="1:26" ht="18" customHeight="1">
-      <c r="A3" s="113"/>
-      <c r="B3" s="55"/>
-      <c r="C3" s="55"/>
-      <c r="D3" s="55"/>
-      <c r="E3" s="55"/>
-      <c r="F3" s="114"/>
-      <c r="G3" s="122"/>
-      <c r="H3" s="55"/>
-      <c r="I3" s="55"/>
-      <c r="J3" s="114"/>
-      <c r="K3" s="122"/>
-      <c r="L3" s="55"/>
-      <c r="M3" s="55"/>
-      <c r="N3" s="114"/>
-      <c r="O3" s="122"/>
-      <c r="P3" s="114"/>
-      <c r="Q3" s="122"/>
-      <c r="R3" s="114"/>
-      <c r="S3" s="122"/>
-      <c r="T3" s="175"/>
-    </row>
-    <row r="4" spans="1:26" ht="18" customHeight="1">
-      <c r="A4" s="115"/>
-      <c r="B4" s="116"/>
-      <c r="C4" s="116"/>
-      <c r="D4" s="116"/>
-      <c r="E4" s="116"/>
-      <c r="F4" s="117"/>
-      <c r="G4" s="123"/>
-      <c r="H4" s="116"/>
-      <c r="I4" s="116"/>
-      <c r="J4" s="117"/>
-      <c r="K4" s="123"/>
-      <c r="L4" s="116"/>
-      <c r="M4" s="116"/>
-      <c r="N4" s="117"/>
-      <c r="O4" s="123"/>
-      <c r="P4" s="117"/>
-      <c r="Q4" s="123"/>
-      <c r="R4" s="117"/>
-      <c r="S4" s="123"/>
-      <c r="T4" s="176"/>
-    </row>
-    <row r="5" spans="1:26" ht="18" customHeight="1">
-      <c r="A5" s="180" t="s">
-        <v>33</v>
-      </c>
-      <c r="B5" s="178"/>
-      <c r="C5" s="178"/>
-      <c r="D5" s="178"/>
-      <c r="E5" s="178"/>
-      <c r="F5" s="119"/>
-      <c r="G5" s="181" t="s">
-        <v>34</v>
-      </c>
-      <c r="H5" s="178"/>
-      <c r="I5" s="178"/>
-      <c r="J5" s="178"/>
-      <c r="K5" s="178"/>
-      <c r="L5" s="178"/>
-      <c r="M5" s="178"/>
-      <c r="N5" s="178"/>
-      <c r="O5" s="178"/>
-      <c r="P5" s="178"/>
-      <c r="Q5" s="178"/>
-      <c r="R5" s="178"/>
-      <c r="S5" s="178"/>
-      <c r="T5" s="179"/>
-    </row>
-    <row r="6" spans="1:26" ht="18" customHeight="1">
-      <c r="A6" s="182" t="s">
-        <v>35</v>
-      </c>
-      <c r="B6" s="52"/>
-      <c r="C6" s="52"/>
-      <c r="D6" s="52"/>
-      <c r="E6" s="52"/>
-      <c r="F6" s="53"/>
-      <c r="G6" s="183" t="s">
-        <v>19</v>
-      </c>
-      <c r="H6" s="52"/>
-      <c r="I6" s="52"/>
-      <c r="J6" s="52"/>
-      <c r="K6" s="52"/>
-      <c r="L6" s="52"/>
-      <c r="M6" s="52"/>
-      <c r="N6" s="52"/>
-      <c r="O6" s="52"/>
-      <c r="P6" s="52"/>
-      <c r="Q6" s="52"/>
-      <c r="R6" s="52"/>
-      <c r="S6" s="52"/>
-      <c r="T6" s="184"/>
-    </row>
-    <row r="7" spans="1:26" ht="18" customHeight="1">
-      <c r="A7" s="182" t="s">
-        <v>36</v>
-      </c>
-      <c r="B7" s="52"/>
-      <c r="C7" s="52"/>
-      <c r="D7" s="52"/>
-      <c r="E7" s="52"/>
-      <c r="F7" s="53"/>
-      <c r="G7" s="183" t="s">
-        <v>37</v>
-      </c>
-      <c r="H7" s="52"/>
-      <c r="I7" s="52"/>
-      <c r="J7" s="52"/>
-      <c r="K7" s="52"/>
-      <c r="L7" s="52"/>
-      <c r="M7" s="52"/>
-      <c r="N7" s="52"/>
-      <c r="O7" s="52"/>
-      <c r="P7" s="52"/>
-      <c r="Q7" s="52"/>
-      <c r="R7" s="52"/>
-      <c r="S7" s="52"/>
-      <c r="T7" s="184"/>
-    </row>
-    <row r="8" spans="1:26" ht="7.5" customHeight="1">
-      <c r="A8" s="7"/>
-      <c r="B8" s="8"/>
-      <c r="C8" s="8"/>
-      <c r="D8" s="8"/>
-      <c r="E8" s="8"/>
-      <c r="F8" s="8"/>
-      <c r="G8" s="8"/>
-      <c r="H8" s="8"/>
-      <c r="I8" s="8"/>
-      <c r="J8" s="8"/>
-      <c r="K8" s="8"/>
-      <c r="L8" s="8"/>
-      <c r="M8" s="8"/>
-      <c r="N8" s="8"/>
-      <c r="O8" s="8"/>
-      <c r="P8" s="8"/>
-      <c r="Q8" s="8"/>
-      <c r="R8" s="8"/>
-      <c r="S8" s="8"/>
-      <c r="T8" s="9"/>
-    </row>
-    <row r="9" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A9" s="15"/>
-      <c r="B9" s="16"/>
-      <c r="C9" s="17" t="s">
-        <v>38</v>
-      </c>
-      <c r="D9" s="18"/>
-      <c r="E9" s="18" t="s">
-        <v>39</v>
-      </c>
-      <c r="F9" s="18"/>
-      <c r="G9" s="19"/>
-      <c r="H9" s="18"/>
-      <c r="I9" s="18"/>
-      <c r="J9" s="18"/>
-      <c r="K9" s="19"/>
-      <c r="L9" s="16"/>
-      <c r="M9" s="16"/>
-      <c r="N9" s="16"/>
-      <c r="O9" s="16"/>
-      <c r="P9" s="16"/>
-      <c r="Q9" s="16"/>
-      <c r="R9" s="16"/>
-      <c r="S9" s="16"/>
-      <c r="T9" s="20"/>
-      <c r="U9" s="16"/>
-      <c r="V9" s="16"/>
-      <c r="W9" s="16"/>
-      <c r="X9" s="16"/>
-      <c r="Y9" s="16"/>
-      <c r="Z9" s="16"/>
-    </row>
-    <row r="10" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A10" s="15"/>
-      <c r="B10" s="16"/>
-      <c r="C10" s="21"/>
-      <c r="D10" s="16"/>
-      <c r="E10" s="16" t="s">
-        <v>40</v>
-      </c>
-      <c r="F10" s="16"/>
-      <c r="G10" s="22"/>
-      <c r="H10" s="16"/>
-      <c r="I10" s="16"/>
-      <c r="J10" s="16"/>
-      <c r="K10" s="22"/>
-      <c r="L10" s="16"/>
-      <c r="M10" s="16"/>
-      <c r="N10" s="16"/>
-      <c r="O10" s="16"/>
-      <c r="P10" s="16"/>
-      <c r="Q10" s="16"/>
-      <c r="R10" s="16"/>
-      <c r="S10" s="16"/>
-      <c r="T10" s="20"/>
-      <c r="U10" s="16"/>
-      <c r="V10" s="16"/>
-      <c r="W10" s="16"/>
-      <c r="X10" s="16"/>
-      <c r="Y10" s="16"/>
-      <c r="Z10" s="16"/>
-    </row>
-    <row r="11" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A11" s="15"/>
-      <c r="B11" s="16"/>
-      <c r="C11" s="21"/>
-      <c r="D11" s="16"/>
-      <c r="E11" s="16" t="s">
-        <v>41</v>
-      </c>
-      <c r="F11" s="16"/>
-      <c r="G11" s="22"/>
-      <c r="H11" s="16"/>
-      <c r="I11" s="16"/>
-      <c r="J11" s="16"/>
-      <c r="K11" s="22"/>
-      <c r="L11" s="16"/>
-      <c r="M11" s="16"/>
-      <c r="N11" s="16"/>
-      <c r="O11" s="16"/>
-      <c r="P11" s="16"/>
-      <c r="Q11" s="16"/>
-      <c r="R11" s="16"/>
-      <c r="S11" s="16"/>
-      <c r="T11" s="20"/>
-      <c r="U11" s="16"/>
-      <c r="V11" s="16"/>
-      <c r="W11" s="16"/>
-      <c r="X11" s="16"/>
-      <c r="Y11" s="16"/>
-      <c r="Z11" s="16"/>
-    </row>
-    <row r="12" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A12" s="15"/>
-      <c r="B12" s="16"/>
-      <c r="C12" s="21"/>
-      <c r="D12" s="16"/>
-      <c r="E12" s="16" t="s">
-        <v>42</v>
-      </c>
-      <c r="F12" s="16"/>
-      <c r="G12" s="22"/>
-      <c r="H12" s="16"/>
-      <c r="I12" s="16"/>
-      <c r="J12" s="16"/>
-      <c r="K12" s="22"/>
-      <c r="L12" s="16"/>
-      <c r="M12" s="16"/>
-      <c r="N12" s="16"/>
-      <c r="O12" s="16"/>
-      <c r="P12" s="16"/>
-      <c r="Q12" s="16"/>
-      <c r="R12" s="16"/>
-      <c r="S12" s="16"/>
-      <c r="T12" s="20"/>
-      <c r="U12" s="16"/>
-      <c r="V12" s="16"/>
-      <c r="W12" s="16"/>
-      <c r="X12" s="16"/>
-      <c r="Y12" s="16"/>
-      <c r="Z12" s="16"/>
-    </row>
-    <row r="13" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A13" s="15"/>
-      <c r="B13" s="16"/>
-      <c r="C13" s="23"/>
-      <c r="D13" s="24"/>
-      <c r="E13" s="24" t="s">
-        <v>43</v>
-      </c>
-      <c r="F13" s="24"/>
-      <c r="G13" s="25"/>
-      <c r="H13" s="24"/>
-      <c r="I13" s="24"/>
-      <c r="J13" s="24"/>
-      <c r="K13" s="25"/>
-      <c r="L13" s="16"/>
-      <c r="M13" s="16"/>
-      <c r="N13" s="16"/>
-      <c r="O13" s="16"/>
-      <c r="P13" s="16"/>
-      <c r="Q13" s="16"/>
-      <c r="R13" s="16"/>
-      <c r="S13" s="16"/>
-      <c r="T13" s="20"/>
-      <c r="U13" s="16"/>
-      <c r="V13" s="16"/>
-      <c r="W13" s="16"/>
-      <c r="X13" s="16"/>
-      <c r="Y13" s="16"/>
-      <c r="Z13" s="16"/>
-    </row>
-    <row r="14" spans="1:26" ht="8.25" customHeight="1">
-      <c r="A14" s="7"/>
-      <c r="B14" s="8"/>
-      <c r="C14" s="8"/>
-      <c r="D14" s="8"/>
-      <c r="E14" s="8"/>
-      <c r="F14" s="8"/>
-      <c r="G14" s="8"/>
-      <c r="H14" s="8"/>
-      <c r="I14" s="8"/>
-      <c r="J14" s="8"/>
-      <c r="K14" s="8"/>
-      <c r="L14" s="8"/>
-      <c r="M14" s="8"/>
-      <c r="N14" s="8"/>
-      <c r="O14" s="8"/>
-      <c r="P14" s="8"/>
-      <c r="Q14" s="8"/>
-      <c r="R14" s="8"/>
-      <c r="S14" s="8"/>
-      <c r="T14" s="9"/>
-    </row>
-    <row r="15" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A15" s="182" t="s">
-        <v>44</v>
-      </c>
-      <c r="B15" s="53"/>
-      <c r="C15" s="188" t="s">
-        <v>38</v>
-      </c>
-      <c r="D15" s="53"/>
-      <c r="E15" s="166" t="s">
-        <v>45</v>
-      </c>
-      <c r="F15" s="53"/>
-      <c r="G15" s="166" t="s">
-        <v>46</v>
-      </c>
-      <c r="H15" s="52"/>
-      <c r="I15" s="53"/>
-      <c r="J15" s="166" t="s">
-        <v>47</v>
-      </c>
-      <c r="K15" s="53"/>
-      <c r="L15" s="166" t="s">
-        <v>48</v>
-      </c>
-      <c r="M15" s="52"/>
-      <c r="N15" s="53"/>
-      <c r="O15" s="166" t="s">
-        <v>49</v>
-      </c>
-      <c r="P15" s="52"/>
-      <c r="Q15" s="53"/>
-      <c r="R15" s="14" t="s">
-        <v>50</v>
-      </c>
-      <c r="S15" s="14" t="s">
-        <v>51</v>
-      </c>
-      <c r="T15" s="26" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="16" spans="1:26" ht="48" customHeight="1">
-      <c r="A16" s="185">
-        <v>1</v>
-      </c>
-      <c r="B16" s="53"/>
-      <c r="C16" s="186" t="s">
-        <v>53</v>
-      </c>
-      <c r="D16" s="53"/>
-      <c r="E16" s="186" t="s">
-        <v>54</v>
-      </c>
-      <c r="F16" s="53"/>
-      <c r="G16" s="167" t="s">
-        <v>55</v>
-      </c>
-      <c r="H16" s="52"/>
-      <c r="I16" s="53"/>
-      <c r="J16" s="167" t="s">
-        <v>56</v>
-      </c>
-      <c r="K16" s="53"/>
-      <c r="L16" s="187" t="s">
-        <v>65</v>
-      </c>
-      <c r="M16" s="52"/>
-      <c r="N16" s="53"/>
-      <c r="O16" s="171" t="s">
-        <v>57</v>
-      </c>
-      <c r="P16" s="52"/>
-      <c r="Q16" s="53"/>
-      <c r="R16" s="27"/>
-      <c r="S16" s="27"/>
-      <c r="T16" s="28"/>
-      <c r="U16" s="29"/>
-      <c r="V16" s="29"/>
-      <c r="W16" s="29"/>
-      <c r="X16" s="29"/>
-      <c r="Y16" s="29"/>
-      <c r="Z16" s="29"/>
-    </row>
-    <row r="17" spans="1:26" ht="41.25" customHeight="1">
-      <c r="A17" s="185">
-        <v>2</v>
-      </c>
-      <c r="B17" s="53"/>
-      <c r="C17" s="186" t="s">
-        <v>58</v>
-      </c>
-      <c r="D17" s="53"/>
-      <c r="E17" s="186" t="s">
-        <v>59</v>
-      </c>
-      <c r="F17" s="53"/>
-      <c r="G17" s="167" t="s">
-        <v>60</v>
-      </c>
-      <c r="H17" s="52"/>
-      <c r="I17" s="53"/>
-      <c r="J17" s="167" t="s">
-        <v>61</v>
-      </c>
-      <c r="K17" s="53"/>
-      <c r="L17" s="171" t="s">
-        <v>62</v>
-      </c>
-      <c r="M17" s="52"/>
-      <c r="N17" s="53"/>
-      <c r="O17" s="171" t="s">
-        <v>63</v>
-      </c>
-      <c r="P17" s="52"/>
-      <c r="Q17" s="53"/>
-      <c r="R17" s="27"/>
-      <c r="S17" s="27"/>
-      <c r="T17" s="28"/>
-      <c r="U17" s="29"/>
-      <c r="V17" s="29"/>
-      <c r="W17" s="29"/>
-      <c r="X17" s="29"/>
-      <c r="Y17" s="29"/>
-      <c r="Z17" s="29"/>
-    </row>
-    <row r="18" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A18" s="185"/>
-      <c r="B18" s="53"/>
-      <c r="C18" s="186"/>
-      <c r="D18" s="53"/>
-      <c r="E18" s="186"/>
-      <c r="F18" s="53"/>
-      <c r="G18" s="167"/>
-      <c r="H18" s="52"/>
-      <c r="I18" s="53"/>
-      <c r="J18" s="167"/>
-      <c r="K18" s="53"/>
-      <c r="L18" s="171"/>
-      <c r="M18" s="52"/>
-      <c r="N18" s="53"/>
-      <c r="O18" s="171"/>
-      <c r="P18" s="52"/>
-      <c r="Q18" s="53"/>
-      <c r="R18" s="27"/>
-      <c r="S18" s="27"/>
-      <c r="T18" s="28"/>
-      <c r="U18" s="29"/>
-      <c r="V18" s="29"/>
-      <c r="W18" s="29"/>
-      <c r="X18" s="29"/>
-      <c r="Y18" s="29"/>
-      <c r="Z18" s="29"/>
-    </row>
-    <row r="19" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A19" s="185"/>
-      <c r="B19" s="53"/>
-      <c r="C19" s="186"/>
-      <c r="D19" s="53"/>
-      <c r="E19" s="186"/>
-      <c r="F19" s="53"/>
-      <c r="G19" s="167"/>
-      <c r="H19" s="52"/>
-      <c r="I19" s="53"/>
-      <c r="J19" s="167"/>
-      <c r="K19" s="53"/>
-      <c r="L19" s="171"/>
-      <c r="M19" s="52"/>
-      <c r="N19" s="53"/>
-      <c r="O19" s="171"/>
-      <c r="P19" s="52"/>
-      <c r="Q19" s="53"/>
-      <c r="R19" s="27"/>
-      <c r="S19" s="27"/>
-      <c r="T19" s="28"/>
-      <c r="U19" s="29"/>
-      <c r="V19" s="29"/>
-      <c r="W19" s="29"/>
-      <c r="X19" s="29"/>
-      <c r="Y19" s="29"/>
-      <c r="Z19" s="29"/>
-    </row>
-    <row r="20" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A20" s="185"/>
-      <c r="B20" s="53"/>
-      <c r="C20" s="186"/>
-      <c r="D20" s="53"/>
-      <c r="E20" s="186"/>
-      <c r="F20" s="53"/>
-      <c r="G20" s="167"/>
-      <c r="H20" s="52"/>
-      <c r="I20" s="53"/>
-      <c r="J20" s="167"/>
-      <c r="K20" s="53"/>
-      <c r="L20" s="171"/>
-      <c r="M20" s="52"/>
-      <c r="N20" s="53"/>
-      <c r="O20" s="171"/>
-      <c r="P20" s="52"/>
-      <c r="Q20" s="53"/>
-      <c r="R20" s="27"/>
-      <c r="S20" s="27"/>
-      <c r="T20" s="28"/>
-      <c r="U20" s="29"/>
-      <c r="V20" s="29"/>
-      <c r="W20" s="29"/>
-      <c r="X20" s="29"/>
-      <c r="Y20" s="29"/>
-      <c r="Z20" s="29"/>
-    </row>
-    <row r="21" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A21" s="185"/>
-      <c r="B21" s="53"/>
-      <c r="C21" s="186"/>
-      <c r="D21" s="53"/>
-      <c r="E21" s="186"/>
-      <c r="F21" s="53"/>
-      <c r="G21" s="167"/>
-      <c r="H21" s="52"/>
-      <c r="I21" s="53"/>
-      <c r="J21" s="167"/>
-      <c r="K21" s="53"/>
-      <c r="L21" s="171"/>
-      <c r="M21" s="52"/>
-      <c r="N21" s="53"/>
-      <c r="O21" s="171"/>
-      <c r="P21" s="52"/>
-      <c r="Q21" s="53"/>
-      <c r="R21" s="27"/>
-      <c r="S21" s="27"/>
-      <c r="T21" s="28"/>
-      <c r="U21" s="29"/>
-      <c r="V21" s="29"/>
-      <c r="W21" s="29"/>
-      <c r="X21" s="29"/>
-      <c r="Y21" s="29"/>
-      <c r="Z21" s="29"/>
-    </row>
-    <row r="22" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A22" s="185"/>
-      <c r="B22" s="53"/>
-      <c r="C22" s="186"/>
-      <c r="D22" s="53"/>
-      <c r="E22" s="186"/>
-      <c r="F22" s="53"/>
-      <c r="G22" s="167"/>
-      <c r="H22" s="52"/>
-      <c r="I22" s="53"/>
-      <c r="J22" s="167"/>
-      <c r="K22" s="53"/>
-      <c r="L22" s="171"/>
-      <c r="M22" s="52"/>
-      <c r="N22" s="53"/>
-      <c r="O22" s="171"/>
-      <c r="P22" s="52"/>
-      <c r="Q22" s="53"/>
-      <c r="R22" s="27"/>
-      <c r="S22" s="27"/>
-      <c r="T22" s="28"/>
-      <c r="U22" s="29"/>
-      <c r="V22" s="29"/>
-      <c r="W22" s="29"/>
-      <c r="X22" s="29"/>
-      <c r="Y22" s="29"/>
-      <c r="Z22" s="29"/>
-    </row>
-    <row r="23" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A23" s="185"/>
-      <c r="B23" s="53"/>
-      <c r="C23" s="186"/>
-      <c r="D23" s="53"/>
-      <c r="E23" s="186"/>
-      <c r="F23" s="53"/>
-      <c r="G23" s="167"/>
-      <c r="H23" s="52"/>
-      <c r="I23" s="53"/>
-      <c r="J23" s="167"/>
-      <c r="K23" s="53"/>
-      <c r="L23" s="171"/>
-      <c r="M23" s="52"/>
-      <c r="N23" s="53"/>
-      <c r="O23" s="171"/>
-      <c r="P23" s="52"/>
-      <c r="Q23" s="53"/>
-      <c r="R23" s="27"/>
-      <c r="S23" s="27"/>
-      <c r="T23" s="28"/>
-      <c r="U23" s="29"/>
-      <c r="V23" s="29"/>
-      <c r="W23" s="29"/>
-      <c r="X23" s="29"/>
-      <c r="Y23" s="29"/>
-      <c r="Z23" s="29"/>
-    </row>
-    <row r="24" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A24" s="185"/>
-      <c r="B24" s="53"/>
-      <c r="C24" s="186"/>
-      <c r="D24" s="53"/>
-      <c r="E24" s="186"/>
-      <c r="F24" s="53"/>
-      <c r="G24" s="167"/>
-      <c r="H24" s="52"/>
-      <c r="I24" s="53"/>
-      <c r="J24" s="167"/>
-      <c r="K24" s="53"/>
-      <c r="L24" s="171"/>
-      <c r="M24" s="52"/>
-      <c r="N24" s="53"/>
-      <c r="O24" s="171"/>
-      <c r="P24" s="52"/>
-      <c r="Q24" s="53"/>
-      <c r="R24" s="27"/>
-      <c r="S24" s="27"/>
-      <c r="T24" s="28"/>
-      <c r="U24" s="29"/>
-      <c r="V24" s="29"/>
-      <c r="W24" s="29"/>
-      <c r="X24" s="29"/>
-      <c r="Y24" s="29"/>
-      <c r="Z24" s="29"/>
-    </row>
-    <row r="25" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A25" s="185"/>
-      <c r="B25" s="53"/>
-      <c r="C25" s="186"/>
-      <c r="D25" s="53"/>
-      <c r="E25" s="186"/>
-      <c r="F25" s="53"/>
-      <c r="G25" s="167"/>
-      <c r="H25" s="52"/>
-      <c r="I25" s="53"/>
-      <c r="J25" s="167"/>
-      <c r="K25" s="53"/>
-      <c r="L25" s="171"/>
-      <c r="M25" s="52"/>
-      <c r="N25" s="53"/>
-      <c r="O25" s="171"/>
-      <c r="P25" s="52"/>
-      <c r="Q25" s="53"/>
-      <c r="R25" s="27"/>
-      <c r="S25" s="27"/>
-      <c r="T25" s="28"/>
-      <c r="U25" s="29"/>
-      <c r="V25" s="29"/>
-      <c r="W25" s="29"/>
-      <c r="X25" s="29"/>
-      <c r="Y25" s="29"/>
-      <c r="Z25" s="29"/>
-    </row>
-    <row r="26" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A26" s="185"/>
-      <c r="B26" s="53"/>
-      <c r="C26" s="186"/>
-      <c r="D26" s="53"/>
-      <c r="E26" s="186"/>
-      <c r="F26" s="53"/>
-      <c r="G26" s="167"/>
-      <c r="H26" s="52"/>
-      <c r="I26" s="53"/>
-      <c r="J26" s="167"/>
-      <c r="K26" s="53"/>
-      <c r="L26" s="171"/>
-      <c r="M26" s="52"/>
-      <c r="N26" s="53"/>
-      <c r="O26" s="171"/>
-      <c r="P26" s="52"/>
-      <c r="Q26" s="53"/>
-      <c r="R26" s="27"/>
-      <c r="S26" s="27"/>
-      <c r="T26" s="28"/>
-      <c r="U26" s="29"/>
-      <c r="V26" s="29"/>
-      <c r="W26" s="29"/>
-      <c r="X26" s="29"/>
-      <c r="Y26" s="29"/>
-      <c r="Z26" s="29"/>
-    </row>
-    <row r="27" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A27" s="185"/>
-      <c r="B27" s="53"/>
-      <c r="C27" s="186"/>
-      <c r="D27" s="53"/>
-      <c r="E27" s="186"/>
-      <c r="F27" s="53"/>
-      <c r="G27" s="167"/>
-      <c r="H27" s="52"/>
-      <c r="I27" s="53"/>
-      <c r="J27" s="167"/>
-      <c r="K27" s="53"/>
-      <c r="L27" s="171"/>
-      <c r="M27" s="52"/>
-      <c r="N27" s="53"/>
-      <c r="O27" s="171"/>
-      <c r="P27" s="52"/>
-      <c r="Q27" s="53"/>
-      <c r="R27" s="27"/>
-      <c r="S27" s="27"/>
-      <c r="T27" s="28"/>
-      <c r="U27" s="29"/>
-      <c r="V27" s="29"/>
-      <c r="W27" s="29"/>
-      <c r="X27" s="29"/>
-      <c r="Y27" s="29"/>
-      <c r="Z27" s="29"/>
-    </row>
-    <row r="28" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A28" s="185"/>
-      <c r="B28" s="53"/>
-      <c r="C28" s="186"/>
-      <c r="D28" s="53"/>
-      <c r="E28" s="186"/>
-      <c r="F28" s="53"/>
-      <c r="G28" s="167"/>
-      <c r="H28" s="52"/>
-      <c r="I28" s="53"/>
-      <c r="J28" s="167"/>
-      <c r="K28" s="53"/>
-      <c r="L28" s="171"/>
-      <c r="M28" s="52"/>
-      <c r="N28" s="53"/>
-      <c r="O28" s="171"/>
-      <c r="P28" s="52"/>
-      <c r="Q28" s="53"/>
-      <c r="R28" s="27"/>
-      <c r="S28" s="27"/>
-      <c r="T28" s="28"/>
-      <c r="U28" s="29"/>
-      <c r="V28" s="29"/>
-      <c r="W28" s="29"/>
-      <c r="X28" s="29"/>
-      <c r="Y28" s="29"/>
-      <c r="Z28" s="29"/>
-    </row>
-    <row r="29" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A29" s="185"/>
-      <c r="B29" s="53"/>
-      <c r="C29" s="186"/>
-      <c r="D29" s="53"/>
-      <c r="E29" s="186"/>
-      <c r="F29" s="53"/>
-      <c r="G29" s="167"/>
-      <c r="H29" s="52"/>
-      <c r="I29" s="53"/>
-      <c r="J29" s="167"/>
-      <c r="K29" s="53"/>
-      <c r="L29" s="171"/>
-      <c r="M29" s="52"/>
-      <c r="N29" s="53"/>
-      <c r="O29" s="171"/>
-      <c r="P29" s="52"/>
-      <c r="Q29" s="53"/>
-      <c r="R29" s="27"/>
-      <c r="S29" s="27"/>
-      <c r="T29" s="28"/>
-      <c r="U29" s="29"/>
-      <c r="V29" s="29"/>
-      <c r="W29" s="29"/>
-      <c r="X29" s="29"/>
-      <c r="Y29" s="29"/>
-      <c r="Z29" s="29"/>
-    </row>
-    <row r="30" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A30" s="185"/>
-      <c r="B30" s="53"/>
-      <c r="C30" s="186"/>
-      <c r="D30" s="53"/>
-      <c r="E30" s="186"/>
-      <c r="F30" s="53"/>
-      <c r="G30" s="167"/>
-      <c r="H30" s="52"/>
-      <c r="I30" s="53"/>
-      <c r="J30" s="167"/>
-      <c r="K30" s="53"/>
-      <c r="L30" s="171"/>
-      <c r="M30" s="52"/>
-      <c r="N30" s="53"/>
-      <c r="O30" s="171"/>
-      <c r="P30" s="52"/>
-      <c r="Q30" s="53"/>
-      <c r="R30" s="27"/>
-      <c r="S30" s="27"/>
-      <c r="T30" s="28"/>
-      <c r="U30" s="29"/>
-      <c r="V30" s="29"/>
-      <c r="W30" s="29"/>
-      <c r="X30" s="29"/>
-      <c r="Y30" s="29"/>
-      <c r="Z30" s="29"/>
-    </row>
-    <row r="31" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A31" s="189"/>
-      <c r="B31" s="170"/>
-      <c r="C31" s="190"/>
-      <c r="D31" s="170"/>
-      <c r="E31" s="190"/>
-      <c r="F31" s="170"/>
-      <c r="G31" s="168"/>
-      <c r="H31" s="169"/>
-      <c r="I31" s="170"/>
-      <c r="J31" s="168"/>
-      <c r="K31" s="170"/>
-      <c r="L31" s="172"/>
-      <c r="M31" s="169"/>
-      <c r="N31" s="170"/>
-      <c r="O31" s="172"/>
-      <c r="P31" s="169"/>
-      <c r="Q31" s="170"/>
-      <c r="R31" s="30"/>
-      <c r="S31" s="30"/>
-      <c r="T31" s="31"/>
-      <c r="U31" s="29"/>
-      <c r="V31" s="29"/>
-      <c r="W31" s="29"/>
-      <c r="X31" s="29"/>
-      <c r="Y31" s="29"/>
-      <c r="Z31" s="29"/>
-    </row>
-    <row r="32" spans="1:26" ht="12.75" customHeight="1">
-      <c r="D32" s="3"/>
-      <c r="E32" s="3"/>
-      <c r="F32" s="3"/>
-      <c r="G32" s="3"/>
-      <c r="H32" s="3"/>
-      <c r="I32" s="3"/>
-      <c r="J32" s="3"/>
-    </row>
-    <row r="33" spans="4:10" ht="12.75" customHeight="1">
-      <c r="D33" s="3"/>
-      <c r="E33" s="3"/>
-      <c r="F33" s="3"/>
-      <c r="G33" s="3"/>
-      <c r="H33" s="3"/>
-      <c r="I33" s="3"/>
-      <c r="J33" s="3"/>
-    </row>
-    <row r="34" spans="4:10" ht="12.75" customHeight="1"/>
-    <row r="35" spans="4:10" ht="12.75" customHeight="1"/>
-    <row r="36" spans="4:10" ht="12.75" customHeight="1"/>
-    <row r="37" spans="4:10" ht="12.75" customHeight="1"/>
-    <row r="38" spans="4:10" ht="12.75" customHeight="1"/>
-    <row r="39" spans="4:10" ht="12.75" customHeight="1"/>
-    <row r="40" spans="4:10" ht="12.75" customHeight="1"/>
-    <row r="41" spans="4:10" ht="12.75" customHeight="1"/>
-    <row r="42" spans="4:10" ht="12.75" customHeight="1"/>
-    <row r="43" spans="4:10" ht="12.75" customHeight="1"/>
-    <row r="44" spans="4:10" ht="12.75" customHeight="1"/>
-    <row r="45" spans="4:10" ht="12.75" customHeight="1"/>
-    <row r="46" spans="4:10" ht="12.75" customHeight="1"/>
-    <row r="47" spans="4:10" ht="12.75" customHeight="1"/>
-    <row r="48" spans="4:10" ht="12.75" customHeight="1"/>
-    <row r="49" ht="12.75" customHeight="1"/>
-    <row r="50" ht="12.75" customHeight="1"/>
-    <row r="51" ht="12.75" customHeight="1"/>
-    <row r="52" ht="12.75" customHeight="1"/>
-    <row r="53" ht="12.75" customHeight="1"/>
-    <row r="54" ht="12.75" customHeight="1"/>
-    <row r="55" ht="12.75" customHeight="1"/>
-    <row r="56" ht="12.75" customHeight="1"/>
-    <row r="57" ht="12.75" customHeight="1"/>
-    <row r="58" ht="12.75" customHeight="1"/>
-    <row r="59" ht="12.75" customHeight="1"/>
-    <row r="60" ht="12.75" customHeight="1"/>
-    <row r="61" ht="12.75" customHeight="1"/>
-    <row r="62" ht="12.75" customHeight="1"/>
-    <row r="63" ht="12.75" customHeight="1"/>
-    <row r="64" ht="12.75" customHeight="1"/>
-    <row r="65" ht="12.75" customHeight="1"/>
-    <row r="66" ht="12.75" customHeight="1"/>
-    <row r="67" ht="12.75" customHeight="1"/>
-    <row r="68" ht="12.75" customHeight="1"/>
-    <row r="69" ht="12.75" customHeight="1"/>
-    <row r="70" ht="12.75" customHeight="1"/>
-    <row r="71" ht="12.75" customHeight="1"/>
-    <row r="72" ht="12.75" customHeight="1"/>
-    <row r="73" ht="12.75" customHeight="1"/>
-    <row r="74" ht="12.75" customHeight="1"/>
-    <row r="75" ht="12.75" customHeight="1"/>
-    <row r="76" ht="12.75" customHeight="1"/>
-    <row r="77" ht="12.75" customHeight="1"/>
-    <row r="78" ht="12.75" customHeight="1"/>
-    <row r="79" ht="12.75" customHeight="1"/>
-    <row r="80" ht="12.75" customHeight="1"/>
-    <row r="81" ht="12.75" customHeight="1"/>
-    <row r="82" ht="12.75" customHeight="1"/>
-    <row r="83" ht="12.75" customHeight="1"/>
-    <row r="84" ht="12.75" customHeight="1"/>
-    <row r="85" ht="12.75" customHeight="1"/>
-    <row r="86" ht="12.75" customHeight="1"/>
-    <row r="87" ht="12.75" customHeight="1"/>
-    <row r="88" ht="12.75" customHeight="1"/>
-    <row r="89" ht="12.75" customHeight="1"/>
-    <row r="90" ht="12.75" customHeight="1"/>
-    <row r="91" ht="12.75" customHeight="1"/>
-    <row r="92" ht="12.75" customHeight="1"/>
-    <row r="93" ht="12.75" customHeight="1"/>
-    <row r="94" ht="12.75" customHeight="1"/>
-    <row r="95" ht="12.75" customHeight="1"/>
-    <row r="96" ht="12.75" customHeight="1"/>
-    <row r="97" ht="12.75" customHeight="1"/>
-    <row r="98" ht="12.75" customHeight="1"/>
-    <row r="99" ht="12.75" customHeight="1"/>
-    <row r="100" ht="12.75" customHeight="1"/>
-    <row r="101" ht="12.75" customHeight="1"/>
-    <row r="102" ht="12.75" customHeight="1"/>
-    <row r="103" ht="12.75" customHeight="1"/>
-    <row r="104" ht="12.75" customHeight="1"/>
-    <row r="105" ht="12.75" customHeight="1"/>
-    <row r="106" ht="12.75" customHeight="1"/>
-    <row r="107" ht="12.75" customHeight="1"/>
-    <row r="108" ht="12.75" customHeight="1"/>
-    <row r="109" ht="12.75" customHeight="1"/>
-    <row r="110" ht="12.75" customHeight="1"/>
-    <row r="111" ht="12.75" customHeight="1"/>
-    <row r="112" ht="12.75" customHeight="1"/>
-    <row r="113" ht="12.75" customHeight="1"/>
-    <row r="114" ht="12.75" customHeight="1"/>
-    <row r="115" ht="12.75" customHeight="1"/>
-    <row r="116" ht="12.75" customHeight="1"/>
-    <row r="117" ht="12.75" customHeight="1"/>
-    <row r="118" ht="12.75" customHeight="1"/>
-    <row r="119" ht="12.75" customHeight="1"/>
-    <row r="120" ht="12.75" customHeight="1"/>
-    <row r="121" ht="12.75" customHeight="1"/>
-    <row r="122" ht="12.75" customHeight="1"/>
-    <row r="123" ht="12.75" customHeight="1"/>
-    <row r="124" ht="12.75" customHeight="1"/>
-    <row r="125" ht="12.75" customHeight="1"/>
-    <row r="126" ht="12.75" customHeight="1"/>
-    <row r="127" ht="12.75" customHeight="1"/>
-    <row r="128" ht="12.75" customHeight="1"/>
-    <row r="129" ht="12.75" customHeight="1"/>
-    <row r="130" ht="12.75" customHeight="1"/>
-    <row r="131" ht="12.75" customHeight="1"/>
-    <row r="132" ht="12.75" customHeight="1"/>
-    <row r="133" ht="12.75" customHeight="1"/>
-    <row r="134" ht="12.75" customHeight="1"/>
-    <row r="135" ht="12.75" customHeight="1"/>
-    <row r="136" ht="12.75" customHeight="1"/>
-    <row r="137" ht="12.75" customHeight="1"/>
-    <row r="138" ht="12.75" customHeight="1"/>
-    <row r="139" ht="12.75" customHeight="1"/>
-    <row r="140" ht="12.75" customHeight="1"/>
-    <row r="141" ht="12.75" customHeight="1"/>
-    <row r="142" ht="12.75" customHeight="1"/>
-    <row r="143" ht="12.75" customHeight="1"/>
-    <row r="144" ht="12.75" customHeight="1"/>
-    <row r="145" ht="12.75" customHeight="1"/>
-    <row r="146" ht="12.75" customHeight="1"/>
-    <row r="147" ht="12.75" customHeight="1"/>
-    <row r="148" ht="12.75" customHeight="1"/>
-    <row r="149" ht="12.75" customHeight="1"/>
-    <row r="150" ht="12.75" customHeight="1"/>
-    <row r="151" ht="12.75" customHeight="1"/>
-    <row r="152" ht="12.75" customHeight="1"/>
-    <row r="153" ht="12.75" customHeight="1"/>
-    <row r="154" ht="12.75" customHeight="1"/>
-    <row r="155" ht="12.75" customHeight="1"/>
-    <row r="156" ht="12.75" customHeight="1"/>
-    <row r="157" ht="12.75" customHeight="1"/>
-    <row r="158" ht="12.75" customHeight="1"/>
-    <row r="159" ht="12.75" customHeight="1"/>
-    <row r="160" ht="12.75" customHeight="1"/>
-    <row r="161" ht="12.75" customHeight="1"/>
-    <row r="162" ht="12.75" customHeight="1"/>
-    <row r="163" ht="12.75" customHeight="1"/>
-    <row r="164" ht="12.75" customHeight="1"/>
-    <row r="165" ht="12.75" customHeight="1"/>
-    <row r="166" ht="12.75" customHeight="1"/>
-    <row r="167" ht="12.75" customHeight="1"/>
-    <row r="168" ht="12.75" customHeight="1"/>
-    <row r="169" ht="12.75" customHeight="1"/>
-    <row r="170" ht="12.75" customHeight="1"/>
-    <row r="171" ht="12.75" customHeight="1"/>
-    <row r="172" ht="12.75" customHeight="1"/>
-    <row r="173" ht="12.75" customHeight="1"/>
-    <row r="174" ht="12.75" customHeight="1"/>
-    <row r="175" ht="12.75" customHeight="1"/>
-    <row r="176" ht="12.75" customHeight="1"/>
-    <row r="177" ht="12.75" customHeight="1"/>
-    <row r="178" ht="12.75" customHeight="1"/>
-    <row r="179" ht="12.75" customHeight="1"/>
-    <row r="180" ht="12.75" customHeight="1"/>
-    <row r="181" ht="12.75" customHeight="1"/>
-    <row r="182" ht="12.75" customHeight="1"/>
-    <row r="183" ht="12.75" customHeight="1"/>
-    <row r="184" ht="12.75" customHeight="1"/>
-    <row r="185" ht="12.75" customHeight="1"/>
-    <row r="186" ht="12.75" customHeight="1"/>
-    <row r="187" ht="12.75" customHeight="1"/>
-    <row r="188" ht="12.75" customHeight="1"/>
-    <row r="189" ht="12.75" customHeight="1"/>
-    <row r="190" ht="12.75" customHeight="1"/>
-    <row r="191" ht="12.75" customHeight="1"/>
-    <row r="192" ht="12.75" customHeight="1"/>
-    <row r="193" ht="12.75" customHeight="1"/>
-    <row r="194" ht="12.75" customHeight="1"/>
-    <row r="195" ht="12.75" customHeight="1"/>
-    <row r="196" ht="12.75" customHeight="1"/>
-    <row r="197" ht="12.75" customHeight="1"/>
-    <row r="198" ht="12.75" customHeight="1"/>
-    <row r="199" ht="12.75" customHeight="1"/>
-    <row r="200" ht="12.75" customHeight="1"/>
-    <row r="201" ht="12.75" customHeight="1"/>
-    <row r="202" ht="12.75" customHeight="1"/>
-    <row r="203" ht="12.75" customHeight="1"/>
-    <row r="204" ht="12.75" customHeight="1"/>
-    <row r="205" ht="12.75" customHeight="1"/>
-    <row r="206" ht="12.75" customHeight="1"/>
-    <row r="207" ht="12.75" customHeight="1"/>
-    <row r="208" ht="12.75" customHeight="1"/>
-    <row r="209" ht="12.75" customHeight="1"/>
-    <row r="210" ht="12.75" customHeight="1"/>
-    <row r="211" ht="12.75" customHeight="1"/>
-    <row r="212" ht="12.75" customHeight="1"/>
-    <row r="213" ht="12.75" customHeight="1"/>
-    <row r="214" ht="12.75" customHeight="1"/>
-    <row r="215" ht="12.75" customHeight="1"/>
-    <row r="216" ht="12.75" customHeight="1"/>
-    <row r="217" ht="12.75" customHeight="1"/>
-    <row r="218" ht="12.75" customHeight="1"/>
-    <row r="219" ht="12.75" customHeight="1"/>
-    <row r="220" ht="12.75" customHeight="1"/>
-    <row r="221" ht="12.75" customHeight="1"/>
-    <row r="222" ht="12.75" customHeight="1"/>
-    <row r="223" ht="12.75" customHeight="1"/>
-    <row r="224" ht="12.75" customHeight="1"/>
-    <row r="225" ht="12.75" customHeight="1"/>
-    <row r="226" ht="12.75" customHeight="1"/>
-    <row r="227" ht="12.75" customHeight="1"/>
-    <row r="228" ht="12.75" customHeight="1"/>
-    <row r="229" ht="12.75" customHeight="1"/>
-    <row r="230" ht="12.75" customHeight="1"/>
-    <row r="231" ht="12.75" customHeight="1"/>
-    <row r="232" ht="12.75" customHeight="1"/>
-    <row r="233" ht="12.75" customHeight="1"/>
-    <row r="234" ht="12.75" customHeight="1"/>
-    <row r="235" ht="12.75" customHeight="1"/>
-    <row r="236" ht="12.75" customHeight="1"/>
-    <row r="237" ht="12.75" customHeight="1"/>
-    <row r="238" ht="12.75" customHeight="1"/>
-    <row r="239" ht="12.75" customHeight="1"/>
-    <row r="240" ht="12.75" customHeight="1"/>
-    <row r="241" ht="12.75" customHeight="1"/>
-    <row r="242" ht="12.75" customHeight="1"/>
-    <row r="243" ht="12.75" customHeight="1"/>
-    <row r="244" ht="12.75" customHeight="1"/>
-    <row r="245" ht="12.75" customHeight="1"/>
-    <row r="246" ht="12.75" customHeight="1"/>
-    <row r="247" ht="12.75" customHeight="1"/>
-    <row r="248" ht="12.75" customHeight="1"/>
-    <row r="249" ht="12.75" customHeight="1"/>
-    <row r="250" ht="12.75" customHeight="1"/>
-    <row r="251" ht="12.75" customHeight="1"/>
-    <row r="252" ht="12.75" customHeight="1"/>
-    <row r="253" ht="12.75" customHeight="1"/>
-    <row r="254" ht="12.75" customHeight="1"/>
-    <row r="255" ht="12.75" customHeight="1"/>
-    <row r="256" ht="12.75" customHeight="1"/>
-    <row r="257" ht="12.75" customHeight="1"/>
-    <row r="258" ht="12.75" customHeight="1"/>
-    <row r="259" ht="12.75" customHeight="1"/>
-    <row r="260" ht="12.75" customHeight="1"/>
-    <row r="261" ht="12.75" customHeight="1"/>
-    <row r="262" ht="12.75" customHeight="1"/>
-    <row r="263" ht="12.75" customHeight="1"/>
-    <row r="264" ht="12.75" customHeight="1"/>
-    <row r="265" ht="12.75" customHeight="1"/>
-    <row r="266" ht="12.75" customHeight="1"/>
-    <row r="267" ht="12.75" customHeight="1"/>
-    <row r="268" ht="12.75" customHeight="1"/>
-    <row r="269" ht="12.75" customHeight="1"/>
-    <row r="270" ht="12.75" customHeight="1"/>
-    <row r="271" ht="12.75" customHeight="1"/>
-    <row r="272" ht="12.75" customHeight="1"/>
-    <row r="273" ht="12.75" customHeight="1"/>
-    <row r="274" ht="12.75" customHeight="1"/>
-    <row r="275" ht="12.75" customHeight="1"/>
-    <row r="276" ht="12.75" customHeight="1"/>
-    <row r="277" ht="12.75" customHeight="1"/>
-    <row r="278" ht="12.75" customHeight="1"/>
-    <row r="279" ht="12.75" customHeight="1"/>
-    <row r="280" ht="12.75" customHeight="1"/>
-    <row r="281" ht="12.75" customHeight="1"/>
-    <row r="282" ht="12.75" customHeight="1"/>
-    <row r="283" ht="12.75" customHeight="1"/>
-    <row r="284" ht="12.75" customHeight="1"/>
-    <row r="285" ht="12.75" customHeight="1"/>
-    <row r="286" ht="12.75" customHeight="1"/>
-    <row r="287" ht="12.75" customHeight="1"/>
-    <row r="288" ht="12.75" customHeight="1"/>
-    <row r="289" ht="12.75" customHeight="1"/>
-    <row r="290" ht="12.75" customHeight="1"/>
-    <row r="291" ht="12.75" customHeight="1"/>
-    <row r="292" ht="12.75" customHeight="1"/>
-    <row r="293" ht="12.75" customHeight="1"/>
-    <row r="294" ht="12.75" customHeight="1"/>
-    <row r="295" ht="12.75" customHeight="1"/>
-    <row r="296" ht="12.75" customHeight="1"/>
-    <row r="297" ht="12.75" customHeight="1"/>
-    <row r="298" ht="12.75" customHeight="1"/>
-    <row r="299" ht="12.75" customHeight="1"/>
-    <row r="300" ht="12.75" customHeight="1"/>
-    <row r="301" ht="12.75" customHeight="1"/>
-    <row r="302" ht="12.75" customHeight="1"/>
-    <row r="303" ht="12.75" customHeight="1"/>
-    <row r="304" ht="12.75" customHeight="1"/>
-    <row r="305" ht="12.75" customHeight="1"/>
-    <row r="306" ht="12.75" customHeight="1"/>
-    <row r="307" ht="12.75" customHeight="1"/>
-    <row r="308" ht="12.75" customHeight="1"/>
-    <row r="309" ht="12.75" customHeight="1"/>
-    <row r="310" ht="12.75" customHeight="1"/>
-    <row r="311" ht="12.75" customHeight="1"/>
-    <row r="312" ht="12.75" customHeight="1"/>
-    <row r="313" ht="12.75" customHeight="1"/>
-    <row r="314" ht="12.75" customHeight="1"/>
-    <row r="315" ht="12.75" customHeight="1"/>
-    <row r="316" ht="12.75" customHeight="1"/>
-    <row r="317" ht="12.75" customHeight="1"/>
-    <row r="318" ht="12.75" customHeight="1"/>
-    <row r="319" ht="12.75" customHeight="1"/>
-    <row r="320" ht="12.75" customHeight="1"/>
-    <row r="321" ht="12.75" customHeight="1"/>
-    <row r="322" ht="12.75" customHeight="1"/>
-    <row r="323" ht="12.75" customHeight="1"/>
-    <row r="324" ht="12.75" customHeight="1"/>
-    <row r="325" ht="12.75" customHeight="1"/>
-    <row r="326" ht="12.75" customHeight="1"/>
-    <row r="327" ht="12.75" customHeight="1"/>
-    <row r="328" ht="12.75" customHeight="1"/>
-    <row r="329" ht="12.75" customHeight="1"/>
-    <row r="330" ht="12.75" customHeight="1"/>
-    <row r="331" ht="12.75" customHeight="1"/>
-    <row r="332" ht="12.75" customHeight="1"/>
-    <row r="333" ht="12.75" customHeight="1"/>
-    <row r="334" ht="12.75" customHeight="1"/>
-    <row r="335" ht="12.75" customHeight="1"/>
-    <row r="336" ht="12.75" customHeight="1"/>
-    <row r="337" ht="12.75" customHeight="1"/>
-    <row r="338" ht="12.75" customHeight="1"/>
-    <row r="339" ht="12.75" customHeight="1"/>
-    <row r="340" ht="12.75" customHeight="1"/>
-    <row r="341" ht="12.75" customHeight="1"/>
-    <row r="342" ht="12.75" customHeight="1"/>
-    <row r="343" ht="12.75" customHeight="1"/>
-    <row r="344" ht="12.75" customHeight="1"/>
-    <row r="345" ht="12.75" customHeight="1"/>
-    <row r="346" ht="12.75" customHeight="1"/>
-    <row r="347" ht="12.75" customHeight="1"/>
-    <row r="348" ht="12.75" customHeight="1"/>
-    <row r="349" ht="12.75" customHeight="1"/>
-    <row r="350" ht="12.75" customHeight="1"/>
-    <row r="351" ht="12.75" customHeight="1"/>
-    <row r="352" ht="12.75" customHeight="1"/>
-    <row r="353" ht="12.75" customHeight="1"/>
-    <row r="354" ht="12.75" customHeight="1"/>
-    <row r="355" ht="12.75" customHeight="1"/>
-    <row r="356" ht="12.75" customHeight="1"/>
-    <row r="357" ht="12.75" customHeight="1"/>
-    <row r="358" ht="12.75" customHeight="1"/>
-    <row r="359" ht="12.75" customHeight="1"/>
-    <row r="360" ht="12.75" customHeight="1"/>
-    <row r="361" ht="12.75" customHeight="1"/>
-    <row r="362" ht="12.75" customHeight="1"/>
-    <row r="363" ht="12.75" customHeight="1"/>
-    <row r="364" ht="12.75" customHeight="1"/>
-    <row r="365" ht="12.75" customHeight="1"/>
-    <row r="366" ht="12.75" customHeight="1"/>
-    <row r="367" ht="12.75" customHeight="1"/>
-    <row r="368" ht="12.75" customHeight="1"/>
-    <row r="369" ht="12.75" customHeight="1"/>
-    <row r="370" ht="12.75" customHeight="1"/>
-    <row r="371" ht="12.75" customHeight="1"/>
-    <row r="372" ht="12.75" customHeight="1"/>
-    <row r="373" ht="12.75" customHeight="1"/>
-    <row r="374" ht="12.75" customHeight="1"/>
-    <row r="375" ht="12.75" customHeight="1"/>
-    <row r="376" ht="12.75" customHeight="1"/>
-    <row r="377" ht="12.75" customHeight="1"/>
-    <row r="378" ht="12.75" customHeight="1"/>
-    <row r="379" ht="12.75" customHeight="1"/>
-    <row r="380" ht="12.75" customHeight="1"/>
-    <row r="381" ht="12.75" customHeight="1"/>
-    <row r="382" ht="12.75" customHeight="1"/>
-    <row r="383" ht="12.75" customHeight="1"/>
-    <row r="384" ht="12.75" customHeight="1"/>
-    <row r="385" ht="12.75" customHeight="1"/>
-    <row r="386" ht="12.75" customHeight="1"/>
-    <row r="387" ht="12.75" customHeight="1"/>
-    <row r="388" ht="12.75" customHeight="1"/>
-    <row r="389" ht="12.75" customHeight="1"/>
-    <row r="390" ht="12.75" customHeight="1"/>
-    <row r="391" ht="12.75" customHeight="1"/>
-    <row r="392" ht="12.75" customHeight="1"/>
-    <row r="393" ht="12.75" customHeight="1"/>
-    <row r="394" ht="12.75" customHeight="1"/>
-    <row r="395" ht="12.75" customHeight="1"/>
-    <row r="396" ht="12.75" customHeight="1"/>
-    <row r="397" ht="12.75" customHeight="1"/>
-    <row r="398" ht="12.75" customHeight="1"/>
-    <row r="399" ht="12.75" customHeight="1"/>
-    <row r="400" ht="12.75" customHeight="1"/>
-    <row r="401" ht="12.75" customHeight="1"/>
-    <row r="402" ht="12.75" customHeight="1"/>
-    <row r="403" ht="12.75" customHeight="1"/>
-    <row r="404" ht="12.75" customHeight="1"/>
-    <row r="405" ht="12.75" customHeight="1"/>
-    <row r="406" ht="12.75" customHeight="1"/>
-    <row r="407" ht="12.75" customHeight="1"/>
-    <row r="408" ht="12.75" customHeight="1"/>
-    <row r="409" ht="12.75" customHeight="1"/>
-    <row r="410" ht="12.75" customHeight="1"/>
-    <row r="411" ht="12.75" customHeight="1"/>
-    <row r="412" ht="12.75" customHeight="1"/>
-    <row r="413" ht="12.75" customHeight="1"/>
-    <row r="414" ht="12.75" customHeight="1"/>
-    <row r="415" ht="12.75" customHeight="1"/>
-    <row r="416" ht="12.75" customHeight="1"/>
-    <row r="417" ht="12.75" customHeight="1"/>
-    <row r="418" ht="12.75" customHeight="1"/>
-    <row r="419" ht="12.75" customHeight="1"/>
-    <row r="420" ht="12.75" customHeight="1"/>
-    <row r="421" ht="12.75" customHeight="1"/>
-    <row r="422" ht="12.75" customHeight="1"/>
-    <row r="423" ht="12.75" customHeight="1"/>
-    <row r="424" ht="12.75" customHeight="1"/>
-    <row r="425" ht="12.75" customHeight="1"/>
-    <row r="426" ht="12.75" customHeight="1"/>
-    <row r="427" ht="12.75" customHeight="1"/>
-    <row r="428" ht="12.75" customHeight="1"/>
-    <row r="429" ht="12.75" customHeight="1"/>
-    <row r="430" ht="12.75" customHeight="1"/>
-    <row r="431" ht="12.75" customHeight="1"/>
-    <row r="432" ht="12.75" customHeight="1"/>
-    <row r="433" ht="12.75" customHeight="1"/>
-    <row r="434" ht="12.75" customHeight="1"/>
-    <row r="435" ht="12.75" customHeight="1"/>
-    <row r="436" ht="12.75" customHeight="1"/>
-    <row r="437" ht="12.75" customHeight="1"/>
-    <row r="438" ht="12.75" customHeight="1"/>
-    <row r="439" ht="12.75" customHeight="1"/>
-    <row r="440" ht="12.75" customHeight="1"/>
-    <row r="441" ht="12.75" customHeight="1"/>
-    <row r="442" ht="12.75" customHeight="1"/>
-    <row r="443" ht="12.75" customHeight="1"/>
-    <row r="444" ht="12.75" customHeight="1"/>
-    <row r="445" ht="12.75" customHeight="1"/>
-    <row r="446" ht="12.75" customHeight="1"/>
-    <row r="447" ht="12.75" customHeight="1"/>
-    <row r="448" ht="12.75" customHeight="1"/>
-    <row r="449" ht="12.75" customHeight="1"/>
-    <row r="450" ht="12.75" customHeight="1"/>
-    <row r="451" ht="12.75" customHeight="1"/>
-    <row r="452" ht="12.75" customHeight="1"/>
-    <row r="453" ht="12.75" customHeight="1"/>
-    <row r="454" ht="12.75" customHeight="1"/>
-    <row r="455" ht="12.75" customHeight="1"/>
-    <row r="456" ht="12.75" customHeight="1"/>
-    <row r="457" ht="12.75" customHeight="1"/>
-    <row r="458" ht="12.75" customHeight="1"/>
-    <row r="459" ht="12.75" customHeight="1"/>
-    <row r="460" ht="12.75" customHeight="1"/>
-    <row r="461" ht="12.75" customHeight="1"/>
-    <row r="462" ht="12.75" customHeight="1"/>
-    <row r="463" ht="12.75" customHeight="1"/>
-    <row r="464" ht="12.75" customHeight="1"/>
-    <row r="465" ht="12.75" customHeight="1"/>
-    <row r="466" ht="12.75" customHeight="1"/>
-    <row r="467" ht="12.75" customHeight="1"/>
-    <row r="468" ht="12.75" customHeight="1"/>
-    <row r="469" ht="12.75" customHeight="1"/>
-    <row r="470" ht="12.75" customHeight="1"/>
-    <row r="471" ht="12.75" customHeight="1"/>
-    <row r="472" ht="12.75" customHeight="1"/>
-    <row r="473" ht="12.75" customHeight="1"/>
-    <row r="474" ht="12.75" customHeight="1"/>
-    <row r="475" ht="12.75" customHeight="1"/>
-    <row r="476" ht="12.75" customHeight="1"/>
-    <row r="477" ht="12.75" customHeight="1"/>
-    <row r="478" ht="12.75" customHeight="1"/>
-    <row r="479" ht="12.75" customHeight="1"/>
-    <row r="480" ht="12.75" customHeight="1"/>
-    <row r="481" ht="12.75" customHeight="1"/>
-    <row r="482" ht="12.75" customHeight="1"/>
-    <row r="483" ht="12.75" customHeight="1"/>
-    <row r="484" ht="12.75" customHeight="1"/>
-    <row r="485" ht="12.75" customHeight="1"/>
-    <row r="486" ht="12.75" customHeight="1"/>
-    <row r="487" ht="12.75" customHeight="1"/>
-    <row r="488" ht="12.75" customHeight="1"/>
-    <row r="489" ht="12.75" customHeight="1"/>
-    <row r="490" ht="12.75" customHeight="1"/>
-    <row r="491" ht="12.75" customHeight="1"/>
-    <row r="492" ht="12.75" customHeight="1"/>
-    <row r="493" ht="12.75" customHeight="1"/>
-    <row r="494" ht="12.75" customHeight="1"/>
-    <row r="495" ht="12.75" customHeight="1"/>
-    <row r="496" ht="12.75" customHeight="1"/>
-    <row r="497" ht="12.75" customHeight="1"/>
-    <row r="498" ht="12.75" customHeight="1"/>
-    <row r="499" ht="12.75" customHeight="1"/>
-    <row r="500" ht="12.75" customHeight="1"/>
-    <row r="501" ht="12.75" customHeight="1"/>
-    <row r="502" ht="12.75" customHeight="1"/>
-    <row r="503" ht="12.75" customHeight="1"/>
-    <row r="504" ht="12.75" customHeight="1"/>
-    <row r="505" ht="12.75" customHeight="1"/>
-    <row r="506" ht="12.75" customHeight="1"/>
-    <row r="507" ht="12.75" customHeight="1"/>
-    <row r="508" ht="12.75" customHeight="1"/>
-    <row r="509" ht="12.75" customHeight="1"/>
-    <row r="510" ht="12.75" customHeight="1"/>
-    <row r="511" ht="12.75" customHeight="1"/>
-    <row r="512" ht="12.75" customHeight="1"/>
-    <row r="513" ht="12.75" customHeight="1"/>
-    <row r="514" ht="12.75" customHeight="1"/>
-    <row r="515" ht="12.75" customHeight="1"/>
-    <row r="516" ht="12.75" customHeight="1"/>
-    <row r="517" ht="12.75" customHeight="1"/>
-    <row r="518" ht="12.75" customHeight="1"/>
-    <row r="519" ht="12.75" customHeight="1"/>
-    <row r="520" ht="12.75" customHeight="1"/>
-    <row r="521" ht="12.75" customHeight="1"/>
-    <row r="522" ht="12.75" customHeight="1"/>
-    <row r="523" ht="12.75" customHeight="1"/>
-    <row r="524" ht="12.75" customHeight="1"/>
-    <row r="525" ht="12.75" customHeight="1"/>
-    <row r="526" ht="12.75" customHeight="1"/>
-    <row r="527" ht="12.75" customHeight="1"/>
-    <row r="528" ht="12.75" customHeight="1"/>
-    <row r="529" ht="12.75" customHeight="1"/>
-    <row r="530" ht="12.75" customHeight="1"/>
-    <row r="531" ht="12.75" customHeight="1"/>
-    <row r="532" ht="12.75" customHeight="1"/>
-    <row r="533" ht="12.75" customHeight="1"/>
-    <row r="534" ht="12.75" customHeight="1"/>
-    <row r="535" ht="12.75" customHeight="1"/>
-    <row r="536" ht="12.75" customHeight="1"/>
-    <row r="537" ht="12.75" customHeight="1"/>
-    <row r="538" ht="12.75" customHeight="1"/>
-    <row r="539" ht="12.75" customHeight="1"/>
-    <row r="540" ht="12.75" customHeight="1"/>
-    <row r="541" ht="12.75" customHeight="1"/>
-    <row r="542" ht="12.75" customHeight="1"/>
-    <row r="543" ht="12.75" customHeight="1"/>
-    <row r="544" ht="12.75" customHeight="1"/>
-    <row r="545" ht="12.75" customHeight="1"/>
-    <row r="546" ht="12.75" customHeight="1"/>
-    <row r="547" ht="12.75" customHeight="1"/>
-    <row r="548" ht="12.75" customHeight="1"/>
-    <row r="549" ht="12.75" customHeight="1"/>
-    <row r="550" ht="12.75" customHeight="1"/>
-    <row r="551" ht="12.75" customHeight="1"/>
-    <row r="552" ht="12.75" customHeight="1"/>
-    <row r="553" ht="12.75" customHeight="1"/>
-    <row r="554" ht="12.75" customHeight="1"/>
-    <row r="555" ht="12.75" customHeight="1"/>
-    <row r="556" ht="12.75" customHeight="1"/>
-    <row r="557" ht="12.75" customHeight="1"/>
-    <row r="558" ht="12.75" customHeight="1"/>
-    <row r="559" ht="12.75" customHeight="1"/>
-    <row r="560" ht="12.75" customHeight="1"/>
-    <row r="561" ht="12.75" customHeight="1"/>
-    <row r="562" ht="12.75" customHeight="1"/>
-    <row r="563" ht="12.75" customHeight="1"/>
-    <row r="564" ht="12.75" customHeight="1"/>
-    <row r="565" ht="12.75" customHeight="1"/>
-    <row r="566" ht="12.75" customHeight="1"/>
-    <row r="567" ht="12.75" customHeight="1"/>
-    <row r="568" ht="12.75" customHeight="1"/>
-    <row r="569" ht="12.75" customHeight="1"/>
-    <row r="570" ht="12.75" customHeight="1"/>
-    <row r="571" ht="12.75" customHeight="1"/>
-    <row r="572" ht="12.75" customHeight="1"/>
-    <row r="573" ht="12.75" customHeight="1"/>
-    <row r="574" ht="12.75" customHeight="1"/>
-    <row r="575" ht="12.75" customHeight="1"/>
-    <row r="576" ht="12.75" customHeight="1"/>
-    <row r="577" ht="12.75" customHeight="1"/>
-    <row r="578" ht="12.75" customHeight="1"/>
-    <row r="579" ht="12.75" customHeight="1"/>
-    <row r="580" ht="12.75" customHeight="1"/>
-    <row r="581" ht="12.75" customHeight="1"/>
-    <row r="582" ht="12.75" customHeight="1"/>
-    <row r="583" ht="12.75" customHeight="1"/>
-    <row r="584" ht="12.75" customHeight="1"/>
-    <row r="585" ht="12.75" customHeight="1"/>
-    <row r="586" ht="12.75" customHeight="1"/>
-    <row r="587" ht="12.75" customHeight="1"/>
-    <row r="588" ht="12.75" customHeight="1"/>
-    <row r="589" ht="12.75" customHeight="1"/>
-    <row r="590" ht="12.75" customHeight="1"/>
-    <row r="591" ht="12.75" customHeight="1"/>
-    <row r="592" ht="12.75" customHeight="1"/>
-    <row r="593" ht="12.75" customHeight="1"/>
-    <row r="594" ht="12.75" customHeight="1"/>
-    <row r="595" ht="12.75" customHeight="1"/>
-    <row r="596" ht="12.75" customHeight="1"/>
-    <row r="597" ht="12.75" customHeight="1"/>
-    <row r="598" ht="12.75" customHeight="1"/>
-    <row r="599" ht="12.75" customHeight="1"/>
-    <row r="600" ht="12.75" customHeight="1"/>
-    <row r="601" ht="12.75" customHeight="1"/>
-    <row r="602" ht="12.75" customHeight="1"/>
-    <row r="603" ht="12.75" customHeight="1"/>
-    <row r="604" ht="12.75" customHeight="1"/>
-    <row r="605" ht="12.75" customHeight="1"/>
-    <row r="606" ht="12.75" customHeight="1"/>
-    <row r="607" ht="12.75" customHeight="1"/>
-    <row r="608" ht="12.75" customHeight="1"/>
-    <row r="609" ht="12.75" customHeight="1"/>
-    <row r="610" ht="12.75" customHeight="1"/>
-    <row r="611" ht="12.75" customHeight="1"/>
-    <row r="612" ht="12.75" customHeight="1"/>
-    <row r="613" ht="12.75" customHeight="1"/>
-    <row r="614" ht="12.75" customHeight="1"/>
-    <row r="615" ht="12.75" customHeight="1"/>
-    <row r="616" ht="12.75" customHeight="1"/>
-    <row r="617" ht="12.75" customHeight="1"/>
-    <row r="618" ht="12.75" customHeight="1"/>
-    <row r="619" ht="12.75" customHeight="1"/>
-    <row r="620" ht="12.75" customHeight="1"/>
-    <row r="621" ht="12.75" customHeight="1"/>
-    <row r="622" ht="12.75" customHeight="1"/>
-    <row r="623" ht="12.75" customHeight="1"/>
-    <row r="624" ht="12.75" customHeight="1"/>
-    <row r="625" ht="12.75" customHeight="1"/>
-    <row r="626" ht="12.75" customHeight="1"/>
-    <row r="627" ht="12.75" customHeight="1"/>
-    <row r="628" ht="12.75" customHeight="1"/>
-    <row r="629" ht="12.75" customHeight="1"/>
-    <row r="630" ht="12.75" customHeight="1"/>
-    <row r="631" ht="12.75" customHeight="1"/>
-    <row r="632" ht="12.75" customHeight="1"/>
-    <row r="633" ht="12.75" customHeight="1"/>
-    <row r="634" ht="12.75" customHeight="1"/>
-    <row r="635" ht="12.75" customHeight="1"/>
-    <row r="636" ht="12.75" customHeight="1"/>
-    <row r="637" ht="12.75" customHeight="1"/>
-    <row r="638" ht="12.75" customHeight="1"/>
-    <row r="639" ht="12.75" customHeight="1"/>
-    <row r="640" ht="12.75" customHeight="1"/>
-    <row r="641" ht="12.75" customHeight="1"/>
-    <row r="642" ht="12.75" customHeight="1"/>
-    <row r="643" ht="12.75" customHeight="1"/>
-    <row r="644" ht="12.75" customHeight="1"/>
-    <row r="645" ht="12.75" customHeight="1"/>
-    <row r="646" ht="12.75" customHeight="1"/>
-    <row r="647" ht="12.75" customHeight="1"/>
-    <row r="648" ht="12.75" customHeight="1"/>
-    <row r="649" ht="12.75" customHeight="1"/>
-    <row r="650" ht="12.75" customHeight="1"/>
-    <row r="651" ht="12.75" customHeight="1"/>
-    <row r="652" ht="12.75" customHeight="1"/>
-    <row r="653" ht="12.75" customHeight="1"/>
-    <row r="654" ht="12.75" customHeight="1"/>
-    <row r="655" ht="12.75" customHeight="1"/>
-    <row r="656" ht="12.75" customHeight="1"/>
-    <row r="657" ht="12.75" customHeight="1"/>
-    <row r="658" ht="12.75" customHeight="1"/>
-    <row r="659" ht="12.75" customHeight="1"/>
-    <row r="660" ht="12.75" customHeight="1"/>
-    <row r="661" ht="12.75" customHeight="1"/>
-    <row r="662" ht="12.75" customHeight="1"/>
-    <row r="663" ht="12.75" customHeight="1"/>
-    <row r="664" ht="12.75" customHeight="1"/>
-    <row r="665" ht="12.75" customHeight="1"/>
-    <row r="666" ht="12.75" customHeight="1"/>
-    <row r="667" ht="12.75" customHeight="1"/>
-    <row r="668" ht="12.75" customHeight="1"/>
-    <row r="669" ht="12.75" customHeight="1"/>
-    <row r="670" ht="12.75" customHeight="1"/>
-    <row r="671" ht="12.75" customHeight="1"/>
-    <row r="672" ht="12.75" customHeight="1"/>
-    <row r="673" ht="12.75" customHeight="1"/>
-    <row r="674" ht="12.75" customHeight="1"/>
-    <row r="675" ht="12.75" customHeight="1"/>
-    <row r="676" ht="12.75" customHeight="1"/>
-    <row r="677" ht="12.75" customHeight="1"/>
-    <row r="678" ht="12.75" customHeight="1"/>
-    <row r="679" ht="12.75" customHeight="1"/>
-    <row r="680" ht="12.75" customHeight="1"/>
-    <row r="681" ht="12.75" customHeight="1"/>
-    <row r="682" ht="12.75" customHeight="1"/>
-    <row r="683" ht="12.75" customHeight="1"/>
-    <row r="684" ht="12.75" customHeight="1"/>
-    <row r="685" ht="12.75" customHeight="1"/>
-    <row r="686" ht="12.75" customHeight="1"/>
-    <row r="687" ht="12.75" customHeight="1"/>
-    <row r="688" ht="12.75" customHeight="1"/>
-    <row r="689" ht="12.75" customHeight="1"/>
-    <row r="690" ht="12.75" customHeight="1"/>
-    <row r="691" ht="12.75" customHeight="1"/>
-    <row r="692" ht="12.75" customHeight="1"/>
-    <row r="693" ht="12.75" customHeight="1"/>
-    <row r="694" ht="12.75" customHeight="1"/>
-    <row r="695" ht="12.75" customHeight="1"/>
-    <row r="696" ht="12.75" customHeight="1"/>
-    <row r="697" ht="12.75" customHeight="1"/>
-    <row r="698" ht="12.75" customHeight="1"/>
-    <row r="699" ht="12.75" customHeight="1"/>
-    <row r="700" ht="12.75" customHeight="1"/>
-    <row r="701" ht="12.75" customHeight="1"/>
-    <row r="702" ht="12.75" customHeight="1"/>
-    <row r="703" ht="12.75" customHeight="1"/>
-    <row r="704" ht="12.75" customHeight="1"/>
-    <row r="705" ht="12.75" customHeight="1"/>
-    <row r="706" ht="12.75" customHeight="1"/>
-    <row r="707" ht="12.75" customHeight="1"/>
-    <row r="708" ht="12.75" customHeight="1"/>
-    <row r="709" ht="12.75" customHeight="1"/>
-    <row r="710" ht="12.75" customHeight="1"/>
-    <row r="711" ht="12.75" customHeight="1"/>
-    <row r="712" ht="12.75" customHeight="1"/>
-    <row r="713" ht="12.75" customHeight="1"/>
-    <row r="714" ht="12.75" customHeight="1"/>
-    <row r="715" ht="12.75" customHeight="1"/>
-    <row r="716" ht="12.75" customHeight="1"/>
-    <row r="717" ht="12.75" customHeight="1"/>
-    <row r="718" ht="12.75" customHeight="1"/>
-    <row r="719" ht="12.75" customHeight="1"/>
-    <row r="720" ht="12.75" customHeight="1"/>
-    <row r="721" ht="12.75" customHeight="1"/>
-    <row r="722" ht="12.75" customHeight="1"/>
-    <row r="723" ht="12.75" customHeight="1"/>
-    <row r="724" ht="12.75" customHeight="1"/>
-    <row r="725" ht="12.75" customHeight="1"/>
-    <row r="726" ht="12.75" customHeight="1"/>
-    <row r="727" ht="12.75" customHeight="1"/>
-    <row r="728" ht="12.75" customHeight="1"/>
-    <row r="729" ht="12.75" customHeight="1"/>
-    <row r="730" ht="12.75" customHeight="1"/>
-    <row r="731" ht="12.75" customHeight="1"/>
-    <row r="732" ht="12.75" customHeight="1"/>
-    <row r="733" ht="12.75" customHeight="1"/>
-    <row r="734" ht="12.75" customHeight="1"/>
-    <row r="735" ht="12.75" customHeight="1"/>
-    <row r="736" ht="12.75" customHeight="1"/>
-    <row r="737" ht="12.75" customHeight="1"/>
-    <row r="738" ht="12.75" customHeight="1"/>
-    <row r="739" ht="12.75" customHeight="1"/>
-    <row r="740" ht="12.75" customHeight="1"/>
-    <row r="741" ht="12.75" customHeight="1"/>
-    <row r="742" ht="12.75" customHeight="1"/>
-    <row r="743" ht="12.75" customHeight="1"/>
-    <row r="744" ht="12.75" customHeight="1"/>
-    <row r="745" ht="12.75" customHeight="1"/>
-    <row r="746" ht="12.75" customHeight="1"/>
-    <row r="747" ht="12.75" customHeight="1"/>
-    <row r="748" ht="12.75" customHeight="1"/>
-    <row r="749" ht="12.75" customHeight="1"/>
-    <row r="750" ht="12.75" customHeight="1"/>
-    <row r="751" ht="12.75" customHeight="1"/>
-    <row r="752" ht="12.75" customHeight="1"/>
-    <row r="753" ht="12.75" customHeight="1"/>
-    <row r="754" ht="12.75" customHeight="1"/>
-    <row r="755" ht="12.75" customHeight="1"/>
-    <row r="756" ht="12.75" customHeight="1"/>
-    <row r="757" ht="12.75" customHeight="1"/>
-    <row r="758" ht="12.75" customHeight="1"/>
-    <row r="759" ht="12.75" customHeight="1"/>
-    <row r="760" ht="12.75" customHeight="1"/>
-    <row r="761" ht="12.75" customHeight="1"/>
-    <row r="762" ht="12.75" customHeight="1"/>
-    <row r="763" ht="12.75" customHeight="1"/>
-    <row r="764" ht="12.75" customHeight="1"/>
-    <row r="765" ht="12.75" customHeight="1"/>
-    <row r="766" ht="12.75" customHeight="1"/>
-    <row r="767" ht="12.75" customHeight="1"/>
-    <row r="768" ht="12.75" customHeight="1"/>
-    <row r="769" ht="12.75" customHeight="1"/>
-    <row r="770" ht="12.75" customHeight="1"/>
-    <row r="771" ht="12.75" customHeight="1"/>
-    <row r="772" ht="12.75" customHeight="1"/>
-    <row r="773" ht="12.75" customHeight="1"/>
-    <row r="774" ht="12.75" customHeight="1"/>
-    <row r="775" ht="12.75" customHeight="1"/>
-    <row r="776" ht="12.75" customHeight="1"/>
-    <row r="777" ht="12.75" customHeight="1"/>
-    <row r="778" ht="12.75" customHeight="1"/>
-    <row r="779" ht="12.75" customHeight="1"/>
-    <row r="780" ht="12.75" customHeight="1"/>
-    <row r="781" ht="12.75" customHeight="1"/>
-    <row r="782" ht="12.75" customHeight="1"/>
-    <row r="783" ht="12.75" customHeight="1"/>
-    <row r="784" ht="12.75" customHeight="1"/>
-    <row r="785" ht="12.75" customHeight="1"/>
-    <row r="786" ht="12.75" customHeight="1"/>
-    <row r="787" ht="12.75" customHeight="1"/>
-    <row r="788" ht="12.75" customHeight="1"/>
-    <row r="789" ht="12.75" customHeight="1"/>
-    <row r="790" ht="12.75" customHeight="1"/>
-    <row r="791" ht="12.75" customHeight="1"/>
-    <row r="792" ht="12.75" customHeight="1"/>
-    <row r="793" ht="12.75" customHeight="1"/>
-    <row r="794" ht="12.75" customHeight="1"/>
-    <row r="795" ht="12.75" customHeight="1"/>
-    <row r="796" ht="12.75" customHeight="1"/>
-    <row r="797" ht="12.75" customHeight="1"/>
-    <row r="798" ht="12.75" customHeight="1"/>
-    <row r="799" ht="12.75" customHeight="1"/>
-    <row r="800" ht="12.75" customHeight="1"/>
-    <row r="801" ht="12.75" customHeight="1"/>
-    <row r="802" ht="12.75" customHeight="1"/>
-    <row r="803" ht="12.75" customHeight="1"/>
-    <row r="804" ht="12.75" customHeight="1"/>
-    <row r="805" ht="12.75" customHeight="1"/>
-    <row r="806" ht="12.75" customHeight="1"/>
-    <row r="807" ht="12.75" customHeight="1"/>
-    <row r="808" ht="12.75" customHeight="1"/>
-    <row r="809" ht="12.75" customHeight="1"/>
-    <row r="810" ht="12.75" customHeight="1"/>
-    <row r="811" ht="12.75" customHeight="1"/>
-    <row r="812" ht="12.75" customHeight="1"/>
-    <row r="813" ht="12.75" customHeight="1"/>
-    <row r="814" ht="12.75" customHeight="1"/>
-    <row r="815" ht="12.75" customHeight="1"/>
-    <row r="816" ht="12.75" customHeight="1"/>
-    <row r="817" ht="12.75" customHeight="1"/>
-    <row r="818" ht="12.75" customHeight="1"/>
-    <row r="819" ht="12.75" customHeight="1"/>
-    <row r="820" ht="12.75" customHeight="1"/>
-    <row r="821" ht="12.75" customHeight="1"/>
-    <row r="822" ht="12.75" customHeight="1"/>
-    <row r="823" ht="12.75" customHeight="1"/>
-    <row r="824" ht="12.75" customHeight="1"/>
-    <row r="825" ht="12.75" customHeight="1"/>
-    <row r="826" ht="12.75" customHeight="1"/>
-    <row r="827" ht="12.75" customHeight="1"/>
-    <row r="828" ht="12.75" customHeight="1"/>
-    <row r="829" ht="12.75" customHeight="1"/>
-    <row r="830" ht="12.75" customHeight="1"/>
-    <row r="831" ht="12.75" customHeight="1"/>
-    <row r="832" ht="12.75" customHeight="1"/>
-    <row r="833" ht="12.75" customHeight="1"/>
-    <row r="834" ht="12.75" customHeight="1"/>
-    <row r="835" ht="12.75" customHeight="1"/>
-    <row r="836" ht="12.75" customHeight="1"/>
-    <row r="837" ht="12.75" customHeight="1"/>
-    <row r="838" ht="12.75" customHeight="1"/>
-    <row r="839" ht="12.75" customHeight="1"/>
-    <row r="840" ht="12.75" customHeight="1"/>
-    <row r="841" ht="12.75" customHeight="1"/>
-    <row r="842" ht="12.75" customHeight="1"/>
-    <row r="843" ht="12.75" customHeight="1"/>
-    <row r="844" ht="12.75" customHeight="1"/>
-    <row r="845" ht="12.75" customHeight="1"/>
-    <row r="846" ht="12.75" customHeight="1"/>
-    <row r="847" ht="12.75" customHeight="1"/>
-    <row r="848" ht="12.75" customHeight="1"/>
-    <row r="849" ht="12.75" customHeight="1"/>
-    <row r="850" ht="12.75" customHeight="1"/>
-    <row r="851" ht="12.75" customHeight="1"/>
-    <row r="852" ht="12.75" customHeight="1"/>
-    <row r="853" ht="12.75" customHeight="1"/>
-    <row r="854" ht="12.75" customHeight="1"/>
-    <row r="855" ht="12.75" customHeight="1"/>
-    <row r="856" ht="12.75" customHeight="1"/>
-    <row r="857" ht="12.75" customHeight="1"/>
-    <row r="858" ht="12.75" customHeight="1"/>
-    <row r="859" ht="12.75" customHeight="1"/>
-    <row r="860" ht="12.75" customHeight="1"/>
-    <row r="861" ht="12.75" customHeight="1"/>
-    <row r="862" ht="12.75" customHeight="1"/>
-    <row r="863" ht="12.75" customHeight="1"/>
-    <row r="864" ht="12.75" customHeight="1"/>
-    <row r="865" ht="12.75" customHeight="1"/>
-    <row r="866" ht="12.75" customHeight="1"/>
-    <row r="867" ht="12.75" customHeight="1"/>
-    <row r="868" ht="12.75" customHeight="1"/>
-    <row r="869" ht="12.75" customHeight="1"/>
-    <row r="870" ht="12.75" customHeight="1"/>
-    <row r="871" ht="12.75" customHeight="1"/>
-    <row r="872" ht="12.75" customHeight="1"/>
-    <row r="873" ht="12.75" customHeight="1"/>
-    <row r="874" ht="12.75" customHeight="1"/>
-    <row r="875" ht="12.75" customHeight="1"/>
-    <row r="876" ht="12.75" customHeight="1"/>
-    <row r="877" ht="12.75" customHeight="1"/>
-    <row r="878" ht="12.75" customHeight="1"/>
-    <row r="879" ht="12.75" customHeight="1"/>
-    <row r="880" ht="12.75" customHeight="1"/>
-    <row r="881" ht="12.75" customHeight="1"/>
-    <row r="882" ht="12.75" customHeight="1"/>
-    <row r="883" ht="12.75" customHeight="1"/>
-    <row r="884" ht="12.75" customHeight="1"/>
-    <row r="885" ht="12.75" customHeight="1"/>
-    <row r="886" ht="12.75" customHeight="1"/>
-    <row r="887" ht="12.75" customHeight="1"/>
-    <row r="888" ht="12.75" customHeight="1"/>
-    <row r="889" ht="12.75" customHeight="1"/>
-    <row r="890" ht="12.75" customHeight="1"/>
-    <row r="891" ht="12.75" customHeight="1"/>
-    <row r="892" ht="12.75" customHeight="1"/>
-    <row r="893" ht="12.75" customHeight="1"/>
-    <row r="894" ht="12.75" customHeight="1"/>
-    <row r="895" ht="12.75" customHeight="1"/>
-    <row r="896" ht="12.75" customHeight="1"/>
-    <row r="897" ht="12.75" customHeight="1"/>
-    <row r="898" ht="12.75" customHeight="1"/>
-    <row r="899" ht="12.75" customHeight="1"/>
-    <row r="900" ht="12.75" customHeight="1"/>
-    <row r="901" ht="12.75" customHeight="1"/>
-    <row r="902" ht="12.75" customHeight="1"/>
-    <row r="903" ht="12.75" customHeight="1"/>
-    <row r="904" ht="12.75" customHeight="1"/>
-    <row r="905" ht="12.75" customHeight="1"/>
-    <row r="906" ht="12.75" customHeight="1"/>
-    <row r="907" ht="12.75" customHeight="1"/>
-    <row r="908" ht="12.75" customHeight="1"/>
-    <row r="909" ht="12.75" customHeight="1"/>
-    <row r="910" ht="12.75" customHeight="1"/>
-    <row r="911" ht="12.75" customHeight="1"/>
-    <row r="912" ht="12.75" customHeight="1"/>
-    <row r="913" ht="12.75" customHeight="1"/>
-    <row r="914" ht="12.75" customHeight="1"/>
-    <row r="915" ht="12.75" customHeight="1"/>
-    <row r="916" ht="12.75" customHeight="1"/>
-    <row r="917" ht="12.75" customHeight="1"/>
-    <row r="918" ht="12.75" customHeight="1"/>
-    <row r="919" ht="12.75" customHeight="1"/>
-    <row r="920" ht="12.75" customHeight="1"/>
-    <row r="921" ht="12.75" customHeight="1"/>
-    <row r="922" ht="12.75" customHeight="1"/>
-    <row r="923" ht="12.75" customHeight="1"/>
-    <row r="924" ht="12.75" customHeight="1"/>
-    <row r="925" ht="12.75" customHeight="1"/>
-    <row r="926" ht="12.75" customHeight="1"/>
-    <row r="927" ht="12.75" customHeight="1"/>
-    <row r="928" ht="12.75" customHeight="1"/>
-    <row r="929" ht="12.75" customHeight="1"/>
-    <row r="930" ht="12.75" customHeight="1"/>
-    <row r="931" ht="12.75" customHeight="1"/>
-    <row r="932" ht="12.75" customHeight="1"/>
-    <row r="933" ht="12.75" customHeight="1"/>
-    <row r="934" ht="12.75" customHeight="1"/>
-    <row r="935" ht="12.75" customHeight="1"/>
-    <row r="936" ht="12.75" customHeight="1"/>
-    <row r="937" ht="12.75" customHeight="1"/>
-    <row r="938" ht="12.75" customHeight="1"/>
-    <row r="939" ht="12.75" customHeight="1"/>
-    <row r="940" ht="12.75" customHeight="1"/>
-    <row r="941" ht="12.75" customHeight="1"/>
-    <row r="942" ht="12.75" customHeight="1"/>
-    <row r="943" ht="12.75" customHeight="1"/>
-    <row r="944" ht="12.75" customHeight="1"/>
-    <row r="945" ht="12.75" customHeight="1"/>
-    <row r="946" ht="12.75" customHeight="1"/>
-    <row r="947" ht="12.75" customHeight="1"/>
-    <row r="948" ht="12.75" customHeight="1"/>
-    <row r="949" ht="12.75" customHeight="1"/>
-    <row r="950" ht="12.75" customHeight="1"/>
-    <row r="951" ht="12.75" customHeight="1"/>
-    <row r="952" ht="12.75" customHeight="1"/>
-    <row r="953" ht="12.75" customHeight="1"/>
-    <row r="954" ht="12.75" customHeight="1"/>
-    <row r="955" ht="12.75" customHeight="1"/>
-    <row r="956" ht="12.75" customHeight="1"/>
-    <row r="957" ht="12.75" customHeight="1"/>
-    <row r="958" ht="12.75" customHeight="1"/>
-    <row r="959" ht="12.75" customHeight="1"/>
-    <row r="960" ht="12.75" customHeight="1"/>
-    <row r="961" ht="12.75" customHeight="1"/>
-    <row r="962" ht="12.75" customHeight="1"/>
-    <row r="963" ht="12.75" customHeight="1"/>
-    <row r="964" ht="12.75" customHeight="1"/>
-    <row r="965" ht="12.75" customHeight="1"/>
-    <row r="966" ht="12.75" customHeight="1"/>
-    <row r="967" ht="12.75" customHeight="1"/>
-    <row r="968" ht="12.75" customHeight="1"/>
-    <row r="969" ht="12.75" customHeight="1"/>
-    <row r="970" ht="12.75" customHeight="1"/>
-    <row r="971" ht="12.75" customHeight="1"/>
-    <row r="972" ht="12.75" customHeight="1"/>
-    <row r="973" ht="12.75" customHeight="1"/>
-    <row r="974" ht="12.75" customHeight="1"/>
-    <row r="975" ht="12.75" customHeight="1"/>
-    <row r="976" ht="12.75" customHeight="1"/>
-    <row r="977" ht="12.75" customHeight="1"/>
-    <row r="978" ht="12.75" customHeight="1"/>
-    <row r="979" ht="12.75" customHeight="1"/>
-    <row r="980" ht="12.75" customHeight="1"/>
-    <row r="981" ht="12.75" customHeight="1"/>
-    <row r="982" ht="12.75" customHeight="1"/>
-    <row r="983" ht="12.75" customHeight="1"/>
-    <row r="984" ht="12.75" customHeight="1"/>
-    <row r="985" ht="12.75" customHeight="1"/>
-    <row r="986" ht="12.75" customHeight="1"/>
-    <row r="987" ht="12.75" customHeight="1"/>
-    <row r="988" ht="12.75" customHeight="1"/>
-    <row r="989" ht="12.75" customHeight="1"/>
-    <row r="990" ht="12.75" customHeight="1"/>
-    <row r="991" ht="12.75" customHeight="1"/>
-    <row r="992" ht="12.75" customHeight="1"/>
-    <row r="993" ht="12.75" customHeight="1"/>
-    <row r="994" ht="12.75" customHeight="1"/>
-    <row r="995" ht="12.75" customHeight="1"/>
-    <row r="996" ht="12.75" customHeight="1"/>
-    <row r="997" ht="12.75" customHeight="1"/>
-    <row r="998" ht="12.75" customHeight="1"/>
-    <row r="999" ht="12.75" customHeight="1"/>
-    <row r="1000" ht="12.75" customHeight="1"/>
-  </sheetData>
-  <mergeCells count="136">
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="E30:F30"/>
-    <mergeCell ref="A31:B31"/>
-    <mergeCell ref="C31:D31"/>
-    <mergeCell ref="E31:F31"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="E26:F26"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="E24:F24"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="E29:F29"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="E27:F27"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="E28:F28"/>
-    <mergeCell ref="A29:B29"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="O27:Q27"/>
-    <mergeCell ref="O28:Q28"/>
-    <mergeCell ref="O29:Q29"/>
-    <mergeCell ref="O30:Q30"/>
-    <mergeCell ref="O31:Q31"/>
-    <mergeCell ref="O19:Q19"/>
-    <mergeCell ref="O21:Q21"/>
-    <mergeCell ref="O22:Q22"/>
-    <mergeCell ref="O23:Q23"/>
-    <mergeCell ref="O24:Q24"/>
-    <mergeCell ref="O25:Q25"/>
-    <mergeCell ref="O26:Q26"/>
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="G5:T5"/>
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="G6:T6"/>
-    <mergeCell ref="A7:F7"/>
-    <mergeCell ref="G7:T7"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="G20:I20"/>
-    <mergeCell ref="J20:K20"/>
-    <mergeCell ref="L20:N20"/>
-    <mergeCell ref="O20:Q20"/>
-    <mergeCell ref="L15:N15"/>
-    <mergeCell ref="O15:Q15"/>
-    <mergeCell ref="L16:N16"/>
-    <mergeCell ref="O16:Q16"/>
-    <mergeCell ref="L17:N17"/>
-    <mergeCell ref="O17:Q17"/>
-    <mergeCell ref="O18:Q18"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="K2:N4"/>
-    <mergeCell ref="O2:P4"/>
-    <mergeCell ref="Q2:R4"/>
-    <mergeCell ref="S2:T4"/>
-    <mergeCell ref="A1:F4"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="O1:P1"/>
-    <mergeCell ref="Q1:R1"/>
-    <mergeCell ref="S1:T1"/>
-    <mergeCell ref="G2:J4"/>
-    <mergeCell ref="L26:N26"/>
-    <mergeCell ref="L27:N27"/>
-    <mergeCell ref="L28:N28"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="L18:N18"/>
-    <mergeCell ref="L19:N19"/>
-    <mergeCell ref="L21:N21"/>
-    <mergeCell ref="L22:N22"/>
-    <mergeCell ref="L23:N23"/>
-    <mergeCell ref="L24:N24"/>
-    <mergeCell ref="L25:N25"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="J30:K30"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="J29:K29"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="G23:I23"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="J18:K18"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="J19:K19"/>
-  </mergeCells>
-  <phoneticPr fontId="8"/>
-  <hyperlinks>
-    <hyperlink ref="L16" r:id="rId1" xr:uid="{BEB6392E-95EB-4E97-9AAC-19AD7E8B9DE3}"/>
-  </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
-  <pageSetup paperSize="9" orientation="landscape"/>
-</worksheet>
 </file>
--- a/Documents/登録機能詳細設計書.xlsx
+++ b/Documents/登録機能詳細設計書.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\S-47\Documents\project\taskUN\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A029222-2765-44E1-9468-0F599AFDB827}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34A78630-FBCC-44F8-BC69-3280335D790A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7155" yWindow="690" windowWidth="11415" windowHeight="8955" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="168">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="169">
   <si>
     <t>プロジェクト型演習　成果ドキュメント</t>
   </si>
@@ -1352,6 +1352,10 @@
     <rPh sb="44" eb="46">
       <t>ヒョウジ</t>
     </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>〇</t>
     <phoneticPr fontId="8"/>
   </si>
 </sst>
@@ -2487,7 +2491,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="272">
+  <cellXfs count="270">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -2762,6 +2766,93 @@
     <xf numFmtId="14" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2792,9 +2883,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2807,90 +2895,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2969,6 +2973,12 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3041,10 +3051,31 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3053,118 +3084,180 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="5" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="58" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="59" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="60" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="63" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="64" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="5" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="65" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="66" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="64" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="66" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="57" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="58" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="59" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="60" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="58" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="59" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="60" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="18" fillId="0" borderId="58" xfId="6" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    <xf numFmtId="14" fontId="18" fillId="0" borderId="60" xfId="6" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="18" fillId="0" borderId="58" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="60" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="67" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="68" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="69" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="70" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="67" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="68" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="69" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="70" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="68" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="69" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3173,87 +3266,6 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="70" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="68" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="69" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="70" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="67" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="63" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="68" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="69" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="70" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="58" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="59" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="60" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="64" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="65" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="66" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="64" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="66" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="57" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="58" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="59" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="60" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="58" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="59" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="60" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="18" fillId="0" borderId="58" xfId="6" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="18" fillId="0" borderId="60" xfId="6" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="18" fillId="0" borderId="58" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="60" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="26" fillId="4" borderId="58" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3283,20 +3295,6 @@
     </xf>
     <xf numFmtId="9" fontId="20" fillId="0" borderId="58" xfId="7" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="45" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="46" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="8">
@@ -5763,23 +5761,23 @@
       <c r="AL1" s="66"/>
       <c r="AM1" s="66"/>
       <c r="AN1" s="66"/>
-      <c r="AO1" s="259" t="s">
+      <c r="AO1" s="263" t="s">
         <v>156</v>
       </c>
-      <c r="AP1" s="259"/>
-      <c r="AQ1" s="259"/>
-      <c r="AR1" s="259"/>
-      <c r="AS1" s="259"/>
-      <c r="AT1" s="260">
+      <c r="AP1" s="263"/>
+      <c r="AQ1" s="263"/>
+      <c r="AR1" s="263"/>
+      <c r="AS1" s="263"/>
+      <c r="AT1" s="264">
         <v>45821</v>
       </c>
-      <c r="AU1" s="261"/>
-      <c r="AV1" s="261"/>
-      <c r="AW1" s="261"/>
-      <c r="AX1" s="261"/>
-      <c r="AY1" s="261"/>
-      <c r="AZ1" s="261"/>
-      <c r="BA1" s="261"/>
+      <c r="AU1" s="265"/>
+      <c r="AV1" s="265"/>
+      <c r="AW1" s="265"/>
+      <c r="AX1" s="265"/>
+      <c r="AY1" s="265"/>
+      <c r="AZ1" s="265"/>
+      <c r="BA1" s="265"/>
     </row>
     <row r="2" spans="1:53" ht="9.9499999999999993" customHeight="1"/>
     <row r="3" spans="1:53" ht="9.9499999999999993" customHeight="1"/>
@@ -5825,54 +5823,54 @@
       <c r="AK4" s="73"/>
     </row>
     <row r="5" spans="1:53" ht="24.95" customHeight="1">
-      <c r="A5" s="256" t="s">
+      <c r="A5" s="260" t="s">
         <v>158</v>
       </c>
-      <c r="B5" s="257"/>
-      <c r="C5" s="257"/>
-      <c r="D5" s="257"/>
-      <c r="E5" s="257"/>
-      <c r="F5" s="258"/>
-      <c r="G5" s="262" t="s">
+      <c r="B5" s="261"/>
+      <c r="C5" s="261"/>
+      <c r="D5" s="261"/>
+      <c r="E5" s="261"/>
+      <c r="F5" s="262"/>
+      <c r="G5" s="266" t="s">
         <v>164</v>
       </c>
-      <c r="H5" s="263"/>
-      <c r="I5" s="263"/>
-      <c r="J5" s="263"/>
-      <c r="K5" s="263"/>
-      <c r="L5" s="263"/>
-      <c r="M5" s="263"/>
-      <c r="N5" s="263"/>
-      <c r="O5" s="263"/>
-      <c r="P5" s="263"/>
-      <c r="Q5" s="263"/>
-      <c r="R5" s="263"/>
-      <c r="S5" s="264"/>
+      <c r="H5" s="267"/>
+      <c r="I5" s="267"/>
+      <c r="J5" s="267"/>
+      <c r="K5" s="267"/>
+      <c r="L5" s="267"/>
+      <c r="M5" s="267"/>
+      <c r="N5" s="267"/>
+      <c r="O5" s="267"/>
+      <c r="P5" s="267"/>
+      <c r="Q5" s="267"/>
+      <c r="R5" s="267"/>
+      <c r="S5" s="268"/>
     </row>
     <row r="6" spans="1:53" ht="24.95" customHeight="1">
-      <c r="A6" s="256" t="s">
+      <c r="A6" s="260" t="s">
         <v>159</v>
       </c>
-      <c r="B6" s="257"/>
-      <c r="C6" s="257"/>
-      <c r="D6" s="257"/>
-      <c r="E6" s="257"/>
-      <c r="F6" s="258"/>
-      <c r="G6" s="265">
+      <c r="B6" s="261"/>
+      <c r="C6" s="261"/>
+      <c r="D6" s="261"/>
+      <c r="E6" s="261"/>
+      <c r="F6" s="262"/>
+      <c r="G6" s="269">
         <v>1</v>
       </c>
-      <c r="H6" s="263"/>
-      <c r="I6" s="263"/>
-      <c r="J6" s="263"/>
-      <c r="K6" s="263"/>
-      <c r="L6" s="263"/>
-      <c r="M6" s="263"/>
-      <c r="N6" s="263"/>
-      <c r="O6" s="263"/>
-      <c r="P6" s="263"/>
-      <c r="Q6" s="263"/>
-      <c r="R6" s="263"/>
-      <c r="S6" s="264"/>
+      <c r="H6" s="267"/>
+      <c r="I6" s="267"/>
+      <c r="J6" s="267"/>
+      <c r="K6" s="267"/>
+      <c r="L6" s="267"/>
+      <c r="M6" s="267"/>
+      <c r="N6" s="267"/>
+      <c r="O6" s="267"/>
+      <c r="P6" s="267"/>
+      <c r="Q6" s="267"/>
+      <c r="R6" s="267"/>
+      <c r="S6" s="268"/>
     </row>
     <row r="7" spans="1:53" ht="9.9499999999999993" customHeight="1"/>
     <row r="8" spans="1:53" ht="18" customHeight="1">
@@ -5881,61 +5879,61 @@
       </c>
     </row>
     <row r="9" spans="1:53" ht="18" customHeight="1">
-      <c r="A9" s="256" t="s">
+      <c r="A9" s="260" t="s">
         <v>161</v>
       </c>
-      <c r="B9" s="257"/>
-      <c r="C9" s="257"/>
-      <c r="D9" s="257"/>
-      <c r="E9" s="257"/>
-      <c r="F9" s="257"/>
-      <c r="G9" s="257"/>
-      <c r="H9" s="257"/>
-      <c r="I9" s="257"/>
-      <c r="J9" s="257"/>
-      <c r="K9" s="257"/>
-      <c r="L9" s="257"/>
-      <c r="M9" s="257"/>
-      <c r="N9" s="257"/>
-      <c r="O9" s="257"/>
-      <c r="P9" s="257"/>
-      <c r="Q9" s="257"/>
-      <c r="R9" s="257"/>
-      <c r="S9" s="257"/>
-      <c r="T9" s="257"/>
-      <c r="U9" s="257"/>
-      <c r="V9" s="257"/>
-      <c r="W9" s="257"/>
-      <c r="X9" s="257"/>
-      <c r="Y9" s="257"/>
-      <c r="Z9" s="257"/>
-      <c r="AA9" s="257"/>
-      <c r="AB9" s="257"/>
-      <c r="AC9" s="257"/>
-      <c r="AD9" s="257"/>
-      <c r="AE9" s="257"/>
-      <c r="AF9" s="257"/>
-      <c r="AG9" s="257"/>
-      <c r="AH9" s="257"/>
-      <c r="AI9" s="257"/>
-      <c r="AJ9" s="257"/>
-      <c r="AK9" s="257"/>
-      <c r="AL9" s="257"/>
-      <c r="AM9" s="257"/>
-      <c r="AN9" s="257"/>
-      <c r="AO9" s="257"/>
-      <c r="AP9" s="257"/>
-      <c r="AQ9" s="257"/>
-      <c r="AR9" s="257"/>
-      <c r="AS9" s="257"/>
-      <c r="AT9" s="257"/>
-      <c r="AU9" s="257"/>
-      <c r="AV9" s="257"/>
-      <c r="AW9" s="257"/>
-      <c r="AX9" s="257"/>
-      <c r="AY9" s="257"/>
-      <c r="AZ9" s="257"/>
-      <c r="BA9" s="258"/>
+      <c r="B9" s="261"/>
+      <c r="C9" s="261"/>
+      <c r="D9" s="261"/>
+      <c r="E9" s="261"/>
+      <c r="F9" s="261"/>
+      <c r="G9" s="261"/>
+      <c r="H9" s="261"/>
+      <c r="I9" s="261"/>
+      <c r="J9" s="261"/>
+      <c r="K9" s="261"/>
+      <c r="L9" s="261"/>
+      <c r="M9" s="261"/>
+      <c r="N9" s="261"/>
+      <c r="O9" s="261"/>
+      <c r="P9" s="261"/>
+      <c r="Q9" s="261"/>
+      <c r="R9" s="261"/>
+      <c r="S9" s="261"/>
+      <c r="T9" s="261"/>
+      <c r="U9" s="261"/>
+      <c r="V9" s="261"/>
+      <c r="W9" s="261"/>
+      <c r="X9" s="261"/>
+      <c r="Y9" s="261"/>
+      <c r="Z9" s="261"/>
+      <c r="AA9" s="261"/>
+      <c r="AB9" s="261"/>
+      <c r="AC9" s="261"/>
+      <c r="AD9" s="261"/>
+      <c r="AE9" s="261"/>
+      <c r="AF9" s="261"/>
+      <c r="AG9" s="261"/>
+      <c r="AH9" s="261"/>
+      <c r="AI9" s="261"/>
+      <c r="AJ9" s="261"/>
+      <c r="AK9" s="261"/>
+      <c r="AL9" s="261"/>
+      <c r="AM9" s="261"/>
+      <c r="AN9" s="261"/>
+      <c r="AO9" s="261"/>
+      <c r="AP9" s="261"/>
+      <c r="AQ9" s="261"/>
+      <c r="AR9" s="261"/>
+      <c r="AS9" s="261"/>
+      <c r="AT9" s="261"/>
+      <c r="AU9" s="261"/>
+      <c r="AV9" s="261"/>
+      <c r="AW9" s="261"/>
+      <c r="AX9" s="261"/>
+      <c r="AY9" s="261"/>
+      <c r="AZ9" s="261"/>
+      <c r="BA9" s="262"/>
     </row>
     <row r="10" spans="1:53" ht="21.95" customHeight="1">
       <c r="A10" s="75"/>
@@ -9658,61 +9656,61 @@
       <c r="BA102" s="77"/>
     </row>
     <row r="103" spans="1:53" ht="18" customHeight="1">
-      <c r="A103" s="256" t="s">
+      <c r="A103" s="260" t="s">
         <v>162</v>
       </c>
-      <c r="B103" s="257"/>
-      <c r="C103" s="257"/>
-      <c r="D103" s="257"/>
-      <c r="E103" s="257"/>
-      <c r="F103" s="257"/>
-      <c r="G103" s="257"/>
-      <c r="H103" s="257"/>
-      <c r="I103" s="257"/>
-      <c r="J103" s="257"/>
-      <c r="K103" s="257"/>
-      <c r="L103" s="257"/>
-      <c r="M103" s="257"/>
-      <c r="N103" s="257"/>
-      <c r="O103" s="257"/>
-      <c r="P103" s="257"/>
-      <c r="Q103" s="257"/>
-      <c r="R103" s="257"/>
-      <c r="S103" s="257"/>
-      <c r="T103" s="257"/>
-      <c r="U103" s="257"/>
-      <c r="V103" s="257"/>
-      <c r="W103" s="257"/>
-      <c r="X103" s="257"/>
-      <c r="Y103" s="257"/>
-      <c r="Z103" s="257"/>
-      <c r="AA103" s="257"/>
-      <c r="AB103" s="257"/>
-      <c r="AC103" s="257"/>
-      <c r="AD103" s="257"/>
-      <c r="AE103" s="257"/>
-      <c r="AF103" s="257"/>
-      <c r="AG103" s="257"/>
-      <c r="AH103" s="257"/>
-      <c r="AI103" s="257"/>
-      <c r="AJ103" s="257"/>
-      <c r="AK103" s="257"/>
-      <c r="AL103" s="257"/>
-      <c r="AM103" s="257"/>
-      <c r="AN103" s="257"/>
-      <c r="AO103" s="257"/>
-      <c r="AP103" s="257"/>
-      <c r="AQ103" s="257"/>
-      <c r="AR103" s="257"/>
-      <c r="AS103" s="257"/>
-      <c r="AT103" s="257"/>
-      <c r="AU103" s="257"/>
-      <c r="AV103" s="257"/>
-      <c r="AW103" s="257"/>
-      <c r="AX103" s="257"/>
-      <c r="AY103" s="257"/>
-      <c r="AZ103" s="257"/>
-      <c r="BA103" s="258"/>
+      <c r="B103" s="261"/>
+      <c r="C103" s="261"/>
+      <c r="D103" s="261"/>
+      <c r="E103" s="261"/>
+      <c r="F103" s="261"/>
+      <c r="G103" s="261"/>
+      <c r="H103" s="261"/>
+      <c r="I103" s="261"/>
+      <c r="J103" s="261"/>
+      <c r="K103" s="261"/>
+      <c r="L103" s="261"/>
+      <c r="M103" s="261"/>
+      <c r="N103" s="261"/>
+      <c r="O103" s="261"/>
+      <c r="P103" s="261"/>
+      <c r="Q103" s="261"/>
+      <c r="R103" s="261"/>
+      <c r="S103" s="261"/>
+      <c r="T103" s="261"/>
+      <c r="U103" s="261"/>
+      <c r="V103" s="261"/>
+      <c r="W103" s="261"/>
+      <c r="X103" s="261"/>
+      <c r="Y103" s="261"/>
+      <c r="Z103" s="261"/>
+      <c r="AA103" s="261"/>
+      <c r="AB103" s="261"/>
+      <c r="AC103" s="261"/>
+      <c r="AD103" s="261"/>
+      <c r="AE103" s="261"/>
+      <c r="AF103" s="261"/>
+      <c r="AG103" s="261"/>
+      <c r="AH103" s="261"/>
+      <c r="AI103" s="261"/>
+      <c r="AJ103" s="261"/>
+      <c r="AK103" s="261"/>
+      <c r="AL103" s="261"/>
+      <c r="AM103" s="261"/>
+      <c r="AN103" s="261"/>
+      <c r="AO103" s="261"/>
+      <c r="AP103" s="261"/>
+      <c r="AQ103" s="261"/>
+      <c r="AR103" s="261"/>
+      <c r="AS103" s="261"/>
+      <c r="AT103" s="261"/>
+      <c r="AU103" s="261"/>
+      <c r="AV103" s="261"/>
+      <c r="AW103" s="261"/>
+      <c r="AX103" s="261"/>
+      <c r="AY103" s="261"/>
+      <c r="AZ103" s="261"/>
+      <c r="BA103" s="262"/>
     </row>
     <row r="104" spans="1:53" ht="21.95" customHeight="1">
       <c r="A104" s="78"/>
@@ -10035,61 +10033,61 @@
       <c r="BA111" s="77"/>
     </row>
     <row r="112" spans="1:53" ht="18" customHeight="1">
-      <c r="A112" s="256" t="s">
+      <c r="A112" s="260" t="s">
         <v>163</v>
       </c>
-      <c r="B112" s="257"/>
-      <c r="C112" s="257"/>
-      <c r="D112" s="257"/>
-      <c r="E112" s="257"/>
-      <c r="F112" s="257"/>
-      <c r="G112" s="257"/>
-      <c r="H112" s="257"/>
-      <c r="I112" s="257"/>
-      <c r="J112" s="257"/>
-      <c r="K112" s="257"/>
-      <c r="L112" s="257"/>
-      <c r="M112" s="257"/>
-      <c r="N112" s="257"/>
-      <c r="O112" s="257"/>
-      <c r="P112" s="257"/>
-      <c r="Q112" s="257"/>
-      <c r="R112" s="257"/>
-      <c r="S112" s="257"/>
-      <c r="T112" s="257"/>
-      <c r="U112" s="257"/>
-      <c r="V112" s="257"/>
-      <c r="W112" s="257"/>
-      <c r="X112" s="257"/>
-      <c r="Y112" s="257"/>
-      <c r="Z112" s="257"/>
-      <c r="AA112" s="257"/>
-      <c r="AB112" s="257"/>
-      <c r="AC112" s="257"/>
-      <c r="AD112" s="257"/>
-      <c r="AE112" s="257"/>
-      <c r="AF112" s="257"/>
-      <c r="AG112" s="257"/>
-      <c r="AH112" s="257"/>
-      <c r="AI112" s="257"/>
-      <c r="AJ112" s="257"/>
-      <c r="AK112" s="257"/>
-      <c r="AL112" s="257"/>
-      <c r="AM112" s="257"/>
-      <c r="AN112" s="257"/>
-      <c r="AO112" s="257"/>
-      <c r="AP112" s="257"/>
-      <c r="AQ112" s="257"/>
-      <c r="AR112" s="257"/>
-      <c r="AS112" s="257"/>
-      <c r="AT112" s="257"/>
-      <c r="AU112" s="257"/>
-      <c r="AV112" s="257"/>
-      <c r="AW112" s="257"/>
-      <c r="AX112" s="257"/>
-      <c r="AY112" s="257"/>
-      <c r="AZ112" s="257"/>
-      <c r="BA112" s="257"/>
+      <c r="B112" s="261"/>
+      <c r="C112" s="261"/>
+      <c r="D112" s="261"/>
+      <c r="E112" s="261"/>
+      <c r="F112" s="261"/>
+      <c r="G112" s="261"/>
+      <c r="H112" s="261"/>
+      <c r="I112" s="261"/>
+      <c r="J112" s="261"/>
+      <c r="K112" s="261"/>
+      <c r="L112" s="261"/>
+      <c r="M112" s="261"/>
+      <c r="N112" s="261"/>
+      <c r="O112" s="261"/>
+      <c r="P112" s="261"/>
+      <c r="Q112" s="261"/>
+      <c r="R112" s="261"/>
+      <c r="S112" s="261"/>
+      <c r="T112" s="261"/>
+      <c r="U112" s="261"/>
+      <c r="V112" s="261"/>
+      <c r="W112" s="261"/>
+      <c r="X112" s="261"/>
+      <c r="Y112" s="261"/>
+      <c r="Z112" s="261"/>
+      <c r="AA112" s="261"/>
+      <c r="AB112" s="261"/>
+      <c r="AC112" s="261"/>
+      <c r="AD112" s="261"/>
+      <c r="AE112" s="261"/>
+      <c r="AF112" s="261"/>
+      <c r="AG112" s="261"/>
+      <c r="AH112" s="261"/>
+      <c r="AI112" s="261"/>
+      <c r="AJ112" s="261"/>
+      <c r="AK112" s="261"/>
+      <c r="AL112" s="261"/>
+      <c r="AM112" s="261"/>
+      <c r="AN112" s="261"/>
+      <c r="AO112" s="261"/>
+      <c r="AP112" s="261"/>
+      <c r="AQ112" s="261"/>
+      <c r="AR112" s="261"/>
+      <c r="AS112" s="261"/>
+      <c r="AT112" s="261"/>
+      <c r="AU112" s="261"/>
+      <c r="AV112" s="261"/>
+      <c r="AW112" s="261"/>
+      <c r="AX112" s="261"/>
+      <c r="AY112" s="261"/>
+      <c r="AZ112" s="261"/>
+      <c r="BA112" s="261"/>
     </row>
     <row r="113" spans="1:53" ht="21.95" customHeight="1">
       <c r="A113" s="78"/>
@@ -10263,19 +10261,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="92" t="s">
+      <c r="A1" s="121" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="93"/>
-      <c r="C1" s="94"/>
-      <c r="D1" s="101" t="s">
+      <c r="B1" s="122"/>
+      <c r="C1" s="123"/>
+      <c r="D1" s="130" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="102"/>
-      <c r="F1" s="101" t="s">
+      <c r="E1" s="115"/>
+      <c r="F1" s="130" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="102"/>
+      <c r="G1" s="115"/>
       <c r="H1" s="34" t="s">
         <v>6</v>
       </c>
@@ -10287,192 +10285,192 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="95"/>
-      <c r="B2" s="96"/>
-      <c r="C2" s="97"/>
-      <c r="D2" s="103" t="s">
+      <c r="A2" s="124"/>
+      <c r="B2" s="125"/>
+      <c r="C2" s="126"/>
+      <c r="D2" s="131" t="s">
         <v>61</v>
       </c>
-      <c r="E2" s="104"/>
-      <c r="F2" s="103">
+      <c r="E2" s="132"/>
+      <c r="F2" s="131">
         <v>56</v>
       </c>
-      <c r="G2" s="104"/>
-      <c r="H2" s="107">
+      <c r="G2" s="132"/>
+      <c r="H2" s="100">
         <v>45806</v>
       </c>
-      <c r="I2" s="121" t="s">
+      <c r="I2" s="109" t="s">
         <v>60</v>
       </c>
-      <c r="J2" s="122"/>
+      <c r="J2" s="110"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="95"/>
-      <c r="B3" s="96"/>
-      <c r="C3" s="97"/>
-      <c r="D3" s="105"/>
-      <c r="E3" s="97"/>
-      <c r="F3" s="105"/>
-      <c r="G3" s="97"/>
-      <c r="H3" s="108"/>
-      <c r="I3" s="108"/>
-      <c r="J3" s="123"/>
+      <c r="A3" s="124"/>
+      <c r="B3" s="125"/>
+      <c r="C3" s="126"/>
+      <c r="D3" s="133"/>
+      <c r="E3" s="126"/>
+      <c r="F3" s="133"/>
+      <c r="G3" s="126"/>
+      <c r="H3" s="101"/>
+      <c r="I3" s="101"/>
+      <c r="J3" s="111"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="98"/>
-      <c r="B4" s="99"/>
-      <c r="C4" s="100"/>
-      <c r="D4" s="106"/>
-      <c r="E4" s="100"/>
-      <c r="F4" s="106"/>
-      <c r="G4" s="100"/>
-      <c r="H4" s="109"/>
-      <c r="I4" s="109"/>
-      <c r="J4" s="124"/>
+      <c r="A4" s="127"/>
+      <c r="B4" s="128"/>
+      <c r="C4" s="129"/>
+      <c r="D4" s="134"/>
+      <c r="E4" s="129"/>
+      <c r="F4" s="134"/>
+      <c r="G4" s="129"/>
+      <c r="H4" s="102"/>
+      <c r="I4" s="102"/>
+      <c r="J4" s="112"/>
     </row>
     <row r="5" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A5" s="125" t="s">
+      <c r="A5" s="113" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="126"/>
-      <c r="C5" s="102"/>
-      <c r="D5" s="127" t="s">
+      <c r="B5" s="114"/>
+      <c r="C5" s="115"/>
+      <c r="D5" s="116" t="s">
         <v>59</v>
       </c>
-      <c r="E5" s="126"/>
-      <c r="F5" s="126"/>
-      <c r="G5" s="126"/>
-      <c r="H5" s="126"/>
-      <c r="I5" s="126"/>
-      <c r="J5" s="128"/>
+      <c r="E5" s="114"/>
+      <c r="F5" s="114"/>
+      <c r="G5" s="114"/>
+      <c r="H5" s="114"/>
+      <c r="I5" s="114"/>
+      <c r="J5" s="117"/>
     </row>
     <row r="6" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A6" s="110" t="s">
+      <c r="A6" s="103" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="111"/>
-      <c r="C6" s="112"/>
-      <c r="D6" s="120" t="s">
+      <c r="B6" s="98"/>
+      <c r="C6" s="93"/>
+      <c r="D6" s="97" t="s">
         <v>58</v>
       </c>
-      <c r="E6" s="111"/>
-      <c r="F6" s="111"/>
-      <c r="G6" s="111"/>
-      <c r="H6" s="111"/>
-      <c r="I6" s="111"/>
-      <c r="J6" s="114"/>
+      <c r="E6" s="98"/>
+      <c r="F6" s="98"/>
+      <c r="G6" s="98"/>
+      <c r="H6" s="98"/>
+      <c r="I6" s="98"/>
+      <c r="J6" s="99"/>
     </row>
     <row r="7" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A7" s="110" t="s">
+      <c r="A7" s="103" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="111"/>
-      <c r="C7" s="112"/>
-      <c r="D7" s="120" t="s">
+      <c r="B7" s="98"/>
+      <c r="C7" s="93"/>
+      <c r="D7" s="97" t="s">
         <v>57</v>
       </c>
-      <c r="E7" s="111"/>
-      <c r="F7" s="111"/>
-      <c r="G7" s="111"/>
-      <c r="H7" s="111"/>
-      <c r="I7" s="111"/>
-      <c r="J7" s="114"/>
+      <c r="E7" s="98"/>
+      <c r="F7" s="98"/>
+      <c r="G7" s="98"/>
+      <c r="H7" s="98"/>
+      <c r="I7" s="98"/>
+      <c r="J7" s="99"/>
     </row>
     <row r="8" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A8" s="110" t="s">
+      <c r="A8" s="103" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="111"/>
-      <c r="C8" s="112"/>
-      <c r="D8" s="113" t="s">
+      <c r="B8" s="98"/>
+      <c r="C8" s="93"/>
+      <c r="D8" s="94" t="s">
         <v>107</v>
       </c>
-      <c r="E8" s="111"/>
-      <c r="F8" s="111"/>
-      <c r="G8" s="111"/>
-      <c r="H8" s="111"/>
-      <c r="I8" s="111"/>
-      <c r="J8" s="114"/>
+      <c r="E8" s="98"/>
+      <c r="F8" s="98"/>
+      <c r="G8" s="98"/>
+      <c r="H8" s="98"/>
+      <c r="I8" s="98"/>
+      <c r="J8" s="99"/>
     </row>
     <row r="9" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A9" s="129" t="s">
+      <c r="A9" s="118" t="s">
         <v>13</v>
       </c>
-      <c r="B9" s="132" t="s">
+      <c r="B9" s="92" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="112"/>
-      <c r="D9" s="113" t="s">
+      <c r="C9" s="93"/>
+      <c r="D9" s="94" t="s">
         <v>105</v>
       </c>
-      <c r="E9" s="133"/>
-      <c r="F9" s="133"/>
-      <c r="G9" s="133"/>
-      <c r="H9" s="133"/>
-      <c r="I9" s="133"/>
-      <c r="J9" s="134"/>
+      <c r="E9" s="95"/>
+      <c r="F9" s="95"/>
+      <c r="G9" s="95"/>
+      <c r="H9" s="95"/>
+      <c r="I9" s="95"/>
+      <c r="J9" s="96"/>
     </row>
     <row r="10" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A10" s="130"/>
-      <c r="B10" s="132" t="s">
+      <c r="A10" s="119"/>
+      <c r="B10" s="92" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="112"/>
-      <c r="D10" s="120" t="s">
+      <c r="C10" s="93"/>
+      <c r="D10" s="97" t="s">
         <v>93</v>
       </c>
-      <c r="E10" s="111"/>
-      <c r="F10" s="111"/>
-      <c r="G10" s="111"/>
-      <c r="H10" s="111"/>
-      <c r="I10" s="111"/>
-      <c r="J10" s="114"/>
+      <c r="E10" s="98"/>
+      <c r="F10" s="98"/>
+      <c r="G10" s="98"/>
+      <c r="H10" s="98"/>
+      <c r="I10" s="98"/>
+      <c r="J10" s="99"/>
     </row>
     <row r="11" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A11" s="131"/>
-      <c r="B11" s="132" t="s">
+      <c r="A11" s="120"/>
+      <c r="B11" s="92" t="s">
         <v>16</v>
       </c>
-      <c r="C11" s="112"/>
-      <c r="D11" s="113" t="s">
+      <c r="C11" s="93"/>
+      <c r="D11" s="94" t="s">
         <v>108</v>
       </c>
-      <c r="E11" s="111"/>
-      <c r="F11" s="111"/>
-      <c r="G11" s="111"/>
-      <c r="H11" s="111"/>
-      <c r="I11" s="111"/>
-      <c r="J11" s="114"/>
+      <c r="E11" s="98"/>
+      <c r="F11" s="98"/>
+      <c r="G11" s="98"/>
+      <c r="H11" s="98"/>
+      <c r="I11" s="98"/>
+      <c r="J11" s="99"/>
     </row>
     <row r="12" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A12" s="110" t="s">
+      <c r="A12" s="103" t="s">
         <v>17</v>
       </c>
-      <c r="B12" s="111"/>
-      <c r="C12" s="112"/>
-      <c r="D12" s="113" t="s">
+      <c r="B12" s="98"/>
+      <c r="C12" s="93"/>
+      <c r="D12" s="94" t="s">
         <v>106</v>
       </c>
-      <c r="E12" s="111"/>
-      <c r="F12" s="111"/>
-      <c r="G12" s="111"/>
-      <c r="H12" s="111"/>
-      <c r="I12" s="111"/>
-      <c r="J12" s="114"/>
+      <c r="E12" s="98"/>
+      <c r="F12" s="98"/>
+      <c r="G12" s="98"/>
+      <c r="H12" s="98"/>
+      <c r="I12" s="98"/>
+      <c r="J12" s="99"/>
     </row>
     <row r="13" spans="1:10" ht="26.25" customHeight="1" thickBot="1">
-      <c r="A13" s="115" t="s">
+      <c r="A13" s="104" t="s">
         <v>18</v>
       </c>
-      <c r="B13" s="116"/>
-      <c r="C13" s="117"/>
-      <c r="D13" s="118"/>
-      <c r="E13" s="116"/>
-      <c r="F13" s="116"/>
-      <c r="G13" s="116"/>
-      <c r="H13" s="116"/>
-      <c r="I13" s="116"/>
-      <c r="J13" s="119"/>
+      <c r="B13" s="105"/>
+      <c r="C13" s="106"/>
+      <c r="D13" s="107"/>
+      <c r="E13" s="105"/>
+      <c r="F13" s="105"/>
+      <c r="G13" s="105"/>
+      <c r="H13" s="105"/>
+      <c r="I13" s="105"/>
+      <c r="J13" s="108"/>
     </row>
     <row r="14" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="15" spans="1:10" ht="12.75" customHeight="1"/>
@@ -11463,12 +11461,11 @@
     <row r="1000" s="32" customFormat="1" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="D9:J9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="D10:J10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="D11:J11"/>
+    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="F2:G4"/>
     <mergeCell ref="H2:H4"/>
     <mergeCell ref="A12:C12"/>
     <mergeCell ref="D12:J12"/>
@@ -11485,11 +11482,12 @@
     <mergeCell ref="A6:C6"/>
     <mergeCell ref="D6:J6"/>
     <mergeCell ref="A9:A11"/>
-    <mergeCell ref="A1:C4"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="D2:E4"/>
-    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="D9:J9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="D10:J10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="D11:J11"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.70833333333333304" right="0.70833333333333304" top="0.74791666666666701" bottom="0.74791666666666701" header="0" footer="0"/>
@@ -14347,19 +14345,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="167" t="s">
+      <c r="A1" s="169" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="168"/>
-      <c r="C1" s="169"/>
-      <c r="D1" s="171" t="s">
+      <c r="B1" s="170"/>
+      <c r="C1" s="171"/>
+      <c r="D1" s="173" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="172"/>
-      <c r="F1" s="171" t="s">
+      <c r="E1" s="174"/>
+      <c r="F1" s="173" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="172"/>
+      <c r="G1" s="174"/>
       <c r="H1" s="43" t="s">
         <v>6</v>
       </c>
@@ -14371,67 +14369,67 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="164"/>
-      <c r="B2" s="165"/>
-      <c r="C2" s="170"/>
-      <c r="D2" s="173" t="s">
+      <c r="A2" s="166"/>
+      <c r="B2" s="167"/>
+      <c r="C2" s="172"/>
+      <c r="D2" s="175" t="s">
         <v>84</v>
       </c>
-      <c r="E2" s="174"/>
-      <c r="F2" s="173">
+      <c r="E2" s="176"/>
+      <c r="F2" s="175">
         <v>56</v>
       </c>
-      <c r="G2" s="174"/>
-      <c r="H2" s="176">
+      <c r="G2" s="176"/>
+      <c r="H2" s="178">
         <v>45806</v>
       </c>
-      <c r="I2" s="178" t="s">
+      <c r="I2" s="180" t="s">
         <v>83</v>
       </c>
-      <c r="J2" s="179"/>
+      <c r="J2" s="181"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="164"/>
-      <c r="B3" s="165"/>
-      <c r="C3" s="170"/>
-      <c r="D3" s="175"/>
-      <c r="E3" s="170"/>
-      <c r="F3" s="175"/>
-      <c r="G3" s="170"/>
-      <c r="H3" s="177"/>
-      <c r="I3" s="177"/>
-      <c r="J3" s="180"/>
+      <c r="A3" s="166"/>
+      <c r="B3" s="167"/>
+      <c r="C3" s="172"/>
+      <c r="D3" s="177"/>
+      <c r="E3" s="172"/>
+      <c r="F3" s="177"/>
+      <c r="G3" s="172"/>
+      <c r="H3" s="179"/>
+      <c r="I3" s="179"/>
+      <c r="J3" s="182"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="164"/>
-      <c r="B4" s="165"/>
-      <c r="C4" s="170"/>
-      <c r="D4" s="175"/>
-      <c r="E4" s="170"/>
-      <c r="F4" s="175"/>
-      <c r="G4" s="170"/>
-      <c r="H4" s="177"/>
-      <c r="I4" s="177"/>
-      <c r="J4" s="180"/>
+      <c r="A4" s="166"/>
+      <c r="B4" s="167"/>
+      <c r="C4" s="172"/>
+      <c r="D4" s="177"/>
+      <c r="E4" s="172"/>
+      <c r="F4" s="177"/>
+      <c r="G4" s="172"/>
+      <c r="H4" s="179"/>
+      <c r="I4" s="179"/>
+      <c r="J4" s="182"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="181" t="s">
+      <c r="A5" s="183" t="s">
         <v>22</v>
       </c>
-      <c r="B5" s="182"/>
-      <c r="C5" s="172"/>
-      <c r="D5" s="183" t="s">
+      <c r="B5" s="184"/>
+      <c r="C5" s="174"/>
+      <c r="D5" s="185" t="s">
         <v>92</v>
       </c>
-      <c r="E5" s="182"/>
-      <c r="F5" s="182"/>
-      <c r="G5" s="182"/>
-      <c r="H5" s="182"/>
-      <c r="I5" s="182"/>
-      <c r="J5" s="184"/>
+      <c r="E5" s="184"/>
+      <c r="F5" s="184"/>
+      <c r="G5" s="184"/>
+      <c r="H5" s="184"/>
+      <c r="I5" s="184"/>
+      <c r="J5" s="186"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="185" t="s">
+      <c r="A6" s="162" t="s">
         <v>23</v>
       </c>
       <c r="B6" s="157"/>
@@ -14445,91 +14443,91 @@
       <c r="J6" s="160"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="161"/>
-      <c r="B7" s="162"/>
-      <c r="C7" s="162"/>
-      <c r="D7" s="162"/>
-      <c r="E7" s="162"/>
-      <c r="F7" s="162"/>
-      <c r="G7" s="162"/>
-      <c r="H7" s="162"/>
-      <c r="I7" s="162"/>
-      <c r="J7" s="163"/>
+      <c r="A7" s="163"/>
+      <c r="B7" s="164"/>
+      <c r="C7" s="164"/>
+      <c r="D7" s="164"/>
+      <c r="E7" s="164"/>
+      <c r="F7" s="164"/>
+      <c r="G7" s="164"/>
+      <c r="H7" s="164"/>
+      <c r="I7" s="164"/>
+      <c r="J7" s="165"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="164"/>
-      <c r="B8" s="165"/>
-      <c r="C8" s="165"/>
-      <c r="D8" s="165"/>
-      <c r="E8" s="165"/>
-      <c r="F8" s="165"/>
-      <c r="G8" s="165"/>
-      <c r="H8" s="165"/>
-      <c r="I8" s="165"/>
-      <c r="J8" s="166"/>
+      <c r="A8" s="166"/>
+      <c r="B8" s="167"/>
+      <c r="C8" s="167"/>
+      <c r="D8" s="167"/>
+      <c r="E8" s="167"/>
+      <c r="F8" s="167"/>
+      <c r="G8" s="167"/>
+      <c r="H8" s="167"/>
+      <c r="I8" s="167"/>
+      <c r="J8" s="168"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="164"/>
-      <c r="B9" s="165"/>
-      <c r="C9" s="165"/>
-      <c r="D9" s="165"/>
-      <c r="E9" s="165"/>
-      <c r="F9" s="165"/>
-      <c r="G9" s="165"/>
-      <c r="H9" s="165"/>
-      <c r="I9" s="165"/>
-      <c r="J9" s="166"/>
+      <c r="A9" s="166"/>
+      <c r="B9" s="167"/>
+      <c r="C9" s="167"/>
+      <c r="D9" s="167"/>
+      <c r="E9" s="167"/>
+      <c r="F9" s="167"/>
+      <c r="G9" s="167"/>
+      <c r="H9" s="167"/>
+      <c r="I9" s="167"/>
+      <c r="J9" s="168"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="164"/>
-      <c r="B10" s="165"/>
-      <c r="C10" s="165"/>
-      <c r="D10" s="165"/>
-      <c r="E10" s="165"/>
-      <c r="F10" s="165"/>
-      <c r="G10" s="165"/>
-      <c r="H10" s="165"/>
-      <c r="I10" s="165"/>
-      <c r="J10" s="166"/>
+      <c r="A10" s="166"/>
+      <c r="B10" s="167"/>
+      <c r="C10" s="167"/>
+      <c r="D10" s="167"/>
+      <c r="E10" s="167"/>
+      <c r="F10" s="167"/>
+      <c r="G10" s="167"/>
+      <c r="H10" s="167"/>
+      <c r="I10" s="167"/>
+      <c r="J10" s="168"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="164"/>
-      <c r="B11" s="165"/>
-      <c r="C11" s="165"/>
-      <c r="D11" s="165"/>
-      <c r="E11" s="165"/>
-      <c r="F11" s="165"/>
-      <c r="G11" s="165"/>
-      <c r="H11" s="165"/>
-      <c r="I11" s="165"/>
-      <c r="J11" s="166"/>
+      <c r="A11" s="166"/>
+      <c r="B11" s="167"/>
+      <c r="C11" s="167"/>
+      <c r="D11" s="167"/>
+      <c r="E11" s="167"/>
+      <c r="F11" s="167"/>
+      <c r="G11" s="167"/>
+      <c r="H11" s="167"/>
+      <c r="I11" s="167"/>
+      <c r="J11" s="168"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="164"/>
-      <c r="B12" s="165"/>
-      <c r="C12" s="165"/>
-      <c r="D12" s="165"/>
-      <c r="E12" s="165"/>
-      <c r="F12" s="165"/>
-      <c r="G12" s="165"/>
-      <c r="H12" s="165"/>
-      <c r="I12" s="165"/>
-      <c r="J12" s="166"/>
+      <c r="A12" s="166"/>
+      <c r="B12" s="167"/>
+      <c r="C12" s="167"/>
+      <c r="D12" s="167"/>
+      <c r="E12" s="167"/>
+      <c r="F12" s="167"/>
+      <c r="G12" s="167"/>
+      <c r="H12" s="167"/>
+      <c r="I12" s="167"/>
+      <c r="J12" s="168"/>
     </row>
     <row r="13" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A13" s="164"/>
-      <c r="B13" s="165"/>
-      <c r="C13" s="165"/>
-      <c r="D13" s="165"/>
-      <c r="E13" s="165"/>
-      <c r="F13" s="165"/>
-      <c r="G13" s="165"/>
-      <c r="H13" s="165"/>
-      <c r="I13" s="165"/>
-      <c r="J13" s="166"/>
+      <c r="A13" s="166"/>
+      <c r="B13" s="167"/>
+      <c r="C13" s="167"/>
+      <c r="D13" s="167"/>
+      <c r="E13" s="167"/>
+      <c r="F13" s="167"/>
+      <c r="G13" s="167"/>
+      <c r="H13" s="167"/>
+      <c r="I13" s="167"/>
+      <c r="J13" s="168"/>
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A14" s="185" t="s">
+      <c r="A14" s="162" t="s">
         <v>24</v>
       </c>
       <c r="B14" s="157"/>
@@ -14543,7 +14541,7 @@
       <c r="J14" s="160"/>
     </row>
     <row r="15" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A15" s="185" t="s">
+      <c r="A15" s="162" t="s">
         <v>25</v>
       </c>
       <c r="B15" s="157"/>
@@ -14563,7 +14561,7 @@
       </c>
     </row>
     <row r="16" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A16" s="185" t="s">
+      <c r="A16" s="162" t="s">
         <v>27</v>
       </c>
       <c r="B16" s="157"/>
@@ -14580,7 +14578,7 @@
       <c r="G16" s="39" t="s">
         <v>31</v>
       </c>
-      <c r="H16" s="186" t="s">
+      <c r="H16" s="161" t="s">
         <v>18</v>
       </c>
       <c r="I16" s="157"/>
@@ -15752,23 +15750,6 @@
     <row r="1000" s="36" customFormat="1" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="33">
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="H19:J19"/>
-    <mergeCell ref="A23:C23"/>
-    <mergeCell ref="H23:J23"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="H20:J20"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="H21:J21"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="H22:J22"/>
-    <mergeCell ref="H16:J16"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="A15:C15"/>
-    <mergeCell ref="D15:H15"/>
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="H17:J17"/>
     <mergeCell ref="A24:C24"/>
     <mergeCell ref="H24:J24"/>
     <mergeCell ref="A7:J13"/>
@@ -15785,6 +15766,23 @@
     <mergeCell ref="A6:J6"/>
     <mergeCell ref="A14:J14"/>
     <mergeCell ref="A16:C16"/>
+    <mergeCell ref="H16:J16"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="H18:J18"/>
+    <mergeCell ref="A15:C15"/>
+    <mergeCell ref="D15:H15"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="H17:J17"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="H19:J19"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="H23:J23"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="H20:J20"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="H21:J21"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="H22:J22"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -15808,19 +15806,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="195" t="s">
+      <c r="A1" s="192" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="93"/>
-      <c r="C1" s="94"/>
-      <c r="D1" s="101" t="s">
+      <c r="B1" s="122"/>
+      <c r="C1" s="123"/>
+      <c r="D1" s="130" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="102"/>
-      <c r="F1" s="101" t="s">
+      <c r="E1" s="115"/>
+      <c r="F1" s="130" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="102"/>
+      <c r="G1" s="115"/>
       <c r="H1" s="35" t="s">
         <v>6</v>
       </c>
@@ -15832,190 +15830,190 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="95"/>
-      <c r="B2" s="96"/>
-      <c r="C2" s="97"/>
-      <c r="D2" s="103" t="s">
+      <c r="A2" s="124"/>
+      <c r="B2" s="125"/>
+      <c r="C2" s="126"/>
+      <c r="D2" s="131" t="s">
         <v>85</v>
       </c>
-      <c r="E2" s="104"/>
-      <c r="F2" s="103">
+      <c r="E2" s="132"/>
+      <c r="F2" s="131">
         <v>56</v>
       </c>
-      <c r="G2" s="104"/>
-      <c r="H2" s="107">
+      <c r="G2" s="132"/>
+      <c r="H2" s="100">
         <v>45805</v>
       </c>
-      <c r="I2" s="121" t="s">
+      <c r="I2" s="109" t="s">
         <v>83</v>
       </c>
-      <c r="J2" s="122"/>
+      <c r="J2" s="110"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="95"/>
-      <c r="B3" s="96"/>
-      <c r="C3" s="97"/>
-      <c r="D3" s="105"/>
-      <c r="E3" s="97"/>
-      <c r="F3" s="105"/>
-      <c r="G3" s="97"/>
-      <c r="H3" s="108"/>
-      <c r="I3" s="108"/>
-      <c r="J3" s="123"/>
+      <c r="A3" s="124"/>
+      <c r="B3" s="125"/>
+      <c r="C3" s="126"/>
+      <c r="D3" s="133"/>
+      <c r="E3" s="126"/>
+      <c r="F3" s="133"/>
+      <c r="G3" s="126"/>
+      <c r="H3" s="101"/>
+      <c r="I3" s="101"/>
+      <c r="J3" s="111"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="95"/>
-      <c r="B4" s="96"/>
-      <c r="C4" s="97"/>
-      <c r="D4" s="105"/>
-      <c r="E4" s="97"/>
-      <c r="F4" s="105"/>
-      <c r="G4" s="97"/>
-      <c r="H4" s="108"/>
-      <c r="I4" s="108"/>
-      <c r="J4" s="123"/>
+      <c r="A4" s="124"/>
+      <c r="B4" s="125"/>
+      <c r="C4" s="126"/>
+      <c r="D4" s="133"/>
+      <c r="E4" s="126"/>
+      <c r="F4" s="133"/>
+      <c r="G4" s="126"/>
+      <c r="H4" s="101"/>
+      <c r="I4" s="101"/>
+      <c r="J4" s="111"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="196" t="s">
+      <c r="A5" s="193" t="s">
         <v>22</v>
       </c>
-      <c r="B5" s="126"/>
-      <c r="C5" s="102"/>
-      <c r="D5" s="197" t="s">
+      <c r="B5" s="114"/>
+      <c r="C5" s="115"/>
+      <c r="D5" s="194" t="s">
         <v>86</v>
       </c>
-      <c r="E5" s="126"/>
-      <c r="F5" s="126"/>
-      <c r="G5" s="126"/>
-      <c r="H5" s="126"/>
-      <c r="I5" s="126"/>
-      <c r="J5" s="128"/>
+      <c r="E5" s="114"/>
+      <c r="F5" s="114"/>
+      <c r="G5" s="114"/>
+      <c r="H5" s="114"/>
+      <c r="I5" s="114"/>
+      <c r="J5" s="117"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="189" t="s">
+      <c r="A6" s="187" t="s">
         <v>23</v>
       </c>
-      <c r="B6" s="111"/>
-      <c r="C6" s="111"/>
-      <c r="D6" s="111"/>
-      <c r="E6" s="111"/>
-      <c r="F6" s="111"/>
-      <c r="G6" s="111"/>
-      <c r="H6" s="111"/>
-      <c r="I6" s="111"/>
-      <c r="J6" s="114"/>
+      <c r="B6" s="98"/>
+      <c r="C6" s="98"/>
+      <c r="D6" s="98"/>
+      <c r="E6" s="98"/>
+      <c r="F6" s="98"/>
+      <c r="G6" s="98"/>
+      <c r="H6" s="98"/>
+      <c r="I6" s="98"/>
+      <c r="J6" s="99"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="191"/>
-      <c r="B7" s="192"/>
-      <c r="C7" s="192"/>
-      <c r="D7" s="192"/>
-      <c r="E7" s="192"/>
-      <c r="F7" s="192"/>
-      <c r="G7" s="192"/>
-      <c r="H7" s="192"/>
-      <c r="I7" s="192"/>
-      <c r="J7" s="193"/>
+      <c r="A7" s="188"/>
+      <c r="B7" s="189"/>
+      <c r="C7" s="189"/>
+      <c r="D7" s="189"/>
+      <c r="E7" s="189"/>
+      <c r="F7" s="189"/>
+      <c r="G7" s="189"/>
+      <c r="H7" s="189"/>
+      <c r="I7" s="189"/>
+      <c r="J7" s="190"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="95"/>
-      <c r="B8" s="96"/>
-      <c r="C8" s="96"/>
-      <c r="D8" s="96"/>
-      <c r="E8" s="96"/>
-      <c r="F8" s="96"/>
-      <c r="G8" s="96"/>
-      <c r="H8" s="96"/>
-      <c r="I8" s="96"/>
-      <c r="J8" s="194"/>
+      <c r="A8" s="124"/>
+      <c r="B8" s="125"/>
+      <c r="C8" s="125"/>
+      <c r="D8" s="125"/>
+      <c r="E8" s="125"/>
+      <c r="F8" s="125"/>
+      <c r="G8" s="125"/>
+      <c r="H8" s="125"/>
+      <c r="I8" s="125"/>
+      <c r="J8" s="191"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="95"/>
-      <c r="B9" s="96"/>
-      <c r="C9" s="96"/>
-      <c r="D9" s="96"/>
-      <c r="E9" s="96"/>
-      <c r="F9" s="96"/>
-      <c r="G9" s="96"/>
-      <c r="H9" s="96"/>
-      <c r="I9" s="96"/>
-      <c r="J9" s="194"/>
+      <c r="A9" s="124"/>
+      <c r="B9" s="125"/>
+      <c r="C9" s="125"/>
+      <c r="D9" s="125"/>
+      <c r="E9" s="125"/>
+      <c r="F9" s="125"/>
+      <c r="G9" s="125"/>
+      <c r="H9" s="125"/>
+      <c r="I9" s="125"/>
+      <c r="J9" s="191"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="95"/>
-      <c r="B10" s="96"/>
-      <c r="C10" s="96"/>
-      <c r="D10" s="96"/>
-      <c r="E10" s="96"/>
-      <c r="F10" s="96"/>
-      <c r="G10" s="96"/>
-      <c r="H10" s="96"/>
-      <c r="I10" s="96"/>
-      <c r="J10" s="194"/>
+      <c r="A10" s="124"/>
+      <c r="B10" s="125"/>
+      <c r="C10" s="125"/>
+      <c r="D10" s="125"/>
+      <c r="E10" s="125"/>
+      <c r="F10" s="125"/>
+      <c r="G10" s="125"/>
+      <c r="H10" s="125"/>
+      <c r="I10" s="125"/>
+      <c r="J10" s="191"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="95"/>
-      <c r="B11" s="96"/>
-      <c r="C11" s="96"/>
-      <c r="D11" s="96"/>
-      <c r="E11" s="96"/>
-      <c r="F11" s="96"/>
-      <c r="G11" s="96"/>
-      <c r="H11" s="96"/>
-      <c r="I11" s="96"/>
-      <c r="J11" s="194"/>
+      <c r="A11" s="124"/>
+      <c r="B11" s="125"/>
+      <c r="C11" s="125"/>
+      <c r="D11" s="125"/>
+      <c r="E11" s="125"/>
+      <c r="F11" s="125"/>
+      <c r="G11" s="125"/>
+      <c r="H11" s="125"/>
+      <c r="I11" s="125"/>
+      <c r="J11" s="191"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="95"/>
-      <c r="B12" s="96"/>
-      <c r="C12" s="96"/>
-      <c r="D12" s="96"/>
-      <c r="E12" s="96"/>
-      <c r="F12" s="96"/>
-      <c r="G12" s="96"/>
-      <c r="H12" s="96"/>
-      <c r="I12" s="96"/>
-      <c r="J12" s="194"/>
+      <c r="A12" s="124"/>
+      <c r="B12" s="125"/>
+      <c r="C12" s="125"/>
+      <c r="D12" s="125"/>
+      <c r="E12" s="125"/>
+      <c r="F12" s="125"/>
+      <c r="G12" s="125"/>
+      <c r="H12" s="125"/>
+      <c r="I12" s="125"/>
+      <c r="J12" s="191"/>
     </row>
     <row r="13" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A13" s="95"/>
-      <c r="B13" s="96"/>
-      <c r="C13" s="96"/>
-      <c r="D13" s="96"/>
-      <c r="E13" s="96"/>
-      <c r="F13" s="96"/>
-      <c r="G13" s="96"/>
-      <c r="H13" s="96"/>
-      <c r="I13" s="96"/>
-      <c r="J13" s="194"/>
+      <c r="A13" s="124"/>
+      <c r="B13" s="125"/>
+      <c r="C13" s="125"/>
+      <c r="D13" s="125"/>
+      <c r="E13" s="125"/>
+      <c r="F13" s="125"/>
+      <c r="G13" s="125"/>
+      <c r="H13" s="125"/>
+      <c r="I13" s="125"/>
+      <c r="J13" s="191"/>
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A14" s="189" t="s">
+      <c r="A14" s="187" t="s">
         <v>24</v>
       </c>
-      <c r="B14" s="111"/>
-      <c r="C14" s="111"/>
-      <c r="D14" s="111"/>
-      <c r="E14" s="111"/>
-      <c r="F14" s="111"/>
-      <c r="G14" s="111"/>
-      <c r="H14" s="111"/>
-      <c r="I14" s="111"/>
-      <c r="J14" s="114"/>
+      <c r="B14" s="98"/>
+      <c r="C14" s="98"/>
+      <c r="D14" s="98"/>
+      <c r="E14" s="98"/>
+      <c r="F14" s="98"/>
+      <c r="G14" s="98"/>
+      <c r="H14" s="98"/>
+      <c r="I14" s="98"/>
+      <c r="J14" s="99"/>
     </row>
     <row r="15" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A15" s="189" t="s">
+      <c r="A15" s="187" t="s">
         <v>25</v>
       </c>
-      <c r="B15" s="111"/>
-      <c r="C15" s="112"/>
-      <c r="D15" s="120" t="s">
+      <c r="B15" s="98"/>
+      <c r="C15" s="93"/>
+      <c r="D15" s="97" t="s">
         <v>87</v>
       </c>
-      <c r="E15" s="111"/>
-      <c r="F15" s="111"/>
-      <c r="G15" s="111"/>
-      <c r="H15" s="112"/>
+      <c r="E15" s="98"/>
+      <c r="F15" s="98"/>
+      <c r="G15" s="98"/>
+      <c r="H15" s="93"/>
       <c r="I15" s="45" t="s">
         <v>26</v>
       </c>
@@ -16024,11 +16022,11 @@
       </c>
     </row>
     <row r="16" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A16" s="189" t="s">
+      <c r="A16" s="187" t="s">
         <v>27</v>
       </c>
-      <c r="B16" s="111"/>
-      <c r="C16" s="112"/>
+      <c r="B16" s="98"/>
+      <c r="C16" s="93"/>
       <c r="D16" s="45" t="s">
         <v>28</v>
       </c>
@@ -16041,18 +16039,18 @@
       <c r="G16" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="H16" s="190" t="s">
+      <c r="H16" s="195" t="s">
         <v>18</v>
       </c>
-      <c r="I16" s="111"/>
-      <c r="J16" s="114"/>
+      <c r="I16" s="98"/>
+      <c r="J16" s="99"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="187">
+      <c r="A17" s="196">
         <v>1</v>
       </c>
-      <c r="B17" s="111"/>
-      <c r="C17" s="112"/>
+      <c r="B17" s="98"/>
+      <c r="C17" s="93"/>
       <c r="D17" s="47" t="s">
         <v>64</v>
       </c>
@@ -16065,83 +16063,83 @@
       <c r="G17" s="48" t="s">
         <v>89</v>
       </c>
-      <c r="H17" s="120" t="s">
+      <c r="H17" s="97" t="s">
         <v>90</v>
       </c>
-      <c r="I17" s="111"/>
-      <c r="J17" s="114"/>
+      <c r="I17" s="98"/>
+      <c r="J17" s="99"/>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A18" s="187"/>
-      <c r="B18" s="111"/>
-      <c r="C18" s="112"/>
+      <c r="A18" s="196"/>
+      <c r="B18" s="98"/>
+      <c r="C18" s="93"/>
       <c r="D18" s="47"/>
       <c r="E18" s="47"/>
       <c r="F18" s="48"/>
       <c r="G18" s="48"/>
-      <c r="H18" s="120"/>
-      <c r="I18" s="111"/>
-      <c r="J18" s="114"/>
+      <c r="H18" s="97"/>
+      <c r="I18" s="98"/>
+      <c r="J18" s="99"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="187"/>
-      <c r="B19" s="111"/>
-      <c r="C19" s="112"/>
+      <c r="A19" s="196"/>
+      <c r="B19" s="98"/>
+      <c r="C19" s="93"/>
       <c r="D19" s="47"/>
       <c r="E19" s="47"/>
       <c r="F19" s="48"/>
       <c r="G19" s="48"/>
-      <c r="H19" s="120"/>
-      <c r="I19" s="111"/>
-      <c r="J19" s="114"/>
+      <c r="H19" s="97"/>
+      <c r="I19" s="98"/>
+      <c r="J19" s="99"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="187"/>
-      <c r="B20" s="111"/>
-      <c r="C20" s="112"/>
+      <c r="A20" s="196"/>
+      <c r="B20" s="98"/>
+      <c r="C20" s="93"/>
       <c r="D20" s="47"/>
       <c r="E20" s="47"/>
       <c r="F20" s="48"/>
       <c r="G20" s="48"/>
-      <c r="H20" s="120"/>
-      <c r="I20" s="111"/>
-      <c r="J20" s="114"/>
+      <c r="H20" s="97"/>
+      <c r="I20" s="98"/>
+      <c r="J20" s="99"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="187"/>
-      <c r="B21" s="111"/>
-      <c r="C21" s="112"/>
+      <c r="A21" s="196"/>
+      <c r="B21" s="98"/>
+      <c r="C21" s="93"/>
       <c r="D21" s="47"/>
       <c r="E21" s="47"/>
       <c r="F21" s="48"/>
       <c r="G21" s="48"/>
-      <c r="H21" s="120"/>
-      <c r="I21" s="111"/>
-      <c r="J21" s="114"/>
+      <c r="H21" s="97"/>
+      <c r="I21" s="98"/>
+      <c r="J21" s="99"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="187"/>
-      <c r="B22" s="111"/>
-      <c r="C22" s="112"/>
+      <c r="A22" s="196"/>
+      <c r="B22" s="98"/>
+      <c r="C22" s="93"/>
       <c r="D22" s="47"/>
       <c r="E22" s="47"/>
       <c r="F22" s="48"/>
       <c r="G22" s="48"/>
-      <c r="H22" s="120"/>
-      <c r="I22" s="111"/>
-      <c r="J22" s="114"/>
+      <c r="H22" s="97"/>
+      <c r="I22" s="98"/>
+      <c r="J22" s="99"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A23" s="188"/>
-      <c r="B23" s="116"/>
-      <c r="C23" s="117"/>
+      <c r="A23" s="197"/>
+      <c r="B23" s="105"/>
+      <c r="C23" s="106"/>
       <c r="D23" s="49"/>
       <c r="E23" s="49"/>
       <c r="F23" s="50"/>
       <c r="G23" s="50"/>
-      <c r="H23" s="118"/>
-      <c r="I23" s="116"/>
-      <c r="J23" s="119"/>
+      <c r="H23" s="107"/>
+      <c r="I23" s="105"/>
+      <c r="J23" s="108"/>
     </row>
     <row r="24" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="25" spans="1:10" ht="12.75" customHeight="1"/>
@@ -17122,6 +17120,22 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="31">
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="H23:J23"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="H19:J19"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="H20:J20"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="H21:J21"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="H16:J16"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="H18:J18"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="H17:J17"/>
     <mergeCell ref="A14:J14"/>
     <mergeCell ref="A15:C15"/>
     <mergeCell ref="A7:J13"/>
@@ -17137,22 +17151,6 @@
     <mergeCell ref="D5:J5"/>
     <mergeCell ref="A6:J6"/>
     <mergeCell ref="D15:H15"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="H16:J16"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="H17:J17"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="H22:J22"/>
-    <mergeCell ref="A23:C23"/>
-    <mergeCell ref="H23:J23"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="H19:J19"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="H20:J20"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="H21:J21"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -17176,19 +17174,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="195" t="s">
+      <c r="A1" s="192" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="93"/>
-      <c r="C1" s="94"/>
-      <c r="D1" s="101" t="s">
+      <c r="B1" s="122"/>
+      <c r="C1" s="123"/>
+      <c r="D1" s="130" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="102"/>
-      <c r="F1" s="101" t="s">
+      <c r="E1" s="115"/>
+      <c r="F1" s="130" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="102"/>
+      <c r="G1" s="115"/>
       <c r="H1" s="35" t="s">
         <v>6</v>
       </c>
@@ -17200,190 +17198,190 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="95"/>
-      <c r="B2" s="96"/>
-      <c r="C2" s="97"/>
-      <c r="D2" s="103" t="s">
+      <c r="A2" s="124"/>
+      <c r="B2" s="125"/>
+      <c r="C2" s="126"/>
+      <c r="D2" s="131" t="s">
         <v>84</v>
       </c>
-      <c r="E2" s="104"/>
-      <c r="F2" s="103">
+      <c r="E2" s="132"/>
+      <c r="F2" s="131">
         <v>56</v>
       </c>
-      <c r="G2" s="104"/>
-      <c r="H2" s="107">
+      <c r="G2" s="132"/>
+      <c r="H2" s="100">
         <v>45805</v>
       </c>
-      <c r="I2" s="121" t="s">
+      <c r="I2" s="109" t="s">
         <v>83</v>
       </c>
-      <c r="J2" s="122"/>
+      <c r="J2" s="110"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="95"/>
-      <c r="B3" s="96"/>
-      <c r="C3" s="97"/>
-      <c r="D3" s="105"/>
-      <c r="E3" s="97"/>
-      <c r="F3" s="105"/>
-      <c r="G3" s="97"/>
-      <c r="H3" s="108"/>
-      <c r="I3" s="108"/>
-      <c r="J3" s="123"/>
+      <c r="A3" s="124"/>
+      <c r="B3" s="125"/>
+      <c r="C3" s="126"/>
+      <c r="D3" s="133"/>
+      <c r="E3" s="126"/>
+      <c r="F3" s="133"/>
+      <c r="G3" s="126"/>
+      <c r="H3" s="101"/>
+      <c r="I3" s="101"/>
+      <c r="J3" s="111"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="95"/>
-      <c r="B4" s="96"/>
-      <c r="C4" s="97"/>
-      <c r="D4" s="105"/>
-      <c r="E4" s="97"/>
-      <c r="F4" s="105"/>
-      <c r="G4" s="97"/>
-      <c r="H4" s="108"/>
-      <c r="I4" s="108"/>
-      <c r="J4" s="123"/>
+      <c r="A4" s="124"/>
+      <c r="B4" s="125"/>
+      <c r="C4" s="126"/>
+      <c r="D4" s="133"/>
+      <c r="E4" s="126"/>
+      <c r="F4" s="133"/>
+      <c r="G4" s="126"/>
+      <c r="H4" s="101"/>
+      <c r="I4" s="101"/>
+      <c r="J4" s="111"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="196" t="s">
+      <c r="A5" s="193" t="s">
         <v>22</v>
       </c>
-      <c r="B5" s="126"/>
-      <c r="C5" s="102"/>
-      <c r="D5" s="197" t="s">
+      <c r="B5" s="114"/>
+      <c r="C5" s="115"/>
+      <c r="D5" s="194" t="s">
         <v>91</v>
       </c>
-      <c r="E5" s="126"/>
-      <c r="F5" s="126"/>
-      <c r="G5" s="126"/>
-      <c r="H5" s="126"/>
-      <c r="I5" s="126"/>
-      <c r="J5" s="128"/>
+      <c r="E5" s="114"/>
+      <c r="F5" s="114"/>
+      <c r="G5" s="114"/>
+      <c r="H5" s="114"/>
+      <c r="I5" s="114"/>
+      <c r="J5" s="117"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="189" t="s">
+      <c r="A6" s="187" t="s">
         <v>23</v>
       </c>
-      <c r="B6" s="111"/>
-      <c r="C6" s="111"/>
-      <c r="D6" s="111"/>
-      <c r="E6" s="111"/>
-      <c r="F6" s="111"/>
-      <c r="G6" s="111"/>
-      <c r="H6" s="111"/>
-      <c r="I6" s="111"/>
-      <c r="J6" s="114"/>
+      <c r="B6" s="98"/>
+      <c r="C6" s="98"/>
+      <c r="D6" s="98"/>
+      <c r="E6" s="98"/>
+      <c r="F6" s="98"/>
+      <c r="G6" s="98"/>
+      <c r="H6" s="98"/>
+      <c r="I6" s="98"/>
+      <c r="J6" s="99"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="191"/>
-      <c r="B7" s="192"/>
-      <c r="C7" s="192"/>
-      <c r="D7" s="192"/>
-      <c r="E7" s="192"/>
-      <c r="F7" s="192"/>
-      <c r="G7" s="192"/>
-      <c r="H7" s="192"/>
-      <c r="I7" s="192"/>
-      <c r="J7" s="193"/>
+      <c r="A7" s="188"/>
+      <c r="B7" s="189"/>
+      <c r="C7" s="189"/>
+      <c r="D7" s="189"/>
+      <c r="E7" s="189"/>
+      <c r="F7" s="189"/>
+      <c r="G7" s="189"/>
+      <c r="H7" s="189"/>
+      <c r="I7" s="189"/>
+      <c r="J7" s="190"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="95"/>
-      <c r="B8" s="96"/>
-      <c r="C8" s="96"/>
-      <c r="D8" s="96"/>
-      <c r="E8" s="96"/>
-      <c r="F8" s="96"/>
-      <c r="G8" s="96"/>
-      <c r="H8" s="96"/>
-      <c r="I8" s="96"/>
-      <c r="J8" s="194"/>
+      <c r="A8" s="124"/>
+      <c r="B8" s="125"/>
+      <c r="C8" s="125"/>
+      <c r="D8" s="125"/>
+      <c r="E8" s="125"/>
+      <c r="F8" s="125"/>
+      <c r="G8" s="125"/>
+      <c r="H8" s="125"/>
+      <c r="I8" s="125"/>
+      <c r="J8" s="191"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="95"/>
-      <c r="B9" s="96"/>
-      <c r="C9" s="96"/>
-      <c r="D9" s="96"/>
-      <c r="E9" s="96"/>
-      <c r="F9" s="96"/>
-      <c r="G9" s="96"/>
-      <c r="H9" s="96"/>
-      <c r="I9" s="96"/>
-      <c r="J9" s="194"/>
+      <c r="A9" s="124"/>
+      <c r="B9" s="125"/>
+      <c r="C9" s="125"/>
+      <c r="D9" s="125"/>
+      <c r="E9" s="125"/>
+      <c r="F9" s="125"/>
+      <c r="G9" s="125"/>
+      <c r="H9" s="125"/>
+      <c r="I9" s="125"/>
+      <c r="J9" s="191"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="95"/>
-      <c r="B10" s="96"/>
-      <c r="C10" s="96"/>
-      <c r="D10" s="96"/>
-      <c r="E10" s="96"/>
-      <c r="F10" s="96"/>
-      <c r="G10" s="96"/>
-      <c r="H10" s="96"/>
-      <c r="I10" s="96"/>
-      <c r="J10" s="194"/>
+      <c r="A10" s="124"/>
+      <c r="B10" s="125"/>
+      <c r="C10" s="125"/>
+      <c r="D10" s="125"/>
+      <c r="E10" s="125"/>
+      <c r="F10" s="125"/>
+      <c r="G10" s="125"/>
+      <c r="H10" s="125"/>
+      <c r="I10" s="125"/>
+      <c r="J10" s="191"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="95"/>
-      <c r="B11" s="96"/>
-      <c r="C11" s="96"/>
-      <c r="D11" s="96"/>
-      <c r="E11" s="96"/>
-      <c r="F11" s="96"/>
-      <c r="G11" s="96"/>
-      <c r="H11" s="96"/>
-      <c r="I11" s="96"/>
-      <c r="J11" s="194"/>
+      <c r="A11" s="124"/>
+      <c r="B11" s="125"/>
+      <c r="C11" s="125"/>
+      <c r="D11" s="125"/>
+      <c r="E11" s="125"/>
+      <c r="F11" s="125"/>
+      <c r="G11" s="125"/>
+      <c r="H11" s="125"/>
+      <c r="I11" s="125"/>
+      <c r="J11" s="191"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="95"/>
-      <c r="B12" s="96"/>
-      <c r="C12" s="96"/>
-      <c r="D12" s="96"/>
-      <c r="E12" s="96"/>
-      <c r="F12" s="96"/>
-      <c r="G12" s="96"/>
-      <c r="H12" s="96"/>
-      <c r="I12" s="96"/>
-      <c r="J12" s="194"/>
+      <c r="A12" s="124"/>
+      <c r="B12" s="125"/>
+      <c r="C12" s="125"/>
+      <c r="D12" s="125"/>
+      <c r="E12" s="125"/>
+      <c r="F12" s="125"/>
+      <c r="G12" s="125"/>
+      <c r="H12" s="125"/>
+      <c r="I12" s="125"/>
+      <c r="J12" s="191"/>
     </row>
     <row r="13" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A13" s="95"/>
-      <c r="B13" s="96"/>
-      <c r="C13" s="96"/>
-      <c r="D13" s="96"/>
-      <c r="E13" s="96"/>
-      <c r="F13" s="96"/>
-      <c r="G13" s="96"/>
-      <c r="H13" s="96"/>
-      <c r="I13" s="96"/>
-      <c r="J13" s="194"/>
+      <c r="A13" s="124"/>
+      <c r="B13" s="125"/>
+      <c r="C13" s="125"/>
+      <c r="D13" s="125"/>
+      <c r="E13" s="125"/>
+      <c r="F13" s="125"/>
+      <c r="G13" s="125"/>
+      <c r="H13" s="125"/>
+      <c r="I13" s="125"/>
+      <c r="J13" s="191"/>
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A14" s="189" t="s">
+      <c r="A14" s="187" t="s">
         <v>24</v>
       </c>
-      <c r="B14" s="111"/>
-      <c r="C14" s="111"/>
-      <c r="D14" s="111"/>
-      <c r="E14" s="111"/>
-      <c r="F14" s="111"/>
-      <c r="G14" s="111"/>
-      <c r="H14" s="111"/>
-      <c r="I14" s="111"/>
-      <c r="J14" s="114"/>
+      <c r="B14" s="98"/>
+      <c r="C14" s="98"/>
+      <c r="D14" s="98"/>
+      <c r="E14" s="98"/>
+      <c r="F14" s="98"/>
+      <c r="G14" s="98"/>
+      <c r="H14" s="98"/>
+      <c r="I14" s="98"/>
+      <c r="J14" s="99"/>
     </row>
     <row r="15" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A15" s="189" t="s">
+      <c r="A15" s="187" t="s">
         <v>25</v>
       </c>
-      <c r="B15" s="111"/>
-      <c r="C15" s="112"/>
-      <c r="D15" s="120" t="s">
+      <c r="B15" s="98"/>
+      <c r="C15" s="93"/>
+      <c r="D15" s="97" t="s">
         <v>87</v>
       </c>
-      <c r="E15" s="111"/>
-      <c r="F15" s="111"/>
-      <c r="G15" s="111"/>
-      <c r="H15" s="112"/>
+      <c r="E15" s="98"/>
+      <c r="F15" s="98"/>
+      <c r="G15" s="98"/>
+      <c r="H15" s="93"/>
       <c r="I15" s="45" t="s">
         <v>26</v>
       </c>
@@ -17392,11 +17390,11 @@
       </c>
     </row>
     <row r="16" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A16" s="189" t="s">
+      <c r="A16" s="187" t="s">
         <v>27</v>
       </c>
-      <c r="B16" s="111"/>
-      <c r="C16" s="112"/>
+      <c r="B16" s="98"/>
+      <c r="C16" s="93"/>
       <c r="D16" s="45" t="s">
         <v>28</v>
       </c>
@@ -17409,18 +17407,18 @@
       <c r="G16" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="H16" s="190" t="s">
+      <c r="H16" s="195" t="s">
         <v>18</v>
       </c>
-      <c r="I16" s="111"/>
-      <c r="J16" s="114"/>
+      <c r="I16" s="98"/>
+      <c r="J16" s="99"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="187">
+      <c r="A17" s="196">
         <v>1</v>
       </c>
-      <c r="B17" s="111"/>
-      <c r="C17" s="112"/>
+      <c r="B17" s="98"/>
+      <c r="C17" s="93"/>
       <c r="D17" s="47" t="s">
         <v>64</v>
       </c>
@@ -17433,83 +17431,83 @@
       <c r="G17" s="48" t="s">
         <v>89</v>
       </c>
-      <c r="H17" s="120" t="s">
+      <c r="H17" s="97" t="s">
         <v>90</v>
       </c>
-      <c r="I17" s="111"/>
-      <c r="J17" s="114"/>
+      <c r="I17" s="98"/>
+      <c r="J17" s="99"/>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A18" s="187"/>
-      <c r="B18" s="111"/>
-      <c r="C18" s="112"/>
+      <c r="A18" s="196"/>
+      <c r="B18" s="98"/>
+      <c r="C18" s="93"/>
       <c r="D18" s="47"/>
       <c r="E18" s="47"/>
       <c r="F18" s="48"/>
       <c r="G18" s="48"/>
-      <c r="H18" s="120"/>
-      <c r="I18" s="111"/>
-      <c r="J18" s="114"/>
+      <c r="H18" s="97"/>
+      <c r="I18" s="98"/>
+      <c r="J18" s="99"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="187"/>
-      <c r="B19" s="111"/>
-      <c r="C19" s="112"/>
+      <c r="A19" s="196"/>
+      <c r="B19" s="98"/>
+      <c r="C19" s="93"/>
       <c r="D19" s="47"/>
       <c r="E19" s="47"/>
       <c r="F19" s="48"/>
       <c r="G19" s="48"/>
-      <c r="H19" s="120"/>
-      <c r="I19" s="111"/>
-      <c r="J19" s="114"/>
+      <c r="H19" s="97"/>
+      <c r="I19" s="98"/>
+      <c r="J19" s="99"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="187"/>
-      <c r="B20" s="111"/>
-      <c r="C20" s="112"/>
+      <c r="A20" s="196"/>
+      <c r="B20" s="98"/>
+      <c r="C20" s="93"/>
       <c r="D20" s="47"/>
       <c r="E20" s="47"/>
       <c r="F20" s="48"/>
       <c r="G20" s="48"/>
-      <c r="H20" s="120"/>
-      <c r="I20" s="111"/>
-      <c r="J20" s="114"/>
+      <c r="H20" s="97"/>
+      <c r="I20" s="98"/>
+      <c r="J20" s="99"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="187"/>
-      <c r="B21" s="111"/>
-      <c r="C21" s="112"/>
+      <c r="A21" s="196"/>
+      <c r="B21" s="98"/>
+      <c r="C21" s="93"/>
       <c r="D21" s="47"/>
       <c r="E21" s="47"/>
       <c r="F21" s="48"/>
       <c r="G21" s="48"/>
-      <c r="H21" s="120"/>
-      <c r="I21" s="111"/>
-      <c r="J21" s="114"/>
+      <c r="H21" s="97"/>
+      <c r="I21" s="98"/>
+      <c r="J21" s="99"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="187"/>
-      <c r="B22" s="111"/>
-      <c r="C22" s="112"/>
+      <c r="A22" s="196"/>
+      <c r="B22" s="98"/>
+      <c r="C22" s="93"/>
       <c r="D22" s="47"/>
       <c r="E22" s="47"/>
       <c r="F22" s="48"/>
       <c r="G22" s="48"/>
-      <c r="H22" s="120"/>
-      <c r="I22" s="111"/>
-      <c r="J22" s="114"/>
+      <c r="H22" s="97"/>
+      <c r="I22" s="98"/>
+      <c r="J22" s="99"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A23" s="188"/>
-      <c r="B23" s="116"/>
-      <c r="C23" s="117"/>
+      <c r="A23" s="197"/>
+      <c r="B23" s="105"/>
+      <c r="C23" s="106"/>
       <c r="D23" s="49"/>
       <c r="E23" s="49"/>
       <c r="F23" s="50"/>
       <c r="G23" s="50"/>
-      <c r="H23" s="118"/>
-      <c r="I23" s="116"/>
-      <c r="J23" s="119"/>
+      <c r="H23" s="107"/>
+      <c r="I23" s="105"/>
+      <c r="J23" s="108"/>
     </row>
     <row r="24" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="25" spans="1:10" ht="12.75" customHeight="1"/>
@@ -18490,6 +18488,22 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="31">
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="H23:J23"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="H19:J19"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="H20:J20"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="H21:J21"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="H16:J16"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="H18:J18"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="H17:J17"/>
     <mergeCell ref="A14:J14"/>
     <mergeCell ref="A15:C15"/>
     <mergeCell ref="A7:J13"/>
@@ -18505,22 +18519,6 @@
     <mergeCell ref="D5:J5"/>
     <mergeCell ref="A6:J6"/>
     <mergeCell ref="D15:H15"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="H16:J16"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="H17:J17"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="H22:J22"/>
-    <mergeCell ref="A23:C23"/>
-    <mergeCell ref="H23:J23"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="H19:J19"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="H20:J20"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="H21:J21"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -18540,7 +18538,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="18" customHeight="1">
-      <c r="A1" s="211" t="s">
+      <c r="A1" s="224" t="s">
         <v>32</v>
       </c>
       <c r="B1" s="143"/>
@@ -18551,14 +18549,14 @@
       <c r="G1" s="150" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="212"/>
-      <c r="I1" s="212"/>
+      <c r="H1" s="209"/>
+      <c r="I1" s="209"/>
       <c r="J1" s="151"/>
       <c r="K1" s="150" t="s">
         <v>5</v>
       </c>
-      <c r="L1" s="212"/>
-      <c r="M1" s="212"/>
+      <c r="L1" s="209"/>
+      <c r="M1" s="209"/>
       <c r="N1" s="151"/>
       <c r="O1" s="150" t="s">
         <v>6</v>
@@ -18571,7 +18569,7 @@
       <c r="S1" s="150" t="s">
         <v>8</v>
       </c>
-      <c r="T1" s="213"/>
+      <c r="T1" s="211"/>
     </row>
     <row r="2" spans="1:26" ht="18" customHeight="1">
       <c r="A2" s="145"/>
@@ -18583,16 +18581,16 @@
       <c r="G2" s="152" t="s">
         <v>84</v>
       </c>
-      <c r="H2" s="206"/>
-      <c r="I2" s="206"/>
+      <c r="H2" s="219"/>
+      <c r="I2" s="219"/>
       <c r="J2" s="153"/>
       <c r="K2" s="152" t="s">
         <v>54</v>
       </c>
-      <c r="L2" s="206"/>
-      <c r="M2" s="206"/>
+      <c r="L2" s="219"/>
+      <c r="M2" s="219"/>
       <c r="N2" s="153"/>
-      <c r="O2" s="207">
+      <c r="O2" s="220">
         <v>45821</v>
       </c>
       <c r="P2" s="153"/>
@@ -18601,7 +18599,7 @@
       </c>
       <c r="R2" s="153"/>
       <c r="S2" s="152"/>
-      <c r="T2" s="208"/>
+      <c r="T2" s="221"/>
     </row>
     <row r="3" spans="1:26" ht="18" customHeight="1">
       <c r="A3" s="145"/>
@@ -18623,7 +18621,7 @@
       <c r="Q3" s="154"/>
       <c r="R3" s="146"/>
       <c r="S3" s="154"/>
-      <c r="T3" s="209"/>
+      <c r="T3" s="222"/>
     </row>
     <row r="4" spans="1:26" ht="18" customHeight="1">
       <c r="A4" s="147"/>
@@ -18645,36 +18643,36 @@
       <c r="Q4" s="155"/>
       <c r="R4" s="149"/>
       <c r="S4" s="155"/>
-      <c r="T4" s="210"/>
+      <c r="T4" s="223"/>
     </row>
     <row r="5" spans="1:26" ht="18" customHeight="1">
-      <c r="A5" s="214" t="s">
+      <c r="A5" s="208" t="s">
         <v>33</v>
       </c>
-      <c r="B5" s="212"/>
-      <c r="C5" s="212"/>
-      <c r="D5" s="212"/>
-      <c r="E5" s="212"/>
+      <c r="B5" s="209"/>
+      <c r="C5" s="209"/>
+      <c r="D5" s="209"/>
+      <c r="E5" s="209"/>
       <c r="F5" s="151"/>
-      <c r="G5" s="215" t="s">
+      <c r="G5" s="210" t="s">
         <v>34</v>
       </c>
-      <c r="H5" s="212"/>
-      <c r="I5" s="212"/>
-      <c r="J5" s="212"/>
-      <c r="K5" s="212"/>
-      <c r="L5" s="212"/>
-      <c r="M5" s="212"/>
-      <c r="N5" s="212"/>
-      <c r="O5" s="212"/>
-      <c r="P5" s="212"/>
-      <c r="Q5" s="212"/>
-      <c r="R5" s="212"/>
-      <c r="S5" s="212"/>
-      <c r="T5" s="213"/>
+      <c r="H5" s="209"/>
+      <c r="I5" s="209"/>
+      <c r="J5" s="209"/>
+      <c r="K5" s="209"/>
+      <c r="L5" s="209"/>
+      <c r="M5" s="209"/>
+      <c r="N5" s="209"/>
+      <c r="O5" s="209"/>
+      <c r="P5" s="209"/>
+      <c r="Q5" s="209"/>
+      <c r="R5" s="209"/>
+      <c r="S5" s="209"/>
+      <c r="T5" s="211"/>
     </row>
     <row r="6" spans="1:26" ht="18" customHeight="1">
-      <c r="A6" s="216" t="s">
+      <c r="A6" s="212" t="s">
         <v>35</v>
       </c>
       <c r="B6" s="84"/>
@@ -18682,7 +18680,7 @@
       <c r="D6" s="84"/>
       <c r="E6" s="84"/>
       <c r="F6" s="85"/>
-      <c r="G6" s="217" t="s">
+      <c r="G6" s="213" t="s">
         <v>19</v>
       </c>
       <c r="H6" s="84"/>
@@ -18697,10 +18695,10 @@
       <c r="Q6" s="84"/>
       <c r="R6" s="84"/>
       <c r="S6" s="84"/>
-      <c r="T6" s="218"/>
+      <c r="T6" s="214"/>
     </row>
     <row r="7" spans="1:26" ht="18" customHeight="1">
-      <c r="A7" s="216" t="s">
+      <c r="A7" s="212" t="s">
         <v>36</v>
       </c>
       <c r="B7" s="84"/>
@@ -18708,7 +18706,7 @@
       <c r="D7" s="84"/>
       <c r="E7" s="84"/>
       <c r="F7" s="85"/>
-      <c r="G7" s="217" t="s">
+      <c r="G7" s="213" t="s">
         <v>111</v>
       </c>
       <c r="H7" s="84"/>
@@ -18723,7 +18721,7 @@
       <c r="Q7" s="84"/>
       <c r="R7" s="84"/>
       <c r="S7" s="84"/>
-      <c r="T7" s="218"/>
+      <c r="T7" s="214"/>
     </row>
     <row r="8" spans="1:26" ht="7.5" customHeight="1">
       <c r="A8" s="7"/>
@@ -18922,33 +18920,33 @@
       <c r="T14" s="9"/>
     </row>
     <row r="15" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A15" s="216" t="s">
+      <c r="A15" s="212" t="s">
         <v>43</v>
       </c>
       <c r="B15" s="85"/>
-      <c r="C15" s="222" t="s">
+      <c r="C15" s="218" t="s">
         <v>37</v>
       </c>
       <c r="D15" s="85"/>
-      <c r="E15" s="198" t="s">
+      <c r="E15" s="216" t="s">
         <v>44</v>
       </c>
       <c r="F15" s="85"/>
-      <c r="G15" s="198" t="s">
+      <c r="G15" s="216" t="s">
         <v>45</v>
       </c>
       <c r="H15" s="84"/>
       <c r="I15" s="85"/>
-      <c r="J15" s="198" t="s">
+      <c r="J15" s="216" t="s">
         <v>46</v>
       </c>
       <c r="K15" s="85"/>
-      <c r="L15" s="198" t="s">
+      <c r="L15" s="216" t="s">
         <v>47</v>
       </c>
       <c r="M15" s="84"/>
       <c r="N15" s="85"/>
-      <c r="O15" s="198" t="s">
+      <c r="O15" s="216" t="s">
         <v>48</v>
       </c>
       <c r="P15" s="84"/>
@@ -18964,44 +18962,46 @@
       </c>
     </row>
     <row r="16" spans="1:26" ht="48" customHeight="1">
-      <c r="A16" s="219">
+      <c r="A16" s="198">
         <v>1</v>
       </c>
       <c r="B16" s="85"/>
-      <c r="C16" s="220" t="s">
+      <c r="C16" s="199" t="s">
         <v>52</v>
       </c>
       <c r="D16" s="85"/>
-      <c r="E16" s="220" t="s">
+      <c r="E16" s="199" t="s">
         <v>53</v>
       </c>
       <c r="F16" s="85"/>
-      <c r="G16" s="199" t="s">
+      <c r="G16" s="215" t="s">
         <v>112</v>
       </c>
       <c r="H16" s="84"/>
       <c r="I16" s="85"/>
-      <c r="J16" s="200" t="s">
+      <c r="J16" s="228" t="s">
         <v>113</v>
       </c>
-      <c r="K16" s="112"/>
-      <c r="L16" s="204" t="s">
+      <c r="K16" s="93"/>
+      <c r="L16" s="205" t="s">
         <v>114</v>
       </c>
       <c r="M16" s="84"/>
       <c r="N16" s="85"/>
-      <c r="O16" s="204" t="s">
+      <c r="O16" s="205" t="s">
         <v>115</v>
       </c>
       <c r="P16" s="84"/>
       <c r="Q16" s="85"/>
       <c r="R16" s="65">
-        <v>45824</v>
+        <v>45825</v>
       </c>
       <c r="S16" s="27" t="s">
-        <v>83</v>
-      </c>
-      <c r="T16" s="28"/>
+        <v>110</v>
+      </c>
+      <c r="T16" s="28" t="s">
+        <v>168</v>
+      </c>
       <c r="U16" s="29"/>
       <c r="V16" s="29"/>
       <c r="W16" s="29"/>
@@ -19010,42 +19010,46 @@
       <c r="Z16" s="29"/>
     </row>
     <row r="17" spans="1:26" ht="51" customHeight="1">
-      <c r="A17" s="219">
+      <c r="A17" s="198">
         <v>2</v>
       </c>
       <c r="B17" s="85"/>
-      <c r="C17" s="220" t="s">
+      <c r="C17" s="199" t="s">
         <v>52</v>
       </c>
       <c r="D17" s="85"/>
-      <c r="E17" s="220" t="s">
+      <c r="E17" s="199" t="s">
         <v>118</v>
       </c>
       <c r="F17" s="85"/>
-      <c r="G17" s="199" t="s">
+      <c r="G17" s="215" t="s">
         <v>116</v>
       </c>
       <c r="H17" s="84"/>
       <c r="I17" s="85"/>
-      <c r="J17" s="199" t="s">
+      <c r="J17" s="215" t="s">
         <v>117</v>
       </c>
       <c r="K17" s="85"/>
-      <c r="L17" s="221" t="s">
+      <c r="L17" s="217" t="s">
         <v>119</v>
       </c>
       <c r="M17" s="84"/>
       <c r="N17" s="85"/>
-      <c r="O17" s="204" t="s">
+      <c r="O17" s="205" t="s">
         <v>122</v>
       </c>
       <c r="P17" s="84"/>
       <c r="Q17" s="85"/>
-      <c r="R17" s="27"/>
+      <c r="R17" s="65">
+        <v>45825</v>
+      </c>
       <c r="S17" s="27" t="s">
-        <v>83</v>
-      </c>
-      <c r="T17" s="28"/>
+        <v>110</v>
+      </c>
+      <c r="T17" s="28" t="s">
+        <v>168</v>
+      </c>
       <c r="U17" s="29"/>
       <c r="V17" s="29"/>
       <c r="W17" s="29"/>
@@ -19054,42 +19058,46 @@
       <c r="Z17" s="29"/>
     </row>
     <row r="18" spans="1:26" ht="120" customHeight="1">
-      <c r="A18" s="219">
+      <c r="A18" s="198">
         <v>3</v>
       </c>
       <c r="B18" s="85"/>
-      <c r="C18" s="220" t="s">
+      <c r="C18" s="199" t="s">
         <v>52</v>
       </c>
       <c r="D18" s="85"/>
-      <c r="E18" s="220" t="s">
+      <c r="E18" s="199" t="s">
         <v>53</v>
       </c>
       <c r="F18" s="85"/>
-      <c r="G18" s="199" t="s">
+      <c r="G18" s="215" t="s">
         <v>139</v>
       </c>
       <c r="H18" s="84"/>
       <c r="I18" s="85"/>
-      <c r="J18" s="199" t="s">
+      <c r="J18" s="215" t="s">
         <v>140</v>
       </c>
       <c r="K18" s="85"/>
-      <c r="L18" s="204" t="s">
+      <c r="L18" s="205" t="s">
         <v>114</v>
       </c>
       <c r="M18" s="84"/>
       <c r="N18" s="85"/>
-      <c r="O18" s="204" t="s">
+      <c r="O18" s="205" t="s">
         <v>120</v>
       </c>
       <c r="P18" s="84"/>
       <c r="Q18" s="85"/>
-      <c r="R18" s="27"/>
+      <c r="R18" s="65">
+        <v>45825</v>
+      </c>
       <c r="S18" s="27" t="s">
-        <v>83</v>
-      </c>
-      <c r="T18" s="28"/>
+        <v>110</v>
+      </c>
+      <c r="T18" s="28" t="s">
+        <v>168</v>
+      </c>
       <c r="U18" s="29"/>
       <c r="V18" s="29"/>
       <c r="W18" s="29"/>
@@ -19098,42 +19106,46 @@
       <c r="Z18" s="29"/>
     </row>
     <row r="19" spans="1:26" ht="94.5" customHeight="1">
-      <c r="A19" s="219">
+      <c r="A19" s="198">
         <v>4</v>
       </c>
       <c r="B19" s="85"/>
-      <c r="C19" s="220" t="s">
+      <c r="C19" s="199" t="s">
         <v>52</v>
       </c>
       <c r="D19" s="85"/>
-      <c r="E19" s="220" t="s">
+      <c r="E19" s="199" t="s">
         <v>118</v>
       </c>
       <c r="F19" s="85"/>
-      <c r="G19" s="199" t="s">
+      <c r="G19" s="215" t="s">
         <v>141</v>
       </c>
       <c r="H19" s="84"/>
       <c r="I19" s="85"/>
-      <c r="J19" s="199" t="s">
+      <c r="J19" s="215" t="s">
         <v>142</v>
       </c>
       <c r="K19" s="85"/>
-      <c r="L19" s="204" t="s">
+      <c r="L19" s="205" t="s">
         <v>114</v>
       </c>
       <c r="M19" s="84"/>
       <c r="N19" s="85"/>
-      <c r="O19" s="204" t="s">
+      <c r="O19" s="205" t="s">
         <v>121</v>
       </c>
       <c r="P19" s="84"/>
       <c r="Q19" s="85"/>
-      <c r="R19" s="27"/>
+      <c r="R19" s="65">
+        <v>45825</v>
+      </c>
       <c r="S19" s="27" t="s">
-        <v>83</v>
-      </c>
-      <c r="T19" s="28"/>
+        <v>110</v>
+      </c>
+      <c r="T19" s="28" t="s">
+        <v>168</v>
+      </c>
       <c r="U19" s="29"/>
       <c r="V19" s="29"/>
       <c r="W19" s="29"/>
@@ -19142,42 +19154,44 @@
       <c r="Z19" s="29"/>
     </row>
     <row r="20" spans="1:26" ht="120" customHeight="1">
-      <c r="A20" s="219">
+      <c r="A20" s="198">
         <v>5</v>
       </c>
       <c r="B20" s="85"/>
-      <c r="C20" s="220" t="s">
+      <c r="C20" s="199" t="s">
         <v>138</v>
       </c>
       <c r="D20" s="85"/>
-      <c r="E20" s="220" t="s">
+      <c r="E20" s="199" t="s">
         <v>143</v>
       </c>
       <c r="F20" s="85"/>
-      <c r="G20" s="199" t="s">
+      <c r="G20" s="215" t="s">
         <v>146</v>
       </c>
       <c r="H20" s="84"/>
       <c r="I20" s="85"/>
-      <c r="J20" s="199" t="s">
+      <c r="J20" s="215" t="s">
         <v>145</v>
       </c>
       <c r="K20" s="85"/>
-      <c r="L20" s="204" t="s">
+      <c r="L20" s="205" t="s">
         <v>114</v>
       </c>
       <c r="M20" s="84"/>
       <c r="N20" s="85"/>
-      <c r="O20" s="204" t="s">
+      <c r="O20" s="205" t="s">
         <v>120</v>
       </c>
       <c r="P20" s="84"/>
       <c r="Q20" s="85"/>
       <c r="R20" s="27"/>
       <c r="S20" s="27" t="s">
-        <v>83</v>
-      </c>
-      <c r="T20" s="28"/>
+        <v>110</v>
+      </c>
+      <c r="T20" s="28" t="s">
+        <v>168</v>
+      </c>
       <c r="U20" s="29"/>
       <c r="V20" s="29"/>
       <c r="W20" s="29"/>
@@ -19186,42 +19200,46 @@
       <c r="Z20" s="29"/>
     </row>
     <row r="21" spans="1:26" ht="75" customHeight="1">
-      <c r="A21" s="219">
+      <c r="A21" s="198">
         <v>6</v>
       </c>
       <c r="B21" s="85"/>
-      <c r="C21" s="220" t="s">
+      <c r="C21" s="199" t="s">
         <v>138</v>
       </c>
       <c r="D21" s="85"/>
-      <c r="E21" s="220" t="s">
+      <c r="E21" s="199" t="s">
         <v>118</v>
       </c>
       <c r="F21" s="85"/>
-      <c r="G21" s="199" t="s">
+      <c r="G21" s="215" t="s">
         <v>154</v>
       </c>
       <c r="H21" s="84"/>
       <c r="I21" s="85"/>
-      <c r="J21" s="199" t="s">
+      <c r="J21" s="215" t="s">
         <v>144</v>
       </c>
       <c r="K21" s="85"/>
-      <c r="L21" s="204" t="s">
+      <c r="L21" s="205" t="s">
         <v>114</v>
       </c>
       <c r="M21" s="84"/>
       <c r="N21" s="85"/>
-      <c r="O21" s="204" t="s">
+      <c r="O21" s="205" t="s">
         <v>121</v>
       </c>
       <c r="P21" s="84"/>
       <c r="Q21" s="85"/>
-      <c r="R21" s="27"/>
+      <c r="R21" s="65">
+        <v>45825</v>
+      </c>
       <c r="S21" s="27" t="s">
-        <v>83</v>
-      </c>
-      <c r="T21" s="28"/>
+        <v>110</v>
+      </c>
+      <c r="T21" s="28" t="s">
+        <v>168</v>
+      </c>
       <c r="U21" s="29"/>
       <c r="V21" s="29"/>
       <c r="W21" s="29"/>
@@ -19230,40 +19248,46 @@
       <c r="Z21" s="29"/>
     </row>
     <row r="22" spans="1:26" ht="57" customHeight="1">
-      <c r="A22" s="266">
+      <c r="A22" s="203">
         <v>7</v>
       </c>
-      <c r="B22" s="112"/>
-      <c r="C22" s="267" t="s">
+      <c r="B22" s="93"/>
+      <c r="C22" s="204" t="s">
         <v>52</v>
       </c>
-      <c r="D22" s="112"/>
-      <c r="E22" s="267" t="s">
+      <c r="D22" s="93"/>
+      <c r="E22" s="204" t="s">
         <v>165</v>
       </c>
-      <c r="F22" s="112"/>
-      <c r="G22" s="200" t="s">
+      <c r="F22" s="93"/>
+      <c r="G22" s="228" t="s">
         <v>166</v>
       </c>
-      <c r="H22" s="111"/>
-      <c r="I22" s="112"/>
-      <c r="J22" s="200" t="s">
+      <c r="H22" s="98"/>
+      <c r="I22" s="93"/>
+      <c r="J22" s="228" t="s">
         <v>117</v>
       </c>
-      <c r="K22" s="112"/>
-      <c r="L22" s="268" t="s">
+      <c r="K22" s="93"/>
+      <c r="L22" s="225" t="s">
         <v>119</v>
       </c>
-      <c r="M22" s="269"/>
-      <c r="N22" s="269"/>
-      <c r="O22" s="204" t="s">
+      <c r="M22" s="226"/>
+      <c r="N22" s="226"/>
+      <c r="O22" s="205" t="s">
         <v>167</v>
       </c>
       <c r="P22" s="84"/>
       <c r="Q22" s="85"/>
-      <c r="R22" s="270"/>
-      <c r="S22" s="270"/>
-      <c r="T22" s="271"/>
+      <c r="R22" s="65">
+        <v>45825</v>
+      </c>
+      <c r="S22" s="27" t="s">
+        <v>110</v>
+      </c>
+      <c r="T22" s="28" t="s">
+        <v>168</v>
+      </c>
       <c r="U22" s="29"/>
       <c r="V22" s="29"/>
       <c r="W22" s="29"/>
@@ -19272,21 +19296,21 @@
       <c r="Z22" s="29"/>
     </row>
     <row r="23" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A23" s="219"/>
+      <c r="A23" s="198"/>
       <c r="B23" s="85"/>
-      <c r="C23" s="220"/>
+      <c r="C23" s="199"/>
       <c r="D23" s="85"/>
-      <c r="E23" s="220"/>
+      <c r="E23" s="199"/>
       <c r="F23" s="85"/>
-      <c r="G23" s="199"/>
+      <c r="G23" s="215"/>
       <c r="H23" s="84"/>
       <c r="I23" s="85"/>
-      <c r="J23" s="199"/>
+      <c r="J23" s="215"/>
       <c r="K23" s="85"/>
-      <c r="L23" s="204"/>
+      <c r="L23" s="205"/>
       <c r="M23" s="84"/>
       <c r="N23" s="85"/>
-      <c r="O23" s="204"/>
+      <c r="O23" s="205"/>
       <c r="P23" s="84"/>
       <c r="Q23" s="85"/>
       <c r="R23" s="27"/>
@@ -19300,21 +19324,21 @@
       <c r="Z23" s="29"/>
     </row>
     <row r="24" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A24" s="219"/>
+      <c r="A24" s="198"/>
       <c r="B24" s="85"/>
-      <c r="C24" s="220"/>
+      <c r="C24" s="199"/>
       <c r="D24" s="85"/>
-      <c r="E24" s="220"/>
+      <c r="E24" s="199"/>
       <c r="F24" s="85"/>
-      <c r="G24" s="199"/>
+      <c r="G24" s="215"/>
       <c r="H24" s="84"/>
       <c r="I24" s="85"/>
-      <c r="J24" s="199"/>
+      <c r="J24" s="215"/>
       <c r="K24" s="85"/>
-      <c r="L24" s="204"/>
+      <c r="L24" s="205"/>
       <c r="M24" s="84"/>
       <c r="N24" s="85"/>
-      <c r="O24" s="204"/>
+      <c r="O24" s="205"/>
       <c r="P24" s="84"/>
       <c r="Q24" s="85"/>
       <c r="R24" s="27"/>
@@ -19328,21 +19352,21 @@
       <c r="Z24" s="29"/>
     </row>
     <row r="25" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A25" s="219"/>
+      <c r="A25" s="198"/>
       <c r="B25" s="85"/>
-      <c r="C25" s="220"/>
+      <c r="C25" s="199"/>
       <c r="D25" s="85"/>
-      <c r="E25" s="220"/>
+      <c r="E25" s="199"/>
       <c r="F25" s="85"/>
-      <c r="G25" s="199"/>
+      <c r="G25" s="215"/>
       <c r="H25" s="84"/>
       <c r="I25" s="85"/>
-      <c r="J25" s="199"/>
+      <c r="J25" s="215"/>
       <c r="K25" s="85"/>
-      <c r="L25" s="204"/>
+      <c r="L25" s="205"/>
       <c r="M25" s="84"/>
       <c r="N25" s="85"/>
-      <c r="O25" s="204"/>
+      <c r="O25" s="205"/>
       <c r="P25" s="84"/>
       <c r="Q25" s="85"/>
       <c r="R25" s="27"/>
@@ -19356,21 +19380,21 @@
       <c r="Z25" s="29"/>
     </row>
     <row r="26" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A26" s="219"/>
+      <c r="A26" s="198"/>
       <c r="B26" s="85"/>
-      <c r="C26" s="220"/>
+      <c r="C26" s="199"/>
       <c r="D26" s="85"/>
-      <c r="E26" s="220"/>
+      <c r="E26" s="199"/>
       <c r="F26" s="85"/>
-      <c r="G26" s="199"/>
+      <c r="G26" s="215"/>
       <c r="H26" s="84"/>
       <c r="I26" s="85"/>
-      <c r="J26" s="199"/>
+      <c r="J26" s="215"/>
       <c r="K26" s="85"/>
-      <c r="L26" s="204"/>
+      <c r="L26" s="205"/>
       <c r="M26" s="84"/>
       <c r="N26" s="85"/>
-      <c r="O26" s="204"/>
+      <c r="O26" s="205"/>
       <c r="P26" s="84"/>
       <c r="Q26" s="85"/>
       <c r="R26" s="27"/>
@@ -19384,21 +19408,21 @@
       <c r="Z26" s="29"/>
     </row>
     <row r="27" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A27" s="219"/>
+      <c r="A27" s="198"/>
       <c r="B27" s="85"/>
-      <c r="C27" s="220"/>
+      <c r="C27" s="199"/>
       <c r="D27" s="85"/>
-      <c r="E27" s="220"/>
+      <c r="E27" s="199"/>
       <c r="F27" s="85"/>
-      <c r="G27" s="199"/>
+      <c r="G27" s="215"/>
       <c r="H27" s="84"/>
       <c r="I27" s="85"/>
-      <c r="J27" s="199"/>
+      <c r="J27" s="215"/>
       <c r="K27" s="85"/>
-      <c r="L27" s="204"/>
+      <c r="L27" s="205"/>
       <c r="M27" s="84"/>
       <c r="N27" s="85"/>
-      <c r="O27" s="204"/>
+      <c r="O27" s="205"/>
       <c r="P27" s="84"/>
       <c r="Q27" s="85"/>
       <c r="R27" s="27"/>
@@ -19412,21 +19436,21 @@
       <c r="Z27" s="29"/>
     </row>
     <row r="28" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A28" s="219"/>
+      <c r="A28" s="198"/>
       <c r="B28" s="85"/>
-      <c r="C28" s="220"/>
+      <c r="C28" s="199"/>
       <c r="D28" s="85"/>
-      <c r="E28" s="220"/>
+      <c r="E28" s="199"/>
       <c r="F28" s="85"/>
-      <c r="G28" s="199"/>
+      <c r="G28" s="215"/>
       <c r="H28" s="84"/>
       <c r="I28" s="85"/>
-      <c r="J28" s="199"/>
+      <c r="J28" s="215"/>
       <c r="K28" s="85"/>
-      <c r="L28" s="204"/>
+      <c r="L28" s="205"/>
       <c r="M28" s="84"/>
       <c r="N28" s="85"/>
-      <c r="O28" s="204"/>
+      <c r="O28" s="205"/>
       <c r="P28" s="84"/>
       <c r="Q28" s="85"/>
       <c r="R28" s="27"/>
@@ -19440,21 +19464,21 @@
       <c r="Z28" s="29"/>
     </row>
     <row r="29" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A29" s="219"/>
+      <c r="A29" s="198"/>
       <c r="B29" s="85"/>
-      <c r="C29" s="220"/>
+      <c r="C29" s="199"/>
       <c r="D29" s="85"/>
-      <c r="E29" s="220"/>
+      <c r="E29" s="199"/>
       <c r="F29" s="85"/>
-      <c r="G29" s="199"/>
+      <c r="G29" s="215"/>
       <c r="H29" s="84"/>
       <c r="I29" s="85"/>
-      <c r="J29" s="199"/>
+      <c r="J29" s="215"/>
       <c r="K29" s="85"/>
-      <c r="L29" s="204"/>
+      <c r="L29" s="205"/>
       <c r="M29" s="84"/>
       <c r="N29" s="85"/>
-      <c r="O29" s="204"/>
+      <c r="O29" s="205"/>
       <c r="P29" s="84"/>
       <c r="Q29" s="85"/>
       <c r="R29" s="27"/>
@@ -19468,21 +19492,21 @@
       <c r="Z29" s="29"/>
     </row>
     <row r="30" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A30" s="219"/>
+      <c r="A30" s="198"/>
       <c r="B30" s="85"/>
-      <c r="C30" s="220"/>
+      <c r="C30" s="199"/>
       <c r="D30" s="85"/>
-      <c r="E30" s="220"/>
+      <c r="E30" s="199"/>
       <c r="F30" s="85"/>
-      <c r="G30" s="199"/>
+      <c r="G30" s="215"/>
       <c r="H30" s="84"/>
       <c r="I30" s="85"/>
-      <c r="J30" s="199"/>
+      <c r="J30" s="215"/>
       <c r="K30" s="85"/>
-      <c r="L30" s="204"/>
+      <c r="L30" s="205"/>
       <c r="M30" s="84"/>
       <c r="N30" s="85"/>
-      <c r="O30" s="204"/>
+      <c r="O30" s="205"/>
       <c r="P30" s="84"/>
       <c r="Q30" s="85"/>
       <c r="R30" s="27"/>
@@ -19496,23 +19520,23 @@
       <c r="Z30" s="29"/>
     </row>
     <row r="31" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A31" s="223"/>
-      <c r="B31" s="203"/>
-      <c r="C31" s="224"/>
-      <c r="D31" s="203"/>
-      <c r="E31" s="224"/>
-      <c r="F31" s="203"/>
-      <c r="G31" s="201"/>
-      <c r="H31" s="202"/>
-      <c r="I31" s="203"/>
-      <c r="J31" s="201"/>
-      <c r="K31" s="203"/>
-      <c r="L31" s="205"/>
-      <c r="M31" s="202"/>
-      <c r="N31" s="203"/>
-      <c r="O31" s="205"/>
-      <c r="P31" s="202"/>
-      <c r="Q31" s="203"/>
+      <c r="A31" s="200"/>
+      <c r="B31" s="201"/>
+      <c r="C31" s="202"/>
+      <c r="D31" s="201"/>
+      <c r="E31" s="202"/>
+      <c r="F31" s="201"/>
+      <c r="G31" s="227"/>
+      <c r="H31" s="207"/>
+      <c r="I31" s="201"/>
+      <c r="J31" s="227"/>
+      <c r="K31" s="201"/>
+      <c r="L31" s="206"/>
+      <c r="M31" s="207"/>
+      <c r="N31" s="201"/>
+      <c r="O31" s="206"/>
+      <c r="P31" s="207"/>
+      <c r="Q31" s="201"/>
       <c r="R31" s="30"/>
       <c r="S31" s="30"/>
       <c r="T31" s="31"/>
@@ -20510,6 +20534,118 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="136">
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="J19:K19"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="J30:K30"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="J29:K29"/>
+    <mergeCell ref="L26:N26"/>
+    <mergeCell ref="L27:N27"/>
+    <mergeCell ref="L28:N28"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="L18:N18"/>
+    <mergeCell ref="L19:N19"/>
+    <mergeCell ref="L21:N21"/>
+    <mergeCell ref="L22:N22"/>
+    <mergeCell ref="L23:N23"/>
+    <mergeCell ref="L24:N24"/>
+    <mergeCell ref="L25:N25"/>
+    <mergeCell ref="K2:N4"/>
+    <mergeCell ref="O2:P4"/>
+    <mergeCell ref="Q2:R4"/>
+    <mergeCell ref="S2:T4"/>
+    <mergeCell ref="A1:F4"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="S1:T1"/>
+    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="G5:T5"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="G6:T6"/>
+    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="G7:T7"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="G20:I20"/>
+    <mergeCell ref="J20:K20"/>
+    <mergeCell ref="L20:N20"/>
+    <mergeCell ref="O20:Q20"/>
+    <mergeCell ref="L15:N15"/>
+    <mergeCell ref="O15:Q15"/>
+    <mergeCell ref="L16:N16"/>
+    <mergeCell ref="O16:Q16"/>
+    <mergeCell ref="L17:N17"/>
+    <mergeCell ref="O17:Q17"/>
+    <mergeCell ref="O18:Q18"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="O27:Q27"/>
+    <mergeCell ref="O28:Q28"/>
+    <mergeCell ref="O29:Q29"/>
+    <mergeCell ref="O30:Q30"/>
+    <mergeCell ref="O31:Q31"/>
+    <mergeCell ref="O19:Q19"/>
+    <mergeCell ref="O21:Q21"/>
+    <mergeCell ref="O22:Q22"/>
+    <mergeCell ref="O23:Q23"/>
+    <mergeCell ref="O24:Q24"/>
+    <mergeCell ref="O25:Q25"/>
+    <mergeCell ref="O26:Q26"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="A23:B23"/>
     <mergeCell ref="A30:B30"/>
     <mergeCell ref="C30:D30"/>
     <mergeCell ref="E30:F30"/>
@@ -20534,118 +20670,6 @@
     <mergeCell ref="C28:D28"/>
     <mergeCell ref="E28:F28"/>
     <mergeCell ref="A29:B29"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="O27:Q27"/>
-    <mergeCell ref="O28:Q28"/>
-    <mergeCell ref="O29:Q29"/>
-    <mergeCell ref="O30:Q30"/>
-    <mergeCell ref="O31:Q31"/>
-    <mergeCell ref="O19:Q19"/>
-    <mergeCell ref="O21:Q21"/>
-    <mergeCell ref="O22:Q22"/>
-    <mergeCell ref="O23:Q23"/>
-    <mergeCell ref="O24:Q24"/>
-    <mergeCell ref="O25:Q25"/>
-    <mergeCell ref="O26:Q26"/>
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="G5:T5"/>
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="G6:T6"/>
-    <mergeCell ref="A7:F7"/>
-    <mergeCell ref="G7:T7"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="G20:I20"/>
-    <mergeCell ref="J20:K20"/>
-    <mergeCell ref="L20:N20"/>
-    <mergeCell ref="O20:Q20"/>
-    <mergeCell ref="L15:N15"/>
-    <mergeCell ref="O15:Q15"/>
-    <mergeCell ref="L16:N16"/>
-    <mergeCell ref="O16:Q16"/>
-    <mergeCell ref="L17:N17"/>
-    <mergeCell ref="O17:Q17"/>
-    <mergeCell ref="O18:Q18"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="K2:N4"/>
-    <mergeCell ref="O2:P4"/>
-    <mergeCell ref="Q2:R4"/>
-    <mergeCell ref="S2:T4"/>
-    <mergeCell ref="A1:F4"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="O1:P1"/>
-    <mergeCell ref="Q1:R1"/>
-    <mergeCell ref="S1:T1"/>
-    <mergeCell ref="G2:J4"/>
-    <mergeCell ref="L26:N26"/>
-    <mergeCell ref="L27:N27"/>
-    <mergeCell ref="L28:N28"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="L18:N18"/>
-    <mergeCell ref="L19:N19"/>
-    <mergeCell ref="L21:N21"/>
-    <mergeCell ref="L22:N22"/>
-    <mergeCell ref="L23:N23"/>
-    <mergeCell ref="L24:N24"/>
-    <mergeCell ref="L25:N25"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="J30:K30"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="J29:K29"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="G23:I23"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="J18:K18"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="J19:K19"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <hyperlinks>
@@ -20672,72 +20696,72 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="18.75" customHeight="1">
-      <c r="A1" s="245" t="s">
+      <c r="A1" s="238" t="s">
         <v>123</v>
       </c>
-      <c r="B1" s="245"/>
-      <c r="C1" s="246" t="s">
+      <c r="B1" s="238"/>
+      <c r="C1" s="239" t="s">
         <v>124</v>
       </c>
-      <c r="D1" s="247"/>
-      <c r="E1" s="248"/>
-      <c r="F1" s="249" t="s">
+      <c r="D1" s="240"/>
+      <c r="E1" s="241"/>
+      <c r="F1" s="242" t="s">
         <v>84</v>
       </c>
-      <c r="G1" s="250"/>
-      <c r="H1" s="250"/>
-      <c r="I1" s="250"/>
-      <c r="J1" s="250"/>
-      <c r="K1" s="250"/>
-      <c r="L1" s="250"/>
-      <c r="M1" s="251"/>
+      <c r="G1" s="243"/>
+      <c r="H1" s="243"/>
+      <c r="I1" s="243"/>
+      <c r="J1" s="243"/>
+      <c r="K1" s="243"/>
+      <c r="L1" s="243"/>
+      <c r="M1" s="244"/>
       <c r="N1" s="51" t="s">
         <v>125</v>
       </c>
-      <c r="O1" s="249" t="s">
+      <c r="O1" s="242" t="s">
         <v>83</v>
       </c>
-      <c r="P1" s="251"/>
+      <c r="P1" s="244"/>
       <c r="Q1" s="51" t="s">
         <v>126</v>
       </c>
-      <c r="R1" s="249" t="s">
+      <c r="R1" s="242" t="s">
         <v>127</v>
       </c>
-      <c r="S1" s="251"/>
+      <c r="S1" s="244"/>
     </row>
     <row r="2" spans="1:19" ht="18.75" customHeight="1">
-      <c r="A2" s="245"/>
-      <c r="B2" s="245"/>
-      <c r="C2" s="246" t="s">
+      <c r="A2" s="238"/>
+      <c r="B2" s="238"/>
+      <c r="C2" s="239" t="s">
         <v>128</v>
       </c>
-      <c r="D2" s="247"/>
-      <c r="E2" s="248"/>
-      <c r="F2" s="249" t="s">
+      <c r="D2" s="240"/>
+      <c r="E2" s="241"/>
+      <c r="F2" s="242" t="s">
         <v>147</v>
       </c>
-      <c r="G2" s="250"/>
-      <c r="H2" s="250"/>
-      <c r="I2" s="250"/>
-      <c r="J2" s="250"/>
-      <c r="K2" s="250"/>
-      <c r="L2" s="250"/>
-      <c r="M2" s="251"/>
+      <c r="G2" s="243"/>
+      <c r="H2" s="243"/>
+      <c r="I2" s="243"/>
+      <c r="J2" s="243"/>
+      <c r="K2" s="243"/>
+      <c r="L2" s="243"/>
+      <c r="M2" s="244"/>
       <c r="N2" s="51" t="s">
         <v>129</v>
       </c>
-      <c r="O2" s="252">
+      <c r="O2" s="245">
         <v>45824</v>
       </c>
-      <c r="P2" s="253"/>
+      <c r="P2" s="246"/>
       <c r="Q2" s="53" t="s">
         <v>130</v>
       </c>
-      <c r="R2" s="254">
+      <c r="R2" s="247">
         <v>44771</v>
       </c>
-      <c r="S2" s="255"/>
+      <c r="S2" s="248"/>
     </row>
     <row r="3" spans="1:19" ht="11.25" customHeight="1">
       <c r="A3" s="54"/>
@@ -20767,33 +20791,33 @@
       <c r="B4" s="57" t="s">
         <v>132</v>
       </c>
-      <c r="C4" s="237" t="s">
+      <c r="C4" s="229" t="s">
         <v>133</v>
       </c>
-      <c r="D4" s="238"/>
-      <c r="E4" s="238"/>
-      <c r="F4" s="238"/>
-      <c r="G4" s="239"/>
-      <c r="H4" s="237" t="s">
+      <c r="D4" s="230"/>
+      <c r="E4" s="230"/>
+      <c r="F4" s="230"/>
+      <c r="G4" s="231"/>
+      <c r="H4" s="229" t="s">
         <v>134</v>
       </c>
-      <c r="I4" s="238"/>
-      <c r="J4" s="238"/>
-      <c r="K4" s="238"/>
-      <c r="L4" s="238"/>
-      <c r="M4" s="239"/>
-      <c r="N4" s="237" t="s">
+      <c r="I4" s="230"/>
+      <c r="J4" s="230"/>
+      <c r="K4" s="230"/>
+      <c r="L4" s="230"/>
+      <c r="M4" s="231"/>
+      <c r="N4" s="229" t="s">
         <v>135</v>
       </c>
-      <c r="O4" s="238"/>
-      <c r="P4" s="239"/>
+      <c r="O4" s="230"/>
+      <c r="P4" s="231"/>
       <c r="Q4" s="56" t="s">
         <v>136</v>
       </c>
-      <c r="R4" s="237" t="s">
+      <c r="R4" s="229" t="s">
         <v>137</v>
       </c>
-      <c r="S4" s="239"/>
+      <c r="S4" s="231"/>
     </row>
     <row r="5" spans="1:19" ht="50.1" customHeight="1">
       <c r="A5" s="58">
@@ -20802,31 +20826,31 @@
       <c r="B5" s="59" t="s">
         <v>148</v>
       </c>
-      <c r="C5" s="233" t="s">
+      <c r="C5" s="232" t="s">
         <v>150</v>
       </c>
-      <c r="D5" s="233"/>
-      <c r="E5" s="233"/>
-      <c r="F5" s="233"/>
-      <c r="G5" s="233"/>
-      <c r="H5" s="233" t="s">
+      <c r="D5" s="232"/>
+      <c r="E5" s="232"/>
+      <c r="F5" s="232"/>
+      <c r="G5" s="232"/>
+      <c r="H5" s="232" t="s">
         <v>149</v>
       </c>
-      <c r="I5" s="233"/>
-      <c r="J5" s="233"/>
-      <c r="K5" s="233"/>
-      <c r="L5" s="233"/>
-      <c r="M5" s="233"/>
-      <c r="N5" s="240" t="s">
+      <c r="I5" s="232"/>
+      <c r="J5" s="232"/>
+      <c r="K5" s="232"/>
+      <c r="L5" s="232"/>
+      <c r="M5" s="232"/>
+      <c r="N5" s="233" t="s">
         <v>151</v>
       </c>
-      <c r="O5" s="241"/>
-      <c r="P5" s="242"/>
+      <c r="O5" s="234"/>
+      <c r="P5" s="235"/>
       <c r="Q5" s="64">
         <v>45824</v>
       </c>
-      <c r="R5" s="243"/>
-      <c r="S5" s="244"/>
+      <c r="R5" s="236"/>
+      <c r="S5" s="237"/>
     </row>
     <row r="6" spans="1:19" ht="30" customHeight="1">
       <c r="A6" s="60">
@@ -20835,31 +20859,31 @@
       <c r="B6" s="59" t="s">
         <v>148</v>
       </c>
-      <c r="C6" s="233" t="s">
+      <c r="C6" s="232" t="s">
         <v>150</v>
       </c>
-      <c r="D6" s="233"/>
-      <c r="E6" s="233"/>
-      <c r="F6" s="233"/>
-      <c r="G6" s="233"/>
-      <c r="H6" s="233" t="s">
+      <c r="D6" s="232"/>
+      <c r="E6" s="232"/>
+      <c r="F6" s="232"/>
+      <c r="G6" s="232"/>
+      <c r="H6" s="232" t="s">
         <v>149</v>
       </c>
-      <c r="I6" s="233"/>
-      <c r="J6" s="233"/>
-      <c r="K6" s="233"/>
-      <c r="L6" s="233"/>
-      <c r="M6" s="233"/>
-      <c r="N6" s="234" t="s">
+      <c r="I6" s="232"/>
+      <c r="J6" s="232"/>
+      <c r="K6" s="232"/>
+      <c r="L6" s="232"/>
+      <c r="M6" s="232"/>
+      <c r="N6" s="254" t="s">
         <v>152</v>
       </c>
-      <c r="O6" s="235"/>
-      <c r="P6" s="236"/>
+      <c r="O6" s="255"/>
+      <c r="P6" s="256"/>
       <c r="Q6" s="64">
         <v>45824</v>
       </c>
-      <c r="R6" s="232"/>
-      <c r="S6" s="232"/>
+      <c r="R6" s="253"/>
+      <c r="S6" s="253"/>
     </row>
     <row r="7" spans="1:19" ht="30" customHeight="1">
       <c r="A7" s="60">
@@ -20868,979 +20892,1167 @@
       <c r="B7" s="63" t="s">
         <v>118</v>
       </c>
-      <c r="C7" s="233" t="s">
+      <c r="C7" s="232" t="s">
         <v>150</v>
       </c>
-      <c r="D7" s="233"/>
-      <c r="E7" s="233"/>
-      <c r="F7" s="233"/>
-      <c r="G7" s="233"/>
-      <c r="H7" s="233" t="s">
+      <c r="D7" s="232"/>
+      <c r="E7" s="232"/>
+      <c r="F7" s="232"/>
+      <c r="G7" s="232"/>
+      <c r="H7" s="232" t="s">
         <v>149</v>
       </c>
-      <c r="I7" s="233"/>
-      <c r="J7" s="233"/>
-      <c r="K7" s="233"/>
-      <c r="L7" s="233"/>
-      <c r="M7" s="233"/>
-      <c r="N7" s="229" t="s">
+      <c r="I7" s="232"/>
+      <c r="J7" s="232"/>
+      <c r="K7" s="232"/>
+      <c r="L7" s="232"/>
+      <c r="M7" s="232"/>
+      <c r="N7" s="250" t="s">
         <v>153</v>
       </c>
-      <c r="O7" s="230"/>
-      <c r="P7" s="231"/>
+      <c r="O7" s="251"/>
+      <c r="P7" s="252"/>
       <c r="Q7" s="64">
         <v>45824</v>
       </c>
-      <c r="R7" s="232"/>
-      <c r="S7" s="232"/>
+      <c r="R7" s="253"/>
+      <c r="S7" s="253"/>
     </row>
     <row r="8" spans="1:19" ht="30" customHeight="1">
       <c r="A8" s="60"/>
       <c r="B8" s="60"/>
-      <c r="C8" s="225"/>
-      <c r="D8" s="225"/>
-      <c r="E8" s="225"/>
-      <c r="F8" s="225"/>
-      <c r="G8" s="225"/>
-      <c r="H8" s="225"/>
-      <c r="I8" s="225"/>
-      <c r="J8" s="225"/>
-      <c r="K8" s="225"/>
-      <c r="L8" s="225"/>
-      <c r="M8" s="225"/>
-      <c r="N8" s="229"/>
-      <c r="O8" s="230"/>
-      <c r="P8" s="231"/>
+      <c r="C8" s="249"/>
+      <c r="D8" s="249"/>
+      <c r="E8" s="249"/>
+      <c r="F8" s="249"/>
+      <c r="G8" s="249"/>
+      <c r="H8" s="249"/>
+      <c r="I8" s="249"/>
+      <c r="J8" s="249"/>
+      <c r="K8" s="249"/>
+      <c r="L8" s="249"/>
+      <c r="M8" s="249"/>
+      <c r="N8" s="250"/>
+      <c r="O8" s="251"/>
+      <c r="P8" s="252"/>
       <c r="Q8" s="61"/>
-      <c r="R8" s="232"/>
-      <c r="S8" s="232"/>
+      <c r="R8" s="253"/>
+      <c r="S8" s="253"/>
     </row>
     <row r="9" spans="1:19" ht="30" customHeight="1">
       <c r="A9" s="60"/>
       <c r="B9" s="60"/>
-      <c r="C9" s="225"/>
-      <c r="D9" s="225"/>
-      <c r="E9" s="225"/>
-      <c r="F9" s="225"/>
-      <c r="G9" s="225"/>
-      <c r="H9" s="225"/>
-      <c r="I9" s="225"/>
-      <c r="J9" s="225"/>
-      <c r="K9" s="225"/>
-      <c r="L9" s="225"/>
-      <c r="M9" s="225"/>
-      <c r="N9" s="229"/>
-      <c r="O9" s="230"/>
-      <c r="P9" s="231"/>
+      <c r="C9" s="249"/>
+      <c r="D9" s="249"/>
+      <c r="E9" s="249"/>
+      <c r="F9" s="249"/>
+      <c r="G9" s="249"/>
+      <c r="H9" s="249"/>
+      <c r="I9" s="249"/>
+      <c r="J9" s="249"/>
+      <c r="K9" s="249"/>
+      <c r="L9" s="249"/>
+      <c r="M9" s="249"/>
+      <c r="N9" s="250"/>
+      <c r="O9" s="251"/>
+      <c r="P9" s="252"/>
       <c r="Q9" s="60"/>
-      <c r="R9" s="232"/>
-      <c r="S9" s="232"/>
+      <c r="R9" s="253"/>
+      <c r="S9" s="253"/>
     </row>
     <row r="10" spans="1:19" ht="30" customHeight="1">
       <c r="A10" s="60"/>
       <c r="B10" s="60"/>
-      <c r="C10" s="225"/>
-      <c r="D10" s="225"/>
-      <c r="E10" s="225"/>
-      <c r="F10" s="225"/>
-      <c r="G10" s="225"/>
-      <c r="H10" s="226"/>
-      <c r="I10" s="227"/>
-      <c r="J10" s="227"/>
-      <c r="K10" s="227"/>
-      <c r="L10" s="227"/>
-      <c r="M10" s="228"/>
-      <c r="N10" s="229"/>
-      <c r="O10" s="230"/>
-      <c r="P10" s="231"/>
+      <c r="C10" s="249"/>
+      <c r="D10" s="249"/>
+      <c r="E10" s="249"/>
+      <c r="F10" s="249"/>
+      <c r="G10" s="249"/>
+      <c r="H10" s="257"/>
+      <c r="I10" s="258"/>
+      <c r="J10" s="258"/>
+      <c r="K10" s="258"/>
+      <c r="L10" s="258"/>
+      <c r="M10" s="259"/>
+      <c r="N10" s="250"/>
+      <c r="O10" s="251"/>
+      <c r="P10" s="252"/>
       <c r="Q10" s="61"/>
-      <c r="R10" s="232"/>
-      <c r="S10" s="232"/>
+      <c r="R10" s="253"/>
+      <c r="S10" s="253"/>
     </row>
     <row r="11" spans="1:19" ht="30" customHeight="1">
       <c r="A11" s="60"/>
       <c r="B11" s="60"/>
-      <c r="C11" s="225"/>
-      <c r="D11" s="225"/>
-      <c r="E11" s="225"/>
-      <c r="F11" s="225"/>
-      <c r="G11" s="225"/>
-      <c r="H11" s="226"/>
-      <c r="I11" s="227"/>
-      <c r="J11" s="227"/>
-      <c r="K11" s="227"/>
-      <c r="L11" s="227"/>
-      <c r="M11" s="228"/>
-      <c r="N11" s="229"/>
-      <c r="O11" s="230"/>
-      <c r="P11" s="231"/>
+      <c r="C11" s="249"/>
+      <c r="D11" s="249"/>
+      <c r="E11" s="249"/>
+      <c r="F11" s="249"/>
+      <c r="G11" s="249"/>
+      <c r="H11" s="257"/>
+      <c r="I11" s="258"/>
+      <c r="J11" s="258"/>
+      <c r="K11" s="258"/>
+      <c r="L11" s="258"/>
+      <c r="M11" s="259"/>
+      <c r="N11" s="250"/>
+      <c r="O11" s="251"/>
+      <c r="P11" s="252"/>
       <c r="Q11" s="60"/>
-      <c r="R11" s="232"/>
-      <c r="S11" s="232"/>
+      <c r="R11" s="253"/>
+      <c r="S11" s="253"/>
     </row>
     <row r="12" spans="1:19" ht="30" customHeight="1">
       <c r="A12" s="60"/>
       <c r="B12" s="60"/>
-      <c r="C12" s="225"/>
-      <c r="D12" s="225"/>
-      <c r="E12" s="225"/>
-      <c r="F12" s="225"/>
-      <c r="G12" s="225"/>
-      <c r="H12" s="226"/>
-      <c r="I12" s="227"/>
-      <c r="J12" s="227"/>
-      <c r="K12" s="227"/>
-      <c r="L12" s="227"/>
-      <c r="M12" s="228"/>
-      <c r="N12" s="229"/>
-      <c r="O12" s="230"/>
-      <c r="P12" s="231"/>
+      <c r="C12" s="249"/>
+      <c r="D12" s="249"/>
+      <c r="E12" s="249"/>
+      <c r="F12" s="249"/>
+      <c r="G12" s="249"/>
+      <c r="H12" s="257"/>
+      <c r="I12" s="258"/>
+      <c r="J12" s="258"/>
+      <c r="K12" s="258"/>
+      <c r="L12" s="258"/>
+      <c r="M12" s="259"/>
+      <c r="N12" s="250"/>
+      <c r="O12" s="251"/>
+      <c r="P12" s="252"/>
       <c r="Q12" s="60"/>
-      <c r="R12" s="232"/>
-      <c r="S12" s="232"/>
+      <c r="R12" s="253"/>
+      <c r="S12" s="253"/>
     </row>
     <row r="13" spans="1:19" ht="30" customHeight="1">
       <c r="A13" s="60"/>
       <c r="B13" s="60"/>
-      <c r="C13" s="225"/>
-      <c r="D13" s="225"/>
-      <c r="E13" s="225"/>
-      <c r="F13" s="225"/>
-      <c r="G13" s="225"/>
-      <c r="H13" s="226"/>
-      <c r="I13" s="227"/>
-      <c r="J13" s="227"/>
-      <c r="K13" s="227"/>
-      <c r="L13" s="227"/>
-      <c r="M13" s="228"/>
-      <c r="N13" s="229"/>
-      <c r="O13" s="230"/>
-      <c r="P13" s="231"/>
+      <c r="C13" s="249"/>
+      <c r="D13" s="249"/>
+      <c r="E13" s="249"/>
+      <c r="F13" s="249"/>
+      <c r="G13" s="249"/>
+      <c r="H13" s="257"/>
+      <c r="I13" s="258"/>
+      <c r="J13" s="258"/>
+      <c r="K13" s="258"/>
+      <c r="L13" s="258"/>
+      <c r="M13" s="259"/>
+      <c r="N13" s="250"/>
+      <c r="O13" s="251"/>
+      <c r="P13" s="252"/>
       <c r="Q13" s="60"/>
-      <c r="R13" s="232"/>
-      <c r="S13" s="232"/>
+      <c r="R13" s="253"/>
+      <c r="S13" s="253"/>
     </row>
     <row r="14" spans="1:19" ht="30" customHeight="1">
       <c r="A14" s="60"/>
       <c r="B14" s="60"/>
-      <c r="C14" s="225"/>
-      <c r="D14" s="225"/>
-      <c r="E14" s="225"/>
-      <c r="F14" s="225"/>
-      <c r="G14" s="225"/>
-      <c r="H14" s="226"/>
-      <c r="I14" s="227"/>
-      <c r="J14" s="227"/>
-      <c r="K14" s="227"/>
-      <c r="L14" s="227"/>
-      <c r="M14" s="228"/>
-      <c r="N14" s="229"/>
-      <c r="O14" s="230"/>
-      <c r="P14" s="231"/>
+      <c r="C14" s="249"/>
+      <c r="D14" s="249"/>
+      <c r="E14" s="249"/>
+      <c r="F14" s="249"/>
+      <c r="G14" s="249"/>
+      <c r="H14" s="257"/>
+      <c r="I14" s="258"/>
+      <c r="J14" s="258"/>
+      <c r="K14" s="258"/>
+      <c r="L14" s="258"/>
+      <c r="M14" s="259"/>
+      <c r="N14" s="250"/>
+      <c r="O14" s="251"/>
+      <c r="P14" s="252"/>
       <c r="Q14" s="60"/>
-      <c r="R14" s="232"/>
-      <c r="S14" s="232"/>
+      <c r="R14" s="253"/>
+      <c r="S14" s="253"/>
     </row>
     <row r="15" spans="1:19" ht="30" customHeight="1">
       <c r="A15" s="60"/>
       <c r="B15" s="60"/>
-      <c r="C15" s="225"/>
-      <c r="D15" s="225"/>
-      <c r="E15" s="225"/>
-      <c r="F15" s="225"/>
-      <c r="G15" s="225"/>
-      <c r="H15" s="226"/>
-      <c r="I15" s="227"/>
-      <c r="J15" s="227"/>
-      <c r="K15" s="227"/>
-      <c r="L15" s="227"/>
-      <c r="M15" s="228"/>
-      <c r="N15" s="229"/>
-      <c r="O15" s="230"/>
-      <c r="P15" s="231"/>
+      <c r="C15" s="249"/>
+      <c r="D15" s="249"/>
+      <c r="E15" s="249"/>
+      <c r="F15" s="249"/>
+      <c r="G15" s="249"/>
+      <c r="H15" s="257"/>
+      <c r="I15" s="258"/>
+      <c r="J15" s="258"/>
+      <c r="K15" s="258"/>
+      <c r="L15" s="258"/>
+      <c r="M15" s="259"/>
+      <c r="N15" s="250"/>
+      <c r="O15" s="251"/>
+      <c r="P15" s="252"/>
       <c r="Q15" s="60"/>
-      <c r="R15" s="232"/>
-      <c r="S15" s="232"/>
+      <c r="R15" s="253"/>
+      <c r="S15" s="253"/>
     </row>
     <row r="16" spans="1:19" ht="30" customHeight="1">
       <c r="A16" s="60"/>
       <c r="B16" s="60"/>
-      <c r="C16" s="225"/>
-      <c r="D16" s="225"/>
-      <c r="E16" s="225"/>
-      <c r="F16" s="225"/>
-      <c r="G16" s="225"/>
-      <c r="H16" s="226"/>
-      <c r="I16" s="227"/>
-      <c r="J16" s="227"/>
-      <c r="K16" s="227"/>
-      <c r="L16" s="227"/>
-      <c r="M16" s="228"/>
-      <c r="N16" s="229"/>
-      <c r="O16" s="230"/>
-      <c r="P16" s="231"/>
+      <c r="C16" s="249"/>
+      <c r="D16" s="249"/>
+      <c r="E16" s="249"/>
+      <c r="F16" s="249"/>
+      <c r="G16" s="249"/>
+      <c r="H16" s="257"/>
+      <c r="I16" s="258"/>
+      <c r="J16" s="258"/>
+      <c r="K16" s="258"/>
+      <c r="L16" s="258"/>
+      <c r="M16" s="259"/>
+      <c r="N16" s="250"/>
+      <c r="O16" s="251"/>
+      <c r="P16" s="252"/>
       <c r="Q16" s="60"/>
-      <c r="R16" s="232"/>
-      <c r="S16" s="232"/>
+      <c r="R16" s="253"/>
+      <c r="S16" s="253"/>
     </row>
     <row r="17" spans="1:19" ht="30" customHeight="1">
       <c r="A17" s="60"/>
       <c r="B17" s="60"/>
-      <c r="C17" s="225"/>
-      <c r="D17" s="225"/>
-      <c r="E17" s="225"/>
-      <c r="F17" s="225"/>
-      <c r="G17" s="225"/>
-      <c r="H17" s="226"/>
-      <c r="I17" s="227"/>
-      <c r="J17" s="227"/>
-      <c r="K17" s="227"/>
-      <c r="L17" s="227"/>
-      <c r="M17" s="228"/>
-      <c r="N17" s="229"/>
-      <c r="O17" s="230"/>
-      <c r="P17" s="231"/>
+      <c r="C17" s="249"/>
+      <c r="D17" s="249"/>
+      <c r="E17" s="249"/>
+      <c r="F17" s="249"/>
+      <c r="G17" s="249"/>
+      <c r="H17" s="257"/>
+      <c r="I17" s="258"/>
+      <c r="J17" s="258"/>
+      <c r="K17" s="258"/>
+      <c r="L17" s="258"/>
+      <c r="M17" s="259"/>
+      <c r="N17" s="250"/>
+      <c r="O17" s="251"/>
+      <c r="P17" s="252"/>
       <c r="Q17" s="60"/>
-      <c r="R17" s="232"/>
-      <c r="S17" s="232"/>
+      <c r="R17" s="253"/>
+      <c r="S17" s="253"/>
     </row>
     <row r="18" spans="1:19" ht="30" customHeight="1">
       <c r="A18" s="60"/>
       <c r="B18" s="60"/>
-      <c r="C18" s="225"/>
-      <c r="D18" s="225"/>
-      <c r="E18" s="225"/>
-      <c r="F18" s="225"/>
-      <c r="G18" s="225"/>
-      <c r="H18" s="226"/>
-      <c r="I18" s="227"/>
-      <c r="J18" s="227"/>
-      <c r="K18" s="227"/>
-      <c r="L18" s="227"/>
-      <c r="M18" s="228"/>
-      <c r="N18" s="229"/>
-      <c r="O18" s="230"/>
-      <c r="P18" s="231"/>
+      <c r="C18" s="249"/>
+      <c r="D18" s="249"/>
+      <c r="E18" s="249"/>
+      <c r="F18" s="249"/>
+      <c r="G18" s="249"/>
+      <c r="H18" s="257"/>
+      <c r="I18" s="258"/>
+      <c r="J18" s="258"/>
+      <c r="K18" s="258"/>
+      <c r="L18" s="258"/>
+      <c r="M18" s="259"/>
+      <c r="N18" s="250"/>
+      <c r="O18" s="251"/>
+      <c r="P18" s="252"/>
       <c r="Q18" s="60"/>
-      <c r="R18" s="232"/>
-      <c r="S18" s="232"/>
+      <c r="R18" s="253"/>
+      <c r="S18" s="253"/>
     </row>
     <row r="19" spans="1:19" ht="30" customHeight="1">
       <c r="A19" s="60"/>
       <c r="B19" s="60"/>
-      <c r="C19" s="225"/>
-      <c r="D19" s="225"/>
-      <c r="E19" s="225"/>
-      <c r="F19" s="225"/>
-      <c r="G19" s="225"/>
-      <c r="H19" s="226"/>
-      <c r="I19" s="227"/>
-      <c r="J19" s="227"/>
-      <c r="K19" s="227"/>
-      <c r="L19" s="227"/>
-      <c r="M19" s="228"/>
-      <c r="N19" s="229"/>
-      <c r="O19" s="230"/>
-      <c r="P19" s="231"/>
+      <c r="C19" s="249"/>
+      <c r="D19" s="249"/>
+      <c r="E19" s="249"/>
+      <c r="F19" s="249"/>
+      <c r="G19" s="249"/>
+      <c r="H19" s="257"/>
+      <c r="I19" s="258"/>
+      <c r="J19" s="258"/>
+      <c r="K19" s="258"/>
+      <c r="L19" s="258"/>
+      <c r="M19" s="259"/>
+      <c r="N19" s="250"/>
+      <c r="O19" s="251"/>
+      <c r="P19" s="252"/>
       <c r="Q19" s="60"/>
-      <c r="R19" s="232"/>
-      <c r="S19" s="232"/>
+      <c r="R19" s="253"/>
+      <c r="S19" s="253"/>
     </row>
     <row r="20" spans="1:19" ht="30" customHeight="1">
       <c r="A20" s="60"/>
       <c r="B20" s="60"/>
-      <c r="C20" s="225"/>
-      <c r="D20" s="225"/>
-      <c r="E20" s="225"/>
-      <c r="F20" s="225"/>
-      <c r="G20" s="225"/>
-      <c r="H20" s="226"/>
-      <c r="I20" s="227"/>
-      <c r="J20" s="227"/>
-      <c r="K20" s="227"/>
-      <c r="L20" s="227"/>
-      <c r="M20" s="228"/>
-      <c r="N20" s="229"/>
-      <c r="O20" s="230"/>
-      <c r="P20" s="231"/>
+      <c r="C20" s="249"/>
+      <c r="D20" s="249"/>
+      <c r="E20" s="249"/>
+      <c r="F20" s="249"/>
+      <c r="G20" s="249"/>
+      <c r="H20" s="257"/>
+      <c r="I20" s="258"/>
+      <c r="J20" s="258"/>
+      <c r="K20" s="258"/>
+      <c r="L20" s="258"/>
+      <c r="M20" s="259"/>
+      <c r="N20" s="250"/>
+      <c r="O20" s="251"/>
+      <c r="P20" s="252"/>
       <c r="Q20" s="60"/>
-      <c r="R20" s="232"/>
-      <c r="S20" s="232"/>
+      <c r="R20" s="253"/>
+      <c r="S20" s="253"/>
     </row>
     <row r="21" spans="1:19" ht="30" customHeight="1">
       <c r="A21" s="60"/>
       <c r="B21" s="60"/>
-      <c r="C21" s="225"/>
-      <c r="D21" s="225"/>
-      <c r="E21" s="225"/>
-      <c r="F21" s="225"/>
-      <c r="G21" s="225"/>
-      <c r="H21" s="226"/>
-      <c r="I21" s="227"/>
-      <c r="J21" s="227"/>
-      <c r="K21" s="227"/>
-      <c r="L21" s="227"/>
-      <c r="M21" s="228"/>
-      <c r="N21" s="229"/>
-      <c r="O21" s="230"/>
-      <c r="P21" s="231"/>
+      <c r="C21" s="249"/>
+      <c r="D21" s="249"/>
+      <c r="E21" s="249"/>
+      <c r="F21" s="249"/>
+      <c r="G21" s="249"/>
+      <c r="H21" s="257"/>
+      <c r="I21" s="258"/>
+      <c r="J21" s="258"/>
+      <c r="K21" s="258"/>
+      <c r="L21" s="258"/>
+      <c r="M21" s="259"/>
+      <c r="N21" s="250"/>
+      <c r="O21" s="251"/>
+      <c r="P21" s="252"/>
       <c r="Q21" s="60"/>
-      <c r="R21" s="232"/>
-      <c r="S21" s="232"/>
+      <c r="R21" s="253"/>
+      <c r="S21" s="253"/>
     </row>
     <row r="22" spans="1:19" ht="30" customHeight="1">
       <c r="A22" s="60"/>
       <c r="B22" s="60"/>
-      <c r="C22" s="225"/>
-      <c r="D22" s="225"/>
-      <c r="E22" s="225"/>
-      <c r="F22" s="225"/>
-      <c r="G22" s="225"/>
-      <c r="H22" s="226"/>
-      <c r="I22" s="227"/>
-      <c r="J22" s="227"/>
-      <c r="K22" s="227"/>
-      <c r="L22" s="227"/>
-      <c r="M22" s="228"/>
-      <c r="N22" s="229"/>
-      <c r="O22" s="230"/>
-      <c r="P22" s="231"/>
+      <c r="C22" s="249"/>
+      <c r="D22" s="249"/>
+      <c r="E22" s="249"/>
+      <c r="F22" s="249"/>
+      <c r="G22" s="249"/>
+      <c r="H22" s="257"/>
+      <c r="I22" s="258"/>
+      <c r="J22" s="258"/>
+      <c r="K22" s="258"/>
+      <c r="L22" s="258"/>
+      <c r="M22" s="259"/>
+      <c r="N22" s="250"/>
+      <c r="O22" s="251"/>
+      <c r="P22" s="252"/>
       <c r="Q22" s="60"/>
-      <c r="R22" s="232"/>
-      <c r="S22" s="232"/>
+      <c r="R22" s="253"/>
+      <c r="S22" s="253"/>
     </row>
     <row r="23" spans="1:19" ht="30" customHeight="1">
       <c r="A23" s="60"/>
       <c r="B23" s="60"/>
-      <c r="C23" s="225"/>
-      <c r="D23" s="225"/>
-      <c r="E23" s="225"/>
-      <c r="F23" s="225"/>
-      <c r="G23" s="225"/>
-      <c r="H23" s="226"/>
-      <c r="I23" s="227"/>
-      <c r="J23" s="227"/>
-      <c r="K23" s="227"/>
-      <c r="L23" s="227"/>
-      <c r="M23" s="228"/>
-      <c r="N23" s="229"/>
-      <c r="O23" s="230"/>
-      <c r="P23" s="231"/>
+      <c r="C23" s="249"/>
+      <c r="D23" s="249"/>
+      <c r="E23" s="249"/>
+      <c r="F23" s="249"/>
+      <c r="G23" s="249"/>
+      <c r="H23" s="257"/>
+      <c r="I23" s="258"/>
+      <c r="J23" s="258"/>
+      <c r="K23" s="258"/>
+      <c r="L23" s="258"/>
+      <c r="M23" s="259"/>
+      <c r="N23" s="250"/>
+      <c r="O23" s="251"/>
+      <c r="P23" s="252"/>
       <c r="Q23" s="60"/>
-      <c r="R23" s="232"/>
-      <c r="S23" s="232"/>
+      <c r="R23" s="253"/>
+      <c r="S23" s="253"/>
     </row>
     <row r="24" spans="1:19" ht="30" customHeight="1">
       <c r="A24" s="60"/>
       <c r="B24" s="60"/>
-      <c r="C24" s="225"/>
-      <c r="D24" s="225"/>
-      <c r="E24" s="225"/>
-      <c r="F24" s="225"/>
-      <c r="G24" s="225"/>
-      <c r="H24" s="226"/>
-      <c r="I24" s="227"/>
-      <c r="J24" s="227"/>
-      <c r="K24" s="227"/>
-      <c r="L24" s="227"/>
-      <c r="M24" s="228"/>
-      <c r="N24" s="229"/>
-      <c r="O24" s="230"/>
-      <c r="P24" s="231"/>
+      <c r="C24" s="249"/>
+      <c r="D24" s="249"/>
+      <c r="E24" s="249"/>
+      <c r="F24" s="249"/>
+      <c r="G24" s="249"/>
+      <c r="H24" s="257"/>
+      <c r="I24" s="258"/>
+      <c r="J24" s="258"/>
+      <c r="K24" s="258"/>
+      <c r="L24" s="258"/>
+      <c r="M24" s="259"/>
+      <c r="N24" s="250"/>
+      <c r="O24" s="251"/>
+      <c r="P24" s="252"/>
       <c r="Q24" s="60"/>
-      <c r="R24" s="232"/>
-      <c r="S24" s="232"/>
+      <c r="R24" s="253"/>
+      <c r="S24" s="253"/>
     </row>
     <row r="25" spans="1:19" ht="30" customHeight="1">
       <c r="A25" s="60"/>
       <c r="B25" s="60"/>
-      <c r="C25" s="225"/>
-      <c r="D25" s="225"/>
-      <c r="E25" s="225"/>
-      <c r="F25" s="225"/>
-      <c r="G25" s="225"/>
-      <c r="H25" s="226"/>
-      <c r="I25" s="227"/>
-      <c r="J25" s="227"/>
-      <c r="K25" s="227"/>
-      <c r="L25" s="227"/>
-      <c r="M25" s="228"/>
-      <c r="N25" s="229"/>
-      <c r="O25" s="230"/>
-      <c r="P25" s="231"/>
+      <c r="C25" s="249"/>
+      <c r="D25" s="249"/>
+      <c r="E25" s="249"/>
+      <c r="F25" s="249"/>
+      <c r="G25" s="249"/>
+      <c r="H25" s="257"/>
+      <c r="I25" s="258"/>
+      <c r="J25" s="258"/>
+      <c r="K25" s="258"/>
+      <c r="L25" s="258"/>
+      <c r="M25" s="259"/>
+      <c r="N25" s="250"/>
+      <c r="O25" s="251"/>
+      <c r="P25" s="252"/>
       <c r="Q25" s="60"/>
-      <c r="R25" s="232"/>
-      <c r="S25" s="232"/>
+      <c r="R25" s="253"/>
+      <c r="S25" s="253"/>
     </row>
     <row r="26" spans="1:19" ht="30" customHeight="1">
       <c r="A26" s="60"/>
       <c r="B26" s="60"/>
-      <c r="C26" s="225"/>
-      <c r="D26" s="225"/>
-      <c r="E26" s="225"/>
-      <c r="F26" s="225"/>
-      <c r="G26" s="225"/>
-      <c r="H26" s="226"/>
-      <c r="I26" s="227"/>
-      <c r="J26" s="227"/>
-      <c r="K26" s="227"/>
-      <c r="L26" s="227"/>
-      <c r="M26" s="228"/>
-      <c r="N26" s="229"/>
-      <c r="O26" s="230"/>
-      <c r="P26" s="231"/>
+      <c r="C26" s="249"/>
+      <c r="D26" s="249"/>
+      <c r="E26" s="249"/>
+      <c r="F26" s="249"/>
+      <c r="G26" s="249"/>
+      <c r="H26" s="257"/>
+      <c r="I26" s="258"/>
+      <c r="J26" s="258"/>
+      <c r="K26" s="258"/>
+      <c r="L26" s="258"/>
+      <c r="M26" s="259"/>
+      <c r="N26" s="250"/>
+      <c r="O26" s="251"/>
+      <c r="P26" s="252"/>
       <c r="Q26" s="60"/>
-      <c r="R26" s="232"/>
-      <c r="S26" s="232"/>
+      <c r="R26" s="253"/>
+      <c r="S26" s="253"/>
     </row>
     <row r="27" spans="1:19" ht="30" customHeight="1">
       <c r="A27" s="60"/>
       <c r="B27" s="60"/>
-      <c r="C27" s="225"/>
-      <c r="D27" s="225"/>
-      <c r="E27" s="225"/>
-      <c r="F27" s="225"/>
-      <c r="G27" s="225"/>
-      <c r="H27" s="226"/>
-      <c r="I27" s="227"/>
-      <c r="J27" s="227"/>
-      <c r="K27" s="227"/>
-      <c r="L27" s="227"/>
-      <c r="M27" s="228"/>
-      <c r="N27" s="229"/>
-      <c r="O27" s="230"/>
-      <c r="P27" s="231"/>
+      <c r="C27" s="249"/>
+      <c r="D27" s="249"/>
+      <c r="E27" s="249"/>
+      <c r="F27" s="249"/>
+      <c r="G27" s="249"/>
+      <c r="H27" s="257"/>
+      <c r="I27" s="258"/>
+      <c r="J27" s="258"/>
+      <c r="K27" s="258"/>
+      <c r="L27" s="258"/>
+      <c r="M27" s="259"/>
+      <c r="N27" s="250"/>
+      <c r="O27" s="251"/>
+      <c r="P27" s="252"/>
       <c r="Q27" s="60"/>
-      <c r="R27" s="232"/>
-      <c r="S27" s="232"/>
+      <c r="R27" s="253"/>
+      <c r="S27" s="253"/>
     </row>
     <row r="28" spans="1:19" ht="30" customHeight="1">
       <c r="A28" s="60"/>
       <c r="B28" s="60"/>
-      <c r="C28" s="225"/>
-      <c r="D28" s="225"/>
-      <c r="E28" s="225"/>
-      <c r="F28" s="225"/>
-      <c r="G28" s="225"/>
-      <c r="H28" s="226"/>
-      <c r="I28" s="227"/>
-      <c r="J28" s="227"/>
-      <c r="K28" s="227"/>
-      <c r="L28" s="227"/>
-      <c r="M28" s="228"/>
-      <c r="N28" s="229"/>
-      <c r="O28" s="230"/>
-      <c r="P28" s="231"/>
+      <c r="C28" s="249"/>
+      <c r="D28" s="249"/>
+      <c r="E28" s="249"/>
+      <c r="F28" s="249"/>
+      <c r="G28" s="249"/>
+      <c r="H28" s="257"/>
+      <c r="I28" s="258"/>
+      <c r="J28" s="258"/>
+      <c r="K28" s="258"/>
+      <c r="L28" s="258"/>
+      <c r="M28" s="259"/>
+      <c r="N28" s="250"/>
+      <c r="O28" s="251"/>
+      <c r="P28" s="252"/>
       <c r="Q28" s="60"/>
-      <c r="R28" s="232"/>
-      <c r="S28" s="232"/>
+      <c r="R28" s="253"/>
+      <c r="S28" s="253"/>
     </row>
     <row r="29" spans="1:19" ht="30" customHeight="1">
       <c r="A29" s="60"/>
       <c r="B29" s="60"/>
-      <c r="C29" s="225"/>
-      <c r="D29" s="225"/>
-      <c r="E29" s="225"/>
-      <c r="F29" s="225"/>
-      <c r="G29" s="225"/>
-      <c r="H29" s="226"/>
-      <c r="I29" s="227"/>
-      <c r="J29" s="227"/>
-      <c r="K29" s="227"/>
-      <c r="L29" s="227"/>
-      <c r="M29" s="228"/>
-      <c r="N29" s="229"/>
-      <c r="O29" s="230"/>
-      <c r="P29" s="231"/>
+      <c r="C29" s="249"/>
+      <c r="D29" s="249"/>
+      <c r="E29" s="249"/>
+      <c r="F29" s="249"/>
+      <c r="G29" s="249"/>
+      <c r="H29" s="257"/>
+      <c r="I29" s="258"/>
+      <c r="J29" s="258"/>
+      <c r="K29" s="258"/>
+      <c r="L29" s="258"/>
+      <c r="M29" s="259"/>
+      <c r="N29" s="250"/>
+      <c r="O29" s="251"/>
+      <c r="P29" s="252"/>
       <c r="Q29" s="60"/>
-      <c r="R29" s="232"/>
-      <c r="S29" s="232"/>
+      <c r="R29" s="253"/>
+      <c r="S29" s="253"/>
     </row>
     <row r="30" spans="1:19" ht="30" customHeight="1">
       <c r="A30" s="60"/>
       <c r="B30" s="60"/>
-      <c r="C30" s="225"/>
-      <c r="D30" s="225"/>
-      <c r="E30" s="225"/>
-      <c r="F30" s="225"/>
-      <c r="G30" s="225"/>
-      <c r="H30" s="226"/>
-      <c r="I30" s="227"/>
-      <c r="J30" s="227"/>
-      <c r="K30" s="227"/>
-      <c r="L30" s="227"/>
-      <c r="M30" s="228"/>
-      <c r="N30" s="229"/>
-      <c r="O30" s="230"/>
-      <c r="P30" s="231"/>
+      <c r="C30" s="249"/>
+      <c r="D30" s="249"/>
+      <c r="E30" s="249"/>
+      <c r="F30" s="249"/>
+      <c r="G30" s="249"/>
+      <c r="H30" s="257"/>
+      <c r="I30" s="258"/>
+      <c r="J30" s="258"/>
+      <c r="K30" s="258"/>
+      <c r="L30" s="258"/>
+      <c r="M30" s="259"/>
+      <c r="N30" s="250"/>
+      <c r="O30" s="251"/>
+      <c r="P30" s="252"/>
       <c r="Q30" s="60"/>
-      <c r="R30" s="232"/>
-      <c r="S30" s="232"/>
+      <c r="R30" s="253"/>
+      <c r="S30" s="253"/>
     </row>
     <row r="31" spans="1:19" ht="30" customHeight="1">
       <c r="A31" s="60"/>
       <c r="B31" s="60"/>
-      <c r="C31" s="225"/>
-      <c r="D31" s="225"/>
-      <c r="E31" s="225"/>
-      <c r="F31" s="225"/>
-      <c r="G31" s="225"/>
-      <c r="H31" s="226"/>
-      <c r="I31" s="227"/>
-      <c r="J31" s="227"/>
-      <c r="K31" s="227"/>
-      <c r="L31" s="227"/>
-      <c r="M31" s="228"/>
-      <c r="N31" s="229"/>
-      <c r="O31" s="230"/>
-      <c r="P31" s="231"/>
+      <c r="C31" s="249"/>
+      <c r="D31" s="249"/>
+      <c r="E31" s="249"/>
+      <c r="F31" s="249"/>
+      <c r="G31" s="249"/>
+      <c r="H31" s="257"/>
+      <c r="I31" s="258"/>
+      <c r="J31" s="258"/>
+      <c r="K31" s="258"/>
+      <c r="L31" s="258"/>
+      <c r="M31" s="259"/>
+      <c r="N31" s="250"/>
+      <c r="O31" s="251"/>
+      <c r="P31" s="252"/>
       <c r="Q31" s="60"/>
-      <c r="R31" s="232"/>
-      <c r="S31" s="232"/>
+      <c r="R31" s="253"/>
+      <c r="S31" s="253"/>
     </row>
     <row r="32" spans="1:19" ht="30" customHeight="1">
       <c r="A32" s="60"/>
       <c r="B32" s="60"/>
-      <c r="C32" s="225"/>
-      <c r="D32" s="225"/>
-      <c r="E32" s="225"/>
-      <c r="F32" s="225"/>
-      <c r="G32" s="225"/>
-      <c r="H32" s="226"/>
-      <c r="I32" s="227"/>
-      <c r="J32" s="227"/>
-      <c r="K32" s="227"/>
-      <c r="L32" s="227"/>
-      <c r="M32" s="228"/>
-      <c r="N32" s="229"/>
-      <c r="O32" s="230"/>
-      <c r="P32" s="231"/>
+      <c r="C32" s="249"/>
+      <c r="D32" s="249"/>
+      <c r="E32" s="249"/>
+      <c r="F32" s="249"/>
+      <c r="G32" s="249"/>
+      <c r="H32" s="257"/>
+      <c r="I32" s="258"/>
+      <c r="J32" s="258"/>
+      <c r="K32" s="258"/>
+      <c r="L32" s="258"/>
+      <c r="M32" s="259"/>
+      <c r="N32" s="250"/>
+      <c r="O32" s="251"/>
+      <c r="P32" s="252"/>
       <c r="Q32" s="60"/>
-      <c r="R32" s="232"/>
-      <c r="S32" s="232"/>
+      <c r="R32" s="253"/>
+      <c r="S32" s="253"/>
     </row>
     <row r="33" spans="1:19" ht="30" customHeight="1">
       <c r="A33" s="60"/>
       <c r="B33" s="60"/>
-      <c r="C33" s="225"/>
-      <c r="D33" s="225"/>
-      <c r="E33" s="225"/>
-      <c r="F33" s="225"/>
-      <c r="G33" s="225"/>
-      <c r="H33" s="226"/>
-      <c r="I33" s="227"/>
-      <c r="J33" s="227"/>
-      <c r="K33" s="227"/>
-      <c r="L33" s="227"/>
-      <c r="M33" s="228"/>
-      <c r="N33" s="229"/>
-      <c r="O33" s="230"/>
-      <c r="P33" s="231"/>
+      <c r="C33" s="249"/>
+      <c r="D33" s="249"/>
+      <c r="E33" s="249"/>
+      <c r="F33" s="249"/>
+      <c r="G33" s="249"/>
+      <c r="H33" s="257"/>
+      <c r="I33" s="258"/>
+      <c r="J33" s="258"/>
+      <c r="K33" s="258"/>
+      <c r="L33" s="258"/>
+      <c r="M33" s="259"/>
+      <c r="N33" s="250"/>
+      <c r="O33" s="251"/>
+      <c r="P33" s="252"/>
       <c r="Q33" s="60"/>
-      <c r="R33" s="232"/>
-      <c r="S33" s="232"/>
+      <c r="R33" s="253"/>
+      <c r="S33" s="253"/>
     </row>
     <row r="34" spans="1:19" ht="30" customHeight="1">
       <c r="A34" s="60"/>
       <c r="B34" s="60"/>
-      <c r="C34" s="225"/>
-      <c r="D34" s="225"/>
-      <c r="E34" s="225"/>
-      <c r="F34" s="225"/>
-      <c r="G34" s="225"/>
-      <c r="H34" s="226"/>
-      <c r="I34" s="227"/>
-      <c r="J34" s="227"/>
-      <c r="K34" s="227"/>
-      <c r="L34" s="227"/>
-      <c r="M34" s="228"/>
-      <c r="N34" s="229"/>
-      <c r="O34" s="230"/>
-      <c r="P34" s="231"/>
+      <c r="C34" s="249"/>
+      <c r="D34" s="249"/>
+      <c r="E34" s="249"/>
+      <c r="F34" s="249"/>
+      <c r="G34" s="249"/>
+      <c r="H34" s="257"/>
+      <c r="I34" s="258"/>
+      <c r="J34" s="258"/>
+      <c r="K34" s="258"/>
+      <c r="L34" s="258"/>
+      <c r="M34" s="259"/>
+      <c r="N34" s="250"/>
+      <c r="O34" s="251"/>
+      <c r="P34" s="252"/>
       <c r="Q34" s="60"/>
-      <c r="R34" s="232"/>
-      <c r="S34" s="232"/>
+      <c r="R34" s="253"/>
+      <c r="S34" s="253"/>
     </row>
     <row r="35" spans="1:19" ht="30" customHeight="1">
       <c r="A35" s="60"/>
       <c r="B35" s="60"/>
-      <c r="C35" s="225"/>
-      <c r="D35" s="225"/>
-      <c r="E35" s="225"/>
-      <c r="F35" s="225"/>
-      <c r="G35" s="225"/>
-      <c r="H35" s="226"/>
-      <c r="I35" s="227"/>
-      <c r="J35" s="227"/>
-      <c r="K35" s="227"/>
-      <c r="L35" s="227"/>
-      <c r="M35" s="228"/>
-      <c r="N35" s="229"/>
-      <c r="O35" s="230"/>
-      <c r="P35" s="231"/>
+      <c r="C35" s="249"/>
+      <c r="D35" s="249"/>
+      <c r="E35" s="249"/>
+      <c r="F35" s="249"/>
+      <c r="G35" s="249"/>
+      <c r="H35" s="257"/>
+      <c r="I35" s="258"/>
+      <c r="J35" s="258"/>
+      <c r="K35" s="258"/>
+      <c r="L35" s="258"/>
+      <c r="M35" s="259"/>
+      <c r="N35" s="250"/>
+      <c r="O35" s="251"/>
+      <c r="P35" s="252"/>
       <c r="Q35" s="60"/>
-      <c r="R35" s="232"/>
-      <c r="S35" s="232"/>
+      <c r="R35" s="253"/>
+      <c r="S35" s="253"/>
     </row>
     <row r="36" spans="1:19" ht="30" customHeight="1">
       <c r="A36" s="60"/>
       <c r="B36" s="60"/>
-      <c r="C36" s="225"/>
-      <c r="D36" s="225"/>
-      <c r="E36" s="225"/>
-      <c r="F36" s="225"/>
-      <c r="G36" s="225"/>
-      <c r="H36" s="226"/>
-      <c r="I36" s="227"/>
-      <c r="J36" s="227"/>
-      <c r="K36" s="227"/>
-      <c r="L36" s="227"/>
-      <c r="M36" s="228"/>
-      <c r="N36" s="229"/>
-      <c r="O36" s="230"/>
-      <c r="P36" s="231"/>
+      <c r="C36" s="249"/>
+      <c r="D36" s="249"/>
+      <c r="E36" s="249"/>
+      <c r="F36" s="249"/>
+      <c r="G36" s="249"/>
+      <c r="H36" s="257"/>
+      <c r="I36" s="258"/>
+      <c r="J36" s="258"/>
+      <c r="K36" s="258"/>
+      <c r="L36" s="258"/>
+      <c r="M36" s="259"/>
+      <c r="N36" s="250"/>
+      <c r="O36" s="251"/>
+      <c r="P36" s="252"/>
       <c r="Q36" s="60"/>
-      <c r="R36" s="232"/>
-      <c r="S36" s="232"/>
+      <c r="R36" s="253"/>
+      <c r="S36" s="253"/>
     </row>
     <row r="37" spans="1:19" ht="30" customHeight="1">
       <c r="A37" s="60"/>
       <c r="B37" s="60"/>
-      <c r="C37" s="225"/>
-      <c r="D37" s="225"/>
-      <c r="E37" s="225"/>
-      <c r="F37" s="225"/>
-      <c r="G37" s="225"/>
-      <c r="H37" s="226"/>
-      <c r="I37" s="227"/>
-      <c r="J37" s="227"/>
-      <c r="K37" s="227"/>
-      <c r="L37" s="227"/>
-      <c r="M37" s="228"/>
-      <c r="N37" s="229"/>
-      <c r="O37" s="230"/>
-      <c r="P37" s="231"/>
+      <c r="C37" s="249"/>
+      <c r="D37" s="249"/>
+      <c r="E37" s="249"/>
+      <c r="F37" s="249"/>
+      <c r="G37" s="249"/>
+      <c r="H37" s="257"/>
+      <c r="I37" s="258"/>
+      <c r="J37" s="258"/>
+      <c r="K37" s="258"/>
+      <c r="L37" s="258"/>
+      <c r="M37" s="259"/>
+      <c r="N37" s="250"/>
+      <c r="O37" s="251"/>
+      <c r="P37" s="252"/>
       <c r="Q37" s="60"/>
-      <c r="R37" s="232"/>
-      <c r="S37" s="232"/>
+      <c r="R37" s="253"/>
+      <c r="S37" s="253"/>
     </row>
     <row r="38" spans="1:19" ht="30" customHeight="1">
       <c r="A38" s="60"/>
       <c r="B38" s="60"/>
-      <c r="C38" s="225"/>
-      <c r="D38" s="225"/>
-      <c r="E38" s="225"/>
-      <c r="F38" s="225"/>
-      <c r="G38" s="225"/>
-      <c r="H38" s="226"/>
-      <c r="I38" s="227"/>
-      <c r="J38" s="227"/>
-      <c r="K38" s="227"/>
-      <c r="L38" s="227"/>
-      <c r="M38" s="228"/>
-      <c r="N38" s="229"/>
-      <c r="O38" s="230"/>
-      <c r="P38" s="231"/>
+      <c r="C38" s="249"/>
+      <c r="D38" s="249"/>
+      <c r="E38" s="249"/>
+      <c r="F38" s="249"/>
+      <c r="G38" s="249"/>
+      <c r="H38" s="257"/>
+      <c r="I38" s="258"/>
+      <c r="J38" s="258"/>
+      <c r="K38" s="258"/>
+      <c r="L38" s="258"/>
+      <c r="M38" s="259"/>
+      <c r="N38" s="250"/>
+      <c r="O38" s="251"/>
+      <c r="P38" s="252"/>
       <c r="Q38" s="60"/>
-      <c r="R38" s="232"/>
-      <c r="S38" s="232"/>
+      <c r="R38" s="253"/>
+      <c r="S38" s="253"/>
     </row>
     <row r="39" spans="1:19" ht="30" customHeight="1">
       <c r="A39" s="60"/>
       <c r="B39" s="60"/>
-      <c r="C39" s="225"/>
-      <c r="D39" s="225"/>
-      <c r="E39" s="225"/>
-      <c r="F39" s="225"/>
-      <c r="G39" s="225"/>
-      <c r="H39" s="226"/>
-      <c r="I39" s="227"/>
-      <c r="J39" s="227"/>
-      <c r="K39" s="227"/>
-      <c r="L39" s="227"/>
-      <c r="M39" s="228"/>
-      <c r="N39" s="229"/>
-      <c r="O39" s="230"/>
-      <c r="P39" s="231"/>
+      <c r="C39" s="249"/>
+      <c r="D39" s="249"/>
+      <c r="E39" s="249"/>
+      <c r="F39" s="249"/>
+      <c r="G39" s="249"/>
+      <c r="H39" s="257"/>
+      <c r="I39" s="258"/>
+      <c r="J39" s="258"/>
+      <c r="K39" s="258"/>
+      <c r="L39" s="258"/>
+      <c r="M39" s="259"/>
+      <c r="N39" s="250"/>
+      <c r="O39" s="251"/>
+      <c r="P39" s="252"/>
       <c r="Q39" s="60"/>
-      <c r="R39" s="232"/>
-      <c r="S39" s="232"/>
+      <c r="R39" s="253"/>
+      <c r="S39" s="253"/>
     </row>
     <row r="40" spans="1:19" ht="30" customHeight="1">
       <c r="A40" s="60"/>
       <c r="B40" s="60"/>
-      <c r="C40" s="225"/>
-      <c r="D40" s="225"/>
-      <c r="E40" s="225"/>
-      <c r="F40" s="225"/>
-      <c r="G40" s="225"/>
-      <c r="H40" s="226"/>
-      <c r="I40" s="227"/>
-      <c r="J40" s="227"/>
-      <c r="K40" s="227"/>
-      <c r="L40" s="227"/>
-      <c r="M40" s="228"/>
-      <c r="N40" s="229"/>
-      <c r="O40" s="230"/>
-      <c r="P40" s="231"/>
+      <c r="C40" s="249"/>
+      <c r="D40" s="249"/>
+      <c r="E40" s="249"/>
+      <c r="F40" s="249"/>
+      <c r="G40" s="249"/>
+      <c r="H40" s="257"/>
+      <c r="I40" s="258"/>
+      <c r="J40" s="258"/>
+      <c r="K40" s="258"/>
+      <c r="L40" s="258"/>
+      <c r="M40" s="259"/>
+      <c r="N40" s="250"/>
+      <c r="O40" s="251"/>
+      <c r="P40" s="252"/>
       <c r="Q40" s="60"/>
-      <c r="R40" s="232"/>
-      <c r="S40" s="232"/>
+      <c r="R40" s="253"/>
+      <c r="S40" s="253"/>
     </row>
     <row r="41" spans="1:19" ht="30" customHeight="1">
       <c r="A41" s="60"/>
       <c r="B41" s="60"/>
-      <c r="C41" s="225"/>
-      <c r="D41" s="225"/>
-      <c r="E41" s="225"/>
-      <c r="F41" s="225"/>
-      <c r="G41" s="225"/>
-      <c r="H41" s="226"/>
-      <c r="I41" s="227"/>
-      <c r="J41" s="227"/>
-      <c r="K41" s="227"/>
-      <c r="L41" s="227"/>
-      <c r="M41" s="228"/>
-      <c r="N41" s="229"/>
-      <c r="O41" s="230"/>
-      <c r="P41" s="231"/>
+      <c r="C41" s="249"/>
+      <c r="D41" s="249"/>
+      <c r="E41" s="249"/>
+      <c r="F41" s="249"/>
+      <c r="G41" s="249"/>
+      <c r="H41" s="257"/>
+      <c r="I41" s="258"/>
+      <c r="J41" s="258"/>
+      <c r="K41" s="258"/>
+      <c r="L41" s="258"/>
+      <c r="M41" s="259"/>
+      <c r="N41" s="250"/>
+      <c r="O41" s="251"/>
+      <c r="P41" s="252"/>
       <c r="Q41" s="60"/>
-      <c r="R41" s="232"/>
-      <c r="S41" s="232"/>
+      <c r="R41" s="253"/>
+      <c r="S41" s="253"/>
     </row>
     <row r="42" spans="1:19" ht="30" customHeight="1">
       <c r="A42" s="60"/>
       <c r="B42" s="60"/>
-      <c r="C42" s="225"/>
-      <c r="D42" s="225"/>
-      <c r="E42" s="225"/>
-      <c r="F42" s="225"/>
-      <c r="G42" s="225"/>
-      <c r="H42" s="226"/>
-      <c r="I42" s="227"/>
-      <c r="J42" s="227"/>
-      <c r="K42" s="227"/>
-      <c r="L42" s="227"/>
-      <c r="M42" s="228"/>
-      <c r="N42" s="229"/>
-      <c r="O42" s="230"/>
-      <c r="P42" s="231"/>
+      <c r="C42" s="249"/>
+      <c r="D42" s="249"/>
+      <c r="E42" s="249"/>
+      <c r="F42" s="249"/>
+      <c r="G42" s="249"/>
+      <c r="H42" s="257"/>
+      <c r="I42" s="258"/>
+      <c r="J42" s="258"/>
+      <c r="K42" s="258"/>
+      <c r="L42" s="258"/>
+      <c r="M42" s="259"/>
+      <c r="N42" s="250"/>
+      <c r="O42" s="251"/>
+      <c r="P42" s="252"/>
       <c r="Q42" s="60"/>
-      <c r="R42" s="232"/>
-      <c r="S42" s="232"/>
+      <c r="R42" s="253"/>
+      <c r="S42" s="253"/>
     </row>
     <row r="43" spans="1:19" ht="30" customHeight="1">
       <c r="A43" s="60"/>
       <c r="B43" s="60"/>
-      <c r="C43" s="225"/>
-      <c r="D43" s="225"/>
-      <c r="E43" s="225"/>
-      <c r="F43" s="225"/>
-      <c r="G43" s="225"/>
-      <c r="H43" s="226"/>
-      <c r="I43" s="227"/>
-      <c r="J43" s="227"/>
-      <c r="K43" s="227"/>
-      <c r="L43" s="227"/>
-      <c r="M43" s="228"/>
-      <c r="N43" s="229"/>
-      <c r="O43" s="230"/>
-      <c r="P43" s="231"/>
+      <c r="C43" s="249"/>
+      <c r="D43" s="249"/>
+      <c r="E43" s="249"/>
+      <c r="F43" s="249"/>
+      <c r="G43" s="249"/>
+      <c r="H43" s="257"/>
+      <c r="I43" s="258"/>
+      <c r="J43" s="258"/>
+      <c r="K43" s="258"/>
+      <c r="L43" s="258"/>
+      <c r="M43" s="259"/>
+      <c r="N43" s="250"/>
+      <c r="O43" s="251"/>
+      <c r="P43" s="252"/>
       <c r="Q43" s="60"/>
-      <c r="R43" s="232"/>
-      <c r="S43" s="232"/>
+      <c r="R43" s="253"/>
+      <c r="S43" s="253"/>
     </row>
     <row r="44" spans="1:19" ht="30" customHeight="1">
       <c r="A44" s="60"/>
       <c r="B44" s="60"/>
-      <c r="C44" s="225"/>
-      <c r="D44" s="225"/>
-      <c r="E44" s="225"/>
-      <c r="F44" s="225"/>
-      <c r="G44" s="225"/>
-      <c r="H44" s="226"/>
-      <c r="I44" s="227"/>
-      <c r="J44" s="227"/>
-      <c r="K44" s="227"/>
-      <c r="L44" s="227"/>
-      <c r="M44" s="228"/>
-      <c r="N44" s="229"/>
-      <c r="O44" s="230"/>
-      <c r="P44" s="231"/>
+      <c r="C44" s="249"/>
+      <c r="D44" s="249"/>
+      <c r="E44" s="249"/>
+      <c r="F44" s="249"/>
+      <c r="G44" s="249"/>
+      <c r="H44" s="257"/>
+      <c r="I44" s="258"/>
+      <c r="J44" s="258"/>
+      <c r="K44" s="258"/>
+      <c r="L44" s="258"/>
+      <c r="M44" s="259"/>
+      <c r="N44" s="250"/>
+      <c r="O44" s="251"/>
+      <c r="P44" s="252"/>
       <c r="Q44" s="60"/>
-      <c r="R44" s="232"/>
-      <c r="S44" s="232"/>
+      <c r="R44" s="253"/>
+      <c r="S44" s="253"/>
     </row>
     <row r="45" spans="1:19" ht="30" customHeight="1">
       <c r="A45" s="60"/>
       <c r="B45" s="60"/>
-      <c r="C45" s="225"/>
-      <c r="D45" s="225"/>
-      <c r="E45" s="225"/>
-      <c r="F45" s="225"/>
-      <c r="G45" s="225"/>
-      <c r="H45" s="226"/>
-      <c r="I45" s="227"/>
-      <c r="J45" s="227"/>
-      <c r="K45" s="227"/>
-      <c r="L45" s="227"/>
-      <c r="M45" s="228"/>
-      <c r="N45" s="229"/>
-      <c r="O45" s="230"/>
-      <c r="P45" s="231"/>
+      <c r="C45" s="249"/>
+      <c r="D45" s="249"/>
+      <c r="E45" s="249"/>
+      <c r="F45" s="249"/>
+      <c r="G45" s="249"/>
+      <c r="H45" s="257"/>
+      <c r="I45" s="258"/>
+      <c r="J45" s="258"/>
+      <c r="K45" s="258"/>
+      <c r="L45" s="258"/>
+      <c r="M45" s="259"/>
+      <c r="N45" s="250"/>
+      <c r="O45" s="251"/>
+      <c r="P45" s="252"/>
       <c r="Q45" s="60"/>
-      <c r="R45" s="232"/>
-      <c r="S45" s="232"/>
+      <c r="R45" s="253"/>
+      <c r="S45" s="253"/>
     </row>
     <row r="46" spans="1:19" ht="30" customHeight="1">
       <c r="A46" s="60"/>
       <c r="B46" s="60"/>
-      <c r="C46" s="225"/>
-      <c r="D46" s="225"/>
-      <c r="E46" s="225"/>
-      <c r="F46" s="225"/>
-      <c r="G46" s="225"/>
-      <c r="H46" s="226"/>
-      <c r="I46" s="227"/>
-      <c r="J46" s="227"/>
-      <c r="K46" s="227"/>
-      <c r="L46" s="227"/>
-      <c r="M46" s="228"/>
-      <c r="N46" s="229"/>
-      <c r="O46" s="230"/>
-      <c r="P46" s="231"/>
+      <c r="C46" s="249"/>
+      <c r="D46" s="249"/>
+      <c r="E46" s="249"/>
+      <c r="F46" s="249"/>
+      <c r="G46" s="249"/>
+      <c r="H46" s="257"/>
+      <c r="I46" s="258"/>
+      <c r="J46" s="258"/>
+      <c r="K46" s="258"/>
+      <c r="L46" s="258"/>
+      <c r="M46" s="259"/>
+      <c r="N46" s="250"/>
+      <c r="O46" s="251"/>
+      <c r="P46" s="252"/>
       <c r="Q46" s="60"/>
-      <c r="R46" s="232"/>
-      <c r="S46" s="232"/>
+      <c r="R46" s="253"/>
+      <c r="S46" s="253"/>
     </row>
     <row r="47" spans="1:19" ht="30" customHeight="1">
       <c r="A47" s="60"/>
       <c r="B47" s="60"/>
-      <c r="C47" s="225"/>
-      <c r="D47" s="225"/>
-      <c r="E47" s="225"/>
-      <c r="F47" s="225"/>
-      <c r="G47" s="225"/>
-      <c r="H47" s="226"/>
-      <c r="I47" s="227"/>
-      <c r="J47" s="227"/>
-      <c r="K47" s="227"/>
-      <c r="L47" s="227"/>
-      <c r="M47" s="228"/>
-      <c r="N47" s="229"/>
-      <c r="O47" s="230"/>
-      <c r="P47" s="231"/>
+      <c r="C47" s="249"/>
+      <c r="D47" s="249"/>
+      <c r="E47" s="249"/>
+      <c r="F47" s="249"/>
+      <c r="G47" s="249"/>
+      <c r="H47" s="257"/>
+      <c r="I47" s="258"/>
+      <c r="J47" s="258"/>
+      <c r="K47" s="258"/>
+      <c r="L47" s="258"/>
+      <c r="M47" s="259"/>
+      <c r="N47" s="250"/>
+      <c r="O47" s="251"/>
+      <c r="P47" s="252"/>
       <c r="Q47" s="60"/>
-      <c r="R47" s="232"/>
-      <c r="S47" s="232"/>
+      <c r="R47" s="253"/>
+      <c r="S47" s="253"/>
     </row>
     <row r="48" spans="1:19" ht="30" customHeight="1">
       <c r="A48" s="60"/>
       <c r="B48" s="60"/>
-      <c r="C48" s="225"/>
-      <c r="D48" s="225"/>
-      <c r="E48" s="225"/>
-      <c r="F48" s="225"/>
-      <c r="G48" s="225"/>
-      <c r="H48" s="226"/>
-      <c r="I48" s="227"/>
-      <c r="J48" s="227"/>
-      <c r="K48" s="227"/>
-      <c r="L48" s="227"/>
-      <c r="M48" s="228"/>
-      <c r="N48" s="229"/>
-      <c r="O48" s="230"/>
-      <c r="P48" s="231"/>
+      <c r="C48" s="249"/>
+      <c r="D48" s="249"/>
+      <c r="E48" s="249"/>
+      <c r="F48" s="249"/>
+      <c r="G48" s="249"/>
+      <c r="H48" s="257"/>
+      <c r="I48" s="258"/>
+      <c r="J48" s="258"/>
+      <c r="K48" s="258"/>
+      <c r="L48" s="258"/>
+      <c r="M48" s="259"/>
+      <c r="N48" s="250"/>
+      <c r="O48" s="251"/>
+      <c r="P48" s="252"/>
       <c r="Q48" s="60"/>
-      <c r="R48" s="232"/>
-      <c r="S48" s="232"/>
+      <c r="R48" s="253"/>
+      <c r="S48" s="253"/>
     </row>
     <row r="49" spans="1:19" ht="30" customHeight="1">
       <c r="A49" s="60"/>
       <c r="B49" s="60"/>
-      <c r="C49" s="225"/>
-      <c r="D49" s="225"/>
-      <c r="E49" s="225"/>
-      <c r="F49" s="225"/>
-      <c r="G49" s="225"/>
-      <c r="H49" s="226"/>
-      <c r="I49" s="227"/>
-      <c r="J49" s="227"/>
-      <c r="K49" s="227"/>
-      <c r="L49" s="227"/>
-      <c r="M49" s="228"/>
-      <c r="N49" s="229"/>
-      <c r="O49" s="230"/>
-      <c r="P49" s="231"/>
+      <c r="C49" s="249"/>
+      <c r="D49" s="249"/>
+      <c r="E49" s="249"/>
+      <c r="F49" s="249"/>
+      <c r="G49" s="249"/>
+      <c r="H49" s="257"/>
+      <c r="I49" s="258"/>
+      <c r="J49" s="258"/>
+      <c r="K49" s="258"/>
+      <c r="L49" s="258"/>
+      <c r="M49" s="259"/>
+      <c r="N49" s="250"/>
+      <c r="O49" s="251"/>
+      <c r="P49" s="252"/>
       <c r="Q49" s="60"/>
-      <c r="R49" s="232"/>
-      <c r="S49" s="232"/>
+      <c r="R49" s="253"/>
+      <c r="S49" s="253"/>
     </row>
     <row r="50" spans="1:19" ht="30" customHeight="1">
       <c r="A50" s="60"/>
       <c r="B50" s="60"/>
-      <c r="C50" s="225"/>
-      <c r="D50" s="225"/>
-      <c r="E50" s="225"/>
-      <c r="F50" s="225"/>
-      <c r="G50" s="225"/>
-      <c r="H50" s="226"/>
-      <c r="I50" s="227"/>
-      <c r="J50" s="227"/>
-      <c r="K50" s="227"/>
-      <c r="L50" s="227"/>
-      <c r="M50" s="228"/>
-      <c r="N50" s="229"/>
-      <c r="O50" s="230"/>
-      <c r="P50" s="231"/>
+      <c r="C50" s="249"/>
+      <c r="D50" s="249"/>
+      <c r="E50" s="249"/>
+      <c r="F50" s="249"/>
+      <c r="G50" s="249"/>
+      <c r="H50" s="257"/>
+      <c r="I50" s="258"/>
+      <c r="J50" s="258"/>
+      <c r="K50" s="258"/>
+      <c r="L50" s="258"/>
+      <c r="M50" s="259"/>
+      <c r="N50" s="250"/>
+      <c r="O50" s="251"/>
+      <c r="P50" s="252"/>
       <c r="Q50" s="60"/>
-      <c r="R50" s="232"/>
-      <c r="S50" s="232"/>
+      <c r="R50" s="253"/>
+      <c r="S50" s="253"/>
     </row>
     <row r="51" spans="1:19" ht="30" customHeight="1">
       <c r="A51" s="60"/>
       <c r="B51" s="60"/>
-      <c r="C51" s="225"/>
-      <c r="D51" s="225"/>
-      <c r="E51" s="225"/>
-      <c r="F51" s="225"/>
-      <c r="G51" s="225"/>
-      <c r="H51" s="226"/>
-      <c r="I51" s="227"/>
-      <c r="J51" s="227"/>
-      <c r="K51" s="227"/>
-      <c r="L51" s="227"/>
-      <c r="M51" s="228"/>
-      <c r="N51" s="229"/>
-      <c r="O51" s="230"/>
-      <c r="P51" s="231"/>
+      <c r="C51" s="249"/>
+      <c r="D51" s="249"/>
+      <c r="E51" s="249"/>
+      <c r="F51" s="249"/>
+      <c r="G51" s="249"/>
+      <c r="H51" s="257"/>
+      <c r="I51" s="258"/>
+      <c r="J51" s="258"/>
+      <c r="K51" s="258"/>
+      <c r="L51" s="258"/>
+      <c r="M51" s="259"/>
+      <c r="N51" s="250"/>
+      <c r="O51" s="251"/>
+      <c r="P51" s="252"/>
       <c r="Q51" s="60"/>
-      <c r="R51" s="232"/>
-      <c r="S51" s="232"/>
+      <c r="R51" s="253"/>
+      <c r="S51" s="253"/>
     </row>
     <row r="52" spans="1:19" ht="30" customHeight="1">
       <c r="A52" s="60"/>
       <c r="B52" s="60"/>
-      <c r="C52" s="225"/>
-      <c r="D52" s="225"/>
-      <c r="E52" s="225"/>
-      <c r="F52" s="225"/>
-      <c r="G52" s="225"/>
-      <c r="H52" s="226"/>
-      <c r="I52" s="227"/>
-      <c r="J52" s="227"/>
-      <c r="K52" s="227"/>
-      <c r="L52" s="227"/>
-      <c r="M52" s="228"/>
-      <c r="N52" s="229"/>
-      <c r="O52" s="230"/>
-      <c r="P52" s="231"/>
+      <c r="C52" s="249"/>
+      <c r="D52" s="249"/>
+      <c r="E52" s="249"/>
+      <c r="F52" s="249"/>
+      <c r="G52" s="249"/>
+      <c r="H52" s="257"/>
+      <c r="I52" s="258"/>
+      <c r="J52" s="258"/>
+      <c r="K52" s="258"/>
+      <c r="L52" s="258"/>
+      <c r="M52" s="259"/>
+      <c r="N52" s="250"/>
+      <c r="O52" s="251"/>
+      <c r="P52" s="252"/>
       <c r="Q52" s="60"/>
-      <c r="R52" s="232"/>
-      <c r="S52" s="232"/>
+      <c r="R52" s="253"/>
+      <c r="S52" s="253"/>
     </row>
   </sheetData>
   <mergeCells count="205">
+    <mergeCell ref="C52:G52"/>
+    <mergeCell ref="H52:M52"/>
+    <mergeCell ref="N52:P52"/>
+    <mergeCell ref="R52:S52"/>
+    <mergeCell ref="C50:G50"/>
+    <mergeCell ref="H50:M50"/>
+    <mergeCell ref="N50:P50"/>
+    <mergeCell ref="R50:S50"/>
+    <mergeCell ref="C51:G51"/>
+    <mergeCell ref="H51:M51"/>
+    <mergeCell ref="N51:P51"/>
+    <mergeCell ref="R51:S51"/>
+    <mergeCell ref="C48:G48"/>
+    <mergeCell ref="H48:M48"/>
+    <mergeCell ref="N48:P48"/>
+    <mergeCell ref="R48:S48"/>
+    <mergeCell ref="C49:G49"/>
+    <mergeCell ref="H49:M49"/>
+    <mergeCell ref="N49:P49"/>
+    <mergeCell ref="R49:S49"/>
+    <mergeCell ref="C46:G46"/>
+    <mergeCell ref="H46:M46"/>
+    <mergeCell ref="N46:P46"/>
+    <mergeCell ref="R46:S46"/>
+    <mergeCell ref="C47:G47"/>
+    <mergeCell ref="H47:M47"/>
+    <mergeCell ref="N47:P47"/>
+    <mergeCell ref="R47:S47"/>
+    <mergeCell ref="C44:G44"/>
+    <mergeCell ref="H44:M44"/>
+    <mergeCell ref="N44:P44"/>
+    <mergeCell ref="R44:S44"/>
+    <mergeCell ref="C45:G45"/>
+    <mergeCell ref="H45:M45"/>
+    <mergeCell ref="N45:P45"/>
+    <mergeCell ref="R45:S45"/>
+    <mergeCell ref="C42:G42"/>
+    <mergeCell ref="H42:M42"/>
+    <mergeCell ref="N42:P42"/>
+    <mergeCell ref="R42:S42"/>
+    <mergeCell ref="C43:G43"/>
+    <mergeCell ref="H43:M43"/>
+    <mergeCell ref="N43:P43"/>
+    <mergeCell ref="R43:S43"/>
+    <mergeCell ref="C40:G40"/>
+    <mergeCell ref="H40:M40"/>
+    <mergeCell ref="N40:P40"/>
+    <mergeCell ref="R40:S40"/>
+    <mergeCell ref="C41:G41"/>
+    <mergeCell ref="H41:M41"/>
+    <mergeCell ref="N41:P41"/>
+    <mergeCell ref="R41:S41"/>
+    <mergeCell ref="C38:G38"/>
+    <mergeCell ref="H38:M38"/>
+    <mergeCell ref="N38:P38"/>
+    <mergeCell ref="R38:S38"/>
+    <mergeCell ref="C39:G39"/>
+    <mergeCell ref="H39:M39"/>
+    <mergeCell ref="N39:P39"/>
+    <mergeCell ref="R39:S39"/>
+    <mergeCell ref="C36:G36"/>
+    <mergeCell ref="H36:M36"/>
+    <mergeCell ref="N36:P36"/>
+    <mergeCell ref="R36:S36"/>
+    <mergeCell ref="C37:G37"/>
+    <mergeCell ref="H37:M37"/>
+    <mergeCell ref="N37:P37"/>
+    <mergeCell ref="R37:S37"/>
+    <mergeCell ref="C34:G34"/>
+    <mergeCell ref="H34:M34"/>
+    <mergeCell ref="N34:P34"/>
+    <mergeCell ref="R34:S34"/>
+    <mergeCell ref="C35:G35"/>
+    <mergeCell ref="H35:M35"/>
+    <mergeCell ref="N35:P35"/>
+    <mergeCell ref="R35:S35"/>
+    <mergeCell ref="C32:G32"/>
+    <mergeCell ref="H32:M32"/>
+    <mergeCell ref="N32:P32"/>
+    <mergeCell ref="R32:S32"/>
+    <mergeCell ref="C33:G33"/>
+    <mergeCell ref="H33:M33"/>
+    <mergeCell ref="N33:P33"/>
+    <mergeCell ref="R33:S33"/>
+    <mergeCell ref="C30:G30"/>
+    <mergeCell ref="H30:M30"/>
+    <mergeCell ref="N30:P30"/>
+    <mergeCell ref="R30:S30"/>
+    <mergeCell ref="C31:G31"/>
+    <mergeCell ref="H31:M31"/>
+    <mergeCell ref="N31:P31"/>
+    <mergeCell ref="R31:S31"/>
+    <mergeCell ref="C28:G28"/>
+    <mergeCell ref="H28:M28"/>
+    <mergeCell ref="N28:P28"/>
+    <mergeCell ref="R28:S28"/>
+    <mergeCell ref="C29:G29"/>
+    <mergeCell ref="H29:M29"/>
+    <mergeCell ref="N29:P29"/>
+    <mergeCell ref="R29:S29"/>
+    <mergeCell ref="C26:G26"/>
+    <mergeCell ref="H26:M26"/>
+    <mergeCell ref="N26:P26"/>
+    <mergeCell ref="R26:S26"/>
+    <mergeCell ref="C27:G27"/>
+    <mergeCell ref="H27:M27"/>
+    <mergeCell ref="N27:P27"/>
+    <mergeCell ref="R27:S27"/>
+    <mergeCell ref="C24:G24"/>
+    <mergeCell ref="H24:M24"/>
+    <mergeCell ref="N24:P24"/>
+    <mergeCell ref="R24:S24"/>
+    <mergeCell ref="C25:G25"/>
+    <mergeCell ref="H25:M25"/>
+    <mergeCell ref="N25:P25"/>
+    <mergeCell ref="R25:S25"/>
+    <mergeCell ref="C22:G22"/>
+    <mergeCell ref="H22:M22"/>
+    <mergeCell ref="N22:P22"/>
+    <mergeCell ref="R22:S22"/>
+    <mergeCell ref="C23:G23"/>
+    <mergeCell ref="H23:M23"/>
+    <mergeCell ref="N23:P23"/>
+    <mergeCell ref="R23:S23"/>
+    <mergeCell ref="C20:G20"/>
+    <mergeCell ref="H20:M20"/>
+    <mergeCell ref="N20:P20"/>
+    <mergeCell ref="R20:S20"/>
+    <mergeCell ref="C21:G21"/>
+    <mergeCell ref="H21:M21"/>
+    <mergeCell ref="N21:P21"/>
+    <mergeCell ref="R21:S21"/>
+    <mergeCell ref="C18:G18"/>
+    <mergeCell ref="H18:M18"/>
+    <mergeCell ref="N18:P18"/>
+    <mergeCell ref="R18:S18"/>
+    <mergeCell ref="C19:G19"/>
+    <mergeCell ref="H19:M19"/>
+    <mergeCell ref="N19:P19"/>
+    <mergeCell ref="R19:S19"/>
+    <mergeCell ref="C16:G16"/>
+    <mergeCell ref="H16:M16"/>
+    <mergeCell ref="N16:P16"/>
+    <mergeCell ref="R16:S16"/>
+    <mergeCell ref="C17:G17"/>
+    <mergeCell ref="H17:M17"/>
+    <mergeCell ref="N17:P17"/>
+    <mergeCell ref="R17:S17"/>
+    <mergeCell ref="C14:G14"/>
+    <mergeCell ref="H14:M14"/>
+    <mergeCell ref="N14:P14"/>
+    <mergeCell ref="R14:S14"/>
+    <mergeCell ref="C15:G15"/>
+    <mergeCell ref="H15:M15"/>
+    <mergeCell ref="N15:P15"/>
+    <mergeCell ref="R15:S15"/>
+    <mergeCell ref="C12:G12"/>
+    <mergeCell ref="H12:M12"/>
+    <mergeCell ref="N12:P12"/>
+    <mergeCell ref="R12:S12"/>
+    <mergeCell ref="C13:G13"/>
+    <mergeCell ref="H13:M13"/>
+    <mergeCell ref="N13:P13"/>
+    <mergeCell ref="R13:S13"/>
+    <mergeCell ref="C10:G10"/>
+    <mergeCell ref="H10:M10"/>
+    <mergeCell ref="N10:P10"/>
+    <mergeCell ref="R10:S10"/>
+    <mergeCell ref="C11:G11"/>
+    <mergeCell ref="H11:M11"/>
+    <mergeCell ref="N11:P11"/>
+    <mergeCell ref="R11:S11"/>
+    <mergeCell ref="C8:G8"/>
+    <mergeCell ref="H8:M8"/>
+    <mergeCell ref="N8:P8"/>
+    <mergeCell ref="R8:S8"/>
+    <mergeCell ref="C9:G9"/>
+    <mergeCell ref="H9:M9"/>
+    <mergeCell ref="N9:P9"/>
+    <mergeCell ref="R9:S9"/>
+    <mergeCell ref="C6:G6"/>
+    <mergeCell ref="H6:M6"/>
+    <mergeCell ref="N6:P6"/>
+    <mergeCell ref="R6:S6"/>
+    <mergeCell ref="C7:G7"/>
+    <mergeCell ref="H7:M7"/>
+    <mergeCell ref="N7:P7"/>
+    <mergeCell ref="R7:S7"/>
     <mergeCell ref="C4:G4"/>
     <mergeCell ref="H4:M4"/>
     <mergeCell ref="N4:P4"/>
@@ -21858,194 +22070,6 @@
     <mergeCell ref="F2:M2"/>
     <mergeCell ref="O2:P2"/>
     <mergeCell ref="R2:S2"/>
-    <mergeCell ref="C8:G8"/>
-    <mergeCell ref="H8:M8"/>
-    <mergeCell ref="N8:P8"/>
-    <mergeCell ref="R8:S8"/>
-    <mergeCell ref="C9:G9"/>
-    <mergeCell ref="H9:M9"/>
-    <mergeCell ref="N9:P9"/>
-    <mergeCell ref="R9:S9"/>
-    <mergeCell ref="C6:G6"/>
-    <mergeCell ref="H6:M6"/>
-    <mergeCell ref="N6:P6"/>
-    <mergeCell ref="R6:S6"/>
-    <mergeCell ref="C7:G7"/>
-    <mergeCell ref="H7:M7"/>
-    <mergeCell ref="N7:P7"/>
-    <mergeCell ref="R7:S7"/>
-    <mergeCell ref="C12:G12"/>
-    <mergeCell ref="H12:M12"/>
-    <mergeCell ref="N12:P12"/>
-    <mergeCell ref="R12:S12"/>
-    <mergeCell ref="C13:G13"/>
-    <mergeCell ref="H13:M13"/>
-    <mergeCell ref="N13:P13"/>
-    <mergeCell ref="R13:S13"/>
-    <mergeCell ref="C10:G10"/>
-    <mergeCell ref="H10:M10"/>
-    <mergeCell ref="N10:P10"/>
-    <mergeCell ref="R10:S10"/>
-    <mergeCell ref="C11:G11"/>
-    <mergeCell ref="H11:M11"/>
-    <mergeCell ref="N11:P11"/>
-    <mergeCell ref="R11:S11"/>
-    <mergeCell ref="C16:G16"/>
-    <mergeCell ref="H16:M16"/>
-    <mergeCell ref="N16:P16"/>
-    <mergeCell ref="R16:S16"/>
-    <mergeCell ref="C17:G17"/>
-    <mergeCell ref="H17:M17"/>
-    <mergeCell ref="N17:P17"/>
-    <mergeCell ref="R17:S17"/>
-    <mergeCell ref="C14:G14"/>
-    <mergeCell ref="H14:M14"/>
-    <mergeCell ref="N14:P14"/>
-    <mergeCell ref="R14:S14"/>
-    <mergeCell ref="C15:G15"/>
-    <mergeCell ref="H15:M15"/>
-    <mergeCell ref="N15:P15"/>
-    <mergeCell ref="R15:S15"/>
-    <mergeCell ref="C20:G20"/>
-    <mergeCell ref="H20:M20"/>
-    <mergeCell ref="N20:P20"/>
-    <mergeCell ref="R20:S20"/>
-    <mergeCell ref="C21:G21"/>
-    <mergeCell ref="H21:M21"/>
-    <mergeCell ref="N21:P21"/>
-    <mergeCell ref="R21:S21"/>
-    <mergeCell ref="C18:G18"/>
-    <mergeCell ref="H18:M18"/>
-    <mergeCell ref="N18:P18"/>
-    <mergeCell ref="R18:S18"/>
-    <mergeCell ref="C19:G19"/>
-    <mergeCell ref="H19:M19"/>
-    <mergeCell ref="N19:P19"/>
-    <mergeCell ref="R19:S19"/>
-    <mergeCell ref="C24:G24"/>
-    <mergeCell ref="H24:M24"/>
-    <mergeCell ref="N24:P24"/>
-    <mergeCell ref="R24:S24"/>
-    <mergeCell ref="C25:G25"/>
-    <mergeCell ref="H25:M25"/>
-    <mergeCell ref="N25:P25"/>
-    <mergeCell ref="R25:S25"/>
-    <mergeCell ref="C22:G22"/>
-    <mergeCell ref="H22:M22"/>
-    <mergeCell ref="N22:P22"/>
-    <mergeCell ref="R22:S22"/>
-    <mergeCell ref="C23:G23"/>
-    <mergeCell ref="H23:M23"/>
-    <mergeCell ref="N23:P23"/>
-    <mergeCell ref="R23:S23"/>
-    <mergeCell ref="C28:G28"/>
-    <mergeCell ref="H28:M28"/>
-    <mergeCell ref="N28:P28"/>
-    <mergeCell ref="R28:S28"/>
-    <mergeCell ref="C29:G29"/>
-    <mergeCell ref="H29:M29"/>
-    <mergeCell ref="N29:P29"/>
-    <mergeCell ref="R29:S29"/>
-    <mergeCell ref="C26:G26"/>
-    <mergeCell ref="H26:M26"/>
-    <mergeCell ref="N26:P26"/>
-    <mergeCell ref="R26:S26"/>
-    <mergeCell ref="C27:G27"/>
-    <mergeCell ref="H27:M27"/>
-    <mergeCell ref="N27:P27"/>
-    <mergeCell ref="R27:S27"/>
-    <mergeCell ref="C32:G32"/>
-    <mergeCell ref="H32:M32"/>
-    <mergeCell ref="N32:P32"/>
-    <mergeCell ref="R32:S32"/>
-    <mergeCell ref="C33:G33"/>
-    <mergeCell ref="H33:M33"/>
-    <mergeCell ref="N33:P33"/>
-    <mergeCell ref="R33:S33"/>
-    <mergeCell ref="C30:G30"/>
-    <mergeCell ref="H30:M30"/>
-    <mergeCell ref="N30:P30"/>
-    <mergeCell ref="R30:S30"/>
-    <mergeCell ref="C31:G31"/>
-    <mergeCell ref="H31:M31"/>
-    <mergeCell ref="N31:P31"/>
-    <mergeCell ref="R31:S31"/>
-    <mergeCell ref="C36:G36"/>
-    <mergeCell ref="H36:M36"/>
-    <mergeCell ref="N36:P36"/>
-    <mergeCell ref="R36:S36"/>
-    <mergeCell ref="C37:G37"/>
-    <mergeCell ref="H37:M37"/>
-    <mergeCell ref="N37:P37"/>
-    <mergeCell ref="R37:S37"/>
-    <mergeCell ref="C34:G34"/>
-    <mergeCell ref="H34:M34"/>
-    <mergeCell ref="N34:P34"/>
-    <mergeCell ref="R34:S34"/>
-    <mergeCell ref="C35:G35"/>
-    <mergeCell ref="H35:M35"/>
-    <mergeCell ref="N35:P35"/>
-    <mergeCell ref="R35:S35"/>
-    <mergeCell ref="C40:G40"/>
-    <mergeCell ref="H40:M40"/>
-    <mergeCell ref="N40:P40"/>
-    <mergeCell ref="R40:S40"/>
-    <mergeCell ref="C41:G41"/>
-    <mergeCell ref="H41:M41"/>
-    <mergeCell ref="N41:P41"/>
-    <mergeCell ref="R41:S41"/>
-    <mergeCell ref="C38:G38"/>
-    <mergeCell ref="H38:M38"/>
-    <mergeCell ref="N38:P38"/>
-    <mergeCell ref="R38:S38"/>
-    <mergeCell ref="C39:G39"/>
-    <mergeCell ref="H39:M39"/>
-    <mergeCell ref="N39:P39"/>
-    <mergeCell ref="R39:S39"/>
-    <mergeCell ref="C44:G44"/>
-    <mergeCell ref="H44:M44"/>
-    <mergeCell ref="N44:P44"/>
-    <mergeCell ref="R44:S44"/>
-    <mergeCell ref="C45:G45"/>
-    <mergeCell ref="H45:M45"/>
-    <mergeCell ref="N45:P45"/>
-    <mergeCell ref="R45:S45"/>
-    <mergeCell ref="C42:G42"/>
-    <mergeCell ref="H42:M42"/>
-    <mergeCell ref="N42:P42"/>
-    <mergeCell ref="R42:S42"/>
-    <mergeCell ref="C43:G43"/>
-    <mergeCell ref="H43:M43"/>
-    <mergeCell ref="N43:P43"/>
-    <mergeCell ref="R43:S43"/>
-    <mergeCell ref="C48:G48"/>
-    <mergeCell ref="H48:M48"/>
-    <mergeCell ref="N48:P48"/>
-    <mergeCell ref="R48:S48"/>
-    <mergeCell ref="C49:G49"/>
-    <mergeCell ref="H49:M49"/>
-    <mergeCell ref="N49:P49"/>
-    <mergeCell ref="R49:S49"/>
-    <mergeCell ref="C46:G46"/>
-    <mergeCell ref="H46:M46"/>
-    <mergeCell ref="N46:P46"/>
-    <mergeCell ref="R46:S46"/>
-    <mergeCell ref="C47:G47"/>
-    <mergeCell ref="H47:M47"/>
-    <mergeCell ref="N47:P47"/>
-    <mergeCell ref="R47:S47"/>
-    <mergeCell ref="C52:G52"/>
-    <mergeCell ref="H52:M52"/>
-    <mergeCell ref="N52:P52"/>
-    <mergeCell ref="R52:S52"/>
-    <mergeCell ref="C50:G50"/>
-    <mergeCell ref="H50:M50"/>
-    <mergeCell ref="N50:P50"/>
-    <mergeCell ref="R50:S50"/>
-    <mergeCell ref="C51:G51"/>
-    <mergeCell ref="H51:M51"/>
-    <mergeCell ref="N51:P51"/>
-    <mergeCell ref="R51:S51"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.31496062992125984" bottom="0.27559055118110237" header="0.35433070866141736" footer="0.15748031496062992"/>

--- a/Documents/登録機能詳細設計書.xlsx
+++ b/Documents/登録機能詳細設計書.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\S-47\Documents\project\taskUN\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34A78630-FBCC-44F8-BC69-3280335D790A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D93AFB4D-8E7C-4D31-B7E6-E593F2EC5A97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="169">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="172">
   <si>
     <t>プロジェクト型演習　成果ドキュメント</t>
   </si>
@@ -1356,6 +1356,66 @@
   </si>
   <si>
     <t>〇</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>タスク名、カテゴリー、ステータス、期限、ユーザ名、メモを入力しタスク登録を行い、登録成功画面に遷移したのち、ブラウザバックをしたときもう一度同じ内容のものを登録することができる</t>
+    <rPh sb="37" eb="38">
+      <t>オコナ</t>
+    </rPh>
+    <rPh sb="40" eb="42">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="42" eb="44">
+      <t>セイコウ</t>
+    </rPh>
+    <rPh sb="44" eb="46">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="47" eb="49">
+      <t>センイ</t>
+    </rPh>
+    <rPh sb="68" eb="70">
+      <t>イチド</t>
+    </rPh>
+    <rPh sb="70" eb="71">
+      <t>オナ</t>
+    </rPh>
+    <rPh sb="72" eb="74">
+      <t>ナイヨウ</t>
+    </rPh>
+    <rPh sb="78" eb="80">
+      <t>トウロク</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>入力されたものが既にデータベース上に存在している</t>
+    <rPh sb="0" eb="2">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>スデ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>ジョウ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>ソンザイ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>ブラウザバックしてからもう一度登録ボタンを押下する</t>
+    <rPh sb="13" eb="15">
+      <t>イチド</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>オウカ</t>
+    </rPh>
     <phoneticPr fontId="8"/>
   </si>
 </sst>
@@ -2766,135 +2826,135 @@
     <xf numFmtId="14" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="3" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="3" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2973,87 +3033,96 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="4" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3075,14 +3144,70 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="5" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -3090,87 +3215,58 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="67" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="68" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="69" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="70" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="68" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="69" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="70" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="67" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="63" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="68" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="5" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="69" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="70" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="3" borderId="58" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3182,9 +3278,6 @@
     <xf numFmtId="0" fontId="18" fillId="3" borderId="60" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="63" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="64" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -3232,39 +3325,6 @@
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="60" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="67" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="68" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="69" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="70" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="67" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="68" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="69" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="70" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="68" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="69" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="70" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="4" borderId="58" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -10261,19 +10321,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="121" t="s">
+      <c r="A1" s="92" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="122"/>
-      <c r="C1" s="123"/>
-      <c r="D1" s="130" t="s">
+      <c r="B1" s="93"/>
+      <c r="C1" s="94"/>
+      <c r="D1" s="101" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="115"/>
-      <c r="F1" s="130" t="s">
+      <c r="E1" s="102"/>
+      <c r="F1" s="101" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="115"/>
+      <c r="G1" s="102"/>
       <c r="H1" s="34" t="s">
         <v>6</v>
       </c>
@@ -10285,192 +10345,192 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="124"/>
-      <c r="B2" s="125"/>
-      <c r="C2" s="126"/>
-      <c r="D2" s="131" t="s">
+      <c r="A2" s="95"/>
+      <c r="B2" s="96"/>
+      <c r="C2" s="97"/>
+      <c r="D2" s="103" t="s">
         <v>61</v>
       </c>
-      <c r="E2" s="132"/>
-      <c r="F2" s="131">
+      <c r="E2" s="104"/>
+      <c r="F2" s="103">
         <v>56</v>
       </c>
-      <c r="G2" s="132"/>
-      <c r="H2" s="100">
+      <c r="G2" s="104"/>
+      <c r="H2" s="107">
         <v>45806</v>
       </c>
-      <c r="I2" s="109" t="s">
+      <c r="I2" s="121" t="s">
         <v>60</v>
       </c>
-      <c r="J2" s="110"/>
+      <c r="J2" s="122"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="124"/>
-      <c r="B3" s="125"/>
-      <c r="C3" s="126"/>
-      <c r="D3" s="133"/>
-      <c r="E3" s="126"/>
-      <c r="F3" s="133"/>
-      <c r="G3" s="126"/>
-      <c r="H3" s="101"/>
-      <c r="I3" s="101"/>
-      <c r="J3" s="111"/>
+      <c r="A3" s="95"/>
+      <c r="B3" s="96"/>
+      <c r="C3" s="97"/>
+      <c r="D3" s="105"/>
+      <c r="E3" s="97"/>
+      <c r="F3" s="105"/>
+      <c r="G3" s="97"/>
+      <c r="H3" s="108"/>
+      <c r="I3" s="108"/>
+      <c r="J3" s="123"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="127"/>
-      <c r="B4" s="128"/>
-      <c r="C4" s="129"/>
-      <c r="D4" s="134"/>
-      <c r="E4" s="129"/>
-      <c r="F4" s="134"/>
-      <c r="G4" s="129"/>
-      <c r="H4" s="102"/>
-      <c r="I4" s="102"/>
-      <c r="J4" s="112"/>
+      <c r="A4" s="98"/>
+      <c r="B4" s="99"/>
+      <c r="C4" s="100"/>
+      <c r="D4" s="106"/>
+      <c r="E4" s="100"/>
+      <c r="F4" s="106"/>
+      <c r="G4" s="100"/>
+      <c r="H4" s="109"/>
+      <c r="I4" s="109"/>
+      <c r="J4" s="124"/>
     </row>
     <row r="5" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A5" s="113" t="s">
+      <c r="A5" s="125" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="114"/>
-      <c r="C5" s="115"/>
-      <c r="D5" s="116" t="s">
+      <c r="B5" s="126"/>
+      <c r="C5" s="102"/>
+      <c r="D5" s="127" t="s">
         <v>59</v>
       </c>
-      <c r="E5" s="114"/>
-      <c r="F5" s="114"/>
-      <c r="G5" s="114"/>
-      <c r="H5" s="114"/>
-      <c r="I5" s="114"/>
-      <c r="J5" s="117"/>
+      <c r="E5" s="126"/>
+      <c r="F5" s="126"/>
+      <c r="G5" s="126"/>
+      <c r="H5" s="126"/>
+      <c r="I5" s="126"/>
+      <c r="J5" s="128"/>
     </row>
     <row r="6" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A6" s="103" t="s">
+      <c r="A6" s="110" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="98"/>
-      <c r="C6" s="93"/>
-      <c r="D6" s="97" t="s">
+      <c r="B6" s="111"/>
+      <c r="C6" s="112"/>
+      <c r="D6" s="120" t="s">
         <v>58</v>
       </c>
-      <c r="E6" s="98"/>
-      <c r="F6" s="98"/>
-      <c r="G6" s="98"/>
-      <c r="H6" s="98"/>
-      <c r="I6" s="98"/>
-      <c r="J6" s="99"/>
+      <c r="E6" s="111"/>
+      <c r="F6" s="111"/>
+      <c r="G6" s="111"/>
+      <c r="H6" s="111"/>
+      <c r="I6" s="111"/>
+      <c r="J6" s="114"/>
     </row>
     <row r="7" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A7" s="103" t="s">
+      <c r="A7" s="110" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="98"/>
-      <c r="C7" s="93"/>
-      <c r="D7" s="97" t="s">
+      <c r="B7" s="111"/>
+      <c r="C7" s="112"/>
+      <c r="D7" s="120" t="s">
         <v>57</v>
       </c>
-      <c r="E7" s="98"/>
-      <c r="F7" s="98"/>
-      <c r="G7" s="98"/>
-      <c r="H7" s="98"/>
-      <c r="I7" s="98"/>
-      <c r="J7" s="99"/>
+      <c r="E7" s="111"/>
+      <c r="F7" s="111"/>
+      <c r="G7" s="111"/>
+      <c r="H7" s="111"/>
+      <c r="I7" s="111"/>
+      <c r="J7" s="114"/>
     </row>
     <row r="8" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A8" s="103" t="s">
+      <c r="A8" s="110" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="98"/>
-      <c r="C8" s="93"/>
-      <c r="D8" s="94" t="s">
+      <c r="B8" s="111"/>
+      <c r="C8" s="112"/>
+      <c r="D8" s="113" t="s">
         <v>107</v>
       </c>
-      <c r="E8" s="98"/>
-      <c r="F8" s="98"/>
-      <c r="G8" s="98"/>
-      <c r="H8" s="98"/>
-      <c r="I8" s="98"/>
-      <c r="J8" s="99"/>
+      <c r="E8" s="111"/>
+      <c r="F8" s="111"/>
+      <c r="G8" s="111"/>
+      <c r="H8" s="111"/>
+      <c r="I8" s="111"/>
+      <c r="J8" s="114"/>
     </row>
     <row r="9" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A9" s="118" t="s">
+      <c r="A9" s="129" t="s">
         <v>13</v>
       </c>
-      <c r="B9" s="92" t="s">
+      <c r="B9" s="132" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="93"/>
-      <c r="D9" s="94" t="s">
+      <c r="C9" s="112"/>
+      <c r="D9" s="113" t="s">
         <v>105</v>
       </c>
-      <c r="E9" s="95"/>
-      <c r="F9" s="95"/>
-      <c r="G9" s="95"/>
-      <c r="H9" s="95"/>
-      <c r="I9" s="95"/>
-      <c r="J9" s="96"/>
+      <c r="E9" s="133"/>
+      <c r="F9" s="133"/>
+      <c r="G9" s="133"/>
+      <c r="H9" s="133"/>
+      <c r="I9" s="133"/>
+      <c r="J9" s="134"/>
     </row>
     <row r="10" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A10" s="119"/>
-      <c r="B10" s="92" t="s">
+      <c r="A10" s="130"/>
+      <c r="B10" s="132" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="93"/>
-      <c r="D10" s="97" t="s">
+      <c r="C10" s="112"/>
+      <c r="D10" s="120" t="s">
         <v>93</v>
       </c>
-      <c r="E10" s="98"/>
-      <c r="F10" s="98"/>
-      <c r="G10" s="98"/>
-      <c r="H10" s="98"/>
-      <c r="I10" s="98"/>
-      <c r="J10" s="99"/>
+      <c r="E10" s="111"/>
+      <c r="F10" s="111"/>
+      <c r="G10" s="111"/>
+      <c r="H10" s="111"/>
+      <c r="I10" s="111"/>
+      <c r="J10" s="114"/>
     </row>
     <row r="11" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A11" s="120"/>
-      <c r="B11" s="92" t="s">
+      <c r="A11" s="131"/>
+      <c r="B11" s="132" t="s">
         <v>16</v>
       </c>
-      <c r="C11" s="93"/>
-      <c r="D11" s="94" t="s">
+      <c r="C11" s="112"/>
+      <c r="D11" s="113" t="s">
         <v>108</v>
       </c>
-      <c r="E11" s="98"/>
-      <c r="F11" s="98"/>
-      <c r="G11" s="98"/>
-      <c r="H11" s="98"/>
-      <c r="I11" s="98"/>
-      <c r="J11" s="99"/>
+      <c r="E11" s="111"/>
+      <c r="F11" s="111"/>
+      <c r="G11" s="111"/>
+      <c r="H11" s="111"/>
+      <c r="I11" s="111"/>
+      <c r="J11" s="114"/>
     </row>
     <row r="12" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A12" s="103" t="s">
+      <c r="A12" s="110" t="s">
         <v>17</v>
       </c>
-      <c r="B12" s="98"/>
-      <c r="C12" s="93"/>
-      <c r="D12" s="94" t="s">
+      <c r="B12" s="111"/>
+      <c r="C12" s="112"/>
+      <c r="D12" s="113" t="s">
         <v>106</v>
       </c>
-      <c r="E12" s="98"/>
-      <c r="F12" s="98"/>
-      <c r="G12" s="98"/>
-      <c r="H12" s="98"/>
-      <c r="I12" s="98"/>
-      <c r="J12" s="99"/>
+      <c r="E12" s="111"/>
+      <c r="F12" s="111"/>
+      <c r="G12" s="111"/>
+      <c r="H12" s="111"/>
+      <c r="I12" s="111"/>
+      <c r="J12" s="114"/>
     </row>
     <row r="13" spans="1:10" ht="26.25" customHeight="1" thickBot="1">
-      <c r="A13" s="104" t="s">
+      <c r="A13" s="115" t="s">
         <v>18</v>
       </c>
-      <c r="B13" s="105"/>
-      <c r="C13" s="106"/>
-      <c r="D13" s="107"/>
-      <c r="E13" s="105"/>
-      <c r="F13" s="105"/>
-      <c r="G13" s="105"/>
-      <c r="H13" s="105"/>
-      <c r="I13" s="105"/>
-      <c r="J13" s="108"/>
+      <c r="B13" s="116"/>
+      <c r="C13" s="117"/>
+      <c r="D13" s="118"/>
+      <c r="E13" s="116"/>
+      <c r="F13" s="116"/>
+      <c r="G13" s="116"/>
+      <c r="H13" s="116"/>
+      <c r="I13" s="116"/>
+      <c r="J13" s="119"/>
     </row>
     <row r="14" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="15" spans="1:10" ht="12.75" customHeight="1"/>
@@ -11461,11 +11521,12 @@
     <row r="1000" s="32" customFormat="1" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="A1:C4"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="D2:E4"/>
-    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="D9:J9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="D10:J10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="D11:J11"/>
     <mergeCell ref="H2:H4"/>
     <mergeCell ref="A12:C12"/>
     <mergeCell ref="D12:J12"/>
@@ -11482,12 +11543,11 @@
     <mergeCell ref="A6:C6"/>
     <mergeCell ref="D6:J6"/>
     <mergeCell ref="A9:A11"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="D9:J9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="D10:J10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="D11:J11"/>
+    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="F2:G4"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.70833333333333304" right="0.70833333333333304" top="0.74791666666666701" bottom="0.74791666666666701" header="0" footer="0"/>
@@ -14345,19 +14405,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="169" t="s">
+      <c r="A1" s="167" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="170"/>
-      <c r="C1" s="171"/>
-      <c r="D1" s="173" t="s">
+      <c r="B1" s="168"/>
+      <c r="C1" s="169"/>
+      <c r="D1" s="171" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="174"/>
-      <c r="F1" s="173" t="s">
+      <c r="E1" s="172"/>
+      <c r="F1" s="171" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="174"/>
+      <c r="G1" s="172"/>
       <c r="H1" s="43" t="s">
         <v>6</v>
       </c>
@@ -14369,67 +14429,67 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="166"/>
-      <c r="B2" s="167"/>
-      <c r="C2" s="172"/>
-      <c r="D2" s="175" t="s">
+      <c r="A2" s="164"/>
+      <c r="B2" s="165"/>
+      <c r="C2" s="170"/>
+      <c r="D2" s="173" t="s">
         <v>84</v>
       </c>
-      <c r="E2" s="176"/>
-      <c r="F2" s="175">
+      <c r="E2" s="174"/>
+      <c r="F2" s="173">
         <v>56</v>
       </c>
-      <c r="G2" s="176"/>
-      <c r="H2" s="178">
+      <c r="G2" s="174"/>
+      <c r="H2" s="176">
         <v>45806</v>
       </c>
-      <c r="I2" s="180" t="s">
+      <c r="I2" s="178" t="s">
         <v>83</v>
       </c>
-      <c r="J2" s="181"/>
+      <c r="J2" s="179"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="166"/>
-      <c r="B3" s="167"/>
-      <c r="C3" s="172"/>
-      <c r="D3" s="177"/>
-      <c r="E3" s="172"/>
-      <c r="F3" s="177"/>
-      <c r="G3" s="172"/>
-      <c r="H3" s="179"/>
-      <c r="I3" s="179"/>
-      <c r="J3" s="182"/>
+      <c r="A3" s="164"/>
+      <c r="B3" s="165"/>
+      <c r="C3" s="170"/>
+      <c r="D3" s="175"/>
+      <c r="E3" s="170"/>
+      <c r="F3" s="175"/>
+      <c r="G3" s="170"/>
+      <c r="H3" s="177"/>
+      <c r="I3" s="177"/>
+      <c r="J3" s="180"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="166"/>
-      <c r="B4" s="167"/>
-      <c r="C4" s="172"/>
-      <c r="D4" s="177"/>
-      <c r="E4" s="172"/>
-      <c r="F4" s="177"/>
-      <c r="G4" s="172"/>
-      <c r="H4" s="179"/>
-      <c r="I4" s="179"/>
-      <c r="J4" s="182"/>
+      <c r="A4" s="164"/>
+      <c r="B4" s="165"/>
+      <c r="C4" s="170"/>
+      <c r="D4" s="175"/>
+      <c r="E4" s="170"/>
+      <c r="F4" s="175"/>
+      <c r="G4" s="170"/>
+      <c r="H4" s="177"/>
+      <c r="I4" s="177"/>
+      <c r="J4" s="180"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="183" t="s">
+      <c r="A5" s="181" t="s">
         <v>22</v>
       </c>
-      <c r="B5" s="184"/>
-      <c r="C5" s="174"/>
-      <c r="D5" s="185" t="s">
+      <c r="B5" s="182"/>
+      <c r="C5" s="172"/>
+      <c r="D5" s="183" t="s">
         <v>92</v>
       </c>
-      <c r="E5" s="184"/>
-      <c r="F5" s="184"/>
-      <c r="G5" s="184"/>
-      <c r="H5" s="184"/>
-      <c r="I5" s="184"/>
-      <c r="J5" s="186"/>
+      <c r="E5" s="182"/>
+      <c r="F5" s="182"/>
+      <c r="G5" s="182"/>
+      <c r="H5" s="182"/>
+      <c r="I5" s="182"/>
+      <c r="J5" s="184"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="162" t="s">
+      <c r="A6" s="185" t="s">
         <v>23</v>
       </c>
       <c r="B6" s="157"/>
@@ -14443,91 +14503,91 @@
       <c r="J6" s="160"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="163"/>
-      <c r="B7" s="164"/>
-      <c r="C7" s="164"/>
-      <c r="D7" s="164"/>
-      <c r="E7" s="164"/>
-      <c r="F7" s="164"/>
-      <c r="G7" s="164"/>
-      <c r="H7" s="164"/>
-      <c r="I7" s="164"/>
-      <c r="J7" s="165"/>
+      <c r="A7" s="161"/>
+      <c r="B7" s="162"/>
+      <c r="C7" s="162"/>
+      <c r="D7" s="162"/>
+      <c r="E7" s="162"/>
+      <c r="F7" s="162"/>
+      <c r="G7" s="162"/>
+      <c r="H7" s="162"/>
+      <c r="I7" s="162"/>
+      <c r="J7" s="163"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="166"/>
-      <c r="B8" s="167"/>
-      <c r="C8" s="167"/>
-      <c r="D8" s="167"/>
-      <c r="E8" s="167"/>
-      <c r="F8" s="167"/>
-      <c r="G8" s="167"/>
-      <c r="H8" s="167"/>
-      <c r="I8" s="167"/>
-      <c r="J8" s="168"/>
+      <c r="A8" s="164"/>
+      <c r="B8" s="165"/>
+      <c r="C8" s="165"/>
+      <c r="D8" s="165"/>
+      <c r="E8" s="165"/>
+      <c r="F8" s="165"/>
+      <c r="G8" s="165"/>
+      <c r="H8" s="165"/>
+      <c r="I8" s="165"/>
+      <c r="J8" s="166"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="166"/>
-      <c r="B9" s="167"/>
-      <c r="C9" s="167"/>
-      <c r="D9" s="167"/>
-      <c r="E9" s="167"/>
-      <c r="F9" s="167"/>
-      <c r="G9" s="167"/>
-      <c r="H9" s="167"/>
-      <c r="I9" s="167"/>
-      <c r="J9" s="168"/>
+      <c r="A9" s="164"/>
+      <c r="B9" s="165"/>
+      <c r="C9" s="165"/>
+      <c r="D9" s="165"/>
+      <c r="E9" s="165"/>
+      <c r="F9" s="165"/>
+      <c r="G9" s="165"/>
+      <c r="H9" s="165"/>
+      <c r="I9" s="165"/>
+      <c r="J9" s="166"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="166"/>
-      <c r="B10" s="167"/>
-      <c r="C10" s="167"/>
-      <c r="D10" s="167"/>
-      <c r="E10" s="167"/>
-      <c r="F10" s="167"/>
-      <c r="G10" s="167"/>
-      <c r="H10" s="167"/>
-      <c r="I10" s="167"/>
-      <c r="J10" s="168"/>
+      <c r="A10" s="164"/>
+      <c r="B10" s="165"/>
+      <c r="C10" s="165"/>
+      <c r="D10" s="165"/>
+      <c r="E10" s="165"/>
+      <c r="F10" s="165"/>
+      <c r="G10" s="165"/>
+      <c r="H10" s="165"/>
+      <c r="I10" s="165"/>
+      <c r="J10" s="166"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="166"/>
-      <c r="B11" s="167"/>
-      <c r="C11" s="167"/>
-      <c r="D11" s="167"/>
-      <c r="E11" s="167"/>
-      <c r="F11" s="167"/>
-      <c r="G11" s="167"/>
-      <c r="H11" s="167"/>
-      <c r="I11" s="167"/>
-      <c r="J11" s="168"/>
+      <c r="A11" s="164"/>
+      <c r="B11" s="165"/>
+      <c r="C11" s="165"/>
+      <c r="D11" s="165"/>
+      <c r="E11" s="165"/>
+      <c r="F11" s="165"/>
+      <c r="G11" s="165"/>
+      <c r="H11" s="165"/>
+      <c r="I11" s="165"/>
+      <c r="J11" s="166"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="166"/>
-      <c r="B12" s="167"/>
-      <c r="C12" s="167"/>
-      <c r="D12" s="167"/>
-      <c r="E12" s="167"/>
-      <c r="F12" s="167"/>
-      <c r="G12" s="167"/>
-      <c r="H12" s="167"/>
-      <c r="I12" s="167"/>
-      <c r="J12" s="168"/>
+      <c r="A12" s="164"/>
+      <c r="B12" s="165"/>
+      <c r="C12" s="165"/>
+      <c r="D12" s="165"/>
+      <c r="E12" s="165"/>
+      <c r="F12" s="165"/>
+      <c r="G12" s="165"/>
+      <c r="H12" s="165"/>
+      <c r="I12" s="165"/>
+      <c r="J12" s="166"/>
     </row>
     <row r="13" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A13" s="166"/>
-      <c r="B13" s="167"/>
-      <c r="C13" s="167"/>
-      <c r="D13" s="167"/>
-      <c r="E13" s="167"/>
-      <c r="F13" s="167"/>
-      <c r="G13" s="167"/>
-      <c r="H13" s="167"/>
-      <c r="I13" s="167"/>
-      <c r="J13" s="168"/>
+      <c r="A13" s="164"/>
+      <c r="B13" s="165"/>
+      <c r="C13" s="165"/>
+      <c r="D13" s="165"/>
+      <c r="E13" s="165"/>
+      <c r="F13" s="165"/>
+      <c r="G13" s="165"/>
+      <c r="H13" s="165"/>
+      <c r="I13" s="165"/>
+      <c r="J13" s="166"/>
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A14" s="162" t="s">
+      <c r="A14" s="185" t="s">
         <v>24</v>
       </c>
       <c r="B14" s="157"/>
@@ -14541,7 +14601,7 @@
       <c r="J14" s="160"/>
     </row>
     <row r="15" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A15" s="162" t="s">
+      <c r="A15" s="185" t="s">
         <v>25</v>
       </c>
       <c r="B15" s="157"/>
@@ -14561,7 +14621,7 @@
       </c>
     </row>
     <row r="16" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A16" s="162" t="s">
+      <c r="A16" s="185" t="s">
         <v>27</v>
       </c>
       <c r="B16" s="157"/>
@@ -14578,7 +14638,7 @@
       <c r="G16" s="39" t="s">
         <v>31</v>
       </c>
-      <c r="H16" s="161" t="s">
+      <c r="H16" s="186" t="s">
         <v>18</v>
       </c>
       <c r="I16" s="157"/>
@@ -15750,6 +15810,23 @@
     <row r="1000" s="36" customFormat="1" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="33">
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="H19:J19"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="H23:J23"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="H20:J20"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="H21:J21"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="H16:J16"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="H18:J18"/>
+    <mergeCell ref="A15:C15"/>
+    <mergeCell ref="D15:H15"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="H17:J17"/>
     <mergeCell ref="A24:C24"/>
     <mergeCell ref="H24:J24"/>
     <mergeCell ref="A7:J13"/>
@@ -15766,23 +15843,6 @@
     <mergeCell ref="A6:J6"/>
     <mergeCell ref="A14:J14"/>
     <mergeCell ref="A16:C16"/>
-    <mergeCell ref="H16:J16"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="A15:C15"/>
-    <mergeCell ref="D15:H15"/>
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="H17:J17"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="H19:J19"/>
-    <mergeCell ref="A23:C23"/>
-    <mergeCell ref="H23:J23"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="H20:J20"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="H21:J21"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="H22:J22"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -15806,19 +15866,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="192" t="s">
+      <c r="A1" s="195" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="122"/>
-      <c r="C1" s="123"/>
-      <c r="D1" s="130" t="s">
+      <c r="B1" s="93"/>
+      <c r="C1" s="94"/>
+      <c r="D1" s="101" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="115"/>
-      <c r="F1" s="130" t="s">
+      <c r="E1" s="102"/>
+      <c r="F1" s="101" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="115"/>
+      <c r="G1" s="102"/>
       <c r="H1" s="35" t="s">
         <v>6</v>
       </c>
@@ -15830,190 +15890,190 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="124"/>
-      <c r="B2" s="125"/>
-      <c r="C2" s="126"/>
-      <c r="D2" s="131" t="s">
+      <c r="A2" s="95"/>
+      <c r="B2" s="96"/>
+      <c r="C2" s="97"/>
+      <c r="D2" s="103" t="s">
         <v>85</v>
       </c>
-      <c r="E2" s="132"/>
-      <c r="F2" s="131">
+      <c r="E2" s="104"/>
+      <c r="F2" s="103">
         <v>56</v>
       </c>
-      <c r="G2" s="132"/>
-      <c r="H2" s="100">
+      <c r="G2" s="104"/>
+      <c r="H2" s="107">
         <v>45805</v>
       </c>
-      <c r="I2" s="109" t="s">
+      <c r="I2" s="121" t="s">
         <v>83</v>
       </c>
-      <c r="J2" s="110"/>
+      <c r="J2" s="122"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="124"/>
-      <c r="B3" s="125"/>
-      <c r="C3" s="126"/>
-      <c r="D3" s="133"/>
-      <c r="E3" s="126"/>
-      <c r="F3" s="133"/>
-      <c r="G3" s="126"/>
-      <c r="H3" s="101"/>
-      <c r="I3" s="101"/>
-      <c r="J3" s="111"/>
+      <c r="A3" s="95"/>
+      <c r="B3" s="96"/>
+      <c r="C3" s="97"/>
+      <c r="D3" s="105"/>
+      <c r="E3" s="97"/>
+      <c r="F3" s="105"/>
+      <c r="G3" s="97"/>
+      <c r="H3" s="108"/>
+      <c r="I3" s="108"/>
+      <c r="J3" s="123"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="124"/>
-      <c r="B4" s="125"/>
-      <c r="C4" s="126"/>
-      <c r="D4" s="133"/>
-      <c r="E4" s="126"/>
-      <c r="F4" s="133"/>
-      <c r="G4" s="126"/>
-      <c r="H4" s="101"/>
-      <c r="I4" s="101"/>
-      <c r="J4" s="111"/>
+      <c r="A4" s="95"/>
+      <c r="B4" s="96"/>
+      <c r="C4" s="97"/>
+      <c r="D4" s="105"/>
+      <c r="E4" s="97"/>
+      <c r="F4" s="105"/>
+      <c r="G4" s="97"/>
+      <c r="H4" s="108"/>
+      <c r="I4" s="108"/>
+      <c r="J4" s="123"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="193" t="s">
+      <c r="A5" s="196" t="s">
         <v>22</v>
       </c>
-      <c r="B5" s="114"/>
-      <c r="C5" s="115"/>
-      <c r="D5" s="194" t="s">
+      <c r="B5" s="126"/>
+      <c r="C5" s="102"/>
+      <c r="D5" s="197" t="s">
         <v>86</v>
       </c>
-      <c r="E5" s="114"/>
-      <c r="F5" s="114"/>
-      <c r="G5" s="114"/>
-      <c r="H5" s="114"/>
-      <c r="I5" s="114"/>
-      <c r="J5" s="117"/>
+      <c r="E5" s="126"/>
+      <c r="F5" s="126"/>
+      <c r="G5" s="126"/>
+      <c r="H5" s="126"/>
+      <c r="I5" s="126"/>
+      <c r="J5" s="128"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="187" t="s">
+      <c r="A6" s="189" t="s">
         <v>23</v>
       </c>
-      <c r="B6" s="98"/>
-      <c r="C6" s="98"/>
-      <c r="D6" s="98"/>
-      <c r="E6" s="98"/>
-      <c r="F6" s="98"/>
-      <c r="G6" s="98"/>
-      <c r="H6" s="98"/>
-      <c r="I6" s="98"/>
-      <c r="J6" s="99"/>
+      <c r="B6" s="111"/>
+      <c r="C6" s="111"/>
+      <c r="D6" s="111"/>
+      <c r="E6" s="111"/>
+      <c r="F6" s="111"/>
+      <c r="G6" s="111"/>
+      <c r="H6" s="111"/>
+      <c r="I6" s="111"/>
+      <c r="J6" s="114"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="188"/>
-      <c r="B7" s="189"/>
-      <c r="C7" s="189"/>
-      <c r="D7" s="189"/>
-      <c r="E7" s="189"/>
-      <c r="F7" s="189"/>
-      <c r="G7" s="189"/>
-      <c r="H7" s="189"/>
-      <c r="I7" s="189"/>
-      <c r="J7" s="190"/>
+      <c r="A7" s="191"/>
+      <c r="B7" s="192"/>
+      <c r="C7" s="192"/>
+      <c r="D7" s="192"/>
+      <c r="E7" s="192"/>
+      <c r="F7" s="192"/>
+      <c r="G7" s="192"/>
+      <c r="H7" s="192"/>
+      <c r="I7" s="192"/>
+      <c r="J7" s="193"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="124"/>
-      <c r="B8" s="125"/>
-      <c r="C8" s="125"/>
-      <c r="D8" s="125"/>
-      <c r="E8" s="125"/>
-      <c r="F8" s="125"/>
-      <c r="G8" s="125"/>
-      <c r="H8" s="125"/>
-      <c r="I8" s="125"/>
-      <c r="J8" s="191"/>
+      <c r="A8" s="95"/>
+      <c r="B8" s="96"/>
+      <c r="C8" s="96"/>
+      <c r="D8" s="96"/>
+      <c r="E8" s="96"/>
+      <c r="F8" s="96"/>
+      <c r="G8" s="96"/>
+      <c r="H8" s="96"/>
+      <c r="I8" s="96"/>
+      <c r="J8" s="194"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="124"/>
-      <c r="B9" s="125"/>
-      <c r="C9" s="125"/>
-      <c r="D9" s="125"/>
-      <c r="E9" s="125"/>
-      <c r="F9" s="125"/>
-      <c r="G9" s="125"/>
-      <c r="H9" s="125"/>
-      <c r="I9" s="125"/>
-      <c r="J9" s="191"/>
+      <c r="A9" s="95"/>
+      <c r="B9" s="96"/>
+      <c r="C9" s="96"/>
+      <c r="D9" s="96"/>
+      <c r="E9" s="96"/>
+      <c r="F9" s="96"/>
+      <c r="G9" s="96"/>
+      <c r="H9" s="96"/>
+      <c r="I9" s="96"/>
+      <c r="J9" s="194"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="124"/>
-      <c r="B10" s="125"/>
-      <c r="C10" s="125"/>
-      <c r="D10" s="125"/>
-      <c r="E10" s="125"/>
-      <c r="F10" s="125"/>
-      <c r="G10" s="125"/>
-      <c r="H10" s="125"/>
-      <c r="I10" s="125"/>
-      <c r="J10" s="191"/>
+      <c r="A10" s="95"/>
+      <c r="B10" s="96"/>
+      <c r="C10" s="96"/>
+      <c r="D10" s="96"/>
+      <c r="E10" s="96"/>
+      <c r="F10" s="96"/>
+      <c r="G10" s="96"/>
+      <c r="H10" s="96"/>
+      <c r="I10" s="96"/>
+      <c r="J10" s="194"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="124"/>
-      <c r="B11" s="125"/>
-      <c r="C11" s="125"/>
-      <c r="D11" s="125"/>
-      <c r="E11" s="125"/>
-      <c r="F11" s="125"/>
-      <c r="G11" s="125"/>
-      <c r="H11" s="125"/>
-      <c r="I11" s="125"/>
-      <c r="J11" s="191"/>
+      <c r="A11" s="95"/>
+      <c r="B11" s="96"/>
+      <c r="C11" s="96"/>
+      <c r="D11" s="96"/>
+      <c r="E11" s="96"/>
+      <c r="F11" s="96"/>
+      <c r="G11" s="96"/>
+      <c r="H11" s="96"/>
+      <c r="I11" s="96"/>
+      <c r="J11" s="194"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="124"/>
-      <c r="B12" s="125"/>
-      <c r="C12" s="125"/>
-      <c r="D12" s="125"/>
-      <c r="E12" s="125"/>
-      <c r="F12" s="125"/>
-      <c r="G12" s="125"/>
-      <c r="H12" s="125"/>
-      <c r="I12" s="125"/>
-      <c r="J12" s="191"/>
+      <c r="A12" s="95"/>
+      <c r="B12" s="96"/>
+      <c r="C12" s="96"/>
+      <c r="D12" s="96"/>
+      <c r="E12" s="96"/>
+      <c r="F12" s="96"/>
+      <c r="G12" s="96"/>
+      <c r="H12" s="96"/>
+      <c r="I12" s="96"/>
+      <c r="J12" s="194"/>
     </row>
     <row r="13" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A13" s="124"/>
-      <c r="B13" s="125"/>
-      <c r="C13" s="125"/>
-      <c r="D13" s="125"/>
-      <c r="E13" s="125"/>
-      <c r="F13" s="125"/>
-      <c r="G13" s="125"/>
-      <c r="H13" s="125"/>
-      <c r="I13" s="125"/>
-      <c r="J13" s="191"/>
+      <c r="A13" s="95"/>
+      <c r="B13" s="96"/>
+      <c r="C13" s="96"/>
+      <c r="D13" s="96"/>
+      <c r="E13" s="96"/>
+      <c r="F13" s="96"/>
+      <c r="G13" s="96"/>
+      <c r="H13" s="96"/>
+      <c r="I13" s="96"/>
+      <c r="J13" s="194"/>
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A14" s="187" t="s">
+      <c r="A14" s="189" t="s">
         <v>24</v>
       </c>
-      <c r="B14" s="98"/>
-      <c r="C14" s="98"/>
-      <c r="D14" s="98"/>
-      <c r="E14" s="98"/>
-      <c r="F14" s="98"/>
-      <c r="G14" s="98"/>
-      <c r="H14" s="98"/>
-      <c r="I14" s="98"/>
-      <c r="J14" s="99"/>
+      <c r="B14" s="111"/>
+      <c r="C14" s="111"/>
+      <c r="D14" s="111"/>
+      <c r="E14" s="111"/>
+      <c r="F14" s="111"/>
+      <c r="G14" s="111"/>
+      <c r="H14" s="111"/>
+      <c r="I14" s="111"/>
+      <c r="J14" s="114"/>
     </row>
     <row r="15" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A15" s="187" t="s">
+      <c r="A15" s="189" t="s">
         <v>25</v>
       </c>
-      <c r="B15" s="98"/>
-      <c r="C15" s="93"/>
-      <c r="D15" s="97" t="s">
+      <c r="B15" s="111"/>
+      <c r="C15" s="112"/>
+      <c r="D15" s="120" t="s">
         <v>87</v>
       </c>
-      <c r="E15" s="98"/>
-      <c r="F15" s="98"/>
-      <c r="G15" s="98"/>
-      <c r="H15" s="93"/>
+      <c r="E15" s="111"/>
+      <c r="F15" s="111"/>
+      <c r="G15" s="111"/>
+      <c r="H15" s="112"/>
       <c r="I15" s="45" t="s">
         <v>26</v>
       </c>
@@ -16022,11 +16082,11 @@
       </c>
     </row>
     <row r="16" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A16" s="187" t="s">
+      <c r="A16" s="189" t="s">
         <v>27</v>
       </c>
-      <c r="B16" s="98"/>
-      <c r="C16" s="93"/>
+      <c r="B16" s="111"/>
+      <c r="C16" s="112"/>
       <c r="D16" s="45" t="s">
         <v>28</v>
       </c>
@@ -16039,18 +16099,18 @@
       <c r="G16" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="H16" s="195" t="s">
+      <c r="H16" s="190" t="s">
         <v>18</v>
       </c>
-      <c r="I16" s="98"/>
-      <c r="J16" s="99"/>
+      <c r="I16" s="111"/>
+      <c r="J16" s="114"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="196">
+      <c r="A17" s="187">
         <v>1</v>
       </c>
-      <c r="B17" s="98"/>
-      <c r="C17" s="93"/>
+      <c r="B17" s="111"/>
+      <c r="C17" s="112"/>
       <c r="D17" s="47" t="s">
         <v>64</v>
       </c>
@@ -16063,83 +16123,83 @@
       <c r="G17" s="48" t="s">
         <v>89</v>
       </c>
-      <c r="H17" s="97" t="s">
+      <c r="H17" s="120" t="s">
         <v>90</v>
       </c>
-      <c r="I17" s="98"/>
-      <c r="J17" s="99"/>
+      <c r="I17" s="111"/>
+      <c r="J17" s="114"/>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A18" s="196"/>
-      <c r="B18" s="98"/>
-      <c r="C18" s="93"/>
+      <c r="A18" s="187"/>
+      <c r="B18" s="111"/>
+      <c r="C18" s="112"/>
       <c r="D18" s="47"/>
       <c r="E18" s="47"/>
       <c r="F18" s="48"/>
       <c r="G18" s="48"/>
-      <c r="H18" s="97"/>
-      <c r="I18" s="98"/>
-      <c r="J18" s="99"/>
+      <c r="H18" s="120"/>
+      <c r="I18" s="111"/>
+      <c r="J18" s="114"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="196"/>
-      <c r="B19" s="98"/>
-      <c r="C19" s="93"/>
+      <c r="A19" s="187"/>
+      <c r="B19" s="111"/>
+      <c r="C19" s="112"/>
       <c r="D19" s="47"/>
       <c r="E19" s="47"/>
       <c r="F19" s="48"/>
       <c r="G19" s="48"/>
-      <c r="H19" s="97"/>
-      <c r="I19" s="98"/>
-      <c r="J19" s="99"/>
+      <c r="H19" s="120"/>
+      <c r="I19" s="111"/>
+      <c r="J19" s="114"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="196"/>
-      <c r="B20" s="98"/>
-      <c r="C20" s="93"/>
+      <c r="A20" s="187"/>
+      <c r="B20" s="111"/>
+      <c r="C20" s="112"/>
       <c r="D20" s="47"/>
       <c r="E20" s="47"/>
       <c r="F20" s="48"/>
       <c r="G20" s="48"/>
-      <c r="H20" s="97"/>
-      <c r="I20" s="98"/>
-      <c r="J20" s="99"/>
+      <c r="H20" s="120"/>
+      <c r="I20" s="111"/>
+      <c r="J20" s="114"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="196"/>
-      <c r="B21" s="98"/>
-      <c r="C21" s="93"/>
+      <c r="A21" s="187"/>
+      <c r="B21" s="111"/>
+      <c r="C21" s="112"/>
       <c r="D21" s="47"/>
       <c r="E21" s="47"/>
       <c r="F21" s="48"/>
       <c r="G21" s="48"/>
-      <c r="H21" s="97"/>
-      <c r="I21" s="98"/>
-      <c r="J21" s="99"/>
+      <c r="H21" s="120"/>
+      <c r="I21" s="111"/>
+      <c r="J21" s="114"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="196"/>
-      <c r="B22" s="98"/>
-      <c r="C22" s="93"/>
+      <c r="A22" s="187"/>
+      <c r="B22" s="111"/>
+      <c r="C22" s="112"/>
       <c r="D22" s="47"/>
       <c r="E22" s="47"/>
       <c r="F22" s="48"/>
       <c r="G22" s="48"/>
-      <c r="H22" s="97"/>
-      <c r="I22" s="98"/>
-      <c r="J22" s="99"/>
+      <c r="H22" s="120"/>
+      <c r="I22" s="111"/>
+      <c r="J22" s="114"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A23" s="197"/>
-      <c r="B23" s="105"/>
-      <c r="C23" s="106"/>
+      <c r="A23" s="188"/>
+      <c r="B23" s="116"/>
+      <c r="C23" s="117"/>
       <c r="D23" s="49"/>
       <c r="E23" s="49"/>
       <c r="F23" s="50"/>
       <c r="G23" s="50"/>
-      <c r="H23" s="107"/>
-      <c r="I23" s="105"/>
-      <c r="J23" s="108"/>
+      <c r="H23" s="118"/>
+      <c r="I23" s="116"/>
+      <c r="J23" s="119"/>
     </row>
     <row r="24" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="25" spans="1:10" ht="12.75" customHeight="1"/>
@@ -17120,22 +17180,6 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="31">
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="H22:J22"/>
-    <mergeCell ref="A23:C23"/>
-    <mergeCell ref="H23:J23"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="H19:J19"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="H20:J20"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="H21:J21"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="H16:J16"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="H17:J17"/>
     <mergeCell ref="A14:J14"/>
     <mergeCell ref="A15:C15"/>
     <mergeCell ref="A7:J13"/>
@@ -17151,6 +17195,22 @@
     <mergeCell ref="D5:J5"/>
     <mergeCell ref="A6:J6"/>
     <mergeCell ref="D15:H15"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="H16:J16"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="H18:J18"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="H17:J17"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="H23:J23"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="H19:J19"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="H20:J20"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="H21:J21"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -17174,19 +17234,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="192" t="s">
+      <c r="A1" s="195" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="122"/>
-      <c r="C1" s="123"/>
-      <c r="D1" s="130" t="s">
+      <c r="B1" s="93"/>
+      <c r="C1" s="94"/>
+      <c r="D1" s="101" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="115"/>
-      <c r="F1" s="130" t="s">
+      <c r="E1" s="102"/>
+      <c r="F1" s="101" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="115"/>
+      <c r="G1" s="102"/>
       <c r="H1" s="35" t="s">
         <v>6</v>
       </c>
@@ -17198,190 +17258,190 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="124"/>
-      <c r="B2" s="125"/>
-      <c r="C2" s="126"/>
-      <c r="D2" s="131" t="s">
+      <c r="A2" s="95"/>
+      <c r="B2" s="96"/>
+      <c r="C2" s="97"/>
+      <c r="D2" s="103" t="s">
         <v>84</v>
       </c>
-      <c r="E2" s="132"/>
-      <c r="F2" s="131">
+      <c r="E2" s="104"/>
+      <c r="F2" s="103">
         <v>56</v>
       </c>
-      <c r="G2" s="132"/>
-      <c r="H2" s="100">
+      <c r="G2" s="104"/>
+      <c r="H2" s="107">
         <v>45805</v>
       </c>
-      <c r="I2" s="109" t="s">
+      <c r="I2" s="121" t="s">
         <v>83</v>
       </c>
-      <c r="J2" s="110"/>
+      <c r="J2" s="122"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="124"/>
-      <c r="B3" s="125"/>
-      <c r="C3" s="126"/>
-      <c r="D3" s="133"/>
-      <c r="E3" s="126"/>
-      <c r="F3" s="133"/>
-      <c r="G3" s="126"/>
-      <c r="H3" s="101"/>
-      <c r="I3" s="101"/>
-      <c r="J3" s="111"/>
+      <c r="A3" s="95"/>
+      <c r="B3" s="96"/>
+      <c r="C3" s="97"/>
+      <c r="D3" s="105"/>
+      <c r="E3" s="97"/>
+      <c r="F3" s="105"/>
+      <c r="G3" s="97"/>
+      <c r="H3" s="108"/>
+      <c r="I3" s="108"/>
+      <c r="J3" s="123"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="124"/>
-      <c r="B4" s="125"/>
-      <c r="C4" s="126"/>
-      <c r="D4" s="133"/>
-      <c r="E4" s="126"/>
-      <c r="F4" s="133"/>
-      <c r="G4" s="126"/>
-      <c r="H4" s="101"/>
-      <c r="I4" s="101"/>
-      <c r="J4" s="111"/>
+      <c r="A4" s="95"/>
+      <c r="B4" s="96"/>
+      <c r="C4" s="97"/>
+      <c r="D4" s="105"/>
+      <c r="E4" s="97"/>
+      <c r="F4" s="105"/>
+      <c r="G4" s="97"/>
+      <c r="H4" s="108"/>
+      <c r="I4" s="108"/>
+      <c r="J4" s="123"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="193" t="s">
+      <c r="A5" s="196" t="s">
         <v>22</v>
       </c>
-      <c r="B5" s="114"/>
-      <c r="C5" s="115"/>
-      <c r="D5" s="194" t="s">
+      <c r="B5" s="126"/>
+      <c r="C5" s="102"/>
+      <c r="D5" s="197" t="s">
         <v>91</v>
       </c>
-      <c r="E5" s="114"/>
-      <c r="F5" s="114"/>
-      <c r="G5" s="114"/>
-      <c r="H5" s="114"/>
-      <c r="I5" s="114"/>
-      <c r="J5" s="117"/>
+      <c r="E5" s="126"/>
+      <c r="F5" s="126"/>
+      <c r="G5" s="126"/>
+      <c r="H5" s="126"/>
+      <c r="I5" s="126"/>
+      <c r="J5" s="128"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="187" t="s">
+      <c r="A6" s="189" t="s">
         <v>23</v>
       </c>
-      <c r="B6" s="98"/>
-      <c r="C6" s="98"/>
-      <c r="D6" s="98"/>
-      <c r="E6" s="98"/>
-      <c r="F6" s="98"/>
-      <c r="G6" s="98"/>
-      <c r="H6" s="98"/>
-      <c r="I6" s="98"/>
-      <c r="J6" s="99"/>
+      <c r="B6" s="111"/>
+      <c r="C6" s="111"/>
+      <c r="D6" s="111"/>
+      <c r="E6" s="111"/>
+      <c r="F6" s="111"/>
+      <c r="G6" s="111"/>
+      <c r="H6" s="111"/>
+      <c r="I6" s="111"/>
+      <c r="J6" s="114"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="188"/>
-      <c r="B7" s="189"/>
-      <c r="C7" s="189"/>
-      <c r="D7" s="189"/>
-      <c r="E7" s="189"/>
-      <c r="F7" s="189"/>
-      <c r="G7" s="189"/>
-      <c r="H7" s="189"/>
-      <c r="I7" s="189"/>
-      <c r="J7" s="190"/>
+      <c r="A7" s="191"/>
+      <c r="B7" s="192"/>
+      <c r="C7" s="192"/>
+      <c r="D7" s="192"/>
+      <c r="E7" s="192"/>
+      <c r="F7" s="192"/>
+      <c r="G7" s="192"/>
+      <c r="H7" s="192"/>
+      <c r="I7" s="192"/>
+      <c r="J7" s="193"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="124"/>
-      <c r="B8" s="125"/>
-      <c r="C8" s="125"/>
-      <c r="D8" s="125"/>
-      <c r="E8" s="125"/>
-      <c r="F8" s="125"/>
-      <c r="G8" s="125"/>
-      <c r="H8" s="125"/>
-      <c r="I8" s="125"/>
-      <c r="J8" s="191"/>
+      <c r="A8" s="95"/>
+      <c r="B8" s="96"/>
+      <c r="C8" s="96"/>
+      <c r="D8" s="96"/>
+      <c r="E8" s="96"/>
+      <c r="F8" s="96"/>
+      <c r="G8" s="96"/>
+      <c r="H8" s="96"/>
+      <c r="I8" s="96"/>
+      <c r="J8" s="194"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="124"/>
-      <c r="B9" s="125"/>
-      <c r="C9" s="125"/>
-      <c r="D9" s="125"/>
-      <c r="E9" s="125"/>
-      <c r="F9" s="125"/>
-      <c r="G9" s="125"/>
-      <c r="H9" s="125"/>
-      <c r="I9" s="125"/>
-      <c r="J9" s="191"/>
+      <c r="A9" s="95"/>
+      <c r="B9" s="96"/>
+      <c r="C9" s="96"/>
+      <c r="D9" s="96"/>
+      <c r="E9" s="96"/>
+      <c r="F9" s="96"/>
+      <c r="G9" s="96"/>
+      <c r="H9" s="96"/>
+      <c r="I9" s="96"/>
+      <c r="J9" s="194"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="124"/>
-      <c r="B10" s="125"/>
-      <c r="C10" s="125"/>
-      <c r="D10" s="125"/>
-      <c r="E10" s="125"/>
-      <c r="F10" s="125"/>
-      <c r="G10" s="125"/>
-      <c r="H10" s="125"/>
-      <c r="I10" s="125"/>
-      <c r="J10" s="191"/>
+      <c r="A10" s="95"/>
+      <c r="B10" s="96"/>
+      <c r="C10" s="96"/>
+      <c r="D10" s="96"/>
+      <c r="E10" s="96"/>
+      <c r="F10" s="96"/>
+      <c r="G10" s="96"/>
+      <c r="H10" s="96"/>
+      <c r="I10" s="96"/>
+      <c r="J10" s="194"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="124"/>
-      <c r="B11" s="125"/>
-      <c r="C11" s="125"/>
-      <c r="D11" s="125"/>
-      <c r="E11" s="125"/>
-      <c r="F11" s="125"/>
-      <c r="G11" s="125"/>
-      <c r="H11" s="125"/>
-      <c r="I11" s="125"/>
-      <c r="J11" s="191"/>
+      <c r="A11" s="95"/>
+      <c r="B11" s="96"/>
+      <c r="C11" s="96"/>
+      <c r="D11" s="96"/>
+      <c r="E11" s="96"/>
+      <c r="F11" s="96"/>
+      <c r="G11" s="96"/>
+      <c r="H11" s="96"/>
+      <c r="I11" s="96"/>
+      <c r="J11" s="194"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="124"/>
-      <c r="B12" s="125"/>
-      <c r="C12" s="125"/>
-      <c r="D12" s="125"/>
-      <c r="E12" s="125"/>
-      <c r="F12" s="125"/>
-      <c r="G12" s="125"/>
-      <c r="H12" s="125"/>
-      <c r="I12" s="125"/>
-      <c r="J12" s="191"/>
+      <c r="A12" s="95"/>
+      <c r="B12" s="96"/>
+      <c r="C12" s="96"/>
+      <c r="D12" s="96"/>
+      <c r="E12" s="96"/>
+      <c r="F12" s="96"/>
+      <c r="G12" s="96"/>
+      <c r="H12" s="96"/>
+      <c r="I12" s="96"/>
+      <c r="J12" s="194"/>
     </row>
     <row r="13" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A13" s="124"/>
-      <c r="B13" s="125"/>
-      <c r="C13" s="125"/>
-      <c r="D13" s="125"/>
-      <c r="E13" s="125"/>
-      <c r="F13" s="125"/>
-      <c r="G13" s="125"/>
-      <c r="H13" s="125"/>
-      <c r="I13" s="125"/>
-      <c r="J13" s="191"/>
+      <c r="A13" s="95"/>
+      <c r="B13" s="96"/>
+      <c r="C13" s="96"/>
+      <c r="D13" s="96"/>
+      <c r="E13" s="96"/>
+      <c r="F13" s="96"/>
+      <c r="G13" s="96"/>
+      <c r="H13" s="96"/>
+      <c r="I13" s="96"/>
+      <c r="J13" s="194"/>
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A14" s="187" t="s">
+      <c r="A14" s="189" t="s">
         <v>24</v>
       </c>
-      <c r="B14" s="98"/>
-      <c r="C14" s="98"/>
-      <c r="D14" s="98"/>
-      <c r="E14" s="98"/>
-      <c r="F14" s="98"/>
-      <c r="G14" s="98"/>
-      <c r="H14" s="98"/>
-      <c r="I14" s="98"/>
-      <c r="J14" s="99"/>
+      <c r="B14" s="111"/>
+      <c r="C14" s="111"/>
+      <c r="D14" s="111"/>
+      <c r="E14" s="111"/>
+      <c r="F14" s="111"/>
+      <c r="G14" s="111"/>
+      <c r="H14" s="111"/>
+      <c r="I14" s="111"/>
+      <c r="J14" s="114"/>
     </row>
     <row r="15" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A15" s="187" t="s">
+      <c r="A15" s="189" t="s">
         <v>25</v>
       </c>
-      <c r="B15" s="98"/>
-      <c r="C15" s="93"/>
-      <c r="D15" s="97" t="s">
+      <c r="B15" s="111"/>
+      <c r="C15" s="112"/>
+      <c r="D15" s="120" t="s">
         <v>87</v>
       </c>
-      <c r="E15" s="98"/>
-      <c r="F15" s="98"/>
-      <c r="G15" s="98"/>
-      <c r="H15" s="93"/>
+      <c r="E15" s="111"/>
+      <c r="F15" s="111"/>
+      <c r="G15" s="111"/>
+      <c r="H15" s="112"/>
       <c r="I15" s="45" t="s">
         <v>26</v>
       </c>
@@ -17390,11 +17450,11 @@
       </c>
     </row>
     <row r="16" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A16" s="187" t="s">
+      <c r="A16" s="189" t="s">
         <v>27</v>
       </c>
-      <c r="B16" s="98"/>
-      <c r="C16" s="93"/>
+      <c r="B16" s="111"/>
+      <c r="C16" s="112"/>
       <c r="D16" s="45" t="s">
         <v>28</v>
       </c>
@@ -17407,18 +17467,18 @@
       <c r="G16" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="H16" s="195" t="s">
+      <c r="H16" s="190" t="s">
         <v>18</v>
       </c>
-      <c r="I16" s="98"/>
-      <c r="J16" s="99"/>
+      <c r="I16" s="111"/>
+      <c r="J16" s="114"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="196">
+      <c r="A17" s="187">
         <v>1</v>
       </c>
-      <c r="B17" s="98"/>
-      <c r="C17" s="93"/>
+      <c r="B17" s="111"/>
+      <c r="C17" s="112"/>
       <c r="D17" s="47" t="s">
         <v>64</v>
       </c>
@@ -17431,83 +17491,83 @@
       <c r="G17" s="48" t="s">
         <v>89</v>
       </c>
-      <c r="H17" s="97" t="s">
+      <c r="H17" s="120" t="s">
         <v>90</v>
       </c>
-      <c r="I17" s="98"/>
-      <c r="J17" s="99"/>
+      <c r="I17" s="111"/>
+      <c r="J17" s="114"/>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A18" s="196"/>
-      <c r="B18" s="98"/>
-      <c r="C18" s="93"/>
+      <c r="A18" s="187"/>
+      <c r="B18" s="111"/>
+      <c r="C18" s="112"/>
       <c r="D18" s="47"/>
       <c r="E18" s="47"/>
       <c r="F18" s="48"/>
       <c r="G18" s="48"/>
-      <c r="H18" s="97"/>
-      <c r="I18" s="98"/>
-      <c r="J18" s="99"/>
+      <c r="H18" s="120"/>
+      <c r="I18" s="111"/>
+      <c r="J18" s="114"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="196"/>
-      <c r="B19" s="98"/>
-      <c r="C19" s="93"/>
+      <c r="A19" s="187"/>
+      <c r="B19" s="111"/>
+      <c r="C19" s="112"/>
       <c r="D19" s="47"/>
       <c r="E19" s="47"/>
       <c r="F19" s="48"/>
       <c r="G19" s="48"/>
-      <c r="H19" s="97"/>
-      <c r="I19" s="98"/>
-      <c r="J19" s="99"/>
+      <c r="H19" s="120"/>
+      <c r="I19" s="111"/>
+      <c r="J19" s="114"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="196"/>
-      <c r="B20" s="98"/>
-      <c r="C20" s="93"/>
+      <c r="A20" s="187"/>
+      <c r="B20" s="111"/>
+      <c r="C20" s="112"/>
       <c r="D20" s="47"/>
       <c r="E20" s="47"/>
       <c r="F20" s="48"/>
       <c r="G20" s="48"/>
-      <c r="H20" s="97"/>
-      <c r="I20" s="98"/>
-      <c r="J20" s="99"/>
+      <c r="H20" s="120"/>
+      <c r="I20" s="111"/>
+      <c r="J20" s="114"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="196"/>
-      <c r="B21" s="98"/>
-      <c r="C21" s="93"/>
+      <c r="A21" s="187"/>
+      <c r="B21" s="111"/>
+      <c r="C21" s="112"/>
       <c r="D21" s="47"/>
       <c r="E21" s="47"/>
       <c r="F21" s="48"/>
       <c r="G21" s="48"/>
-      <c r="H21" s="97"/>
-      <c r="I21" s="98"/>
-      <c r="J21" s="99"/>
+      <c r="H21" s="120"/>
+      <c r="I21" s="111"/>
+      <c r="J21" s="114"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="196"/>
-      <c r="B22" s="98"/>
-      <c r="C22" s="93"/>
+      <c r="A22" s="187"/>
+      <c r="B22" s="111"/>
+      <c r="C22" s="112"/>
       <c r="D22" s="47"/>
       <c r="E22" s="47"/>
       <c r="F22" s="48"/>
       <c r="G22" s="48"/>
-      <c r="H22" s="97"/>
-      <c r="I22" s="98"/>
-      <c r="J22" s="99"/>
+      <c r="H22" s="120"/>
+      <c r="I22" s="111"/>
+      <c r="J22" s="114"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A23" s="197"/>
-      <c r="B23" s="105"/>
-      <c r="C23" s="106"/>
+      <c r="A23" s="188"/>
+      <c r="B23" s="116"/>
+      <c r="C23" s="117"/>
       <c r="D23" s="49"/>
       <c r="E23" s="49"/>
       <c r="F23" s="50"/>
       <c r="G23" s="50"/>
-      <c r="H23" s="107"/>
-      <c r="I23" s="105"/>
-      <c r="J23" s="108"/>
+      <c r="H23" s="118"/>
+      <c r="I23" s="116"/>
+      <c r="J23" s="119"/>
     </row>
     <row r="24" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="25" spans="1:10" ht="12.75" customHeight="1"/>
@@ -18488,22 +18548,6 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="31">
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="H22:J22"/>
-    <mergeCell ref="A23:C23"/>
-    <mergeCell ref="H23:J23"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="H19:J19"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="H20:J20"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="H21:J21"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="H16:J16"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="H17:J17"/>
     <mergeCell ref="A14:J14"/>
     <mergeCell ref="A15:C15"/>
     <mergeCell ref="A7:J13"/>
@@ -18519,6 +18563,22 @@
     <mergeCell ref="D5:J5"/>
     <mergeCell ref="A6:J6"/>
     <mergeCell ref="D15:H15"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="H16:J16"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="H18:J18"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="H17:J17"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="H23:J23"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="H19:J19"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="H20:J20"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="H21:J21"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -18538,7 +18598,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="18" customHeight="1">
-      <c r="A1" s="224" t="s">
+      <c r="A1" s="213" t="s">
         <v>32</v>
       </c>
       <c r="B1" s="143"/>
@@ -18549,14 +18609,14 @@
       <c r="G1" s="150" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="209"/>
-      <c r="I1" s="209"/>
+      <c r="H1" s="214"/>
+      <c r="I1" s="214"/>
       <c r="J1" s="151"/>
       <c r="K1" s="150" t="s">
         <v>5</v>
       </c>
-      <c r="L1" s="209"/>
-      <c r="M1" s="209"/>
+      <c r="L1" s="214"/>
+      <c r="M1" s="214"/>
       <c r="N1" s="151"/>
       <c r="O1" s="150" t="s">
         <v>6</v>
@@ -18569,7 +18629,7 @@
       <c r="S1" s="150" t="s">
         <v>8</v>
       </c>
-      <c r="T1" s="211"/>
+      <c r="T1" s="215"/>
     </row>
     <row r="2" spans="1:26" ht="18" customHeight="1">
       <c r="A2" s="145"/>
@@ -18581,16 +18641,16 @@
       <c r="G2" s="152" t="s">
         <v>84</v>
       </c>
-      <c r="H2" s="219"/>
-      <c r="I2" s="219"/>
+      <c r="H2" s="208"/>
+      <c r="I2" s="208"/>
       <c r="J2" s="153"/>
       <c r="K2" s="152" t="s">
         <v>54</v>
       </c>
-      <c r="L2" s="219"/>
-      <c r="M2" s="219"/>
+      <c r="L2" s="208"/>
+      <c r="M2" s="208"/>
       <c r="N2" s="153"/>
-      <c r="O2" s="220">
+      <c r="O2" s="209">
         <v>45821</v>
       </c>
       <c r="P2" s="153"/>
@@ -18599,7 +18659,7 @@
       </c>
       <c r="R2" s="153"/>
       <c r="S2" s="152"/>
-      <c r="T2" s="221"/>
+      <c r="T2" s="210"/>
     </row>
     <row r="3" spans="1:26" ht="18" customHeight="1">
       <c r="A3" s="145"/>
@@ -18621,7 +18681,7 @@
       <c r="Q3" s="154"/>
       <c r="R3" s="146"/>
       <c r="S3" s="154"/>
-      <c r="T3" s="222"/>
+      <c r="T3" s="211"/>
     </row>
     <row r="4" spans="1:26" ht="18" customHeight="1">
       <c r="A4" s="147"/>
@@ -18643,36 +18703,36 @@
       <c r="Q4" s="155"/>
       <c r="R4" s="149"/>
       <c r="S4" s="155"/>
-      <c r="T4" s="223"/>
+      <c r="T4" s="212"/>
     </row>
     <row r="5" spans="1:26" ht="18" customHeight="1">
-      <c r="A5" s="208" t="s">
+      <c r="A5" s="216" t="s">
         <v>33</v>
       </c>
-      <c r="B5" s="209"/>
-      <c r="C5" s="209"/>
-      <c r="D5" s="209"/>
-      <c r="E5" s="209"/>
+      <c r="B5" s="214"/>
+      <c r="C5" s="214"/>
+      <c r="D5" s="214"/>
+      <c r="E5" s="214"/>
       <c r="F5" s="151"/>
-      <c r="G5" s="210" t="s">
+      <c r="G5" s="217" t="s">
         <v>34</v>
       </c>
-      <c r="H5" s="209"/>
-      <c r="I5" s="209"/>
-      <c r="J5" s="209"/>
-      <c r="K5" s="209"/>
-      <c r="L5" s="209"/>
-      <c r="M5" s="209"/>
-      <c r="N5" s="209"/>
-      <c r="O5" s="209"/>
-      <c r="P5" s="209"/>
-      <c r="Q5" s="209"/>
-      <c r="R5" s="209"/>
-      <c r="S5" s="209"/>
-      <c r="T5" s="211"/>
+      <c r="H5" s="214"/>
+      <c r="I5" s="214"/>
+      <c r="J5" s="214"/>
+      <c r="K5" s="214"/>
+      <c r="L5" s="214"/>
+      <c r="M5" s="214"/>
+      <c r="N5" s="214"/>
+      <c r="O5" s="214"/>
+      <c r="P5" s="214"/>
+      <c r="Q5" s="214"/>
+      <c r="R5" s="214"/>
+      <c r="S5" s="214"/>
+      <c r="T5" s="215"/>
     </row>
     <row r="6" spans="1:26" ht="18" customHeight="1">
-      <c r="A6" s="212" t="s">
+      <c r="A6" s="218" t="s">
         <v>35</v>
       </c>
       <c r="B6" s="84"/>
@@ -18680,7 +18740,7 @@
       <c r="D6" s="84"/>
       <c r="E6" s="84"/>
       <c r="F6" s="85"/>
-      <c r="G6" s="213" t="s">
+      <c r="G6" s="219" t="s">
         <v>19</v>
       </c>
       <c r="H6" s="84"/>
@@ -18695,10 +18755,10 @@
       <c r="Q6" s="84"/>
       <c r="R6" s="84"/>
       <c r="S6" s="84"/>
-      <c r="T6" s="214"/>
+      <c r="T6" s="220"/>
     </row>
     <row r="7" spans="1:26" ht="18" customHeight="1">
-      <c r="A7" s="212" t="s">
+      <c r="A7" s="218" t="s">
         <v>36</v>
       </c>
       <c r="B7" s="84"/>
@@ -18706,7 +18766,7 @@
       <c r="D7" s="84"/>
       <c r="E7" s="84"/>
       <c r="F7" s="85"/>
-      <c r="G7" s="213" t="s">
+      <c r="G7" s="219" t="s">
         <v>111</v>
       </c>
       <c r="H7" s="84"/>
@@ -18721,7 +18781,7 @@
       <c r="Q7" s="84"/>
       <c r="R7" s="84"/>
       <c r="S7" s="84"/>
-      <c r="T7" s="214"/>
+      <c r="T7" s="220"/>
     </row>
     <row r="8" spans="1:26" ht="7.5" customHeight="1">
       <c r="A8" s="7"/>
@@ -18920,33 +18980,33 @@
       <c r="T14" s="9"/>
     </row>
     <row r="15" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A15" s="212" t="s">
+      <c r="A15" s="218" t="s">
         <v>43</v>
       </c>
       <c r="B15" s="85"/>
-      <c r="C15" s="218" t="s">
+      <c r="C15" s="224" t="s">
         <v>37</v>
       </c>
       <c r="D15" s="85"/>
-      <c r="E15" s="216" t="s">
+      <c r="E15" s="198" t="s">
         <v>44</v>
       </c>
       <c r="F15" s="85"/>
-      <c r="G15" s="216" t="s">
+      <c r="G15" s="198" t="s">
         <v>45</v>
       </c>
       <c r="H15" s="84"/>
       <c r="I15" s="85"/>
-      <c r="J15" s="216" t="s">
+      <c r="J15" s="198" t="s">
         <v>46</v>
       </c>
       <c r="K15" s="85"/>
-      <c r="L15" s="216" t="s">
+      <c r="L15" s="198" t="s">
         <v>47</v>
       </c>
       <c r="M15" s="84"/>
       <c r="N15" s="85"/>
-      <c r="O15" s="216" t="s">
+      <c r="O15" s="198" t="s">
         <v>48</v>
       </c>
       <c r="P15" s="84"/>
@@ -18962,33 +19022,33 @@
       </c>
     </row>
     <row r="16" spans="1:26" ht="48" customHeight="1">
-      <c r="A16" s="198">
+      <c r="A16" s="221">
         <v>1</v>
       </c>
       <c r="B16" s="85"/>
-      <c r="C16" s="199" t="s">
+      <c r="C16" s="222" t="s">
         <v>52</v>
       </c>
       <c r="D16" s="85"/>
-      <c r="E16" s="199" t="s">
+      <c r="E16" s="222" t="s">
         <v>53</v>
       </c>
       <c r="F16" s="85"/>
-      <c r="G16" s="215" t="s">
+      <c r="G16" s="199" t="s">
         <v>112</v>
       </c>
       <c r="H16" s="84"/>
       <c r="I16" s="85"/>
-      <c r="J16" s="228" t="s">
+      <c r="J16" s="200" t="s">
         <v>113</v>
       </c>
-      <c r="K16" s="93"/>
-      <c r="L16" s="205" t="s">
+      <c r="K16" s="112"/>
+      <c r="L16" s="204" t="s">
         <v>114</v>
       </c>
       <c r="M16" s="84"/>
       <c r="N16" s="85"/>
-      <c r="O16" s="205" t="s">
+      <c r="O16" s="204" t="s">
         <v>115</v>
       </c>
       <c r="P16" s="84"/>
@@ -19010,33 +19070,33 @@
       <c r="Z16" s="29"/>
     </row>
     <row r="17" spans="1:26" ht="51" customHeight="1">
-      <c r="A17" s="198">
+      <c r="A17" s="221">
         <v>2</v>
       </c>
       <c r="B17" s="85"/>
-      <c r="C17" s="199" t="s">
+      <c r="C17" s="222" t="s">
         <v>52</v>
       </c>
       <c r="D17" s="85"/>
-      <c r="E17" s="199" t="s">
+      <c r="E17" s="222" t="s">
         <v>118</v>
       </c>
       <c r="F17" s="85"/>
-      <c r="G17" s="215" t="s">
+      <c r="G17" s="199" t="s">
         <v>116</v>
       </c>
       <c r="H17" s="84"/>
       <c r="I17" s="85"/>
-      <c r="J17" s="215" t="s">
+      <c r="J17" s="199" t="s">
         <v>117</v>
       </c>
       <c r="K17" s="85"/>
-      <c r="L17" s="217" t="s">
+      <c r="L17" s="223" t="s">
         <v>119</v>
       </c>
       <c r="M17" s="84"/>
       <c r="N17" s="85"/>
-      <c r="O17" s="205" t="s">
+      <c r="O17" s="204" t="s">
         <v>122</v>
       </c>
       <c r="P17" s="84"/>
@@ -19058,33 +19118,33 @@
       <c r="Z17" s="29"/>
     </row>
     <row r="18" spans="1:26" ht="120" customHeight="1">
-      <c r="A18" s="198">
+      <c r="A18" s="221">
         <v>3</v>
       </c>
       <c r="B18" s="85"/>
-      <c r="C18" s="199" t="s">
+      <c r="C18" s="222" t="s">
         <v>52</v>
       </c>
       <c r="D18" s="85"/>
-      <c r="E18" s="199" t="s">
+      <c r="E18" s="222" t="s">
         <v>53</v>
       </c>
       <c r="F18" s="85"/>
-      <c r="G18" s="215" t="s">
+      <c r="G18" s="199" t="s">
         <v>139</v>
       </c>
       <c r="H18" s="84"/>
       <c r="I18" s="85"/>
-      <c r="J18" s="215" t="s">
+      <c r="J18" s="199" t="s">
         <v>140</v>
       </c>
       <c r="K18" s="85"/>
-      <c r="L18" s="205" t="s">
+      <c r="L18" s="204" t="s">
         <v>114</v>
       </c>
       <c r="M18" s="84"/>
       <c r="N18" s="85"/>
-      <c r="O18" s="205" t="s">
+      <c r="O18" s="204" t="s">
         <v>120</v>
       </c>
       <c r="P18" s="84"/>
@@ -19106,33 +19166,33 @@
       <c r="Z18" s="29"/>
     </row>
     <row r="19" spans="1:26" ht="94.5" customHeight="1">
-      <c r="A19" s="198">
+      <c r="A19" s="221">
         <v>4</v>
       </c>
       <c r="B19" s="85"/>
-      <c r="C19" s="199" t="s">
+      <c r="C19" s="222" t="s">
         <v>52</v>
       </c>
       <c r="D19" s="85"/>
-      <c r="E19" s="199" t="s">
+      <c r="E19" s="222" t="s">
         <v>118</v>
       </c>
       <c r="F19" s="85"/>
-      <c r="G19" s="215" t="s">
+      <c r="G19" s="199" t="s">
         <v>141</v>
       </c>
       <c r="H19" s="84"/>
       <c r="I19" s="85"/>
-      <c r="J19" s="215" t="s">
+      <c r="J19" s="199" t="s">
         <v>142</v>
       </c>
       <c r="K19" s="85"/>
-      <c r="L19" s="205" t="s">
+      <c r="L19" s="204" t="s">
         <v>114</v>
       </c>
       <c r="M19" s="84"/>
       <c r="N19" s="85"/>
-      <c r="O19" s="205" t="s">
+      <c r="O19" s="204" t="s">
         <v>121</v>
       </c>
       <c r="P19" s="84"/>
@@ -19154,33 +19214,33 @@
       <c r="Z19" s="29"/>
     </row>
     <row r="20" spans="1:26" ht="120" customHeight="1">
-      <c r="A20" s="198">
+      <c r="A20" s="221">
         <v>5</v>
       </c>
       <c r="B20" s="85"/>
-      <c r="C20" s="199" t="s">
+      <c r="C20" s="222" t="s">
         <v>138</v>
       </c>
       <c r="D20" s="85"/>
-      <c r="E20" s="199" t="s">
+      <c r="E20" s="222" t="s">
         <v>143</v>
       </c>
       <c r="F20" s="85"/>
-      <c r="G20" s="215" t="s">
+      <c r="G20" s="199" t="s">
         <v>146</v>
       </c>
       <c r="H20" s="84"/>
       <c r="I20" s="85"/>
-      <c r="J20" s="215" t="s">
+      <c r="J20" s="199" t="s">
         <v>145</v>
       </c>
       <c r="K20" s="85"/>
-      <c r="L20" s="205" t="s">
+      <c r="L20" s="204" t="s">
         <v>114</v>
       </c>
       <c r="M20" s="84"/>
       <c r="N20" s="85"/>
-      <c r="O20" s="205" t="s">
+      <c r="O20" s="204" t="s">
         <v>120</v>
       </c>
       <c r="P20" s="84"/>
@@ -19200,33 +19260,33 @@
       <c r="Z20" s="29"/>
     </row>
     <row r="21" spans="1:26" ht="75" customHeight="1">
-      <c r="A21" s="198">
+      <c r="A21" s="221">
         <v>6</v>
       </c>
       <c r="B21" s="85"/>
-      <c r="C21" s="199" t="s">
+      <c r="C21" s="222" t="s">
         <v>138</v>
       </c>
       <c r="D21" s="85"/>
-      <c r="E21" s="199" t="s">
+      <c r="E21" s="222" t="s">
         <v>118</v>
       </c>
       <c r="F21" s="85"/>
-      <c r="G21" s="215" t="s">
+      <c r="G21" s="199" t="s">
         <v>154</v>
       </c>
       <c r="H21" s="84"/>
       <c r="I21" s="85"/>
-      <c r="J21" s="215" t="s">
+      <c r="J21" s="199" t="s">
         <v>144</v>
       </c>
       <c r="K21" s="85"/>
-      <c r="L21" s="205" t="s">
+      <c r="L21" s="204" t="s">
         <v>114</v>
       </c>
       <c r="M21" s="84"/>
       <c r="N21" s="85"/>
-      <c r="O21" s="205" t="s">
+      <c r="O21" s="204" t="s">
         <v>121</v>
       </c>
       <c r="P21" s="84"/>
@@ -19248,33 +19308,33 @@
       <c r="Z21" s="29"/>
     </row>
     <row r="22" spans="1:26" ht="57" customHeight="1">
-      <c r="A22" s="203">
+      <c r="A22" s="225">
         <v>7</v>
       </c>
-      <c r="B22" s="93"/>
-      <c r="C22" s="204" t="s">
+      <c r="B22" s="112"/>
+      <c r="C22" s="226" t="s">
         <v>52</v>
       </c>
-      <c r="D22" s="93"/>
-      <c r="E22" s="204" t="s">
+      <c r="D22" s="112"/>
+      <c r="E22" s="226" t="s">
         <v>165</v>
       </c>
-      <c r="F22" s="93"/>
-      <c r="G22" s="228" t="s">
+      <c r="F22" s="112"/>
+      <c r="G22" s="200" t="s">
         <v>166</v>
       </c>
-      <c r="H22" s="98"/>
-      <c r="I22" s="93"/>
-      <c r="J22" s="228" t="s">
+      <c r="H22" s="111"/>
+      <c r="I22" s="112"/>
+      <c r="J22" s="200" t="s">
         <v>117</v>
       </c>
-      <c r="K22" s="93"/>
-      <c r="L22" s="225" t="s">
+      <c r="K22" s="112"/>
+      <c r="L22" s="206" t="s">
         <v>119</v>
       </c>
-      <c r="M22" s="226"/>
-      <c r="N22" s="226"/>
-      <c r="O22" s="205" t="s">
+      <c r="M22" s="207"/>
+      <c r="N22" s="207"/>
+      <c r="O22" s="204" t="s">
         <v>167</v>
       </c>
       <c r="P22" s="84"/>
@@ -19295,27 +19355,47 @@
       <c r="Y22" s="29"/>
       <c r="Z22" s="29"/>
     </row>
-    <row r="23" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A23" s="198"/>
-      <c r="B23" s="85"/>
-      <c r="C23" s="199"/>
-      <c r="D23" s="85"/>
-      <c r="E23" s="199"/>
+    <row r="23" spans="1:26" ht="88.5" customHeight="1">
+      <c r="A23" s="225">
+        <v>8</v>
+      </c>
+      <c r="B23" s="112"/>
+      <c r="C23" s="226" t="s">
+        <v>52</v>
+      </c>
+      <c r="D23" s="112"/>
+      <c r="E23" s="222" t="s">
+        <v>143</v>
+      </c>
       <c r="F23" s="85"/>
-      <c r="G23" s="215"/>
+      <c r="G23" s="199" t="s">
+        <v>169</v>
+      </c>
       <c r="H23" s="84"/>
       <c r="I23" s="85"/>
-      <c r="J23" s="215"/>
+      <c r="J23" s="199" t="s">
+        <v>170</v>
+      </c>
       <c r="K23" s="85"/>
-      <c r="L23" s="205"/>
+      <c r="L23" s="204" t="s">
+        <v>171</v>
+      </c>
       <c r="M23" s="84"/>
       <c r="N23" s="85"/>
-      <c r="O23" s="205"/>
+      <c r="O23" s="204" t="s">
+        <v>115</v>
+      </c>
       <c r="P23" s="84"/>
       <c r="Q23" s="85"/>
-      <c r="R23" s="27"/>
-      <c r="S23" s="27"/>
-      <c r="T23" s="28"/>
+      <c r="R23" s="65">
+        <v>45826</v>
+      </c>
+      <c r="S23" s="27" t="s">
+        <v>110</v>
+      </c>
+      <c r="T23" s="28" t="s">
+        <v>168</v>
+      </c>
       <c r="U23" s="29"/>
       <c r="V23" s="29"/>
       <c r="W23" s="29"/>
@@ -19324,21 +19404,21 @@
       <c r="Z23" s="29"/>
     </row>
     <row r="24" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A24" s="198"/>
+      <c r="A24" s="221"/>
       <c r="B24" s="85"/>
-      <c r="C24" s="199"/>
+      <c r="C24" s="222"/>
       <c r="D24" s="85"/>
-      <c r="E24" s="199"/>
+      <c r="E24" s="222"/>
       <c r="F24" s="85"/>
-      <c r="G24" s="215"/>
+      <c r="G24" s="199"/>
       <c r="H24" s="84"/>
       <c r="I24" s="85"/>
-      <c r="J24" s="215"/>
+      <c r="J24" s="199"/>
       <c r="K24" s="85"/>
-      <c r="L24" s="205"/>
+      <c r="L24" s="204"/>
       <c r="M24" s="84"/>
       <c r="N24" s="85"/>
-      <c r="O24" s="205"/>
+      <c r="O24" s="204"/>
       <c r="P24" s="84"/>
       <c r="Q24" s="85"/>
       <c r="R24" s="27"/>
@@ -19352,21 +19432,21 @@
       <c r="Z24" s="29"/>
     </row>
     <row r="25" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A25" s="198"/>
+      <c r="A25" s="221"/>
       <c r="B25" s="85"/>
-      <c r="C25" s="199"/>
+      <c r="C25" s="222"/>
       <c r="D25" s="85"/>
-      <c r="E25" s="199"/>
+      <c r="E25" s="222"/>
       <c r="F25" s="85"/>
-      <c r="G25" s="215"/>
+      <c r="G25" s="199"/>
       <c r="H25" s="84"/>
       <c r="I25" s="85"/>
-      <c r="J25" s="215"/>
+      <c r="J25" s="199"/>
       <c r="K25" s="85"/>
-      <c r="L25" s="205"/>
+      <c r="L25" s="204"/>
       <c r="M25" s="84"/>
       <c r="N25" s="85"/>
-      <c r="O25" s="205"/>
+      <c r="O25" s="204"/>
       <c r="P25" s="84"/>
       <c r="Q25" s="85"/>
       <c r="R25" s="27"/>
@@ -19380,21 +19460,21 @@
       <c r="Z25" s="29"/>
     </row>
     <row r="26" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A26" s="198"/>
+      <c r="A26" s="221"/>
       <c r="B26" s="85"/>
-      <c r="C26" s="199"/>
+      <c r="C26" s="222"/>
       <c r="D26" s="85"/>
-      <c r="E26" s="199"/>
+      <c r="E26" s="222"/>
       <c r="F26" s="85"/>
-      <c r="G26" s="215"/>
+      <c r="G26" s="199"/>
       <c r="H26" s="84"/>
       <c r="I26" s="85"/>
-      <c r="J26" s="215"/>
+      <c r="J26" s="199"/>
       <c r="K26" s="85"/>
-      <c r="L26" s="205"/>
+      <c r="L26" s="204"/>
       <c r="M26" s="84"/>
       <c r="N26" s="85"/>
-      <c r="O26" s="205"/>
+      <c r="O26" s="204"/>
       <c r="P26" s="84"/>
       <c r="Q26" s="85"/>
       <c r="R26" s="27"/>
@@ -19408,21 +19488,21 @@
       <c r="Z26" s="29"/>
     </row>
     <row r="27" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A27" s="198"/>
+      <c r="A27" s="221"/>
       <c r="B27" s="85"/>
-      <c r="C27" s="199"/>
+      <c r="C27" s="222"/>
       <c r="D27" s="85"/>
-      <c r="E27" s="199"/>
+      <c r="E27" s="222"/>
       <c r="F27" s="85"/>
-      <c r="G27" s="215"/>
+      <c r="G27" s="199"/>
       <c r="H27" s="84"/>
       <c r="I27" s="85"/>
-      <c r="J27" s="215"/>
+      <c r="J27" s="199"/>
       <c r="K27" s="85"/>
-      <c r="L27" s="205"/>
+      <c r="L27" s="204"/>
       <c r="M27" s="84"/>
       <c r="N27" s="85"/>
-      <c r="O27" s="205"/>
+      <c r="O27" s="204"/>
       <c r="P27" s="84"/>
       <c r="Q27" s="85"/>
       <c r="R27" s="27"/>
@@ -19436,21 +19516,21 @@
       <c r="Z27" s="29"/>
     </row>
     <row r="28" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A28" s="198"/>
+      <c r="A28" s="221"/>
       <c r="B28" s="85"/>
-      <c r="C28" s="199"/>
+      <c r="C28" s="222"/>
       <c r="D28" s="85"/>
-      <c r="E28" s="199"/>
+      <c r="E28" s="222"/>
       <c r="F28" s="85"/>
-      <c r="G28" s="215"/>
+      <c r="G28" s="199"/>
       <c r="H28" s="84"/>
       <c r="I28" s="85"/>
-      <c r="J28" s="215"/>
+      <c r="J28" s="199"/>
       <c r="K28" s="85"/>
-      <c r="L28" s="205"/>
+      <c r="L28" s="204"/>
       <c r="M28" s="84"/>
       <c r="N28" s="85"/>
-      <c r="O28" s="205"/>
+      <c r="O28" s="204"/>
       <c r="P28" s="84"/>
       <c r="Q28" s="85"/>
       <c r="R28" s="27"/>
@@ -19464,21 +19544,21 @@
       <c r="Z28" s="29"/>
     </row>
     <row r="29" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A29" s="198"/>
+      <c r="A29" s="221"/>
       <c r="B29" s="85"/>
-      <c r="C29" s="199"/>
+      <c r="C29" s="222"/>
       <c r="D29" s="85"/>
-      <c r="E29" s="199"/>
+      <c r="E29" s="222"/>
       <c r="F29" s="85"/>
-      <c r="G29" s="215"/>
+      <c r="G29" s="199"/>
       <c r="H29" s="84"/>
       <c r="I29" s="85"/>
-      <c r="J29" s="215"/>
+      <c r="J29" s="199"/>
       <c r="K29" s="85"/>
-      <c r="L29" s="205"/>
+      <c r="L29" s="204"/>
       <c r="M29" s="84"/>
       <c r="N29" s="85"/>
-      <c r="O29" s="205"/>
+      <c r="O29" s="204"/>
       <c r="P29" s="84"/>
       <c r="Q29" s="85"/>
       <c r="R29" s="27"/>
@@ -19492,21 +19572,21 @@
       <c r="Z29" s="29"/>
     </row>
     <row r="30" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A30" s="198"/>
+      <c r="A30" s="221"/>
       <c r="B30" s="85"/>
-      <c r="C30" s="199"/>
+      <c r="C30" s="222"/>
       <c r="D30" s="85"/>
-      <c r="E30" s="199"/>
+      <c r="E30" s="222"/>
       <c r="F30" s="85"/>
-      <c r="G30" s="215"/>
+      <c r="G30" s="199"/>
       <c r="H30" s="84"/>
       <c r="I30" s="85"/>
-      <c r="J30" s="215"/>
+      <c r="J30" s="199"/>
       <c r="K30" s="85"/>
-      <c r="L30" s="205"/>
+      <c r="L30" s="204"/>
       <c r="M30" s="84"/>
       <c r="N30" s="85"/>
-      <c r="O30" s="205"/>
+      <c r="O30" s="204"/>
       <c r="P30" s="84"/>
       <c r="Q30" s="85"/>
       <c r="R30" s="27"/>
@@ -19520,23 +19600,23 @@
       <c r="Z30" s="29"/>
     </row>
     <row r="31" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A31" s="200"/>
-      <c r="B31" s="201"/>
-      <c r="C31" s="202"/>
-      <c r="D31" s="201"/>
-      <c r="E31" s="202"/>
-      <c r="F31" s="201"/>
-      <c r="G31" s="227"/>
-      <c r="H31" s="207"/>
-      <c r="I31" s="201"/>
-      <c r="J31" s="227"/>
-      <c r="K31" s="201"/>
-      <c r="L31" s="206"/>
-      <c r="M31" s="207"/>
-      <c r="N31" s="201"/>
-      <c r="O31" s="206"/>
-      <c r="P31" s="207"/>
-      <c r="Q31" s="201"/>
+      <c r="A31" s="227"/>
+      <c r="B31" s="203"/>
+      <c r="C31" s="228"/>
+      <c r="D31" s="203"/>
+      <c r="E31" s="228"/>
+      <c r="F31" s="203"/>
+      <c r="G31" s="201"/>
+      <c r="H31" s="202"/>
+      <c r="I31" s="203"/>
+      <c r="J31" s="201"/>
+      <c r="K31" s="203"/>
+      <c r="L31" s="205"/>
+      <c r="M31" s="202"/>
+      <c r="N31" s="203"/>
+      <c r="O31" s="205"/>
+      <c r="P31" s="202"/>
+      <c r="Q31" s="203"/>
       <c r="R31" s="30"/>
       <c r="S31" s="30"/>
       <c r="T31" s="31"/>
@@ -20534,62 +20614,62 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="136">
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="J18:K18"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="J19:K19"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="G23:I23"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="J30:K30"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="J29:K29"/>
-    <mergeCell ref="L26:N26"/>
-    <mergeCell ref="L27:N27"/>
-    <mergeCell ref="L28:N28"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="L18:N18"/>
-    <mergeCell ref="L19:N19"/>
-    <mergeCell ref="L21:N21"/>
-    <mergeCell ref="L22:N22"/>
-    <mergeCell ref="L23:N23"/>
-    <mergeCell ref="L24:N24"/>
-    <mergeCell ref="L25:N25"/>
-    <mergeCell ref="K2:N4"/>
-    <mergeCell ref="O2:P4"/>
-    <mergeCell ref="Q2:R4"/>
-    <mergeCell ref="S2:T4"/>
-    <mergeCell ref="A1:F4"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="O1:P1"/>
-    <mergeCell ref="Q1:R1"/>
-    <mergeCell ref="S1:T1"/>
-    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="E30:F30"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="E31:F31"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="E26:F26"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="E29:F29"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="E27:F27"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="E28:F28"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="O27:Q27"/>
+    <mergeCell ref="O28:Q28"/>
+    <mergeCell ref="O29:Q29"/>
+    <mergeCell ref="O30:Q30"/>
+    <mergeCell ref="O31:Q31"/>
+    <mergeCell ref="O19:Q19"/>
+    <mergeCell ref="O21:Q21"/>
+    <mergeCell ref="O22:Q22"/>
+    <mergeCell ref="O23:Q23"/>
+    <mergeCell ref="O24:Q24"/>
+    <mergeCell ref="O25:Q25"/>
+    <mergeCell ref="O26:Q26"/>
     <mergeCell ref="A5:F5"/>
     <mergeCell ref="G5:T5"/>
     <mergeCell ref="A6:F6"/>
@@ -20614,62 +20694,62 @@
     <mergeCell ref="C15:D15"/>
     <mergeCell ref="E15:F15"/>
     <mergeCell ref="A16:B16"/>
-    <mergeCell ref="O27:Q27"/>
-    <mergeCell ref="O28:Q28"/>
-    <mergeCell ref="O29:Q29"/>
-    <mergeCell ref="O30:Q30"/>
-    <mergeCell ref="O31:Q31"/>
-    <mergeCell ref="O19:Q19"/>
-    <mergeCell ref="O21:Q21"/>
-    <mergeCell ref="O22:Q22"/>
-    <mergeCell ref="O23:Q23"/>
-    <mergeCell ref="O24:Q24"/>
-    <mergeCell ref="O25:Q25"/>
-    <mergeCell ref="O26:Q26"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="E30:F30"/>
-    <mergeCell ref="A31:B31"/>
-    <mergeCell ref="C31:D31"/>
-    <mergeCell ref="E31:F31"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="E26:F26"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="E24:F24"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="E29:F29"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="E27:F27"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="E28:F28"/>
-    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="K2:N4"/>
+    <mergeCell ref="O2:P4"/>
+    <mergeCell ref="Q2:R4"/>
+    <mergeCell ref="S2:T4"/>
+    <mergeCell ref="A1:F4"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="S1:T1"/>
+    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="L26:N26"/>
+    <mergeCell ref="L27:N27"/>
+    <mergeCell ref="L28:N28"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="L18:N18"/>
+    <mergeCell ref="L19:N19"/>
+    <mergeCell ref="L21:N21"/>
+    <mergeCell ref="L22:N22"/>
+    <mergeCell ref="L23:N23"/>
+    <mergeCell ref="L24:N24"/>
+    <mergeCell ref="L25:N25"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="J30:K30"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="J29:K29"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="J19:K19"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <hyperlinks>
@@ -20696,72 +20776,72 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="18.75" customHeight="1">
-      <c r="A1" s="238" t="s">
+      <c r="A1" s="249" t="s">
         <v>123</v>
       </c>
-      <c r="B1" s="238"/>
-      <c r="C1" s="239" t="s">
+      <c r="B1" s="249"/>
+      <c r="C1" s="250" t="s">
         <v>124</v>
       </c>
-      <c r="D1" s="240"/>
-      <c r="E1" s="241"/>
-      <c r="F1" s="242" t="s">
+      <c r="D1" s="251"/>
+      <c r="E1" s="252"/>
+      <c r="F1" s="253" t="s">
         <v>84</v>
       </c>
-      <c r="G1" s="243"/>
-      <c r="H1" s="243"/>
-      <c r="I1" s="243"/>
-      <c r="J1" s="243"/>
-      <c r="K1" s="243"/>
-      <c r="L1" s="243"/>
-      <c r="M1" s="244"/>
+      <c r="G1" s="254"/>
+      <c r="H1" s="254"/>
+      <c r="I1" s="254"/>
+      <c r="J1" s="254"/>
+      <c r="K1" s="254"/>
+      <c r="L1" s="254"/>
+      <c r="M1" s="255"/>
       <c r="N1" s="51" t="s">
         <v>125</v>
       </c>
-      <c r="O1" s="242" t="s">
+      <c r="O1" s="253" t="s">
         <v>83</v>
       </c>
-      <c r="P1" s="244"/>
+      <c r="P1" s="255"/>
       <c r="Q1" s="51" t="s">
         <v>126</v>
       </c>
-      <c r="R1" s="242" t="s">
+      <c r="R1" s="253" t="s">
         <v>127</v>
       </c>
-      <c r="S1" s="244"/>
+      <c r="S1" s="255"/>
     </row>
     <row r="2" spans="1:19" ht="18.75" customHeight="1">
-      <c r="A2" s="238"/>
-      <c r="B2" s="238"/>
-      <c r="C2" s="239" t="s">
+      <c r="A2" s="249"/>
+      <c r="B2" s="249"/>
+      <c r="C2" s="250" t="s">
         <v>128</v>
       </c>
-      <c r="D2" s="240"/>
-      <c r="E2" s="241"/>
-      <c r="F2" s="242" t="s">
+      <c r="D2" s="251"/>
+      <c r="E2" s="252"/>
+      <c r="F2" s="253" t="s">
         <v>147</v>
       </c>
-      <c r="G2" s="243"/>
-      <c r="H2" s="243"/>
-      <c r="I2" s="243"/>
-      <c r="J2" s="243"/>
-      <c r="K2" s="243"/>
-      <c r="L2" s="243"/>
-      <c r="M2" s="244"/>
+      <c r="G2" s="254"/>
+      <c r="H2" s="254"/>
+      <c r="I2" s="254"/>
+      <c r="J2" s="254"/>
+      <c r="K2" s="254"/>
+      <c r="L2" s="254"/>
+      <c r="M2" s="255"/>
       <c r="N2" s="51" t="s">
         <v>129</v>
       </c>
-      <c r="O2" s="245">
+      <c r="O2" s="256">
         <v>45824</v>
       </c>
-      <c r="P2" s="246"/>
+      <c r="P2" s="257"/>
       <c r="Q2" s="53" t="s">
         <v>130</v>
       </c>
-      <c r="R2" s="247">
+      <c r="R2" s="258">
         <v>44771</v>
       </c>
-      <c r="S2" s="248"/>
+      <c r="S2" s="259"/>
     </row>
     <row r="3" spans="1:19" ht="11.25" customHeight="1">
       <c r="A3" s="54"/>
@@ -20791,33 +20871,33 @@
       <c r="B4" s="57" t="s">
         <v>132</v>
       </c>
-      <c r="C4" s="229" t="s">
+      <c r="C4" s="241" t="s">
         <v>133</v>
       </c>
-      <c r="D4" s="230"/>
-      <c r="E4" s="230"/>
-      <c r="F4" s="230"/>
-      <c r="G4" s="231"/>
-      <c r="H4" s="229" t="s">
+      <c r="D4" s="242"/>
+      <c r="E4" s="242"/>
+      <c r="F4" s="242"/>
+      <c r="G4" s="243"/>
+      <c r="H4" s="241" t="s">
         <v>134</v>
       </c>
-      <c r="I4" s="230"/>
-      <c r="J4" s="230"/>
-      <c r="K4" s="230"/>
-      <c r="L4" s="230"/>
-      <c r="M4" s="231"/>
-      <c r="N4" s="229" t="s">
+      <c r="I4" s="242"/>
+      <c r="J4" s="242"/>
+      <c r="K4" s="242"/>
+      <c r="L4" s="242"/>
+      <c r="M4" s="243"/>
+      <c r="N4" s="241" t="s">
         <v>135</v>
       </c>
-      <c r="O4" s="230"/>
-      <c r="P4" s="231"/>
+      <c r="O4" s="242"/>
+      <c r="P4" s="243"/>
       <c r="Q4" s="56" t="s">
         <v>136</v>
       </c>
-      <c r="R4" s="229" t="s">
+      <c r="R4" s="241" t="s">
         <v>137</v>
       </c>
-      <c r="S4" s="231"/>
+      <c r="S4" s="243"/>
     </row>
     <row r="5" spans="1:19" ht="50.1" customHeight="1">
       <c r="A5" s="58">
@@ -20826,31 +20906,31 @@
       <c r="B5" s="59" t="s">
         <v>148</v>
       </c>
-      <c r="C5" s="232" t="s">
+      <c r="C5" s="237" t="s">
         <v>150</v>
       </c>
-      <c r="D5" s="232"/>
-      <c r="E5" s="232"/>
-      <c r="F5" s="232"/>
-      <c r="G5" s="232"/>
-      <c r="H5" s="232" t="s">
+      <c r="D5" s="237"/>
+      <c r="E5" s="237"/>
+      <c r="F5" s="237"/>
+      <c r="G5" s="237"/>
+      <c r="H5" s="237" t="s">
         <v>149</v>
       </c>
-      <c r="I5" s="232"/>
-      <c r="J5" s="232"/>
-      <c r="K5" s="232"/>
-      <c r="L5" s="232"/>
-      <c r="M5" s="232"/>
-      <c r="N5" s="233" t="s">
+      <c r="I5" s="237"/>
+      <c r="J5" s="237"/>
+      <c r="K5" s="237"/>
+      <c r="L5" s="237"/>
+      <c r="M5" s="237"/>
+      <c r="N5" s="244" t="s">
         <v>151</v>
       </c>
-      <c r="O5" s="234"/>
-      <c r="P5" s="235"/>
+      <c r="O5" s="245"/>
+      <c r="P5" s="246"/>
       <c r="Q5" s="64">
         <v>45824</v>
       </c>
-      <c r="R5" s="236"/>
-      <c r="S5" s="237"/>
+      <c r="R5" s="247"/>
+      <c r="S5" s="248"/>
     </row>
     <row r="6" spans="1:19" ht="30" customHeight="1">
       <c r="A6" s="60">
@@ -20859,31 +20939,31 @@
       <c r="B6" s="59" t="s">
         <v>148</v>
       </c>
-      <c r="C6" s="232" t="s">
+      <c r="C6" s="237" t="s">
         <v>150</v>
       </c>
-      <c r="D6" s="232"/>
-      <c r="E6" s="232"/>
-      <c r="F6" s="232"/>
-      <c r="G6" s="232"/>
-      <c r="H6" s="232" t="s">
+      <c r="D6" s="237"/>
+      <c r="E6" s="237"/>
+      <c r="F6" s="237"/>
+      <c r="G6" s="237"/>
+      <c r="H6" s="237" t="s">
         <v>149</v>
       </c>
-      <c r="I6" s="232"/>
-      <c r="J6" s="232"/>
-      <c r="K6" s="232"/>
-      <c r="L6" s="232"/>
-      <c r="M6" s="232"/>
-      <c r="N6" s="254" t="s">
+      <c r="I6" s="237"/>
+      <c r="J6" s="237"/>
+      <c r="K6" s="237"/>
+      <c r="L6" s="237"/>
+      <c r="M6" s="237"/>
+      <c r="N6" s="238" t="s">
         <v>152</v>
       </c>
-      <c r="O6" s="255"/>
-      <c r="P6" s="256"/>
+      <c r="O6" s="239"/>
+      <c r="P6" s="240"/>
       <c r="Q6" s="64">
         <v>45824</v>
       </c>
-      <c r="R6" s="253"/>
-      <c r="S6" s="253"/>
+      <c r="R6" s="236"/>
+      <c r="S6" s="236"/>
     </row>
     <row r="7" spans="1:19" ht="30" customHeight="1">
       <c r="A7" s="60">
@@ -20892,1167 +20972,979 @@
       <c r="B7" s="63" t="s">
         <v>118</v>
       </c>
-      <c r="C7" s="232" t="s">
+      <c r="C7" s="237" t="s">
         <v>150</v>
       </c>
-      <c r="D7" s="232"/>
-      <c r="E7" s="232"/>
-      <c r="F7" s="232"/>
-      <c r="G7" s="232"/>
-      <c r="H7" s="232" t="s">
+      <c r="D7" s="237"/>
+      <c r="E7" s="237"/>
+      <c r="F7" s="237"/>
+      <c r="G7" s="237"/>
+      <c r="H7" s="237" t="s">
         <v>149</v>
       </c>
-      <c r="I7" s="232"/>
-      <c r="J7" s="232"/>
-      <c r="K7" s="232"/>
-      <c r="L7" s="232"/>
-      <c r="M7" s="232"/>
-      <c r="N7" s="250" t="s">
+      <c r="I7" s="237"/>
+      <c r="J7" s="237"/>
+      <c r="K7" s="237"/>
+      <c r="L7" s="237"/>
+      <c r="M7" s="237"/>
+      <c r="N7" s="233" t="s">
         <v>153</v>
       </c>
-      <c r="O7" s="251"/>
-      <c r="P7" s="252"/>
+      <c r="O7" s="234"/>
+      <c r="P7" s="235"/>
       <c r="Q7" s="64">
         <v>45824</v>
       </c>
-      <c r="R7" s="253"/>
-      <c r="S7" s="253"/>
+      <c r="R7" s="236"/>
+      <c r="S7" s="236"/>
     </row>
     <row r="8" spans="1:19" ht="30" customHeight="1">
       <c r="A8" s="60"/>
       <c r="B8" s="60"/>
-      <c r="C8" s="249"/>
-      <c r="D8" s="249"/>
-      <c r="E8" s="249"/>
-      <c r="F8" s="249"/>
-      <c r="G8" s="249"/>
-      <c r="H8" s="249"/>
-      <c r="I8" s="249"/>
-      <c r="J8" s="249"/>
-      <c r="K8" s="249"/>
-      <c r="L8" s="249"/>
-      <c r="M8" s="249"/>
-      <c r="N8" s="250"/>
-      <c r="O8" s="251"/>
-      <c r="P8" s="252"/>
+      <c r="C8" s="229"/>
+      <c r="D8" s="229"/>
+      <c r="E8" s="229"/>
+      <c r="F8" s="229"/>
+      <c r="G8" s="229"/>
+      <c r="H8" s="229"/>
+      <c r="I8" s="229"/>
+      <c r="J8" s="229"/>
+      <c r="K8" s="229"/>
+      <c r="L8" s="229"/>
+      <c r="M8" s="229"/>
+      <c r="N8" s="233"/>
+      <c r="O8" s="234"/>
+      <c r="P8" s="235"/>
       <c r="Q8" s="61"/>
-      <c r="R8" s="253"/>
-      <c r="S8" s="253"/>
+      <c r="R8" s="236"/>
+      <c r="S8" s="236"/>
     </row>
     <row r="9" spans="1:19" ht="30" customHeight="1">
       <c r="A9" s="60"/>
       <c r="B9" s="60"/>
-      <c r="C9" s="249"/>
-      <c r="D9" s="249"/>
-      <c r="E9" s="249"/>
-      <c r="F9" s="249"/>
-      <c r="G9" s="249"/>
-      <c r="H9" s="249"/>
-      <c r="I9" s="249"/>
-      <c r="J9" s="249"/>
-      <c r="K9" s="249"/>
-      <c r="L9" s="249"/>
-      <c r="M9" s="249"/>
-      <c r="N9" s="250"/>
-      <c r="O9" s="251"/>
-      <c r="P9" s="252"/>
+      <c r="C9" s="229"/>
+      <c r="D9" s="229"/>
+      <c r="E9" s="229"/>
+      <c r="F9" s="229"/>
+      <c r="G9" s="229"/>
+      <c r="H9" s="229"/>
+      <c r="I9" s="229"/>
+      <c r="J9" s="229"/>
+      <c r="K9" s="229"/>
+      <c r="L9" s="229"/>
+      <c r="M9" s="229"/>
+      <c r="N9" s="233"/>
+      <c r="O9" s="234"/>
+      <c r="P9" s="235"/>
       <c r="Q9" s="60"/>
-      <c r="R9" s="253"/>
-      <c r="S9" s="253"/>
+      <c r="R9" s="236"/>
+      <c r="S9" s="236"/>
     </row>
     <row r="10" spans="1:19" ht="30" customHeight="1">
       <c r="A10" s="60"/>
       <c r="B10" s="60"/>
-      <c r="C10" s="249"/>
-      <c r="D10" s="249"/>
-      <c r="E10" s="249"/>
-      <c r="F10" s="249"/>
-      <c r="G10" s="249"/>
-      <c r="H10" s="257"/>
-      <c r="I10" s="258"/>
-      <c r="J10" s="258"/>
-      <c r="K10" s="258"/>
-      <c r="L10" s="258"/>
-      <c r="M10" s="259"/>
-      <c r="N10" s="250"/>
-      <c r="O10" s="251"/>
-      <c r="P10" s="252"/>
+      <c r="C10" s="229"/>
+      <c r="D10" s="229"/>
+      <c r="E10" s="229"/>
+      <c r="F10" s="229"/>
+      <c r="G10" s="229"/>
+      <c r="H10" s="230"/>
+      <c r="I10" s="231"/>
+      <c r="J10" s="231"/>
+      <c r="K10" s="231"/>
+      <c r="L10" s="231"/>
+      <c r="M10" s="232"/>
+      <c r="N10" s="233"/>
+      <c r="O10" s="234"/>
+      <c r="P10" s="235"/>
       <c r="Q10" s="61"/>
-      <c r="R10" s="253"/>
-      <c r="S10" s="253"/>
+      <c r="R10" s="236"/>
+      <c r="S10" s="236"/>
     </row>
     <row r="11" spans="1:19" ht="30" customHeight="1">
       <c r="A11" s="60"/>
       <c r="B11" s="60"/>
-      <c r="C11" s="249"/>
-      <c r="D11" s="249"/>
-      <c r="E11" s="249"/>
-      <c r="F11" s="249"/>
-      <c r="G11" s="249"/>
-      <c r="H11" s="257"/>
-      <c r="I11" s="258"/>
-      <c r="J11" s="258"/>
-      <c r="K11" s="258"/>
-      <c r="L11" s="258"/>
-      <c r="M11" s="259"/>
-      <c r="N11" s="250"/>
-      <c r="O11" s="251"/>
-      <c r="P11" s="252"/>
+      <c r="C11" s="229"/>
+      <c r="D11" s="229"/>
+      <c r="E11" s="229"/>
+      <c r="F11" s="229"/>
+      <c r="G11" s="229"/>
+      <c r="H11" s="230"/>
+      <c r="I11" s="231"/>
+      <c r="J11" s="231"/>
+      <c r="K11" s="231"/>
+      <c r="L11" s="231"/>
+      <c r="M11" s="232"/>
+      <c r="N11" s="233"/>
+      <c r="O11" s="234"/>
+      <c r="P11" s="235"/>
       <c r="Q11" s="60"/>
-      <c r="R11" s="253"/>
-      <c r="S11" s="253"/>
+      <c r="R11" s="236"/>
+      <c r="S11" s="236"/>
     </row>
     <row r="12" spans="1:19" ht="30" customHeight="1">
       <c r="A12" s="60"/>
       <c r="B12" s="60"/>
-      <c r="C12" s="249"/>
-      <c r="D12" s="249"/>
-      <c r="E12" s="249"/>
-      <c r="F12" s="249"/>
-      <c r="G12" s="249"/>
-      <c r="H12" s="257"/>
-      <c r="I12" s="258"/>
-      <c r="J12" s="258"/>
-      <c r="K12" s="258"/>
-      <c r="L12" s="258"/>
-      <c r="M12" s="259"/>
-      <c r="N12" s="250"/>
-      <c r="O12" s="251"/>
-      <c r="P12" s="252"/>
+      <c r="C12" s="229"/>
+      <c r="D12" s="229"/>
+      <c r="E12" s="229"/>
+      <c r="F12" s="229"/>
+      <c r="G12" s="229"/>
+      <c r="H12" s="230"/>
+      <c r="I12" s="231"/>
+      <c r="J12" s="231"/>
+      <c r="K12" s="231"/>
+      <c r="L12" s="231"/>
+      <c r="M12" s="232"/>
+      <c r="N12" s="233"/>
+      <c r="O12" s="234"/>
+      <c r="P12" s="235"/>
       <c r="Q12" s="60"/>
-      <c r="R12" s="253"/>
-      <c r="S12" s="253"/>
+      <c r="R12" s="236"/>
+      <c r="S12" s="236"/>
     </row>
     <row r="13" spans="1:19" ht="30" customHeight="1">
       <c r="A13" s="60"/>
       <c r="B13" s="60"/>
-      <c r="C13" s="249"/>
-      <c r="D13" s="249"/>
-      <c r="E13" s="249"/>
-      <c r="F13" s="249"/>
-      <c r="G13" s="249"/>
-      <c r="H13" s="257"/>
-      <c r="I13" s="258"/>
-      <c r="J13" s="258"/>
-      <c r="K13" s="258"/>
-      <c r="L13" s="258"/>
-      <c r="M13" s="259"/>
-      <c r="N13" s="250"/>
-      <c r="O13" s="251"/>
-      <c r="P13" s="252"/>
+      <c r="C13" s="229"/>
+      <c r="D13" s="229"/>
+      <c r="E13" s="229"/>
+      <c r="F13" s="229"/>
+      <c r="G13" s="229"/>
+      <c r="H13" s="230"/>
+      <c r="I13" s="231"/>
+      <c r="J13" s="231"/>
+      <c r="K13" s="231"/>
+      <c r="L13" s="231"/>
+      <c r="M13" s="232"/>
+      <c r="N13" s="233"/>
+      <c r="O13" s="234"/>
+      <c r="P13" s="235"/>
       <c r="Q13" s="60"/>
-      <c r="R13" s="253"/>
-      <c r="S13" s="253"/>
+      <c r="R13" s="236"/>
+      <c r="S13" s="236"/>
     </row>
     <row r="14" spans="1:19" ht="30" customHeight="1">
       <c r="A14" s="60"/>
       <c r="B14" s="60"/>
-      <c r="C14" s="249"/>
-      <c r="D14" s="249"/>
-      <c r="E14" s="249"/>
-      <c r="F14" s="249"/>
-      <c r="G14" s="249"/>
-      <c r="H14" s="257"/>
-      <c r="I14" s="258"/>
-      <c r="J14" s="258"/>
-      <c r="K14" s="258"/>
-      <c r="L14" s="258"/>
-      <c r="M14" s="259"/>
-      <c r="N14" s="250"/>
-      <c r="O14" s="251"/>
-      <c r="P14" s="252"/>
+      <c r="C14" s="229"/>
+      <c r="D14" s="229"/>
+      <c r="E14" s="229"/>
+      <c r="F14" s="229"/>
+      <c r="G14" s="229"/>
+      <c r="H14" s="230"/>
+      <c r="I14" s="231"/>
+      <c r="J14" s="231"/>
+      <c r="K14" s="231"/>
+      <c r="L14" s="231"/>
+      <c r="M14" s="232"/>
+      <c r="N14" s="233"/>
+      <c r="O14" s="234"/>
+      <c r="P14" s="235"/>
       <c r="Q14" s="60"/>
-      <c r="R14" s="253"/>
-      <c r="S14" s="253"/>
+      <c r="R14" s="236"/>
+      <c r="S14" s="236"/>
     </row>
     <row r="15" spans="1:19" ht="30" customHeight="1">
       <c r="A15" s="60"/>
       <c r="B15" s="60"/>
-      <c r="C15" s="249"/>
-      <c r="D15" s="249"/>
-      <c r="E15" s="249"/>
-      <c r="F15" s="249"/>
-      <c r="G15" s="249"/>
-      <c r="H15" s="257"/>
-      <c r="I15" s="258"/>
-      <c r="J15" s="258"/>
-      <c r="K15" s="258"/>
-      <c r="L15" s="258"/>
-      <c r="M15" s="259"/>
-      <c r="N15" s="250"/>
-      <c r="O15" s="251"/>
-      <c r="P15" s="252"/>
+      <c r="C15" s="229"/>
+      <c r="D15" s="229"/>
+      <c r="E15" s="229"/>
+      <c r="F15" s="229"/>
+      <c r="G15" s="229"/>
+      <c r="H15" s="230"/>
+      <c r="I15" s="231"/>
+      <c r="J15" s="231"/>
+      <c r="K15" s="231"/>
+      <c r="L15" s="231"/>
+      <c r="M15" s="232"/>
+      <c r="N15" s="233"/>
+      <c r="O15" s="234"/>
+      <c r="P15" s="235"/>
       <c r="Q15" s="60"/>
-      <c r="R15" s="253"/>
-      <c r="S15" s="253"/>
+      <c r="R15" s="236"/>
+      <c r="S15" s="236"/>
     </row>
     <row r="16" spans="1:19" ht="30" customHeight="1">
       <c r="A16" s="60"/>
       <c r="B16" s="60"/>
-      <c r="C16" s="249"/>
-      <c r="D16" s="249"/>
-      <c r="E16" s="249"/>
-      <c r="F16" s="249"/>
-      <c r="G16" s="249"/>
-      <c r="H16" s="257"/>
-      <c r="I16" s="258"/>
-      <c r="J16" s="258"/>
-      <c r="K16" s="258"/>
-      <c r="L16" s="258"/>
-      <c r="M16" s="259"/>
-      <c r="N16" s="250"/>
-      <c r="O16" s="251"/>
-      <c r="P16" s="252"/>
+      <c r="C16" s="229"/>
+      <c r="D16" s="229"/>
+      <c r="E16" s="229"/>
+      <c r="F16" s="229"/>
+      <c r="G16" s="229"/>
+      <c r="H16" s="230"/>
+      <c r="I16" s="231"/>
+      <c r="J16" s="231"/>
+      <c r="K16" s="231"/>
+      <c r="L16" s="231"/>
+      <c r="M16" s="232"/>
+      <c r="N16" s="233"/>
+      <c r="O16" s="234"/>
+      <c r="P16" s="235"/>
       <c r="Q16" s="60"/>
-      <c r="R16" s="253"/>
-      <c r="S16" s="253"/>
+      <c r="R16" s="236"/>
+      <c r="S16" s="236"/>
     </row>
     <row r="17" spans="1:19" ht="30" customHeight="1">
       <c r="A17" s="60"/>
       <c r="B17" s="60"/>
-      <c r="C17" s="249"/>
-      <c r="D17" s="249"/>
-      <c r="E17" s="249"/>
-      <c r="F17" s="249"/>
-      <c r="G17" s="249"/>
-      <c r="H17" s="257"/>
-      <c r="I17" s="258"/>
-      <c r="J17" s="258"/>
-      <c r="K17" s="258"/>
-      <c r="L17" s="258"/>
-      <c r="M17" s="259"/>
-      <c r="N17" s="250"/>
-      <c r="O17" s="251"/>
-      <c r="P17" s="252"/>
+      <c r="C17" s="229"/>
+      <c r="D17" s="229"/>
+      <c r="E17" s="229"/>
+      <c r="F17" s="229"/>
+      <c r="G17" s="229"/>
+      <c r="H17" s="230"/>
+      <c r="I17" s="231"/>
+      <c r="J17" s="231"/>
+      <c r="K17" s="231"/>
+      <c r="L17" s="231"/>
+      <c r="M17" s="232"/>
+      <c r="N17" s="233"/>
+      <c r="O17" s="234"/>
+      <c r="P17" s="235"/>
       <c r="Q17" s="60"/>
-      <c r="R17" s="253"/>
-      <c r="S17" s="253"/>
+      <c r="R17" s="236"/>
+      <c r="S17" s="236"/>
     </row>
     <row r="18" spans="1:19" ht="30" customHeight="1">
       <c r="A18" s="60"/>
       <c r="B18" s="60"/>
-      <c r="C18" s="249"/>
-      <c r="D18" s="249"/>
-      <c r="E18" s="249"/>
-      <c r="F18" s="249"/>
-      <c r="G18" s="249"/>
-      <c r="H18" s="257"/>
-      <c r="I18" s="258"/>
-      <c r="J18" s="258"/>
-      <c r="K18" s="258"/>
-      <c r="L18" s="258"/>
-      <c r="M18" s="259"/>
-      <c r="N18" s="250"/>
-      <c r="O18" s="251"/>
-      <c r="P18" s="252"/>
+      <c r="C18" s="229"/>
+      <c r="D18" s="229"/>
+      <c r="E18" s="229"/>
+      <c r="F18" s="229"/>
+      <c r="G18" s="229"/>
+      <c r="H18" s="230"/>
+      <c r="I18" s="231"/>
+      <c r="J18" s="231"/>
+      <c r="K18" s="231"/>
+      <c r="L18" s="231"/>
+      <c r="M18" s="232"/>
+      <c r="N18" s="233"/>
+      <c r="O18" s="234"/>
+      <c r="P18" s="235"/>
       <c r="Q18" s="60"/>
-      <c r="R18" s="253"/>
-      <c r="S18" s="253"/>
+      <c r="R18" s="236"/>
+      <c r="S18" s="236"/>
     </row>
     <row r="19" spans="1:19" ht="30" customHeight="1">
       <c r="A19" s="60"/>
       <c r="B19" s="60"/>
-      <c r="C19" s="249"/>
-      <c r="D19" s="249"/>
-      <c r="E19" s="249"/>
-      <c r="F19" s="249"/>
-      <c r="G19" s="249"/>
-      <c r="H19" s="257"/>
-      <c r="I19" s="258"/>
-      <c r="J19" s="258"/>
-      <c r="K19" s="258"/>
-      <c r="L19" s="258"/>
-      <c r="M19" s="259"/>
-      <c r="N19" s="250"/>
-      <c r="O19" s="251"/>
-      <c r="P19" s="252"/>
+      <c r="C19" s="229"/>
+      <c r="D19" s="229"/>
+      <c r="E19" s="229"/>
+      <c r="F19" s="229"/>
+      <c r="G19" s="229"/>
+      <c r="H19" s="230"/>
+      <c r="I19" s="231"/>
+      <c r="J19" s="231"/>
+      <c r="K19" s="231"/>
+      <c r="L19" s="231"/>
+      <c r="M19" s="232"/>
+      <c r="N19" s="233"/>
+      <c r="O19" s="234"/>
+      <c r="P19" s="235"/>
       <c r="Q19" s="60"/>
-      <c r="R19" s="253"/>
-      <c r="S19" s="253"/>
+      <c r="R19" s="236"/>
+      <c r="S19" s="236"/>
     </row>
     <row r="20" spans="1:19" ht="30" customHeight="1">
       <c r="A20" s="60"/>
       <c r="B20" s="60"/>
-      <c r="C20" s="249"/>
-      <c r="D20" s="249"/>
-      <c r="E20" s="249"/>
-      <c r="F20" s="249"/>
-      <c r="G20" s="249"/>
-      <c r="H20" s="257"/>
-      <c r="I20" s="258"/>
-      <c r="J20" s="258"/>
-      <c r="K20" s="258"/>
-      <c r="L20" s="258"/>
-      <c r="M20" s="259"/>
-      <c r="N20" s="250"/>
-      <c r="O20" s="251"/>
-      <c r="P20" s="252"/>
+      <c r="C20" s="229"/>
+      <c r="D20" s="229"/>
+      <c r="E20" s="229"/>
+      <c r="F20" s="229"/>
+      <c r="G20" s="229"/>
+      <c r="H20" s="230"/>
+      <c r="I20" s="231"/>
+      <c r="J20" s="231"/>
+      <c r="K20" s="231"/>
+      <c r="L20" s="231"/>
+      <c r="M20" s="232"/>
+      <c r="N20" s="233"/>
+      <c r="O20" s="234"/>
+      <c r="P20" s="235"/>
       <c r="Q20" s="60"/>
-      <c r="R20" s="253"/>
-      <c r="S20" s="253"/>
+      <c r="R20" s="236"/>
+      <c r="S20" s="236"/>
     </row>
     <row r="21" spans="1:19" ht="30" customHeight="1">
       <c r="A21" s="60"/>
       <c r="B21" s="60"/>
-      <c r="C21" s="249"/>
-      <c r="D21" s="249"/>
-      <c r="E21" s="249"/>
-      <c r="F21" s="249"/>
-      <c r="G21" s="249"/>
-      <c r="H21" s="257"/>
-      <c r="I21" s="258"/>
-      <c r="J21" s="258"/>
-      <c r="K21" s="258"/>
-      <c r="L21" s="258"/>
-      <c r="M21" s="259"/>
-      <c r="N21" s="250"/>
-      <c r="O21" s="251"/>
-      <c r="P21" s="252"/>
+      <c r="C21" s="229"/>
+      <c r="D21" s="229"/>
+      <c r="E21" s="229"/>
+      <c r="F21" s="229"/>
+      <c r="G21" s="229"/>
+      <c r="H21" s="230"/>
+      <c r="I21" s="231"/>
+      <c r="J21" s="231"/>
+      <c r="K21" s="231"/>
+      <c r="L21" s="231"/>
+      <c r="M21" s="232"/>
+      <c r="N21" s="233"/>
+      <c r="O21" s="234"/>
+      <c r="P21" s="235"/>
       <c r="Q21" s="60"/>
-      <c r="R21" s="253"/>
-      <c r="S21" s="253"/>
+      <c r="R21" s="236"/>
+      <c r="S21" s="236"/>
     </row>
     <row r="22" spans="1:19" ht="30" customHeight="1">
       <c r="A22" s="60"/>
       <c r="B22" s="60"/>
-      <c r="C22" s="249"/>
-      <c r="D22" s="249"/>
-      <c r="E22" s="249"/>
-      <c r="F22" s="249"/>
-      <c r="G22" s="249"/>
-      <c r="H22" s="257"/>
-      <c r="I22" s="258"/>
-      <c r="J22" s="258"/>
-      <c r="K22" s="258"/>
-      <c r="L22" s="258"/>
-      <c r="M22" s="259"/>
-      <c r="N22" s="250"/>
-      <c r="O22" s="251"/>
-      <c r="P22" s="252"/>
+      <c r="C22" s="229"/>
+      <c r="D22" s="229"/>
+      <c r="E22" s="229"/>
+      <c r="F22" s="229"/>
+      <c r="G22" s="229"/>
+      <c r="H22" s="230"/>
+      <c r="I22" s="231"/>
+      <c r="J22" s="231"/>
+      <c r="K22" s="231"/>
+      <c r="L22" s="231"/>
+      <c r="M22" s="232"/>
+      <c r="N22" s="233"/>
+      <c r="O22" s="234"/>
+      <c r="P22" s="235"/>
       <c r="Q22" s="60"/>
-      <c r="R22" s="253"/>
-      <c r="S22" s="253"/>
+      <c r="R22" s="236"/>
+      <c r="S22" s="236"/>
     </row>
     <row r="23" spans="1:19" ht="30" customHeight="1">
       <c r="A23" s="60"/>
       <c r="B23" s="60"/>
-      <c r="C23" s="249"/>
-      <c r="D23" s="249"/>
-      <c r="E23" s="249"/>
-      <c r="F23" s="249"/>
-      <c r="G23" s="249"/>
-      <c r="H23" s="257"/>
-      <c r="I23" s="258"/>
-      <c r="J23" s="258"/>
-      <c r="K23" s="258"/>
-      <c r="L23" s="258"/>
-      <c r="M23" s="259"/>
-      <c r="N23" s="250"/>
-      <c r="O23" s="251"/>
-      <c r="P23" s="252"/>
+      <c r="C23" s="229"/>
+      <c r="D23" s="229"/>
+      <c r="E23" s="229"/>
+      <c r="F23" s="229"/>
+      <c r="G23" s="229"/>
+      <c r="H23" s="230"/>
+      <c r="I23" s="231"/>
+      <c r="J23" s="231"/>
+      <c r="K23" s="231"/>
+      <c r="L23" s="231"/>
+      <c r="M23" s="232"/>
+      <c r="N23" s="233"/>
+      <c r="O23" s="234"/>
+      <c r="P23" s="235"/>
       <c r="Q23" s="60"/>
-      <c r="R23" s="253"/>
-      <c r="S23" s="253"/>
+      <c r="R23" s="236"/>
+      <c r="S23" s="236"/>
     </row>
     <row r="24" spans="1:19" ht="30" customHeight="1">
       <c r="A24" s="60"/>
       <c r="B24" s="60"/>
-      <c r="C24" s="249"/>
-      <c r="D24" s="249"/>
-      <c r="E24" s="249"/>
-      <c r="F24" s="249"/>
-      <c r="G24" s="249"/>
-      <c r="H24" s="257"/>
-      <c r="I24" s="258"/>
-      <c r="J24" s="258"/>
-      <c r="K24" s="258"/>
-      <c r="L24" s="258"/>
-      <c r="M24" s="259"/>
-      <c r="N24" s="250"/>
-      <c r="O24" s="251"/>
-      <c r="P24" s="252"/>
+      <c r="C24" s="229"/>
+      <c r="D24" s="229"/>
+      <c r="E24" s="229"/>
+      <c r="F24" s="229"/>
+      <c r="G24" s="229"/>
+      <c r="H24" s="230"/>
+      <c r="I24" s="231"/>
+      <c r="J24" s="231"/>
+      <c r="K24" s="231"/>
+      <c r="L24" s="231"/>
+      <c r="M24" s="232"/>
+      <c r="N24" s="233"/>
+      <c r="O24" s="234"/>
+      <c r="P24" s="235"/>
       <c r="Q24" s="60"/>
-      <c r="R24" s="253"/>
-      <c r="S24" s="253"/>
+      <c r="R24" s="236"/>
+      <c r="S24" s="236"/>
     </row>
     <row r="25" spans="1:19" ht="30" customHeight="1">
       <c r="A25" s="60"/>
       <c r="B25" s="60"/>
-      <c r="C25" s="249"/>
-      <c r="D25" s="249"/>
-      <c r="E25" s="249"/>
-      <c r="F25" s="249"/>
-      <c r="G25" s="249"/>
-      <c r="H25" s="257"/>
-      <c r="I25" s="258"/>
-      <c r="J25" s="258"/>
-      <c r="K25" s="258"/>
-      <c r="L25" s="258"/>
-      <c r="M25" s="259"/>
-      <c r="N25" s="250"/>
-      <c r="O25" s="251"/>
-      <c r="P25" s="252"/>
+      <c r="C25" s="229"/>
+      <c r="D25" s="229"/>
+      <c r="E25" s="229"/>
+      <c r="F25" s="229"/>
+      <c r="G25" s="229"/>
+      <c r="H25" s="230"/>
+      <c r="I25" s="231"/>
+      <c r="J25" s="231"/>
+      <c r="K25" s="231"/>
+      <c r="L25" s="231"/>
+      <c r="M25" s="232"/>
+      <c r="N25" s="233"/>
+      <c r="O25" s="234"/>
+      <c r="P25" s="235"/>
       <c r="Q25" s="60"/>
-      <c r="R25" s="253"/>
-      <c r="S25" s="253"/>
+      <c r="R25" s="236"/>
+      <c r="S25" s="236"/>
     </row>
     <row r="26" spans="1:19" ht="30" customHeight="1">
       <c r="A26" s="60"/>
       <c r="B26" s="60"/>
-      <c r="C26" s="249"/>
-      <c r="D26" s="249"/>
-      <c r="E26" s="249"/>
-      <c r="F26" s="249"/>
-      <c r="G26" s="249"/>
-      <c r="H26" s="257"/>
-      <c r="I26" s="258"/>
-      <c r="J26" s="258"/>
-      <c r="K26" s="258"/>
-      <c r="L26" s="258"/>
-      <c r="M26" s="259"/>
-      <c r="N26" s="250"/>
-      <c r="O26" s="251"/>
-      <c r="P26" s="252"/>
+      <c r="C26" s="229"/>
+      <c r="D26" s="229"/>
+      <c r="E26" s="229"/>
+      <c r="F26" s="229"/>
+      <c r="G26" s="229"/>
+      <c r="H26" s="230"/>
+      <c r="I26" s="231"/>
+      <c r="J26" s="231"/>
+      <c r="K26" s="231"/>
+      <c r="L26" s="231"/>
+      <c r="M26" s="232"/>
+      <c r="N26" s="233"/>
+      <c r="O26" s="234"/>
+      <c r="P26" s="235"/>
       <c r="Q26" s="60"/>
-      <c r="R26" s="253"/>
-      <c r="S26" s="253"/>
+      <c r="R26" s="236"/>
+      <c r="S26" s="236"/>
     </row>
     <row r="27" spans="1:19" ht="30" customHeight="1">
       <c r="A27" s="60"/>
       <c r="B27" s="60"/>
-      <c r="C27" s="249"/>
-      <c r="D27" s="249"/>
-      <c r="E27" s="249"/>
-      <c r="F27" s="249"/>
-      <c r="G27" s="249"/>
-      <c r="H27" s="257"/>
-      <c r="I27" s="258"/>
-      <c r="J27" s="258"/>
-      <c r="K27" s="258"/>
-      <c r="L27" s="258"/>
-      <c r="M27" s="259"/>
-      <c r="N27" s="250"/>
-      <c r="O27" s="251"/>
-      <c r="P27" s="252"/>
+      <c r="C27" s="229"/>
+      <c r="D27" s="229"/>
+      <c r="E27" s="229"/>
+      <c r="F27" s="229"/>
+      <c r="G27" s="229"/>
+      <c r="H27" s="230"/>
+      <c r="I27" s="231"/>
+      <c r="J27" s="231"/>
+      <c r="K27" s="231"/>
+      <c r="L27" s="231"/>
+      <c r="M27" s="232"/>
+      <c r="N27" s="233"/>
+      <c r="O27" s="234"/>
+      <c r="P27" s="235"/>
       <c r="Q27" s="60"/>
-      <c r="R27" s="253"/>
-      <c r="S27" s="253"/>
+      <c r="R27" s="236"/>
+      <c r="S27" s="236"/>
     </row>
     <row r="28" spans="1:19" ht="30" customHeight="1">
       <c r="A28" s="60"/>
       <c r="B28" s="60"/>
-      <c r="C28" s="249"/>
-      <c r="D28" s="249"/>
-      <c r="E28" s="249"/>
-      <c r="F28" s="249"/>
-      <c r="G28" s="249"/>
-      <c r="H28" s="257"/>
-      <c r="I28" s="258"/>
-      <c r="J28" s="258"/>
-      <c r="K28" s="258"/>
-      <c r="L28" s="258"/>
-      <c r="M28" s="259"/>
-      <c r="N28" s="250"/>
-      <c r="O28" s="251"/>
-      <c r="P28" s="252"/>
+      <c r="C28" s="229"/>
+      <c r="D28" s="229"/>
+      <c r="E28" s="229"/>
+      <c r="F28" s="229"/>
+      <c r="G28" s="229"/>
+      <c r="H28" s="230"/>
+      <c r="I28" s="231"/>
+      <c r="J28" s="231"/>
+      <c r="K28" s="231"/>
+      <c r="L28" s="231"/>
+      <c r="M28" s="232"/>
+      <c r="N28" s="233"/>
+      <c r="O28" s="234"/>
+      <c r="P28" s="235"/>
       <c r="Q28" s="60"/>
-      <c r="R28" s="253"/>
-      <c r="S28" s="253"/>
+      <c r="R28" s="236"/>
+      <c r="S28" s="236"/>
     </row>
     <row r="29" spans="1:19" ht="30" customHeight="1">
       <c r="A29" s="60"/>
       <c r="B29" s="60"/>
-      <c r="C29" s="249"/>
-      <c r="D29" s="249"/>
-      <c r="E29" s="249"/>
-      <c r="F29" s="249"/>
-      <c r="G29" s="249"/>
-      <c r="H29" s="257"/>
-      <c r="I29" s="258"/>
-      <c r="J29" s="258"/>
-      <c r="K29" s="258"/>
-      <c r="L29" s="258"/>
-      <c r="M29" s="259"/>
-      <c r="N29" s="250"/>
-      <c r="O29" s="251"/>
-      <c r="P29" s="252"/>
+      <c r="C29" s="229"/>
+      <c r="D29" s="229"/>
+      <c r="E29" s="229"/>
+      <c r="F29" s="229"/>
+      <c r="G29" s="229"/>
+      <c r="H29" s="230"/>
+      <c r="I29" s="231"/>
+      <c r="J29" s="231"/>
+      <c r="K29" s="231"/>
+      <c r="L29" s="231"/>
+      <c r="M29" s="232"/>
+      <c r="N29" s="233"/>
+      <c r="O29" s="234"/>
+      <c r="P29" s="235"/>
       <c r="Q29" s="60"/>
-      <c r="R29" s="253"/>
-      <c r="S29" s="253"/>
+      <c r="R29" s="236"/>
+      <c r="S29" s="236"/>
     </row>
     <row r="30" spans="1:19" ht="30" customHeight="1">
       <c r="A30" s="60"/>
       <c r="B30" s="60"/>
-      <c r="C30" s="249"/>
-      <c r="D30" s="249"/>
-      <c r="E30" s="249"/>
-      <c r="F30" s="249"/>
-      <c r="G30" s="249"/>
-      <c r="H30" s="257"/>
-      <c r="I30" s="258"/>
-      <c r="J30" s="258"/>
-      <c r="K30" s="258"/>
-      <c r="L30" s="258"/>
-      <c r="M30" s="259"/>
-      <c r="N30" s="250"/>
-      <c r="O30" s="251"/>
-      <c r="P30" s="252"/>
+      <c r="C30" s="229"/>
+      <c r="D30" s="229"/>
+      <c r="E30" s="229"/>
+      <c r="F30" s="229"/>
+      <c r="G30" s="229"/>
+      <c r="H30" s="230"/>
+      <c r="I30" s="231"/>
+      <c r="J30" s="231"/>
+      <c r="K30" s="231"/>
+      <c r="L30" s="231"/>
+      <c r="M30" s="232"/>
+      <c r="N30" s="233"/>
+      <c r="O30" s="234"/>
+      <c r="P30" s="235"/>
       <c r="Q30" s="60"/>
-      <c r="R30" s="253"/>
-      <c r="S30" s="253"/>
+      <c r="R30" s="236"/>
+      <c r="S30" s="236"/>
     </row>
     <row r="31" spans="1:19" ht="30" customHeight="1">
       <c r="A31" s="60"/>
       <c r="B31" s="60"/>
-      <c r="C31" s="249"/>
-      <c r="D31" s="249"/>
-      <c r="E31" s="249"/>
-      <c r="F31" s="249"/>
-      <c r="G31" s="249"/>
-      <c r="H31" s="257"/>
-      <c r="I31" s="258"/>
-      <c r="J31" s="258"/>
-      <c r="K31" s="258"/>
-      <c r="L31" s="258"/>
-      <c r="M31" s="259"/>
-      <c r="N31" s="250"/>
-      <c r="O31" s="251"/>
-      <c r="P31" s="252"/>
+      <c r="C31" s="229"/>
+      <c r="D31" s="229"/>
+      <c r="E31" s="229"/>
+      <c r="F31" s="229"/>
+      <c r="G31" s="229"/>
+      <c r="H31" s="230"/>
+      <c r="I31" s="231"/>
+      <c r="J31" s="231"/>
+      <c r="K31" s="231"/>
+      <c r="L31" s="231"/>
+      <c r="M31" s="232"/>
+      <c r="N31" s="233"/>
+      <c r="O31" s="234"/>
+      <c r="P31" s="235"/>
       <c r="Q31" s="60"/>
-      <c r="R31" s="253"/>
-      <c r="S31" s="253"/>
+      <c r="R31" s="236"/>
+      <c r="S31" s="236"/>
     </row>
     <row r="32" spans="1:19" ht="30" customHeight="1">
       <c r="A32" s="60"/>
       <c r="B32" s="60"/>
-      <c r="C32" s="249"/>
-      <c r="D32" s="249"/>
-      <c r="E32" s="249"/>
-      <c r="F32" s="249"/>
-      <c r="G32" s="249"/>
-      <c r="H32" s="257"/>
-      <c r="I32" s="258"/>
-      <c r="J32" s="258"/>
-      <c r="K32" s="258"/>
-      <c r="L32" s="258"/>
-      <c r="M32" s="259"/>
-      <c r="N32" s="250"/>
-      <c r="O32" s="251"/>
-      <c r="P32" s="252"/>
+      <c r="C32" s="229"/>
+      <c r="D32" s="229"/>
+      <c r="E32" s="229"/>
+      <c r="F32" s="229"/>
+      <c r="G32" s="229"/>
+      <c r="H32" s="230"/>
+      <c r="I32" s="231"/>
+      <c r="J32" s="231"/>
+      <c r="K32" s="231"/>
+      <c r="L32" s="231"/>
+      <c r="M32" s="232"/>
+      <c r="N32" s="233"/>
+      <c r="O32" s="234"/>
+      <c r="P32" s="235"/>
       <c r="Q32" s="60"/>
-      <c r="R32" s="253"/>
-      <c r="S32" s="253"/>
+      <c r="R32" s="236"/>
+      <c r="S32" s="236"/>
     </row>
     <row r="33" spans="1:19" ht="30" customHeight="1">
       <c r="A33" s="60"/>
       <c r="B33" s="60"/>
-      <c r="C33" s="249"/>
-      <c r="D33" s="249"/>
-      <c r="E33" s="249"/>
-      <c r="F33" s="249"/>
-      <c r="G33" s="249"/>
-      <c r="H33" s="257"/>
-      <c r="I33" s="258"/>
-      <c r="J33" s="258"/>
-      <c r="K33" s="258"/>
-      <c r="L33" s="258"/>
-      <c r="M33" s="259"/>
-      <c r="N33" s="250"/>
-      <c r="O33" s="251"/>
-      <c r="P33" s="252"/>
+      <c r="C33" s="229"/>
+      <c r="D33" s="229"/>
+      <c r="E33" s="229"/>
+      <c r="F33" s="229"/>
+      <c r="G33" s="229"/>
+      <c r="H33" s="230"/>
+      <c r="I33" s="231"/>
+      <c r="J33" s="231"/>
+      <c r="K33" s="231"/>
+      <c r="L33" s="231"/>
+      <c r="M33" s="232"/>
+      <c r="N33" s="233"/>
+      <c r="O33" s="234"/>
+      <c r="P33" s="235"/>
       <c r="Q33" s="60"/>
-      <c r="R33" s="253"/>
-      <c r="S33" s="253"/>
+      <c r="R33" s="236"/>
+      <c r="S33" s="236"/>
     </row>
     <row r="34" spans="1:19" ht="30" customHeight="1">
       <c r="A34" s="60"/>
       <c r="B34" s="60"/>
-      <c r="C34" s="249"/>
-      <c r="D34" s="249"/>
-      <c r="E34" s="249"/>
-      <c r="F34" s="249"/>
-      <c r="G34" s="249"/>
-      <c r="H34" s="257"/>
-      <c r="I34" s="258"/>
-      <c r="J34" s="258"/>
-      <c r="K34" s="258"/>
-      <c r="L34" s="258"/>
-      <c r="M34" s="259"/>
-      <c r="N34" s="250"/>
-      <c r="O34" s="251"/>
-      <c r="P34" s="252"/>
+      <c r="C34" s="229"/>
+      <c r="D34" s="229"/>
+      <c r="E34" s="229"/>
+      <c r="F34" s="229"/>
+      <c r="G34" s="229"/>
+      <c r="H34" s="230"/>
+      <c r="I34" s="231"/>
+      <c r="J34" s="231"/>
+      <c r="K34" s="231"/>
+      <c r="L34" s="231"/>
+      <c r="M34" s="232"/>
+      <c r="N34" s="233"/>
+      <c r="O34" s="234"/>
+      <c r="P34" s="235"/>
       <c r="Q34" s="60"/>
-      <c r="R34" s="253"/>
-      <c r="S34" s="253"/>
+      <c r="R34" s="236"/>
+      <c r="S34" s="236"/>
     </row>
     <row r="35" spans="1:19" ht="30" customHeight="1">
       <c r="A35" s="60"/>
       <c r="B35" s="60"/>
-      <c r="C35" s="249"/>
-      <c r="D35" s="249"/>
-      <c r="E35" s="249"/>
-      <c r="F35" s="249"/>
-      <c r="G35" s="249"/>
-      <c r="H35" s="257"/>
-      <c r="I35" s="258"/>
-      <c r="J35" s="258"/>
-      <c r="K35" s="258"/>
-      <c r="L35" s="258"/>
-      <c r="M35" s="259"/>
-      <c r="N35" s="250"/>
-      <c r="O35" s="251"/>
-      <c r="P35" s="252"/>
+      <c r="C35" s="229"/>
+      <c r="D35" s="229"/>
+      <c r="E35" s="229"/>
+      <c r="F35" s="229"/>
+      <c r="G35" s="229"/>
+      <c r="H35" s="230"/>
+      <c r="I35" s="231"/>
+      <c r="J35" s="231"/>
+      <c r="K35" s="231"/>
+      <c r="L35" s="231"/>
+      <c r="M35" s="232"/>
+      <c r="N35" s="233"/>
+      <c r="O35" s="234"/>
+      <c r="P35" s="235"/>
       <c r="Q35" s="60"/>
-      <c r="R35" s="253"/>
-      <c r="S35" s="253"/>
+      <c r="R35" s="236"/>
+      <c r="S35" s="236"/>
     </row>
     <row r="36" spans="1:19" ht="30" customHeight="1">
       <c r="A36" s="60"/>
       <c r="B36" s="60"/>
-      <c r="C36" s="249"/>
-      <c r="D36" s="249"/>
-      <c r="E36" s="249"/>
-      <c r="F36" s="249"/>
-      <c r="G36" s="249"/>
-      <c r="H36" s="257"/>
-      <c r="I36" s="258"/>
-      <c r="J36" s="258"/>
-      <c r="K36" s="258"/>
-      <c r="L36" s="258"/>
-      <c r="M36" s="259"/>
-      <c r="N36" s="250"/>
-      <c r="O36" s="251"/>
-      <c r="P36" s="252"/>
+      <c r="C36" s="229"/>
+      <c r="D36" s="229"/>
+      <c r="E36" s="229"/>
+      <c r="F36" s="229"/>
+      <c r="G36" s="229"/>
+      <c r="H36" s="230"/>
+      <c r="I36" s="231"/>
+      <c r="J36" s="231"/>
+      <c r="K36" s="231"/>
+      <c r="L36" s="231"/>
+      <c r="M36" s="232"/>
+      <c r="N36" s="233"/>
+      <c r="O36" s="234"/>
+      <c r="P36" s="235"/>
       <c r="Q36" s="60"/>
-      <c r="R36" s="253"/>
-      <c r="S36" s="253"/>
+      <c r="R36" s="236"/>
+      <c r="S36" s="236"/>
     </row>
     <row r="37" spans="1:19" ht="30" customHeight="1">
       <c r="A37" s="60"/>
       <c r="B37" s="60"/>
-      <c r="C37" s="249"/>
-      <c r="D37" s="249"/>
-      <c r="E37" s="249"/>
-      <c r="F37" s="249"/>
-      <c r="G37" s="249"/>
-      <c r="H37" s="257"/>
-      <c r="I37" s="258"/>
-      <c r="J37" s="258"/>
-      <c r="K37" s="258"/>
-      <c r="L37" s="258"/>
-      <c r="M37" s="259"/>
-      <c r="N37" s="250"/>
-      <c r="O37" s="251"/>
-      <c r="P37" s="252"/>
+      <c r="C37" s="229"/>
+      <c r="D37" s="229"/>
+      <c r="E37" s="229"/>
+      <c r="F37" s="229"/>
+      <c r="G37" s="229"/>
+      <c r="H37" s="230"/>
+      <c r="I37" s="231"/>
+      <c r="J37" s="231"/>
+      <c r="K37" s="231"/>
+      <c r="L37" s="231"/>
+      <c r="M37" s="232"/>
+      <c r="N37" s="233"/>
+      <c r="O37" s="234"/>
+      <c r="P37" s="235"/>
       <c r="Q37" s="60"/>
-      <c r="R37" s="253"/>
-      <c r="S37" s="253"/>
+      <c r="R37" s="236"/>
+      <c r="S37" s="236"/>
     </row>
     <row r="38" spans="1:19" ht="30" customHeight="1">
       <c r="A38" s="60"/>
       <c r="B38" s="60"/>
-      <c r="C38" s="249"/>
-      <c r="D38" s="249"/>
-      <c r="E38" s="249"/>
-      <c r="F38" s="249"/>
-      <c r="G38" s="249"/>
-      <c r="H38" s="257"/>
-      <c r="I38" s="258"/>
-      <c r="J38" s="258"/>
-      <c r="K38" s="258"/>
-      <c r="L38" s="258"/>
-      <c r="M38" s="259"/>
-      <c r="N38" s="250"/>
-      <c r="O38" s="251"/>
-      <c r="P38" s="252"/>
+      <c r="C38" s="229"/>
+      <c r="D38" s="229"/>
+      <c r="E38" s="229"/>
+      <c r="F38" s="229"/>
+      <c r="G38" s="229"/>
+      <c r="H38" s="230"/>
+      <c r="I38" s="231"/>
+      <c r="J38" s="231"/>
+      <c r="K38" s="231"/>
+      <c r="L38" s="231"/>
+      <c r="M38" s="232"/>
+      <c r="N38" s="233"/>
+      <c r="O38" s="234"/>
+      <c r="P38" s="235"/>
       <c r="Q38" s="60"/>
-      <c r="R38" s="253"/>
-      <c r="S38" s="253"/>
+      <c r="R38" s="236"/>
+      <c r="S38" s="236"/>
     </row>
     <row r="39" spans="1:19" ht="30" customHeight="1">
       <c r="A39" s="60"/>
       <c r="B39" s="60"/>
-      <c r="C39" s="249"/>
-      <c r="D39" s="249"/>
-      <c r="E39" s="249"/>
-      <c r="F39" s="249"/>
-      <c r="G39" s="249"/>
-      <c r="H39" s="257"/>
-      <c r="I39" s="258"/>
-      <c r="J39" s="258"/>
-      <c r="K39" s="258"/>
-      <c r="L39" s="258"/>
-      <c r="M39" s="259"/>
-      <c r="N39" s="250"/>
-      <c r="O39" s="251"/>
-      <c r="P39" s="252"/>
+      <c r="C39" s="229"/>
+      <c r="D39" s="229"/>
+      <c r="E39" s="229"/>
+      <c r="F39" s="229"/>
+      <c r="G39" s="229"/>
+      <c r="H39" s="230"/>
+      <c r="I39" s="231"/>
+      <c r="J39" s="231"/>
+      <c r="K39" s="231"/>
+      <c r="L39" s="231"/>
+      <c r="M39" s="232"/>
+      <c r="N39" s="233"/>
+      <c r="O39" s="234"/>
+      <c r="P39" s="235"/>
       <c r="Q39" s="60"/>
-      <c r="R39" s="253"/>
-      <c r="S39" s="253"/>
+      <c r="R39" s="236"/>
+      <c r="S39" s="236"/>
     </row>
     <row r="40" spans="1:19" ht="30" customHeight="1">
       <c r="A40" s="60"/>
       <c r="B40" s="60"/>
-      <c r="C40" s="249"/>
-      <c r="D40" s="249"/>
-      <c r="E40" s="249"/>
-      <c r="F40" s="249"/>
-      <c r="G40" s="249"/>
-      <c r="H40" s="257"/>
-      <c r="I40" s="258"/>
-      <c r="J40" s="258"/>
-      <c r="K40" s="258"/>
-      <c r="L40" s="258"/>
-      <c r="M40" s="259"/>
-      <c r="N40" s="250"/>
-      <c r="O40" s="251"/>
-      <c r="P40" s="252"/>
+      <c r="C40" s="229"/>
+      <c r="D40" s="229"/>
+      <c r="E40" s="229"/>
+      <c r="F40" s="229"/>
+      <c r="G40" s="229"/>
+      <c r="H40" s="230"/>
+      <c r="I40" s="231"/>
+      <c r="J40" s="231"/>
+      <c r="K40" s="231"/>
+      <c r="L40" s="231"/>
+      <c r="M40" s="232"/>
+      <c r="N40" s="233"/>
+      <c r="O40" s="234"/>
+      <c r="P40" s="235"/>
       <c r="Q40" s="60"/>
-      <c r="R40" s="253"/>
-      <c r="S40" s="253"/>
+      <c r="R40" s="236"/>
+      <c r="S40" s="236"/>
     </row>
     <row r="41" spans="1:19" ht="30" customHeight="1">
       <c r="A41" s="60"/>
       <c r="B41" s="60"/>
-      <c r="C41" s="249"/>
-      <c r="D41" s="249"/>
-      <c r="E41" s="249"/>
-      <c r="F41" s="249"/>
-      <c r="G41" s="249"/>
-      <c r="H41" s="257"/>
-      <c r="I41" s="258"/>
-      <c r="J41" s="258"/>
-      <c r="K41" s="258"/>
-      <c r="L41" s="258"/>
-      <c r="M41" s="259"/>
-      <c r="N41" s="250"/>
-      <c r="O41" s="251"/>
-      <c r="P41" s="252"/>
+      <c r="C41" s="229"/>
+      <c r="D41" s="229"/>
+      <c r="E41" s="229"/>
+      <c r="F41" s="229"/>
+      <c r="G41" s="229"/>
+      <c r="H41" s="230"/>
+      <c r="I41" s="231"/>
+      <c r="J41" s="231"/>
+      <c r="K41" s="231"/>
+      <c r="L41" s="231"/>
+      <c r="M41" s="232"/>
+      <c r="N41" s="233"/>
+      <c r="O41" s="234"/>
+      <c r="P41" s="235"/>
       <c r="Q41" s="60"/>
-      <c r="R41" s="253"/>
-      <c r="S41" s="253"/>
+      <c r="R41" s="236"/>
+      <c r="S41" s="236"/>
     </row>
     <row r="42" spans="1:19" ht="30" customHeight="1">
       <c r="A42" s="60"/>
       <c r="B42" s="60"/>
-      <c r="C42" s="249"/>
-      <c r="D42" s="249"/>
-      <c r="E42" s="249"/>
-      <c r="F42" s="249"/>
-      <c r="G42" s="249"/>
-      <c r="H42" s="257"/>
-      <c r="I42" s="258"/>
-      <c r="J42" s="258"/>
-      <c r="K42" s="258"/>
-      <c r="L42" s="258"/>
-      <c r="M42" s="259"/>
-      <c r="N42" s="250"/>
-      <c r="O42" s="251"/>
-      <c r="P42" s="252"/>
+      <c r="C42" s="229"/>
+      <c r="D42" s="229"/>
+      <c r="E42" s="229"/>
+      <c r="F42" s="229"/>
+      <c r="G42" s="229"/>
+      <c r="H42" s="230"/>
+      <c r="I42" s="231"/>
+      <c r="J42" s="231"/>
+      <c r="K42" s="231"/>
+      <c r="L42" s="231"/>
+      <c r="M42" s="232"/>
+      <c r="N42" s="233"/>
+      <c r="O42" s="234"/>
+      <c r="P42" s="235"/>
       <c r="Q42" s="60"/>
-      <c r="R42" s="253"/>
-      <c r="S42" s="253"/>
+      <c r="R42" s="236"/>
+      <c r="S42" s="236"/>
     </row>
     <row r="43" spans="1:19" ht="30" customHeight="1">
       <c r="A43" s="60"/>
       <c r="B43" s="60"/>
-      <c r="C43" s="249"/>
-      <c r="D43" s="249"/>
-      <c r="E43" s="249"/>
-      <c r="F43" s="249"/>
-      <c r="G43" s="249"/>
-      <c r="H43" s="257"/>
-      <c r="I43" s="258"/>
-      <c r="J43" s="258"/>
-      <c r="K43" s="258"/>
-      <c r="L43" s="258"/>
-      <c r="M43" s="259"/>
-      <c r="N43" s="250"/>
-      <c r="O43" s="251"/>
-      <c r="P43" s="252"/>
+      <c r="C43" s="229"/>
+      <c r="D43" s="229"/>
+      <c r="E43" s="229"/>
+      <c r="F43" s="229"/>
+      <c r="G43" s="229"/>
+      <c r="H43" s="230"/>
+      <c r="I43" s="231"/>
+      <c r="J43" s="231"/>
+      <c r="K43" s="231"/>
+      <c r="L43" s="231"/>
+      <c r="M43" s="232"/>
+      <c r="N43" s="233"/>
+      <c r="O43" s="234"/>
+      <c r="P43" s="235"/>
       <c r="Q43" s="60"/>
-      <c r="R43" s="253"/>
-      <c r="S43" s="253"/>
+      <c r="R43" s="236"/>
+      <c r="S43" s="236"/>
     </row>
     <row r="44" spans="1:19" ht="30" customHeight="1">
       <c r="A44" s="60"/>
       <c r="B44" s="60"/>
-      <c r="C44" s="249"/>
-      <c r="D44" s="249"/>
-      <c r="E44" s="249"/>
-      <c r="F44" s="249"/>
-      <c r="G44" s="249"/>
-      <c r="H44" s="257"/>
-      <c r="I44" s="258"/>
-      <c r="J44" s="258"/>
-      <c r="K44" s="258"/>
-      <c r="L44" s="258"/>
-      <c r="M44" s="259"/>
-      <c r="N44" s="250"/>
-      <c r="O44" s="251"/>
-      <c r="P44" s="252"/>
+      <c r="C44" s="229"/>
+      <c r="D44" s="229"/>
+      <c r="E44" s="229"/>
+      <c r="F44" s="229"/>
+      <c r="G44" s="229"/>
+      <c r="H44" s="230"/>
+      <c r="I44" s="231"/>
+      <c r="J44" s="231"/>
+      <c r="K44" s="231"/>
+      <c r="L44" s="231"/>
+      <c r="M44" s="232"/>
+      <c r="N44" s="233"/>
+      <c r="O44" s="234"/>
+      <c r="P44" s="235"/>
       <c r="Q44" s="60"/>
-      <c r="R44" s="253"/>
-      <c r="S44" s="253"/>
+      <c r="R44" s="236"/>
+      <c r="S44" s="236"/>
     </row>
     <row r="45" spans="1:19" ht="30" customHeight="1">
       <c r="A45" s="60"/>
       <c r="B45" s="60"/>
-      <c r="C45" s="249"/>
-      <c r="D45" s="249"/>
-      <c r="E45" s="249"/>
-      <c r="F45" s="249"/>
-      <c r="G45" s="249"/>
-      <c r="H45" s="257"/>
-      <c r="I45" s="258"/>
-      <c r="J45" s="258"/>
-      <c r="K45" s="258"/>
-      <c r="L45" s="258"/>
-      <c r="M45" s="259"/>
-      <c r="N45" s="250"/>
-      <c r="O45" s="251"/>
-      <c r="P45" s="252"/>
+      <c r="C45" s="229"/>
+      <c r="D45" s="229"/>
+      <c r="E45" s="229"/>
+      <c r="F45" s="229"/>
+      <c r="G45" s="229"/>
+      <c r="H45" s="230"/>
+      <c r="I45" s="231"/>
+      <c r="J45" s="231"/>
+      <c r="K45" s="231"/>
+      <c r="L45" s="231"/>
+      <c r="M45" s="232"/>
+      <c r="N45" s="233"/>
+      <c r="O45" s="234"/>
+      <c r="P45" s="235"/>
       <c r="Q45" s="60"/>
-      <c r="R45" s="253"/>
-      <c r="S45" s="253"/>
+      <c r="R45" s="236"/>
+      <c r="S45" s="236"/>
     </row>
     <row r="46" spans="1:19" ht="30" customHeight="1">
       <c r="A46" s="60"/>
       <c r="B46" s="60"/>
-      <c r="C46" s="249"/>
-      <c r="D46" s="249"/>
-      <c r="E46" s="249"/>
-      <c r="F46" s="249"/>
-      <c r="G46" s="249"/>
-      <c r="H46" s="257"/>
-      <c r="I46" s="258"/>
-      <c r="J46" s="258"/>
-      <c r="K46" s="258"/>
-      <c r="L46" s="258"/>
-      <c r="M46" s="259"/>
-      <c r="N46" s="250"/>
-      <c r="O46" s="251"/>
-      <c r="P46" s="252"/>
+      <c r="C46" s="229"/>
+      <c r="D46" s="229"/>
+      <c r="E46" s="229"/>
+      <c r="F46" s="229"/>
+      <c r="G46" s="229"/>
+      <c r="H46" s="230"/>
+      <c r="I46" s="231"/>
+      <c r="J46" s="231"/>
+      <c r="K46" s="231"/>
+      <c r="L46" s="231"/>
+      <c r="M46" s="232"/>
+      <c r="N46" s="233"/>
+      <c r="O46" s="234"/>
+      <c r="P46" s="235"/>
       <c r="Q46" s="60"/>
-      <c r="R46" s="253"/>
-      <c r="S46" s="253"/>
+      <c r="R46" s="236"/>
+      <c r="S46" s="236"/>
     </row>
     <row r="47" spans="1:19" ht="30" customHeight="1">
       <c r="A47" s="60"/>
       <c r="B47" s="60"/>
-      <c r="C47" s="249"/>
-      <c r="D47" s="249"/>
-      <c r="E47" s="249"/>
-      <c r="F47" s="249"/>
-      <c r="G47" s="249"/>
-      <c r="H47" s="257"/>
-      <c r="I47" s="258"/>
-      <c r="J47" s="258"/>
-      <c r="K47" s="258"/>
-      <c r="L47" s="258"/>
-      <c r="M47" s="259"/>
-      <c r="N47" s="250"/>
-      <c r="O47" s="251"/>
-      <c r="P47" s="252"/>
+      <c r="C47" s="229"/>
+      <c r="D47" s="229"/>
+      <c r="E47" s="229"/>
+      <c r="F47" s="229"/>
+      <c r="G47" s="229"/>
+      <c r="H47" s="230"/>
+      <c r="I47" s="231"/>
+      <c r="J47" s="231"/>
+      <c r="K47" s="231"/>
+      <c r="L47" s="231"/>
+      <c r="M47" s="232"/>
+      <c r="N47" s="233"/>
+      <c r="O47" s="234"/>
+      <c r="P47" s="235"/>
       <c r="Q47" s="60"/>
-      <c r="R47" s="253"/>
-      <c r="S47" s="253"/>
+      <c r="R47" s="236"/>
+      <c r="S47" s="236"/>
     </row>
     <row r="48" spans="1:19" ht="30" customHeight="1">
       <c r="A48" s="60"/>
       <c r="B48" s="60"/>
-      <c r="C48" s="249"/>
-      <c r="D48" s="249"/>
-      <c r="E48" s="249"/>
-      <c r="F48" s="249"/>
-      <c r="G48" s="249"/>
-      <c r="H48" s="257"/>
-      <c r="I48" s="258"/>
-      <c r="J48" s="258"/>
-      <c r="K48" s="258"/>
-      <c r="L48" s="258"/>
-      <c r="M48" s="259"/>
-      <c r="N48" s="250"/>
-      <c r="O48" s="251"/>
-      <c r="P48" s="252"/>
+      <c r="C48" s="229"/>
+      <c r="D48" s="229"/>
+      <c r="E48" s="229"/>
+      <c r="F48" s="229"/>
+      <c r="G48" s="229"/>
+      <c r="H48" s="230"/>
+      <c r="I48" s="231"/>
+      <c r="J48" s="231"/>
+      <c r="K48" s="231"/>
+      <c r="L48" s="231"/>
+      <c r="M48" s="232"/>
+      <c r="N48" s="233"/>
+      <c r="O48" s="234"/>
+      <c r="P48" s="235"/>
       <c r="Q48" s="60"/>
-      <c r="R48" s="253"/>
-      <c r="S48" s="253"/>
+      <c r="R48" s="236"/>
+      <c r="S48" s="236"/>
     </row>
     <row r="49" spans="1:19" ht="30" customHeight="1">
       <c r="A49" s="60"/>
       <c r="B49" s="60"/>
-      <c r="C49" s="249"/>
-      <c r="D49" s="249"/>
-      <c r="E49" s="249"/>
-      <c r="F49" s="249"/>
-      <c r="G49" s="249"/>
-      <c r="H49" s="257"/>
-      <c r="I49" s="258"/>
-      <c r="J49" s="258"/>
-      <c r="K49" s="258"/>
-      <c r="L49" s="258"/>
-      <c r="M49" s="259"/>
-      <c r="N49" s="250"/>
-      <c r="O49" s="251"/>
-      <c r="P49" s="252"/>
+      <c r="C49" s="229"/>
+      <c r="D49" s="229"/>
+      <c r="E49" s="229"/>
+      <c r="F49" s="229"/>
+      <c r="G49" s="229"/>
+      <c r="H49" s="230"/>
+      <c r="I49" s="231"/>
+      <c r="J49" s="231"/>
+      <c r="K49" s="231"/>
+      <c r="L49" s="231"/>
+      <c r="M49" s="232"/>
+      <c r="N49" s="233"/>
+      <c r="O49" s="234"/>
+      <c r="P49" s="235"/>
       <c r="Q49" s="60"/>
-      <c r="R49" s="253"/>
-      <c r="S49" s="253"/>
+      <c r="R49" s="236"/>
+      <c r="S49" s="236"/>
     </row>
     <row r="50" spans="1:19" ht="30" customHeight="1">
       <c r="A50" s="60"/>
       <c r="B50" s="60"/>
-      <c r="C50" s="249"/>
-      <c r="D50" s="249"/>
-      <c r="E50" s="249"/>
-      <c r="F50" s="249"/>
-      <c r="G50" s="249"/>
-      <c r="H50" s="257"/>
-      <c r="I50" s="258"/>
-      <c r="J50" s="258"/>
-      <c r="K50" s="258"/>
-      <c r="L50" s="258"/>
-      <c r="M50" s="259"/>
-      <c r="N50" s="250"/>
-      <c r="O50" s="251"/>
-      <c r="P50" s="252"/>
+      <c r="C50" s="229"/>
+      <c r="D50" s="229"/>
+      <c r="E50" s="229"/>
+      <c r="F50" s="229"/>
+      <c r="G50" s="229"/>
+      <c r="H50" s="230"/>
+      <c r="I50" s="231"/>
+      <c r="J50" s="231"/>
+      <c r="K50" s="231"/>
+      <c r="L50" s="231"/>
+      <c r="M50" s="232"/>
+      <c r="N50" s="233"/>
+      <c r="O50" s="234"/>
+      <c r="P50" s="235"/>
       <c r="Q50" s="60"/>
-      <c r="R50" s="253"/>
-      <c r="S50" s="253"/>
+      <c r="R50" s="236"/>
+      <c r="S50" s="236"/>
     </row>
     <row r="51" spans="1:19" ht="30" customHeight="1">
       <c r="A51" s="60"/>
       <c r="B51" s="60"/>
-      <c r="C51" s="249"/>
-      <c r="D51" s="249"/>
-      <c r="E51" s="249"/>
-      <c r="F51" s="249"/>
-      <c r="G51" s="249"/>
-      <c r="H51" s="257"/>
-      <c r="I51" s="258"/>
-      <c r="J51" s="258"/>
-      <c r="K51" s="258"/>
-      <c r="L51" s="258"/>
-      <c r="M51" s="259"/>
-      <c r="N51" s="250"/>
-      <c r="O51" s="251"/>
-      <c r="P51" s="252"/>
+      <c r="C51" s="229"/>
+      <c r="D51" s="229"/>
+      <c r="E51" s="229"/>
+      <c r="F51" s="229"/>
+      <c r="G51" s="229"/>
+      <c r="H51" s="230"/>
+      <c r="I51" s="231"/>
+      <c r="J51" s="231"/>
+      <c r="K51" s="231"/>
+      <c r="L51" s="231"/>
+      <c r="M51" s="232"/>
+      <c r="N51" s="233"/>
+      <c r="O51" s="234"/>
+      <c r="P51" s="235"/>
       <c r="Q51" s="60"/>
-      <c r="R51" s="253"/>
-      <c r="S51" s="253"/>
+      <c r="R51" s="236"/>
+      <c r="S51" s="236"/>
     </row>
     <row r="52" spans="1:19" ht="30" customHeight="1">
       <c r="A52" s="60"/>
       <c r="B52" s="60"/>
-      <c r="C52" s="249"/>
-      <c r="D52" s="249"/>
-      <c r="E52" s="249"/>
-      <c r="F52" s="249"/>
-      <c r="G52" s="249"/>
-      <c r="H52" s="257"/>
-      <c r="I52" s="258"/>
-      <c r="J52" s="258"/>
-      <c r="K52" s="258"/>
-      <c r="L52" s="258"/>
-      <c r="M52" s="259"/>
-      <c r="N52" s="250"/>
-      <c r="O52" s="251"/>
-      <c r="P52" s="252"/>
+      <c r="C52" s="229"/>
+      <c r="D52" s="229"/>
+      <c r="E52" s="229"/>
+      <c r="F52" s="229"/>
+      <c r="G52" s="229"/>
+      <c r="H52" s="230"/>
+      <c r="I52" s="231"/>
+      <c r="J52" s="231"/>
+      <c r="K52" s="231"/>
+      <c r="L52" s="231"/>
+      <c r="M52" s="232"/>
+      <c r="N52" s="233"/>
+      <c r="O52" s="234"/>
+      <c r="P52" s="235"/>
       <c r="Q52" s="60"/>
-      <c r="R52" s="253"/>
-      <c r="S52" s="253"/>
+      <c r="R52" s="236"/>
+      <c r="S52" s="236"/>
     </row>
   </sheetData>
   <mergeCells count="205">
-    <mergeCell ref="C52:G52"/>
-    <mergeCell ref="H52:M52"/>
-    <mergeCell ref="N52:P52"/>
-    <mergeCell ref="R52:S52"/>
-    <mergeCell ref="C50:G50"/>
-    <mergeCell ref="H50:M50"/>
-    <mergeCell ref="N50:P50"/>
-    <mergeCell ref="R50:S50"/>
-    <mergeCell ref="C51:G51"/>
-    <mergeCell ref="H51:M51"/>
-    <mergeCell ref="N51:P51"/>
-    <mergeCell ref="R51:S51"/>
-    <mergeCell ref="C48:G48"/>
-    <mergeCell ref="H48:M48"/>
-    <mergeCell ref="N48:P48"/>
-    <mergeCell ref="R48:S48"/>
-    <mergeCell ref="C49:G49"/>
-    <mergeCell ref="H49:M49"/>
-    <mergeCell ref="N49:P49"/>
-    <mergeCell ref="R49:S49"/>
-    <mergeCell ref="C46:G46"/>
-    <mergeCell ref="H46:M46"/>
-    <mergeCell ref="N46:P46"/>
-    <mergeCell ref="R46:S46"/>
-    <mergeCell ref="C47:G47"/>
-    <mergeCell ref="H47:M47"/>
-    <mergeCell ref="N47:P47"/>
-    <mergeCell ref="R47:S47"/>
-    <mergeCell ref="C44:G44"/>
-    <mergeCell ref="H44:M44"/>
-    <mergeCell ref="N44:P44"/>
-    <mergeCell ref="R44:S44"/>
-    <mergeCell ref="C45:G45"/>
-    <mergeCell ref="H45:M45"/>
-    <mergeCell ref="N45:P45"/>
-    <mergeCell ref="R45:S45"/>
-    <mergeCell ref="C42:G42"/>
-    <mergeCell ref="H42:M42"/>
-    <mergeCell ref="N42:P42"/>
-    <mergeCell ref="R42:S42"/>
-    <mergeCell ref="C43:G43"/>
-    <mergeCell ref="H43:M43"/>
-    <mergeCell ref="N43:P43"/>
-    <mergeCell ref="R43:S43"/>
-    <mergeCell ref="C40:G40"/>
-    <mergeCell ref="H40:M40"/>
-    <mergeCell ref="N40:P40"/>
-    <mergeCell ref="R40:S40"/>
-    <mergeCell ref="C41:G41"/>
-    <mergeCell ref="H41:M41"/>
-    <mergeCell ref="N41:P41"/>
-    <mergeCell ref="R41:S41"/>
-    <mergeCell ref="C38:G38"/>
-    <mergeCell ref="H38:M38"/>
-    <mergeCell ref="N38:P38"/>
-    <mergeCell ref="R38:S38"/>
-    <mergeCell ref="C39:G39"/>
-    <mergeCell ref="H39:M39"/>
-    <mergeCell ref="N39:P39"/>
-    <mergeCell ref="R39:S39"/>
-    <mergeCell ref="C36:G36"/>
-    <mergeCell ref="H36:M36"/>
-    <mergeCell ref="N36:P36"/>
-    <mergeCell ref="R36:S36"/>
-    <mergeCell ref="C37:G37"/>
-    <mergeCell ref="H37:M37"/>
-    <mergeCell ref="N37:P37"/>
-    <mergeCell ref="R37:S37"/>
-    <mergeCell ref="C34:G34"/>
-    <mergeCell ref="H34:M34"/>
-    <mergeCell ref="N34:P34"/>
-    <mergeCell ref="R34:S34"/>
-    <mergeCell ref="C35:G35"/>
-    <mergeCell ref="H35:M35"/>
-    <mergeCell ref="N35:P35"/>
-    <mergeCell ref="R35:S35"/>
-    <mergeCell ref="C32:G32"/>
-    <mergeCell ref="H32:M32"/>
-    <mergeCell ref="N32:P32"/>
-    <mergeCell ref="R32:S32"/>
-    <mergeCell ref="C33:G33"/>
-    <mergeCell ref="H33:M33"/>
-    <mergeCell ref="N33:P33"/>
-    <mergeCell ref="R33:S33"/>
-    <mergeCell ref="C30:G30"/>
-    <mergeCell ref="H30:M30"/>
-    <mergeCell ref="N30:P30"/>
-    <mergeCell ref="R30:S30"/>
-    <mergeCell ref="C31:G31"/>
-    <mergeCell ref="H31:M31"/>
-    <mergeCell ref="N31:P31"/>
-    <mergeCell ref="R31:S31"/>
-    <mergeCell ref="C28:G28"/>
-    <mergeCell ref="H28:M28"/>
-    <mergeCell ref="N28:P28"/>
-    <mergeCell ref="R28:S28"/>
-    <mergeCell ref="C29:G29"/>
-    <mergeCell ref="H29:M29"/>
-    <mergeCell ref="N29:P29"/>
-    <mergeCell ref="R29:S29"/>
-    <mergeCell ref="C26:G26"/>
-    <mergeCell ref="H26:M26"/>
-    <mergeCell ref="N26:P26"/>
-    <mergeCell ref="R26:S26"/>
-    <mergeCell ref="C27:G27"/>
-    <mergeCell ref="H27:M27"/>
-    <mergeCell ref="N27:P27"/>
-    <mergeCell ref="R27:S27"/>
-    <mergeCell ref="C24:G24"/>
-    <mergeCell ref="H24:M24"/>
-    <mergeCell ref="N24:P24"/>
-    <mergeCell ref="R24:S24"/>
-    <mergeCell ref="C25:G25"/>
-    <mergeCell ref="H25:M25"/>
-    <mergeCell ref="N25:P25"/>
-    <mergeCell ref="R25:S25"/>
-    <mergeCell ref="C22:G22"/>
-    <mergeCell ref="H22:M22"/>
-    <mergeCell ref="N22:P22"/>
-    <mergeCell ref="R22:S22"/>
-    <mergeCell ref="C23:G23"/>
-    <mergeCell ref="H23:M23"/>
-    <mergeCell ref="N23:P23"/>
-    <mergeCell ref="R23:S23"/>
-    <mergeCell ref="C20:G20"/>
-    <mergeCell ref="H20:M20"/>
-    <mergeCell ref="N20:P20"/>
-    <mergeCell ref="R20:S20"/>
-    <mergeCell ref="C21:G21"/>
-    <mergeCell ref="H21:M21"/>
-    <mergeCell ref="N21:P21"/>
-    <mergeCell ref="R21:S21"/>
-    <mergeCell ref="C18:G18"/>
-    <mergeCell ref="H18:M18"/>
-    <mergeCell ref="N18:P18"/>
-    <mergeCell ref="R18:S18"/>
-    <mergeCell ref="C19:G19"/>
-    <mergeCell ref="H19:M19"/>
-    <mergeCell ref="N19:P19"/>
-    <mergeCell ref="R19:S19"/>
-    <mergeCell ref="C16:G16"/>
-    <mergeCell ref="H16:M16"/>
-    <mergeCell ref="N16:P16"/>
-    <mergeCell ref="R16:S16"/>
-    <mergeCell ref="C17:G17"/>
-    <mergeCell ref="H17:M17"/>
-    <mergeCell ref="N17:P17"/>
-    <mergeCell ref="R17:S17"/>
-    <mergeCell ref="C14:G14"/>
-    <mergeCell ref="H14:M14"/>
-    <mergeCell ref="N14:P14"/>
-    <mergeCell ref="R14:S14"/>
-    <mergeCell ref="C15:G15"/>
-    <mergeCell ref="H15:M15"/>
-    <mergeCell ref="N15:P15"/>
-    <mergeCell ref="R15:S15"/>
-    <mergeCell ref="C12:G12"/>
-    <mergeCell ref="H12:M12"/>
-    <mergeCell ref="N12:P12"/>
-    <mergeCell ref="R12:S12"/>
-    <mergeCell ref="C13:G13"/>
-    <mergeCell ref="H13:M13"/>
-    <mergeCell ref="N13:P13"/>
-    <mergeCell ref="R13:S13"/>
-    <mergeCell ref="C10:G10"/>
-    <mergeCell ref="H10:M10"/>
-    <mergeCell ref="N10:P10"/>
-    <mergeCell ref="R10:S10"/>
-    <mergeCell ref="C11:G11"/>
-    <mergeCell ref="H11:M11"/>
-    <mergeCell ref="N11:P11"/>
-    <mergeCell ref="R11:S11"/>
-    <mergeCell ref="C8:G8"/>
-    <mergeCell ref="H8:M8"/>
-    <mergeCell ref="N8:P8"/>
-    <mergeCell ref="R8:S8"/>
-    <mergeCell ref="C9:G9"/>
-    <mergeCell ref="H9:M9"/>
-    <mergeCell ref="N9:P9"/>
-    <mergeCell ref="R9:S9"/>
-    <mergeCell ref="C6:G6"/>
-    <mergeCell ref="H6:M6"/>
-    <mergeCell ref="N6:P6"/>
-    <mergeCell ref="R6:S6"/>
-    <mergeCell ref="C7:G7"/>
-    <mergeCell ref="H7:M7"/>
-    <mergeCell ref="N7:P7"/>
-    <mergeCell ref="R7:S7"/>
     <mergeCell ref="C4:G4"/>
     <mergeCell ref="H4:M4"/>
     <mergeCell ref="N4:P4"/>
@@ -22070,6 +21962,194 @@
     <mergeCell ref="F2:M2"/>
     <mergeCell ref="O2:P2"/>
     <mergeCell ref="R2:S2"/>
+    <mergeCell ref="C8:G8"/>
+    <mergeCell ref="H8:M8"/>
+    <mergeCell ref="N8:P8"/>
+    <mergeCell ref="R8:S8"/>
+    <mergeCell ref="C9:G9"/>
+    <mergeCell ref="H9:M9"/>
+    <mergeCell ref="N9:P9"/>
+    <mergeCell ref="R9:S9"/>
+    <mergeCell ref="C6:G6"/>
+    <mergeCell ref="H6:M6"/>
+    <mergeCell ref="N6:P6"/>
+    <mergeCell ref="R6:S6"/>
+    <mergeCell ref="C7:G7"/>
+    <mergeCell ref="H7:M7"/>
+    <mergeCell ref="N7:P7"/>
+    <mergeCell ref="R7:S7"/>
+    <mergeCell ref="C12:G12"/>
+    <mergeCell ref="H12:M12"/>
+    <mergeCell ref="N12:P12"/>
+    <mergeCell ref="R12:S12"/>
+    <mergeCell ref="C13:G13"/>
+    <mergeCell ref="H13:M13"/>
+    <mergeCell ref="N13:P13"/>
+    <mergeCell ref="R13:S13"/>
+    <mergeCell ref="C10:G10"/>
+    <mergeCell ref="H10:M10"/>
+    <mergeCell ref="N10:P10"/>
+    <mergeCell ref="R10:S10"/>
+    <mergeCell ref="C11:G11"/>
+    <mergeCell ref="H11:M11"/>
+    <mergeCell ref="N11:P11"/>
+    <mergeCell ref="R11:S11"/>
+    <mergeCell ref="C16:G16"/>
+    <mergeCell ref="H16:M16"/>
+    <mergeCell ref="N16:P16"/>
+    <mergeCell ref="R16:S16"/>
+    <mergeCell ref="C17:G17"/>
+    <mergeCell ref="H17:M17"/>
+    <mergeCell ref="N17:P17"/>
+    <mergeCell ref="R17:S17"/>
+    <mergeCell ref="C14:G14"/>
+    <mergeCell ref="H14:M14"/>
+    <mergeCell ref="N14:P14"/>
+    <mergeCell ref="R14:S14"/>
+    <mergeCell ref="C15:G15"/>
+    <mergeCell ref="H15:M15"/>
+    <mergeCell ref="N15:P15"/>
+    <mergeCell ref="R15:S15"/>
+    <mergeCell ref="C20:G20"/>
+    <mergeCell ref="H20:M20"/>
+    <mergeCell ref="N20:P20"/>
+    <mergeCell ref="R20:S20"/>
+    <mergeCell ref="C21:G21"/>
+    <mergeCell ref="H21:M21"/>
+    <mergeCell ref="N21:P21"/>
+    <mergeCell ref="R21:S21"/>
+    <mergeCell ref="C18:G18"/>
+    <mergeCell ref="H18:M18"/>
+    <mergeCell ref="N18:P18"/>
+    <mergeCell ref="R18:S18"/>
+    <mergeCell ref="C19:G19"/>
+    <mergeCell ref="H19:M19"/>
+    <mergeCell ref="N19:P19"/>
+    <mergeCell ref="R19:S19"/>
+    <mergeCell ref="C24:G24"/>
+    <mergeCell ref="H24:M24"/>
+    <mergeCell ref="N24:P24"/>
+    <mergeCell ref="R24:S24"/>
+    <mergeCell ref="C25:G25"/>
+    <mergeCell ref="H25:M25"/>
+    <mergeCell ref="N25:P25"/>
+    <mergeCell ref="R25:S25"/>
+    <mergeCell ref="C22:G22"/>
+    <mergeCell ref="H22:M22"/>
+    <mergeCell ref="N22:P22"/>
+    <mergeCell ref="R22:S22"/>
+    <mergeCell ref="C23:G23"/>
+    <mergeCell ref="H23:M23"/>
+    <mergeCell ref="N23:P23"/>
+    <mergeCell ref="R23:S23"/>
+    <mergeCell ref="C28:G28"/>
+    <mergeCell ref="H28:M28"/>
+    <mergeCell ref="N28:P28"/>
+    <mergeCell ref="R28:S28"/>
+    <mergeCell ref="C29:G29"/>
+    <mergeCell ref="H29:M29"/>
+    <mergeCell ref="N29:P29"/>
+    <mergeCell ref="R29:S29"/>
+    <mergeCell ref="C26:G26"/>
+    <mergeCell ref="H26:M26"/>
+    <mergeCell ref="N26:P26"/>
+    <mergeCell ref="R26:S26"/>
+    <mergeCell ref="C27:G27"/>
+    <mergeCell ref="H27:M27"/>
+    <mergeCell ref="N27:P27"/>
+    <mergeCell ref="R27:S27"/>
+    <mergeCell ref="C32:G32"/>
+    <mergeCell ref="H32:M32"/>
+    <mergeCell ref="N32:P32"/>
+    <mergeCell ref="R32:S32"/>
+    <mergeCell ref="C33:G33"/>
+    <mergeCell ref="H33:M33"/>
+    <mergeCell ref="N33:P33"/>
+    <mergeCell ref="R33:S33"/>
+    <mergeCell ref="C30:G30"/>
+    <mergeCell ref="H30:M30"/>
+    <mergeCell ref="N30:P30"/>
+    <mergeCell ref="R30:S30"/>
+    <mergeCell ref="C31:G31"/>
+    <mergeCell ref="H31:M31"/>
+    <mergeCell ref="N31:P31"/>
+    <mergeCell ref="R31:S31"/>
+    <mergeCell ref="C36:G36"/>
+    <mergeCell ref="H36:M36"/>
+    <mergeCell ref="N36:P36"/>
+    <mergeCell ref="R36:S36"/>
+    <mergeCell ref="C37:G37"/>
+    <mergeCell ref="H37:M37"/>
+    <mergeCell ref="N37:P37"/>
+    <mergeCell ref="R37:S37"/>
+    <mergeCell ref="C34:G34"/>
+    <mergeCell ref="H34:M34"/>
+    <mergeCell ref="N34:P34"/>
+    <mergeCell ref="R34:S34"/>
+    <mergeCell ref="C35:G35"/>
+    <mergeCell ref="H35:M35"/>
+    <mergeCell ref="N35:P35"/>
+    <mergeCell ref="R35:S35"/>
+    <mergeCell ref="C40:G40"/>
+    <mergeCell ref="H40:M40"/>
+    <mergeCell ref="N40:P40"/>
+    <mergeCell ref="R40:S40"/>
+    <mergeCell ref="C41:G41"/>
+    <mergeCell ref="H41:M41"/>
+    <mergeCell ref="N41:P41"/>
+    <mergeCell ref="R41:S41"/>
+    <mergeCell ref="C38:G38"/>
+    <mergeCell ref="H38:M38"/>
+    <mergeCell ref="N38:P38"/>
+    <mergeCell ref="R38:S38"/>
+    <mergeCell ref="C39:G39"/>
+    <mergeCell ref="H39:M39"/>
+    <mergeCell ref="N39:P39"/>
+    <mergeCell ref="R39:S39"/>
+    <mergeCell ref="C44:G44"/>
+    <mergeCell ref="H44:M44"/>
+    <mergeCell ref="N44:P44"/>
+    <mergeCell ref="R44:S44"/>
+    <mergeCell ref="C45:G45"/>
+    <mergeCell ref="H45:M45"/>
+    <mergeCell ref="N45:P45"/>
+    <mergeCell ref="R45:S45"/>
+    <mergeCell ref="C42:G42"/>
+    <mergeCell ref="H42:M42"/>
+    <mergeCell ref="N42:P42"/>
+    <mergeCell ref="R42:S42"/>
+    <mergeCell ref="C43:G43"/>
+    <mergeCell ref="H43:M43"/>
+    <mergeCell ref="N43:P43"/>
+    <mergeCell ref="R43:S43"/>
+    <mergeCell ref="C48:G48"/>
+    <mergeCell ref="H48:M48"/>
+    <mergeCell ref="N48:P48"/>
+    <mergeCell ref="R48:S48"/>
+    <mergeCell ref="C49:G49"/>
+    <mergeCell ref="H49:M49"/>
+    <mergeCell ref="N49:P49"/>
+    <mergeCell ref="R49:S49"/>
+    <mergeCell ref="C46:G46"/>
+    <mergeCell ref="H46:M46"/>
+    <mergeCell ref="N46:P46"/>
+    <mergeCell ref="R46:S46"/>
+    <mergeCell ref="C47:G47"/>
+    <mergeCell ref="H47:M47"/>
+    <mergeCell ref="N47:P47"/>
+    <mergeCell ref="R47:S47"/>
+    <mergeCell ref="C52:G52"/>
+    <mergeCell ref="H52:M52"/>
+    <mergeCell ref="N52:P52"/>
+    <mergeCell ref="R52:S52"/>
+    <mergeCell ref="C50:G50"/>
+    <mergeCell ref="H50:M50"/>
+    <mergeCell ref="N50:P50"/>
+    <mergeCell ref="R50:S50"/>
+    <mergeCell ref="C51:G51"/>
+    <mergeCell ref="H51:M51"/>
+    <mergeCell ref="N51:P51"/>
+    <mergeCell ref="R51:S51"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.31496062992125984" bottom="0.27559055118110237" header="0.35433070866141736" footer="0.15748031496062992"/>

--- a/Documents/登録機能詳細設計書.xlsx
+++ b/Documents/登録機能詳細設計書.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\S-47\Documents\project\taskUN\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34A78630-FBCC-44F8-BC69-3280335D790A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41EEBBBA-3DDE-43CC-849C-3444A7C69FD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,8 +23,15 @@
     <sheet name="テスト仕様書兼結果報告書" sheetId="6" r:id="rId8"/>
     <sheet name="JUnitテスト仕様書兼報告書" sheetId="15" r:id="rId9"/>
     <sheet name="カバレッジレポート" sheetId="16" r:id="rId10"/>
+    <sheet name="エビデンス" sheetId="17" r:id="rId11"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId12"/>
+    <externalReference r:id="rId13"/>
+  </externalReferences>
   <definedNames>
+    <definedName name="あ">#REF!</definedName>
+    <definedName name="ああ" localSheetId="10">#REF!</definedName>
     <definedName name="ああ">#REF!</definedName>
     <definedName name="範囲１" localSheetId="8">#REF!</definedName>
     <definedName name="範囲１">#REF!</definedName>
@@ -34,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="169">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="178">
   <si>
     <t>プロジェクト型演習　成果ドキュメント</t>
   </si>
@@ -204,7 +211,7 @@
     <rPh sb="2" eb="3">
       <t>キ</t>
     </rPh>
-    <phoneticPr fontId="8"/>
+    <phoneticPr fontId="9"/>
   </si>
   <si>
     <t>登録機能詳細設計書</t>
@@ -217,18 +224,18 @@
     <rPh sb="6" eb="9">
       <t>セッケイショ</t>
     </rPh>
-    <phoneticPr fontId="8"/>
+    <phoneticPr fontId="9"/>
   </si>
   <si>
     <t>山本あずさ</t>
     <rPh sb="0" eb="2">
       <t>ヤマモト</t>
     </rPh>
-    <phoneticPr fontId="8"/>
+    <phoneticPr fontId="9"/>
   </si>
   <si>
     <t>ユーザ</t>
-    <phoneticPr fontId="12"/>
+    <phoneticPr fontId="13"/>
   </si>
   <si>
     <t>新規のタスクを登録する</t>
@@ -238,7 +245,7 @@
     <rPh sb="7" eb="9">
       <t>トウロク</t>
     </rPh>
-    <phoneticPr fontId="12"/>
+    <phoneticPr fontId="13"/>
   </si>
   <si>
     <t>新規タスク登録</t>
@@ -248,34 +255,34 @@
     <rPh sb="5" eb="7">
       <t>トウロク</t>
     </rPh>
-    <phoneticPr fontId="12"/>
+    <phoneticPr fontId="13"/>
   </si>
   <si>
     <t>山本（あ）</t>
     <rPh sb="0" eb="2">
       <t>ヤマモト</t>
     </rPh>
-    <phoneticPr fontId="12"/>
+    <phoneticPr fontId="13"/>
   </si>
   <si>
     <t>taskUN</t>
-    <phoneticPr fontId="12"/>
+    <phoneticPr fontId="13"/>
   </si>
   <si>
     <t>クリア</t>
-    <phoneticPr fontId="8"/>
+    <phoneticPr fontId="9"/>
   </si>
   <si>
     <t>reset</t>
-    <phoneticPr fontId="8"/>
+    <phoneticPr fontId="9"/>
   </si>
   <si>
     <t>なし</t>
-    <phoneticPr fontId="8"/>
+    <phoneticPr fontId="9"/>
   </si>
   <si>
     <t>submit</t>
-    <phoneticPr fontId="8"/>
+    <phoneticPr fontId="9"/>
   </si>
   <si>
     <t>選択されたカテゴリ名のカテゴリIDを送る,必須入力</t>
@@ -291,23 +298,23 @@
     <rPh sb="21" eb="25">
       <t>ヒッスニュウリョク</t>
     </rPh>
-    <phoneticPr fontId="8"/>
+    <phoneticPr fontId="9"/>
   </si>
   <si>
     <t>カテゴリーID</t>
-    <phoneticPr fontId="8"/>
+    <phoneticPr fontId="9"/>
   </si>
   <si>
     <t>category</t>
-    <phoneticPr fontId="8"/>
+    <phoneticPr fontId="9"/>
   </si>
   <si>
     <t>select</t>
-    <phoneticPr fontId="8"/>
+    <phoneticPr fontId="9"/>
   </si>
   <si>
     <t>カテゴリ</t>
-    <phoneticPr fontId="8"/>
+    <phoneticPr fontId="9"/>
   </si>
   <si>
     <t>入力値</t>
@@ -317,34 +324,34 @@
     <rPh sb="2" eb="3">
       <t>チ</t>
     </rPh>
-    <phoneticPr fontId="8"/>
+    <phoneticPr fontId="9"/>
   </si>
   <si>
     <t>memo</t>
-    <phoneticPr fontId="8"/>
+    <phoneticPr fontId="9"/>
   </si>
   <si>
     <t>text</t>
-    <phoneticPr fontId="8"/>
+    <phoneticPr fontId="9"/>
   </si>
   <si>
     <t>メモ</t>
-    <phoneticPr fontId="8"/>
+    <phoneticPr fontId="9"/>
   </si>
   <si>
     <t>limit</t>
-    <phoneticPr fontId="8"/>
+    <phoneticPr fontId="9"/>
   </si>
   <si>
     <t>date</t>
-    <phoneticPr fontId="8"/>
+    <phoneticPr fontId="9"/>
   </si>
   <si>
     <t>期限</t>
     <rPh sb="0" eb="2">
       <t>キゲン</t>
     </rPh>
-    <phoneticPr fontId="8"/>
+    <phoneticPr fontId="9"/>
   </si>
   <si>
     <t>50文字以内,必須入力</t>
@@ -357,41 +364,41 @@
     <rPh sb="7" eb="11">
       <t>ヒッスニュウリョク</t>
     </rPh>
-    <phoneticPr fontId="8"/>
+    <phoneticPr fontId="9"/>
   </si>
   <si>
     <t>taskName</t>
-    <phoneticPr fontId="8"/>
+    <phoneticPr fontId="9"/>
   </si>
   <si>
     <t>タスク名</t>
     <rPh sb="3" eb="4">
       <t>メイ</t>
     </rPh>
-    <phoneticPr fontId="8"/>
+    <phoneticPr fontId="9"/>
   </si>
   <si>
     <t>post</t>
-    <phoneticPr fontId="8"/>
+    <phoneticPr fontId="9"/>
   </si>
   <si>
     <t>task-add-servlet</t>
-    <phoneticPr fontId="8"/>
+    <phoneticPr fontId="9"/>
   </si>
   <si>
     <t>山本（あ）</t>
     <rPh sb="0" eb="2">
       <t>ヤマモト</t>
     </rPh>
-    <phoneticPr fontId="8"/>
+    <phoneticPr fontId="9"/>
   </si>
   <si>
     <t>taskUN</t>
-    <phoneticPr fontId="8"/>
+    <phoneticPr fontId="9"/>
   </si>
   <si>
     <t>taskUk</t>
-    <phoneticPr fontId="8"/>
+    <phoneticPr fontId="9"/>
   </si>
   <si>
     <t>タスク登録完了画面/task-add-success.jsp</t>
@@ -401,15 +408,15 @@
     <rPh sb="5" eb="9">
       <t>カンリョウガメン</t>
     </rPh>
-    <phoneticPr fontId="8"/>
+    <phoneticPr fontId="9"/>
   </si>
   <si>
     <t>menu.jsp</t>
-    <phoneticPr fontId="8"/>
+    <phoneticPr fontId="9"/>
   </si>
   <si>
     <t>get</t>
-    <phoneticPr fontId="8"/>
+    <phoneticPr fontId="9"/>
   </si>
   <si>
     <t>メニュー画面に戻る</t>
@@ -419,7 +426,7 @@
     <rPh sb="7" eb="8">
       <t>モド</t>
     </rPh>
-    <phoneticPr fontId="8"/>
+    <phoneticPr fontId="9"/>
   </si>
   <si>
     <t>全部左上に寄せる</t>
@@ -432,7 +439,7 @@
     <rPh sb="5" eb="6">
       <t>ヨ</t>
     </rPh>
-    <phoneticPr fontId="8"/>
+    <phoneticPr fontId="9"/>
   </si>
   <si>
     <t>エラー（登録失敗）画面/task-add-failure.jsp</t>
@@ -442,7 +449,7 @@
     <rPh sb="9" eb="11">
       <t>ガメン</t>
     </rPh>
-    <phoneticPr fontId="8"/>
+    <phoneticPr fontId="9"/>
   </si>
   <si>
     <t>新規タスク登録/task-add-form</t>
@@ -452,7 +459,7 @@
     <rPh sb="5" eb="7">
       <t>トウロク</t>
     </rPh>
-    <phoneticPr fontId="8"/>
+    <phoneticPr fontId="9"/>
   </si>
   <si>
     <t>3.1：備考、期限の情報は入力しなくても登録できる。</t>
@@ -468,33 +475,33 @@
     <rPh sb="20" eb="22">
       <t>トウロク</t>
     </rPh>
-    <phoneticPr fontId="12"/>
+    <phoneticPr fontId="13"/>
   </si>
   <si>
     <t>担当者のユーザID</t>
     <rPh sb="0" eb="3">
       <t>タントウシャ</t>
     </rPh>
-    <phoneticPr fontId="8"/>
+    <phoneticPr fontId="9"/>
   </si>
   <si>
     <t>userId</t>
-    <phoneticPr fontId="8"/>
+    <phoneticPr fontId="9"/>
   </si>
   <si>
     <t>入力値</t>
     <rPh sb="0" eb="3">
       <t>ニュウリョクチ</t>
     </rPh>
-    <phoneticPr fontId="8"/>
+    <phoneticPr fontId="9"/>
   </si>
   <si>
     <t>ステータス</t>
-    <phoneticPr fontId="8"/>
+    <phoneticPr fontId="9"/>
   </si>
   <si>
     <t>ステータスID</t>
-    <phoneticPr fontId="8"/>
+    <phoneticPr fontId="9"/>
   </si>
   <si>
     <t>選択されたステータス名のステータスIDを送る,必須入力</t>
@@ -510,11 +517,11 @@
     <rPh sb="23" eb="27">
       <t>ヒッスニュウリョク</t>
     </rPh>
-    <phoneticPr fontId="8"/>
+    <phoneticPr fontId="9"/>
   </si>
   <si>
     <t>status</t>
-    <phoneticPr fontId="8"/>
+    <phoneticPr fontId="9"/>
   </si>
   <si>
     <t>登録実行</t>
@@ -524,14 +531,14 @@
     <rPh sb="2" eb="4">
       <t>ジッコウ</t>
     </rPh>
-    <phoneticPr fontId="8"/>
+    <phoneticPr fontId="9"/>
   </si>
   <si>
     <t>カレンダーで選択</t>
     <rPh sb="6" eb="8">
       <t>センタク</t>
     </rPh>
-    <phoneticPr fontId="8"/>
+    <phoneticPr fontId="9"/>
   </si>
   <si>
     <t>100文字以内必須入力</t>
@@ -541,14 +548,14 @@
     <rPh sb="7" eb="11">
       <t>ヒッスニュウリョク</t>
     </rPh>
-    <phoneticPr fontId="8"/>
+    <phoneticPr fontId="9"/>
   </si>
   <si>
     <t>必須入力</t>
     <rPh sb="0" eb="4">
       <t>ヒッスニュウリョク</t>
     </rPh>
-    <phoneticPr fontId="8"/>
+    <phoneticPr fontId="9"/>
   </si>
   <si>
     <t>1:：タスク名、カテゴリ情報(プルダウン)、期限、担当者情報(ユーザID)、ステータス情報(プルダウン)、備考(メモ)を入力する。
@@ -591,7 +598,7 @@
     <rPh sb="136" eb="138">
       <t>センイ</t>
     </rPh>
-    <phoneticPr fontId="12"/>
+    <phoneticPr fontId="13"/>
   </si>
   <si>
     <t>基本・代替フロー：タスクテーブルに入力した情報が追加されタスク登録完了画面に遷移する。
@@ -641,7 +648,7 @@
     <rPh sb="75" eb="77">
       <t>センイ</t>
     </rPh>
-    <phoneticPr fontId="12"/>
+    <phoneticPr fontId="13"/>
   </si>
   <si>
     <t>ログイン済みであること、入力する担当者情報(ユーザID)がユーザマスタに存在していること、
@@ -670,7 +677,7 @@
     <rPh sb="87" eb="89">
       <t>ソンザイ</t>
     </rPh>
-    <phoneticPr fontId="12"/>
+    <phoneticPr fontId="13"/>
   </si>
   <si>
     <t>3.2：備考、期限以外の情報が1つでも入力されていない場合登録は失敗し、
@@ -693,28 +700,28 @@
     <rPh sb="51" eb="53">
       <t>センイ</t>
     </rPh>
-    <phoneticPr fontId="12"/>
+    <phoneticPr fontId="13"/>
   </si>
   <si>
     <t>山本(あ)</t>
     <rPh sb="0" eb="2">
       <t>ヤマモト</t>
     </rPh>
-    <phoneticPr fontId="8"/>
+    <phoneticPr fontId="9"/>
   </si>
   <si>
     <t>山形</t>
     <rPh sb="0" eb="2">
       <t>ヤマガタ</t>
     </rPh>
-    <phoneticPr fontId="8"/>
+    <phoneticPr fontId="9"/>
   </si>
   <si>
     <t>登録画面</t>
     <rPh sb="0" eb="4">
       <t>トウロクガメン</t>
     </rPh>
-    <phoneticPr fontId="8"/>
+    <phoneticPr fontId="9"/>
   </si>
   <si>
     <t>メニュー画面から登録画面へページ遷移</t>
@@ -727,7 +734,7 @@
     <rPh sb="16" eb="18">
       <t>センイ</t>
     </rPh>
-    <phoneticPr fontId="8"/>
+    <phoneticPr fontId="9"/>
   </si>
   <si>
     <t>ログイン状態かつデータベースに接続されていること</t>
@@ -737,7 +744,7 @@
     <rPh sb="15" eb="17">
       <t>セツゾク</t>
     </rPh>
-    <phoneticPr fontId="8"/>
+    <phoneticPr fontId="9"/>
   </si>
   <si>
     <t>タスク登録ボタンを押下する</t>
@@ -747,7 +754,7 @@
     <rPh sb="9" eb="11">
       <t>オウカ</t>
     </rPh>
-    <phoneticPr fontId="8"/>
+    <phoneticPr fontId="9"/>
   </si>
   <si>
     <t>タスク登録画面が表示される</t>
@@ -757,7 +764,7 @@
     <rPh sb="8" eb="10">
       <t>ヒョウジ</t>
     </rPh>
-    <phoneticPr fontId="8"/>
+    <phoneticPr fontId="9"/>
   </si>
   <si>
     <t>ログインされていない状態でタスク登録画面の表示させる</t>
@@ -773,25 +780,25 @@
     <rPh sb="21" eb="23">
       <t>ヒョウジ</t>
     </rPh>
-    <phoneticPr fontId="8"/>
+    <phoneticPr fontId="9"/>
   </si>
   <si>
     <t>ログアウト状態であること</t>
     <rPh sb="5" eb="7">
       <t>ジョウタイ</t>
     </rPh>
-    <phoneticPr fontId="8"/>
+    <phoneticPr fontId="9"/>
   </si>
   <si>
     <t>異常系</t>
     <rPh sb="0" eb="3">
       <t>イジョウケイ</t>
     </rPh>
-    <phoneticPr fontId="8"/>
+    <phoneticPr fontId="9"/>
   </si>
   <si>
     <t>http://localhost:8080/taskUN/task-add-form.jsp</t>
-    <phoneticPr fontId="8"/>
+    <phoneticPr fontId="9"/>
   </si>
   <si>
     <t>タスク登録成功画面が表示される</t>
@@ -807,7 +814,7 @@
     <rPh sb="10" eb="12">
       <t>ヒョウジ</t>
     </rPh>
-    <phoneticPr fontId="8"/>
+    <phoneticPr fontId="9"/>
   </si>
   <si>
     <t>タスク登録失敗画面が表示される</t>
@@ -823,7 +830,7 @@
     <rPh sb="10" eb="12">
       <t>ヒョウジ</t>
     </rPh>
-    <phoneticPr fontId="8"/>
+    <phoneticPr fontId="9"/>
   </si>
   <si>
     <t>ログインされていませんというメッセージとログイン画面に誘導するリンクが表示される</t>
@@ -836,7 +843,7 @@
     <rPh sb="35" eb="37">
       <t>ヒョウジ</t>
     </rPh>
-    <phoneticPr fontId="8"/>
+    <phoneticPr fontId="9"/>
   </si>
   <si>
     <t>JUnitテスト仕様書兼報告書</t>
@@ -849,14 +856,14 @@
     <rPh sb="12" eb="15">
       <t>ホウコクショ</t>
     </rPh>
-    <phoneticPr fontId="16"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>システム名</t>
     <rPh sb="4" eb="5">
       <t>メイ</t>
     </rPh>
-    <phoneticPr fontId="16"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>作成者</t>
@@ -866,25 +873,25 @@
     <rPh sb="0" eb="3">
       <t>カイシャメイ</t>
     </rPh>
-    <phoneticPr fontId="16"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>コンサイズ</t>
-    <phoneticPr fontId="16"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>サブシステム名</t>
     <rPh sb="6" eb="7">
       <t>メイ</t>
     </rPh>
-    <phoneticPr fontId="16"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>作成日</t>
     <rPh sb="0" eb="3">
       <t>サクセイビ</t>
     </rPh>
-    <phoneticPr fontId="16"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>実施者</t>
@@ -894,29 +901,29 @@
     <rPh sb="2" eb="3">
       <t>シャ</t>
     </rPh>
-    <phoneticPr fontId="16"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>No</t>
-    <phoneticPr fontId="16"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>分類</t>
     <rPh sb="0" eb="2">
       <t>ブンルイ</t>
     </rPh>
-    <phoneticPr fontId="16"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>テストクラス</t>
-    <phoneticPr fontId="16"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>検証するメソッド</t>
     <rPh sb="0" eb="2">
       <t>ケンショウ</t>
     </rPh>
-    <phoneticPr fontId="16"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>期待する結果</t>
@@ -926,14 +933,14 @@
     <rPh sb="4" eb="6">
       <t>ケッカ</t>
     </rPh>
-    <phoneticPr fontId="16"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>実施日</t>
     <rPh sb="0" eb="3">
       <t>ジッシビ</t>
     </rPh>
-    <phoneticPr fontId="16"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>備考・特記事項</t>
@@ -946,11 +953,11 @@
     <rPh sb="5" eb="7">
       <t>ジコウ</t>
     </rPh>
-    <phoneticPr fontId="16"/>
+    <phoneticPr fontId="17"/>
   </si>
   <si>
     <t>◎</t>
-    <phoneticPr fontId="8"/>
+    <phoneticPr fontId="9"/>
   </si>
   <si>
     <t>タスク名、カテゴリー、ステータス、期限、ユーザ名、メモを入力しタスク登録を行ったときタスク登録成功ページが表示される</t>
@@ -981,7 +988,7 @@
     <rPh sb="53" eb="55">
       <t>ヒョウジ</t>
     </rPh>
-    <phoneticPr fontId="8"/>
+    <phoneticPr fontId="9"/>
   </si>
   <si>
     <t>タスク名、カテゴリー、ユーザーID、ステータスが未入力ではない、タスク名が50文字以下メモが100文字以下、ユーザーIDが24文字以下、期限が今日より後であること</t>
@@ -1000,7 +1007,7 @@
     <rPh sb="75" eb="76">
       <t>アト</t>
     </rPh>
-    <phoneticPr fontId="8"/>
+    <phoneticPr fontId="9"/>
   </si>
   <si>
     <t>タスク名、ユーザーID、カテゴリー、ステータスのいずれか1つでも入力せずタスク登録を行ったときタスク登録失敗ページが表示される</t>
@@ -1025,19 +1032,19 @@
     <rPh sb="58" eb="60">
       <t>ヒョウジ</t>
     </rPh>
-    <phoneticPr fontId="8"/>
+    <phoneticPr fontId="9"/>
   </si>
   <si>
     <t>タスク名、ユーザーID、カテゴリー、ステータスのいずれか1つでも未入力</t>
     <rPh sb="32" eb="35">
       <t>ミニュウリョク</t>
     </rPh>
-    <phoneticPr fontId="8"/>
+    <phoneticPr fontId="9"/>
   </si>
   <si>
     <t xml:space="preserve">正常系
 </t>
-    <phoneticPr fontId="8"/>
+    <phoneticPr fontId="9"/>
   </si>
   <si>
     <t>タスク名が５１文字以上またはユーザ名が25文字以上またはメモが１０１文字以上である</t>
@@ -1062,7 +1069,7 @@
     <rPh sb="36" eb="38">
       <t>イジョウ</t>
     </rPh>
-    <phoneticPr fontId="8"/>
+    <phoneticPr fontId="9"/>
   </si>
   <si>
     <t>タスク名、カテゴリー、ユーザーID、ステータスが未入力ではない、タスク名が50文字以下ユーザーIDが24文字以下であること</t>
@@ -1072,7 +1079,7 @@
     <rPh sb="39" eb="43">
       <t>モジイカ</t>
     </rPh>
-    <phoneticPr fontId="8"/>
+    <phoneticPr fontId="9"/>
   </si>
   <si>
     <t>タスク名、カテゴリー、ステータス、ユーザ名、入力しタスク登録を行ったときタスク登録成功ページが表示される。（期限、メモは入力しない)</t>
@@ -1106,29 +1113,29 @@
     <rPh sb="60" eb="62">
       <t>ニュウリョク</t>
     </rPh>
-    <phoneticPr fontId="8"/>
+    <phoneticPr fontId="9"/>
   </si>
   <si>
     <t>登録機能</t>
     <rPh sb="0" eb="4">
       <t>トウロクキノウ</t>
     </rPh>
-    <phoneticPr fontId="8"/>
+    <phoneticPr fontId="9"/>
   </si>
   <si>
     <t>正常系</t>
     <rPh sb="0" eb="3">
       <t>セイジョウケイ</t>
     </rPh>
-    <phoneticPr fontId="8"/>
+    <phoneticPr fontId="9"/>
   </si>
   <si>
     <t>insert(TaskBean)</t>
-    <phoneticPr fontId="8"/>
+    <phoneticPr fontId="9"/>
   </si>
   <si>
     <t>TaskDAOTest</t>
-    <phoneticPr fontId="8"/>
+    <phoneticPr fontId="9"/>
   </si>
   <si>
     <t>正しいタスク名、カテゴリー、ユーザID、ステータス、期限、メモを入力した時に返ってくる値が１</t>
@@ -1153,7 +1160,7 @@
     <rPh sb="43" eb="44">
       <t>アタイ</t>
     </rPh>
-    <phoneticPr fontId="8"/>
+    <phoneticPr fontId="9"/>
   </si>
   <si>
     <t>期限、メモがnull、他が正しい値を入力した時返ってくる値が１</t>
@@ -1181,7 +1188,7 @@
     <rPh sb="28" eb="29">
       <t>アタイ</t>
     </rPh>
-    <phoneticPr fontId="8"/>
+    <phoneticPr fontId="9"/>
   </si>
   <si>
     <t>不正な値を入力した時返ってくる値が0</t>
@@ -1203,7 +1210,7 @@
     <rPh sb="15" eb="16">
       <t>アタイ</t>
     </rPh>
-    <phoneticPr fontId="8"/>
+    <phoneticPr fontId="9"/>
   </si>
   <si>
     <t>タスク名、ユーザ名、メモのいずれかが最大の文字数を超過しているときタスク登録に失敗する。タスク名(100文字以下)ユーザ名(24文字以下)メモ(100文字以下)</t>
@@ -1243,39 +1250,39 @@
     <rPh sb="75" eb="79">
       <t>モジイカ</t>
     </rPh>
-    <phoneticPr fontId="8"/>
+    <phoneticPr fontId="9"/>
   </si>
   <si>
     <t>カバレッジレポート</t>
-    <phoneticPr fontId="23"/>
+    <phoneticPr fontId="24"/>
   </si>
   <si>
     <t>実施日</t>
     <rPh sb="0" eb="3">
       <t>ジッシビ</t>
     </rPh>
-    <phoneticPr fontId="23"/>
+    <phoneticPr fontId="24"/>
   </si>
   <si>
     <t>（１）概要</t>
     <rPh sb="3" eb="5">
       <t>ガイヨウ</t>
     </rPh>
-    <phoneticPr fontId="23"/>
+    <phoneticPr fontId="24"/>
   </si>
   <si>
     <t>対象クラス</t>
     <rPh sb="0" eb="2">
       <t>タイショウ</t>
     </rPh>
-    <phoneticPr fontId="23"/>
+    <phoneticPr fontId="24"/>
   </si>
   <si>
     <t>カバレッジ率</t>
     <rPh sb="5" eb="6">
       <t>リツ</t>
     </rPh>
-    <phoneticPr fontId="23"/>
+    <phoneticPr fontId="24"/>
   </si>
   <si>
     <t>（２）報告事項</t>
@@ -1285,7 +1292,7 @@
     <rPh sb="5" eb="7">
       <t>ジコウ</t>
     </rPh>
-    <phoneticPr fontId="23"/>
+    <phoneticPr fontId="24"/>
   </si>
   <si>
     <t>調査結果</t>
@@ -1295,7 +1302,7 @@
     <rPh sb="2" eb="4">
       <t>ケッカ</t>
     </rPh>
-    <phoneticPr fontId="23"/>
+    <phoneticPr fontId="24"/>
   </si>
   <si>
     <t>分析・考察</t>
@@ -1305,7 +1312,7 @@
     <rPh sb="3" eb="5">
       <t>コウサツ</t>
     </rPh>
-    <phoneticPr fontId="23"/>
+    <phoneticPr fontId="24"/>
   </si>
   <si>
     <t>備　考</t>
@@ -1315,15 +1322,15 @@
     <rPh sb="2" eb="3">
       <t>コウ</t>
     </rPh>
-    <phoneticPr fontId="23"/>
+    <phoneticPr fontId="24"/>
   </si>
   <si>
     <t>TaskDAO.Java</t>
-    <phoneticPr fontId="8"/>
+    <phoneticPr fontId="9"/>
   </si>
   <si>
     <t>異常系</t>
-    <phoneticPr fontId="8"/>
+    <phoneticPr fontId="9"/>
   </si>
   <si>
     <t>ログアウト状態でのページ表示</t>
@@ -1333,7 +1340,7 @@
     <rPh sb="12" eb="14">
       <t>ヒョウジ</t>
     </rPh>
-    <phoneticPr fontId="8"/>
+    <phoneticPr fontId="9"/>
   </si>
   <si>
     <t>ログインされていませんというメッセージが表示され、その下にログイン画面へ誘導するリンクが表示される</t>
@@ -1352,11 +1359,71 @@
     <rPh sb="44" eb="46">
       <t>ヒョウジ</t>
     </rPh>
-    <phoneticPr fontId="8"/>
+    <phoneticPr fontId="9"/>
   </si>
   <si>
     <t>〇</t>
-    <phoneticPr fontId="8"/>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>テストエビデンス</t>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>システム名</t>
+    <rPh sb="4" eb="5">
+      <t>メイ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>グループ名</t>
+    <rPh sb="4" eb="5">
+      <t>メイ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>作成日</t>
+    <rPh sb="0" eb="3">
+      <t>サクセイビ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>担当</t>
+    <rPh sb="0" eb="2">
+      <t>タントウ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>承認印</t>
+    <rPh sb="0" eb="3">
+      <t>ショウニンイン</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>機能名称</t>
+    <rPh sb="0" eb="2">
+      <t>キノウ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>メイショウ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>項番</t>
+    <rPh sb="0" eb="2">
+      <t>コウバン</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>エビデンス</t>
+    <phoneticPr fontId="13"/>
   </si>
 </sst>
 </file>
@@ -1366,11 +1433,19 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="[$-411]h:mm"/>
   </numFmts>
-  <fonts count="28">
+  <fonts count="29">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="128"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1580,7 +1655,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="77">
+  <borders count="88">
     <border>
       <left/>
       <right/>
@@ -2478,24 +2553,403 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="8">
+  <cellStyleXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="270">
+  <cellXfs count="299">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="3" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="45" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="45" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="45" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="46" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="29" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="29" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="45" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="46" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="45" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="45" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="47" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="47" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="57" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="5" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="57" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="61" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="61" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="57" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="62" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="63" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="63" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="67" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="19" fillId="0" borderId="67" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="5" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="67" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="19" fillId="0" borderId="63" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="8" fillId="0" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="71" xfId="7" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="71" xfId="7" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="71" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="71" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="71" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="7" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="7" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="7" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="7" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="72" xfId="7" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="7" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="73" xfId="7" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="74" xfId="7" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="61" xfId="7" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="75" xfId="7" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="71" xfId="7" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="76" xfId="7" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2504,712 +2958,477 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="3" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="56" fontId="6" fillId="0" borderId="16" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="30" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="31" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="35" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="36" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="37" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="38" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="39" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="27" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="28" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="29" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="32" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="33" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="34" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="31" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="56" fontId="6" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="30" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="31" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="42" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="43" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="44" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="40" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="6" fillId="0" borderId="16" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="27" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="28" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="29" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="30" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="30" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="35" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="30" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="42" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="43" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="44" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="40" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="27" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="6" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="3" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="30" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="67" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="68" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="69" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="70" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="68" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="69" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="70" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="67" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="63" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="68" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="69" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="70" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="58" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="59" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="4" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="45" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="45" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="60" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="45" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="64" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="65" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="66" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="64" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="46" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="66" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="29" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="29" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="45" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="46" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="45" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="45" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="47" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="47" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="57" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="5" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="57" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="61" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="61" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="57" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="62" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="63" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="63" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="67" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="18" fillId="0" borderId="67" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="5" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="67" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="18" fillId="0" borderId="63" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="7" fillId="0" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="71" xfId="7" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="71" xfId="7" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="71" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="71" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="71" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="7" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="7" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="7" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="7" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="72" xfId="7" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="7" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="73" xfId="7" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="74" xfId="7" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="61" xfId="7" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="75" xfId="7" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="71" xfId="7" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="76" xfId="7" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="3" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="4" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="5" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="58" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="59" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="60" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="63" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="64" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="65" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="66" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="64" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="66" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="57" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="58" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="59" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="60" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="57" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="58" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3221,89 +3440,153 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="60" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="18" fillId="0" borderId="58" xfId="6" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="58" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="59" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="60" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="19" fillId="0" borderId="58" xfId="6" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="18" fillId="0" borderId="60" xfId="6" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="19" fillId="0" borderId="60" xfId="6" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="18" fillId="0" borderId="58" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="19" fillId="0" borderId="58" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="60" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="60" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="67" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="4" borderId="58" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="4" borderId="59" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="4" borderId="60" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="71" xfId="7" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="22" fillId="0" borderId="71" xfId="7" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="71" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="58" xfId="7" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="59" xfId="7" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="60" xfId="7" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="21" fillId="0" borderId="58" xfId="7" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="77" xfId="8" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="78" xfId="8" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="79" xfId="8" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="80" xfId="8" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="81" xfId="8" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="80" xfId="8" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="79" xfId="8" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="81" xfId="8" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="80" xfId="8" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="77" xfId="8" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="82" xfId="8" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="83" xfId="8" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="84" xfId="8" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="82" xfId="8" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="85" xfId="8" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="86" xfId="8" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="87" xfId="8" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="77" xfId="8" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="68" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="69" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="70" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="67" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="68" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="69" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="70" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="68" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="84" xfId="8" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="69" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="78" xfId="8" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="70" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="85" xfId="8" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="4" borderId="58" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="4" borderId="59" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="4" borderId="60" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="71" xfId="7" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="21" fillId="0" borderId="71" xfId="7" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="71" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="58" xfId="7" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="59" xfId="7" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="60" xfId="7" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="58" xfId="7" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="87" xfId="8" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="86" xfId="8" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="84" xfId="8" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="83" xfId="8" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="87" xfId="8" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="86" xfId="8" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="78" xfId="8" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="8">
+  <cellStyles count="9">
     <cellStyle name="ハイパーリンク" xfId="1" builtinId="8"/>
     <cellStyle name="標準" xfId="0" builtinId="0"/>
     <cellStyle name="標準 2" xfId="2" xr:uid="{34200FF7-2CB0-43CE-9E54-7B88C1A054C5}"/>
     <cellStyle name="標準 2 2" xfId="3" xr:uid="{27F598B5-3CA0-4DB2-BB0A-B46AD58157ED}"/>
     <cellStyle name="標準 2 3" xfId="7" xr:uid="{4ECCCC5E-944E-4450-86C5-CF50D6385316}"/>
     <cellStyle name="標準 3" xfId="4" xr:uid="{64517715-78F6-483F-A73E-3584FBD47293}"/>
+    <cellStyle name="標準 3 2" xfId="8" xr:uid="{DA101DE2-9DC6-45D1-B7AA-3D3E6C34B6C3}"/>
     <cellStyle name="標準_生産計画ED書" xfId="5" xr:uid="{DAF71B83-AD85-4492-B576-533DAD2D280C}"/>
     <cellStyle name="標準_東京理科大DBレイアウト" xfId="6" xr:uid="{691F0CCF-F00E-45EC-8616-60155DDBDDF4}"/>
   </cellStyles>
@@ -4340,6 +4623,60 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="ユースケース記述"/>
+      <sheetName val="画面設計書"/>
+      <sheetName val="画面遷移図"/>
+      <sheetName val="テスト仕様書兼結果報告書"/>
+      <sheetName val="エビデンス"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="3" refreshError="1"/>
+      <sheetData sheetId="4" refreshError="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="ユースケース記述"/>
+      <sheetName val="画面設計書"/>
+      <sheetName val="画面遷移図"/>
+      <sheetName val="詳細クラス図"/>
+      <sheetName val="テスト仕様書兼結果報告書"/>
+      <sheetName val="JUnitテスト仕様書兼報告書"/>
+      <sheetName val="カバレッジレポート"/>
+      <sheetName val="エビデンス"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="3" refreshError="1"/>
+      <sheetData sheetId="4" refreshError="1"/>
+      <sheetData sheetId="5" refreshError="1"/>
+      <sheetData sheetId="6" refreshError="1"/>
+      <sheetData sheetId="7" refreshError="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
@@ -5700,7 +6037,7 @@
     <mergeCell ref="I14:K14"/>
     <mergeCell ref="G15:H15"/>
   </mergeCells>
-  <phoneticPr fontId="8"/>
+  <phoneticPr fontId="9"/>
   <pageMargins left="0.70833333333333304" right="0.70833333333333304" top="0.74791666666666701" bottom="0.74791666666666701" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="landscape"/>
 </worksheet>
@@ -10236,7 +10573,7 @@
     <mergeCell ref="A6:F6"/>
     <mergeCell ref="G6:S6"/>
   </mergeCells>
-  <phoneticPr fontId="8"/>
+  <phoneticPr fontId="9"/>
   <dataValidations count="2">
     <dataValidation imeMode="off" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AO1:AS1" xr:uid="{E529940F-725C-40CB-9DD6-F6B69C91FE0E}"/>
     <dataValidation imeMode="on" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A10:AK102 N1:O1 I1:L1 A113:AK115 G5:G6 V1 AC1 AE1 A104:AK111" xr:uid="{A9A22422-DCD7-4FA2-90B4-A4918EEEF3F3}"/>
@@ -10246,6 +10583,436 @@
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
   <headerFooter alignWithMargins="0"/>
   <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86A9C52F-7DFE-42C7-9C25-FC28C996F829}">
+  <dimension ref="A1:O42"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="16384" width="9.140625" style="280"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:15" ht="15.75" thickBot="1">
+      <c r="A1" s="270" t="s">
+        <v>169</v>
+      </c>
+      <c r="B1" s="271"/>
+      <c r="C1" s="272"/>
+      <c r="D1" s="273" t="s">
+        <v>170</v>
+      </c>
+      <c r="E1" s="274"/>
+      <c r="F1" s="272"/>
+      <c r="G1" s="275" t="s">
+        <v>171</v>
+      </c>
+      <c r="H1" s="274"/>
+      <c r="I1" s="276" t="s">
+        <v>172</v>
+      </c>
+      <c r="J1" s="277"/>
+      <c r="K1" s="276" t="s">
+        <v>173</v>
+      </c>
+      <c r="L1" s="277"/>
+      <c r="M1" s="276" t="s">
+        <v>174</v>
+      </c>
+      <c r="N1" s="278"/>
+      <c r="O1" s="279"/>
+    </row>
+    <row r="2" spans="1:15">
+      <c r="A2" s="281"/>
+      <c r="B2" s="282"/>
+      <c r="C2" s="270"/>
+      <c r="D2" s="283"/>
+      <c r="E2" s="271"/>
+      <c r="F2" s="270"/>
+      <c r="G2" s="283"/>
+      <c r="H2" s="271"/>
+      <c r="I2" s="270"/>
+      <c r="J2" s="271"/>
+      <c r="K2" s="270"/>
+      <c r="L2" s="271"/>
+      <c r="M2" s="270"/>
+      <c r="N2" s="271"/>
+      <c r="O2" s="284"/>
+    </row>
+    <row r="3" spans="1:15" ht="15.75" thickBot="1">
+      <c r="A3" s="285"/>
+      <c r="B3" s="286"/>
+      <c r="C3" s="285"/>
+      <c r="D3" s="287"/>
+      <c r="E3" s="286"/>
+      <c r="F3" s="285"/>
+      <c r="G3" s="287"/>
+      <c r="H3" s="286"/>
+      <c r="I3" s="285"/>
+      <c r="J3" s="286"/>
+      <c r="K3" s="285"/>
+      <c r="L3" s="286"/>
+      <c r="M3" s="285"/>
+      <c r="N3" s="286"/>
+      <c r="O3" s="284"/>
+    </row>
+    <row r="4" spans="1:15">
+      <c r="A4" s="270" t="s">
+        <v>175</v>
+      </c>
+      <c r="B4" s="271"/>
+      <c r="C4" s="288"/>
+      <c r="D4" s="289"/>
+      <c r="E4" s="289"/>
+      <c r="F4" s="289"/>
+      <c r="G4" s="289"/>
+      <c r="H4" s="289"/>
+      <c r="I4" s="289"/>
+      <c r="J4" s="289"/>
+      <c r="K4" s="289"/>
+      <c r="L4" s="289"/>
+      <c r="M4" s="289"/>
+      <c r="N4" s="290"/>
+      <c r="O4" s="284"/>
+    </row>
+    <row r="5" spans="1:15" ht="15.75" thickBot="1">
+      <c r="A5" s="285"/>
+      <c r="B5" s="286"/>
+      <c r="C5" s="291"/>
+      <c r="D5" s="292"/>
+      <c r="E5" s="292"/>
+      <c r="F5" s="292"/>
+      <c r="G5" s="292"/>
+      <c r="H5" s="292"/>
+      <c r="I5" s="292"/>
+      <c r="J5" s="292"/>
+      <c r="K5" s="292"/>
+      <c r="L5" s="292"/>
+      <c r="M5" s="292"/>
+      <c r="N5" s="293"/>
+      <c r="O5" s="284"/>
+    </row>
+    <row r="6" spans="1:15" ht="15.75" thickBot="1">
+      <c r="A6" s="276" t="s">
+        <v>176</v>
+      </c>
+      <c r="B6" s="277"/>
+      <c r="C6" s="276" t="s">
+        <v>177</v>
+      </c>
+      <c r="D6" s="278"/>
+      <c r="E6" s="278"/>
+      <c r="F6" s="278"/>
+      <c r="G6" s="278"/>
+      <c r="H6" s="278"/>
+      <c r="I6" s="278"/>
+      <c r="J6" s="278"/>
+      <c r="K6" s="278"/>
+      <c r="L6" s="278"/>
+      <c r="M6" s="278"/>
+      <c r="N6" s="277"/>
+      <c r="O6" s="284"/>
+    </row>
+    <row r="7" spans="1:15">
+      <c r="A7" s="270">
+        <v>1</v>
+      </c>
+      <c r="B7" s="271"/>
+      <c r="C7" s="294"/>
+      <c r="D7" s="294"/>
+      <c r="E7" s="294"/>
+      <c r="F7" s="294"/>
+      <c r="G7" s="294"/>
+      <c r="H7" s="294"/>
+      <c r="I7" s="294"/>
+      <c r="J7" s="294"/>
+      <c r="K7" s="294"/>
+      <c r="L7" s="294"/>
+      <c r="M7" s="294"/>
+      <c r="N7" s="294"/>
+      <c r="O7" s="284"/>
+    </row>
+    <row r="8" spans="1:15">
+      <c r="A8" s="281"/>
+      <c r="B8" s="282"/>
+      <c r="O8" s="284"/>
+    </row>
+    <row r="9" spans="1:15">
+      <c r="A9" s="281"/>
+      <c r="B9" s="282"/>
+      <c r="N9" s="295"/>
+    </row>
+    <row r="10" spans="1:15">
+      <c r="A10" s="281"/>
+      <c r="B10" s="282"/>
+      <c r="O10" s="284"/>
+    </row>
+    <row r="11" spans="1:15">
+      <c r="A11" s="281"/>
+      <c r="B11" s="282"/>
+      <c r="O11" s="284"/>
+    </row>
+    <row r="12" spans="1:15">
+      <c r="A12" s="281"/>
+      <c r="B12" s="282"/>
+      <c r="O12" s="284"/>
+    </row>
+    <row r="13" spans="1:15">
+      <c r="A13" s="281"/>
+      <c r="B13" s="282"/>
+      <c r="O13" s="284"/>
+    </row>
+    <row r="14" spans="1:15">
+      <c r="A14" s="281"/>
+      <c r="B14" s="282"/>
+      <c r="O14" s="284"/>
+    </row>
+    <row r="15" spans="1:15" ht="15.75" thickBot="1">
+      <c r="A15" s="285"/>
+      <c r="B15" s="286"/>
+      <c r="C15" s="296"/>
+      <c r="D15" s="296"/>
+      <c r="E15" s="296"/>
+      <c r="F15" s="296"/>
+      <c r="G15" s="296"/>
+      <c r="H15" s="296"/>
+      <c r="I15" s="296"/>
+      <c r="J15" s="296"/>
+      <c r="K15" s="296"/>
+      <c r="L15" s="296"/>
+      <c r="M15" s="296"/>
+      <c r="N15" s="297"/>
+      <c r="O15" s="284"/>
+    </row>
+    <row r="16" spans="1:15">
+      <c r="A16" s="270">
+        <v>2</v>
+      </c>
+      <c r="B16" s="271"/>
+      <c r="C16" s="294"/>
+      <c r="D16" s="294"/>
+      <c r="E16" s="294"/>
+      <c r="F16" s="294"/>
+      <c r="G16" s="294"/>
+      <c r="H16" s="294"/>
+      <c r="I16" s="294"/>
+      <c r="J16" s="294"/>
+      <c r="K16" s="294"/>
+      <c r="L16" s="294"/>
+      <c r="M16" s="294"/>
+      <c r="N16" s="295"/>
+    </row>
+    <row r="17" spans="1:14">
+      <c r="A17" s="281"/>
+      <c r="B17" s="282"/>
+      <c r="N17" s="295"/>
+    </row>
+    <row r="18" spans="1:14">
+      <c r="A18" s="281"/>
+      <c r="B18" s="282"/>
+      <c r="N18" s="295"/>
+    </row>
+    <row r="19" spans="1:14">
+      <c r="A19" s="281"/>
+      <c r="B19" s="282"/>
+      <c r="N19" s="295"/>
+    </row>
+    <row r="20" spans="1:14">
+      <c r="A20" s="281"/>
+      <c r="B20" s="282"/>
+      <c r="N20" s="295"/>
+    </row>
+    <row r="21" spans="1:14">
+      <c r="A21" s="281"/>
+      <c r="B21" s="282"/>
+      <c r="N21" s="295"/>
+    </row>
+    <row r="22" spans="1:14">
+      <c r="A22" s="281"/>
+      <c r="B22" s="282"/>
+      <c r="N22" s="295"/>
+    </row>
+    <row r="23" spans="1:14">
+      <c r="A23" s="281"/>
+      <c r="B23" s="282"/>
+      <c r="N23" s="295"/>
+    </row>
+    <row r="24" spans="1:14" ht="15.75" thickBot="1">
+      <c r="A24" s="285"/>
+      <c r="B24" s="286"/>
+      <c r="C24" s="296"/>
+      <c r="D24" s="296"/>
+      <c r="E24" s="296"/>
+      <c r="F24" s="296"/>
+      <c r="G24" s="296"/>
+      <c r="H24" s="296"/>
+      <c r="I24" s="296"/>
+      <c r="J24" s="296"/>
+      <c r="K24" s="296"/>
+      <c r="L24" s="296"/>
+      <c r="M24" s="296"/>
+      <c r="N24" s="297"/>
+    </row>
+    <row r="25" spans="1:14">
+      <c r="A25" s="270">
+        <v>3</v>
+      </c>
+      <c r="B25" s="271"/>
+      <c r="C25" s="294"/>
+      <c r="D25" s="294"/>
+      <c r="E25" s="294"/>
+      <c r="F25" s="294"/>
+      <c r="G25" s="294"/>
+      <c r="H25" s="294"/>
+      <c r="I25" s="294"/>
+      <c r="J25" s="294"/>
+      <c r="K25" s="294"/>
+      <c r="L25" s="294"/>
+      <c r="M25" s="294"/>
+      <c r="N25" s="295"/>
+    </row>
+    <row r="26" spans="1:14">
+      <c r="A26" s="281"/>
+      <c r="B26" s="282"/>
+      <c r="N26" s="295"/>
+    </row>
+    <row r="27" spans="1:14">
+      <c r="A27" s="281"/>
+      <c r="B27" s="282"/>
+      <c r="N27" s="295"/>
+    </row>
+    <row r="28" spans="1:14">
+      <c r="A28" s="281"/>
+      <c r="B28" s="282"/>
+      <c r="N28" s="295"/>
+    </row>
+    <row r="29" spans="1:14">
+      <c r="A29" s="281"/>
+      <c r="B29" s="282"/>
+      <c r="N29" s="295"/>
+    </row>
+    <row r="30" spans="1:14">
+      <c r="A30" s="281"/>
+      <c r="B30" s="282"/>
+      <c r="N30" s="295"/>
+    </row>
+    <row r="31" spans="1:14">
+      <c r="A31" s="281"/>
+      <c r="B31" s="282"/>
+      <c r="N31" s="295"/>
+    </row>
+    <row r="32" spans="1:14">
+      <c r="A32" s="281"/>
+      <c r="B32" s="282"/>
+      <c r="N32" s="295"/>
+    </row>
+    <row r="33" spans="1:14" ht="15.75" thickBot="1">
+      <c r="A33" s="285"/>
+      <c r="B33" s="286"/>
+      <c r="C33" s="296"/>
+      <c r="D33" s="296"/>
+      <c r="E33" s="296"/>
+      <c r="F33" s="296"/>
+      <c r="G33" s="296"/>
+      <c r="H33" s="296"/>
+      <c r="I33" s="296"/>
+      <c r="J33" s="296"/>
+      <c r="K33" s="296"/>
+      <c r="L33" s="296"/>
+      <c r="N33" s="295"/>
+    </row>
+    <row r="34" spans="1:14">
+      <c r="A34" s="270">
+        <v>4</v>
+      </c>
+      <c r="B34" s="271"/>
+      <c r="C34" s="294"/>
+      <c r="D34" s="294"/>
+      <c r="E34" s="294"/>
+      <c r="F34" s="294"/>
+      <c r="G34" s="294"/>
+      <c r="H34" s="294"/>
+      <c r="I34" s="294"/>
+      <c r="J34" s="294"/>
+      <c r="K34" s="294"/>
+      <c r="L34" s="294"/>
+      <c r="M34" s="294"/>
+      <c r="N34" s="298"/>
+    </row>
+    <row r="35" spans="1:14">
+      <c r="A35" s="281"/>
+      <c r="B35" s="282"/>
+      <c r="N35" s="295"/>
+    </row>
+    <row r="36" spans="1:14">
+      <c r="A36" s="281"/>
+      <c r="B36" s="282"/>
+      <c r="N36" s="295"/>
+    </row>
+    <row r="37" spans="1:14">
+      <c r="A37" s="281"/>
+      <c r="B37" s="282"/>
+      <c r="N37" s="295"/>
+    </row>
+    <row r="38" spans="1:14">
+      <c r="A38" s="281"/>
+      <c r="B38" s="282"/>
+      <c r="N38" s="295"/>
+    </row>
+    <row r="39" spans="1:14">
+      <c r="A39" s="281"/>
+      <c r="B39" s="282"/>
+      <c r="N39" s="295"/>
+    </row>
+    <row r="40" spans="1:14">
+      <c r="A40" s="281"/>
+      <c r="B40" s="282"/>
+      <c r="N40" s="295"/>
+    </row>
+    <row r="41" spans="1:14">
+      <c r="A41" s="281"/>
+      <c r="B41" s="282"/>
+      <c r="N41" s="295"/>
+    </row>
+    <row r="42" spans="1:14" ht="15.75" thickBot="1">
+      <c r="A42" s="285"/>
+      <c r="B42" s="286"/>
+      <c r="C42" s="296"/>
+      <c r="D42" s="296"/>
+      <c r="E42" s="296"/>
+      <c r="F42" s="296"/>
+      <c r="G42" s="296"/>
+      <c r="H42" s="296"/>
+      <c r="I42" s="296"/>
+      <c r="J42" s="296"/>
+      <c r="K42" s="296"/>
+      <c r="L42" s="296"/>
+      <c r="M42" s="296"/>
+      <c r="N42" s="297"/>
+    </row>
+  </sheetData>
+  <mergeCells count="17">
+    <mergeCell ref="A25:B33"/>
+    <mergeCell ref="A34:B42"/>
+    <mergeCell ref="A4:B5"/>
+    <mergeCell ref="C4:N5"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="C6:N6"/>
+    <mergeCell ref="A7:B15"/>
+    <mergeCell ref="A16:B24"/>
+    <mergeCell ref="A1:B3"/>
+    <mergeCell ref="I1:J1"/>
+    <mergeCell ref="K1:L1"/>
+    <mergeCell ref="M1:N1"/>
+    <mergeCell ref="C2:E3"/>
+    <mergeCell ref="F2:H3"/>
+    <mergeCell ref="I2:J3"/>
+    <mergeCell ref="K2:L3"/>
+    <mergeCell ref="M2:N3"/>
+  </mergeCells>
+  <phoneticPr fontId="9"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -10261,19 +11028,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="121" t="s">
+      <c r="A1" s="92" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="122"/>
-      <c r="C1" s="123"/>
-      <c r="D1" s="130" t="s">
+      <c r="B1" s="93"/>
+      <c r="C1" s="94"/>
+      <c r="D1" s="101" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="115"/>
-      <c r="F1" s="130" t="s">
+      <c r="E1" s="102"/>
+      <c r="F1" s="101" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="115"/>
+      <c r="G1" s="102"/>
       <c r="H1" s="34" t="s">
         <v>6</v>
       </c>
@@ -10285,192 +11052,192 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="124"/>
-      <c r="B2" s="125"/>
-      <c r="C2" s="126"/>
-      <c r="D2" s="131" t="s">
+      <c r="A2" s="95"/>
+      <c r="B2" s="96"/>
+      <c r="C2" s="97"/>
+      <c r="D2" s="103" t="s">
         <v>61</v>
       </c>
-      <c r="E2" s="132"/>
-      <c r="F2" s="131">
+      <c r="E2" s="104"/>
+      <c r="F2" s="103">
         <v>56</v>
       </c>
-      <c r="G2" s="132"/>
-      <c r="H2" s="100">
+      <c r="G2" s="104"/>
+      <c r="H2" s="107">
         <v>45806</v>
       </c>
-      <c r="I2" s="109" t="s">
+      <c r="I2" s="121" t="s">
         <v>60</v>
       </c>
-      <c r="J2" s="110"/>
+      <c r="J2" s="122"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="124"/>
-      <c r="B3" s="125"/>
-      <c r="C3" s="126"/>
-      <c r="D3" s="133"/>
-      <c r="E3" s="126"/>
-      <c r="F3" s="133"/>
-      <c r="G3" s="126"/>
-      <c r="H3" s="101"/>
-      <c r="I3" s="101"/>
-      <c r="J3" s="111"/>
+      <c r="A3" s="95"/>
+      <c r="B3" s="96"/>
+      <c r="C3" s="97"/>
+      <c r="D3" s="105"/>
+      <c r="E3" s="97"/>
+      <c r="F3" s="105"/>
+      <c r="G3" s="97"/>
+      <c r="H3" s="108"/>
+      <c r="I3" s="108"/>
+      <c r="J3" s="123"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="127"/>
-      <c r="B4" s="128"/>
-      <c r="C4" s="129"/>
-      <c r="D4" s="134"/>
-      <c r="E4" s="129"/>
-      <c r="F4" s="134"/>
-      <c r="G4" s="129"/>
-      <c r="H4" s="102"/>
-      <c r="I4" s="102"/>
-      <c r="J4" s="112"/>
+      <c r="A4" s="98"/>
+      <c r="B4" s="99"/>
+      <c r="C4" s="100"/>
+      <c r="D4" s="106"/>
+      <c r="E4" s="100"/>
+      <c r="F4" s="106"/>
+      <c r="G4" s="100"/>
+      <c r="H4" s="109"/>
+      <c r="I4" s="109"/>
+      <c r="J4" s="124"/>
     </row>
     <row r="5" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A5" s="113" t="s">
+      <c r="A5" s="125" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="114"/>
-      <c r="C5" s="115"/>
-      <c r="D5" s="116" t="s">
+      <c r="B5" s="126"/>
+      <c r="C5" s="102"/>
+      <c r="D5" s="127" t="s">
         <v>59</v>
       </c>
-      <c r="E5" s="114"/>
-      <c r="F5" s="114"/>
-      <c r="G5" s="114"/>
-      <c r="H5" s="114"/>
-      <c r="I5" s="114"/>
-      <c r="J5" s="117"/>
+      <c r="E5" s="126"/>
+      <c r="F5" s="126"/>
+      <c r="G5" s="126"/>
+      <c r="H5" s="126"/>
+      <c r="I5" s="126"/>
+      <c r="J5" s="128"/>
     </row>
     <row r="6" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A6" s="103" t="s">
+      <c r="A6" s="110" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="98"/>
-      <c r="C6" s="93"/>
-      <c r="D6" s="97" t="s">
+      <c r="B6" s="111"/>
+      <c r="C6" s="112"/>
+      <c r="D6" s="120" t="s">
         <v>58</v>
       </c>
-      <c r="E6" s="98"/>
-      <c r="F6" s="98"/>
-      <c r="G6" s="98"/>
-      <c r="H6" s="98"/>
-      <c r="I6" s="98"/>
-      <c r="J6" s="99"/>
+      <c r="E6" s="111"/>
+      <c r="F6" s="111"/>
+      <c r="G6" s="111"/>
+      <c r="H6" s="111"/>
+      <c r="I6" s="111"/>
+      <c r="J6" s="114"/>
     </row>
     <row r="7" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A7" s="103" t="s">
+      <c r="A7" s="110" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="98"/>
-      <c r="C7" s="93"/>
-      <c r="D7" s="97" t="s">
+      <c r="B7" s="111"/>
+      <c r="C7" s="112"/>
+      <c r="D7" s="120" t="s">
         <v>57</v>
       </c>
-      <c r="E7" s="98"/>
-      <c r="F7" s="98"/>
-      <c r="G7" s="98"/>
-      <c r="H7" s="98"/>
-      <c r="I7" s="98"/>
-      <c r="J7" s="99"/>
+      <c r="E7" s="111"/>
+      <c r="F7" s="111"/>
+      <c r="G7" s="111"/>
+      <c r="H7" s="111"/>
+      <c r="I7" s="111"/>
+      <c r="J7" s="114"/>
     </row>
     <row r="8" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A8" s="103" t="s">
+      <c r="A8" s="110" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="98"/>
-      <c r="C8" s="93"/>
-      <c r="D8" s="94" t="s">
+      <c r="B8" s="111"/>
+      <c r="C8" s="112"/>
+      <c r="D8" s="113" t="s">
         <v>107</v>
       </c>
-      <c r="E8" s="98"/>
-      <c r="F8" s="98"/>
-      <c r="G8" s="98"/>
-      <c r="H8" s="98"/>
-      <c r="I8" s="98"/>
-      <c r="J8" s="99"/>
+      <c r="E8" s="111"/>
+      <c r="F8" s="111"/>
+      <c r="G8" s="111"/>
+      <c r="H8" s="111"/>
+      <c r="I8" s="111"/>
+      <c r="J8" s="114"/>
     </row>
     <row r="9" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A9" s="118" t="s">
+      <c r="A9" s="129" t="s">
         <v>13</v>
       </c>
-      <c r="B9" s="92" t="s">
+      <c r="B9" s="132" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="93"/>
-      <c r="D9" s="94" t="s">
+      <c r="C9" s="112"/>
+      <c r="D9" s="113" t="s">
         <v>105</v>
       </c>
-      <c r="E9" s="95"/>
-      <c r="F9" s="95"/>
-      <c r="G9" s="95"/>
-      <c r="H9" s="95"/>
-      <c r="I9" s="95"/>
-      <c r="J9" s="96"/>
+      <c r="E9" s="133"/>
+      <c r="F9" s="133"/>
+      <c r="G9" s="133"/>
+      <c r="H9" s="133"/>
+      <c r="I9" s="133"/>
+      <c r="J9" s="134"/>
     </row>
     <row r="10" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A10" s="119"/>
-      <c r="B10" s="92" t="s">
+      <c r="A10" s="130"/>
+      <c r="B10" s="132" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="93"/>
-      <c r="D10" s="97" t="s">
+      <c r="C10" s="112"/>
+      <c r="D10" s="120" t="s">
         <v>93</v>
       </c>
-      <c r="E10" s="98"/>
-      <c r="F10" s="98"/>
-      <c r="G10" s="98"/>
-      <c r="H10" s="98"/>
-      <c r="I10" s="98"/>
-      <c r="J10" s="99"/>
+      <c r="E10" s="111"/>
+      <c r="F10" s="111"/>
+      <c r="G10" s="111"/>
+      <c r="H10" s="111"/>
+      <c r="I10" s="111"/>
+      <c r="J10" s="114"/>
     </row>
     <row r="11" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A11" s="120"/>
-      <c r="B11" s="92" t="s">
+      <c r="A11" s="131"/>
+      <c r="B11" s="132" t="s">
         <v>16</v>
       </c>
-      <c r="C11" s="93"/>
-      <c r="D11" s="94" t="s">
+      <c r="C11" s="112"/>
+      <c r="D11" s="113" t="s">
         <v>108</v>
       </c>
-      <c r="E11" s="98"/>
-      <c r="F11" s="98"/>
-      <c r="G11" s="98"/>
-      <c r="H11" s="98"/>
-      <c r="I11" s="98"/>
-      <c r="J11" s="99"/>
+      <c r="E11" s="111"/>
+      <c r="F11" s="111"/>
+      <c r="G11" s="111"/>
+      <c r="H11" s="111"/>
+      <c r="I11" s="111"/>
+      <c r="J11" s="114"/>
     </row>
     <row r="12" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A12" s="103" t="s">
+      <c r="A12" s="110" t="s">
         <v>17</v>
       </c>
-      <c r="B12" s="98"/>
-      <c r="C12" s="93"/>
-      <c r="D12" s="94" t="s">
+      <c r="B12" s="111"/>
+      <c r="C12" s="112"/>
+      <c r="D12" s="113" t="s">
         <v>106</v>
       </c>
-      <c r="E12" s="98"/>
-      <c r="F12" s="98"/>
-      <c r="G12" s="98"/>
-      <c r="H12" s="98"/>
-      <c r="I12" s="98"/>
-      <c r="J12" s="99"/>
+      <c r="E12" s="111"/>
+      <c r="F12" s="111"/>
+      <c r="G12" s="111"/>
+      <c r="H12" s="111"/>
+      <c r="I12" s="111"/>
+      <c r="J12" s="114"/>
     </row>
     <row r="13" spans="1:10" ht="26.25" customHeight="1" thickBot="1">
-      <c r="A13" s="104" t="s">
+      <c r="A13" s="115" t="s">
         <v>18</v>
       </c>
-      <c r="B13" s="105"/>
-      <c r="C13" s="106"/>
-      <c r="D13" s="107"/>
-      <c r="E13" s="105"/>
-      <c r="F13" s="105"/>
-      <c r="G13" s="105"/>
-      <c r="H13" s="105"/>
-      <c r="I13" s="105"/>
-      <c r="J13" s="108"/>
+      <c r="B13" s="116"/>
+      <c r="C13" s="117"/>
+      <c r="D13" s="118"/>
+      <c r="E13" s="116"/>
+      <c r="F13" s="116"/>
+      <c r="G13" s="116"/>
+      <c r="H13" s="116"/>
+      <c r="I13" s="116"/>
+      <c r="J13" s="119"/>
     </row>
     <row r="14" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="15" spans="1:10" ht="12.75" customHeight="1"/>
@@ -11461,11 +12228,12 @@
     <row r="1000" s="32" customFormat="1" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="A1:C4"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="D2:E4"/>
-    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="D9:J9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="D10:J10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="D11:J11"/>
     <mergeCell ref="H2:H4"/>
     <mergeCell ref="A12:C12"/>
     <mergeCell ref="D12:J12"/>
@@ -11482,14 +12250,13 @@
     <mergeCell ref="A6:C6"/>
     <mergeCell ref="D6:J6"/>
     <mergeCell ref="A9:A11"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="D9:J9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="D10:J10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="D11:J11"/>
+    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="F2:G4"/>
   </mergeCells>
-  <phoneticPr fontId="8"/>
+  <phoneticPr fontId="9"/>
   <pageMargins left="0.70833333333333304" right="0.70833333333333304" top="0.74791666666666701" bottom="0.74791666666666701" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="landscape"/>
 </worksheet>
@@ -12910,7 +13677,7 @@
     <mergeCell ref="D2:E4"/>
     <mergeCell ref="F2:G4"/>
   </mergeCells>
-  <phoneticPr fontId="8"/>
+  <phoneticPr fontId="9"/>
   <pageMargins left="0.70833333333333304" right="0.70833333333333304" top="0.74791666666666701" bottom="0.74791666666666701" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="landscape"/>
   <drawing r:id="rId1"/>
@@ -14323,7 +15090,7 @@
     <mergeCell ref="D2:E4"/>
     <mergeCell ref="F2:G4"/>
   </mergeCells>
-  <phoneticPr fontId="8"/>
+  <phoneticPr fontId="9"/>
   <pageMargins left="0.70833333333333304" right="0.70833333333333304" top="0.74791666666666701" bottom="0.74791666666666701" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="landscape"/>
   <drawing r:id="rId1"/>
@@ -14345,19 +15112,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="169" t="s">
+      <c r="A1" s="167" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="170"/>
-      <c r="C1" s="171"/>
-      <c r="D1" s="173" t="s">
+      <c r="B1" s="168"/>
+      <c r="C1" s="169"/>
+      <c r="D1" s="171" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="174"/>
-      <c r="F1" s="173" t="s">
+      <c r="E1" s="172"/>
+      <c r="F1" s="171" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="174"/>
+      <c r="G1" s="172"/>
       <c r="H1" s="43" t="s">
         <v>6</v>
       </c>
@@ -14369,67 +15136,67 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="166"/>
-      <c r="B2" s="167"/>
-      <c r="C2" s="172"/>
-      <c r="D2" s="175" t="s">
+      <c r="A2" s="164"/>
+      <c r="B2" s="165"/>
+      <c r="C2" s="170"/>
+      <c r="D2" s="173" t="s">
         <v>84</v>
       </c>
-      <c r="E2" s="176"/>
-      <c r="F2" s="175">
+      <c r="E2" s="174"/>
+      <c r="F2" s="173">
         <v>56</v>
       </c>
-      <c r="G2" s="176"/>
-      <c r="H2" s="178">
+      <c r="G2" s="174"/>
+      <c r="H2" s="176">
         <v>45806</v>
       </c>
-      <c r="I2" s="180" t="s">
+      <c r="I2" s="178" t="s">
         <v>83</v>
       </c>
-      <c r="J2" s="181"/>
+      <c r="J2" s="179"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="166"/>
-      <c r="B3" s="167"/>
-      <c r="C3" s="172"/>
-      <c r="D3" s="177"/>
-      <c r="E3" s="172"/>
-      <c r="F3" s="177"/>
-      <c r="G3" s="172"/>
-      <c r="H3" s="179"/>
-      <c r="I3" s="179"/>
-      <c r="J3" s="182"/>
+      <c r="A3" s="164"/>
+      <c r="B3" s="165"/>
+      <c r="C3" s="170"/>
+      <c r="D3" s="175"/>
+      <c r="E3" s="170"/>
+      <c r="F3" s="175"/>
+      <c r="G3" s="170"/>
+      <c r="H3" s="177"/>
+      <c r="I3" s="177"/>
+      <c r="J3" s="180"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="166"/>
-      <c r="B4" s="167"/>
-      <c r="C4" s="172"/>
-      <c r="D4" s="177"/>
-      <c r="E4" s="172"/>
-      <c r="F4" s="177"/>
-      <c r="G4" s="172"/>
-      <c r="H4" s="179"/>
-      <c r="I4" s="179"/>
-      <c r="J4" s="182"/>
+      <c r="A4" s="164"/>
+      <c r="B4" s="165"/>
+      <c r="C4" s="170"/>
+      <c r="D4" s="175"/>
+      <c r="E4" s="170"/>
+      <c r="F4" s="175"/>
+      <c r="G4" s="170"/>
+      <c r="H4" s="177"/>
+      <c r="I4" s="177"/>
+      <c r="J4" s="180"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="183" t="s">
+      <c r="A5" s="181" t="s">
         <v>22</v>
       </c>
-      <c r="B5" s="184"/>
-      <c r="C5" s="174"/>
-      <c r="D5" s="185" t="s">
+      <c r="B5" s="182"/>
+      <c r="C5" s="172"/>
+      <c r="D5" s="183" t="s">
         <v>92</v>
       </c>
-      <c r="E5" s="184"/>
-      <c r="F5" s="184"/>
-      <c r="G5" s="184"/>
-      <c r="H5" s="184"/>
-      <c r="I5" s="184"/>
-      <c r="J5" s="186"/>
+      <c r="E5" s="182"/>
+      <c r="F5" s="182"/>
+      <c r="G5" s="182"/>
+      <c r="H5" s="182"/>
+      <c r="I5" s="182"/>
+      <c r="J5" s="184"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="162" t="s">
+      <c r="A6" s="185" t="s">
         <v>23</v>
       </c>
       <c r="B6" s="157"/>
@@ -14443,91 +15210,91 @@
       <c r="J6" s="160"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="163"/>
-      <c r="B7" s="164"/>
-      <c r="C7" s="164"/>
-      <c r="D7" s="164"/>
-      <c r="E7" s="164"/>
-      <c r="F7" s="164"/>
-      <c r="G7" s="164"/>
-      <c r="H7" s="164"/>
-      <c r="I7" s="164"/>
-      <c r="J7" s="165"/>
+      <c r="A7" s="161"/>
+      <c r="B7" s="162"/>
+      <c r="C7" s="162"/>
+      <c r="D7" s="162"/>
+      <c r="E7" s="162"/>
+      <c r="F7" s="162"/>
+      <c r="G7" s="162"/>
+      <c r="H7" s="162"/>
+      <c r="I7" s="162"/>
+      <c r="J7" s="163"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="166"/>
-      <c r="B8" s="167"/>
-      <c r="C8" s="167"/>
-      <c r="D8" s="167"/>
-      <c r="E8" s="167"/>
-      <c r="F8" s="167"/>
-      <c r="G8" s="167"/>
-      <c r="H8" s="167"/>
-      <c r="I8" s="167"/>
-      <c r="J8" s="168"/>
+      <c r="A8" s="164"/>
+      <c r="B8" s="165"/>
+      <c r="C8" s="165"/>
+      <c r="D8" s="165"/>
+      <c r="E8" s="165"/>
+      <c r="F8" s="165"/>
+      <c r="G8" s="165"/>
+      <c r="H8" s="165"/>
+      <c r="I8" s="165"/>
+      <c r="J8" s="166"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="166"/>
-      <c r="B9" s="167"/>
-      <c r="C9" s="167"/>
-      <c r="D9" s="167"/>
-      <c r="E9" s="167"/>
-      <c r="F9" s="167"/>
-      <c r="G9" s="167"/>
-      <c r="H9" s="167"/>
-      <c r="I9" s="167"/>
-      <c r="J9" s="168"/>
+      <c r="A9" s="164"/>
+      <c r="B9" s="165"/>
+      <c r="C9" s="165"/>
+      <c r="D9" s="165"/>
+      <c r="E9" s="165"/>
+      <c r="F9" s="165"/>
+      <c r="G9" s="165"/>
+      <c r="H9" s="165"/>
+      <c r="I9" s="165"/>
+      <c r="J9" s="166"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="166"/>
-      <c r="B10" s="167"/>
-      <c r="C10" s="167"/>
-      <c r="D10" s="167"/>
-      <c r="E10" s="167"/>
-      <c r="F10" s="167"/>
-      <c r="G10" s="167"/>
-      <c r="H10" s="167"/>
-      <c r="I10" s="167"/>
-      <c r="J10" s="168"/>
+      <c r="A10" s="164"/>
+      <c r="B10" s="165"/>
+      <c r="C10" s="165"/>
+      <c r="D10" s="165"/>
+      <c r="E10" s="165"/>
+      <c r="F10" s="165"/>
+      <c r="G10" s="165"/>
+      <c r="H10" s="165"/>
+      <c r="I10" s="165"/>
+      <c r="J10" s="166"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="166"/>
-      <c r="B11" s="167"/>
-      <c r="C11" s="167"/>
-      <c r="D11" s="167"/>
-      <c r="E11" s="167"/>
-      <c r="F11" s="167"/>
-      <c r="G11" s="167"/>
-      <c r="H11" s="167"/>
-      <c r="I11" s="167"/>
-      <c r="J11" s="168"/>
+      <c r="A11" s="164"/>
+      <c r="B11" s="165"/>
+      <c r="C11" s="165"/>
+      <c r="D11" s="165"/>
+      <c r="E11" s="165"/>
+      <c r="F11" s="165"/>
+      <c r="G11" s="165"/>
+      <c r="H11" s="165"/>
+      <c r="I11" s="165"/>
+      <c r="J11" s="166"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="166"/>
-      <c r="B12" s="167"/>
-      <c r="C12" s="167"/>
-      <c r="D12" s="167"/>
-      <c r="E12" s="167"/>
-      <c r="F12" s="167"/>
-      <c r="G12" s="167"/>
-      <c r="H12" s="167"/>
-      <c r="I12" s="167"/>
-      <c r="J12" s="168"/>
+      <c r="A12" s="164"/>
+      <c r="B12" s="165"/>
+      <c r="C12" s="165"/>
+      <c r="D12" s="165"/>
+      <c r="E12" s="165"/>
+      <c r="F12" s="165"/>
+      <c r="G12" s="165"/>
+      <c r="H12" s="165"/>
+      <c r="I12" s="165"/>
+      <c r="J12" s="166"/>
     </row>
     <row r="13" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A13" s="166"/>
-      <c r="B13" s="167"/>
-      <c r="C13" s="167"/>
-      <c r="D13" s="167"/>
-      <c r="E13" s="167"/>
-      <c r="F13" s="167"/>
-      <c r="G13" s="167"/>
-      <c r="H13" s="167"/>
-      <c r="I13" s="167"/>
-      <c r="J13" s="168"/>
+      <c r="A13" s="164"/>
+      <c r="B13" s="165"/>
+      <c r="C13" s="165"/>
+      <c r="D13" s="165"/>
+      <c r="E13" s="165"/>
+      <c r="F13" s="165"/>
+      <c r="G13" s="165"/>
+      <c r="H13" s="165"/>
+      <c r="I13" s="165"/>
+      <c r="J13" s="166"/>
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A14" s="162" t="s">
+      <c r="A14" s="185" t="s">
         <v>24</v>
       </c>
       <c r="B14" s="157"/>
@@ -14541,7 +15308,7 @@
       <c r="J14" s="160"/>
     </row>
     <row r="15" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A15" s="162" t="s">
+      <c r="A15" s="185" t="s">
         <v>25</v>
       </c>
       <c r="B15" s="157"/>
@@ -14561,7 +15328,7 @@
       </c>
     </row>
     <row r="16" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A16" s="162" t="s">
+      <c r="A16" s="185" t="s">
         <v>27</v>
       </c>
       <c r="B16" s="157"/>
@@ -14578,7 +15345,7 @@
       <c r="G16" s="39" t="s">
         <v>31</v>
       </c>
-      <c r="H16" s="161" t="s">
+      <c r="H16" s="186" t="s">
         <v>18</v>
       </c>
       <c r="I16" s="157"/>
@@ -15750,6 +16517,23 @@
     <row r="1000" s="36" customFormat="1" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="33">
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="H19:J19"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="H23:J23"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="H20:J20"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="H21:J21"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="H16:J16"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="H18:J18"/>
+    <mergeCell ref="A15:C15"/>
+    <mergeCell ref="D15:H15"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="H17:J17"/>
     <mergeCell ref="A24:C24"/>
     <mergeCell ref="H24:J24"/>
     <mergeCell ref="A7:J13"/>
@@ -15766,25 +16550,8 @@
     <mergeCell ref="A6:J6"/>
     <mergeCell ref="A14:J14"/>
     <mergeCell ref="A16:C16"/>
-    <mergeCell ref="H16:J16"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="A15:C15"/>
-    <mergeCell ref="D15:H15"/>
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="H17:J17"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="H19:J19"/>
-    <mergeCell ref="A23:C23"/>
-    <mergeCell ref="H23:J23"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="H20:J20"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="H21:J21"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="H22:J22"/>
   </mergeCells>
-  <phoneticPr fontId="8"/>
+  <phoneticPr fontId="9"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="landscape"/>
   <drawing r:id="rId1"/>
@@ -15806,19 +16573,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="192" t="s">
+      <c r="A1" s="195" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="122"/>
-      <c r="C1" s="123"/>
-      <c r="D1" s="130" t="s">
+      <c r="B1" s="93"/>
+      <c r="C1" s="94"/>
+      <c r="D1" s="101" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="115"/>
-      <c r="F1" s="130" t="s">
+      <c r="E1" s="102"/>
+      <c r="F1" s="101" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="115"/>
+      <c r="G1" s="102"/>
       <c r="H1" s="35" t="s">
         <v>6</v>
       </c>
@@ -15830,190 +16597,190 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="124"/>
-      <c r="B2" s="125"/>
-      <c r="C2" s="126"/>
-      <c r="D2" s="131" t="s">
+      <c r="A2" s="95"/>
+      <c r="B2" s="96"/>
+      <c r="C2" s="97"/>
+      <c r="D2" s="103" t="s">
         <v>85</v>
       </c>
-      <c r="E2" s="132"/>
-      <c r="F2" s="131">
+      <c r="E2" s="104"/>
+      <c r="F2" s="103">
         <v>56</v>
       </c>
-      <c r="G2" s="132"/>
-      <c r="H2" s="100">
+      <c r="G2" s="104"/>
+      <c r="H2" s="107">
         <v>45805</v>
       </c>
-      <c r="I2" s="109" t="s">
+      <c r="I2" s="121" t="s">
         <v>83</v>
       </c>
-      <c r="J2" s="110"/>
+      <c r="J2" s="122"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="124"/>
-      <c r="B3" s="125"/>
-      <c r="C3" s="126"/>
-      <c r="D3" s="133"/>
-      <c r="E3" s="126"/>
-      <c r="F3" s="133"/>
-      <c r="G3" s="126"/>
-      <c r="H3" s="101"/>
-      <c r="I3" s="101"/>
-      <c r="J3" s="111"/>
+      <c r="A3" s="95"/>
+      <c r="B3" s="96"/>
+      <c r="C3" s="97"/>
+      <c r="D3" s="105"/>
+      <c r="E3" s="97"/>
+      <c r="F3" s="105"/>
+      <c r="G3" s="97"/>
+      <c r="H3" s="108"/>
+      <c r="I3" s="108"/>
+      <c r="J3" s="123"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="124"/>
-      <c r="B4" s="125"/>
-      <c r="C4" s="126"/>
-      <c r="D4" s="133"/>
-      <c r="E4" s="126"/>
-      <c r="F4" s="133"/>
-      <c r="G4" s="126"/>
-      <c r="H4" s="101"/>
-      <c r="I4" s="101"/>
-      <c r="J4" s="111"/>
+      <c r="A4" s="95"/>
+      <c r="B4" s="96"/>
+      <c r="C4" s="97"/>
+      <c r="D4" s="105"/>
+      <c r="E4" s="97"/>
+      <c r="F4" s="105"/>
+      <c r="G4" s="97"/>
+      <c r="H4" s="108"/>
+      <c r="I4" s="108"/>
+      <c r="J4" s="123"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="193" t="s">
+      <c r="A5" s="196" t="s">
         <v>22</v>
       </c>
-      <c r="B5" s="114"/>
-      <c r="C5" s="115"/>
-      <c r="D5" s="194" t="s">
+      <c r="B5" s="126"/>
+      <c r="C5" s="102"/>
+      <c r="D5" s="197" t="s">
         <v>86</v>
       </c>
-      <c r="E5" s="114"/>
-      <c r="F5" s="114"/>
-      <c r="G5" s="114"/>
-      <c r="H5" s="114"/>
-      <c r="I5" s="114"/>
-      <c r="J5" s="117"/>
+      <c r="E5" s="126"/>
+      <c r="F5" s="126"/>
+      <c r="G5" s="126"/>
+      <c r="H5" s="126"/>
+      <c r="I5" s="126"/>
+      <c r="J5" s="128"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="187" t="s">
+      <c r="A6" s="189" t="s">
         <v>23</v>
       </c>
-      <c r="B6" s="98"/>
-      <c r="C6" s="98"/>
-      <c r="D6" s="98"/>
-      <c r="E6" s="98"/>
-      <c r="F6" s="98"/>
-      <c r="G6" s="98"/>
-      <c r="H6" s="98"/>
-      <c r="I6" s="98"/>
-      <c r="J6" s="99"/>
+      <c r="B6" s="111"/>
+      <c r="C6" s="111"/>
+      <c r="D6" s="111"/>
+      <c r="E6" s="111"/>
+      <c r="F6" s="111"/>
+      <c r="G6" s="111"/>
+      <c r="H6" s="111"/>
+      <c r="I6" s="111"/>
+      <c r="J6" s="114"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="188"/>
-      <c r="B7" s="189"/>
-      <c r="C7" s="189"/>
-      <c r="D7" s="189"/>
-      <c r="E7" s="189"/>
-      <c r="F7" s="189"/>
-      <c r="G7" s="189"/>
-      <c r="H7" s="189"/>
-      <c r="I7" s="189"/>
-      <c r="J7" s="190"/>
+      <c r="A7" s="191"/>
+      <c r="B7" s="192"/>
+      <c r="C7" s="192"/>
+      <c r="D7" s="192"/>
+      <c r="E7" s="192"/>
+      <c r="F7" s="192"/>
+      <c r="G7" s="192"/>
+      <c r="H7" s="192"/>
+      <c r="I7" s="192"/>
+      <c r="J7" s="193"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="124"/>
-      <c r="B8" s="125"/>
-      <c r="C8" s="125"/>
-      <c r="D8" s="125"/>
-      <c r="E8" s="125"/>
-      <c r="F8" s="125"/>
-      <c r="G8" s="125"/>
-      <c r="H8" s="125"/>
-      <c r="I8" s="125"/>
-      <c r="J8" s="191"/>
+      <c r="A8" s="95"/>
+      <c r="B8" s="96"/>
+      <c r="C8" s="96"/>
+      <c r="D8" s="96"/>
+      <c r="E8" s="96"/>
+      <c r="F8" s="96"/>
+      <c r="G8" s="96"/>
+      <c r="H8" s="96"/>
+      <c r="I8" s="96"/>
+      <c r="J8" s="194"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="124"/>
-      <c r="B9" s="125"/>
-      <c r="C9" s="125"/>
-      <c r="D9" s="125"/>
-      <c r="E9" s="125"/>
-      <c r="F9" s="125"/>
-      <c r="G9" s="125"/>
-      <c r="H9" s="125"/>
-      <c r="I9" s="125"/>
-      <c r="J9" s="191"/>
+      <c r="A9" s="95"/>
+      <c r="B9" s="96"/>
+      <c r="C9" s="96"/>
+      <c r="D9" s="96"/>
+      <c r="E9" s="96"/>
+      <c r="F9" s="96"/>
+      <c r="G9" s="96"/>
+      <c r="H9" s="96"/>
+      <c r="I9" s="96"/>
+      <c r="J9" s="194"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="124"/>
-      <c r="B10" s="125"/>
-      <c r="C10" s="125"/>
-      <c r="D10" s="125"/>
-      <c r="E10" s="125"/>
-      <c r="F10" s="125"/>
-      <c r="G10" s="125"/>
-      <c r="H10" s="125"/>
-      <c r="I10" s="125"/>
-      <c r="J10" s="191"/>
+      <c r="A10" s="95"/>
+      <c r="B10" s="96"/>
+      <c r="C10" s="96"/>
+      <c r="D10" s="96"/>
+      <c r="E10" s="96"/>
+      <c r="F10" s="96"/>
+      <c r="G10" s="96"/>
+      <c r="H10" s="96"/>
+      <c r="I10" s="96"/>
+      <c r="J10" s="194"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="124"/>
-      <c r="B11" s="125"/>
-      <c r="C11" s="125"/>
-      <c r="D11" s="125"/>
-      <c r="E11" s="125"/>
-      <c r="F11" s="125"/>
-      <c r="G11" s="125"/>
-      <c r="H11" s="125"/>
-      <c r="I11" s="125"/>
-      <c r="J11" s="191"/>
+      <c r="A11" s="95"/>
+      <c r="B11" s="96"/>
+      <c r="C11" s="96"/>
+      <c r="D11" s="96"/>
+      <c r="E11" s="96"/>
+      <c r="F11" s="96"/>
+      <c r="G11" s="96"/>
+      <c r="H11" s="96"/>
+      <c r="I11" s="96"/>
+      <c r="J11" s="194"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="124"/>
-      <c r="B12" s="125"/>
-      <c r="C12" s="125"/>
-      <c r="D12" s="125"/>
-      <c r="E12" s="125"/>
-      <c r="F12" s="125"/>
-      <c r="G12" s="125"/>
-      <c r="H12" s="125"/>
-      <c r="I12" s="125"/>
-      <c r="J12" s="191"/>
+      <c r="A12" s="95"/>
+      <c r="B12" s="96"/>
+      <c r="C12" s="96"/>
+      <c r="D12" s="96"/>
+      <c r="E12" s="96"/>
+      <c r="F12" s="96"/>
+      <c r="G12" s="96"/>
+      <c r="H12" s="96"/>
+      <c r="I12" s="96"/>
+      <c r="J12" s="194"/>
     </row>
     <row r="13" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A13" s="124"/>
-      <c r="B13" s="125"/>
-      <c r="C13" s="125"/>
-      <c r="D13" s="125"/>
-      <c r="E13" s="125"/>
-      <c r="F13" s="125"/>
-      <c r="G13" s="125"/>
-      <c r="H13" s="125"/>
-      <c r="I13" s="125"/>
-      <c r="J13" s="191"/>
+      <c r="A13" s="95"/>
+      <c r="B13" s="96"/>
+      <c r="C13" s="96"/>
+      <c r="D13" s="96"/>
+      <c r="E13" s="96"/>
+      <c r="F13" s="96"/>
+      <c r="G13" s="96"/>
+      <c r="H13" s="96"/>
+      <c r="I13" s="96"/>
+      <c r="J13" s="194"/>
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A14" s="187" t="s">
+      <c r="A14" s="189" t="s">
         <v>24</v>
       </c>
-      <c r="B14" s="98"/>
-      <c r="C14" s="98"/>
-      <c r="D14" s="98"/>
-      <c r="E14" s="98"/>
-      <c r="F14" s="98"/>
-      <c r="G14" s="98"/>
-      <c r="H14" s="98"/>
-      <c r="I14" s="98"/>
-      <c r="J14" s="99"/>
+      <c r="B14" s="111"/>
+      <c r="C14" s="111"/>
+      <c r="D14" s="111"/>
+      <c r="E14" s="111"/>
+      <c r="F14" s="111"/>
+      <c r="G14" s="111"/>
+      <c r="H14" s="111"/>
+      <c r="I14" s="111"/>
+      <c r="J14" s="114"/>
     </row>
     <row r="15" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A15" s="187" t="s">
+      <c r="A15" s="189" t="s">
         <v>25</v>
       </c>
-      <c r="B15" s="98"/>
-      <c r="C15" s="93"/>
-      <c r="D15" s="97" t="s">
+      <c r="B15" s="111"/>
+      <c r="C15" s="112"/>
+      <c r="D15" s="120" t="s">
         <v>87</v>
       </c>
-      <c r="E15" s="98"/>
-      <c r="F15" s="98"/>
-      <c r="G15" s="98"/>
-      <c r="H15" s="93"/>
+      <c r="E15" s="111"/>
+      <c r="F15" s="111"/>
+      <c r="G15" s="111"/>
+      <c r="H15" s="112"/>
       <c r="I15" s="45" t="s">
         <v>26</v>
       </c>
@@ -16022,11 +16789,11 @@
       </c>
     </row>
     <row r="16" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A16" s="187" t="s">
+      <c r="A16" s="189" t="s">
         <v>27</v>
       </c>
-      <c r="B16" s="98"/>
-      <c r="C16" s="93"/>
+      <c r="B16" s="111"/>
+      <c r="C16" s="112"/>
       <c r="D16" s="45" t="s">
         <v>28</v>
       </c>
@@ -16039,18 +16806,18 @@
       <c r="G16" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="H16" s="195" t="s">
+      <c r="H16" s="190" t="s">
         <v>18</v>
       </c>
-      <c r="I16" s="98"/>
-      <c r="J16" s="99"/>
+      <c r="I16" s="111"/>
+      <c r="J16" s="114"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="196">
+      <c r="A17" s="187">
         <v>1</v>
       </c>
-      <c r="B17" s="98"/>
-      <c r="C17" s="93"/>
+      <c r="B17" s="111"/>
+      <c r="C17" s="112"/>
       <c r="D17" s="47" t="s">
         <v>64</v>
       </c>
@@ -16063,83 +16830,83 @@
       <c r="G17" s="48" t="s">
         <v>89</v>
       </c>
-      <c r="H17" s="97" t="s">
+      <c r="H17" s="120" t="s">
         <v>90</v>
       </c>
-      <c r="I17" s="98"/>
-      <c r="J17" s="99"/>
+      <c r="I17" s="111"/>
+      <c r="J17" s="114"/>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A18" s="196"/>
-      <c r="B18" s="98"/>
-      <c r="C18" s="93"/>
+      <c r="A18" s="187"/>
+      <c r="B18" s="111"/>
+      <c r="C18" s="112"/>
       <c r="D18" s="47"/>
       <c r="E18" s="47"/>
       <c r="F18" s="48"/>
       <c r="G18" s="48"/>
-      <c r="H18" s="97"/>
-      <c r="I18" s="98"/>
-      <c r="J18" s="99"/>
+      <c r="H18" s="120"/>
+      <c r="I18" s="111"/>
+      <c r="J18" s="114"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="196"/>
-      <c r="B19" s="98"/>
-      <c r="C19" s="93"/>
+      <c r="A19" s="187"/>
+      <c r="B19" s="111"/>
+      <c r="C19" s="112"/>
       <c r="D19" s="47"/>
       <c r="E19" s="47"/>
       <c r="F19" s="48"/>
       <c r="G19" s="48"/>
-      <c r="H19" s="97"/>
-      <c r="I19" s="98"/>
-      <c r="J19" s="99"/>
+      <c r="H19" s="120"/>
+      <c r="I19" s="111"/>
+      <c r="J19" s="114"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="196"/>
-      <c r="B20" s="98"/>
-      <c r="C20" s="93"/>
+      <c r="A20" s="187"/>
+      <c r="B20" s="111"/>
+      <c r="C20" s="112"/>
       <c r="D20" s="47"/>
       <c r="E20" s="47"/>
       <c r="F20" s="48"/>
       <c r="G20" s="48"/>
-      <c r="H20" s="97"/>
-      <c r="I20" s="98"/>
-      <c r="J20" s="99"/>
+      <c r="H20" s="120"/>
+      <c r="I20" s="111"/>
+      <c r="J20" s="114"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="196"/>
-      <c r="B21" s="98"/>
-      <c r="C21" s="93"/>
+      <c r="A21" s="187"/>
+      <c r="B21" s="111"/>
+      <c r="C21" s="112"/>
       <c r="D21" s="47"/>
       <c r="E21" s="47"/>
       <c r="F21" s="48"/>
       <c r="G21" s="48"/>
-      <c r="H21" s="97"/>
-      <c r="I21" s="98"/>
-      <c r="J21" s="99"/>
+      <c r="H21" s="120"/>
+      <c r="I21" s="111"/>
+      <c r="J21" s="114"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="196"/>
-      <c r="B22" s="98"/>
-      <c r="C22" s="93"/>
+      <c r="A22" s="187"/>
+      <c r="B22" s="111"/>
+      <c r="C22" s="112"/>
       <c r="D22" s="47"/>
       <c r="E22" s="47"/>
       <c r="F22" s="48"/>
       <c r="G22" s="48"/>
-      <c r="H22" s="97"/>
-      <c r="I22" s="98"/>
-      <c r="J22" s="99"/>
+      <c r="H22" s="120"/>
+      <c r="I22" s="111"/>
+      <c r="J22" s="114"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A23" s="197"/>
-      <c r="B23" s="105"/>
-      <c r="C23" s="106"/>
+      <c r="A23" s="188"/>
+      <c r="B23" s="116"/>
+      <c r="C23" s="117"/>
       <c r="D23" s="49"/>
       <c r="E23" s="49"/>
       <c r="F23" s="50"/>
       <c r="G23" s="50"/>
-      <c r="H23" s="107"/>
-      <c r="I23" s="105"/>
-      <c r="J23" s="108"/>
+      <c r="H23" s="118"/>
+      <c r="I23" s="116"/>
+      <c r="J23" s="119"/>
     </row>
     <row r="24" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="25" spans="1:10" ht="12.75" customHeight="1"/>
@@ -17120,22 +17887,6 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="31">
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="H22:J22"/>
-    <mergeCell ref="A23:C23"/>
-    <mergeCell ref="H23:J23"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="H19:J19"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="H20:J20"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="H21:J21"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="H16:J16"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="H17:J17"/>
     <mergeCell ref="A14:J14"/>
     <mergeCell ref="A15:C15"/>
     <mergeCell ref="A7:J13"/>
@@ -17151,8 +17902,24 @@
     <mergeCell ref="D5:J5"/>
     <mergeCell ref="A6:J6"/>
     <mergeCell ref="D15:H15"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="H16:J16"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="H18:J18"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="H17:J17"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="H23:J23"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="H19:J19"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="H20:J20"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="H21:J21"/>
   </mergeCells>
-  <phoneticPr fontId="8"/>
+  <phoneticPr fontId="9"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="landscape"/>
   <drawing r:id="rId1"/>
@@ -17174,19 +17941,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="192" t="s">
+      <c r="A1" s="195" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="122"/>
-      <c r="C1" s="123"/>
-      <c r="D1" s="130" t="s">
+      <c r="B1" s="93"/>
+      <c r="C1" s="94"/>
+      <c r="D1" s="101" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="115"/>
-      <c r="F1" s="130" t="s">
+      <c r="E1" s="102"/>
+      <c r="F1" s="101" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="115"/>
+      <c r="G1" s="102"/>
       <c r="H1" s="35" t="s">
         <v>6</v>
       </c>
@@ -17198,190 +17965,190 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="124"/>
-      <c r="B2" s="125"/>
-      <c r="C2" s="126"/>
-      <c r="D2" s="131" t="s">
+      <c r="A2" s="95"/>
+      <c r="B2" s="96"/>
+      <c r="C2" s="97"/>
+      <c r="D2" s="103" t="s">
         <v>84</v>
       </c>
-      <c r="E2" s="132"/>
-      <c r="F2" s="131">
+      <c r="E2" s="104"/>
+      <c r="F2" s="103">
         <v>56</v>
       </c>
-      <c r="G2" s="132"/>
-      <c r="H2" s="100">
+      <c r="G2" s="104"/>
+      <c r="H2" s="107">
         <v>45805</v>
       </c>
-      <c r="I2" s="109" t="s">
+      <c r="I2" s="121" t="s">
         <v>83</v>
       </c>
-      <c r="J2" s="110"/>
+      <c r="J2" s="122"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="124"/>
-      <c r="B3" s="125"/>
-      <c r="C3" s="126"/>
-      <c r="D3" s="133"/>
-      <c r="E3" s="126"/>
-      <c r="F3" s="133"/>
-      <c r="G3" s="126"/>
-      <c r="H3" s="101"/>
-      <c r="I3" s="101"/>
-      <c r="J3" s="111"/>
+      <c r="A3" s="95"/>
+      <c r="B3" s="96"/>
+      <c r="C3" s="97"/>
+      <c r="D3" s="105"/>
+      <c r="E3" s="97"/>
+      <c r="F3" s="105"/>
+      <c r="G3" s="97"/>
+      <c r="H3" s="108"/>
+      <c r="I3" s="108"/>
+      <c r="J3" s="123"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="124"/>
-      <c r="B4" s="125"/>
-      <c r="C4" s="126"/>
-      <c r="D4" s="133"/>
-      <c r="E4" s="126"/>
-      <c r="F4" s="133"/>
-      <c r="G4" s="126"/>
-      <c r="H4" s="101"/>
-      <c r="I4" s="101"/>
-      <c r="J4" s="111"/>
+      <c r="A4" s="95"/>
+      <c r="B4" s="96"/>
+      <c r="C4" s="97"/>
+      <c r="D4" s="105"/>
+      <c r="E4" s="97"/>
+      <c r="F4" s="105"/>
+      <c r="G4" s="97"/>
+      <c r="H4" s="108"/>
+      <c r="I4" s="108"/>
+      <c r="J4" s="123"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="193" t="s">
+      <c r="A5" s="196" t="s">
         <v>22</v>
       </c>
-      <c r="B5" s="114"/>
-      <c r="C5" s="115"/>
-      <c r="D5" s="194" t="s">
+      <c r="B5" s="126"/>
+      <c r="C5" s="102"/>
+      <c r="D5" s="197" t="s">
         <v>91</v>
       </c>
-      <c r="E5" s="114"/>
-      <c r="F5" s="114"/>
-      <c r="G5" s="114"/>
-      <c r="H5" s="114"/>
-      <c r="I5" s="114"/>
-      <c r="J5" s="117"/>
+      <c r="E5" s="126"/>
+      <c r="F5" s="126"/>
+      <c r="G5" s="126"/>
+      <c r="H5" s="126"/>
+      <c r="I5" s="126"/>
+      <c r="J5" s="128"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="187" t="s">
+      <c r="A6" s="189" t="s">
         <v>23</v>
       </c>
-      <c r="B6" s="98"/>
-      <c r="C6" s="98"/>
-      <c r="D6" s="98"/>
-      <c r="E6" s="98"/>
-      <c r="F6" s="98"/>
-      <c r="G6" s="98"/>
-      <c r="H6" s="98"/>
-      <c r="I6" s="98"/>
-      <c r="J6" s="99"/>
+      <c r="B6" s="111"/>
+      <c r="C6" s="111"/>
+      <c r="D6" s="111"/>
+      <c r="E6" s="111"/>
+      <c r="F6" s="111"/>
+      <c r="G6" s="111"/>
+      <c r="H6" s="111"/>
+      <c r="I6" s="111"/>
+      <c r="J6" s="114"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="188"/>
-      <c r="B7" s="189"/>
-      <c r="C7" s="189"/>
-      <c r="D7" s="189"/>
-      <c r="E7" s="189"/>
-      <c r="F7" s="189"/>
-      <c r="G7" s="189"/>
-      <c r="H7" s="189"/>
-      <c r="I7" s="189"/>
-      <c r="J7" s="190"/>
+      <c r="A7" s="191"/>
+      <c r="B7" s="192"/>
+      <c r="C7" s="192"/>
+      <c r="D7" s="192"/>
+      <c r="E7" s="192"/>
+      <c r="F7" s="192"/>
+      <c r="G7" s="192"/>
+      <c r="H7" s="192"/>
+      <c r="I7" s="192"/>
+      <c r="J7" s="193"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="124"/>
-      <c r="B8" s="125"/>
-      <c r="C8" s="125"/>
-      <c r="D8" s="125"/>
-      <c r="E8" s="125"/>
-      <c r="F8" s="125"/>
-      <c r="G8" s="125"/>
-      <c r="H8" s="125"/>
-      <c r="I8" s="125"/>
-      <c r="J8" s="191"/>
+      <c r="A8" s="95"/>
+      <c r="B8" s="96"/>
+      <c r="C8" s="96"/>
+      <c r="D8" s="96"/>
+      <c r="E8" s="96"/>
+      <c r="F8" s="96"/>
+      <c r="G8" s="96"/>
+      <c r="H8" s="96"/>
+      <c r="I8" s="96"/>
+      <c r="J8" s="194"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="124"/>
-      <c r="B9" s="125"/>
-      <c r="C9" s="125"/>
-      <c r="D9" s="125"/>
-      <c r="E9" s="125"/>
-      <c r="F9" s="125"/>
-      <c r="G9" s="125"/>
-      <c r="H9" s="125"/>
-      <c r="I9" s="125"/>
-      <c r="J9" s="191"/>
+      <c r="A9" s="95"/>
+      <c r="B9" s="96"/>
+      <c r="C9" s="96"/>
+      <c r="D9" s="96"/>
+      <c r="E9" s="96"/>
+      <c r="F9" s="96"/>
+      <c r="G9" s="96"/>
+      <c r="H9" s="96"/>
+      <c r="I9" s="96"/>
+      <c r="J9" s="194"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="124"/>
-      <c r="B10" s="125"/>
-      <c r="C10" s="125"/>
-      <c r="D10" s="125"/>
-      <c r="E10" s="125"/>
-      <c r="F10" s="125"/>
-      <c r="G10" s="125"/>
-      <c r="H10" s="125"/>
-      <c r="I10" s="125"/>
-      <c r="J10" s="191"/>
+      <c r="A10" s="95"/>
+      <c r="B10" s="96"/>
+      <c r="C10" s="96"/>
+      <c r="D10" s="96"/>
+      <c r="E10" s="96"/>
+      <c r="F10" s="96"/>
+      <c r="G10" s="96"/>
+      <c r="H10" s="96"/>
+      <c r="I10" s="96"/>
+      <c r="J10" s="194"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="124"/>
-      <c r="B11" s="125"/>
-      <c r="C11" s="125"/>
-      <c r="D11" s="125"/>
-      <c r="E11" s="125"/>
-      <c r="F11" s="125"/>
-      <c r="G11" s="125"/>
-      <c r="H11" s="125"/>
-      <c r="I11" s="125"/>
-      <c r="J11" s="191"/>
+      <c r="A11" s="95"/>
+      <c r="B11" s="96"/>
+      <c r="C11" s="96"/>
+      <c r="D11" s="96"/>
+      <c r="E11" s="96"/>
+      <c r="F11" s="96"/>
+      <c r="G11" s="96"/>
+      <c r="H11" s="96"/>
+      <c r="I11" s="96"/>
+      <c r="J11" s="194"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="124"/>
-      <c r="B12" s="125"/>
-      <c r="C12" s="125"/>
-      <c r="D12" s="125"/>
-      <c r="E12" s="125"/>
-      <c r="F12" s="125"/>
-      <c r="G12" s="125"/>
-      <c r="H12" s="125"/>
-      <c r="I12" s="125"/>
-      <c r="J12" s="191"/>
+      <c r="A12" s="95"/>
+      <c r="B12" s="96"/>
+      <c r="C12" s="96"/>
+      <c r="D12" s="96"/>
+      <c r="E12" s="96"/>
+      <c r="F12" s="96"/>
+      <c r="G12" s="96"/>
+      <c r="H12" s="96"/>
+      <c r="I12" s="96"/>
+      <c r="J12" s="194"/>
     </row>
     <row r="13" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A13" s="124"/>
-      <c r="B13" s="125"/>
-      <c r="C13" s="125"/>
-      <c r="D13" s="125"/>
-      <c r="E13" s="125"/>
-      <c r="F13" s="125"/>
-      <c r="G13" s="125"/>
-      <c r="H13" s="125"/>
-      <c r="I13" s="125"/>
-      <c r="J13" s="191"/>
+      <c r="A13" s="95"/>
+      <c r="B13" s="96"/>
+      <c r="C13" s="96"/>
+      <c r="D13" s="96"/>
+      <c r="E13" s="96"/>
+      <c r="F13" s="96"/>
+      <c r="G13" s="96"/>
+      <c r="H13" s="96"/>
+      <c r="I13" s="96"/>
+      <c r="J13" s="194"/>
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A14" s="187" t="s">
+      <c r="A14" s="189" t="s">
         <v>24</v>
       </c>
-      <c r="B14" s="98"/>
-      <c r="C14" s="98"/>
-      <c r="D14" s="98"/>
-      <c r="E14" s="98"/>
-      <c r="F14" s="98"/>
-      <c r="G14" s="98"/>
-      <c r="H14" s="98"/>
-      <c r="I14" s="98"/>
-      <c r="J14" s="99"/>
+      <c r="B14" s="111"/>
+      <c r="C14" s="111"/>
+      <c r="D14" s="111"/>
+      <c r="E14" s="111"/>
+      <c r="F14" s="111"/>
+      <c r="G14" s="111"/>
+      <c r="H14" s="111"/>
+      <c r="I14" s="111"/>
+      <c r="J14" s="114"/>
     </row>
     <row r="15" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A15" s="187" t="s">
+      <c r="A15" s="189" t="s">
         <v>25</v>
       </c>
-      <c r="B15" s="98"/>
-      <c r="C15" s="93"/>
-      <c r="D15" s="97" t="s">
+      <c r="B15" s="111"/>
+      <c r="C15" s="112"/>
+      <c r="D15" s="120" t="s">
         <v>87</v>
       </c>
-      <c r="E15" s="98"/>
-      <c r="F15" s="98"/>
-      <c r="G15" s="98"/>
-      <c r="H15" s="93"/>
+      <c r="E15" s="111"/>
+      <c r="F15" s="111"/>
+      <c r="G15" s="111"/>
+      <c r="H15" s="112"/>
       <c r="I15" s="45" t="s">
         <v>26</v>
       </c>
@@ -17390,11 +18157,11 @@
       </c>
     </row>
     <row r="16" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A16" s="187" t="s">
+      <c r="A16" s="189" t="s">
         <v>27</v>
       </c>
-      <c r="B16" s="98"/>
-      <c r="C16" s="93"/>
+      <c r="B16" s="111"/>
+      <c r="C16" s="112"/>
       <c r="D16" s="45" t="s">
         <v>28</v>
       </c>
@@ -17407,18 +18174,18 @@
       <c r="G16" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="H16" s="195" t="s">
+      <c r="H16" s="190" t="s">
         <v>18</v>
       </c>
-      <c r="I16" s="98"/>
-      <c r="J16" s="99"/>
+      <c r="I16" s="111"/>
+      <c r="J16" s="114"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="196">
+      <c r="A17" s="187">
         <v>1</v>
       </c>
-      <c r="B17" s="98"/>
-      <c r="C17" s="93"/>
+      <c r="B17" s="111"/>
+      <c r="C17" s="112"/>
       <c r="D17" s="47" t="s">
         <v>64</v>
       </c>
@@ -17431,83 +18198,83 @@
       <c r="G17" s="48" t="s">
         <v>89</v>
       </c>
-      <c r="H17" s="97" t="s">
+      <c r="H17" s="120" t="s">
         <v>90</v>
       </c>
-      <c r="I17" s="98"/>
-      <c r="J17" s="99"/>
+      <c r="I17" s="111"/>
+      <c r="J17" s="114"/>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A18" s="196"/>
-      <c r="B18" s="98"/>
-      <c r="C18" s="93"/>
+      <c r="A18" s="187"/>
+      <c r="B18" s="111"/>
+      <c r="C18" s="112"/>
       <c r="D18" s="47"/>
       <c r="E18" s="47"/>
       <c r="F18" s="48"/>
       <c r="G18" s="48"/>
-      <c r="H18" s="97"/>
-      <c r="I18" s="98"/>
-      <c r="J18" s="99"/>
+      <c r="H18" s="120"/>
+      <c r="I18" s="111"/>
+      <c r="J18" s="114"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="196"/>
-      <c r="B19" s="98"/>
-      <c r="C19" s="93"/>
+      <c r="A19" s="187"/>
+      <c r="B19" s="111"/>
+      <c r="C19" s="112"/>
       <c r="D19" s="47"/>
       <c r="E19" s="47"/>
       <c r="F19" s="48"/>
       <c r="G19" s="48"/>
-      <c r="H19" s="97"/>
-      <c r="I19" s="98"/>
-      <c r="J19" s="99"/>
+      <c r="H19" s="120"/>
+      <c r="I19" s="111"/>
+      <c r="J19" s="114"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="196"/>
-      <c r="B20" s="98"/>
-      <c r="C20" s="93"/>
+      <c r="A20" s="187"/>
+      <c r="B20" s="111"/>
+      <c r="C20" s="112"/>
       <c r="D20" s="47"/>
       <c r="E20" s="47"/>
       <c r="F20" s="48"/>
       <c r="G20" s="48"/>
-      <c r="H20" s="97"/>
-      <c r="I20" s="98"/>
-      <c r="J20" s="99"/>
+      <c r="H20" s="120"/>
+      <c r="I20" s="111"/>
+      <c r="J20" s="114"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="196"/>
-      <c r="B21" s="98"/>
-      <c r="C21" s="93"/>
+      <c r="A21" s="187"/>
+      <c r="B21" s="111"/>
+      <c r="C21" s="112"/>
       <c r="D21" s="47"/>
       <c r="E21" s="47"/>
       <c r="F21" s="48"/>
       <c r="G21" s="48"/>
-      <c r="H21" s="97"/>
-      <c r="I21" s="98"/>
-      <c r="J21" s="99"/>
+      <c r="H21" s="120"/>
+      <c r="I21" s="111"/>
+      <c r="J21" s="114"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="196"/>
-      <c r="B22" s="98"/>
-      <c r="C22" s="93"/>
+      <c r="A22" s="187"/>
+      <c r="B22" s="111"/>
+      <c r="C22" s="112"/>
       <c r="D22" s="47"/>
       <c r="E22" s="47"/>
       <c r="F22" s="48"/>
       <c r="G22" s="48"/>
-      <c r="H22" s="97"/>
-      <c r="I22" s="98"/>
-      <c r="J22" s="99"/>
+      <c r="H22" s="120"/>
+      <c r="I22" s="111"/>
+      <c r="J22" s="114"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A23" s="197"/>
-      <c r="B23" s="105"/>
-      <c r="C23" s="106"/>
+      <c r="A23" s="188"/>
+      <c r="B23" s="116"/>
+      <c r="C23" s="117"/>
       <c r="D23" s="49"/>
       <c r="E23" s="49"/>
       <c r="F23" s="50"/>
       <c r="G23" s="50"/>
-      <c r="H23" s="107"/>
-      <c r="I23" s="105"/>
-      <c r="J23" s="108"/>
+      <c r="H23" s="118"/>
+      <c r="I23" s="116"/>
+      <c r="J23" s="119"/>
     </row>
     <row r="24" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="25" spans="1:10" ht="12.75" customHeight="1"/>
@@ -18488,22 +19255,6 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="31">
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="H22:J22"/>
-    <mergeCell ref="A23:C23"/>
-    <mergeCell ref="H23:J23"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="H19:J19"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="H20:J20"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="H21:J21"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="H16:J16"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="H17:J17"/>
     <mergeCell ref="A14:J14"/>
     <mergeCell ref="A15:C15"/>
     <mergeCell ref="A7:J13"/>
@@ -18519,8 +19270,24 @@
     <mergeCell ref="D5:J5"/>
     <mergeCell ref="A6:J6"/>
     <mergeCell ref="D15:H15"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="H16:J16"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="H18:J18"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="H17:J17"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="H23:J23"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="H19:J19"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="H20:J20"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="H21:J21"/>
   </mergeCells>
-  <phoneticPr fontId="8"/>
+  <phoneticPr fontId="9"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="landscape"/>
   <drawing r:id="rId1"/>
@@ -18538,7 +19305,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="18" customHeight="1">
-      <c r="A1" s="224" t="s">
+      <c r="A1" s="213" t="s">
         <v>32</v>
       </c>
       <c r="B1" s="143"/>
@@ -18549,14 +19316,14 @@
       <c r="G1" s="150" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="209"/>
-      <c r="I1" s="209"/>
+      <c r="H1" s="214"/>
+      <c r="I1" s="214"/>
       <c r="J1" s="151"/>
       <c r="K1" s="150" t="s">
         <v>5</v>
       </c>
-      <c r="L1" s="209"/>
-      <c r="M1" s="209"/>
+      <c r="L1" s="214"/>
+      <c r="M1" s="214"/>
       <c r="N1" s="151"/>
       <c r="O1" s="150" t="s">
         <v>6</v>
@@ -18569,7 +19336,7 @@
       <c r="S1" s="150" t="s">
         <v>8</v>
       </c>
-      <c r="T1" s="211"/>
+      <c r="T1" s="215"/>
     </row>
     <row r="2" spans="1:26" ht="18" customHeight="1">
       <c r="A2" s="145"/>
@@ -18581,16 +19348,16 @@
       <c r="G2" s="152" t="s">
         <v>84</v>
       </c>
-      <c r="H2" s="219"/>
-      <c r="I2" s="219"/>
+      <c r="H2" s="208"/>
+      <c r="I2" s="208"/>
       <c r="J2" s="153"/>
       <c r="K2" s="152" t="s">
         <v>54</v>
       </c>
-      <c r="L2" s="219"/>
-      <c r="M2" s="219"/>
+      <c r="L2" s="208"/>
+      <c r="M2" s="208"/>
       <c r="N2" s="153"/>
-      <c r="O2" s="220">
+      <c r="O2" s="209">
         <v>45821</v>
       </c>
       <c r="P2" s="153"/>
@@ -18599,7 +19366,7 @@
       </c>
       <c r="R2" s="153"/>
       <c r="S2" s="152"/>
-      <c r="T2" s="221"/>
+      <c r="T2" s="210"/>
     </row>
     <row r="3" spans="1:26" ht="18" customHeight="1">
       <c r="A3" s="145"/>
@@ -18621,7 +19388,7 @@
       <c r="Q3" s="154"/>
       <c r="R3" s="146"/>
       <c r="S3" s="154"/>
-      <c r="T3" s="222"/>
+      <c r="T3" s="211"/>
     </row>
     <row r="4" spans="1:26" ht="18" customHeight="1">
       <c r="A4" s="147"/>
@@ -18643,36 +19410,36 @@
       <c r="Q4" s="155"/>
       <c r="R4" s="149"/>
       <c r="S4" s="155"/>
-      <c r="T4" s="223"/>
+      <c r="T4" s="212"/>
     </row>
     <row r="5" spans="1:26" ht="18" customHeight="1">
-      <c r="A5" s="208" t="s">
+      <c r="A5" s="216" t="s">
         <v>33</v>
       </c>
-      <c r="B5" s="209"/>
-      <c r="C5" s="209"/>
-      <c r="D5" s="209"/>
-      <c r="E5" s="209"/>
+      <c r="B5" s="214"/>
+      <c r="C5" s="214"/>
+      <c r="D5" s="214"/>
+      <c r="E5" s="214"/>
       <c r="F5" s="151"/>
-      <c r="G5" s="210" t="s">
+      <c r="G5" s="217" t="s">
         <v>34</v>
       </c>
-      <c r="H5" s="209"/>
-      <c r="I5" s="209"/>
-      <c r="J5" s="209"/>
-      <c r="K5" s="209"/>
-      <c r="L5" s="209"/>
-      <c r="M5" s="209"/>
-      <c r="N5" s="209"/>
-      <c r="O5" s="209"/>
-      <c r="P5" s="209"/>
-      <c r="Q5" s="209"/>
-      <c r="R5" s="209"/>
-      <c r="S5" s="209"/>
-      <c r="T5" s="211"/>
+      <c r="H5" s="214"/>
+      <c r="I5" s="214"/>
+      <c r="J5" s="214"/>
+      <c r="K5" s="214"/>
+      <c r="L5" s="214"/>
+      <c r="M5" s="214"/>
+      <c r="N5" s="214"/>
+      <c r="O5" s="214"/>
+      <c r="P5" s="214"/>
+      <c r="Q5" s="214"/>
+      <c r="R5" s="214"/>
+      <c r="S5" s="214"/>
+      <c r="T5" s="215"/>
     </row>
     <row r="6" spans="1:26" ht="18" customHeight="1">
-      <c r="A6" s="212" t="s">
+      <c r="A6" s="218" t="s">
         <v>35</v>
       </c>
       <c r="B6" s="84"/>
@@ -18680,7 +19447,7 @@
       <c r="D6" s="84"/>
       <c r="E6" s="84"/>
       <c r="F6" s="85"/>
-      <c r="G6" s="213" t="s">
+      <c r="G6" s="219" t="s">
         <v>19</v>
       </c>
       <c r="H6" s="84"/>
@@ -18695,10 +19462,10 @@
       <c r="Q6" s="84"/>
       <c r="R6" s="84"/>
       <c r="S6" s="84"/>
-      <c r="T6" s="214"/>
+      <c r="T6" s="220"/>
     </row>
     <row r="7" spans="1:26" ht="18" customHeight="1">
-      <c r="A7" s="212" t="s">
+      <c r="A7" s="218" t="s">
         <v>36</v>
       </c>
       <c r="B7" s="84"/>
@@ -18706,7 +19473,7 @@
       <c r="D7" s="84"/>
       <c r="E7" s="84"/>
       <c r="F7" s="85"/>
-      <c r="G7" s="213" t="s">
+      <c r="G7" s="219" t="s">
         <v>111</v>
       </c>
       <c r="H7" s="84"/>
@@ -18721,7 +19488,7 @@
       <c r="Q7" s="84"/>
       <c r="R7" s="84"/>
       <c r="S7" s="84"/>
-      <c r="T7" s="214"/>
+      <c r="T7" s="220"/>
     </row>
     <row r="8" spans="1:26" ht="7.5" customHeight="1">
       <c r="A8" s="7"/>
@@ -18920,33 +19687,33 @@
       <c r="T14" s="9"/>
     </row>
     <row r="15" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A15" s="212" t="s">
+      <c r="A15" s="218" t="s">
         <v>43</v>
       </c>
       <c r="B15" s="85"/>
-      <c r="C15" s="218" t="s">
+      <c r="C15" s="224" t="s">
         <v>37</v>
       </c>
       <c r="D15" s="85"/>
-      <c r="E15" s="216" t="s">
+      <c r="E15" s="198" t="s">
         <v>44</v>
       </c>
       <c r="F15" s="85"/>
-      <c r="G15" s="216" t="s">
+      <c r="G15" s="198" t="s">
         <v>45</v>
       </c>
       <c r="H15" s="84"/>
       <c r="I15" s="85"/>
-      <c r="J15" s="216" t="s">
+      <c r="J15" s="198" t="s">
         <v>46</v>
       </c>
       <c r="K15" s="85"/>
-      <c r="L15" s="216" t="s">
+      <c r="L15" s="198" t="s">
         <v>47</v>
       </c>
       <c r="M15" s="84"/>
       <c r="N15" s="85"/>
-      <c r="O15" s="216" t="s">
+      <c r="O15" s="198" t="s">
         <v>48</v>
       </c>
       <c r="P15" s="84"/>
@@ -18962,33 +19729,33 @@
       </c>
     </row>
     <row r="16" spans="1:26" ht="48" customHeight="1">
-      <c r="A16" s="198">
+      <c r="A16" s="221">
         <v>1</v>
       </c>
       <c r="B16" s="85"/>
-      <c r="C16" s="199" t="s">
+      <c r="C16" s="222" t="s">
         <v>52</v>
       </c>
       <c r="D16" s="85"/>
-      <c r="E16" s="199" t="s">
+      <c r="E16" s="222" t="s">
         <v>53</v>
       </c>
       <c r="F16" s="85"/>
-      <c r="G16" s="215" t="s">
+      <c r="G16" s="199" t="s">
         <v>112</v>
       </c>
       <c r="H16" s="84"/>
       <c r="I16" s="85"/>
-      <c r="J16" s="228" t="s">
+      <c r="J16" s="200" t="s">
         <v>113</v>
       </c>
-      <c r="K16" s="93"/>
-      <c r="L16" s="205" t="s">
+      <c r="K16" s="112"/>
+      <c r="L16" s="204" t="s">
         <v>114</v>
       </c>
       <c r="M16" s="84"/>
       <c r="N16" s="85"/>
-      <c r="O16" s="205" t="s">
+      <c r="O16" s="204" t="s">
         <v>115</v>
       </c>
       <c r="P16" s="84"/>
@@ -19010,33 +19777,33 @@
       <c r="Z16" s="29"/>
     </row>
     <row r="17" spans="1:26" ht="51" customHeight="1">
-      <c r="A17" s="198">
+      <c r="A17" s="221">
         <v>2</v>
       </c>
       <c r="B17" s="85"/>
-      <c r="C17" s="199" t="s">
+      <c r="C17" s="222" t="s">
         <v>52</v>
       </c>
       <c r="D17" s="85"/>
-      <c r="E17" s="199" t="s">
+      <c r="E17" s="222" t="s">
         <v>118</v>
       </c>
       <c r="F17" s="85"/>
-      <c r="G17" s="215" t="s">
+      <c r="G17" s="199" t="s">
         <v>116</v>
       </c>
       <c r="H17" s="84"/>
       <c r="I17" s="85"/>
-      <c r="J17" s="215" t="s">
+      <c r="J17" s="199" t="s">
         <v>117</v>
       </c>
       <c r="K17" s="85"/>
-      <c r="L17" s="217" t="s">
+      <c r="L17" s="223" t="s">
         <v>119</v>
       </c>
       <c r="M17" s="84"/>
       <c r="N17" s="85"/>
-      <c r="O17" s="205" t="s">
+      <c r="O17" s="204" t="s">
         <v>122</v>
       </c>
       <c r="P17" s="84"/>
@@ -19058,33 +19825,33 @@
       <c r="Z17" s="29"/>
     </row>
     <row r="18" spans="1:26" ht="120" customHeight="1">
-      <c r="A18" s="198">
+      <c r="A18" s="221">
         <v>3</v>
       </c>
       <c r="B18" s="85"/>
-      <c r="C18" s="199" t="s">
+      <c r="C18" s="222" t="s">
         <v>52</v>
       </c>
       <c r="D18" s="85"/>
-      <c r="E18" s="199" t="s">
+      <c r="E18" s="222" t="s">
         <v>53</v>
       </c>
       <c r="F18" s="85"/>
-      <c r="G18" s="215" t="s">
+      <c r="G18" s="199" t="s">
         <v>139</v>
       </c>
       <c r="H18" s="84"/>
       <c r="I18" s="85"/>
-      <c r="J18" s="215" t="s">
+      <c r="J18" s="199" t="s">
         <v>140</v>
       </c>
       <c r="K18" s="85"/>
-      <c r="L18" s="205" t="s">
+      <c r="L18" s="204" t="s">
         <v>114</v>
       </c>
       <c r="M18" s="84"/>
       <c r="N18" s="85"/>
-      <c r="O18" s="205" t="s">
+      <c r="O18" s="204" t="s">
         <v>120</v>
       </c>
       <c r="P18" s="84"/>
@@ -19106,33 +19873,33 @@
       <c r="Z18" s="29"/>
     </row>
     <row r="19" spans="1:26" ht="94.5" customHeight="1">
-      <c r="A19" s="198">
+      <c r="A19" s="221">
         <v>4</v>
       </c>
       <c r="B19" s="85"/>
-      <c r="C19" s="199" t="s">
+      <c r="C19" s="222" t="s">
         <v>52</v>
       </c>
       <c r="D19" s="85"/>
-      <c r="E19" s="199" t="s">
+      <c r="E19" s="222" t="s">
         <v>118</v>
       </c>
       <c r="F19" s="85"/>
-      <c r="G19" s="215" t="s">
+      <c r="G19" s="199" t="s">
         <v>141</v>
       </c>
       <c r="H19" s="84"/>
       <c r="I19" s="85"/>
-      <c r="J19" s="215" t="s">
+      <c r="J19" s="199" t="s">
         <v>142</v>
       </c>
       <c r="K19" s="85"/>
-      <c r="L19" s="205" t="s">
+      <c r="L19" s="204" t="s">
         <v>114</v>
       </c>
       <c r="M19" s="84"/>
       <c r="N19" s="85"/>
-      <c r="O19" s="205" t="s">
+      <c r="O19" s="204" t="s">
         <v>121</v>
       </c>
       <c r="P19" s="84"/>
@@ -19154,33 +19921,33 @@
       <c r="Z19" s="29"/>
     </row>
     <row r="20" spans="1:26" ht="120" customHeight="1">
-      <c r="A20" s="198">
+      <c r="A20" s="221">
         <v>5</v>
       </c>
       <c r="B20" s="85"/>
-      <c r="C20" s="199" t="s">
+      <c r="C20" s="222" t="s">
         <v>138</v>
       </c>
       <c r="D20" s="85"/>
-      <c r="E20" s="199" t="s">
+      <c r="E20" s="222" t="s">
         <v>143</v>
       </c>
       <c r="F20" s="85"/>
-      <c r="G20" s="215" t="s">
+      <c r="G20" s="199" t="s">
         <v>146</v>
       </c>
       <c r="H20" s="84"/>
       <c r="I20" s="85"/>
-      <c r="J20" s="215" t="s">
+      <c r="J20" s="199" t="s">
         <v>145</v>
       </c>
       <c r="K20" s="85"/>
-      <c r="L20" s="205" t="s">
+      <c r="L20" s="204" t="s">
         <v>114</v>
       </c>
       <c r="M20" s="84"/>
       <c r="N20" s="85"/>
-      <c r="O20" s="205" t="s">
+      <c r="O20" s="204" t="s">
         <v>120</v>
       </c>
       <c r="P20" s="84"/>
@@ -19200,33 +19967,33 @@
       <c r="Z20" s="29"/>
     </row>
     <row r="21" spans="1:26" ht="75" customHeight="1">
-      <c r="A21" s="198">
+      <c r="A21" s="221">
         <v>6</v>
       </c>
       <c r="B21" s="85"/>
-      <c r="C21" s="199" t="s">
+      <c r="C21" s="222" t="s">
         <v>138</v>
       </c>
       <c r="D21" s="85"/>
-      <c r="E21" s="199" t="s">
+      <c r="E21" s="222" t="s">
         <v>118</v>
       </c>
       <c r="F21" s="85"/>
-      <c r="G21" s="215" t="s">
+      <c r="G21" s="199" t="s">
         <v>154</v>
       </c>
       <c r="H21" s="84"/>
       <c r="I21" s="85"/>
-      <c r="J21" s="215" t="s">
+      <c r="J21" s="199" t="s">
         <v>144</v>
       </c>
       <c r="K21" s="85"/>
-      <c r="L21" s="205" t="s">
+      <c r="L21" s="204" t="s">
         <v>114</v>
       </c>
       <c r="M21" s="84"/>
       <c r="N21" s="85"/>
-      <c r="O21" s="205" t="s">
+      <c r="O21" s="204" t="s">
         <v>121</v>
       </c>
       <c r="P21" s="84"/>
@@ -19248,33 +20015,33 @@
       <c r="Z21" s="29"/>
     </row>
     <row r="22" spans="1:26" ht="57" customHeight="1">
-      <c r="A22" s="203">
+      <c r="A22" s="225">
         <v>7</v>
       </c>
-      <c r="B22" s="93"/>
-      <c r="C22" s="204" t="s">
+      <c r="B22" s="112"/>
+      <c r="C22" s="226" t="s">
         <v>52</v>
       </c>
-      <c r="D22" s="93"/>
-      <c r="E22" s="204" t="s">
+      <c r="D22" s="112"/>
+      <c r="E22" s="226" t="s">
         <v>165</v>
       </c>
-      <c r="F22" s="93"/>
-      <c r="G22" s="228" t="s">
+      <c r="F22" s="112"/>
+      <c r="G22" s="200" t="s">
         <v>166</v>
       </c>
-      <c r="H22" s="98"/>
-      <c r="I22" s="93"/>
-      <c r="J22" s="228" t="s">
+      <c r="H22" s="111"/>
+      <c r="I22" s="112"/>
+      <c r="J22" s="200" t="s">
         <v>117</v>
       </c>
-      <c r="K22" s="93"/>
-      <c r="L22" s="225" t="s">
+      <c r="K22" s="112"/>
+      <c r="L22" s="206" t="s">
         <v>119</v>
       </c>
-      <c r="M22" s="226"/>
-      <c r="N22" s="226"/>
-      <c r="O22" s="205" t="s">
+      <c r="M22" s="207"/>
+      <c r="N22" s="207"/>
+      <c r="O22" s="204" t="s">
         <v>167</v>
       </c>
       <c r="P22" s="84"/>
@@ -19296,21 +20063,21 @@
       <c r="Z22" s="29"/>
     </row>
     <row r="23" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A23" s="198"/>
+      <c r="A23" s="221"/>
       <c r="B23" s="85"/>
-      <c r="C23" s="199"/>
+      <c r="C23" s="222"/>
       <c r="D23" s="85"/>
-      <c r="E23" s="199"/>
+      <c r="E23" s="222"/>
       <c r="F23" s="85"/>
-      <c r="G23" s="215"/>
+      <c r="G23" s="199"/>
       <c r="H23" s="84"/>
       <c r="I23" s="85"/>
-      <c r="J23" s="215"/>
+      <c r="J23" s="199"/>
       <c r="K23" s="85"/>
-      <c r="L23" s="205"/>
+      <c r="L23" s="204"/>
       <c r="M23" s="84"/>
       <c r="N23" s="85"/>
-      <c r="O23" s="205"/>
+      <c r="O23" s="204"/>
       <c r="P23" s="84"/>
       <c r="Q23" s="85"/>
       <c r="R23" s="27"/>
@@ -19324,21 +20091,21 @@
       <c r="Z23" s="29"/>
     </row>
     <row r="24" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A24" s="198"/>
+      <c r="A24" s="221"/>
       <c r="B24" s="85"/>
-      <c r="C24" s="199"/>
+      <c r="C24" s="222"/>
       <c r="D24" s="85"/>
-      <c r="E24" s="199"/>
+      <c r="E24" s="222"/>
       <c r="F24" s="85"/>
-      <c r="G24" s="215"/>
+      <c r="G24" s="199"/>
       <c r="H24" s="84"/>
       <c r="I24" s="85"/>
-      <c r="J24" s="215"/>
+      <c r="J24" s="199"/>
       <c r="K24" s="85"/>
-      <c r="L24" s="205"/>
+      <c r="L24" s="204"/>
       <c r="M24" s="84"/>
       <c r="N24" s="85"/>
-      <c r="O24" s="205"/>
+      <c r="O24" s="204"/>
       <c r="P24" s="84"/>
       <c r="Q24" s="85"/>
       <c r="R24" s="27"/>
@@ -19352,21 +20119,21 @@
       <c r="Z24" s="29"/>
     </row>
     <row r="25" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A25" s="198"/>
+      <c r="A25" s="221"/>
       <c r="B25" s="85"/>
-      <c r="C25" s="199"/>
+      <c r="C25" s="222"/>
       <c r="D25" s="85"/>
-      <c r="E25" s="199"/>
+      <c r="E25" s="222"/>
       <c r="F25" s="85"/>
-      <c r="G25" s="215"/>
+      <c r="G25" s="199"/>
       <c r="H25" s="84"/>
       <c r="I25" s="85"/>
-      <c r="J25" s="215"/>
+      <c r="J25" s="199"/>
       <c r="K25" s="85"/>
-      <c r="L25" s="205"/>
+      <c r="L25" s="204"/>
       <c r="M25" s="84"/>
       <c r="N25" s="85"/>
-      <c r="O25" s="205"/>
+      <c r="O25" s="204"/>
       <c r="P25" s="84"/>
       <c r="Q25" s="85"/>
       <c r="R25" s="27"/>
@@ -19380,21 +20147,21 @@
       <c r="Z25" s="29"/>
     </row>
     <row r="26" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A26" s="198"/>
+      <c r="A26" s="221"/>
       <c r="B26" s="85"/>
-      <c r="C26" s="199"/>
+      <c r="C26" s="222"/>
       <c r="D26" s="85"/>
-      <c r="E26" s="199"/>
+      <c r="E26" s="222"/>
       <c r="F26" s="85"/>
-      <c r="G26" s="215"/>
+      <c r="G26" s="199"/>
       <c r="H26" s="84"/>
       <c r="I26" s="85"/>
-      <c r="J26" s="215"/>
+      <c r="J26" s="199"/>
       <c r="K26" s="85"/>
-      <c r="L26" s="205"/>
+      <c r="L26" s="204"/>
       <c r="M26" s="84"/>
       <c r="N26" s="85"/>
-      <c r="O26" s="205"/>
+      <c r="O26" s="204"/>
       <c r="P26" s="84"/>
       <c r="Q26" s="85"/>
       <c r="R26" s="27"/>
@@ -19408,21 +20175,21 @@
       <c r="Z26" s="29"/>
     </row>
     <row r="27" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A27" s="198"/>
+      <c r="A27" s="221"/>
       <c r="B27" s="85"/>
-      <c r="C27" s="199"/>
+      <c r="C27" s="222"/>
       <c r="D27" s="85"/>
-      <c r="E27" s="199"/>
+      <c r="E27" s="222"/>
       <c r="F27" s="85"/>
-      <c r="G27" s="215"/>
+      <c r="G27" s="199"/>
       <c r="H27" s="84"/>
       <c r="I27" s="85"/>
-      <c r="J27" s="215"/>
+      <c r="J27" s="199"/>
       <c r="K27" s="85"/>
-      <c r="L27" s="205"/>
+      <c r="L27" s="204"/>
       <c r="M27" s="84"/>
       <c r="N27" s="85"/>
-      <c r="O27" s="205"/>
+      <c r="O27" s="204"/>
       <c r="P27" s="84"/>
       <c r="Q27" s="85"/>
       <c r="R27" s="27"/>
@@ -19436,21 +20203,21 @@
       <c r="Z27" s="29"/>
     </row>
     <row r="28" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A28" s="198"/>
+      <c r="A28" s="221"/>
       <c r="B28" s="85"/>
-      <c r="C28" s="199"/>
+      <c r="C28" s="222"/>
       <c r="D28" s="85"/>
-      <c r="E28" s="199"/>
+      <c r="E28" s="222"/>
       <c r="F28" s="85"/>
-      <c r="G28" s="215"/>
+      <c r="G28" s="199"/>
       <c r="H28" s="84"/>
       <c r="I28" s="85"/>
-      <c r="J28" s="215"/>
+      <c r="J28" s="199"/>
       <c r="K28" s="85"/>
-      <c r="L28" s="205"/>
+      <c r="L28" s="204"/>
       <c r="M28" s="84"/>
       <c r="N28" s="85"/>
-      <c r="O28" s="205"/>
+      <c r="O28" s="204"/>
       <c r="P28" s="84"/>
       <c r="Q28" s="85"/>
       <c r="R28" s="27"/>
@@ -19464,21 +20231,21 @@
       <c r="Z28" s="29"/>
     </row>
     <row r="29" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A29" s="198"/>
+      <c r="A29" s="221"/>
       <c r="B29" s="85"/>
-      <c r="C29" s="199"/>
+      <c r="C29" s="222"/>
       <c r="D29" s="85"/>
-      <c r="E29" s="199"/>
+      <c r="E29" s="222"/>
       <c r="F29" s="85"/>
-      <c r="G29" s="215"/>
+      <c r="G29" s="199"/>
       <c r="H29" s="84"/>
       <c r="I29" s="85"/>
-      <c r="J29" s="215"/>
+      <c r="J29" s="199"/>
       <c r="K29" s="85"/>
-      <c r="L29" s="205"/>
+      <c r="L29" s="204"/>
       <c r="M29" s="84"/>
       <c r="N29" s="85"/>
-      <c r="O29" s="205"/>
+      <c r="O29" s="204"/>
       <c r="P29" s="84"/>
       <c r="Q29" s="85"/>
       <c r="R29" s="27"/>
@@ -19492,21 +20259,21 @@
       <c r="Z29" s="29"/>
     </row>
     <row r="30" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A30" s="198"/>
+      <c r="A30" s="221"/>
       <c r="B30" s="85"/>
-      <c r="C30" s="199"/>
+      <c r="C30" s="222"/>
       <c r="D30" s="85"/>
-      <c r="E30" s="199"/>
+      <c r="E30" s="222"/>
       <c r="F30" s="85"/>
-      <c r="G30" s="215"/>
+      <c r="G30" s="199"/>
       <c r="H30" s="84"/>
       <c r="I30" s="85"/>
-      <c r="J30" s="215"/>
+      <c r="J30" s="199"/>
       <c r="K30" s="85"/>
-      <c r="L30" s="205"/>
+      <c r="L30" s="204"/>
       <c r="M30" s="84"/>
       <c r="N30" s="85"/>
-      <c r="O30" s="205"/>
+      <c r="O30" s="204"/>
       <c r="P30" s="84"/>
       <c r="Q30" s="85"/>
       <c r="R30" s="27"/>
@@ -19520,23 +20287,23 @@
       <c r="Z30" s="29"/>
     </row>
     <row r="31" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A31" s="200"/>
-      <c r="B31" s="201"/>
-      <c r="C31" s="202"/>
-      <c r="D31" s="201"/>
-      <c r="E31" s="202"/>
-      <c r="F31" s="201"/>
-      <c r="G31" s="227"/>
-      <c r="H31" s="207"/>
-      <c r="I31" s="201"/>
-      <c r="J31" s="227"/>
-      <c r="K31" s="201"/>
-      <c r="L31" s="206"/>
-      <c r="M31" s="207"/>
-      <c r="N31" s="201"/>
-      <c r="O31" s="206"/>
-      <c r="P31" s="207"/>
-      <c r="Q31" s="201"/>
+      <c r="A31" s="227"/>
+      <c r="B31" s="203"/>
+      <c r="C31" s="228"/>
+      <c r="D31" s="203"/>
+      <c r="E31" s="228"/>
+      <c r="F31" s="203"/>
+      <c r="G31" s="201"/>
+      <c r="H31" s="202"/>
+      <c r="I31" s="203"/>
+      <c r="J31" s="201"/>
+      <c r="K31" s="203"/>
+      <c r="L31" s="205"/>
+      <c r="M31" s="202"/>
+      <c r="N31" s="203"/>
+      <c r="O31" s="205"/>
+      <c r="P31" s="202"/>
+      <c r="Q31" s="203"/>
       <c r="R31" s="30"/>
       <c r="S31" s="30"/>
       <c r="T31" s="31"/>
@@ -20534,62 +21301,62 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="136">
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="J18:K18"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="J19:K19"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="G23:I23"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="J30:K30"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="J29:K29"/>
-    <mergeCell ref="L26:N26"/>
-    <mergeCell ref="L27:N27"/>
-    <mergeCell ref="L28:N28"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="L18:N18"/>
-    <mergeCell ref="L19:N19"/>
-    <mergeCell ref="L21:N21"/>
-    <mergeCell ref="L22:N22"/>
-    <mergeCell ref="L23:N23"/>
-    <mergeCell ref="L24:N24"/>
-    <mergeCell ref="L25:N25"/>
-    <mergeCell ref="K2:N4"/>
-    <mergeCell ref="O2:P4"/>
-    <mergeCell ref="Q2:R4"/>
-    <mergeCell ref="S2:T4"/>
-    <mergeCell ref="A1:F4"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="O1:P1"/>
-    <mergeCell ref="Q1:R1"/>
-    <mergeCell ref="S1:T1"/>
-    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="E30:F30"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="E31:F31"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="E26:F26"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="E29:F29"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="E27:F27"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="E28:F28"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="O27:Q27"/>
+    <mergeCell ref="O28:Q28"/>
+    <mergeCell ref="O29:Q29"/>
+    <mergeCell ref="O30:Q30"/>
+    <mergeCell ref="O31:Q31"/>
+    <mergeCell ref="O19:Q19"/>
+    <mergeCell ref="O21:Q21"/>
+    <mergeCell ref="O22:Q22"/>
+    <mergeCell ref="O23:Q23"/>
+    <mergeCell ref="O24:Q24"/>
+    <mergeCell ref="O25:Q25"/>
+    <mergeCell ref="O26:Q26"/>
     <mergeCell ref="A5:F5"/>
     <mergeCell ref="G5:T5"/>
     <mergeCell ref="A6:F6"/>
@@ -20614,64 +21381,64 @@
     <mergeCell ref="C15:D15"/>
     <mergeCell ref="E15:F15"/>
     <mergeCell ref="A16:B16"/>
-    <mergeCell ref="O27:Q27"/>
-    <mergeCell ref="O28:Q28"/>
-    <mergeCell ref="O29:Q29"/>
-    <mergeCell ref="O30:Q30"/>
-    <mergeCell ref="O31:Q31"/>
-    <mergeCell ref="O19:Q19"/>
-    <mergeCell ref="O21:Q21"/>
-    <mergeCell ref="O22:Q22"/>
-    <mergeCell ref="O23:Q23"/>
-    <mergeCell ref="O24:Q24"/>
-    <mergeCell ref="O25:Q25"/>
-    <mergeCell ref="O26:Q26"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="E30:F30"/>
-    <mergeCell ref="A31:B31"/>
-    <mergeCell ref="C31:D31"/>
-    <mergeCell ref="E31:F31"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="E26:F26"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="E24:F24"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="E29:F29"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="E27:F27"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="E28:F28"/>
-    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="K2:N4"/>
+    <mergeCell ref="O2:P4"/>
+    <mergeCell ref="Q2:R4"/>
+    <mergeCell ref="S2:T4"/>
+    <mergeCell ref="A1:F4"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="S1:T1"/>
+    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="L26:N26"/>
+    <mergeCell ref="L27:N27"/>
+    <mergeCell ref="L28:N28"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="L18:N18"/>
+    <mergeCell ref="L19:N19"/>
+    <mergeCell ref="L21:N21"/>
+    <mergeCell ref="L22:N22"/>
+    <mergeCell ref="L23:N23"/>
+    <mergeCell ref="L24:N24"/>
+    <mergeCell ref="L25:N25"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="J30:K30"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="J29:K29"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="J19:K19"/>
   </mergeCells>
-  <phoneticPr fontId="8"/>
+  <phoneticPr fontId="9"/>
   <hyperlinks>
     <hyperlink ref="L17" r:id="rId1" xr:uid="{9C856B3A-5628-4A84-AEB9-83C42CAD3F20}"/>
     <hyperlink ref="L22" r:id="rId2" xr:uid="{F7C32242-0888-4D6E-ACAC-351645776229}"/>
@@ -20696,72 +21463,72 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="18.75" customHeight="1">
-      <c r="A1" s="238" t="s">
+      <c r="A1" s="249" t="s">
         <v>123</v>
       </c>
-      <c r="B1" s="238"/>
-      <c r="C1" s="239" t="s">
+      <c r="B1" s="249"/>
+      <c r="C1" s="250" t="s">
         <v>124</v>
       </c>
-      <c r="D1" s="240"/>
-      <c r="E1" s="241"/>
-      <c r="F1" s="242" t="s">
+      <c r="D1" s="251"/>
+      <c r="E1" s="252"/>
+      <c r="F1" s="253" t="s">
         <v>84</v>
       </c>
-      <c r="G1" s="243"/>
-      <c r="H1" s="243"/>
-      <c r="I1" s="243"/>
-      <c r="J1" s="243"/>
-      <c r="K1" s="243"/>
-      <c r="L1" s="243"/>
-      <c r="M1" s="244"/>
+      <c r="G1" s="254"/>
+      <c r="H1" s="254"/>
+      <c r="I1" s="254"/>
+      <c r="J1" s="254"/>
+      <c r="K1" s="254"/>
+      <c r="L1" s="254"/>
+      <c r="M1" s="255"/>
       <c r="N1" s="51" t="s">
         <v>125</v>
       </c>
-      <c r="O1" s="242" t="s">
+      <c r="O1" s="253" t="s">
         <v>83</v>
       </c>
-      <c r="P1" s="244"/>
+      <c r="P1" s="255"/>
       <c r="Q1" s="51" t="s">
         <v>126</v>
       </c>
-      <c r="R1" s="242" t="s">
+      <c r="R1" s="253" t="s">
         <v>127</v>
       </c>
-      <c r="S1" s="244"/>
+      <c r="S1" s="255"/>
     </row>
     <row r="2" spans="1:19" ht="18.75" customHeight="1">
-      <c r="A2" s="238"/>
-      <c r="B2" s="238"/>
-      <c r="C2" s="239" t="s">
+      <c r="A2" s="249"/>
+      <c r="B2" s="249"/>
+      <c r="C2" s="250" t="s">
         <v>128</v>
       </c>
-      <c r="D2" s="240"/>
-      <c r="E2" s="241"/>
-      <c r="F2" s="242" t="s">
+      <c r="D2" s="251"/>
+      <c r="E2" s="252"/>
+      <c r="F2" s="253" t="s">
         <v>147</v>
       </c>
-      <c r="G2" s="243"/>
-      <c r="H2" s="243"/>
-      <c r="I2" s="243"/>
-      <c r="J2" s="243"/>
-      <c r="K2" s="243"/>
-      <c r="L2" s="243"/>
-      <c r="M2" s="244"/>
+      <c r="G2" s="254"/>
+      <c r="H2" s="254"/>
+      <c r="I2" s="254"/>
+      <c r="J2" s="254"/>
+      <c r="K2" s="254"/>
+      <c r="L2" s="254"/>
+      <c r="M2" s="255"/>
       <c r="N2" s="51" t="s">
         <v>129</v>
       </c>
-      <c r="O2" s="245">
+      <c r="O2" s="256">
         <v>45824</v>
       </c>
-      <c r="P2" s="246"/>
+      <c r="P2" s="257"/>
       <c r="Q2" s="53" t="s">
         <v>130</v>
       </c>
-      <c r="R2" s="247">
+      <c r="R2" s="258">
         <v>44771</v>
       </c>
-      <c r="S2" s="248"/>
+      <c r="S2" s="259"/>
     </row>
     <row r="3" spans="1:19" ht="11.25" customHeight="1">
       <c r="A3" s="54"/>
@@ -20791,33 +21558,33 @@
       <c r="B4" s="57" t="s">
         <v>132</v>
       </c>
-      <c r="C4" s="229" t="s">
+      <c r="C4" s="241" t="s">
         <v>133</v>
       </c>
-      <c r="D4" s="230"/>
-      <c r="E4" s="230"/>
-      <c r="F4" s="230"/>
-      <c r="G4" s="231"/>
-      <c r="H4" s="229" t="s">
+      <c r="D4" s="242"/>
+      <c r="E4" s="242"/>
+      <c r="F4" s="242"/>
+      <c r="G4" s="243"/>
+      <c r="H4" s="241" t="s">
         <v>134</v>
       </c>
-      <c r="I4" s="230"/>
-      <c r="J4" s="230"/>
-      <c r="K4" s="230"/>
-      <c r="L4" s="230"/>
-      <c r="M4" s="231"/>
-      <c r="N4" s="229" t="s">
+      <c r="I4" s="242"/>
+      <c r="J4" s="242"/>
+      <c r="K4" s="242"/>
+      <c r="L4" s="242"/>
+      <c r="M4" s="243"/>
+      <c r="N4" s="241" t="s">
         <v>135</v>
       </c>
-      <c r="O4" s="230"/>
-      <c r="P4" s="231"/>
+      <c r="O4" s="242"/>
+      <c r="P4" s="243"/>
       <c r="Q4" s="56" t="s">
         <v>136</v>
       </c>
-      <c r="R4" s="229" t="s">
+      <c r="R4" s="241" t="s">
         <v>137</v>
       </c>
-      <c r="S4" s="231"/>
+      <c r="S4" s="243"/>
     </row>
     <row r="5" spans="1:19" ht="50.1" customHeight="1">
       <c r="A5" s="58">
@@ -20826,31 +21593,31 @@
       <c r="B5" s="59" t="s">
         <v>148</v>
       </c>
-      <c r="C5" s="232" t="s">
+      <c r="C5" s="237" t="s">
         <v>150</v>
       </c>
-      <c r="D5" s="232"/>
-      <c r="E5" s="232"/>
-      <c r="F5" s="232"/>
-      <c r="G5" s="232"/>
-      <c r="H5" s="232" t="s">
+      <c r="D5" s="237"/>
+      <c r="E5" s="237"/>
+      <c r="F5" s="237"/>
+      <c r="G5" s="237"/>
+      <c r="H5" s="237" t="s">
         <v>149</v>
       </c>
-      <c r="I5" s="232"/>
-      <c r="J5" s="232"/>
-      <c r="K5" s="232"/>
-      <c r="L5" s="232"/>
-      <c r="M5" s="232"/>
-      <c r="N5" s="233" t="s">
+      <c r="I5" s="237"/>
+      <c r="J5" s="237"/>
+      <c r="K5" s="237"/>
+      <c r="L5" s="237"/>
+      <c r="M5" s="237"/>
+      <c r="N5" s="244" t="s">
         <v>151</v>
       </c>
-      <c r="O5" s="234"/>
-      <c r="P5" s="235"/>
+      <c r="O5" s="245"/>
+      <c r="P5" s="246"/>
       <c r="Q5" s="64">
         <v>45824</v>
       </c>
-      <c r="R5" s="236"/>
-      <c r="S5" s="237"/>
+      <c r="R5" s="247"/>
+      <c r="S5" s="248"/>
     </row>
     <row r="6" spans="1:19" ht="30" customHeight="1">
       <c r="A6" s="60">
@@ -20859,31 +21626,31 @@
       <c r="B6" s="59" t="s">
         <v>148</v>
       </c>
-      <c r="C6" s="232" t="s">
+      <c r="C6" s="237" t="s">
         <v>150</v>
       </c>
-      <c r="D6" s="232"/>
-      <c r="E6" s="232"/>
-      <c r="F6" s="232"/>
-      <c r="G6" s="232"/>
-      <c r="H6" s="232" t="s">
+      <c r="D6" s="237"/>
+      <c r="E6" s="237"/>
+      <c r="F6" s="237"/>
+      <c r="G6" s="237"/>
+      <c r="H6" s="237" t="s">
         <v>149</v>
       </c>
-      <c r="I6" s="232"/>
-      <c r="J6" s="232"/>
-      <c r="K6" s="232"/>
-      <c r="L6" s="232"/>
-      <c r="M6" s="232"/>
-      <c r="N6" s="254" t="s">
+      <c r="I6" s="237"/>
+      <c r="J6" s="237"/>
+      <c r="K6" s="237"/>
+      <c r="L6" s="237"/>
+      <c r="M6" s="237"/>
+      <c r="N6" s="238" t="s">
         <v>152</v>
       </c>
-      <c r="O6" s="255"/>
-      <c r="P6" s="256"/>
+      <c r="O6" s="239"/>
+      <c r="P6" s="240"/>
       <c r="Q6" s="64">
         <v>45824</v>
       </c>
-      <c r="R6" s="253"/>
-      <c r="S6" s="253"/>
+      <c r="R6" s="236"/>
+      <c r="S6" s="236"/>
     </row>
     <row r="7" spans="1:19" ht="30" customHeight="1">
       <c r="A7" s="60">
@@ -20892,1167 +21659,979 @@
       <c r="B7" s="63" t="s">
         <v>118</v>
       </c>
-      <c r="C7" s="232" t="s">
+      <c r="C7" s="237" t="s">
         <v>150</v>
       </c>
-      <c r="D7" s="232"/>
-      <c r="E7" s="232"/>
-      <c r="F7" s="232"/>
-      <c r="G7" s="232"/>
-      <c r="H7" s="232" t="s">
+      <c r="D7" s="237"/>
+      <c r="E7" s="237"/>
+      <c r="F7" s="237"/>
+      <c r="G7" s="237"/>
+      <c r="H7" s="237" t="s">
         <v>149</v>
       </c>
-      <c r="I7" s="232"/>
-      <c r="J7" s="232"/>
-      <c r="K7" s="232"/>
-      <c r="L7" s="232"/>
-      <c r="M7" s="232"/>
-      <c r="N7" s="250" t="s">
+      <c r="I7" s="237"/>
+      <c r="J7" s="237"/>
+      <c r="K7" s="237"/>
+      <c r="L7" s="237"/>
+      <c r="M7" s="237"/>
+      <c r="N7" s="233" t="s">
         <v>153</v>
       </c>
-      <c r="O7" s="251"/>
-      <c r="P7" s="252"/>
+      <c r="O7" s="234"/>
+      <c r="P7" s="235"/>
       <c r="Q7" s="64">
         <v>45824</v>
       </c>
-      <c r="R7" s="253"/>
-      <c r="S7" s="253"/>
+      <c r="R7" s="236"/>
+      <c r="S7" s="236"/>
     </row>
     <row r="8" spans="1:19" ht="30" customHeight="1">
       <c r="A8" s="60"/>
       <c r="B8" s="60"/>
-      <c r="C8" s="249"/>
-      <c r="D8" s="249"/>
-      <c r="E8" s="249"/>
-      <c r="F8" s="249"/>
-      <c r="G8" s="249"/>
-      <c r="H8" s="249"/>
-      <c r="I8" s="249"/>
-      <c r="J8" s="249"/>
-      <c r="K8" s="249"/>
-      <c r="L8" s="249"/>
-      <c r="M8" s="249"/>
-      <c r="N8" s="250"/>
-      <c r="O8" s="251"/>
-      <c r="P8" s="252"/>
+      <c r="C8" s="229"/>
+      <c r="D8" s="229"/>
+      <c r="E8" s="229"/>
+      <c r="F8" s="229"/>
+      <c r="G8" s="229"/>
+      <c r="H8" s="229"/>
+      <c r="I8" s="229"/>
+      <c r="J8" s="229"/>
+      <c r="K8" s="229"/>
+      <c r="L8" s="229"/>
+      <c r="M8" s="229"/>
+      <c r="N8" s="233"/>
+      <c r="O8" s="234"/>
+      <c r="P8" s="235"/>
       <c r="Q8" s="61"/>
-      <c r="R8" s="253"/>
-      <c r="S8" s="253"/>
+      <c r="R8" s="236"/>
+      <c r="S8" s="236"/>
     </row>
     <row r="9" spans="1:19" ht="30" customHeight="1">
       <c r="A9" s="60"/>
       <c r="B9" s="60"/>
-      <c r="C9" s="249"/>
-      <c r="D9" s="249"/>
-      <c r="E9" s="249"/>
-      <c r="F9" s="249"/>
-      <c r="G9" s="249"/>
-      <c r="H9" s="249"/>
-      <c r="I9" s="249"/>
-      <c r="J9" s="249"/>
-      <c r="K9" s="249"/>
-      <c r="L9" s="249"/>
-      <c r="M9" s="249"/>
-      <c r="N9" s="250"/>
-      <c r="O9" s="251"/>
-      <c r="P9" s="252"/>
+      <c r="C9" s="229"/>
+      <c r="D9" s="229"/>
+      <c r="E9" s="229"/>
+      <c r="F9" s="229"/>
+      <c r="G9" s="229"/>
+      <c r="H9" s="229"/>
+      <c r="I9" s="229"/>
+      <c r="J9" s="229"/>
+      <c r="K9" s="229"/>
+      <c r="L9" s="229"/>
+      <c r="M9" s="229"/>
+      <c r="N9" s="233"/>
+      <c r="O9" s="234"/>
+      <c r="P9" s="235"/>
       <c r="Q9" s="60"/>
-      <c r="R9" s="253"/>
-      <c r="S9" s="253"/>
+      <c r="R9" s="236"/>
+      <c r="S9" s="236"/>
     </row>
     <row r="10" spans="1:19" ht="30" customHeight="1">
       <c r="A10" s="60"/>
       <c r="B10" s="60"/>
-      <c r="C10" s="249"/>
-      <c r="D10" s="249"/>
-      <c r="E10" s="249"/>
-      <c r="F10" s="249"/>
-      <c r="G10" s="249"/>
-      <c r="H10" s="257"/>
-      <c r="I10" s="258"/>
-      <c r="J10" s="258"/>
-      <c r="K10" s="258"/>
-      <c r="L10" s="258"/>
-      <c r="M10" s="259"/>
-      <c r="N10" s="250"/>
-      <c r="O10" s="251"/>
-      <c r="P10" s="252"/>
+      <c r="C10" s="229"/>
+      <c r="D10" s="229"/>
+      <c r="E10" s="229"/>
+      <c r="F10" s="229"/>
+      <c r="G10" s="229"/>
+      <c r="H10" s="230"/>
+      <c r="I10" s="231"/>
+      <c r="J10" s="231"/>
+      <c r="K10" s="231"/>
+      <c r="L10" s="231"/>
+      <c r="M10" s="232"/>
+      <c r="N10" s="233"/>
+      <c r="O10" s="234"/>
+      <c r="P10" s="235"/>
       <c r="Q10" s="61"/>
-      <c r="R10" s="253"/>
-      <c r="S10" s="253"/>
+      <c r="R10" s="236"/>
+      <c r="S10" s="236"/>
     </row>
     <row r="11" spans="1:19" ht="30" customHeight="1">
       <c r="A11" s="60"/>
       <c r="B11" s="60"/>
-      <c r="C11" s="249"/>
-      <c r="D11" s="249"/>
-      <c r="E11" s="249"/>
-      <c r="F11" s="249"/>
-      <c r="G11" s="249"/>
-      <c r="H11" s="257"/>
-      <c r="I11" s="258"/>
-      <c r="J11" s="258"/>
-      <c r="K11" s="258"/>
-      <c r="L11" s="258"/>
-      <c r="M11" s="259"/>
-      <c r="N11" s="250"/>
-      <c r="O11" s="251"/>
-      <c r="P11" s="252"/>
+      <c r="C11" s="229"/>
+      <c r="D11" s="229"/>
+      <c r="E11" s="229"/>
+      <c r="F11" s="229"/>
+      <c r="G11" s="229"/>
+      <c r="H11" s="230"/>
+      <c r="I11" s="231"/>
+      <c r="J11" s="231"/>
+      <c r="K11" s="231"/>
+      <c r="L11" s="231"/>
+      <c r="M11" s="232"/>
+      <c r="N11" s="233"/>
+      <c r="O11" s="234"/>
+      <c r="P11" s="235"/>
       <c r="Q11" s="60"/>
-      <c r="R11" s="253"/>
-      <c r="S11" s="253"/>
+      <c r="R11" s="236"/>
+      <c r="S11" s="236"/>
     </row>
     <row r="12" spans="1:19" ht="30" customHeight="1">
       <c r="A12" s="60"/>
       <c r="B12" s="60"/>
-      <c r="C12" s="249"/>
-      <c r="D12" s="249"/>
-      <c r="E12" s="249"/>
-      <c r="F12" s="249"/>
-      <c r="G12" s="249"/>
-      <c r="H12" s="257"/>
-      <c r="I12" s="258"/>
-      <c r="J12" s="258"/>
-      <c r="K12" s="258"/>
-      <c r="L12" s="258"/>
-      <c r="M12" s="259"/>
-      <c r="N12" s="250"/>
-      <c r="O12" s="251"/>
-      <c r="P12" s="252"/>
+      <c r="C12" s="229"/>
+      <c r="D12" s="229"/>
+      <c r="E12" s="229"/>
+      <c r="F12" s="229"/>
+      <c r="G12" s="229"/>
+      <c r="H12" s="230"/>
+      <c r="I12" s="231"/>
+      <c r="J12" s="231"/>
+      <c r="K12" s="231"/>
+      <c r="L12" s="231"/>
+      <c r="M12" s="232"/>
+      <c r="N12" s="233"/>
+      <c r="O12" s="234"/>
+      <c r="P12" s="235"/>
       <c r="Q12" s="60"/>
-      <c r="R12" s="253"/>
-      <c r="S12" s="253"/>
+      <c r="R12" s="236"/>
+      <c r="S12" s="236"/>
     </row>
     <row r="13" spans="1:19" ht="30" customHeight="1">
       <c r="A13" s="60"/>
       <c r="B13" s="60"/>
-      <c r="C13" s="249"/>
-      <c r="D13" s="249"/>
-      <c r="E13" s="249"/>
-      <c r="F13" s="249"/>
-      <c r="G13" s="249"/>
-      <c r="H13" s="257"/>
-      <c r="I13" s="258"/>
-      <c r="J13" s="258"/>
-      <c r="K13" s="258"/>
-      <c r="L13" s="258"/>
-      <c r="M13" s="259"/>
-      <c r="N13" s="250"/>
-      <c r="O13" s="251"/>
-      <c r="P13" s="252"/>
+      <c r="C13" s="229"/>
+      <c r="D13" s="229"/>
+      <c r="E13" s="229"/>
+      <c r="F13" s="229"/>
+      <c r="G13" s="229"/>
+      <c r="H13" s="230"/>
+      <c r="I13" s="231"/>
+      <c r="J13" s="231"/>
+      <c r="K13" s="231"/>
+      <c r="L13" s="231"/>
+      <c r="M13" s="232"/>
+      <c r="N13" s="233"/>
+      <c r="O13" s="234"/>
+      <c r="P13" s="235"/>
       <c r="Q13" s="60"/>
-      <c r="R13" s="253"/>
-      <c r="S13" s="253"/>
+      <c r="R13" s="236"/>
+      <c r="S13" s="236"/>
     </row>
     <row r="14" spans="1:19" ht="30" customHeight="1">
       <c r="A14" s="60"/>
       <c r="B14" s="60"/>
-      <c r="C14" s="249"/>
-      <c r="D14" s="249"/>
-      <c r="E14" s="249"/>
-      <c r="F14" s="249"/>
-      <c r="G14" s="249"/>
-      <c r="H14" s="257"/>
-      <c r="I14" s="258"/>
-      <c r="J14" s="258"/>
-      <c r="K14" s="258"/>
-      <c r="L14" s="258"/>
-      <c r="M14" s="259"/>
-      <c r="N14" s="250"/>
-      <c r="O14" s="251"/>
-      <c r="P14" s="252"/>
+      <c r="C14" s="229"/>
+      <c r="D14" s="229"/>
+      <c r="E14" s="229"/>
+      <c r="F14" s="229"/>
+      <c r="G14" s="229"/>
+      <c r="H14" s="230"/>
+      <c r="I14" s="231"/>
+      <c r="J14" s="231"/>
+      <c r="K14" s="231"/>
+      <c r="L14" s="231"/>
+      <c r="M14" s="232"/>
+      <c r="N14" s="233"/>
+      <c r="O14" s="234"/>
+      <c r="P14" s="235"/>
       <c r="Q14" s="60"/>
-      <c r="R14" s="253"/>
-      <c r="S14" s="253"/>
+      <c r="R14" s="236"/>
+      <c r="S14" s="236"/>
     </row>
     <row r="15" spans="1:19" ht="30" customHeight="1">
       <c r="A15" s="60"/>
       <c r="B15" s="60"/>
-      <c r="C15" s="249"/>
-      <c r="D15" s="249"/>
-      <c r="E15" s="249"/>
-      <c r="F15" s="249"/>
-      <c r="G15" s="249"/>
-      <c r="H15" s="257"/>
-      <c r="I15" s="258"/>
-      <c r="J15" s="258"/>
-      <c r="K15" s="258"/>
-      <c r="L15" s="258"/>
-      <c r="M15" s="259"/>
-      <c r="N15" s="250"/>
-      <c r="O15" s="251"/>
-      <c r="P15" s="252"/>
+      <c r="C15" s="229"/>
+      <c r="D15" s="229"/>
+      <c r="E15" s="229"/>
+      <c r="F15" s="229"/>
+      <c r="G15" s="229"/>
+      <c r="H15" s="230"/>
+      <c r="I15" s="231"/>
+      <c r="J15" s="231"/>
+      <c r="K15" s="231"/>
+      <c r="L15" s="231"/>
+      <c r="M15" s="232"/>
+      <c r="N15" s="233"/>
+      <c r="O15" s="234"/>
+      <c r="P15" s="235"/>
       <c r="Q15" s="60"/>
-      <c r="R15" s="253"/>
-      <c r="S15" s="253"/>
+      <c r="R15" s="236"/>
+      <c r="S15" s="236"/>
     </row>
     <row r="16" spans="1:19" ht="30" customHeight="1">
       <c r="A16" s="60"/>
       <c r="B16" s="60"/>
-      <c r="C16" s="249"/>
-      <c r="D16" s="249"/>
-      <c r="E16" s="249"/>
-      <c r="F16" s="249"/>
-      <c r="G16" s="249"/>
-      <c r="H16" s="257"/>
-      <c r="I16" s="258"/>
-      <c r="J16" s="258"/>
-      <c r="K16" s="258"/>
-      <c r="L16" s="258"/>
-      <c r="M16" s="259"/>
-      <c r="N16" s="250"/>
-      <c r="O16" s="251"/>
-      <c r="P16" s="252"/>
+      <c r="C16" s="229"/>
+      <c r="D16" s="229"/>
+      <c r="E16" s="229"/>
+      <c r="F16" s="229"/>
+      <c r="G16" s="229"/>
+      <c r="H16" s="230"/>
+      <c r="I16" s="231"/>
+      <c r="J16" s="231"/>
+      <c r="K16" s="231"/>
+      <c r="L16" s="231"/>
+      <c r="M16" s="232"/>
+      <c r="N16" s="233"/>
+      <c r="O16" s="234"/>
+      <c r="P16" s="235"/>
       <c r="Q16" s="60"/>
-      <c r="R16" s="253"/>
-      <c r="S16" s="253"/>
+      <c r="R16" s="236"/>
+      <c r="S16" s="236"/>
     </row>
     <row r="17" spans="1:19" ht="30" customHeight="1">
       <c r="A17" s="60"/>
       <c r="B17" s="60"/>
-      <c r="C17" s="249"/>
-      <c r="D17" s="249"/>
-      <c r="E17" s="249"/>
-      <c r="F17" s="249"/>
-      <c r="G17" s="249"/>
-      <c r="H17" s="257"/>
-      <c r="I17" s="258"/>
-      <c r="J17" s="258"/>
-      <c r="K17" s="258"/>
-      <c r="L17" s="258"/>
-      <c r="M17" s="259"/>
-      <c r="N17" s="250"/>
-      <c r="O17" s="251"/>
-      <c r="P17" s="252"/>
+      <c r="C17" s="229"/>
+      <c r="D17" s="229"/>
+      <c r="E17" s="229"/>
+      <c r="F17" s="229"/>
+      <c r="G17" s="229"/>
+      <c r="H17" s="230"/>
+      <c r="I17" s="231"/>
+      <c r="J17" s="231"/>
+      <c r="K17" s="231"/>
+      <c r="L17" s="231"/>
+      <c r="M17" s="232"/>
+      <c r="N17" s="233"/>
+      <c r="O17" s="234"/>
+      <c r="P17" s="235"/>
       <c r="Q17" s="60"/>
-      <c r="R17" s="253"/>
-      <c r="S17" s="253"/>
+      <c r="R17" s="236"/>
+      <c r="S17" s="236"/>
     </row>
     <row r="18" spans="1:19" ht="30" customHeight="1">
       <c r="A18" s="60"/>
       <c r="B18" s="60"/>
-      <c r="C18" s="249"/>
-      <c r="D18" s="249"/>
-      <c r="E18" s="249"/>
-      <c r="F18" s="249"/>
-      <c r="G18" s="249"/>
-      <c r="H18" s="257"/>
-      <c r="I18" s="258"/>
-      <c r="J18" s="258"/>
-      <c r="K18" s="258"/>
-      <c r="L18" s="258"/>
-      <c r="M18" s="259"/>
-      <c r="N18" s="250"/>
-      <c r="O18" s="251"/>
-      <c r="P18" s="252"/>
+      <c r="C18" s="229"/>
+      <c r="D18" s="229"/>
+      <c r="E18" s="229"/>
+      <c r="F18" s="229"/>
+      <c r="G18" s="229"/>
+      <c r="H18" s="230"/>
+      <c r="I18" s="231"/>
+      <c r="J18" s="231"/>
+      <c r="K18" s="231"/>
+      <c r="L18" s="231"/>
+      <c r="M18" s="232"/>
+      <c r="N18" s="233"/>
+      <c r="O18" s="234"/>
+      <c r="P18" s="235"/>
       <c r="Q18" s="60"/>
-      <c r="R18" s="253"/>
-      <c r="S18" s="253"/>
+      <c r="R18" s="236"/>
+      <c r="S18" s="236"/>
     </row>
     <row r="19" spans="1:19" ht="30" customHeight="1">
       <c r="A19" s="60"/>
       <c r="B19" s="60"/>
-      <c r="C19" s="249"/>
-      <c r="D19" s="249"/>
-      <c r="E19" s="249"/>
-      <c r="F19" s="249"/>
-      <c r="G19" s="249"/>
-      <c r="H19" s="257"/>
-      <c r="I19" s="258"/>
-      <c r="J19" s="258"/>
-      <c r="K19" s="258"/>
-      <c r="L19" s="258"/>
-      <c r="M19" s="259"/>
-      <c r="N19" s="250"/>
-      <c r="O19" s="251"/>
-      <c r="P19" s="252"/>
+      <c r="C19" s="229"/>
+      <c r="D19" s="229"/>
+      <c r="E19" s="229"/>
+      <c r="F19" s="229"/>
+      <c r="G19" s="229"/>
+      <c r="H19" s="230"/>
+      <c r="I19" s="231"/>
+      <c r="J19" s="231"/>
+      <c r="K19" s="231"/>
+      <c r="L19" s="231"/>
+      <c r="M19" s="232"/>
+      <c r="N19" s="233"/>
+      <c r="O19" s="234"/>
+      <c r="P19" s="235"/>
       <c r="Q19" s="60"/>
-      <c r="R19" s="253"/>
-      <c r="S19" s="253"/>
+      <c r="R19" s="236"/>
+      <c r="S19" s="236"/>
     </row>
     <row r="20" spans="1:19" ht="30" customHeight="1">
       <c r="A20" s="60"/>
       <c r="B20" s="60"/>
-      <c r="C20" s="249"/>
-      <c r="D20" s="249"/>
-      <c r="E20" s="249"/>
-      <c r="F20" s="249"/>
-      <c r="G20" s="249"/>
-      <c r="H20" s="257"/>
-      <c r="I20" s="258"/>
-      <c r="J20" s="258"/>
-      <c r="K20" s="258"/>
-      <c r="L20" s="258"/>
-      <c r="M20" s="259"/>
-      <c r="N20" s="250"/>
-      <c r="O20" s="251"/>
-      <c r="P20" s="252"/>
+      <c r="C20" s="229"/>
+      <c r="D20" s="229"/>
+      <c r="E20" s="229"/>
+      <c r="F20" s="229"/>
+      <c r="G20" s="229"/>
+      <c r="H20" s="230"/>
+      <c r="I20" s="231"/>
+      <c r="J20" s="231"/>
+      <c r="K20" s="231"/>
+      <c r="L20" s="231"/>
+      <c r="M20" s="232"/>
+      <c r="N20" s="233"/>
+      <c r="O20" s="234"/>
+      <c r="P20" s="235"/>
       <c r="Q20" s="60"/>
-      <c r="R20" s="253"/>
-      <c r="S20" s="253"/>
+      <c r="R20" s="236"/>
+      <c r="S20" s="236"/>
     </row>
     <row r="21" spans="1:19" ht="30" customHeight="1">
       <c r="A21" s="60"/>
       <c r="B21" s="60"/>
-      <c r="C21" s="249"/>
-      <c r="D21" s="249"/>
-      <c r="E21" s="249"/>
-      <c r="F21" s="249"/>
-      <c r="G21" s="249"/>
-      <c r="H21" s="257"/>
-      <c r="I21" s="258"/>
-      <c r="J21" s="258"/>
-      <c r="K21" s="258"/>
-      <c r="L21" s="258"/>
-      <c r="M21" s="259"/>
-      <c r="N21" s="250"/>
-      <c r="O21" s="251"/>
-      <c r="P21" s="252"/>
+      <c r="C21" s="229"/>
+      <c r="D21" s="229"/>
+      <c r="E21" s="229"/>
+      <c r="F21" s="229"/>
+      <c r="G21" s="229"/>
+      <c r="H21" s="230"/>
+      <c r="I21" s="231"/>
+      <c r="J21" s="231"/>
+      <c r="K21" s="231"/>
+      <c r="L21" s="231"/>
+      <c r="M21" s="232"/>
+      <c r="N21" s="233"/>
+      <c r="O21" s="234"/>
+      <c r="P21" s="235"/>
       <c r="Q21" s="60"/>
-      <c r="R21" s="253"/>
-      <c r="S21" s="253"/>
+      <c r="R21" s="236"/>
+      <c r="S21" s="236"/>
     </row>
     <row r="22" spans="1:19" ht="30" customHeight="1">
       <c r="A22" s="60"/>
       <c r="B22" s="60"/>
-      <c r="C22" s="249"/>
-      <c r="D22" s="249"/>
-      <c r="E22" s="249"/>
-      <c r="F22" s="249"/>
-      <c r="G22" s="249"/>
-      <c r="H22" s="257"/>
-      <c r="I22" s="258"/>
-      <c r="J22" s="258"/>
-      <c r="K22" s="258"/>
-      <c r="L22" s="258"/>
-      <c r="M22" s="259"/>
-      <c r="N22" s="250"/>
-      <c r="O22" s="251"/>
-      <c r="P22" s="252"/>
+      <c r="C22" s="229"/>
+      <c r="D22" s="229"/>
+      <c r="E22" s="229"/>
+      <c r="F22" s="229"/>
+      <c r="G22" s="229"/>
+      <c r="H22" s="230"/>
+      <c r="I22" s="231"/>
+      <c r="J22" s="231"/>
+      <c r="K22" s="231"/>
+      <c r="L22" s="231"/>
+      <c r="M22" s="232"/>
+      <c r="N22" s="233"/>
+      <c r="O22" s="234"/>
+      <c r="P22" s="235"/>
       <c r="Q22" s="60"/>
-      <c r="R22" s="253"/>
-      <c r="S22" s="253"/>
+      <c r="R22" s="236"/>
+      <c r="S22" s="236"/>
     </row>
     <row r="23" spans="1:19" ht="30" customHeight="1">
       <c r="A23" s="60"/>
       <c r="B23" s="60"/>
-      <c r="C23" s="249"/>
-      <c r="D23" s="249"/>
-      <c r="E23" s="249"/>
-      <c r="F23" s="249"/>
-      <c r="G23" s="249"/>
-      <c r="H23" s="257"/>
-      <c r="I23" s="258"/>
-      <c r="J23" s="258"/>
-      <c r="K23" s="258"/>
-      <c r="L23" s="258"/>
-      <c r="M23" s="259"/>
-      <c r="N23" s="250"/>
-      <c r="O23" s="251"/>
-      <c r="P23" s="252"/>
+      <c r="C23" s="229"/>
+      <c r="D23" s="229"/>
+      <c r="E23" s="229"/>
+      <c r="F23" s="229"/>
+      <c r="G23" s="229"/>
+      <c r="H23" s="230"/>
+      <c r="I23" s="231"/>
+      <c r="J23" s="231"/>
+      <c r="K23" s="231"/>
+      <c r="L23" s="231"/>
+      <c r="M23" s="232"/>
+      <c r="N23" s="233"/>
+      <c r="O23" s="234"/>
+      <c r="P23" s="235"/>
       <c r="Q23" s="60"/>
-      <c r="R23" s="253"/>
-      <c r="S23" s="253"/>
+      <c r="R23" s="236"/>
+      <c r="S23" s="236"/>
     </row>
     <row r="24" spans="1:19" ht="30" customHeight="1">
       <c r="A24" s="60"/>
       <c r="B24" s="60"/>
-      <c r="C24" s="249"/>
-      <c r="D24" s="249"/>
-      <c r="E24" s="249"/>
-      <c r="F24" s="249"/>
-      <c r="G24" s="249"/>
-      <c r="H24" s="257"/>
-      <c r="I24" s="258"/>
-      <c r="J24" s="258"/>
-      <c r="K24" s="258"/>
-      <c r="L24" s="258"/>
-      <c r="M24" s="259"/>
-      <c r="N24" s="250"/>
-      <c r="O24" s="251"/>
-      <c r="P24" s="252"/>
+      <c r="C24" s="229"/>
+      <c r="D24" s="229"/>
+      <c r="E24" s="229"/>
+      <c r="F24" s="229"/>
+      <c r="G24" s="229"/>
+      <c r="H24" s="230"/>
+      <c r="I24" s="231"/>
+      <c r="J24" s="231"/>
+      <c r="K24" s="231"/>
+      <c r="L24" s="231"/>
+      <c r="M24" s="232"/>
+      <c r="N24" s="233"/>
+      <c r="O24" s="234"/>
+      <c r="P24" s="235"/>
       <c r="Q24" s="60"/>
-      <c r="R24" s="253"/>
-      <c r="S24" s="253"/>
+      <c r="R24" s="236"/>
+      <c r="S24" s="236"/>
     </row>
     <row r="25" spans="1:19" ht="30" customHeight="1">
       <c r="A25" s="60"/>
       <c r="B25" s="60"/>
-      <c r="C25" s="249"/>
-      <c r="D25" s="249"/>
-      <c r="E25" s="249"/>
-      <c r="F25" s="249"/>
-      <c r="G25" s="249"/>
-      <c r="H25" s="257"/>
-      <c r="I25" s="258"/>
-      <c r="J25" s="258"/>
-      <c r="K25" s="258"/>
-      <c r="L25" s="258"/>
-      <c r="M25" s="259"/>
-      <c r="N25" s="250"/>
-      <c r="O25" s="251"/>
-      <c r="P25" s="252"/>
+      <c r="C25" s="229"/>
+      <c r="D25" s="229"/>
+      <c r="E25" s="229"/>
+      <c r="F25" s="229"/>
+      <c r="G25" s="229"/>
+      <c r="H25" s="230"/>
+      <c r="I25" s="231"/>
+      <c r="J25" s="231"/>
+      <c r="K25" s="231"/>
+      <c r="L25" s="231"/>
+      <c r="M25" s="232"/>
+      <c r="N25" s="233"/>
+      <c r="O25" s="234"/>
+      <c r="P25" s="235"/>
       <c r="Q25" s="60"/>
-      <c r="R25" s="253"/>
-      <c r="S25" s="253"/>
+      <c r="R25" s="236"/>
+      <c r="S25" s="236"/>
     </row>
     <row r="26" spans="1:19" ht="30" customHeight="1">
       <c r="A26" s="60"/>
       <c r="B26" s="60"/>
-      <c r="C26" s="249"/>
-      <c r="D26" s="249"/>
-      <c r="E26" s="249"/>
-      <c r="F26" s="249"/>
-      <c r="G26" s="249"/>
-      <c r="H26" s="257"/>
-      <c r="I26" s="258"/>
-      <c r="J26" s="258"/>
-      <c r="K26" s="258"/>
-      <c r="L26" s="258"/>
-      <c r="M26" s="259"/>
-      <c r="N26" s="250"/>
-      <c r="O26" s="251"/>
-      <c r="P26" s="252"/>
+      <c r="C26" s="229"/>
+      <c r="D26" s="229"/>
+      <c r="E26" s="229"/>
+      <c r="F26" s="229"/>
+      <c r="G26" s="229"/>
+      <c r="H26" s="230"/>
+      <c r="I26" s="231"/>
+      <c r="J26" s="231"/>
+      <c r="K26" s="231"/>
+      <c r="L26" s="231"/>
+      <c r="M26" s="232"/>
+      <c r="N26" s="233"/>
+      <c r="O26" s="234"/>
+      <c r="P26" s="235"/>
       <c r="Q26" s="60"/>
-      <c r="R26" s="253"/>
-      <c r="S26" s="253"/>
+      <c r="R26" s="236"/>
+      <c r="S26" s="236"/>
     </row>
     <row r="27" spans="1:19" ht="30" customHeight="1">
       <c r="A27" s="60"/>
       <c r="B27" s="60"/>
-      <c r="C27" s="249"/>
-      <c r="D27" s="249"/>
-      <c r="E27" s="249"/>
-      <c r="F27" s="249"/>
-      <c r="G27" s="249"/>
-      <c r="H27" s="257"/>
-      <c r="I27" s="258"/>
-      <c r="J27" s="258"/>
-      <c r="K27" s="258"/>
-      <c r="L27" s="258"/>
-      <c r="M27" s="259"/>
-      <c r="N27" s="250"/>
-      <c r="O27" s="251"/>
-      <c r="P27" s="252"/>
+      <c r="C27" s="229"/>
+      <c r="D27" s="229"/>
+      <c r="E27" s="229"/>
+      <c r="F27" s="229"/>
+      <c r="G27" s="229"/>
+      <c r="H27" s="230"/>
+      <c r="I27" s="231"/>
+      <c r="J27" s="231"/>
+      <c r="K27" s="231"/>
+      <c r="L27" s="231"/>
+      <c r="M27" s="232"/>
+      <c r="N27" s="233"/>
+      <c r="O27" s="234"/>
+      <c r="P27" s="235"/>
       <c r="Q27" s="60"/>
-      <c r="R27" s="253"/>
-      <c r="S27" s="253"/>
+      <c r="R27" s="236"/>
+      <c r="S27" s="236"/>
     </row>
     <row r="28" spans="1:19" ht="30" customHeight="1">
       <c r="A28" s="60"/>
       <c r="B28" s="60"/>
-      <c r="C28" s="249"/>
-      <c r="D28" s="249"/>
-      <c r="E28" s="249"/>
-      <c r="F28" s="249"/>
-      <c r="G28" s="249"/>
-      <c r="H28" s="257"/>
-      <c r="I28" s="258"/>
-      <c r="J28" s="258"/>
-      <c r="K28" s="258"/>
-      <c r="L28" s="258"/>
-      <c r="M28" s="259"/>
-      <c r="N28" s="250"/>
-      <c r="O28" s="251"/>
-      <c r="P28" s="252"/>
+      <c r="C28" s="229"/>
+      <c r="D28" s="229"/>
+      <c r="E28" s="229"/>
+      <c r="F28" s="229"/>
+      <c r="G28" s="229"/>
+      <c r="H28" s="230"/>
+      <c r="I28" s="231"/>
+      <c r="J28" s="231"/>
+      <c r="K28" s="231"/>
+      <c r="L28" s="231"/>
+      <c r="M28" s="232"/>
+      <c r="N28" s="233"/>
+      <c r="O28" s="234"/>
+      <c r="P28" s="235"/>
       <c r="Q28" s="60"/>
-      <c r="R28" s="253"/>
-      <c r="S28" s="253"/>
+      <c r="R28" s="236"/>
+      <c r="S28" s="236"/>
     </row>
     <row r="29" spans="1:19" ht="30" customHeight="1">
       <c r="A29" s="60"/>
       <c r="B29" s="60"/>
-      <c r="C29" s="249"/>
-      <c r="D29" s="249"/>
-      <c r="E29" s="249"/>
-      <c r="F29" s="249"/>
-      <c r="G29" s="249"/>
-      <c r="H29" s="257"/>
-      <c r="I29" s="258"/>
-      <c r="J29" s="258"/>
-      <c r="K29" s="258"/>
-      <c r="L29" s="258"/>
-      <c r="M29" s="259"/>
-      <c r="N29" s="250"/>
-      <c r="O29" s="251"/>
-      <c r="P29" s="252"/>
+      <c r="C29" s="229"/>
+      <c r="D29" s="229"/>
+      <c r="E29" s="229"/>
+      <c r="F29" s="229"/>
+      <c r="G29" s="229"/>
+      <c r="H29" s="230"/>
+      <c r="I29" s="231"/>
+      <c r="J29" s="231"/>
+      <c r="K29" s="231"/>
+      <c r="L29" s="231"/>
+      <c r="M29" s="232"/>
+      <c r="N29" s="233"/>
+      <c r="O29" s="234"/>
+      <c r="P29" s="235"/>
       <c r="Q29" s="60"/>
-      <c r="R29" s="253"/>
-      <c r="S29" s="253"/>
+      <c r="R29" s="236"/>
+      <c r="S29" s="236"/>
     </row>
     <row r="30" spans="1:19" ht="30" customHeight="1">
       <c r="A30" s="60"/>
       <c r="B30" s="60"/>
-      <c r="C30" s="249"/>
-      <c r="D30" s="249"/>
-      <c r="E30" s="249"/>
-      <c r="F30" s="249"/>
-      <c r="G30" s="249"/>
-      <c r="H30" s="257"/>
-      <c r="I30" s="258"/>
-      <c r="J30" s="258"/>
-      <c r="K30" s="258"/>
-      <c r="L30" s="258"/>
-      <c r="M30" s="259"/>
-      <c r="N30" s="250"/>
-      <c r="O30" s="251"/>
-      <c r="P30" s="252"/>
+      <c r="C30" s="229"/>
+      <c r="D30" s="229"/>
+      <c r="E30" s="229"/>
+      <c r="F30" s="229"/>
+      <c r="G30" s="229"/>
+      <c r="H30" s="230"/>
+      <c r="I30" s="231"/>
+      <c r="J30" s="231"/>
+      <c r="K30" s="231"/>
+      <c r="L30" s="231"/>
+      <c r="M30" s="232"/>
+      <c r="N30" s="233"/>
+      <c r="O30" s="234"/>
+      <c r="P30" s="235"/>
       <c r="Q30" s="60"/>
-      <c r="R30" s="253"/>
-      <c r="S30" s="253"/>
+      <c r="R30" s="236"/>
+      <c r="S30" s="236"/>
     </row>
     <row r="31" spans="1:19" ht="30" customHeight="1">
       <c r="A31" s="60"/>
       <c r="B31" s="60"/>
-      <c r="C31" s="249"/>
-      <c r="D31" s="249"/>
-      <c r="E31" s="249"/>
-      <c r="F31" s="249"/>
-      <c r="G31" s="249"/>
-      <c r="H31" s="257"/>
-      <c r="I31" s="258"/>
-      <c r="J31" s="258"/>
-      <c r="K31" s="258"/>
-      <c r="L31" s="258"/>
-      <c r="M31" s="259"/>
-      <c r="N31" s="250"/>
-      <c r="O31" s="251"/>
-      <c r="P31" s="252"/>
+      <c r="C31" s="229"/>
+      <c r="D31" s="229"/>
+      <c r="E31" s="229"/>
+      <c r="F31" s="229"/>
+      <c r="G31" s="229"/>
+      <c r="H31" s="230"/>
+      <c r="I31" s="231"/>
+      <c r="J31" s="231"/>
+      <c r="K31" s="231"/>
+      <c r="L31" s="231"/>
+      <c r="M31" s="232"/>
+      <c r="N31" s="233"/>
+      <c r="O31" s="234"/>
+      <c r="P31" s="235"/>
       <c r="Q31" s="60"/>
-      <c r="R31" s="253"/>
-      <c r="S31" s="253"/>
+      <c r="R31" s="236"/>
+      <c r="S31" s="236"/>
     </row>
     <row r="32" spans="1:19" ht="30" customHeight="1">
       <c r="A32" s="60"/>
       <c r="B32" s="60"/>
-      <c r="C32" s="249"/>
-      <c r="D32" s="249"/>
-      <c r="E32" s="249"/>
-      <c r="F32" s="249"/>
-      <c r="G32" s="249"/>
-      <c r="H32" s="257"/>
-      <c r="I32" s="258"/>
-      <c r="J32" s="258"/>
-      <c r="K32" s="258"/>
-      <c r="L32" s="258"/>
-      <c r="M32" s="259"/>
-      <c r="N32" s="250"/>
-      <c r="O32" s="251"/>
-      <c r="P32" s="252"/>
+      <c r="C32" s="229"/>
+      <c r="D32" s="229"/>
+      <c r="E32" s="229"/>
+      <c r="F32" s="229"/>
+      <c r="G32" s="229"/>
+      <c r="H32" s="230"/>
+      <c r="I32" s="231"/>
+      <c r="J32" s="231"/>
+      <c r="K32" s="231"/>
+      <c r="L32" s="231"/>
+      <c r="M32" s="232"/>
+      <c r="N32" s="233"/>
+      <c r="O32" s="234"/>
+      <c r="P32" s="235"/>
       <c r="Q32" s="60"/>
-      <c r="R32" s="253"/>
-      <c r="S32" s="253"/>
+      <c r="R32" s="236"/>
+      <c r="S32" s="236"/>
     </row>
     <row r="33" spans="1:19" ht="30" customHeight="1">
       <c r="A33" s="60"/>
       <c r="B33" s="60"/>
-      <c r="C33" s="249"/>
-      <c r="D33" s="249"/>
-      <c r="E33" s="249"/>
-      <c r="F33" s="249"/>
-      <c r="G33" s="249"/>
-      <c r="H33" s="257"/>
-      <c r="I33" s="258"/>
-      <c r="J33" s="258"/>
-      <c r="K33" s="258"/>
-      <c r="L33" s="258"/>
-      <c r="M33" s="259"/>
-      <c r="N33" s="250"/>
-      <c r="O33" s="251"/>
-      <c r="P33" s="252"/>
+      <c r="C33" s="229"/>
+      <c r="D33" s="229"/>
+      <c r="E33" s="229"/>
+      <c r="F33" s="229"/>
+      <c r="G33" s="229"/>
+      <c r="H33" s="230"/>
+      <c r="I33" s="231"/>
+      <c r="J33" s="231"/>
+      <c r="K33" s="231"/>
+      <c r="L33" s="231"/>
+      <c r="M33" s="232"/>
+      <c r="N33" s="233"/>
+      <c r="O33" s="234"/>
+      <c r="P33" s="235"/>
       <c r="Q33" s="60"/>
-      <c r="R33" s="253"/>
-      <c r="S33" s="253"/>
+      <c r="R33" s="236"/>
+      <c r="S33" s="236"/>
     </row>
     <row r="34" spans="1:19" ht="30" customHeight="1">
       <c r="A34" s="60"/>
       <c r="B34" s="60"/>
-      <c r="C34" s="249"/>
-      <c r="D34" s="249"/>
-      <c r="E34" s="249"/>
-      <c r="F34" s="249"/>
-      <c r="G34" s="249"/>
-      <c r="H34" s="257"/>
-      <c r="I34" s="258"/>
-      <c r="J34" s="258"/>
-      <c r="K34" s="258"/>
-      <c r="L34" s="258"/>
-      <c r="M34" s="259"/>
-      <c r="N34" s="250"/>
-      <c r="O34" s="251"/>
-      <c r="P34" s="252"/>
+      <c r="C34" s="229"/>
+      <c r="D34" s="229"/>
+      <c r="E34" s="229"/>
+      <c r="F34" s="229"/>
+      <c r="G34" s="229"/>
+      <c r="H34" s="230"/>
+      <c r="I34" s="231"/>
+      <c r="J34" s="231"/>
+      <c r="K34" s="231"/>
+      <c r="L34" s="231"/>
+      <c r="M34" s="232"/>
+      <c r="N34" s="233"/>
+      <c r="O34" s="234"/>
+      <c r="P34" s="235"/>
       <c r="Q34" s="60"/>
-      <c r="R34" s="253"/>
-      <c r="S34" s="253"/>
+      <c r="R34" s="236"/>
+      <c r="S34" s="236"/>
     </row>
     <row r="35" spans="1:19" ht="30" customHeight="1">
       <c r="A35" s="60"/>
       <c r="B35" s="60"/>
-      <c r="C35" s="249"/>
-      <c r="D35" s="249"/>
-      <c r="E35" s="249"/>
-      <c r="F35" s="249"/>
-      <c r="G35" s="249"/>
-      <c r="H35" s="257"/>
-      <c r="I35" s="258"/>
-      <c r="J35" s="258"/>
-      <c r="K35" s="258"/>
-      <c r="L35" s="258"/>
-      <c r="M35" s="259"/>
-      <c r="N35" s="250"/>
-      <c r="O35" s="251"/>
-      <c r="P35" s="252"/>
+      <c r="C35" s="229"/>
+      <c r="D35" s="229"/>
+      <c r="E35" s="229"/>
+      <c r="F35" s="229"/>
+      <c r="G35" s="229"/>
+      <c r="H35" s="230"/>
+      <c r="I35" s="231"/>
+      <c r="J35" s="231"/>
+      <c r="K35" s="231"/>
+      <c r="L35" s="231"/>
+      <c r="M35" s="232"/>
+      <c r="N35" s="233"/>
+      <c r="O35" s="234"/>
+      <c r="P35" s="235"/>
       <c r="Q35" s="60"/>
-      <c r="R35" s="253"/>
-      <c r="S35" s="253"/>
+      <c r="R35" s="236"/>
+      <c r="S35" s="236"/>
     </row>
     <row r="36" spans="1:19" ht="30" customHeight="1">
       <c r="A36" s="60"/>
       <c r="B36" s="60"/>
-      <c r="C36" s="249"/>
-      <c r="D36" s="249"/>
-      <c r="E36" s="249"/>
-      <c r="F36" s="249"/>
-      <c r="G36" s="249"/>
-      <c r="H36" s="257"/>
-      <c r="I36" s="258"/>
-      <c r="J36" s="258"/>
-      <c r="K36" s="258"/>
-      <c r="L36" s="258"/>
-      <c r="M36" s="259"/>
-      <c r="N36" s="250"/>
-      <c r="O36" s="251"/>
-      <c r="P36" s="252"/>
+      <c r="C36" s="229"/>
+      <c r="D36" s="229"/>
+      <c r="E36" s="229"/>
+      <c r="F36" s="229"/>
+      <c r="G36" s="229"/>
+      <c r="H36" s="230"/>
+      <c r="I36" s="231"/>
+      <c r="J36" s="231"/>
+      <c r="K36" s="231"/>
+      <c r="L36" s="231"/>
+      <c r="M36" s="232"/>
+      <c r="N36" s="233"/>
+      <c r="O36" s="234"/>
+      <c r="P36" s="235"/>
       <c r="Q36" s="60"/>
-      <c r="R36" s="253"/>
-      <c r="S36" s="253"/>
+      <c r="R36" s="236"/>
+      <c r="S36" s="236"/>
     </row>
     <row r="37" spans="1:19" ht="30" customHeight="1">
       <c r="A37" s="60"/>
       <c r="B37" s="60"/>
-      <c r="C37" s="249"/>
-      <c r="D37" s="249"/>
-      <c r="E37" s="249"/>
-      <c r="F37" s="249"/>
-      <c r="G37" s="249"/>
-      <c r="H37" s="257"/>
-      <c r="I37" s="258"/>
-      <c r="J37" s="258"/>
-      <c r="K37" s="258"/>
-      <c r="L37" s="258"/>
-      <c r="M37" s="259"/>
-      <c r="N37" s="250"/>
-      <c r="O37" s="251"/>
-      <c r="P37" s="252"/>
+      <c r="C37" s="229"/>
+      <c r="D37" s="229"/>
+      <c r="E37" s="229"/>
+      <c r="F37" s="229"/>
+      <c r="G37" s="229"/>
+      <c r="H37" s="230"/>
+      <c r="I37" s="231"/>
+      <c r="J37" s="231"/>
+      <c r="K37" s="231"/>
+      <c r="L37" s="231"/>
+      <c r="M37" s="232"/>
+      <c r="N37" s="233"/>
+      <c r="O37" s="234"/>
+      <c r="P37" s="235"/>
       <c r="Q37" s="60"/>
-      <c r="R37" s="253"/>
-      <c r="S37" s="253"/>
+      <c r="R37" s="236"/>
+      <c r="S37" s="236"/>
     </row>
     <row r="38" spans="1:19" ht="30" customHeight="1">
       <c r="A38" s="60"/>
       <c r="B38" s="60"/>
-      <c r="C38" s="249"/>
-      <c r="D38" s="249"/>
-      <c r="E38" s="249"/>
-      <c r="F38" s="249"/>
-      <c r="G38" s="249"/>
-      <c r="H38" s="257"/>
-      <c r="I38" s="258"/>
-      <c r="J38" s="258"/>
-      <c r="K38" s="258"/>
-      <c r="L38" s="258"/>
-      <c r="M38" s="259"/>
-      <c r="N38" s="250"/>
-      <c r="O38" s="251"/>
-      <c r="P38" s="252"/>
+      <c r="C38" s="229"/>
+      <c r="D38" s="229"/>
+      <c r="E38" s="229"/>
+      <c r="F38" s="229"/>
+      <c r="G38" s="229"/>
+      <c r="H38" s="230"/>
+      <c r="I38" s="231"/>
+      <c r="J38" s="231"/>
+      <c r="K38" s="231"/>
+      <c r="L38" s="231"/>
+      <c r="M38" s="232"/>
+      <c r="N38" s="233"/>
+      <c r="O38" s="234"/>
+      <c r="P38" s="235"/>
       <c r="Q38" s="60"/>
-      <c r="R38" s="253"/>
-      <c r="S38" s="253"/>
+      <c r="R38" s="236"/>
+      <c r="S38" s="236"/>
     </row>
     <row r="39" spans="1:19" ht="30" customHeight="1">
       <c r="A39" s="60"/>
       <c r="B39" s="60"/>
-      <c r="C39" s="249"/>
-      <c r="D39" s="249"/>
-      <c r="E39" s="249"/>
-      <c r="F39" s="249"/>
-      <c r="G39" s="249"/>
-      <c r="H39" s="257"/>
-      <c r="I39" s="258"/>
-      <c r="J39" s="258"/>
-      <c r="K39" s="258"/>
-      <c r="L39" s="258"/>
-      <c r="M39" s="259"/>
-      <c r="N39" s="250"/>
-      <c r="O39" s="251"/>
-      <c r="P39" s="252"/>
+      <c r="C39" s="229"/>
+      <c r="D39" s="229"/>
+      <c r="E39" s="229"/>
+      <c r="F39" s="229"/>
+      <c r="G39" s="229"/>
+      <c r="H39" s="230"/>
+      <c r="I39" s="231"/>
+      <c r="J39" s="231"/>
+      <c r="K39" s="231"/>
+      <c r="L39" s="231"/>
+      <c r="M39" s="232"/>
+      <c r="N39" s="233"/>
+      <c r="O39" s="234"/>
+      <c r="P39" s="235"/>
       <c r="Q39" s="60"/>
-      <c r="R39" s="253"/>
-      <c r="S39" s="253"/>
+      <c r="R39" s="236"/>
+      <c r="S39" s="236"/>
     </row>
     <row r="40" spans="1:19" ht="30" customHeight="1">
       <c r="A40" s="60"/>
       <c r="B40" s="60"/>
-      <c r="C40" s="249"/>
-      <c r="D40" s="249"/>
-      <c r="E40" s="249"/>
-      <c r="F40" s="249"/>
-      <c r="G40" s="249"/>
-      <c r="H40" s="257"/>
-      <c r="I40" s="258"/>
-      <c r="J40" s="258"/>
-      <c r="K40" s="258"/>
-      <c r="L40" s="258"/>
-      <c r="M40" s="259"/>
-      <c r="N40" s="250"/>
-      <c r="O40" s="251"/>
-      <c r="P40" s="252"/>
+      <c r="C40" s="229"/>
+      <c r="D40" s="229"/>
+      <c r="E40" s="229"/>
+      <c r="F40" s="229"/>
+      <c r="G40" s="229"/>
+      <c r="H40" s="230"/>
+      <c r="I40" s="231"/>
+      <c r="J40" s="231"/>
+      <c r="K40" s="231"/>
+      <c r="L40" s="231"/>
+      <c r="M40" s="232"/>
+      <c r="N40" s="233"/>
+      <c r="O40" s="234"/>
+      <c r="P40" s="235"/>
       <c r="Q40" s="60"/>
-      <c r="R40" s="253"/>
-      <c r="S40" s="253"/>
+      <c r="R40" s="236"/>
+      <c r="S40" s="236"/>
     </row>
     <row r="41" spans="1:19" ht="30" customHeight="1">
       <c r="A41" s="60"/>
       <c r="B41" s="60"/>
-      <c r="C41" s="249"/>
-      <c r="D41" s="249"/>
-      <c r="E41" s="249"/>
-      <c r="F41" s="249"/>
-      <c r="G41" s="249"/>
-      <c r="H41" s="257"/>
-      <c r="I41" s="258"/>
-      <c r="J41" s="258"/>
-      <c r="K41" s="258"/>
-      <c r="L41" s="258"/>
-      <c r="M41" s="259"/>
-      <c r="N41" s="250"/>
-      <c r="O41" s="251"/>
-      <c r="P41" s="252"/>
+      <c r="C41" s="229"/>
+      <c r="D41" s="229"/>
+      <c r="E41" s="229"/>
+      <c r="F41" s="229"/>
+      <c r="G41" s="229"/>
+      <c r="H41" s="230"/>
+      <c r="I41" s="231"/>
+      <c r="J41" s="231"/>
+      <c r="K41" s="231"/>
+      <c r="L41" s="231"/>
+      <c r="M41" s="232"/>
+      <c r="N41" s="233"/>
+      <c r="O41" s="234"/>
+      <c r="P41" s="235"/>
       <c r="Q41" s="60"/>
-      <c r="R41" s="253"/>
-      <c r="S41" s="253"/>
+      <c r="R41" s="236"/>
+      <c r="S41" s="236"/>
     </row>
     <row r="42" spans="1:19" ht="30" customHeight="1">
       <c r="A42" s="60"/>
       <c r="B42" s="60"/>
-      <c r="C42" s="249"/>
-      <c r="D42" s="249"/>
-      <c r="E42" s="249"/>
-      <c r="F42" s="249"/>
-      <c r="G42" s="249"/>
-      <c r="H42" s="257"/>
-      <c r="I42" s="258"/>
-      <c r="J42" s="258"/>
-      <c r="K42" s="258"/>
-      <c r="L42" s="258"/>
-      <c r="M42" s="259"/>
-      <c r="N42" s="250"/>
-      <c r="O42" s="251"/>
-      <c r="P42" s="252"/>
+      <c r="C42" s="229"/>
+      <c r="D42" s="229"/>
+      <c r="E42" s="229"/>
+      <c r="F42" s="229"/>
+      <c r="G42" s="229"/>
+      <c r="H42" s="230"/>
+      <c r="I42" s="231"/>
+      <c r="J42" s="231"/>
+      <c r="K42" s="231"/>
+      <c r="L42" s="231"/>
+      <c r="M42" s="232"/>
+      <c r="N42" s="233"/>
+      <c r="O42" s="234"/>
+      <c r="P42" s="235"/>
       <c r="Q42" s="60"/>
-      <c r="R42" s="253"/>
-      <c r="S42" s="253"/>
+      <c r="R42" s="236"/>
+      <c r="S42" s="236"/>
     </row>
     <row r="43" spans="1:19" ht="30" customHeight="1">
       <c r="A43" s="60"/>
       <c r="B43" s="60"/>
-      <c r="C43" s="249"/>
-      <c r="D43" s="249"/>
-      <c r="E43" s="249"/>
-      <c r="F43" s="249"/>
-      <c r="G43" s="249"/>
-      <c r="H43" s="257"/>
-      <c r="I43" s="258"/>
-      <c r="J43" s="258"/>
-      <c r="K43" s="258"/>
-      <c r="L43" s="258"/>
-      <c r="M43" s="259"/>
-      <c r="N43" s="250"/>
-      <c r="O43" s="251"/>
-      <c r="P43" s="252"/>
+      <c r="C43" s="229"/>
+      <c r="D43" s="229"/>
+      <c r="E43" s="229"/>
+      <c r="F43" s="229"/>
+      <c r="G43" s="229"/>
+      <c r="H43" s="230"/>
+      <c r="I43" s="231"/>
+      <c r="J43" s="231"/>
+      <c r="K43" s="231"/>
+      <c r="L43" s="231"/>
+      <c r="M43" s="232"/>
+      <c r="N43" s="233"/>
+      <c r="O43" s="234"/>
+      <c r="P43" s="235"/>
       <c r="Q43" s="60"/>
-      <c r="R43" s="253"/>
-      <c r="S43" s="253"/>
+      <c r="R43" s="236"/>
+      <c r="S43" s="236"/>
     </row>
     <row r="44" spans="1:19" ht="30" customHeight="1">
       <c r="A44" s="60"/>
       <c r="B44" s="60"/>
-      <c r="C44" s="249"/>
-      <c r="D44" s="249"/>
-      <c r="E44" s="249"/>
-      <c r="F44" s="249"/>
-      <c r="G44" s="249"/>
-      <c r="H44" s="257"/>
-      <c r="I44" s="258"/>
-      <c r="J44" s="258"/>
-      <c r="K44" s="258"/>
-      <c r="L44" s="258"/>
-      <c r="M44" s="259"/>
-      <c r="N44" s="250"/>
-      <c r="O44" s="251"/>
-      <c r="P44" s="252"/>
+      <c r="C44" s="229"/>
+      <c r="D44" s="229"/>
+      <c r="E44" s="229"/>
+      <c r="F44" s="229"/>
+      <c r="G44" s="229"/>
+      <c r="H44" s="230"/>
+      <c r="I44" s="231"/>
+      <c r="J44" s="231"/>
+      <c r="K44" s="231"/>
+      <c r="L44" s="231"/>
+      <c r="M44" s="232"/>
+      <c r="N44" s="233"/>
+      <c r="O44" s="234"/>
+      <c r="P44" s="235"/>
       <c r="Q44" s="60"/>
-      <c r="R44" s="253"/>
-      <c r="S44" s="253"/>
+      <c r="R44" s="236"/>
+      <c r="S44" s="236"/>
     </row>
     <row r="45" spans="1:19" ht="30" customHeight="1">
       <c r="A45" s="60"/>
       <c r="B45" s="60"/>
-      <c r="C45" s="249"/>
-      <c r="D45" s="249"/>
-      <c r="E45" s="249"/>
-      <c r="F45" s="249"/>
-      <c r="G45" s="249"/>
-      <c r="H45" s="257"/>
-      <c r="I45" s="258"/>
-      <c r="J45" s="258"/>
-      <c r="K45" s="258"/>
-      <c r="L45" s="258"/>
-      <c r="M45" s="259"/>
-      <c r="N45" s="250"/>
-      <c r="O45" s="251"/>
-      <c r="P45" s="252"/>
+      <c r="C45" s="229"/>
+      <c r="D45" s="229"/>
+      <c r="E45" s="229"/>
+      <c r="F45" s="229"/>
+      <c r="G45" s="229"/>
+      <c r="H45" s="230"/>
+      <c r="I45" s="231"/>
+      <c r="J45" s="231"/>
+      <c r="K45" s="231"/>
+      <c r="L45" s="231"/>
+      <c r="M45" s="232"/>
+      <c r="N45" s="233"/>
+      <c r="O45" s="234"/>
+      <c r="P45" s="235"/>
       <c r="Q45" s="60"/>
-      <c r="R45" s="253"/>
-      <c r="S45" s="253"/>
+      <c r="R45" s="236"/>
+      <c r="S45" s="236"/>
     </row>
     <row r="46" spans="1:19" ht="30" customHeight="1">
       <c r="A46" s="60"/>
       <c r="B46" s="60"/>
-      <c r="C46" s="249"/>
-      <c r="D46" s="249"/>
-      <c r="E46" s="249"/>
-      <c r="F46" s="249"/>
-      <c r="G46" s="249"/>
-      <c r="H46" s="257"/>
-      <c r="I46" s="258"/>
-      <c r="J46" s="258"/>
-      <c r="K46" s="258"/>
-      <c r="L46" s="258"/>
-      <c r="M46" s="259"/>
-      <c r="N46" s="250"/>
-      <c r="O46" s="251"/>
-      <c r="P46" s="252"/>
+      <c r="C46" s="229"/>
+      <c r="D46" s="229"/>
+      <c r="E46" s="229"/>
+      <c r="F46" s="229"/>
+      <c r="G46" s="229"/>
+      <c r="H46" s="230"/>
+      <c r="I46" s="231"/>
+      <c r="J46" s="231"/>
+      <c r="K46" s="231"/>
+      <c r="L46" s="231"/>
+      <c r="M46" s="232"/>
+      <c r="N46" s="233"/>
+      <c r="O46" s="234"/>
+      <c r="P46" s="235"/>
       <c r="Q46" s="60"/>
-      <c r="R46" s="253"/>
-      <c r="S46" s="253"/>
+      <c r="R46" s="236"/>
+      <c r="S46" s="236"/>
     </row>
     <row r="47" spans="1:19" ht="30" customHeight="1">
       <c r="A47" s="60"/>
       <c r="B47" s="60"/>
-      <c r="C47" s="249"/>
-      <c r="D47" s="249"/>
-      <c r="E47" s="249"/>
-      <c r="F47" s="249"/>
-      <c r="G47" s="249"/>
-      <c r="H47" s="257"/>
-      <c r="I47" s="258"/>
-      <c r="J47" s="258"/>
-      <c r="K47" s="258"/>
-      <c r="L47" s="258"/>
-      <c r="M47" s="259"/>
-      <c r="N47" s="250"/>
-      <c r="O47" s="251"/>
-      <c r="P47" s="252"/>
+      <c r="C47" s="229"/>
+      <c r="D47" s="229"/>
+      <c r="E47" s="229"/>
+      <c r="F47" s="229"/>
+      <c r="G47" s="229"/>
+      <c r="H47" s="230"/>
+      <c r="I47" s="231"/>
+      <c r="J47" s="231"/>
+      <c r="K47" s="231"/>
+      <c r="L47" s="231"/>
+      <c r="M47" s="232"/>
+      <c r="N47" s="233"/>
+      <c r="O47" s="234"/>
+      <c r="P47" s="235"/>
       <c r="Q47" s="60"/>
-      <c r="R47" s="253"/>
-      <c r="S47" s="253"/>
+      <c r="R47" s="236"/>
+      <c r="S47" s="236"/>
     </row>
     <row r="48" spans="1:19" ht="30" customHeight="1">
       <c r="A48" s="60"/>
       <c r="B48" s="60"/>
-      <c r="C48" s="249"/>
-      <c r="D48" s="249"/>
-      <c r="E48" s="249"/>
-      <c r="F48" s="249"/>
-      <c r="G48" s="249"/>
-      <c r="H48" s="257"/>
-      <c r="I48" s="258"/>
-      <c r="J48" s="258"/>
-      <c r="K48" s="258"/>
-      <c r="L48" s="258"/>
-      <c r="M48" s="259"/>
-      <c r="N48" s="250"/>
-      <c r="O48" s="251"/>
-      <c r="P48" s="252"/>
+      <c r="C48" s="229"/>
+      <c r="D48" s="229"/>
+      <c r="E48" s="229"/>
+      <c r="F48" s="229"/>
+      <c r="G48" s="229"/>
+      <c r="H48" s="230"/>
+      <c r="I48" s="231"/>
+      <c r="J48" s="231"/>
+      <c r="K48" s="231"/>
+      <c r="L48" s="231"/>
+      <c r="M48" s="232"/>
+      <c r="N48" s="233"/>
+      <c r="O48" s="234"/>
+      <c r="P48" s="235"/>
       <c r="Q48" s="60"/>
-      <c r="R48" s="253"/>
-      <c r="S48" s="253"/>
+      <c r="R48" s="236"/>
+      <c r="S48" s="236"/>
     </row>
     <row r="49" spans="1:19" ht="30" customHeight="1">
       <c r="A49" s="60"/>
       <c r="B49" s="60"/>
-      <c r="C49" s="249"/>
-      <c r="D49" s="249"/>
-      <c r="E49" s="249"/>
-      <c r="F49" s="249"/>
-      <c r="G49" s="249"/>
-      <c r="H49" s="257"/>
-      <c r="I49" s="258"/>
-      <c r="J49" s="258"/>
-      <c r="K49" s="258"/>
-      <c r="L49" s="258"/>
-      <c r="M49" s="259"/>
-      <c r="N49" s="250"/>
-      <c r="O49" s="251"/>
-      <c r="P49" s="252"/>
+      <c r="C49" s="229"/>
+      <c r="D49" s="229"/>
+      <c r="E49" s="229"/>
+      <c r="F49" s="229"/>
+      <c r="G49" s="229"/>
+      <c r="H49" s="230"/>
+      <c r="I49" s="231"/>
+      <c r="J49" s="231"/>
+      <c r="K49" s="231"/>
+      <c r="L49" s="231"/>
+      <c r="M49" s="232"/>
+      <c r="N49" s="233"/>
+      <c r="O49" s="234"/>
+      <c r="P49" s="235"/>
       <c r="Q49" s="60"/>
-      <c r="R49" s="253"/>
-      <c r="S49" s="253"/>
+      <c r="R49" s="236"/>
+      <c r="S49" s="236"/>
     </row>
     <row r="50" spans="1:19" ht="30" customHeight="1">
       <c r="A50" s="60"/>
       <c r="B50" s="60"/>
-      <c r="C50" s="249"/>
-      <c r="D50" s="249"/>
-      <c r="E50" s="249"/>
-      <c r="F50" s="249"/>
-      <c r="G50" s="249"/>
-      <c r="H50" s="257"/>
-      <c r="I50" s="258"/>
-      <c r="J50" s="258"/>
-      <c r="K50" s="258"/>
-      <c r="L50" s="258"/>
-      <c r="M50" s="259"/>
-      <c r="N50" s="250"/>
-      <c r="O50" s="251"/>
-      <c r="P50" s="252"/>
+      <c r="C50" s="229"/>
+      <c r="D50" s="229"/>
+      <c r="E50" s="229"/>
+      <c r="F50" s="229"/>
+      <c r="G50" s="229"/>
+      <c r="H50" s="230"/>
+      <c r="I50" s="231"/>
+      <c r="J50" s="231"/>
+      <c r="K50" s="231"/>
+      <c r="L50" s="231"/>
+      <c r="M50" s="232"/>
+      <c r="N50" s="233"/>
+      <c r="O50" s="234"/>
+      <c r="P50" s="235"/>
       <c r="Q50" s="60"/>
-      <c r="R50" s="253"/>
-      <c r="S50" s="253"/>
+      <c r="R50" s="236"/>
+      <c r="S50" s="236"/>
     </row>
     <row r="51" spans="1:19" ht="30" customHeight="1">
       <c r="A51" s="60"/>
       <c r="B51" s="60"/>
-      <c r="C51" s="249"/>
-      <c r="D51" s="249"/>
-      <c r="E51" s="249"/>
-      <c r="F51" s="249"/>
-      <c r="G51" s="249"/>
-      <c r="H51" s="257"/>
-      <c r="I51" s="258"/>
-      <c r="J51" s="258"/>
-      <c r="K51" s="258"/>
-      <c r="L51" s="258"/>
-      <c r="M51" s="259"/>
-      <c r="N51" s="250"/>
-      <c r="O51" s="251"/>
-      <c r="P51" s="252"/>
+      <c r="C51" s="229"/>
+      <c r="D51" s="229"/>
+      <c r="E51" s="229"/>
+      <c r="F51" s="229"/>
+      <c r="G51" s="229"/>
+      <c r="H51" s="230"/>
+      <c r="I51" s="231"/>
+      <c r="J51" s="231"/>
+      <c r="K51" s="231"/>
+      <c r="L51" s="231"/>
+      <c r="M51" s="232"/>
+      <c r="N51" s="233"/>
+      <c r="O51" s="234"/>
+      <c r="P51" s="235"/>
       <c r="Q51" s="60"/>
-      <c r="R51" s="253"/>
-      <c r="S51" s="253"/>
+      <c r="R51" s="236"/>
+      <c r="S51" s="236"/>
     </row>
     <row r="52" spans="1:19" ht="30" customHeight="1">
       <c r="A52" s="60"/>
       <c r="B52" s="60"/>
-      <c r="C52" s="249"/>
-      <c r="D52" s="249"/>
-      <c r="E52" s="249"/>
-      <c r="F52" s="249"/>
-      <c r="G52" s="249"/>
-      <c r="H52" s="257"/>
-      <c r="I52" s="258"/>
-      <c r="J52" s="258"/>
-      <c r="K52" s="258"/>
-      <c r="L52" s="258"/>
-      <c r="M52" s="259"/>
-      <c r="N52" s="250"/>
-      <c r="O52" s="251"/>
-      <c r="P52" s="252"/>
+      <c r="C52" s="229"/>
+      <c r="D52" s="229"/>
+      <c r="E52" s="229"/>
+      <c r="F52" s="229"/>
+      <c r="G52" s="229"/>
+      <c r="H52" s="230"/>
+      <c r="I52" s="231"/>
+      <c r="J52" s="231"/>
+      <c r="K52" s="231"/>
+      <c r="L52" s="231"/>
+      <c r="M52" s="232"/>
+      <c r="N52" s="233"/>
+      <c r="O52" s="234"/>
+      <c r="P52" s="235"/>
       <c r="Q52" s="60"/>
-      <c r="R52" s="253"/>
-      <c r="S52" s="253"/>
+      <c r="R52" s="236"/>
+      <c r="S52" s="236"/>
     </row>
   </sheetData>
   <mergeCells count="205">
-    <mergeCell ref="C52:G52"/>
-    <mergeCell ref="H52:M52"/>
-    <mergeCell ref="N52:P52"/>
-    <mergeCell ref="R52:S52"/>
-    <mergeCell ref="C50:G50"/>
-    <mergeCell ref="H50:M50"/>
-    <mergeCell ref="N50:P50"/>
-    <mergeCell ref="R50:S50"/>
-    <mergeCell ref="C51:G51"/>
-    <mergeCell ref="H51:M51"/>
-    <mergeCell ref="N51:P51"/>
-    <mergeCell ref="R51:S51"/>
-    <mergeCell ref="C48:G48"/>
-    <mergeCell ref="H48:M48"/>
-    <mergeCell ref="N48:P48"/>
-    <mergeCell ref="R48:S48"/>
-    <mergeCell ref="C49:G49"/>
-    <mergeCell ref="H49:M49"/>
-    <mergeCell ref="N49:P49"/>
-    <mergeCell ref="R49:S49"/>
-    <mergeCell ref="C46:G46"/>
-    <mergeCell ref="H46:M46"/>
-    <mergeCell ref="N46:P46"/>
-    <mergeCell ref="R46:S46"/>
-    <mergeCell ref="C47:G47"/>
-    <mergeCell ref="H47:M47"/>
-    <mergeCell ref="N47:P47"/>
-    <mergeCell ref="R47:S47"/>
-    <mergeCell ref="C44:G44"/>
-    <mergeCell ref="H44:M44"/>
-    <mergeCell ref="N44:P44"/>
-    <mergeCell ref="R44:S44"/>
-    <mergeCell ref="C45:G45"/>
-    <mergeCell ref="H45:M45"/>
-    <mergeCell ref="N45:P45"/>
-    <mergeCell ref="R45:S45"/>
-    <mergeCell ref="C42:G42"/>
-    <mergeCell ref="H42:M42"/>
-    <mergeCell ref="N42:P42"/>
-    <mergeCell ref="R42:S42"/>
-    <mergeCell ref="C43:G43"/>
-    <mergeCell ref="H43:M43"/>
-    <mergeCell ref="N43:P43"/>
-    <mergeCell ref="R43:S43"/>
-    <mergeCell ref="C40:G40"/>
-    <mergeCell ref="H40:M40"/>
-    <mergeCell ref="N40:P40"/>
-    <mergeCell ref="R40:S40"/>
-    <mergeCell ref="C41:G41"/>
-    <mergeCell ref="H41:M41"/>
-    <mergeCell ref="N41:P41"/>
-    <mergeCell ref="R41:S41"/>
-    <mergeCell ref="C38:G38"/>
-    <mergeCell ref="H38:M38"/>
-    <mergeCell ref="N38:P38"/>
-    <mergeCell ref="R38:S38"/>
-    <mergeCell ref="C39:G39"/>
-    <mergeCell ref="H39:M39"/>
-    <mergeCell ref="N39:P39"/>
-    <mergeCell ref="R39:S39"/>
-    <mergeCell ref="C36:G36"/>
-    <mergeCell ref="H36:M36"/>
-    <mergeCell ref="N36:P36"/>
-    <mergeCell ref="R36:S36"/>
-    <mergeCell ref="C37:G37"/>
-    <mergeCell ref="H37:M37"/>
-    <mergeCell ref="N37:P37"/>
-    <mergeCell ref="R37:S37"/>
-    <mergeCell ref="C34:G34"/>
-    <mergeCell ref="H34:M34"/>
-    <mergeCell ref="N34:P34"/>
-    <mergeCell ref="R34:S34"/>
-    <mergeCell ref="C35:G35"/>
-    <mergeCell ref="H35:M35"/>
-    <mergeCell ref="N35:P35"/>
-    <mergeCell ref="R35:S35"/>
-    <mergeCell ref="C32:G32"/>
-    <mergeCell ref="H32:M32"/>
-    <mergeCell ref="N32:P32"/>
-    <mergeCell ref="R32:S32"/>
-    <mergeCell ref="C33:G33"/>
-    <mergeCell ref="H33:M33"/>
-    <mergeCell ref="N33:P33"/>
-    <mergeCell ref="R33:S33"/>
-    <mergeCell ref="C30:G30"/>
-    <mergeCell ref="H30:M30"/>
-    <mergeCell ref="N30:P30"/>
-    <mergeCell ref="R30:S30"/>
-    <mergeCell ref="C31:G31"/>
-    <mergeCell ref="H31:M31"/>
-    <mergeCell ref="N31:P31"/>
-    <mergeCell ref="R31:S31"/>
-    <mergeCell ref="C28:G28"/>
-    <mergeCell ref="H28:M28"/>
-    <mergeCell ref="N28:P28"/>
-    <mergeCell ref="R28:S28"/>
-    <mergeCell ref="C29:G29"/>
-    <mergeCell ref="H29:M29"/>
-    <mergeCell ref="N29:P29"/>
-    <mergeCell ref="R29:S29"/>
-    <mergeCell ref="C26:G26"/>
-    <mergeCell ref="H26:M26"/>
-    <mergeCell ref="N26:P26"/>
-    <mergeCell ref="R26:S26"/>
-    <mergeCell ref="C27:G27"/>
-    <mergeCell ref="H27:M27"/>
-    <mergeCell ref="N27:P27"/>
-    <mergeCell ref="R27:S27"/>
-    <mergeCell ref="C24:G24"/>
-    <mergeCell ref="H24:M24"/>
-    <mergeCell ref="N24:P24"/>
-    <mergeCell ref="R24:S24"/>
-    <mergeCell ref="C25:G25"/>
-    <mergeCell ref="H25:M25"/>
-    <mergeCell ref="N25:P25"/>
-    <mergeCell ref="R25:S25"/>
-    <mergeCell ref="C22:G22"/>
-    <mergeCell ref="H22:M22"/>
-    <mergeCell ref="N22:P22"/>
-    <mergeCell ref="R22:S22"/>
-    <mergeCell ref="C23:G23"/>
-    <mergeCell ref="H23:M23"/>
-    <mergeCell ref="N23:P23"/>
-    <mergeCell ref="R23:S23"/>
-    <mergeCell ref="C20:G20"/>
-    <mergeCell ref="H20:M20"/>
-    <mergeCell ref="N20:P20"/>
-    <mergeCell ref="R20:S20"/>
-    <mergeCell ref="C21:G21"/>
-    <mergeCell ref="H21:M21"/>
-    <mergeCell ref="N21:P21"/>
-    <mergeCell ref="R21:S21"/>
-    <mergeCell ref="C18:G18"/>
-    <mergeCell ref="H18:M18"/>
-    <mergeCell ref="N18:P18"/>
-    <mergeCell ref="R18:S18"/>
-    <mergeCell ref="C19:G19"/>
-    <mergeCell ref="H19:M19"/>
-    <mergeCell ref="N19:P19"/>
-    <mergeCell ref="R19:S19"/>
-    <mergeCell ref="C16:G16"/>
-    <mergeCell ref="H16:M16"/>
-    <mergeCell ref="N16:P16"/>
-    <mergeCell ref="R16:S16"/>
-    <mergeCell ref="C17:G17"/>
-    <mergeCell ref="H17:M17"/>
-    <mergeCell ref="N17:P17"/>
-    <mergeCell ref="R17:S17"/>
-    <mergeCell ref="C14:G14"/>
-    <mergeCell ref="H14:M14"/>
-    <mergeCell ref="N14:P14"/>
-    <mergeCell ref="R14:S14"/>
-    <mergeCell ref="C15:G15"/>
-    <mergeCell ref="H15:M15"/>
-    <mergeCell ref="N15:P15"/>
-    <mergeCell ref="R15:S15"/>
-    <mergeCell ref="C12:G12"/>
-    <mergeCell ref="H12:M12"/>
-    <mergeCell ref="N12:P12"/>
-    <mergeCell ref="R12:S12"/>
-    <mergeCell ref="C13:G13"/>
-    <mergeCell ref="H13:M13"/>
-    <mergeCell ref="N13:P13"/>
-    <mergeCell ref="R13:S13"/>
-    <mergeCell ref="C10:G10"/>
-    <mergeCell ref="H10:M10"/>
-    <mergeCell ref="N10:P10"/>
-    <mergeCell ref="R10:S10"/>
-    <mergeCell ref="C11:G11"/>
-    <mergeCell ref="H11:M11"/>
-    <mergeCell ref="N11:P11"/>
-    <mergeCell ref="R11:S11"/>
-    <mergeCell ref="C8:G8"/>
-    <mergeCell ref="H8:M8"/>
-    <mergeCell ref="N8:P8"/>
-    <mergeCell ref="R8:S8"/>
-    <mergeCell ref="C9:G9"/>
-    <mergeCell ref="H9:M9"/>
-    <mergeCell ref="N9:P9"/>
-    <mergeCell ref="R9:S9"/>
-    <mergeCell ref="C6:G6"/>
-    <mergeCell ref="H6:M6"/>
-    <mergeCell ref="N6:P6"/>
-    <mergeCell ref="R6:S6"/>
-    <mergeCell ref="C7:G7"/>
-    <mergeCell ref="H7:M7"/>
-    <mergeCell ref="N7:P7"/>
-    <mergeCell ref="R7:S7"/>
     <mergeCell ref="C4:G4"/>
     <mergeCell ref="H4:M4"/>
     <mergeCell ref="N4:P4"/>
@@ -22070,8 +22649,196 @@
     <mergeCell ref="F2:M2"/>
     <mergeCell ref="O2:P2"/>
     <mergeCell ref="R2:S2"/>
+    <mergeCell ref="C8:G8"/>
+    <mergeCell ref="H8:M8"/>
+    <mergeCell ref="N8:P8"/>
+    <mergeCell ref="R8:S8"/>
+    <mergeCell ref="C9:G9"/>
+    <mergeCell ref="H9:M9"/>
+    <mergeCell ref="N9:P9"/>
+    <mergeCell ref="R9:S9"/>
+    <mergeCell ref="C6:G6"/>
+    <mergeCell ref="H6:M6"/>
+    <mergeCell ref="N6:P6"/>
+    <mergeCell ref="R6:S6"/>
+    <mergeCell ref="C7:G7"/>
+    <mergeCell ref="H7:M7"/>
+    <mergeCell ref="N7:P7"/>
+    <mergeCell ref="R7:S7"/>
+    <mergeCell ref="C12:G12"/>
+    <mergeCell ref="H12:M12"/>
+    <mergeCell ref="N12:P12"/>
+    <mergeCell ref="R12:S12"/>
+    <mergeCell ref="C13:G13"/>
+    <mergeCell ref="H13:M13"/>
+    <mergeCell ref="N13:P13"/>
+    <mergeCell ref="R13:S13"/>
+    <mergeCell ref="C10:G10"/>
+    <mergeCell ref="H10:M10"/>
+    <mergeCell ref="N10:P10"/>
+    <mergeCell ref="R10:S10"/>
+    <mergeCell ref="C11:G11"/>
+    <mergeCell ref="H11:M11"/>
+    <mergeCell ref="N11:P11"/>
+    <mergeCell ref="R11:S11"/>
+    <mergeCell ref="C16:G16"/>
+    <mergeCell ref="H16:M16"/>
+    <mergeCell ref="N16:P16"/>
+    <mergeCell ref="R16:S16"/>
+    <mergeCell ref="C17:G17"/>
+    <mergeCell ref="H17:M17"/>
+    <mergeCell ref="N17:P17"/>
+    <mergeCell ref="R17:S17"/>
+    <mergeCell ref="C14:G14"/>
+    <mergeCell ref="H14:M14"/>
+    <mergeCell ref="N14:P14"/>
+    <mergeCell ref="R14:S14"/>
+    <mergeCell ref="C15:G15"/>
+    <mergeCell ref="H15:M15"/>
+    <mergeCell ref="N15:P15"/>
+    <mergeCell ref="R15:S15"/>
+    <mergeCell ref="C20:G20"/>
+    <mergeCell ref="H20:M20"/>
+    <mergeCell ref="N20:P20"/>
+    <mergeCell ref="R20:S20"/>
+    <mergeCell ref="C21:G21"/>
+    <mergeCell ref="H21:M21"/>
+    <mergeCell ref="N21:P21"/>
+    <mergeCell ref="R21:S21"/>
+    <mergeCell ref="C18:G18"/>
+    <mergeCell ref="H18:M18"/>
+    <mergeCell ref="N18:P18"/>
+    <mergeCell ref="R18:S18"/>
+    <mergeCell ref="C19:G19"/>
+    <mergeCell ref="H19:M19"/>
+    <mergeCell ref="N19:P19"/>
+    <mergeCell ref="R19:S19"/>
+    <mergeCell ref="C24:G24"/>
+    <mergeCell ref="H24:M24"/>
+    <mergeCell ref="N24:P24"/>
+    <mergeCell ref="R24:S24"/>
+    <mergeCell ref="C25:G25"/>
+    <mergeCell ref="H25:M25"/>
+    <mergeCell ref="N25:P25"/>
+    <mergeCell ref="R25:S25"/>
+    <mergeCell ref="C22:G22"/>
+    <mergeCell ref="H22:M22"/>
+    <mergeCell ref="N22:P22"/>
+    <mergeCell ref="R22:S22"/>
+    <mergeCell ref="C23:G23"/>
+    <mergeCell ref="H23:M23"/>
+    <mergeCell ref="N23:P23"/>
+    <mergeCell ref="R23:S23"/>
+    <mergeCell ref="C28:G28"/>
+    <mergeCell ref="H28:M28"/>
+    <mergeCell ref="N28:P28"/>
+    <mergeCell ref="R28:S28"/>
+    <mergeCell ref="C29:G29"/>
+    <mergeCell ref="H29:M29"/>
+    <mergeCell ref="N29:P29"/>
+    <mergeCell ref="R29:S29"/>
+    <mergeCell ref="C26:G26"/>
+    <mergeCell ref="H26:M26"/>
+    <mergeCell ref="N26:P26"/>
+    <mergeCell ref="R26:S26"/>
+    <mergeCell ref="C27:G27"/>
+    <mergeCell ref="H27:M27"/>
+    <mergeCell ref="N27:P27"/>
+    <mergeCell ref="R27:S27"/>
+    <mergeCell ref="C32:G32"/>
+    <mergeCell ref="H32:M32"/>
+    <mergeCell ref="N32:P32"/>
+    <mergeCell ref="R32:S32"/>
+    <mergeCell ref="C33:G33"/>
+    <mergeCell ref="H33:M33"/>
+    <mergeCell ref="N33:P33"/>
+    <mergeCell ref="R33:S33"/>
+    <mergeCell ref="C30:G30"/>
+    <mergeCell ref="H30:M30"/>
+    <mergeCell ref="N30:P30"/>
+    <mergeCell ref="R30:S30"/>
+    <mergeCell ref="C31:G31"/>
+    <mergeCell ref="H31:M31"/>
+    <mergeCell ref="N31:P31"/>
+    <mergeCell ref="R31:S31"/>
+    <mergeCell ref="C36:G36"/>
+    <mergeCell ref="H36:M36"/>
+    <mergeCell ref="N36:P36"/>
+    <mergeCell ref="R36:S36"/>
+    <mergeCell ref="C37:G37"/>
+    <mergeCell ref="H37:M37"/>
+    <mergeCell ref="N37:P37"/>
+    <mergeCell ref="R37:S37"/>
+    <mergeCell ref="C34:G34"/>
+    <mergeCell ref="H34:M34"/>
+    <mergeCell ref="N34:P34"/>
+    <mergeCell ref="R34:S34"/>
+    <mergeCell ref="C35:G35"/>
+    <mergeCell ref="H35:M35"/>
+    <mergeCell ref="N35:P35"/>
+    <mergeCell ref="R35:S35"/>
+    <mergeCell ref="C40:G40"/>
+    <mergeCell ref="H40:M40"/>
+    <mergeCell ref="N40:P40"/>
+    <mergeCell ref="R40:S40"/>
+    <mergeCell ref="C41:G41"/>
+    <mergeCell ref="H41:M41"/>
+    <mergeCell ref="N41:P41"/>
+    <mergeCell ref="R41:S41"/>
+    <mergeCell ref="C38:G38"/>
+    <mergeCell ref="H38:M38"/>
+    <mergeCell ref="N38:P38"/>
+    <mergeCell ref="R38:S38"/>
+    <mergeCell ref="C39:G39"/>
+    <mergeCell ref="H39:M39"/>
+    <mergeCell ref="N39:P39"/>
+    <mergeCell ref="R39:S39"/>
+    <mergeCell ref="C44:G44"/>
+    <mergeCell ref="H44:M44"/>
+    <mergeCell ref="N44:P44"/>
+    <mergeCell ref="R44:S44"/>
+    <mergeCell ref="C45:G45"/>
+    <mergeCell ref="H45:M45"/>
+    <mergeCell ref="N45:P45"/>
+    <mergeCell ref="R45:S45"/>
+    <mergeCell ref="C42:G42"/>
+    <mergeCell ref="H42:M42"/>
+    <mergeCell ref="N42:P42"/>
+    <mergeCell ref="R42:S42"/>
+    <mergeCell ref="C43:G43"/>
+    <mergeCell ref="H43:M43"/>
+    <mergeCell ref="N43:P43"/>
+    <mergeCell ref="R43:S43"/>
+    <mergeCell ref="C48:G48"/>
+    <mergeCell ref="H48:M48"/>
+    <mergeCell ref="N48:P48"/>
+    <mergeCell ref="R48:S48"/>
+    <mergeCell ref="C49:G49"/>
+    <mergeCell ref="H49:M49"/>
+    <mergeCell ref="N49:P49"/>
+    <mergeCell ref="R49:S49"/>
+    <mergeCell ref="C46:G46"/>
+    <mergeCell ref="H46:M46"/>
+    <mergeCell ref="N46:P46"/>
+    <mergeCell ref="R46:S46"/>
+    <mergeCell ref="C47:G47"/>
+    <mergeCell ref="H47:M47"/>
+    <mergeCell ref="N47:P47"/>
+    <mergeCell ref="R47:S47"/>
+    <mergeCell ref="C52:G52"/>
+    <mergeCell ref="H52:M52"/>
+    <mergeCell ref="N52:P52"/>
+    <mergeCell ref="R52:S52"/>
+    <mergeCell ref="C50:G50"/>
+    <mergeCell ref="H50:M50"/>
+    <mergeCell ref="N50:P50"/>
+    <mergeCell ref="R50:S50"/>
+    <mergeCell ref="C51:G51"/>
+    <mergeCell ref="H51:M51"/>
+    <mergeCell ref="N51:P51"/>
+    <mergeCell ref="R51:S51"/>
   </mergeCells>
-  <phoneticPr fontId="8"/>
+  <phoneticPr fontId="9"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.31496062992125984" bottom="0.27559055118110237" header="0.35433070866141736" footer="0.15748031496062992"/>
   <pageSetup paperSize="9" orientation="landscape" horizontalDpi="4294967293" r:id="rId1"/>
   <headerFooter alignWithMargins="0"/>

--- a/Documents/登録機能詳細設計書.xlsx
+++ b/Documents/登録機能詳細設計書.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\S-47\Documents\project\taskUN\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D93AFB4D-8E7C-4D31-B7E6-E593F2EC5A97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34A78630-FBCC-44F8-BC69-3280335D790A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="172">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="169">
   <si>
     <t>プロジェクト型演習　成果ドキュメント</t>
   </si>
@@ -1356,66 +1356,6 @@
   </si>
   <si>
     <t>〇</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>タスク名、カテゴリー、ステータス、期限、ユーザ名、メモを入力しタスク登録を行い、登録成功画面に遷移したのち、ブラウザバックをしたときもう一度同じ内容のものを登録することができる</t>
-    <rPh sb="37" eb="38">
-      <t>オコナ</t>
-    </rPh>
-    <rPh sb="40" eb="42">
-      <t>トウロク</t>
-    </rPh>
-    <rPh sb="42" eb="44">
-      <t>セイコウ</t>
-    </rPh>
-    <rPh sb="44" eb="46">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="47" eb="49">
-      <t>センイ</t>
-    </rPh>
-    <rPh sb="68" eb="70">
-      <t>イチド</t>
-    </rPh>
-    <rPh sb="70" eb="71">
-      <t>オナ</t>
-    </rPh>
-    <rPh sb="72" eb="74">
-      <t>ナイヨウ</t>
-    </rPh>
-    <rPh sb="78" eb="80">
-      <t>トウロク</t>
-    </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>入力されたものが既にデータベース上に存在している</t>
-    <rPh sb="0" eb="2">
-      <t>ニュウリョク</t>
-    </rPh>
-    <rPh sb="8" eb="9">
-      <t>スデ</t>
-    </rPh>
-    <rPh sb="16" eb="17">
-      <t>ジョウ</t>
-    </rPh>
-    <rPh sb="18" eb="20">
-      <t>ソンザイ</t>
-    </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>ブラウザバックしてからもう一度登録ボタンを押下する</t>
-    <rPh sb="13" eb="15">
-      <t>イチド</t>
-    </rPh>
-    <rPh sb="15" eb="17">
-      <t>トウロク</t>
-    </rPh>
-    <rPh sb="21" eb="23">
-      <t>オウカ</t>
-    </rPh>
     <phoneticPr fontId="8"/>
   </si>
 </sst>
@@ -2826,6 +2766,93 @@
     <xf numFmtId="14" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2856,9 +2883,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2871,90 +2895,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3033,6 +2973,12 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3105,10 +3051,31 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3117,126 +3084,180 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="5" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="58" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="59" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="60" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="63" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="64" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="5" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="65" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="66" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="64" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="66" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="57" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="58" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="59" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="60" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="58" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="59" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="60" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="18" fillId="0" borderId="58" xfId="6" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    <xf numFmtId="14" fontId="18" fillId="0" borderId="60" xfId="6" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="18" fillId="0" borderId="58" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="60" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="67" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="68" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="69" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="70" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="67" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="68" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="69" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="70" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="68" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="69" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3244,87 +3265,6 @@
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="70" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="68" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="69" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="70" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="67" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="63" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="68" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="69" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="70" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="58" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="59" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="60" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="64" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="65" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="66" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="64" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="66" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="57" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="58" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="59" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="60" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="58" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="59" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="60" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="18" fillId="0" borderId="58" xfId="6" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="18" fillId="0" borderId="60" xfId="6" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="18" fillId="0" borderId="58" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="60" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="4" borderId="58" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -10321,19 +10261,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="92" t="s">
+      <c r="A1" s="121" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="93"/>
-      <c r="C1" s="94"/>
-      <c r="D1" s="101" t="s">
+      <c r="B1" s="122"/>
+      <c r="C1" s="123"/>
+      <c r="D1" s="130" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="102"/>
-      <c r="F1" s="101" t="s">
+      <c r="E1" s="115"/>
+      <c r="F1" s="130" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="102"/>
+      <c r="G1" s="115"/>
       <c r="H1" s="34" t="s">
         <v>6</v>
       </c>
@@ -10345,192 +10285,192 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="95"/>
-      <c r="B2" s="96"/>
-      <c r="C2" s="97"/>
-      <c r="D2" s="103" t="s">
+      <c r="A2" s="124"/>
+      <c r="B2" s="125"/>
+      <c r="C2" s="126"/>
+      <c r="D2" s="131" t="s">
         <v>61</v>
       </c>
-      <c r="E2" s="104"/>
-      <c r="F2" s="103">
+      <c r="E2" s="132"/>
+      <c r="F2" s="131">
         <v>56</v>
       </c>
-      <c r="G2" s="104"/>
-      <c r="H2" s="107">
+      <c r="G2" s="132"/>
+      <c r="H2" s="100">
         <v>45806</v>
       </c>
-      <c r="I2" s="121" t="s">
+      <c r="I2" s="109" t="s">
         <v>60</v>
       </c>
-      <c r="J2" s="122"/>
+      <c r="J2" s="110"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="95"/>
-      <c r="B3" s="96"/>
-      <c r="C3" s="97"/>
-      <c r="D3" s="105"/>
-      <c r="E3" s="97"/>
-      <c r="F3" s="105"/>
-      <c r="G3" s="97"/>
-      <c r="H3" s="108"/>
-      <c r="I3" s="108"/>
-      <c r="J3" s="123"/>
+      <c r="A3" s="124"/>
+      <c r="B3" s="125"/>
+      <c r="C3" s="126"/>
+      <c r="D3" s="133"/>
+      <c r="E3" s="126"/>
+      <c r="F3" s="133"/>
+      <c r="G3" s="126"/>
+      <c r="H3" s="101"/>
+      <c r="I3" s="101"/>
+      <c r="J3" s="111"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="98"/>
-      <c r="B4" s="99"/>
-      <c r="C4" s="100"/>
-      <c r="D4" s="106"/>
-      <c r="E4" s="100"/>
-      <c r="F4" s="106"/>
-      <c r="G4" s="100"/>
-      <c r="H4" s="109"/>
-      <c r="I4" s="109"/>
-      <c r="J4" s="124"/>
+      <c r="A4" s="127"/>
+      <c r="B4" s="128"/>
+      <c r="C4" s="129"/>
+      <c r="D4" s="134"/>
+      <c r="E4" s="129"/>
+      <c r="F4" s="134"/>
+      <c r="G4" s="129"/>
+      <c r="H4" s="102"/>
+      <c r="I4" s="102"/>
+      <c r="J4" s="112"/>
     </row>
     <row r="5" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A5" s="125" t="s">
+      <c r="A5" s="113" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="126"/>
-      <c r="C5" s="102"/>
-      <c r="D5" s="127" t="s">
+      <c r="B5" s="114"/>
+      <c r="C5" s="115"/>
+      <c r="D5" s="116" t="s">
         <v>59</v>
       </c>
-      <c r="E5" s="126"/>
-      <c r="F5" s="126"/>
-      <c r="G5" s="126"/>
-      <c r="H5" s="126"/>
-      <c r="I5" s="126"/>
-      <c r="J5" s="128"/>
+      <c r="E5" s="114"/>
+      <c r="F5" s="114"/>
+      <c r="G5" s="114"/>
+      <c r="H5" s="114"/>
+      <c r="I5" s="114"/>
+      <c r="J5" s="117"/>
     </row>
     <row r="6" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A6" s="110" t="s">
+      <c r="A6" s="103" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="111"/>
-      <c r="C6" s="112"/>
-      <c r="D6" s="120" t="s">
+      <c r="B6" s="98"/>
+      <c r="C6" s="93"/>
+      <c r="D6" s="97" t="s">
         <v>58</v>
       </c>
-      <c r="E6" s="111"/>
-      <c r="F6" s="111"/>
-      <c r="G6" s="111"/>
-      <c r="H6" s="111"/>
-      <c r="I6" s="111"/>
-      <c r="J6" s="114"/>
+      <c r="E6" s="98"/>
+      <c r="F6" s="98"/>
+      <c r="G6" s="98"/>
+      <c r="H6" s="98"/>
+      <c r="I6" s="98"/>
+      <c r="J6" s="99"/>
     </row>
     <row r="7" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A7" s="110" t="s">
+      <c r="A7" s="103" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="111"/>
-      <c r="C7" s="112"/>
-      <c r="D7" s="120" t="s">
+      <c r="B7" s="98"/>
+      <c r="C7" s="93"/>
+      <c r="D7" s="97" t="s">
         <v>57</v>
       </c>
-      <c r="E7" s="111"/>
-      <c r="F7" s="111"/>
-      <c r="G7" s="111"/>
-      <c r="H7" s="111"/>
-      <c r="I7" s="111"/>
-      <c r="J7" s="114"/>
+      <c r="E7" s="98"/>
+      <c r="F7" s="98"/>
+      <c r="G7" s="98"/>
+      <c r="H7" s="98"/>
+      <c r="I7" s="98"/>
+      <c r="J7" s="99"/>
     </row>
     <row r="8" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A8" s="110" t="s">
+      <c r="A8" s="103" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="111"/>
-      <c r="C8" s="112"/>
-      <c r="D8" s="113" t="s">
+      <c r="B8" s="98"/>
+      <c r="C8" s="93"/>
+      <c r="D8" s="94" t="s">
         <v>107</v>
       </c>
-      <c r="E8" s="111"/>
-      <c r="F8" s="111"/>
-      <c r="G8" s="111"/>
-      <c r="H8" s="111"/>
-      <c r="I8" s="111"/>
-      <c r="J8" s="114"/>
+      <c r="E8" s="98"/>
+      <c r="F8" s="98"/>
+      <c r="G8" s="98"/>
+      <c r="H8" s="98"/>
+      <c r="I8" s="98"/>
+      <c r="J8" s="99"/>
     </row>
     <row r="9" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A9" s="129" t="s">
+      <c r="A9" s="118" t="s">
         <v>13</v>
       </c>
-      <c r="B9" s="132" t="s">
+      <c r="B9" s="92" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="112"/>
-      <c r="D9" s="113" t="s">
+      <c r="C9" s="93"/>
+      <c r="D9" s="94" t="s">
         <v>105</v>
       </c>
-      <c r="E9" s="133"/>
-      <c r="F9" s="133"/>
-      <c r="G9" s="133"/>
-      <c r="H9" s="133"/>
-      <c r="I9" s="133"/>
-      <c r="J9" s="134"/>
+      <c r="E9" s="95"/>
+      <c r="F9" s="95"/>
+      <c r="G9" s="95"/>
+      <c r="H9" s="95"/>
+      <c r="I9" s="95"/>
+      <c r="J9" s="96"/>
     </row>
     <row r="10" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A10" s="130"/>
-      <c r="B10" s="132" t="s">
+      <c r="A10" s="119"/>
+      <c r="B10" s="92" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="112"/>
-      <c r="D10" s="120" t="s">
+      <c r="C10" s="93"/>
+      <c r="D10" s="97" t="s">
         <v>93</v>
       </c>
-      <c r="E10" s="111"/>
-      <c r="F10" s="111"/>
-      <c r="G10" s="111"/>
-      <c r="H10" s="111"/>
-      <c r="I10" s="111"/>
-      <c r="J10" s="114"/>
+      <c r="E10" s="98"/>
+      <c r="F10" s="98"/>
+      <c r="G10" s="98"/>
+      <c r="H10" s="98"/>
+      <c r="I10" s="98"/>
+      <c r="J10" s="99"/>
     </row>
     <row r="11" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A11" s="131"/>
-      <c r="B11" s="132" t="s">
+      <c r="A11" s="120"/>
+      <c r="B11" s="92" t="s">
         <v>16</v>
       </c>
-      <c r="C11" s="112"/>
-      <c r="D11" s="113" t="s">
+      <c r="C11" s="93"/>
+      <c r="D11" s="94" t="s">
         <v>108</v>
       </c>
-      <c r="E11" s="111"/>
-      <c r="F11" s="111"/>
-      <c r="G11" s="111"/>
-      <c r="H11" s="111"/>
-      <c r="I11" s="111"/>
-      <c r="J11" s="114"/>
+      <c r="E11" s="98"/>
+      <c r="F11" s="98"/>
+      <c r="G11" s="98"/>
+      <c r="H11" s="98"/>
+      <c r="I11" s="98"/>
+      <c r="J11" s="99"/>
     </row>
     <row r="12" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A12" s="110" t="s">
+      <c r="A12" s="103" t="s">
         <v>17</v>
       </c>
-      <c r="B12" s="111"/>
-      <c r="C12" s="112"/>
-      <c r="D12" s="113" t="s">
+      <c r="B12" s="98"/>
+      <c r="C12" s="93"/>
+      <c r="D12" s="94" t="s">
         <v>106</v>
       </c>
-      <c r="E12" s="111"/>
-      <c r="F12" s="111"/>
-      <c r="G12" s="111"/>
-      <c r="H12" s="111"/>
-      <c r="I12" s="111"/>
-      <c r="J12" s="114"/>
+      <c r="E12" s="98"/>
+      <c r="F12" s="98"/>
+      <c r="G12" s="98"/>
+      <c r="H12" s="98"/>
+      <c r="I12" s="98"/>
+      <c r="J12" s="99"/>
     </row>
     <row r="13" spans="1:10" ht="26.25" customHeight="1" thickBot="1">
-      <c r="A13" s="115" t="s">
+      <c r="A13" s="104" t="s">
         <v>18</v>
       </c>
-      <c r="B13" s="116"/>
-      <c r="C13" s="117"/>
-      <c r="D13" s="118"/>
-      <c r="E13" s="116"/>
-      <c r="F13" s="116"/>
-      <c r="G13" s="116"/>
-      <c r="H13" s="116"/>
-      <c r="I13" s="116"/>
-      <c r="J13" s="119"/>
+      <c r="B13" s="105"/>
+      <c r="C13" s="106"/>
+      <c r="D13" s="107"/>
+      <c r="E13" s="105"/>
+      <c r="F13" s="105"/>
+      <c r="G13" s="105"/>
+      <c r="H13" s="105"/>
+      <c r="I13" s="105"/>
+      <c r="J13" s="108"/>
     </row>
     <row r="14" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="15" spans="1:10" ht="12.75" customHeight="1"/>
@@ -11521,12 +11461,11 @@
     <row r="1000" s="32" customFormat="1" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="D9:J9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="D10:J10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="D11:J11"/>
+    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="F2:G4"/>
     <mergeCell ref="H2:H4"/>
     <mergeCell ref="A12:C12"/>
     <mergeCell ref="D12:J12"/>
@@ -11543,11 +11482,12 @@
     <mergeCell ref="A6:C6"/>
     <mergeCell ref="D6:J6"/>
     <mergeCell ref="A9:A11"/>
-    <mergeCell ref="A1:C4"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="D2:E4"/>
-    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="D9:J9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="D10:J10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="D11:J11"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.70833333333333304" right="0.70833333333333304" top="0.74791666666666701" bottom="0.74791666666666701" header="0" footer="0"/>
@@ -14405,19 +14345,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="167" t="s">
+      <c r="A1" s="169" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="168"/>
-      <c r="C1" s="169"/>
-      <c r="D1" s="171" t="s">
+      <c r="B1" s="170"/>
+      <c r="C1" s="171"/>
+      <c r="D1" s="173" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="172"/>
-      <c r="F1" s="171" t="s">
+      <c r="E1" s="174"/>
+      <c r="F1" s="173" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="172"/>
+      <c r="G1" s="174"/>
       <c r="H1" s="43" t="s">
         <v>6</v>
       </c>
@@ -14429,67 +14369,67 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="164"/>
-      <c r="B2" s="165"/>
-      <c r="C2" s="170"/>
-      <c r="D2" s="173" t="s">
+      <c r="A2" s="166"/>
+      <c r="B2" s="167"/>
+      <c r="C2" s="172"/>
+      <c r="D2" s="175" t="s">
         <v>84</v>
       </c>
-      <c r="E2" s="174"/>
-      <c r="F2" s="173">
+      <c r="E2" s="176"/>
+      <c r="F2" s="175">
         <v>56</v>
       </c>
-      <c r="G2" s="174"/>
-      <c r="H2" s="176">
+      <c r="G2" s="176"/>
+      <c r="H2" s="178">
         <v>45806</v>
       </c>
-      <c r="I2" s="178" t="s">
+      <c r="I2" s="180" t="s">
         <v>83</v>
       </c>
-      <c r="J2" s="179"/>
+      <c r="J2" s="181"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="164"/>
-      <c r="B3" s="165"/>
-      <c r="C3" s="170"/>
-      <c r="D3" s="175"/>
-      <c r="E3" s="170"/>
-      <c r="F3" s="175"/>
-      <c r="G3" s="170"/>
-      <c r="H3" s="177"/>
-      <c r="I3" s="177"/>
-      <c r="J3" s="180"/>
+      <c r="A3" s="166"/>
+      <c r="B3" s="167"/>
+      <c r="C3" s="172"/>
+      <c r="D3" s="177"/>
+      <c r="E3" s="172"/>
+      <c r="F3" s="177"/>
+      <c r="G3" s="172"/>
+      <c r="H3" s="179"/>
+      <c r="I3" s="179"/>
+      <c r="J3" s="182"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="164"/>
-      <c r="B4" s="165"/>
-      <c r="C4" s="170"/>
-      <c r="D4" s="175"/>
-      <c r="E4" s="170"/>
-      <c r="F4" s="175"/>
-      <c r="G4" s="170"/>
-      <c r="H4" s="177"/>
-      <c r="I4" s="177"/>
-      <c r="J4" s="180"/>
+      <c r="A4" s="166"/>
+      <c r="B4" s="167"/>
+      <c r="C4" s="172"/>
+      <c r="D4" s="177"/>
+      <c r="E4" s="172"/>
+      <c r="F4" s="177"/>
+      <c r="G4" s="172"/>
+      <c r="H4" s="179"/>
+      <c r="I4" s="179"/>
+      <c r="J4" s="182"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="181" t="s">
+      <c r="A5" s="183" t="s">
         <v>22</v>
       </c>
-      <c r="B5" s="182"/>
-      <c r="C5" s="172"/>
-      <c r="D5" s="183" t="s">
+      <c r="B5" s="184"/>
+      <c r="C5" s="174"/>
+      <c r="D5" s="185" t="s">
         <v>92</v>
       </c>
-      <c r="E5" s="182"/>
-      <c r="F5" s="182"/>
-      <c r="G5" s="182"/>
-      <c r="H5" s="182"/>
-      <c r="I5" s="182"/>
-      <c r="J5" s="184"/>
+      <c r="E5" s="184"/>
+      <c r="F5" s="184"/>
+      <c r="G5" s="184"/>
+      <c r="H5" s="184"/>
+      <c r="I5" s="184"/>
+      <c r="J5" s="186"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="185" t="s">
+      <c r="A6" s="162" t="s">
         <v>23</v>
       </c>
       <c r="B6" s="157"/>
@@ -14503,91 +14443,91 @@
       <c r="J6" s="160"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="161"/>
-      <c r="B7" s="162"/>
-      <c r="C7" s="162"/>
-      <c r="D7" s="162"/>
-      <c r="E7" s="162"/>
-      <c r="F7" s="162"/>
-      <c r="G7" s="162"/>
-      <c r="H7" s="162"/>
-      <c r="I7" s="162"/>
-      <c r="J7" s="163"/>
+      <c r="A7" s="163"/>
+      <c r="B7" s="164"/>
+      <c r="C7" s="164"/>
+      <c r="D7" s="164"/>
+      <c r="E7" s="164"/>
+      <c r="F7" s="164"/>
+      <c r="G7" s="164"/>
+      <c r="H7" s="164"/>
+      <c r="I7" s="164"/>
+      <c r="J7" s="165"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="164"/>
-      <c r="B8" s="165"/>
-      <c r="C8" s="165"/>
-      <c r="D8" s="165"/>
-      <c r="E8" s="165"/>
-      <c r="F8" s="165"/>
-      <c r="G8" s="165"/>
-      <c r="H8" s="165"/>
-      <c r="I8" s="165"/>
-      <c r="J8" s="166"/>
+      <c r="A8" s="166"/>
+      <c r="B8" s="167"/>
+      <c r="C8" s="167"/>
+      <c r="D8" s="167"/>
+      <c r="E8" s="167"/>
+      <c r="F8" s="167"/>
+      <c r="G8" s="167"/>
+      <c r="H8" s="167"/>
+      <c r="I8" s="167"/>
+      <c r="J8" s="168"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="164"/>
-      <c r="B9" s="165"/>
-      <c r="C9" s="165"/>
-      <c r="D9" s="165"/>
-      <c r="E9" s="165"/>
-      <c r="F9" s="165"/>
-      <c r="G9" s="165"/>
-      <c r="H9" s="165"/>
-      <c r="I9" s="165"/>
-      <c r="J9" s="166"/>
+      <c r="A9" s="166"/>
+      <c r="B9" s="167"/>
+      <c r="C9" s="167"/>
+      <c r="D9" s="167"/>
+      <c r="E9" s="167"/>
+      <c r="F9" s="167"/>
+      <c r="G9" s="167"/>
+      <c r="H9" s="167"/>
+      <c r="I9" s="167"/>
+      <c r="J9" s="168"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="164"/>
-      <c r="B10" s="165"/>
-      <c r="C10" s="165"/>
-      <c r="D10" s="165"/>
-      <c r="E10" s="165"/>
-      <c r="F10" s="165"/>
-      <c r="G10" s="165"/>
-      <c r="H10" s="165"/>
-      <c r="I10" s="165"/>
-      <c r="J10" s="166"/>
+      <c r="A10" s="166"/>
+      <c r="B10" s="167"/>
+      <c r="C10" s="167"/>
+      <c r="D10" s="167"/>
+      <c r="E10" s="167"/>
+      <c r="F10" s="167"/>
+      <c r="G10" s="167"/>
+      <c r="H10" s="167"/>
+      <c r="I10" s="167"/>
+      <c r="J10" s="168"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="164"/>
-      <c r="B11" s="165"/>
-      <c r="C11" s="165"/>
-      <c r="D11" s="165"/>
-      <c r="E11" s="165"/>
-      <c r="F11" s="165"/>
-      <c r="G11" s="165"/>
-      <c r="H11" s="165"/>
-      <c r="I11" s="165"/>
-      <c r="J11" s="166"/>
+      <c r="A11" s="166"/>
+      <c r="B11" s="167"/>
+      <c r="C11" s="167"/>
+      <c r="D11" s="167"/>
+      <c r="E11" s="167"/>
+      <c r="F11" s="167"/>
+      <c r="G11" s="167"/>
+      <c r="H11" s="167"/>
+      <c r="I11" s="167"/>
+      <c r="J11" s="168"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="164"/>
-      <c r="B12" s="165"/>
-      <c r="C12" s="165"/>
-      <c r="D12" s="165"/>
-      <c r="E12" s="165"/>
-      <c r="F12" s="165"/>
-      <c r="G12" s="165"/>
-      <c r="H12" s="165"/>
-      <c r="I12" s="165"/>
-      <c r="J12" s="166"/>
+      <c r="A12" s="166"/>
+      <c r="B12" s="167"/>
+      <c r="C12" s="167"/>
+      <c r="D12" s="167"/>
+      <c r="E12" s="167"/>
+      <c r="F12" s="167"/>
+      <c r="G12" s="167"/>
+      <c r="H12" s="167"/>
+      <c r="I12" s="167"/>
+      <c r="J12" s="168"/>
     </row>
     <row r="13" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A13" s="164"/>
-      <c r="B13" s="165"/>
-      <c r="C13" s="165"/>
-      <c r="D13" s="165"/>
-      <c r="E13" s="165"/>
-      <c r="F13" s="165"/>
-      <c r="G13" s="165"/>
-      <c r="H13" s="165"/>
-      <c r="I13" s="165"/>
-      <c r="J13" s="166"/>
+      <c r="A13" s="166"/>
+      <c r="B13" s="167"/>
+      <c r="C13" s="167"/>
+      <c r="D13" s="167"/>
+      <c r="E13" s="167"/>
+      <c r="F13" s="167"/>
+      <c r="G13" s="167"/>
+      <c r="H13" s="167"/>
+      <c r="I13" s="167"/>
+      <c r="J13" s="168"/>
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A14" s="185" t="s">
+      <c r="A14" s="162" t="s">
         <v>24</v>
       </c>
       <c r="B14" s="157"/>
@@ -14601,7 +14541,7 @@
       <c r="J14" s="160"/>
     </row>
     <row r="15" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A15" s="185" t="s">
+      <c r="A15" s="162" t="s">
         <v>25</v>
       </c>
       <c r="B15" s="157"/>
@@ -14621,7 +14561,7 @@
       </c>
     </row>
     <row r="16" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A16" s="185" t="s">
+      <c r="A16" s="162" t="s">
         <v>27</v>
       </c>
       <c r="B16" s="157"/>
@@ -14638,7 +14578,7 @@
       <c r="G16" s="39" t="s">
         <v>31</v>
       </c>
-      <c r="H16" s="186" t="s">
+      <c r="H16" s="161" t="s">
         <v>18</v>
       </c>
       <c r="I16" s="157"/>
@@ -15810,23 +15750,6 @@
     <row r="1000" s="36" customFormat="1" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="33">
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="H19:J19"/>
-    <mergeCell ref="A23:C23"/>
-    <mergeCell ref="H23:J23"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="H20:J20"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="H21:J21"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="H22:J22"/>
-    <mergeCell ref="H16:J16"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="A15:C15"/>
-    <mergeCell ref="D15:H15"/>
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="H17:J17"/>
     <mergeCell ref="A24:C24"/>
     <mergeCell ref="H24:J24"/>
     <mergeCell ref="A7:J13"/>
@@ -15843,6 +15766,23 @@
     <mergeCell ref="A6:J6"/>
     <mergeCell ref="A14:J14"/>
     <mergeCell ref="A16:C16"/>
+    <mergeCell ref="H16:J16"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="H18:J18"/>
+    <mergeCell ref="A15:C15"/>
+    <mergeCell ref="D15:H15"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="H17:J17"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="H19:J19"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="H23:J23"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="H20:J20"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="H21:J21"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="H22:J22"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -15866,19 +15806,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="195" t="s">
+      <c r="A1" s="192" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="93"/>
-      <c r="C1" s="94"/>
-      <c r="D1" s="101" t="s">
+      <c r="B1" s="122"/>
+      <c r="C1" s="123"/>
+      <c r="D1" s="130" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="102"/>
-      <c r="F1" s="101" t="s">
+      <c r="E1" s="115"/>
+      <c r="F1" s="130" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="102"/>
+      <c r="G1" s="115"/>
       <c r="H1" s="35" t="s">
         <v>6</v>
       </c>
@@ -15890,190 +15830,190 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="95"/>
-      <c r="B2" s="96"/>
-      <c r="C2" s="97"/>
-      <c r="D2" s="103" t="s">
+      <c r="A2" s="124"/>
+      <c r="B2" s="125"/>
+      <c r="C2" s="126"/>
+      <c r="D2" s="131" t="s">
         <v>85</v>
       </c>
-      <c r="E2" s="104"/>
-      <c r="F2" s="103">
+      <c r="E2" s="132"/>
+      <c r="F2" s="131">
         <v>56</v>
       </c>
-      <c r="G2" s="104"/>
-      <c r="H2" s="107">
+      <c r="G2" s="132"/>
+      <c r="H2" s="100">
         <v>45805</v>
       </c>
-      <c r="I2" s="121" t="s">
+      <c r="I2" s="109" t="s">
         <v>83</v>
       </c>
-      <c r="J2" s="122"/>
+      <c r="J2" s="110"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="95"/>
-      <c r="B3" s="96"/>
-      <c r="C3" s="97"/>
-      <c r="D3" s="105"/>
-      <c r="E3" s="97"/>
-      <c r="F3" s="105"/>
-      <c r="G3" s="97"/>
-      <c r="H3" s="108"/>
-      <c r="I3" s="108"/>
-      <c r="J3" s="123"/>
+      <c r="A3" s="124"/>
+      <c r="B3" s="125"/>
+      <c r="C3" s="126"/>
+      <c r="D3" s="133"/>
+      <c r="E3" s="126"/>
+      <c r="F3" s="133"/>
+      <c r="G3" s="126"/>
+      <c r="H3" s="101"/>
+      <c r="I3" s="101"/>
+      <c r="J3" s="111"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="95"/>
-      <c r="B4" s="96"/>
-      <c r="C4" s="97"/>
-      <c r="D4" s="105"/>
-      <c r="E4" s="97"/>
-      <c r="F4" s="105"/>
-      <c r="G4" s="97"/>
-      <c r="H4" s="108"/>
-      <c r="I4" s="108"/>
-      <c r="J4" s="123"/>
+      <c r="A4" s="124"/>
+      <c r="B4" s="125"/>
+      <c r="C4" s="126"/>
+      <c r="D4" s="133"/>
+      <c r="E4" s="126"/>
+      <c r="F4" s="133"/>
+      <c r="G4" s="126"/>
+      <c r="H4" s="101"/>
+      <c r="I4" s="101"/>
+      <c r="J4" s="111"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="196" t="s">
+      <c r="A5" s="193" t="s">
         <v>22</v>
       </c>
-      <c r="B5" s="126"/>
-      <c r="C5" s="102"/>
-      <c r="D5" s="197" t="s">
+      <c r="B5" s="114"/>
+      <c r="C5" s="115"/>
+      <c r="D5" s="194" t="s">
         <v>86</v>
       </c>
-      <c r="E5" s="126"/>
-      <c r="F5" s="126"/>
-      <c r="G5" s="126"/>
-      <c r="H5" s="126"/>
-      <c r="I5" s="126"/>
-      <c r="J5" s="128"/>
+      <c r="E5" s="114"/>
+      <c r="F5" s="114"/>
+      <c r="G5" s="114"/>
+      <c r="H5" s="114"/>
+      <c r="I5" s="114"/>
+      <c r="J5" s="117"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="189" t="s">
+      <c r="A6" s="187" t="s">
         <v>23</v>
       </c>
-      <c r="B6" s="111"/>
-      <c r="C6" s="111"/>
-      <c r="D6" s="111"/>
-      <c r="E6" s="111"/>
-      <c r="F6" s="111"/>
-      <c r="G6" s="111"/>
-      <c r="H6" s="111"/>
-      <c r="I6" s="111"/>
-      <c r="J6" s="114"/>
+      <c r="B6" s="98"/>
+      <c r="C6" s="98"/>
+      <c r="D6" s="98"/>
+      <c r="E6" s="98"/>
+      <c r="F6" s="98"/>
+      <c r="G6" s="98"/>
+      <c r="H6" s="98"/>
+      <c r="I6" s="98"/>
+      <c r="J6" s="99"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="191"/>
-      <c r="B7" s="192"/>
-      <c r="C7" s="192"/>
-      <c r="D7" s="192"/>
-      <c r="E7" s="192"/>
-      <c r="F7" s="192"/>
-      <c r="G7" s="192"/>
-      <c r="H7" s="192"/>
-      <c r="I7" s="192"/>
-      <c r="J7" s="193"/>
+      <c r="A7" s="188"/>
+      <c r="B7" s="189"/>
+      <c r="C7" s="189"/>
+      <c r="D7" s="189"/>
+      <c r="E7" s="189"/>
+      <c r="F7" s="189"/>
+      <c r="G7" s="189"/>
+      <c r="H7" s="189"/>
+      <c r="I7" s="189"/>
+      <c r="J7" s="190"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="95"/>
-      <c r="B8" s="96"/>
-      <c r="C8" s="96"/>
-      <c r="D8" s="96"/>
-      <c r="E8" s="96"/>
-      <c r="F8" s="96"/>
-      <c r="G8" s="96"/>
-      <c r="H8" s="96"/>
-      <c r="I8" s="96"/>
-      <c r="J8" s="194"/>
+      <c r="A8" s="124"/>
+      <c r="B8" s="125"/>
+      <c r="C8" s="125"/>
+      <c r="D8" s="125"/>
+      <c r="E8" s="125"/>
+      <c r="F8" s="125"/>
+      <c r="G8" s="125"/>
+      <c r="H8" s="125"/>
+      <c r="I8" s="125"/>
+      <c r="J8" s="191"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="95"/>
-      <c r="B9" s="96"/>
-      <c r="C9" s="96"/>
-      <c r="D9" s="96"/>
-      <c r="E9" s="96"/>
-      <c r="F9" s="96"/>
-      <c r="G9" s="96"/>
-      <c r="H9" s="96"/>
-      <c r="I9" s="96"/>
-      <c r="J9" s="194"/>
+      <c r="A9" s="124"/>
+      <c r="B9" s="125"/>
+      <c r="C9" s="125"/>
+      <c r="D9" s="125"/>
+      <c r="E9" s="125"/>
+      <c r="F9" s="125"/>
+      <c r="G9" s="125"/>
+      <c r="H9" s="125"/>
+      <c r="I9" s="125"/>
+      <c r="J9" s="191"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="95"/>
-      <c r="B10" s="96"/>
-      <c r="C10" s="96"/>
-      <c r="D10" s="96"/>
-      <c r="E10" s="96"/>
-      <c r="F10" s="96"/>
-      <c r="G10" s="96"/>
-      <c r="H10" s="96"/>
-      <c r="I10" s="96"/>
-      <c r="J10" s="194"/>
+      <c r="A10" s="124"/>
+      <c r="B10" s="125"/>
+      <c r="C10" s="125"/>
+      <c r="D10" s="125"/>
+      <c r="E10" s="125"/>
+      <c r="F10" s="125"/>
+      <c r="G10" s="125"/>
+      <c r="H10" s="125"/>
+      <c r="I10" s="125"/>
+      <c r="J10" s="191"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="95"/>
-      <c r="B11" s="96"/>
-      <c r="C11" s="96"/>
-      <c r="D11" s="96"/>
-      <c r="E11" s="96"/>
-      <c r="F11" s="96"/>
-      <c r="G11" s="96"/>
-      <c r="H11" s="96"/>
-      <c r="I11" s="96"/>
-      <c r="J11" s="194"/>
+      <c r="A11" s="124"/>
+      <c r="B11" s="125"/>
+      <c r="C11" s="125"/>
+      <c r="D11" s="125"/>
+      <c r="E11" s="125"/>
+      <c r="F11" s="125"/>
+      <c r="G11" s="125"/>
+      <c r="H11" s="125"/>
+      <c r="I11" s="125"/>
+      <c r="J11" s="191"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="95"/>
-      <c r="B12" s="96"/>
-      <c r="C12" s="96"/>
-      <c r="D12" s="96"/>
-      <c r="E12" s="96"/>
-      <c r="F12" s="96"/>
-      <c r="G12" s="96"/>
-      <c r="H12" s="96"/>
-      <c r="I12" s="96"/>
-      <c r="J12" s="194"/>
+      <c r="A12" s="124"/>
+      <c r="B12" s="125"/>
+      <c r="C12" s="125"/>
+      <c r="D12" s="125"/>
+      <c r="E12" s="125"/>
+      <c r="F12" s="125"/>
+      <c r="G12" s="125"/>
+      <c r="H12" s="125"/>
+      <c r="I12" s="125"/>
+      <c r="J12" s="191"/>
     </row>
     <row r="13" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A13" s="95"/>
-      <c r="B13" s="96"/>
-      <c r="C13" s="96"/>
-      <c r="D13" s="96"/>
-      <c r="E13" s="96"/>
-      <c r="F13" s="96"/>
-      <c r="G13" s="96"/>
-      <c r="H13" s="96"/>
-      <c r="I13" s="96"/>
-      <c r="J13" s="194"/>
+      <c r="A13" s="124"/>
+      <c r="B13" s="125"/>
+      <c r="C13" s="125"/>
+      <c r="D13" s="125"/>
+      <c r="E13" s="125"/>
+      <c r="F13" s="125"/>
+      <c r="G13" s="125"/>
+      <c r="H13" s="125"/>
+      <c r="I13" s="125"/>
+      <c r="J13" s="191"/>
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A14" s="189" t="s">
+      <c r="A14" s="187" t="s">
         <v>24</v>
       </c>
-      <c r="B14" s="111"/>
-      <c r="C14" s="111"/>
-      <c r="D14" s="111"/>
-      <c r="E14" s="111"/>
-      <c r="F14" s="111"/>
-      <c r="G14" s="111"/>
-      <c r="H14" s="111"/>
-      <c r="I14" s="111"/>
-      <c r="J14" s="114"/>
+      <c r="B14" s="98"/>
+      <c r="C14" s="98"/>
+      <c r="D14" s="98"/>
+      <c r="E14" s="98"/>
+      <c r="F14" s="98"/>
+      <c r="G14" s="98"/>
+      <c r="H14" s="98"/>
+      <c r="I14" s="98"/>
+      <c r="J14" s="99"/>
     </row>
     <row r="15" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A15" s="189" t="s">
+      <c r="A15" s="187" t="s">
         <v>25</v>
       </c>
-      <c r="B15" s="111"/>
-      <c r="C15" s="112"/>
-      <c r="D15" s="120" t="s">
+      <c r="B15" s="98"/>
+      <c r="C15" s="93"/>
+      <c r="D15" s="97" t="s">
         <v>87</v>
       </c>
-      <c r="E15" s="111"/>
-      <c r="F15" s="111"/>
-      <c r="G15" s="111"/>
-      <c r="H15" s="112"/>
+      <c r="E15" s="98"/>
+      <c r="F15" s="98"/>
+      <c r="G15" s="98"/>
+      <c r="H15" s="93"/>
       <c r="I15" s="45" t="s">
         <v>26</v>
       </c>
@@ -16082,11 +16022,11 @@
       </c>
     </row>
     <row r="16" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A16" s="189" t="s">
+      <c r="A16" s="187" t="s">
         <v>27</v>
       </c>
-      <c r="B16" s="111"/>
-      <c r="C16" s="112"/>
+      <c r="B16" s="98"/>
+      <c r="C16" s="93"/>
       <c r="D16" s="45" t="s">
         <v>28</v>
       </c>
@@ -16099,18 +16039,18 @@
       <c r="G16" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="H16" s="190" t="s">
+      <c r="H16" s="195" t="s">
         <v>18</v>
       </c>
-      <c r="I16" s="111"/>
-      <c r="J16" s="114"/>
+      <c r="I16" s="98"/>
+      <c r="J16" s="99"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="187">
+      <c r="A17" s="196">
         <v>1</v>
       </c>
-      <c r="B17" s="111"/>
-      <c r="C17" s="112"/>
+      <c r="B17" s="98"/>
+      <c r="C17" s="93"/>
       <c r="D17" s="47" t="s">
         <v>64</v>
       </c>
@@ -16123,83 +16063,83 @@
       <c r="G17" s="48" t="s">
         <v>89</v>
       </c>
-      <c r="H17" s="120" t="s">
+      <c r="H17" s="97" t="s">
         <v>90</v>
       </c>
-      <c r="I17" s="111"/>
-      <c r="J17" s="114"/>
+      <c r="I17" s="98"/>
+      <c r="J17" s="99"/>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A18" s="187"/>
-      <c r="B18" s="111"/>
-      <c r="C18" s="112"/>
+      <c r="A18" s="196"/>
+      <c r="B18" s="98"/>
+      <c r="C18" s="93"/>
       <c r="D18" s="47"/>
       <c r="E18" s="47"/>
       <c r="F18" s="48"/>
       <c r="G18" s="48"/>
-      <c r="H18" s="120"/>
-      <c r="I18" s="111"/>
-      <c r="J18" s="114"/>
+      <c r="H18" s="97"/>
+      <c r="I18" s="98"/>
+      <c r="J18" s="99"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="187"/>
-      <c r="B19" s="111"/>
-      <c r="C19" s="112"/>
+      <c r="A19" s="196"/>
+      <c r="B19" s="98"/>
+      <c r="C19" s="93"/>
       <c r="D19" s="47"/>
       <c r="E19" s="47"/>
       <c r="F19" s="48"/>
       <c r="G19" s="48"/>
-      <c r="H19" s="120"/>
-      <c r="I19" s="111"/>
-      <c r="J19" s="114"/>
+      <c r="H19" s="97"/>
+      <c r="I19" s="98"/>
+      <c r="J19" s="99"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="187"/>
-      <c r="B20" s="111"/>
-      <c r="C20" s="112"/>
+      <c r="A20" s="196"/>
+      <c r="B20" s="98"/>
+      <c r="C20" s="93"/>
       <c r="D20" s="47"/>
       <c r="E20" s="47"/>
       <c r="F20" s="48"/>
       <c r="G20" s="48"/>
-      <c r="H20" s="120"/>
-      <c r="I20" s="111"/>
-      <c r="J20" s="114"/>
+      <c r="H20" s="97"/>
+      <c r="I20" s="98"/>
+      <c r="J20" s="99"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="187"/>
-      <c r="B21" s="111"/>
-      <c r="C21" s="112"/>
+      <c r="A21" s="196"/>
+      <c r="B21" s="98"/>
+      <c r="C21" s="93"/>
       <c r="D21" s="47"/>
       <c r="E21" s="47"/>
       <c r="F21" s="48"/>
       <c r="G21" s="48"/>
-      <c r="H21" s="120"/>
-      <c r="I21" s="111"/>
-      <c r="J21" s="114"/>
+      <c r="H21" s="97"/>
+      <c r="I21" s="98"/>
+      <c r="J21" s="99"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="187"/>
-      <c r="B22" s="111"/>
-      <c r="C22" s="112"/>
+      <c r="A22" s="196"/>
+      <c r="B22" s="98"/>
+      <c r="C22" s="93"/>
       <c r="D22" s="47"/>
       <c r="E22" s="47"/>
       <c r="F22" s="48"/>
       <c r="G22" s="48"/>
-      <c r="H22" s="120"/>
-      <c r="I22" s="111"/>
-      <c r="J22" s="114"/>
+      <c r="H22" s="97"/>
+      <c r="I22" s="98"/>
+      <c r="J22" s="99"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A23" s="188"/>
-      <c r="B23" s="116"/>
-      <c r="C23" s="117"/>
+      <c r="A23" s="197"/>
+      <c r="B23" s="105"/>
+      <c r="C23" s="106"/>
       <c r="D23" s="49"/>
       <c r="E23" s="49"/>
       <c r="F23" s="50"/>
       <c r="G23" s="50"/>
-      <c r="H23" s="118"/>
-      <c r="I23" s="116"/>
-      <c r="J23" s="119"/>
+      <c r="H23" s="107"/>
+      <c r="I23" s="105"/>
+      <c r="J23" s="108"/>
     </row>
     <row r="24" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="25" spans="1:10" ht="12.75" customHeight="1"/>
@@ -17180,6 +17120,22 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="31">
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="H23:J23"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="H19:J19"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="H20:J20"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="H21:J21"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="H16:J16"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="H18:J18"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="H17:J17"/>
     <mergeCell ref="A14:J14"/>
     <mergeCell ref="A15:C15"/>
     <mergeCell ref="A7:J13"/>
@@ -17195,22 +17151,6 @@
     <mergeCell ref="D5:J5"/>
     <mergeCell ref="A6:J6"/>
     <mergeCell ref="D15:H15"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="H16:J16"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="H17:J17"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="H22:J22"/>
-    <mergeCell ref="A23:C23"/>
-    <mergeCell ref="H23:J23"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="H19:J19"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="H20:J20"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="H21:J21"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -17234,19 +17174,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="195" t="s">
+      <c r="A1" s="192" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="93"/>
-      <c r="C1" s="94"/>
-      <c r="D1" s="101" t="s">
+      <c r="B1" s="122"/>
+      <c r="C1" s="123"/>
+      <c r="D1" s="130" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="102"/>
-      <c r="F1" s="101" t="s">
+      <c r="E1" s="115"/>
+      <c r="F1" s="130" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="102"/>
+      <c r="G1" s="115"/>
       <c r="H1" s="35" t="s">
         <v>6</v>
       </c>
@@ -17258,190 +17198,190 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="95"/>
-      <c r="B2" s="96"/>
-      <c r="C2" s="97"/>
-      <c r="D2" s="103" t="s">
+      <c r="A2" s="124"/>
+      <c r="B2" s="125"/>
+      <c r="C2" s="126"/>
+      <c r="D2" s="131" t="s">
         <v>84</v>
       </c>
-      <c r="E2" s="104"/>
-      <c r="F2" s="103">
+      <c r="E2" s="132"/>
+      <c r="F2" s="131">
         <v>56</v>
       </c>
-      <c r="G2" s="104"/>
-      <c r="H2" s="107">
+      <c r="G2" s="132"/>
+      <c r="H2" s="100">
         <v>45805</v>
       </c>
-      <c r="I2" s="121" t="s">
+      <c r="I2" s="109" t="s">
         <v>83</v>
       </c>
-      <c r="J2" s="122"/>
+      <c r="J2" s="110"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="95"/>
-      <c r="B3" s="96"/>
-      <c r="C3" s="97"/>
-      <c r="D3" s="105"/>
-      <c r="E3" s="97"/>
-      <c r="F3" s="105"/>
-      <c r="G3" s="97"/>
-      <c r="H3" s="108"/>
-      <c r="I3" s="108"/>
-      <c r="J3" s="123"/>
+      <c r="A3" s="124"/>
+      <c r="B3" s="125"/>
+      <c r="C3" s="126"/>
+      <c r="D3" s="133"/>
+      <c r="E3" s="126"/>
+      <c r="F3" s="133"/>
+      <c r="G3" s="126"/>
+      <c r="H3" s="101"/>
+      <c r="I3" s="101"/>
+      <c r="J3" s="111"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="95"/>
-      <c r="B4" s="96"/>
-      <c r="C4" s="97"/>
-      <c r="D4" s="105"/>
-      <c r="E4" s="97"/>
-      <c r="F4" s="105"/>
-      <c r="G4" s="97"/>
-      <c r="H4" s="108"/>
-      <c r="I4" s="108"/>
-      <c r="J4" s="123"/>
+      <c r="A4" s="124"/>
+      <c r="B4" s="125"/>
+      <c r="C4" s="126"/>
+      <c r="D4" s="133"/>
+      <c r="E4" s="126"/>
+      <c r="F4" s="133"/>
+      <c r="G4" s="126"/>
+      <c r="H4" s="101"/>
+      <c r="I4" s="101"/>
+      <c r="J4" s="111"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="196" t="s">
+      <c r="A5" s="193" t="s">
         <v>22</v>
       </c>
-      <c r="B5" s="126"/>
-      <c r="C5" s="102"/>
-      <c r="D5" s="197" t="s">
+      <c r="B5" s="114"/>
+      <c r="C5" s="115"/>
+      <c r="D5" s="194" t="s">
         <v>91</v>
       </c>
-      <c r="E5" s="126"/>
-      <c r="F5" s="126"/>
-      <c r="G5" s="126"/>
-      <c r="H5" s="126"/>
-      <c r="I5" s="126"/>
-      <c r="J5" s="128"/>
+      <c r="E5" s="114"/>
+      <c r="F5" s="114"/>
+      <c r="G5" s="114"/>
+      <c r="H5" s="114"/>
+      <c r="I5" s="114"/>
+      <c r="J5" s="117"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="189" t="s">
+      <c r="A6" s="187" t="s">
         <v>23</v>
       </c>
-      <c r="B6" s="111"/>
-      <c r="C6" s="111"/>
-      <c r="D6" s="111"/>
-      <c r="E6" s="111"/>
-      <c r="F6" s="111"/>
-      <c r="G6" s="111"/>
-      <c r="H6" s="111"/>
-      <c r="I6" s="111"/>
-      <c r="J6" s="114"/>
+      <c r="B6" s="98"/>
+      <c r="C6" s="98"/>
+      <c r="D6" s="98"/>
+      <c r="E6" s="98"/>
+      <c r="F6" s="98"/>
+      <c r="G6" s="98"/>
+      <c r="H6" s="98"/>
+      <c r="I6" s="98"/>
+      <c r="J6" s="99"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="191"/>
-      <c r="B7" s="192"/>
-      <c r="C7" s="192"/>
-      <c r="D7" s="192"/>
-      <c r="E7" s="192"/>
-      <c r="F7" s="192"/>
-      <c r="G7" s="192"/>
-      <c r="H7" s="192"/>
-      <c r="I7" s="192"/>
-      <c r="J7" s="193"/>
+      <c r="A7" s="188"/>
+      <c r="B7" s="189"/>
+      <c r="C7" s="189"/>
+      <c r="D7" s="189"/>
+      <c r="E7" s="189"/>
+      <c r="F7" s="189"/>
+      <c r="G7" s="189"/>
+      <c r="H7" s="189"/>
+      <c r="I7" s="189"/>
+      <c r="J7" s="190"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="95"/>
-      <c r="B8" s="96"/>
-      <c r="C8" s="96"/>
-      <c r="D8" s="96"/>
-      <c r="E8" s="96"/>
-      <c r="F8" s="96"/>
-      <c r="G8" s="96"/>
-      <c r="H8" s="96"/>
-      <c r="I8" s="96"/>
-      <c r="J8" s="194"/>
+      <c r="A8" s="124"/>
+      <c r="B8" s="125"/>
+      <c r="C8" s="125"/>
+      <c r="D8" s="125"/>
+      <c r="E8" s="125"/>
+      <c r="F8" s="125"/>
+      <c r="G8" s="125"/>
+      <c r="H8" s="125"/>
+      <c r="I8" s="125"/>
+      <c r="J8" s="191"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="95"/>
-      <c r="B9" s="96"/>
-      <c r="C9" s="96"/>
-      <c r="D9" s="96"/>
-      <c r="E9" s="96"/>
-      <c r="F9" s="96"/>
-      <c r="G9" s="96"/>
-      <c r="H9" s="96"/>
-      <c r="I9" s="96"/>
-      <c r="J9" s="194"/>
+      <c r="A9" s="124"/>
+      <c r="B9" s="125"/>
+      <c r="C9" s="125"/>
+      <c r="D9" s="125"/>
+      <c r="E9" s="125"/>
+      <c r="F9" s="125"/>
+      <c r="G9" s="125"/>
+      <c r="H9" s="125"/>
+      <c r="I9" s="125"/>
+      <c r="J9" s="191"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="95"/>
-      <c r="B10" s="96"/>
-      <c r="C10" s="96"/>
-      <c r="D10" s="96"/>
-      <c r="E10" s="96"/>
-      <c r="F10" s="96"/>
-      <c r="G10" s="96"/>
-      <c r="H10" s="96"/>
-      <c r="I10" s="96"/>
-      <c r="J10" s="194"/>
+      <c r="A10" s="124"/>
+      <c r="B10" s="125"/>
+      <c r="C10" s="125"/>
+      <c r="D10" s="125"/>
+      <c r="E10" s="125"/>
+      <c r="F10" s="125"/>
+      <c r="G10" s="125"/>
+      <c r="H10" s="125"/>
+      <c r="I10" s="125"/>
+      <c r="J10" s="191"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="95"/>
-      <c r="B11" s="96"/>
-      <c r="C11" s="96"/>
-      <c r="D11" s="96"/>
-      <c r="E11" s="96"/>
-      <c r="F11" s="96"/>
-      <c r="G11" s="96"/>
-      <c r="H11" s="96"/>
-      <c r="I11" s="96"/>
-      <c r="J11" s="194"/>
+      <c r="A11" s="124"/>
+      <c r="B11" s="125"/>
+      <c r="C11" s="125"/>
+      <c r="D11" s="125"/>
+      <c r="E11" s="125"/>
+      <c r="F11" s="125"/>
+      <c r="G11" s="125"/>
+      <c r="H11" s="125"/>
+      <c r="I11" s="125"/>
+      <c r="J11" s="191"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="95"/>
-      <c r="B12" s="96"/>
-      <c r="C12" s="96"/>
-      <c r="D12" s="96"/>
-      <c r="E12" s="96"/>
-      <c r="F12" s="96"/>
-      <c r="G12" s="96"/>
-      <c r="H12" s="96"/>
-      <c r="I12" s="96"/>
-      <c r="J12" s="194"/>
+      <c r="A12" s="124"/>
+      <c r="B12" s="125"/>
+      <c r="C12" s="125"/>
+      <c r="D12" s="125"/>
+      <c r="E12" s="125"/>
+      <c r="F12" s="125"/>
+      <c r="G12" s="125"/>
+      <c r="H12" s="125"/>
+      <c r="I12" s="125"/>
+      <c r="J12" s="191"/>
     </row>
     <row r="13" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A13" s="95"/>
-      <c r="B13" s="96"/>
-      <c r="C13" s="96"/>
-      <c r="D13" s="96"/>
-      <c r="E13" s="96"/>
-      <c r="F13" s="96"/>
-      <c r="G13" s="96"/>
-      <c r="H13" s="96"/>
-      <c r="I13" s="96"/>
-      <c r="J13" s="194"/>
+      <c r="A13" s="124"/>
+      <c r="B13" s="125"/>
+      <c r="C13" s="125"/>
+      <c r="D13" s="125"/>
+      <c r="E13" s="125"/>
+      <c r="F13" s="125"/>
+      <c r="G13" s="125"/>
+      <c r="H13" s="125"/>
+      <c r="I13" s="125"/>
+      <c r="J13" s="191"/>
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A14" s="189" t="s">
+      <c r="A14" s="187" t="s">
         <v>24</v>
       </c>
-      <c r="B14" s="111"/>
-      <c r="C14" s="111"/>
-      <c r="D14" s="111"/>
-      <c r="E14" s="111"/>
-      <c r="F14" s="111"/>
-      <c r="G14" s="111"/>
-      <c r="H14" s="111"/>
-      <c r="I14" s="111"/>
-      <c r="J14" s="114"/>
+      <c r="B14" s="98"/>
+      <c r="C14" s="98"/>
+      <c r="D14" s="98"/>
+      <c r="E14" s="98"/>
+      <c r="F14" s="98"/>
+      <c r="G14" s="98"/>
+      <c r="H14" s="98"/>
+      <c r="I14" s="98"/>
+      <c r="J14" s="99"/>
     </row>
     <row r="15" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A15" s="189" t="s">
+      <c r="A15" s="187" t="s">
         <v>25</v>
       </c>
-      <c r="B15" s="111"/>
-      <c r="C15" s="112"/>
-      <c r="D15" s="120" t="s">
+      <c r="B15" s="98"/>
+      <c r="C15" s="93"/>
+      <c r="D15" s="97" t="s">
         <v>87</v>
       </c>
-      <c r="E15" s="111"/>
-      <c r="F15" s="111"/>
-      <c r="G15" s="111"/>
-      <c r="H15" s="112"/>
+      <c r="E15" s="98"/>
+      <c r="F15" s="98"/>
+      <c r="G15" s="98"/>
+      <c r="H15" s="93"/>
       <c r="I15" s="45" t="s">
         <v>26</v>
       </c>
@@ -17450,11 +17390,11 @@
       </c>
     </row>
     <row r="16" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A16" s="189" t="s">
+      <c r="A16" s="187" t="s">
         <v>27</v>
       </c>
-      <c r="B16" s="111"/>
-      <c r="C16" s="112"/>
+      <c r="B16" s="98"/>
+      <c r="C16" s="93"/>
       <c r="D16" s="45" t="s">
         <v>28</v>
       </c>
@@ -17467,18 +17407,18 @@
       <c r="G16" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="H16" s="190" t="s">
+      <c r="H16" s="195" t="s">
         <v>18</v>
       </c>
-      <c r="I16" s="111"/>
-      <c r="J16" s="114"/>
+      <c r="I16" s="98"/>
+      <c r="J16" s="99"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="187">
+      <c r="A17" s="196">
         <v>1</v>
       </c>
-      <c r="B17" s="111"/>
-      <c r="C17" s="112"/>
+      <c r="B17" s="98"/>
+      <c r="C17" s="93"/>
       <c r="D17" s="47" t="s">
         <v>64</v>
       </c>
@@ -17491,83 +17431,83 @@
       <c r="G17" s="48" t="s">
         <v>89</v>
       </c>
-      <c r="H17" s="120" t="s">
+      <c r="H17" s="97" t="s">
         <v>90</v>
       </c>
-      <c r="I17" s="111"/>
-      <c r="J17" s="114"/>
+      <c r="I17" s="98"/>
+      <c r="J17" s="99"/>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A18" s="187"/>
-      <c r="B18" s="111"/>
-      <c r="C18" s="112"/>
+      <c r="A18" s="196"/>
+      <c r="B18" s="98"/>
+      <c r="C18" s="93"/>
       <c r="D18" s="47"/>
       <c r="E18" s="47"/>
       <c r="F18" s="48"/>
       <c r="G18" s="48"/>
-      <c r="H18" s="120"/>
-      <c r="I18" s="111"/>
-      <c r="J18" s="114"/>
+      <c r="H18" s="97"/>
+      <c r="I18" s="98"/>
+      <c r="J18" s="99"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="187"/>
-      <c r="B19" s="111"/>
-      <c r="C19" s="112"/>
+      <c r="A19" s="196"/>
+      <c r="B19" s="98"/>
+      <c r="C19" s="93"/>
       <c r="D19" s="47"/>
       <c r="E19" s="47"/>
       <c r="F19" s="48"/>
       <c r="G19" s="48"/>
-      <c r="H19" s="120"/>
-      <c r="I19" s="111"/>
-      <c r="J19" s="114"/>
+      <c r="H19" s="97"/>
+      <c r="I19" s="98"/>
+      <c r="J19" s="99"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="187"/>
-      <c r="B20" s="111"/>
-      <c r="C20" s="112"/>
+      <c r="A20" s="196"/>
+      <c r="B20" s="98"/>
+      <c r="C20" s="93"/>
       <c r="D20" s="47"/>
       <c r="E20" s="47"/>
       <c r="F20" s="48"/>
       <c r="G20" s="48"/>
-      <c r="H20" s="120"/>
-      <c r="I20" s="111"/>
-      <c r="J20" s="114"/>
+      <c r="H20" s="97"/>
+      <c r="I20" s="98"/>
+      <c r="J20" s="99"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="187"/>
-      <c r="B21" s="111"/>
-      <c r="C21" s="112"/>
+      <c r="A21" s="196"/>
+      <c r="B21" s="98"/>
+      <c r="C21" s="93"/>
       <c r="D21" s="47"/>
       <c r="E21" s="47"/>
       <c r="F21" s="48"/>
       <c r="G21" s="48"/>
-      <c r="H21" s="120"/>
-      <c r="I21" s="111"/>
-      <c r="J21" s="114"/>
+      <c r="H21" s="97"/>
+      <c r="I21" s="98"/>
+      <c r="J21" s="99"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="187"/>
-      <c r="B22" s="111"/>
-      <c r="C22" s="112"/>
+      <c r="A22" s="196"/>
+      <c r="B22" s="98"/>
+      <c r="C22" s="93"/>
       <c r="D22" s="47"/>
       <c r="E22" s="47"/>
       <c r="F22" s="48"/>
       <c r="G22" s="48"/>
-      <c r="H22" s="120"/>
-      <c r="I22" s="111"/>
-      <c r="J22" s="114"/>
+      <c r="H22" s="97"/>
+      <c r="I22" s="98"/>
+      <c r="J22" s="99"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A23" s="188"/>
-      <c r="B23" s="116"/>
-      <c r="C23" s="117"/>
+      <c r="A23" s="197"/>
+      <c r="B23" s="105"/>
+      <c r="C23" s="106"/>
       <c r="D23" s="49"/>
       <c r="E23" s="49"/>
       <c r="F23" s="50"/>
       <c r="G23" s="50"/>
-      <c r="H23" s="118"/>
-      <c r="I23" s="116"/>
-      <c r="J23" s="119"/>
+      <c r="H23" s="107"/>
+      <c r="I23" s="105"/>
+      <c r="J23" s="108"/>
     </row>
     <row r="24" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="25" spans="1:10" ht="12.75" customHeight="1"/>
@@ -18548,6 +18488,22 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="31">
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="H23:J23"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="H19:J19"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="H20:J20"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="H21:J21"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="H16:J16"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="H18:J18"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="H17:J17"/>
     <mergeCell ref="A14:J14"/>
     <mergeCell ref="A15:C15"/>
     <mergeCell ref="A7:J13"/>
@@ -18563,22 +18519,6 @@
     <mergeCell ref="D5:J5"/>
     <mergeCell ref="A6:J6"/>
     <mergeCell ref="D15:H15"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="H16:J16"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="H17:J17"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="H22:J22"/>
-    <mergeCell ref="A23:C23"/>
-    <mergeCell ref="H23:J23"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="H19:J19"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="H20:J20"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="H21:J21"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -18598,7 +18538,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="18" customHeight="1">
-      <c r="A1" s="213" t="s">
+      <c r="A1" s="224" t="s">
         <v>32</v>
       </c>
       <c r="B1" s="143"/>
@@ -18609,14 +18549,14 @@
       <c r="G1" s="150" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="214"/>
-      <c r="I1" s="214"/>
+      <c r="H1" s="209"/>
+      <c r="I1" s="209"/>
       <c r="J1" s="151"/>
       <c r="K1" s="150" t="s">
         <v>5</v>
       </c>
-      <c r="L1" s="214"/>
-      <c r="M1" s="214"/>
+      <c r="L1" s="209"/>
+      <c r="M1" s="209"/>
       <c r="N1" s="151"/>
       <c r="O1" s="150" t="s">
         <v>6</v>
@@ -18629,7 +18569,7 @@
       <c r="S1" s="150" t="s">
         <v>8</v>
       </c>
-      <c r="T1" s="215"/>
+      <c r="T1" s="211"/>
     </row>
     <row r="2" spans="1:26" ht="18" customHeight="1">
       <c r="A2" s="145"/>
@@ -18641,16 +18581,16 @@
       <c r="G2" s="152" t="s">
         <v>84</v>
       </c>
-      <c r="H2" s="208"/>
-      <c r="I2" s="208"/>
+      <c r="H2" s="219"/>
+      <c r="I2" s="219"/>
       <c r="J2" s="153"/>
       <c r="K2" s="152" t="s">
         <v>54</v>
       </c>
-      <c r="L2" s="208"/>
-      <c r="M2" s="208"/>
+      <c r="L2" s="219"/>
+      <c r="M2" s="219"/>
       <c r="N2" s="153"/>
-      <c r="O2" s="209">
+      <c r="O2" s="220">
         <v>45821</v>
       </c>
       <c r="P2" s="153"/>
@@ -18659,7 +18599,7 @@
       </c>
       <c r="R2" s="153"/>
       <c r="S2" s="152"/>
-      <c r="T2" s="210"/>
+      <c r="T2" s="221"/>
     </row>
     <row r="3" spans="1:26" ht="18" customHeight="1">
       <c r="A3" s="145"/>
@@ -18681,7 +18621,7 @@
       <c r="Q3" s="154"/>
       <c r="R3" s="146"/>
       <c r="S3" s="154"/>
-      <c r="T3" s="211"/>
+      <c r="T3" s="222"/>
     </row>
     <row r="4" spans="1:26" ht="18" customHeight="1">
       <c r="A4" s="147"/>
@@ -18703,36 +18643,36 @@
       <c r="Q4" s="155"/>
       <c r="R4" s="149"/>
       <c r="S4" s="155"/>
-      <c r="T4" s="212"/>
+      <c r="T4" s="223"/>
     </row>
     <row r="5" spans="1:26" ht="18" customHeight="1">
-      <c r="A5" s="216" t="s">
+      <c r="A5" s="208" t="s">
         <v>33</v>
       </c>
-      <c r="B5" s="214"/>
-      <c r="C5" s="214"/>
-      <c r="D5" s="214"/>
-      <c r="E5" s="214"/>
+      <c r="B5" s="209"/>
+      <c r="C5" s="209"/>
+      <c r="D5" s="209"/>
+      <c r="E5" s="209"/>
       <c r="F5" s="151"/>
-      <c r="G5" s="217" t="s">
+      <c r="G5" s="210" t="s">
         <v>34</v>
       </c>
-      <c r="H5" s="214"/>
-      <c r="I5" s="214"/>
-      <c r="J5" s="214"/>
-      <c r="K5" s="214"/>
-      <c r="L5" s="214"/>
-      <c r="M5" s="214"/>
-      <c r="N5" s="214"/>
-      <c r="O5" s="214"/>
-      <c r="P5" s="214"/>
-      <c r="Q5" s="214"/>
-      <c r="R5" s="214"/>
-      <c r="S5" s="214"/>
-      <c r="T5" s="215"/>
+      <c r="H5" s="209"/>
+      <c r="I5" s="209"/>
+      <c r="J5" s="209"/>
+      <c r="K5" s="209"/>
+      <c r="L5" s="209"/>
+      <c r="M5" s="209"/>
+      <c r="N5" s="209"/>
+      <c r="O5" s="209"/>
+      <c r="P5" s="209"/>
+      <c r="Q5" s="209"/>
+      <c r="R5" s="209"/>
+      <c r="S5" s="209"/>
+      <c r="T5" s="211"/>
     </row>
     <row r="6" spans="1:26" ht="18" customHeight="1">
-      <c r="A6" s="218" t="s">
+      <c r="A6" s="212" t="s">
         <v>35</v>
       </c>
       <c r="B6" s="84"/>
@@ -18740,7 +18680,7 @@
       <c r="D6" s="84"/>
       <c r="E6" s="84"/>
       <c r="F6" s="85"/>
-      <c r="G6" s="219" t="s">
+      <c r="G6" s="213" t="s">
         <v>19</v>
       </c>
       <c r="H6" s="84"/>
@@ -18755,10 +18695,10 @@
       <c r="Q6" s="84"/>
       <c r="R6" s="84"/>
       <c r="S6" s="84"/>
-      <c r="T6" s="220"/>
+      <c r="T6" s="214"/>
     </row>
     <row r="7" spans="1:26" ht="18" customHeight="1">
-      <c r="A7" s="218" t="s">
+      <c r="A7" s="212" t="s">
         <v>36</v>
       </c>
       <c r="B7" s="84"/>
@@ -18766,7 +18706,7 @@
       <c r="D7" s="84"/>
       <c r="E7" s="84"/>
       <c r="F7" s="85"/>
-      <c r="G7" s="219" t="s">
+      <c r="G7" s="213" t="s">
         <v>111</v>
       </c>
       <c r="H7" s="84"/>
@@ -18781,7 +18721,7 @@
       <c r="Q7" s="84"/>
       <c r="R7" s="84"/>
       <c r="S7" s="84"/>
-      <c r="T7" s="220"/>
+      <c r="T7" s="214"/>
     </row>
     <row r="8" spans="1:26" ht="7.5" customHeight="1">
       <c r="A8" s="7"/>
@@ -18980,33 +18920,33 @@
       <c r="T14" s="9"/>
     </row>
     <row r="15" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A15" s="218" t="s">
+      <c r="A15" s="212" t="s">
         <v>43</v>
       </c>
       <c r="B15" s="85"/>
-      <c r="C15" s="224" t="s">
+      <c r="C15" s="218" t="s">
         <v>37</v>
       </c>
       <c r="D15" s="85"/>
-      <c r="E15" s="198" t="s">
+      <c r="E15" s="216" t="s">
         <v>44</v>
       </c>
       <c r="F15" s="85"/>
-      <c r="G15" s="198" t="s">
+      <c r="G15" s="216" t="s">
         <v>45</v>
       </c>
       <c r="H15" s="84"/>
       <c r="I15" s="85"/>
-      <c r="J15" s="198" t="s">
+      <c r="J15" s="216" t="s">
         <v>46</v>
       </c>
       <c r="K15" s="85"/>
-      <c r="L15" s="198" t="s">
+      <c r="L15" s="216" t="s">
         <v>47</v>
       </c>
       <c r="M15" s="84"/>
       <c r="N15" s="85"/>
-      <c r="O15" s="198" t="s">
+      <c r="O15" s="216" t="s">
         <v>48</v>
       </c>
       <c r="P15" s="84"/>
@@ -19022,33 +18962,33 @@
       </c>
     </row>
     <row r="16" spans="1:26" ht="48" customHeight="1">
-      <c r="A16" s="221">
+      <c r="A16" s="198">
         <v>1</v>
       </c>
       <c r="B16" s="85"/>
-      <c r="C16" s="222" t="s">
+      <c r="C16" s="199" t="s">
         <v>52</v>
       </c>
       <c r="D16" s="85"/>
-      <c r="E16" s="222" t="s">
+      <c r="E16" s="199" t="s">
         <v>53</v>
       </c>
       <c r="F16" s="85"/>
-      <c r="G16" s="199" t="s">
+      <c r="G16" s="215" t="s">
         <v>112</v>
       </c>
       <c r="H16" s="84"/>
       <c r="I16" s="85"/>
-      <c r="J16" s="200" t="s">
+      <c r="J16" s="228" t="s">
         <v>113</v>
       </c>
-      <c r="K16" s="112"/>
-      <c r="L16" s="204" t="s">
+      <c r="K16" s="93"/>
+      <c r="L16" s="205" t="s">
         <v>114</v>
       </c>
       <c r="M16" s="84"/>
       <c r="N16" s="85"/>
-      <c r="O16" s="204" t="s">
+      <c r="O16" s="205" t="s">
         <v>115</v>
       </c>
       <c r="P16" s="84"/>
@@ -19070,33 +19010,33 @@
       <c r="Z16" s="29"/>
     </row>
     <row r="17" spans="1:26" ht="51" customHeight="1">
-      <c r="A17" s="221">
+      <c r="A17" s="198">
         <v>2</v>
       </c>
       <c r="B17" s="85"/>
-      <c r="C17" s="222" t="s">
+      <c r="C17" s="199" t="s">
         <v>52</v>
       </c>
       <c r="D17" s="85"/>
-      <c r="E17" s="222" t="s">
+      <c r="E17" s="199" t="s">
         <v>118</v>
       </c>
       <c r="F17" s="85"/>
-      <c r="G17" s="199" t="s">
+      <c r="G17" s="215" t="s">
         <v>116</v>
       </c>
       <c r="H17" s="84"/>
       <c r="I17" s="85"/>
-      <c r="J17" s="199" t="s">
+      <c r="J17" s="215" t="s">
         <v>117</v>
       </c>
       <c r="K17" s="85"/>
-      <c r="L17" s="223" t="s">
+      <c r="L17" s="217" t="s">
         <v>119</v>
       </c>
       <c r="M17" s="84"/>
       <c r="N17" s="85"/>
-      <c r="O17" s="204" t="s">
+      <c r="O17" s="205" t="s">
         <v>122</v>
       </c>
       <c r="P17" s="84"/>
@@ -19118,33 +19058,33 @@
       <c r="Z17" s="29"/>
     </row>
     <row r="18" spans="1:26" ht="120" customHeight="1">
-      <c r="A18" s="221">
+      <c r="A18" s="198">
         <v>3</v>
       </c>
       <c r="B18" s="85"/>
-      <c r="C18" s="222" t="s">
+      <c r="C18" s="199" t="s">
         <v>52</v>
       </c>
       <c r="D18" s="85"/>
-      <c r="E18" s="222" t="s">
+      <c r="E18" s="199" t="s">
         <v>53</v>
       </c>
       <c r="F18" s="85"/>
-      <c r="G18" s="199" t="s">
+      <c r="G18" s="215" t="s">
         <v>139</v>
       </c>
       <c r="H18" s="84"/>
       <c r="I18" s="85"/>
-      <c r="J18" s="199" t="s">
+      <c r="J18" s="215" t="s">
         <v>140</v>
       </c>
       <c r="K18" s="85"/>
-      <c r="L18" s="204" t="s">
+      <c r="L18" s="205" t="s">
         <v>114</v>
       </c>
       <c r="M18" s="84"/>
       <c r="N18" s="85"/>
-      <c r="O18" s="204" t="s">
+      <c r="O18" s="205" t="s">
         <v>120</v>
       </c>
       <c r="P18" s="84"/>
@@ -19166,33 +19106,33 @@
       <c r="Z18" s="29"/>
     </row>
     <row r="19" spans="1:26" ht="94.5" customHeight="1">
-      <c r="A19" s="221">
+      <c r="A19" s="198">
         <v>4</v>
       </c>
       <c r="B19" s="85"/>
-      <c r="C19" s="222" t="s">
+      <c r="C19" s="199" t="s">
         <v>52</v>
       </c>
       <c r="D19" s="85"/>
-      <c r="E19" s="222" t="s">
+      <c r="E19" s="199" t="s">
         <v>118</v>
       </c>
       <c r="F19" s="85"/>
-      <c r="G19" s="199" t="s">
+      <c r="G19" s="215" t="s">
         <v>141</v>
       </c>
       <c r="H19" s="84"/>
       <c r="I19" s="85"/>
-      <c r="J19" s="199" t="s">
+      <c r="J19" s="215" t="s">
         <v>142</v>
       </c>
       <c r="K19" s="85"/>
-      <c r="L19" s="204" t="s">
+      <c r="L19" s="205" t="s">
         <v>114</v>
       </c>
       <c r="M19" s="84"/>
       <c r="N19" s="85"/>
-      <c r="O19" s="204" t="s">
+      <c r="O19" s="205" t="s">
         <v>121</v>
       </c>
       <c r="P19" s="84"/>
@@ -19214,33 +19154,33 @@
       <c r="Z19" s="29"/>
     </row>
     <row r="20" spans="1:26" ht="120" customHeight="1">
-      <c r="A20" s="221">
+      <c r="A20" s="198">
         <v>5</v>
       </c>
       <c r="B20" s="85"/>
-      <c r="C20" s="222" t="s">
+      <c r="C20" s="199" t="s">
         <v>138</v>
       </c>
       <c r="D20" s="85"/>
-      <c r="E20" s="222" t="s">
+      <c r="E20" s="199" t="s">
         <v>143</v>
       </c>
       <c r="F20" s="85"/>
-      <c r="G20" s="199" t="s">
+      <c r="G20" s="215" t="s">
         <v>146</v>
       </c>
       <c r="H20" s="84"/>
       <c r="I20" s="85"/>
-      <c r="J20" s="199" t="s">
+      <c r="J20" s="215" t="s">
         <v>145</v>
       </c>
       <c r="K20" s="85"/>
-      <c r="L20" s="204" t="s">
+      <c r="L20" s="205" t="s">
         <v>114</v>
       </c>
       <c r="M20" s="84"/>
       <c r="N20" s="85"/>
-      <c r="O20" s="204" t="s">
+      <c r="O20" s="205" t="s">
         <v>120</v>
       </c>
       <c r="P20" s="84"/>
@@ -19260,33 +19200,33 @@
       <c r="Z20" s="29"/>
     </row>
     <row r="21" spans="1:26" ht="75" customHeight="1">
-      <c r="A21" s="221">
+      <c r="A21" s="198">
         <v>6</v>
       </c>
       <c r="B21" s="85"/>
-      <c r="C21" s="222" t="s">
+      <c r="C21" s="199" t="s">
         <v>138</v>
       </c>
       <c r="D21" s="85"/>
-      <c r="E21" s="222" t="s">
+      <c r="E21" s="199" t="s">
         <v>118</v>
       </c>
       <c r="F21" s="85"/>
-      <c r="G21" s="199" t="s">
+      <c r="G21" s="215" t="s">
         <v>154</v>
       </c>
       <c r="H21" s="84"/>
       <c r="I21" s="85"/>
-      <c r="J21" s="199" t="s">
+      <c r="J21" s="215" t="s">
         <v>144</v>
       </c>
       <c r="K21" s="85"/>
-      <c r="L21" s="204" t="s">
+      <c r="L21" s="205" t="s">
         <v>114</v>
       </c>
       <c r="M21" s="84"/>
       <c r="N21" s="85"/>
-      <c r="O21" s="204" t="s">
+      <c r="O21" s="205" t="s">
         <v>121</v>
       </c>
       <c r="P21" s="84"/>
@@ -19308,33 +19248,33 @@
       <c r="Z21" s="29"/>
     </row>
     <row r="22" spans="1:26" ht="57" customHeight="1">
-      <c r="A22" s="225">
+      <c r="A22" s="203">
         <v>7</v>
       </c>
-      <c r="B22" s="112"/>
-      <c r="C22" s="226" t="s">
+      <c r="B22" s="93"/>
+      <c r="C22" s="204" t="s">
         <v>52</v>
       </c>
-      <c r="D22" s="112"/>
-      <c r="E22" s="226" t="s">
+      <c r="D22" s="93"/>
+      <c r="E22" s="204" t="s">
         <v>165</v>
       </c>
-      <c r="F22" s="112"/>
-      <c r="G22" s="200" t="s">
+      <c r="F22" s="93"/>
+      <c r="G22" s="228" t="s">
         <v>166</v>
       </c>
-      <c r="H22" s="111"/>
-      <c r="I22" s="112"/>
-      <c r="J22" s="200" t="s">
+      <c r="H22" s="98"/>
+      <c r="I22" s="93"/>
+      <c r="J22" s="228" t="s">
         <v>117</v>
       </c>
-      <c r="K22" s="112"/>
-      <c r="L22" s="206" t="s">
+      <c r="K22" s="93"/>
+      <c r="L22" s="225" t="s">
         <v>119</v>
       </c>
-      <c r="M22" s="207"/>
-      <c r="N22" s="207"/>
-      <c r="O22" s="204" t="s">
+      <c r="M22" s="226"/>
+      <c r="N22" s="226"/>
+      <c r="O22" s="205" t="s">
         <v>167</v>
       </c>
       <c r="P22" s="84"/>
@@ -19355,47 +19295,27 @@
       <c r="Y22" s="29"/>
       <c r="Z22" s="29"/>
     </row>
-    <row r="23" spans="1:26" ht="88.5" customHeight="1">
-      <c r="A23" s="225">
-        <v>8</v>
-      </c>
-      <c r="B23" s="112"/>
-      <c r="C23" s="226" t="s">
-        <v>52</v>
-      </c>
-      <c r="D23" s="112"/>
-      <c r="E23" s="222" t="s">
-        <v>143</v>
-      </c>
+    <row r="23" spans="1:26" ht="12.75" customHeight="1">
+      <c r="A23" s="198"/>
+      <c r="B23" s="85"/>
+      <c r="C23" s="199"/>
+      <c r="D23" s="85"/>
+      <c r="E23" s="199"/>
       <c r="F23" s="85"/>
-      <c r="G23" s="199" t="s">
-        <v>169</v>
-      </c>
+      <c r="G23" s="215"/>
       <c r="H23" s="84"/>
       <c r="I23" s="85"/>
-      <c r="J23" s="199" t="s">
-        <v>170</v>
-      </c>
+      <c r="J23" s="215"/>
       <c r="K23" s="85"/>
-      <c r="L23" s="204" t="s">
-        <v>171</v>
-      </c>
+      <c r="L23" s="205"/>
       <c r="M23" s="84"/>
       <c r="N23" s="85"/>
-      <c r="O23" s="204" t="s">
-        <v>115</v>
-      </c>
+      <c r="O23" s="205"/>
       <c r="P23" s="84"/>
       <c r="Q23" s="85"/>
-      <c r="R23" s="65">
-        <v>45826</v>
-      </c>
-      <c r="S23" s="27" t="s">
-        <v>110</v>
-      </c>
-      <c r="T23" s="28" t="s">
-        <v>168</v>
-      </c>
+      <c r="R23" s="27"/>
+      <c r="S23" s="27"/>
+      <c r="T23" s="28"/>
       <c r="U23" s="29"/>
       <c r="V23" s="29"/>
       <c r="W23" s="29"/>
@@ -19404,21 +19324,21 @@
       <c r="Z23" s="29"/>
     </row>
     <row r="24" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A24" s="221"/>
+      <c r="A24" s="198"/>
       <c r="B24" s="85"/>
-      <c r="C24" s="222"/>
+      <c r="C24" s="199"/>
       <c r="D24" s="85"/>
-      <c r="E24" s="222"/>
+      <c r="E24" s="199"/>
       <c r="F24" s="85"/>
-      <c r="G24" s="199"/>
+      <c r="G24" s="215"/>
       <c r="H24" s="84"/>
       <c r="I24" s="85"/>
-      <c r="J24" s="199"/>
+      <c r="J24" s="215"/>
       <c r="K24" s="85"/>
-      <c r="L24" s="204"/>
+      <c r="L24" s="205"/>
       <c r="M24" s="84"/>
       <c r="N24" s="85"/>
-      <c r="O24" s="204"/>
+      <c r="O24" s="205"/>
       <c r="P24" s="84"/>
       <c r="Q24" s="85"/>
       <c r="R24" s="27"/>
@@ -19432,21 +19352,21 @@
       <c r="Z24" s="29"/>
     </row>
     <row r="25" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A25" s="221"/>
+      <c r="A25" s="198"/>
       <c r="B25" s="85"/>
-      <c r="C25" s="222"/>
+      <c r="C25" s="199"/>
       <c r="D25" s="85"/>
-      <c r="E25" s="222"/>
+      <c r="E25" s="199"/>
       <c r="F25" s="85"/>
-      <c r="G25" s="199"/>
+      <c r="G25" s="215"/>
       <c r="H25" s="84"/>
       <c r="I25" s="85"/>
-      <c r="J25" s="199"/>
+      <c r="J25" s="215"/>
       <c r="K25" s="85"/>
-      <c r="L25" s="204"/>
+      <c r="L25" s="205"/>
       <c r="M25" s="84"/>
       <c r="N25" s="85"/>
-      <c r="O25" s="204"/>
+      <c r="O25" s="205"/>
       <c r="P25" s="84"/>
       <c r="Q25" s="85"/>
       <c r="R25" s="27"/>
@@ -19460,21 +19380,21 @@
       <c r="Z25" s="29"/>
     </row>
     <row r="26" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A26" s="221"/>
+      <c r="A26" s="198"/>
       <c r="B26" s="85"/>
-      <c r="C26" s="222"/>
+      <c r="C26" s="199"/>
       <c r="D26" s="85"/>
-      <c r="E26" s="222"/>
+      <c r="E26" s="199"/>
       <c r="F26" s="85"/>
-      <c r="G26" s="199"/>
+      <c r="G26" s="215"/>
       <c r="H26" s="84"/>
       <c r="I26" s="85"/>
-      <c r="J26" s="199"/>
+      <c r="J26" s="215"/>
       <c r="K26" s="85"/>
-      <c r="L26" s="204"/>
+      <c r="L26" s="205"/>
       <c r="M26" s="84"/>
       <c r="N26" s="85"/>
-      <c r="O26" s="204"/>
+      <c r="O26" s="205"/>
       <c r="P26" s="84"/>
       <c r="Q26" s="85"/>
       <c r="R26" s="27"/>
@@ -19488,21 +19408,21 @@
       <c r="Z26" s="29"/>
     </row>
     <row r="27" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A27" s="221"/>
+      <c r="A27" s="198"/>
       <c r="B27" s="85"/>
-      <c r="C27" s="222"/>
+      <c r="C27" s="199"/>
       <c r="D27" s="85"/>
-      <c r="E27" s="222"/>
+      <c r="E27" s="199"/>
       <c r="F27" s="85"/>
-      <c r="G27" s="199"/>
+      <c r="G27" s="215"/>
       <c r="H27" s="84"/>
       <c r="I27" s="85"/>
-      <c r="J27" s="199"/>
+      <c r="J27" s="215"/>
       <c r="K27" s="85"/>
-      <c r="L27" s="204"/>
+      <c r="L27" s="205"/>
       <c r="M27" s="84"/>
       <c r="N27" s="85"/>
-      <c r="O27" s="204"/>
+      <c r="O27" s="205"/>
       <c r="P27" s="84"/>
       <c r="Q27" s="85"/>
       <c r="R27" s="27"/>
@@ -19516,21 +19436,21 @@
       <c r="Z27" s="29"/>
     </row>
     <row r="28" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A28" s="221"/>
+      <c r="A28" s="198"/>
       <c r="B28" s="85"/>
-      <c r="C28" s="222"/>
+      <c r="C28" s="199"/>
       <c r="D28" s="85"/>
-      <c r="E28" s="222"/>
+      <c r="E28" s="199"/>
       <c r="F28" s="85"/>
-      <c r="G28" s="199"/>
+      <c r="G28" s="215"/>
       <c r="H28" s="84"/>
       <c r="I28" s="85"/>
-      <c r="J28" s="199"/>
+      <c r="J28" s="215"/>
       <c r="K28" s="85"/>
-      <c r="L28" s="204"/>
+      <c r="L28" s="205"/>
       <c r="M28" s="84"/>
       <c r="N28" s="85"/>
-      <c r="O28" s="204"/>
+      <c r="O28" s="205"/>
       <c r="P28" s="84"/>
       <c r="Q28" s="85"/>
       <c r="R28" s="27"/>
@@ -19544,21 +19464,21 @@
       <c r="Z28" s="29"/>
     </row>
     <row r="29" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A29" s="221"/>
+      <c r="A29" s="198"/>
       <c r="B29" s="85"/>
-      <c r="C29" s="222"/>
+      <c r="C29" s="199"/>
       <c r="D29" s="85"/>
-      <c r="E29" s="222"/>
+      <c r="E29" s="199"/>
       <c r="F29" s="85"/>
-      <c r="G29" s="199"/>
+      <c r="G29" s="215"/>
       <c r="H29" s="84"/>
       <c r="I29" s="85"/>
-      <c r="J29" s="199"/>
+      <c r="J29" s="215"/>
       <c r="K29" s="85"/>
-      <c r="L29" s="204"/>
+      <c r="L29" s="205"/>
       <c r="M29" s="84"/>
       <c r="N29" s="85"/>
-      <c r="O29" s="204"/>
+      <c r="O29" s="205"/>
       <c r="P29" s="84"/>
       <c r="Q29" s="85"/>
       <c r="R29" s="27"/>
@@ -19572,21 +19492,21 @@
       <c r="Z29" s="29"/>
     </row>
     <row r="30" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A30" s="221"/>
+      <c r="A30" s="198"/>
       <c r="B30" s="85"/>
-      <c r="C30" s="222"/>
+      <c r="C30" s="199"/>
       <c r="D30" s="85"/>
-      <c r="E30" s="222"/>
+      <c r="E30" s="199"/>
       <c r="F30" s="85"/>
-      <c r="G30" s="199"/>
+      <c r="G30" s="215"/>
       <c r="H30" s="84"/>
       <c r="I30" s="85"/>
-      <c r="J30" s="199"/>
+      <c r="J30" s="215"/>
       <c r="K30" s="85"/>
-      <c r="L30" s="204"/>
+      <c r="L30" s="205"/>
       <c r="M30" s="84"/>
       <c r="N30" s="85"/>
-      <c r="O30" s="204"/>
+      <c r="O30" s="205"/>
       <c r="P30" s="84"/>
       <c r="Q30" s="85"/>
       <c r="R30" s="27"/>
@@ -19600,23 +19520,23 @@
       <c r="Z30" s="29"/>
     </row>
     <row r="31" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A31" s="227"/>
-      <c r="B31" s="203"/>
-      <c r="C31" s="228"/>
-      <c r="D31" s="203"/>
-      <c r="E31" s="228"/>
-      <c r="F31" s="203"/>
-      <c r="G31" s="201"/>
-      <c r="H31" s="202"/>
-      <c r="I31" s="203"/>
-      <c r="J31" s="201"/>
-      <c r="K31" s="203"/>
-      <c r="L31" s="205"/>
-      <c r="M31" s="202"/>
-      <c r="N31" s="203"/>
-      <c r="O31" s="205"/>
-      <c r="P31" s="202"/>
-      <c r="Q31" s="203"/>
+      <c r="A31" s="200"/>
+      <c r="B31" s="201"/>
+      <c r="C31" s="202"/>
+      <c r="D31" s="201"/>
+      <c r="E31" s="202"/>
+      <c r="F31" s="201"/>
+      <c r="G31" s="227"/>
+      <c r="H31" s="207"/>
+      <c r="I31" s="201"/>
+      <c r="J31" s="227"/>
+      <c r="K31" s="201"/>
+      <c r="L31" s="206"/>
+      <c r="M31" s="207"/>
+      <c r="N31" s="201"/>
+      <c r="O31" s="206"/>
+      <c r="P31" s="207"/>
+      <c r="Q31" s="201"/>
       <c r="R31" s="30"/>
       <c r="S31" s="30"/>
       <c r="T31" s="31"/>
@@ -20614,6 +20534,118 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="136">
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="J19:K19"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="J30:K30"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="J29:K29"/>
+    <mergeCell ref="L26:N26"/>
+    <mergeCell ref="L27:N27"/>
+    <mergeCell ref="L28:N28"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="L18:N18"/>
+    <mergeCell ref="L19:N19"/>
+    <mergeCell ref="L21:N21"/>
+    <mergeCell ref="L22:N22"/>
+    <mergeCell ref="L23:N23"/>
+    <mergeCell ref="L24:N24"/>
+    <mergeCell ref="L25:N25"/>
+    <mergeCell ref="K2:N4"/>
+    <mergeCell ref="O2:P4"/>
+    <mergeCell ref="Q2:R4"/>
+    <mergeCell ref="S2:T4"/>
+    <mergeCell ref="A1:F4"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="S1:T1"/>
+    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="G5:T5"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="G6:T6"/>
+    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="G7:T7"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="G20:I20"/>
+    <mergeCell ref="J20:K20"/>
+    <mergeCell ref="L20:N20"/>
+    <mergeCell ref="O20:Q20"/>
+    <mergeCell ref="L15:N15"/>
+    <mergeCell ref="O15:Q15"/>
+    <mergeCell ref="L16:N16"/>
+    <mergeCell ref="O16:Q16"/>
+    <mergeCell ref="L17:N17"/>
+    <mergeCell ref="O17:Q17"/>
+    <mergeCell ref="O18:Q18"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="O27:Q27"/>
+    <mergeCell ref="O28:Q28"/>
+    <mergeCell ref="O29:Q29"/>
+    <mergeCell ref="O30:Q30"/>
+    <mergeCell ref="O31:Q31"/>
+    <mergeCell ref="O19:Q19"/>
+    <mergeCell ref="O21:Q21"/>
+    <mergeCell ref="O22:Q22"/>
+    <mergeCell ref="O23:Q23"/>
+    <mergeCell ref="O24:Q24"/>
+    <mergeCell ref="O25:Q25"/>
+    <mergeCell ref="O26:Q26"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="A23:B23"/>
     <mergeCell ref="A30:B30"/>
     <mergeCell ref="C30:D30"/>
     <mergeCell ref="E30:F30"/>
@@ -20638,118 +20670,6 @@
     <mergeCell ref="C28:D28"/>
     <mergeCell ref="E28:F28"/>
     <mergeCell ref="A29:B29"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="O27:Q27"/>
-    <mergeCell ref="O28:Q28"/>
-    <mergeCell ref="O29:Q29"/>
-    <mergeCell ref="O30:Q30"/>
-    <mergeCell ref="O31:Q31"/>
-    <mergeCell ref="O19:Q19"/>
-    <mergeCell ref="O21:Q21"/>
-    <mergeCell ref="O22:Q22"/>
-    <mergeCell ref="O23:Q23"/>
-    <mergeCell ref="O24:Q24"/>
-    <mergeCell ref="O25:Q25"/>
-    <mergeCell ref="O26:Q26"/>
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="G5:T5"/>
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="G6:T6"/>
-    <mergeCell ref="A7:F7"/>
-    <mergeCell ref="G7:T7"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="G20:I20"/>
-    <mergeCell ref="J20:K20"/>
-    <mergeCell ref="L20:N20"/>
-    <mergeCell ref="O20:Q20"/>
-    <mergeCell ref="L15:N15"/>
-    <mergeCell ref="O15:Q15"/>
-    <mergeCell ref="L16:N16"/>
-    <mergeCell ref="O16:Q16"/>
-    <mergeCell ref="L17:N17"/>
-    <mergeCell ref="O17:Q17"/>
-    <mergeCell ref="O18:Q18"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="K2:N4"/>
-    <mergeCell ref="O2:P4"/>
-    <mergeCell ref="Q2:R4"/>
-    <mergeCell ref="S2:T4"/>
-    <mergeCell ref="A1:F4"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="O1:P1"/>
-    <mergeCell ref="Q1:R1"/>
-    <mergeCell ref="S1:T1"/>
-    <mergeCell ref="G2:J4"/>
-    <mergeCell ref="L26:N26"/>
-    <mergeCell ref="L27:N27"/>
-    <mergeCell ref="L28:N28"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="L18:N18"/>
-    <mergeCell ref="L19:N19"/>
-    <mergeCell ref="L21:N21"/>
-    <mergeCell ref="L22:N22"/>
-    <mergeCell ref="L23:N23"/>
-    <mergeCell ref="L24:N24"/>
-    <mergeCell ref="L25:N25"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="J30:K30"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="J29:K29"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="G23:I23"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="J18:K18"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="J19:K19"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <hyperlinks>
@@ -20776,72 +20696,72 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="18.75" customHeight="1">
-      <c r="A1" s="249" t="s">
+      <c r="A1" s="238" t="s">
         <v>123</v>
       </c>
-      <c r="B1" s="249"/>
-      <c r="C1" s="250" t="s">
+      <c r="B1" s="238"/>
+      <c r="C1" s="239" t="s">
         <v>124</v>
       </c>
-      <c r="D1" s="251"/>
-      <c r="E1" s="252"/>
-      <c r="F1" s="253" t="s">
+      <c r="D1" s="240"/>
+      <c r="E1" s="241"/>
+      <c r="F1" s="242" t="s">
         <v>84</v>
       </c>
-      <c r="G1" s="254"/>
-      <c r="H1" s="254"/>
-      <c r="I1" s="254"/>
-      <c r="J1" s="254"/>
-      <c r="K1" s="254"/>
-      <c r="L1" s="254"/>
-      <c r="M1" s="255"/>
+      <c r="G1" s="243"/>
+      <c r="H1" s="243"/>
+      <c r="I1" s="243"/>
+      <c r="J1" s="243"/>
+      <c r="K1" s="243"/>
+      <c r="L1" s="243"/>
+      <c r="M1" s="244"/>
       <c r="N1" s="51" t="s">
         <v>125</v>
       </c>
-      <c r="O1" s="253" t="s">
+      <c r="O1" s="242" t="s">
         <v>83</v>
       </c>
-      <c r="P1" s="255"/>
+      <c r="P1" s="244"/>
       <c r="Q1" s="51" t="s">
         <v>126</v>
       </c>
-      <c r="R1" s="253" t="s">
+      <c r="R1" s="242" t="s">
         <v>127</v>
       </c>
-      <c r="S1" s="255"/>
+      <c r="S1" s="244"/>
     </row>
     <row r="2" spans="1:19" ht="18.75" customHeight="1">
-      <c r="A2" s="249"/>
-      <c r="B2" s="249"/>
-      <c r="C2" s="250" t="s">
+      <c r="A2" s="238"/>
+      <c r="B2" s="238"/>
+      <c r="C2" s="239" t="s">
         <v>128</v>
       </c>
-      <c r="D2" s="251"/>
-      <c r="E2" s="252"/>
-      <c r="F2" s="253" t="s">
+      <c r="D2" s="240"/>
+      <c r="E2" s="241"/>
+      <c r="F2" s="242" t="s">
         <v>147</v>
       </c>
-      <c r="G2" s="254"/>
-      <c r="H2" s="254"/>
-      <c r="I2" s="254"/>
-      <c r="J2" s="254"/>
-      <c r="K2" s="254"/>
-      <c r="L2" s="254"/>
-      <c r="M2" s="255"/>
+      <c r="G2" s="243"/>
+      <c r="H2" s="243"/>
+      <c r="I2" s="243"/>
+      <c r="J2" s="243"/>
+      <c r="K2" s="243"/>
+      <c r="L2" s="243"/>
+      <c r="M2" s="244"/>
       <c r="N2" s="51" t="s">
         <v>129</v>
       </c>
-      <c r="O2" s="256">
+      <c r="O2" s="245">
         <v>45824</v>
       </c>
-      <c r="P2" s="257"/>
+      <c r="P2" s="246"/>
       <c r="Q2" s="53" t="s">
         <v>130</v>
       </c>
-      <c r="R2" s="258">
+      <c r="R2" s="247">
         <v>44771</v>
       </c>
-      <c r="S2" s="259"/>
+      <c r="S2" s="248"/>
     </row>
     <row r="3" spans="1:19" ht="11.25" customHeight="1">
       <c r="A3" s="54"/>
@@ -20871,33 +20791,33 @@
       <c r="B4" s="57" t="s">
         <v>132</v>
       </c>
-      <c r="C4" s="241" t="s">
+      <c r="C4" s="229" t="s">
         <v>133</v>
       </c>
-      <c r="D4" s="242"/>
-      <c r="E4" s="242"/>
-      <c r="F4" s="242"/>
-      <c r="G4" s="243"/>
-      <c r="H4" s="241" t="s">
+      <c r="D4" s="230"/>
+      <c r="E4" s="230"/>
+      <c r="F4" s="230"/>
+      <c r="G4" s="231"/>
+      <c r="H4" s="229" t="s">
         <v>134</v>
       </c>
-      <c r="I4" s="242"/>
-      <c r="J4" s="242"/>
-      <c r="K4" s="242"/>
-      <c r="L4" s="242"/>
-      <c r="M4" s="243"/>
-      <c r="N4" s="241" t="s">
+      <c r="I4" s="230"/>
+      <c r="J4" s="230"/>
+      <c r="K4" s="230"/>
+      <c r="L4" s="230"/>
+      <c r="M4" s="231"/>
+      <c r="N4" s="229" t="s">
         <v>135</v>
       </c>
-      <c r="O4" s="242"/>
-      <c r="P4" s="243"/>
+      <c r="O4" s="230"/>
+      <c r="P4" s="231"/>
       <c r="Q4" s="56" t="s">
         <v>136</v>
       </c>
-      <c r="R4" s="241" t="s">
+      <c r="R4" s="229" t="s">
         <v>137</v>
       </c>
-      <c r="S4" s="243"/>
+      <c r="S4" s="231"/>
     </row>
     <row r="5" spans="1:19" ht="50.1" customHeight="1">
       <c r="A5" s="58">
@@ -20906,31 +20826,31 @@
       <c r="B5" s="59" t="s">
         <v>148</v>
       </c>
-      <c r="C5" s="237" t="s">
+      <c r="C5" s="232" t="s">
         <v>150</v>
       </c>
-      <c r="D5" s="237"/>
-      <c r="E5" s="237"/>
-      <c r="F5" s="237"/>
-      <c r="G5" s="237"/>
-      <c r="H5" s="237" t="s">
+      <c r="D5" s="232"/>
+      <c r="E5" s="232"/>
+      <c r="F5" s="232"/>
+      <c r="G5" s="232"/>
+      <c r="H5" s="232" t="s">
         <v>149</v>
       </c>
-      <c r="I5" s="237"/>
-      <c r="J5" s="237"/>
-      <c r="K5" s="237"/>
-      <c r="L5" s="237"/>
-      <c r="M5" s="237"/>
-      <c r="N5" s="244" t="s">
+      <c r="I5" s="232"/>
+      <c r="J5" s="232"/>
+      <c r="K5" s="232"/>
+      <c r="L5" s="232"/>
+      <c r="M5" s="232"/>
+      <c r="N5" s="233" t="s">
         <v>151</v>
       </c>
-      <c r="O5" s="245"/>
-      <c r="P5" s="246"/>
+      <c r="O5" s="234"/>
+      <c r="P5" s="235"/>
       <c r="Q5" s="64">
         <v>45824</v>
       </c>
-      <c r="R5" s="247"/>
-      <c r="S5" s="248"/>
+      <c r="R5" s="236"/>
+      <c r="S5" s="237"/>
     </row>
     <row r="6" spans="1:19" ht="30" customHeight="1">
       <c r="A6" s="60">
@@ -20939,31 +20859,31 @@
       <c r="B6" s="59" t="s">
         <v>148</v>
       </c>
-      <c r="C6" s="237" t="s">
+      <c r="C6" s="232" t="s">
         <v>150</v>
       </c>
-      <c r="D6" s="237"/>
-      <c r="E6" s="237"/>
-      <c r="F6" s="237"/>
-      <c r="G6" s="237"/>
-      <c r="H6" s="237" t="s">
+      <c r="D6" s="232"/>
+      <c r="E6" s="232"/>
+      <c r="F6" s="232"/>
+      <c r="G6" s="232"/>
+      <c r="H6" s="232" t="s">
         <v>149</v>
       </c>
-      <c r="I6" s="237"/>
-      <c r="J6" s="237"/>
-      <c r="K6" s="237"/>
-      <c r="L6" s="237"/>
-      <c r="M6" s="237"/>
-      <c r="N6" s="238" t="s">
+      <c r="I6" s="232"/>
+      <c r="J6" s="232"/>
+      <c r="K6" s="232"/>
+      <c r="L6" s="232"/>
+      <c r="M6" s="232"/>
+      <c r="N6" s="254" t="s">
         <v>152</v>
       </c>
-      <c r="O6" s="239"/>
-      <c r="P6" s="240"/>
+      <c r="O6" s="255"/>
+      <c r="P6" s="256"/>
       <c r="Q6" s="64">
         <v>45824</v>
       </c>
-      <c r="R6" s="236"/>
-      <c r="S6" s="236"/>
+      <c r="R6" s="253"/>
+      <c r="S6" s="253"/>
     </row>
     <row r="7" spans="1:19" ht="30" customHeight="1">
       <c r="A7" s="60">
@@ -20972,979 +20892,1167 @@
       <c r="B7" s="63" t="s">
         <v>118</v>
       </c>
-      <c r="C7" s="237" t="s">
+      <c r="C7" s="232" t="s">
         <v>150</v>
       </c>
-      <c r="D7" s="237"/>
-      <c r="E7" s="237"/>
-      <c r="F7" s="237"/>
-      <c r="G7" s="237"/>
-      <c r="H7" s="237" t="s">
+      <c r="D7" s="232"/>
+      <c r="E7" s="232"/>
+      <c r="F7" s="232"/>
+      <c r="G7" s="232"/>
+      <c r="H7" s="232" t="s">
         <v>149</v>
       </c>
-      <c r="I7" s="237"/>
-      <c r="J7" s="237"/>
-      <c r="K7" s="237"/>
-      <c r="L7" s="237"/>
-      <c r="M7" s="237"/>
-      <c r="N7" s="233" t="s">
+      <c r="I7" s="232"/>
+      <c r="J7" s="232"/>
+      <c r="K7" s="232"/>
+      <c r="L7" s="232"/>
+      <c r="M7" s="232"/>
+      <c r="N7" s="250" t="s">
         <v>153</v>
       </c>
-      <c r="O7" s="234"/>
-      <c r="P7" s="235"/>
+      <c r="O7" s="251"/>
+      <c r="P7" s="252"/>
       <c r="Q7" s="64">
         <v>45824</v>
       </c>
-      <c r="R7" s="236"/>
-      <c r="S7" s="236"/>
+      <c r="R7" s="253"/>
+      <c r="S7" s="253"/>
     </row>
     <row r="8" spans="1:19" ht="30" customHeight="1">
       <c r="A8" s="60"/>
       <c r="B8" s="60"/>
-      <c r="C8" s="229"/>
-      <c r="D8" s="229"/>
-      <c r="E8" s="229"/>
-      <c r="F8" s="229"/>
-      <c r="G8" s="229"/>
-      <c r="H8" s="229"/>
-      <c r="I8" s="229"/>
-      <c r="J8" s="229"/>
-      <c r="K8" s="229"/>
-      <c r="L8" s="229"/>
-      <c r="M8" s="229"/>
-      <c r="N8" s="233"/>
-      <c r="O8" s="234"/>
-      <c r="P8" s="235"/>
+      <c r="C8" s="249"/>
+      <c r="D8" s="249"/>
+      <c r="E8" s="249"/>
+      <c r="F8" s="249"/>
+      <c r="G8" s="249"/>
+      <c r="H8" s="249"/>
+      <c r="I8" s="249"/>
+      <c r="J8" s="249"/>
+      <c r="K8" s="249"/>
+      <c r="L8" s="249"/>
+      <c r="M8" s="249"/>
+      <c r="N8" s="250"/>
+      <c r="O8" s="251"/>
+      <c r="P8" s="252"/>
       <c r="Q8" s="61"/>
-      <c r="R8" s="236"/>
-      <c r="S8" s="236"/>
+      <c r="R8" s="253"/>
+      <c r="S8" s="253"/>
     </row>
     <row r="9" spans="1:19" ht="30" customHeight="1">
       <c r="A9" s="60"/>
       <c r="B9" s="60"/>
-      <c r="C9" s="229"/>
-      <c r="D9" s="229"/>
-      <c r="E9" s="229"/>
-      <c r="F9" s="229"/>
-      <c r="G9" s="229"/>
-      <c r="H9" s="229"/>
-      <c r="I9" s="229"/>
-      <c r="J9" s="229"/>
-      <c r="K9" s="229"/>
-      <c r="L9" s="229"/>
-      <c r="M9" s="229"/>
-      <c r="N9" s="233"/>
-      <c r="O9" s="234"/>
-      <c r="P9" s="235"/>
+      <c r="C9" s="249"/>
+      <c r="D9" s="249"/>
+      <c r="E9" s="249"/>
+      <c r="F9" s="249"/>
+      <c r="G9" s="249"/>
+      <c r="H9" s="249"/>
+      <c r="I9" s="249"/>
+      <c r="J9" s="249"/>
+      <c r="K9" s="249"/>
+      <c r="L9" s="249"/>
+      <c r="M9" s="249"/>
+      <c r="N9" s="250"/>
+      <c r="O9" s="251"/>
+      <c r="P9" s="252"/>
       <c r="Q9" s="60"/>
-      <c r="R9" s="236"/>
-      <c r="S9" s="236"/>
+      <c r="R9" s="253"/>
+      <c r="S9" s="253"/>
     </row>
     <row r="10" spans="1:19" ht="30" customHeight="1">
       <c r="A10" s="60"/>
       <c r="B10" s="60"/>
-      <c r="C10" s="229"/>
-      <c r="D10" s="229"/>
-      <c r="E10" s="229"/>
-      <c r="F10" s="229"/>
-      <c r="G10" s="229"/>
-      <c r="H10" s="230"/>
-      <c r="I10" s="231"/>
-      <c r="J10" s="231"/>
-      <c r="K10" s="231"/>
-      <c r="L10" s="231"/>
-      <c r="M10" s="232"/>
-      <c r="N10" s="233"/>
-      <c r="O10" s="234"/>
-      <c r="P10" s="235"/>
+      <c r="C10" s="249"/>
+      <c r="D10" s="249"/>
+      <c r="E10" s="249"/>
+      <c r="F10" s="249"/>
+      <c r="G10" s="249"/>
+      <c r="H10" s="257"/>
+      <c r="I10" s="258"/>
+      <c r="J10" s="258"/>
+      <c r="K10" s="258"/>
+      <c r="L10" s="258"/>
+      <c r="M10" s="259"/>
+      <c r="N10" s="250"/>
+      <c r="O10" s="251"/>
+      <c r="P10" s="252"/>
       <c r="Q10" s="61"/>
-      <c r="R10" s="236"/>
-      <c r="S10" s="236"/>
+      <c r="R10" s="253"/>
+      <c r="S10" s="253"/>
     </row>
     <row r="11" spans="1:19" ht="30" customHeight="1">
       <c r="A11" s="60"/>
       <c r="B11" s="60"/>
-      <c r="C11" s="229"/>
-      <c r="D11" s="229"/>
-      <c r="E11" s="229"/>
-      <c r="F11" s="229"/>
-      <c r="G11" s="229"/>
-      <c r="H11" s="230"/>
-      <c r="I11" s="231"/>
-      <c r="J11" s="231"/>
-      <c r="K11" s="231"/>
-      <c r="L11" s="231"/>
-      <c r="M11" s="232"/>
-      <c r="N11" s="233"/>
-      <c r="O11" s="234"/>
-      <c r="P11" s="235"/>
+      <c r="C11" s="249"/>
+      <c r="D11" s="249"/>
+      <c r="E11" s="249"/>
+      <c r="F11" s="249"/>
+      <c r="G11" s="249"/>
+      <c r="H11" s="257"/>
+      <c r="I11" s="258"/>
+      <c r="J11" s="258"/>
+      <c r="K11" s="258"/>
+      <c r="L11" s="258"/>
+      <c r="M11" s="259"/>
+      <c r="N11" s="250"/>
+      <c r="O11" s="251"/>
+      <c r="P11" s="252"/>
       <c r="Q11" s="60"/>
-      <c r="R11" s="236"/>
-      <c r="S11" s="236"/>
+      <c r="R11" s="253"/>
+      <c r="S11" s="253"/>
     </row>
     <row r="12" spans="1:19" ht="30" customHeight="1">
       <c r="A12" s="60"/>
       <c r="B12" s="60"/>
-      <c r="C12" s="229"/>
-      <c r="D12" s="229"/>
-      <c r="E12" s="229"/>
-      <c r="F12" s="229"/>
-      <c r="G12" s="229"/>
-      <c r="H12" s="230"/>
-      <c r="I12" s="231"/>
-      <c r="J12" s="231"/>
-      <c r="K12" s="231"/>
-      <c r="L12" s="231"/>
-      <c r="M12" s="232"/>
-      <c r="N12" s="233"/>
-      <c r="O12" s="234"/>
-      <c r="P12" s="235"/>
+      <c r="C12" s="249"/>
+      <c r="D12" s="249"/>
+      <c r="E12" s="249"/>
+      <c r="F12" s="249"/>
+      <c r="G12" s="249"/>
+      <c r="H12" s="257"/>
+      <c r="I12" s="258"/>
+      <c r="J12" s="258"/>
+      <c r="K12" s="258"/>
+      <c r="L12" s="258"/>
+      <c r="M12" s="259"/>
+      <c r="N12" s="250"/>
+      <c r="O12" s="251"/>
+      <c r="P12" s="252"/>
       <c r="Q12" s="60"/>
-      <c r="R12" s="236"/>
-      <c r="S12" s="236"/>
+      <c r="R12" s="253"/>
+      <c r="S12" s="253"/>
     </row>
     <row r="13" spans="1:19" ht="30" customHeight="1">
       <c r="A13" s="60"/>
       <c r="B13" s="60"/>
-      <c r="C13" s="229"/>
-      <c r="D13" s="229"/>
-      <c r="E13" s="229"/>
-      <c r="F13" s="229"/>
-      <c r="G13" s="229"/>
-      <c r="H13" s="230"/>
-      <c r="I13" s="231"/>
-      <c r="J13" s="231"/>
-      <c r="K13" s="231"/>
-      <c r="L13" s="231"/>
-      <c r="M13" s="232"/>
-      <c r="N13" s="233"/>
-      <c r="O13" s="234"/>
-      <c r="P13" s="235"/>
+      <c r="C13" s="249"/>
+      <c r="D13" s="249"/>
+      <c r="E13" s="249"/>
+      <c r="F13" s="249"/>
+      <c r="G13" s="249"/>
+      <c r="H13" s="257"/>
+      <c r="I13" s="258"/>
+      <c r="J13" s="258"/>
+      <c r="K13" s="258"/>
+      <c r="L13" s="258"/>
+      <c r="M13" s="259"/>
+      <c r="N13" s="250"/>
+      <c r="O13" s="251"/>
+      <c r="P13" s="252"/>
       <c r="Q13" s="60"/>
-      <c r="R13" s="236"/>
-      <c r="S13" s="236"/>
+      <c r="R13" s="253"/>
+      <c r="S13" s="253"/>
     </row>
     <row r="14" spans="1:19" ht="30" customHeight="1">
       <c r="A14" s="60"/>
       <c r="B14" s="60"/>
-      <c r="C14" s="229"/>
-      <c r="D14" s="229"/>
-      <c r="E14" s="229"/>
-      <c r="F14" s="229"/>
-      <c r="G14" s="229"/>
-      <c r="H14" s="230"/>
-      <c r="I14" s="231"/>
-      <c r="J14" s="231"/>
-      <c r="K14" s="231"/>
-      <c r="L14" s="231"/>
-      <c r="M14" s="232"/>
-      <c r="N14" s="233"/>
-      <c r="O14" s="234"/>
-      <c r="P14" s="235"/>
+      <c r="C14" s="249"/>
+      <c r="D14" s="249"/>
+      <c r="E14" s="249"/>
+      <c r="F14" s="249"/>
+      <c r="G14" s="249"/>
+      <c r="H14" s="257"/>
+      <c r="I14" s="258"/>
+      <c r="J14" s="258"/>
+      <c r="K14" s="258"/>
+      <c r="L14" s="258"/>
+      <c r="M14" s="259"/>
+      <c r="N14" s="250"/>
+      <c r="O14" s="251"/>
+      <c r="P14" s="252"/>
       <c r="Q14" s="60"/>
-      <c r="R14" s="236"/>
-      <c r="S14" s="236"/>
+      <c r="R14" s="253"/>
+      <c r="S14" s="253"/>
     </row>
     <row r="15" spans="1:19" ht="30" customHeight="1">
       <c r="A15" s="60"/>
       <c r="B15" s="60"/>
-      <c r="C15" s="229"/>
-      <c r="D15" s="229"/>
-      <c r="E15" s="229"/>
-      <c r="F15" s="229"/>
-      <c r="G15" s="229"/>
-      <c r="H15" s="230"/>
-      <c r="I15" s="231"/>
-      <c r="J15" s="231"/>
-      <c r="K15" s="231"/>
-      <c r="L15" s="231"/>
-      <c r="M15" s="232"/>
-      <c r="N15" s="233"/>
-      <c r="O15" s="234"/>
-      <c r="P15" s="235"/>
+      <c r="C15" s="249"/>
+      <c r="D15" s="249"/>
+      <c r="E15" s="249"/>
+      <c r="F15" s="249"/>
+      <c r="G15" s="249"/>
+      <c r="H15" s="257"/>
+      <c r="I15" s="258"/>
+      <c r="J15" s="258"/>
+      <c r="K15" s="258"/>
+      <c r="L15" s="258"/>
+      <c r="M15" s="259"/>
+      <c r="N15" s="250"/>
+      <c r="O15" s="251"/>
+      <c r="P15" s="252"/>
       <c r="Q15" s="60"/>
-      <c r="R15" s="236"/>
-      <c r="S15" s="236"/>
+      <c r="R15" s="253"/>
+      <c r="S15" s="253"/>
     </row>
     <row r="16" spans="1:19" ht="30" customHeight="1">
       <c r="A16" s="60"/>
       <c r="B16" s="60"/>
-      <c r="C16" s="229"/>
-      <c r="D16" s="229"/>
-      <c r="E16" s="229"/>
-      <c r="F16" s="229"/>
-      <c r="G16" s="229"/>
-      <c r="H16" s="230"/>
-      <c r="I16" s="231"/>
-      <c r="J16" s="231"/>
-      <c r="K16" s="231"/>
-      <c r="L16" s="231"/>
-      <c r="M16" s="232"/>
-      <c r="N16" s="233"/>
-      <c r="O16" s="234"/>
-      <c r="P16" s="235"/>
+      <c r="C16" s="249"/>
+      <c r="D16" s="249"/>
+      <c r="E16" s="249"/>
+      <c r="F16" s="249"/>
+      <c r="G16" s="249"/>
+      <c r="H16" s="257"/>
+      <c r="I16" s="258"/>
+      <c r="J16" s="258"/>
+      <c r="K16" s="258"/>
+      <c r="L16" s="258"/>
+      <c r="M16" s="259"/>
+      <c r="N16" s="250"/>
+      <c r="O16" s="251"/>
+      <c r="P16" s="252"/>
       <c r="Q16" s="60"/>
-      <c r="R16" s="236"/>
-      <c r="S16" s="236"/>
+      <c r="R16" s="253"/>
+      <c r="S16" s="253"/>
     </row>
     <row r="17" spans="1:19" ht="30" customHeight="1">
       <c r="A17" s="60"/>
       <c r="B17" s="60"/>
-      <c r="C17" s="229"/>
-      <c r="D17" s="229"/>
-      <c r="E17" s="229"/>
-      <c r="F17" s="229"/>
-      <c r="G17" s="229"/>
-      <c r="H17" s="230"/>
-      <c r="I17" s="231"/>
-      <c r="J17" s="231"/>
-      <c r="K17" s="231"/>
-      <c r="L17" s="231"/>
-      <c r="M17" s="232"/>
-      <c r="N17" s="233"/>
-      <c r="O17" s="234"/>
-      <c r="P17" s="235"/>
+      <c r="C17" s="249"/>
+      <c r="D17" s="249"/>
+      <c r="E17" s="249"/>
+      <c r="F17" s="249"/>
+      <c r="G17" s="249"/>
+      <c r="H17" s="257"/>
+      <c r="I17" s="258"/>
+      <c r="J17" s="258"/>
+      <c r="K17" s="258"/>
+      <c r="L17" s="258"/>
+      <c r="M17" s="259"/>
+      <c r="N17" s="250"/>
+      <c r="O17" s="251"/>
+      <c r="P17" s="252"/>
       <c r="Q17" s="60"/>
-      <c r="R17" s="236"/>
-      <c r="S17" s="236"/>
+      <c r="R17" s="253"/>
+      <c r="S17" s="253"/>
     </row>
     <row r="18" spans="1:19" ht="30" customHeight="1">
       <c r="A18" s="60"/>
       <c r="B18" s="60"/>
-      <c r="C18" s="229"/>
-      <c r="D18" s="229"/>
-      <c r="E18" s="229"/>
-      <c r="F18" s="229"/>
-      <c r="G18" s="229"/>
-      <c r="H18" s="230"/>
-      <c r="I18" s="231"/>
-      <c r="J18" s="231"/>
-      <c r="K18" s="231"/>
-      <c r="L18" s="231"/>
-      <c r="M18" s="232"/>
-      <c r="N18" s="233"/>
-      <c r="O18" s="234"/>
-      <c r="P18" s="235"/>
+      <c r="C18" s="249"/>
+      <c r="D18" s="249"/>
+      <c r="E18" s="249"/>
+      <c r="F18" s="249"/>
+      <c r="G18" s="249"/>
+      <c r="H18" s="257"/>
+      <c r="I18" s="258"/>
+      <c r="J18" s="258"/>
+      <c r="K18" s="258"/>
+      <c r="L18" s="258"/>
+      <c r="M18" s="259"/>
+      <c r="N18" s="250"/>
+      <c r="O18" s="251"/>
+      <c r="P18" s="252"/>
       <c r="Q18" s="60"/>
-      <c r="R18" s="236"/>
-      <c r="S18" s="236"/>
+      <c r="R18" s="253"/>
+      <c r="S18" s="253"/>
     </row>
     <row r="19" spans="1:19" ht="30" customHeight="1">
       <c r="A19" s="60"/>
       <c r="B19" s="60"/>
-      <c r="C19" s="229"/>
-      <c r="D19" s="229"/>
-      <c r="E19" s="229"/>
-      <c r="F19" s="229"/>
-      <c r="G19" s="229"/>
-      <c r="H19" s="230"/>
-      <c r="I19" s="231"/>
-      <c r="J19" s="231"/>
-      <c r="K19" s="231"/>
-      <c r="L19" s="231"/>
-      <c r="M19" s="232"/>
-      <c r="N19" s="233"/>
-      <c r="O19" s="234"/>
-      <c r="P19" s="235"/>
+      <c r="C19" s="249"/>
+      <c r="D19" s="249"/>
+      <c r="E19" s="249"/>
+      <c r="F19" s="249"/>
+      <c r="G19" s="249"/>
+      <c r="H19" s="257"/>
+      <c r="I19" s="258"/>
+      <c r="J19" s="258"/>
+      <c r="K19" s="258"/>
+      <c r="L19" s="258"/>
+      <c r="M19" s="259"/>
+      <c r="N19" s="250"/>
+      <c r="O19" s="251"/>
+      <c r="P19" s="252"/>
       <c r="Q19" s="60"/>
-      <c r="R19" s="236"/>
-      <c r="S19" s="236"/>
+      <c r="R19" s="253"/>
+      <c r="S19" s="253"/>
     </row>
     <row r="20" spans="1:19" ht="30" customHeight="1">
       <c r="A20" s="60"/>
       <c r="B20" s="60"/>
-      <c r="C20" s="229"/>
-      <c r="D20" s="229"/>
-      <c r="E20" s="229"/>
-      <c r="F20" s="229"/>
-      <c r="G20" s="229"/>
-      <c r="H20" s="230"/>
-      <c r="I20" s="231"/>
-      <c r="J20" s="231"/>
-      <c r="K20" s="231"/>
-      <c r="L20" s="231"/>
-      <c r="M20" s="232"/>
-      <c r="N20" s="233"/>
-      <c r="O20" s="234"/>
-      <c r="P20" s="235"/>
+      <c r="C20" s="249"/>
+      <c r="D20" s="249"/>
+      <c r="E20" s="249"/>
+      <c r="F20" s="249"/>
+      <c r="G20" s="249"/>
+      <c r="H20" s="257"/>
+      <c r="I20" s="258"/>
+      <c r="J20" s="258"/>
+      <c r="K20" s="258"/>
+      <c r="L20" s="258"/>
+      <c r="M20" s="259"/>
+      <c r="N20" s="250"/>
+      <c r="O20" s="251"/>
+      <c r="P20" s="252"/>
       <c r="Q20" s="60"/>
-      <c r="R20" s="236"/>
-      <c r="S20" s="236"/>
+      <c r="R20" s="253"/>
+      <c r="S20" s="253"/>
     </row>
     <row r="21" spans="1:19" ht="30" customHeight="1">
       <c r="A21" s="60"/>
       <c r="B21" s="60"/>
-      <c r="C21" s="229"/>
-      <c r="D21" s="229"/>
-      <c r="E21" s="229"/>
-      <c r="F21" s="229"/>
-      <c r="G21" s="229"/>
-      <c r="H21" s="230"/>
-      <c r="I21" s="231"/>
-      <c r="J21" s="231"/>
-      <c r="K21" s="231"/>
-      <c r="L21" s="231"/>
-      <c r="M21" s="232"/>
-      <c r="N21" s="233"/>
-      <c r="O21" s="234"/>
-      <c r="P21" s="235"/>
+      <c r="C21" s="249"/>
+      <c r="D21" s="249"/>
+      <c r="E21" s="249"/>
+      <c r="F21" s="249"/>
+      <c r="G21" s="249"/>
+      <c r="H21" s="257"/>
+      <c r="I21" s="258"/>
+      <c r="J21" s="258"/>
+      <c r="K21" s="258"/>
+      <c r="L21" s="258"/>
+      <c r="M21" s="259"/>
+      <c r="N21" s="250"/>
+      <c r="O21" s="251"/>
+      <c r="P21" s="252"/>
       <c r="Q21" s="60"/>
-      <c r="R21" s="236"/>
-      <c r="S21" s="236"/>
+      <c r="R21" s="253"/>
+      <c r="S21" s="253"/>
     </row>
     <row r="22" spans="1:19" ht="30" customHeight="1">
       <c r="A22" s="60"/>
       <c r="B22" s="60"/>
-      <c r="C22" s="229"/>
-      <c r="D22" s="229"/>
-      <c r="E22" s="229"/>
-      <c r="F22" s="229"/>
-      <c r="G22" s="229"/>
-      <c r="H22" s="230"/>
-      <c r="I22" s="231"/>
-      <c r="J22" s="231"/>
-      <c r="K22" s="231"/>
-      <c r="L22" s="231"/>
-      <c r="M22" s="232"/>
-      <c r="N22" s="233"/>
-      <c r="O22" s="234"/>
-      <c r="P22" s="235"/>
+      <c r="C22" s="249"/>
+      <c r="D22" s="249"/>
+      <c r="E22" s="249"/>
+      <c r="F22" s="249"/>
+      <c r="G22" s="249"/>
+      <c r="H22" s="257"/>
+      <c r="I22" s="258"/>
+      <c r="J22" s="258"/>
+      <c r="K22" s="258"/>
+      <c r="L22" s="258"/>
+      <c r="M22" s="259"/>
+      <c r="N22" s="250"/>
+      <c r="O22" s="251"/>
+      <c r="P22" s="252"/>
       <c r="Q22" s="60"/>
-      <c r="R22" s="236"/>
-      <c r="S22" s="236"/>
+      <c r="R22" s="253"/>
+      <c r="S22" s="253"/>
     </row>
     <row r="23" spans="1:19" ht="30" customHeight="1">
       <c r="A23" s="60"/>
       <c r="B23" s="60"/>
-      <c r="C23" s="229"/>
-      <c r="D23" s="229"/>
-      <c r="E23" s="229"/>
-      <c r="F23" s="229"/>
-      <c r="G23" s="229"/>
-      <c r="H23" s="230"/>
-      <c r="I23" s="231"/>
-      <c r="J23" s="231"/>
-      <c r="K23" s="231"/>
-      <c r="L23" s="231"/>
-      <c r="M23" s="232"/>
-      <c r="N23" s="233"/>
-      <c r="O23" s="234"/>
-      <c r="P23" s="235"/>
+      <c r="C23" s="249"/>
+      <c r="D23" s="249"/>
+      <c r="E23" s="249"/>
+      <c r="F23" s="249"/>
+      <c r="G23" s="249"/>
+      <c r="H23" s="257"/>
+      <c r="I23" s="258"/>
+      <c r="J23" s="258"/>
+      <c r="K23" s="258"/>
+      <c r="L23" s="258"/>
+      <c r="M23" s="259"/>
+      <c r="N23" s="250"/>
+      <c r="O23" s="251"/>
+      <c r="P23" s="252"/>
       <c r="Q23" s="60"/>
-      <c r="R23" s="236"/>
-      <c r="S23" s="236"/>
+      <c r="R23" s="253"/>
+      <c r="S23" s="253"/>
     </row>
     <row r="24" spans="1:19" ht="30" customHeight="1">
       <c r="A24" s="60"/>
       <c r="B24" s="60"/>
-      <c r="C24" s="229"/>
-      <c r="D24" s="229"/>
-      <c r="E24" s="229"/>
-      <c r="F24" s="229"/>
-      <c r="G24" s="229"/>
-      <c r="H24" s="230"/>
-      <c r="I24" s="231"/>
-      <c r="J24" s="231"/>
-      <c r="K24" s="231"/>
-      <c r="L24" s="231"/>
-      <c r="M24" s="232"/>
-      <c r="N24" s="233"/>
-      <c r="O24" s="234"/>
-      <c r="P24" s="235"/>
+      <c r="C24" s="249"/>
+      <c r="D24" s="249"/>
+      <c r="E24" s="249"/>
+      <c r="F24" s="249"/>
+      <c r="G24" s="249"/>
+      <c r="H24" s="257"/>
+      <c r="I24" s="258"/>
+      <c r="J24" s="258"/>
+      <c r="K24" s="258"/>
+      <c r="L24" s="258"/>
+      <c r="M24" s="259"/>
+      <c r="N24" s="250"/>
+      <c r="O24" s="251"/>
+      <c r="P24" s="252"/>
       <c r="Q24" s="60"/>
-      <c r="R24" s="236"/>
-      <c r="S24" s="236"/>
+      <c r="R24" s="253"/>
+      <c r="S24" s="253"/>
     </row>
     <row r="25" spans="1:19" ht="30" customHeight="1">
       <c r="A25" s="60"/>
       <c r="B25" s="60"/>
-      <c r="C25" s="229"/>
-      <c r="D25" s="229"/>
-      <c r="E25" s="229"/>
-      <c r="F25" s="229"/>
-      <c r="G25" s="229"/>
-      <c r="H25" s="230"/>
-      <c r="I25" s="231"/>
-      <c r="J25" s="231"/>
-      <c r="K25" s="231"/>
-      <c r="L25" s="231"/>
-      <c r="M25" s="232"/>
-      <c r="N25" s="233"/>
-      <c r="O25" s="234"/>
-      <c r="P25" s="235"/>
+      <c r="C25" s="249"/>
+      <c r="D25" s="249"/>
+      <c r="E25" s="249"/>
+      <c r="F25" s="249"/>
+      <c r="G25" s="249"/>
+      <c r="H25" s="257"/>
+      <c r="I25" s="258"/>
+      <c r="J25" s="258"/>
+      <c r="K25" s="258"/>
+      <c r="L25" s="258"/>
+      <c r="M25" s="259"/>
+      <c r="N25" s="250"/>
+      <c r="O25" s="251"/>
+      <c r="P25" s="252"/>
       <c r="Q25" s="60"/>
-      <c r="R25" s="236"/>
-      <c r="S25" s="236"/>
+      <c r="R25" s="253"/>
+      <c r="S25" s="253"/>
     </row>
     <row r="26" spans="1:19" ht="30" customHeight="1">
       <c r="A26" s="60"/>
       <c r="B26" s="60"/>
-      <c r="C26" s="229"/>
-      <c r="D26" s="229"/>
-      <c r="E26" s="229"/>
-      <c r="F26" s="229"/>
-      <c r="G26" s="229"/>
-      <c r="H26" s="230"/>
-      <c r="I26" s="231"/>
-      <c r="J26" s="231"/>
-      <c r="K26" s="231"/>
-      <c r="L26" s="231"/>
-      <c r="M26" s="232"/>
-      <c r="N26" s="233"/>
-      <c r="O26" s="234"/>
-      <c r="P26" s="235"/>
+      <c r="C26" s="249"/>
+      <c r="D26" s="249"/>
+      <c r="E26" s="249"/>
+      <c r="F26" s="249"/>
+      <c r="G26" s="249"/>
+      <c r="H26" s="257"/>
+      <c r="I26" s="258"/>
+      <c r="J26" s="258"/>
+      <c r="K26" s="258"/>
+      <c r="L26" s="258"/>
+      <c r="M26" s="259"/>
+      <c r="N26" s="250"/>
+      <c r="O26" s="251"/>
+      <c r="P26" s="252"/>
       <c r="Q26" s="60"/>
-      <c r="R26" s="236"/>
-      <c r="S26" s="236"/>
+      <c r="R26" s="253"/>
+      <c r="S26" s="253"/>
     </row>
     <row r="27" spans="1:19" ht="30" customHeight="1">
       <c r="A27" s="60"/>
       <c r="B27" s="60"/>
-      <c r="C27" s="229"/>
-      <c r="D27" s="229"/>
-      <c r="E27" s="229"/>
-      <c r="F27" s="229"/>
-      <c r="G27" s="229"/>
-      <c r="H27" s="230"/>
-      <c r="I27" s="231"/>
-      <c r="J27" s="231"/>
-      <c r="K27" s="231"/>
-      <c r="L27" s="231"/>
-      <c r="M27" s="232"/>
-      <c r="N27" s="233"/>
-      <c r="O27" s="234"/>
-      <c r="P27" s="235"/>
+      <c r="C27" s="249"/>
+      <c r="D27" s="249"/>
+      <c r="E27" s="249"/>
+      <c r="F27" s="249"/>
+      <c r="G27" s="249"/>
+      <c r="H27" s="257"/>
+      <c r="I27" s="258"/>
+      <c r="J27" s="258"/>
+      <c r="K27" s="258"/>
+      <c r="L27" s="258"/>
+      <c r="M27" s="259"/>
+      <c r="N27" s="250"/>
+      <c r="O27" s="251"/>
+      <c r="P27" s="252"/>
       <c r="Q27" s="60"/>
-      <c r="R27" s="236"/>
-      <c r="S27" s="236"/>
+      <c r="R27" s="253"/>
+      <c r="S27" s="253"/>
     </row>
     <row r="28" spans="1:19" ht="30" customHeight="1">
       <c r="A28" s="60"/>
       <c r="B28" s="60"/>
-      <c r="C28" s="229"/>
-      <c r="D28" s="229"/>
-      <c r="E28" s="229"/>
-      <c r="F28" s="229"/>
-      <c r="G28" s="229"/>
-      <c r="H28" s="230"/>
-      <c r="I28" s="231"/>
-      <c r="J28" s="231"/>
-      <c r="K28" s="231"/>
-      <c r="L28" s="231"/>
-      <c r="M28" s="232"/>
-      <c r="N28" s="233"/>
-      <c r="O28" s="234"/>
-      <c r="P28" s="235"/>
+      <c r="C28" s="249"/>
+      <c r="D28" s="249"/>
+      <c r="E28" s="249"/>
+      <c r="F28" s="249"/>
+      <c r="G28" s="249"/>
+      <c r="H28" s="257"/>
+      <c r="I28" s="258"/>
+      <c r="J28" s="258"/>
+      <c r="K28" s="258"/>
+      <c r="L28" s="258"/>
+      <c r="M28" s="259"/>
+      <c r="N28" s="250"/>
+      <c r="O28" s="251"/>
+      <c r="P28" s="252"/>
       <c r="Q28" s="60"/>
-      <c r="R28" s="236"/>
-      <c r="S28" s="236"/>
+      <c r="R28" s="253"/>
+      <c r="S28" s="253"/>
     </row>
     <row r="29" spans="1:19" ht="30" customHeight="1">
       <c r="A29" s="60"/>
       <c r="B29" s="60"/>
-      <c r="C29" s="229"/>
-      <c r="D29" s="229"/>
-      <c r="E29" s="229"/>
-      <c r="F29" s="229"/>
-      <c r="G29" s="229"/>
-      <c r="H29" s="230"/>
-      <c r="I29" s="231"/>
-      <c r="J29" s="231"/>
-      <c r="K29" s="231"/>
-      <c r="L29" s="231"/>
-      <c r="M29" s="232"/>
-      <c r="N29" s="233"/>
-      <c r="O29" s="234"/>
-      <c r="P29" s="235"/>
+      <c r="C29" s="249"/>
+      <c r="D29" s="249"/>
+      <c r="E29" s="249"/>
+      <c r="F29" s="249"/>
+      <c r="G29" s="249"/>
+      <c r="H29" s="257"/>
+      <c r="I29" s="258"/>
+      <c r="J29" s="258"/>
+      <c r="K29" s="258"/>
+      <c r="L29" s="258"/>
+      <c r="M29" s="259"/>
+      <c r="N29" s="250"/>
+      <c r="O29" s="251"/>
+      <c r="P29" s="252"/>
       <c r="Q29" s="60"/>
-      <c r="R29" s="236"/>
-      <c r="S29" s="236"/>
+      <c r="R29" s="253"/>
+      <c r="S29" s="253"/>
     </row>
     <row r="30" spans="1:19" ht="30" customHeight="1">
       <c r="A30" s="60"/>
       <c r="B30" s="60"/>
-      <c r="C30" s="229"/>
-      <c r="D30" s="229"/>
-      <c r="E30" s="229"/>
-      <c r="F30" s="229"/>
-      <c r="G30" s="229"/>
-      <c r="H30" s="230"/>
-      <c r="I30" s="231"/>
-      <c r="J30" s="231"/>
-      <c r="K30" s="231"/>
-      <c r="L30" s="231"/>
-      <c r="M30" s="232"/>
-      <c r="N30" s="233"/>
-      <c r="O30" s="234"/>
-      <c r="P30" s="235"/>
+      <c r="C30" s="249"/>
+      <c r="D30" s="249"/>
+      <c r="E30" s="249"/>
+      <c r="F30" s="249"/>
+      <c r="G30" s="249"/>
+      <c r="H30" s="257"/>
+      <c r="I30" s="258"/>
+      <c r="J30" s="258"/>
+      <c r="K30" s="258"/>
+      <c r="L30" s="258"/>
+      <c r="M30" s="259"/>
+      <c r="N30" s="250"/>
+      <c r="O30" s="251"/>
+      <c r="P30" s="252"/>
       <c r="Q30" s="60"/>
-      <c r="R30" s="236"/>
-      <c r="S30" s="236"/>
+      <c r="R30" s="253"/>
+      <c r="S30" s="253"/>
     </row>
     <row r="31" spans="1:19" ht="30" customHeight="1">
       <c r="A31" s="60"/>
       <c r="B31" s="60"/>
-      <c r="C31" s="229"/>
-      <c r="D31" s="229"/>
-      <c r="E31" s="229"/>
-      <c r="F31" s="229"/>
-      <c r="G31" s="229"/>
-      <c r="H31" s="230"/>
-      <c r="I31" s="231"/>
-      <c r="J31" s="231"/>
-      <c r="K31" s="231"/>
-      <c r="L31" s="231"/>
-      <c r="M31" s="232"/>
-      <c r="N31" s="233"/>
-      <c r="O31" s="234"/>
-      <c r="P31" s="235"/>
+      <c r="C31" s="249"/>
+      <c r="D31" s="249"/>
+      <c r="E31" s="249"/>
+      <c r="F31" s="249"/>
+      <c r="G31" s="249"/>
+      <c r="H31" s="257"/>
+      <c r="I31" s="258"/>
+      <c r="J31" s="258"/>
+      <c r="K31" s="258"/>
+      <c r="L31" s="258"/>
+      <c r="M31" s="259"/>
+      <c r="N31" s="250"/>
+      <c r="O31" s="251"/>
+      <c r="P31" s="252"/>
       <c r="Q31" s="60"/>
-      <c r="R31" s="236"/>
-      <c r="S31" s="236"/>
+      <c r="R31" s="253"/>
+      <c r="S31" s="253"/>
     </row>
     <row r="32" spans="1:19" ht="30" customHeight="1">
       <c r="A32" s="60"/>
       <c r="B32" s="60"/>
-      <c r="C32" s="229"/>
-      <c r="D32" s="229"/>
-      <c r="E32" s="229"/>
-      <c r="F32" s="229"/>
-      <c r="G32" s="229"/>
-      <c r="H32" s="230"/>
-      <c r="I32" s="231"/>
-      <c r="J32" s="231"/>
-      <c r="K32" s="231"/>
-      <c r="L32" s="231"/>
-      <c r="M32" s="232"/>
-      <c r="N32" s="233"/>
-      <c r="O32" s="234"/>
-      <c r="P32" s="235"/>
+      <c r="C32" s="249"/>
+      <c r="D32" s="249"/>
+      <c r="E32" s="249"/>
+      <c r="F32" s="249"/>
+      <c r="G32" s="249"/>
+      <c r="H32" s="257"/>
+      <c r="I32" s="258"/>
+      <c r="J32" s="258"/>
+      <c r="K32" s="258"/>
+      <c r="L32" s="258"/>
+      <c r="M32" s="259"/>
+      <c r="N32" s="250"/>
+      <c r="O32" s="251"/>
+      <c r="P32" s="252"/>
       <c r="Q32" s="60"/>
-      <c r="R32" s="236"/>
-      <c r="S32" s="236"/>
+      <c r="R32" s="253"/>
+      <c r="S32" s="253"/>
     </row>
     <row r="33" spans="1:19" ht="30" customHeight="1">
       <c r="A33" s="60"/>
       <c r="B33" s="60"/>
-      <c r="C33" s="229"/>
-      <c r="D33" s="229"/>
-      <c r="E33" s="229"/>
-      <c r="F33" s="229"/>
-      <c r="G33" s="229"/>
-      <c r="H33" s="230"/>
-      <c r="I33" s="231"/>
-      <c r="J33" s="231"/>
-      <c r="K33" s="231"/>
-      <c r="L33" s="231"/>
-      <c r="M33" s="232"/>
-      <c r="N33" s="233"/>
-      <c r="O33" s="234"/>
-      <c r="P33" s="235"/>
+      <c r="C33" s="249"/>
+      <c r="D33" s="249"/>
+      <c r="E33" s="249"/>
+      <c r="F33" s="249"/>
+      <c r="G33" s="249"/>
+      <c r="H33" s="257"/>
+      <c r="I33" s="258"/>
+      <c r="J33" s="258"/>
+      <c r="K33" s="258"/>
+      <c r="L33" s="258"/>
+      <c r="M33" s="259"/>
+      <c r="N33" s="250"/>
+      <c r="O33" s="251"/>
+      <c r="P33" s="252"/>
       <c r="Q33" s="60"/>
-      <c r="R33" s="236"/>
-      <c r="S33" s="236"/>
+      <c r="R33" s="253"/>
+      <c r="S33" s="253"/>
     </row>
     <row r="34" spans="1:19" ht="30" customHeight="1">
       <c r="A34" s="60"/>
       <c r="B34" s="60"/>
-      <c r="C34" s="229"/>
-      <c r="D34" s="229"/>
-      <c r="E34" s="229"/>
-      <c r="F34" s="229"/>
-      <c r="G34" s="229"/>
-      <c r="H34" s="230"/>
-      <c r="I34" s="231"/>
-      <c r="J34" s="231"/>
-      <c r="K34" s="231"/>
-      <c r="L34" s="231"/>
-      <c r="M34" s="232"/>
-      <c r="N34" s="233"/>
-      <c r="O34" s="234"/>
-      <c r="P34" s="235"/>
+      <c r="C34" s="249"/>
+      <c r="D34" s="249"/>
+      <c r="E34" s="249"/>
+      <c r="F34" s="249"/>
+      <c r="G34" s="249"/>
+      <c r="H34" s="257"/>
+      <c r="I34" s="258"/>
+      <c r="J34" s="258"/>
+      <c r="K34" s="258"/>
+      <c r="L34" s="258"/>
+      <c r="M34" s="259"/>
+      <c r="N34" s="250"/>
+      <c r="O34" s="251"/>
+      <c r="P34" s="252"/>
       <c r="Q34" s="60"/>
-      <c r="R34" s="236"/>
-      <c r="S34" s="236"/>
+      <c r="R34" s="253"/>
+      <c r="S34" s="253"/>
     </row>
     <row r="35" spans="1:19" ht="30" customHeight="1">
       <c r="A35" s="60"/>
       <c r="B35" s="60"/>
-      <c r="C35" s="229"/>
-      <c r="D35" s="229"/>
-      <c r="E35" s="229"/>
-      <c r="F35" s="229"/>
-      <c r="G35" s="229"/>
-      <c r="H35" s="230"/>
-      <c r="I35" s="231"/>
-      <c r="J35" s="231"/>
-      <c r="K35" s="231"/>
-      <c r="L35" s="231"/>
-      <c r="M35" s="232"/>
-      <c r="N35" s="233"/>
-      <c r="O35" s="234"/>
-      <c r="P35" s="235"/>
+      <c r="C35" s="249"/>
+      <c r="D35" s="249"/>
+      <c r="E35" s="249"/>
+      <c r="F35" s="249"/>
+      <c r="G35" s="249"/>
+      <c r="H35" s="257"/>
+      <c r="I35" s="258"/>
+      <c r="J35" s="258"/>
+      <c r="K35" s="258"/>
+      <c r="L35" s="258"/>
+      <c r="M35" s="259"/>
+      <c r="N35" s="250"/>
+      <c r="O35" s="251"/>
+      <c r="P35" s="252"/>
       <c r="Q35" s="60"/>
-      <c r="R35" s="236"/>
-      <c r="S35" s="236"/>
+      <c r="R35" s="253"/>
+      <c r="S35" s="253"/>
     </row>
     <row r="36" spans="1:19" ht="30" customHeight="1">
       <c r="A36" s="60"/>
       <c r="B36" s="60"/>
-      <c r="C36" s="229"/>
-      <c r="D36" s="229"/>
-      <c r="E36" s="229"/>
-      <c r="F36" s="229"/>
-      <c r="G36" s="229"/>
-      <c r="H36" s="230"/>
-      <c r="I36" s="231"/>
-      <c r="J36" s="231"/>
-      <c r="K36" s="231"/>
-      <c r="L36" s="231"/>
-      <c r="M36" s="232"/>
-      <c r="N36" s="233"/>
-      <c r="O36" s="234"/>
-      <c r="P36" s="235"/>
+      <c r="C36" s="249"/>
+      <c r="D36" s="249"/>
+      <c r="E36" s="249"/>
+      <c r="F36" s="249"/>
+      <c r="G36" s="249"/>
+      <c r="H36" s="257"/>
+      <c r="I36" s="258"/>
+      <c r="J36" s="258"/>
+      <c r="K36" s="258"/>
+      <c r="L36" s="258"/>
+      <c r="M36" s="259"/>
+      <c r="N36" s="250"/>
+      <c r="O36" s="251"/>
+      <c r="P36" s="252"/>
       <c r="Q36" s="60"/>
-      <c r="R36" s="236"/>
-      <c r="S36" s="236"/>
+      <c r="R36" s="253"/>
+      <c r="S36" s="253"/>
     </row>
     <row r="37" spans="1:19" ht="30" customHeight="1">
       <c r="A37" s="60"/>
       <c r="B37" s="60"/>
-      <c r="C37" s="229"/>
-      <c r="D37" s="229"/>
-      <c r="E37" s="229"/>
-      <c r="F37" s="229"/>
-      <c r="G37" s="229"/>
-      <c r="H37" s="230"/>
-      <c r="I37" s="231"/>
-      <c r="J37" s="231"/>
-      <c r="K37" s="231"/>
-      <c r="L37" s="231"/>
-      <c r="M37" s="232"/>
-      <c r="N37" s="233"/>
-      <c r="O37" s="234"/>
-      <c r="P37" s="235"/>
+      <c r="C37" s="249"/>
+      <c r="D37" s="249"/>
+      <c r="E37" s="249"/>
+      <c r="F37" s="249"/>
+      <c r="G37" s="249"/>
+      <c r="H37" s="257"/>
+      <c r="I37" s="258"/>
+      <c r="J37" s="258"/>
+      <c r="K37" s="258"/>
+      <c r="L37" s="258"/>
+      <c r="M37" s="259"/>
+      <c r="N37" s="250"/>
+      <c r="O37" s="251"/>
+      <c r="P37" s="252"/>
       <c r="Q37" s="60"/>
-      <c r="R37" s="236"/>
-      <c r="S37" s="236"/>
+      <c r="R37" s="253"/>
+      <c r="S37" s="253"/>
     </row>
     <row r="38" spans="1:19" ht="30" customHeight="1">
       <c r="A38" s="60"/>
       <c r="B38" s="60"/>
-      <c r="C38" s="229"/>
-      <c r="D38" s="229"/>
-      <c r="E38" s="229"/>
-      <c r="F38" s="229"/>
-      <c r="G38" s="229"/>
-      <c r="H38" s="230"/>
-      <c r="I38" s="231"/>
-      <c r="J38" s="231"/>
-      <c r="K38" s="231"/>
-      <c r="L38" s="231"/>
-      <c r="M38" s="232"/>
-      <c r="N38" s="233"/>
-      <c r="O38" s="234"/>
-      <c r="P38" s="235"/>
+      <c r="C38" s="249"/>
+      <c r="D38" s="249"/>
+      <c r="E38" s="249"/>
+      <c r="F38" s="249"/>
+      <c r="G38" s="249"/>
+      <c r="H38" s="257"/>
+      <c r="I38" s="258"/>
+      <c r="J38" s="258"/>
+      <c r="K38" s="258"/>
+      <c r="L38" s="258"/>
+      <c r="M38" s="259"/>
+      <c r="N38" s="250"/>
+      <c r="O38" s="251"/>
+      <c r="P38" s="252"/>
       <c r="Q38" s="60"/>
-      <c r="R38" s="236"/>
-      <c r="S38" s="236"/>
+      <c r="R38" s="253"/>
+      <c r="S38" s="253"/>
     </row>
     <row r="39" spans="1:19" ht="30" customHeight="1">
       <c r="A39" s="60"/>
       <c r="B39" s="60"/>
-      <c r="C39" s="229"/>
-      <c r="D39" s="229"/>
-      <c r="E39" s="229"/>
-      <c r="F39" s="229"/>
-      <c r="G39" s="229"/>
-      <c r="H39" s="230"/>
-      <c r="I39" s="231"/>
-      <c r="J39" s="231"/>
-      <c r="K39" s="231"/>
-      <c r="L39" s="231"/>
-      <c r="M39" s="232"/>
-      <c r="N39" s="233"/>
-      <c r="O39" s="234"/>
-      <c r="P39" s="235"/>
+      <c r="C39" s="249"/>
+      <c r="D39" s="249"/>
+      <c r="E39" s="249"/>
+      <c r="F39" s="249"/>
+      <c r="G39" s="249"/>
+      <c r="H39" s="257"/>
+      <c r="I39" s="258"/>
+      <c r="J39" s="258"/>
+      <c r="K39" s="258"/>
+      <c r="L39" s="258"/>
+      <c r="M39" s="259"/>
+      <c r="N39" s="250"/>
+      <c r="O39" s="251"/>
+      <c r="P39" s="252"/>
       <c r="Q39" s="60"/>
-      <c r="R39" s="236"/>
-      <c r="S39" s="236"/>
+      <c r="R39" s="253"/>
+      <c r="S39" s="253"/>
     </row>
     <row r="40" spans="1:19" ht="30" customHeight="1">
       <c r="A40" s="60"/>
       <c r="B40" s="60"/>
-      <c r="C40" s="229"/>
-      <c r="D40" s="229"/>
-      <c r="E40" s="229"/>
-      <c r="F40" s="229"/>
-      <c r="G40" s="229"/>
-      <c r="H40" s="230"/>
-      <c r="I40" s="231"/>
-      <c r="J40" s="231"/>
-      <c r="K40" s="231"/>
-      <c r="L40" s="231"/>
-      <c r="M40" s="232"/>
-      <c r="N40" s="233"/>
-      <c r="O40" s="234"/>
-      <c r="P40" s="235"/>
+      <c r="C40" s="249"/>
+      <c r="D40" s="249"/>
+      <c r="E40" s="249"/>
+      <c r="F40" s="249"/>
+      <c r="G40" s="249"/>
+      <c r="H40" s="257"/>
+      <c r="I40" s="258"/>
+      <c r="J40" s="258"/>
+      <c r="K40" s="258"/>
+      <c r="L40" s="258"/>
+      <c r="M40" s="259"/>
+      <c r="N40" s="250"/>
+      <c r="O40" s="251"/>
+      <c r="P40" s="252"/>
       <c r="Q40" s="60"/>
-      <c r="R40" s="236"/>
-      <c r="S40" s="236"/>
+      <c r="R40" s="253"/>
+      <c r="S40" s="253"/>
     </row>
     <row r="41" spans="1:19" ht="30" customHeight="1">
       <c r="A41" s="60"/>
       <c r="B41" s="60"/>
-      <c r="C41" s="229"/>
-      <c r="D41" s="229"/>
-      <c r="E41" s="229"/>
-      <c r="F41" s="229"/>
-      <c r="G41" s="229"/>
-      <c r="H41" s="230"/>
-      <c r="I41" s="231"/>
-      <c r="J41" s="231"/>
-      <c r="K41" s="231"/>
-      <c r="L41" s="231"/>
-      <c r="M41" s="232"/>
-      <c r="N41" s="233"/>
-      <c r="O41" s="234"/>
-      <c r="P41" s="235"/>
+      <c r="C41" s="249"/>
+      <c r="D41" s="249"/>
+      <c r="E41" s="249"/>
+      <c r="F41" s="249"/>
+      <c r="G41" s="249"/>
+      <c r="H41" s="257"/>
+      <c r="I41" s="258"/>
+      <c r="J41" s="258"/>
+      <c r="K41" s="258"/>
+      <c r="L41" s="258"/>
+      <c r="M41" s="259"/>
+      <c r="N41" s="250"/>
+      <c r="O41" s="251"/>
+      <c r="P41" s="252"/>
       <c r="Q41" s="60"/>
-      <c r="R41" s="236"/>
-      <c r="S41" s="236"/>
+      <c r="R41" s="253"/>
+      <c r="S41" s="253"/>
     </row>
     <row r="42" spans="1:19" ht="30" customHeight="1">
       <c r="A42" s="60"/>
       <c r="B42" s="60"/>
-      <c r="C42" s="229"/>
-      <c r="D42" s="229"/>
-      <c r="E42" s="229"/>
-      <c r="F42" s="229"/>
-      <c r="G42" s="229"/>
-      <c r="H42" s="230"/>
-      <c r="I42" s="231"/>
-      <c r="J42" s="231"/>
-      <c r="K42" s="231"/>
-      <c r="L42" s="231"/>
-      <c r="M42" s="232"/>
-      <c r="N42" s="233"/>
-      <c r="O42" s="234"/>
-      <c r="P42" s="235"/>
+      <c r="C42" s="249"/>
+      <c r="D42" s="249"/>
+      <c r="E42" s="249"/>
+      <c r="F42" s="249"/>
+      <c r="G42" s="249"/>
+      <c r="H42" s="257"/>
+      <c r="I42" s="258"/>
+      <c r="J42" s="258"/>
+      <c r="K42" s="258"/>
+      <c r="L42" s="258"/>
+      <c r="M42" s="259"/>
+      <c r="N42" s="250"/>
+      <c r="O42" s="251"/>
+      <c r="P42" s="252"/>
       <c r="Q42" s="60"/>
-      <c r="R42" s="236"/>
-      <c r="S42" s="236"/>
+      <c r="R42" s="253"/>
+      <c r="S42" s="253"/>
     </row>
     <row r="43" spans="1:19" ht="30" customHeight="1">
       <c r="A43" s="60"/>
       <c r="B43" s="60"/>
-      <c r="C43" s="229"/>
-      <c r="D43" s="229"/>
-      <c r="E43" s="229"/>
-      <c r="F43" s="229"/>
-      <c r="G43" s="229"/>
-      <c r="H43" s="230"/>
-      <c r="I43" s="231"/>
-      <c r="J43" s="231"/>
-      <c r="K43" s="231"/>
-      <c r="L43" s="231"/>
-      <c r="M43" s="232"/>
-      <c r="N43" s="233"/>
-      <c r="O43" s="234"/>
-      <c r="P43" s="235"/>
+      <c r="C43" s="249"/>
+      <c r="D43" s="249"/>
+      <c r="E43" s="249"/>
+      <c r="F43" s="249"/>
+      <c r="G43" s="249"/>
+      <c r="H43" s="257"/>
+      <c r="I43" s="258"/>
+      <c r="J43" s="258"/>
+      <c r="K43" s="258"/>
+      <c r="L43" s="258"/>
+      <c r="M43" s="259"/>
+      <c r="N43" s="250"/>
+      <c r="O43" s="251"/>
+      <c r="P43" s="252"/>
       <c r="Q43" s="60"/>
-      <c r="R43" s="236"/>
-      <c r="S43" s="236"/>
+      <c r="R43" s="253"/>
+      <c r="S43" s="253"/>
     </row>
     <row r="44" spans="1:19" ht="30" customHeight="1">
       <c r="A44" s="60"/>
       <c r="B44" s="60"/>
-      <c r="C44" s="229"/>
-      <c r="D44" s="229"/>
-      <c r="E44" s="229"/>
-      <c r="F44" s="229"/>
-      <c r="G44" s="229"/>
-      <c r="H44" s="230"/>
-      <c r="I44" s="231"/>
-      <c r="J44" s="231"/>
-      <c r="K44" s="231"/>
-      <c r="L44" s="231"/>
-      <c r="M44" s="232"/>
-      <c r="N44" s="233"/>
-      <c r="O44" s="234"/>
-      <c r="P44" s="235"/>
+      <c r="C44" s="249"/>
+      <c r="D44" s="249"/>
+      <c r="E44" s="249"/>
+      <c r="F44" s="249"/>
+      <c r="G44" s="249"/>
+      <c r="H44" s="257"/>
+      <c r="I44" s="258"/>
+      <c r="J44" s="258"/>
+      <c r="K44" s="258"/>
+      <c r="L44" s="258"/>
+      <c r="M44" s="259"/>
+      <c r="N44" s="250"/>
+      <c r="O44" s="251"/>
+      <c r="P44" s="252"/>
       <c r="Q44" s="60"/>
-      <c r="R44" s="236"/>
-      <c r="S44" s="236"/>
+      <c r="R44" s="253"/>
+      <c r="S44" s="253"/>
     </row>
     <row r="45" spans="1:19" ht="30" customHeight="1">
       <c r="A45" s="60"/>
       <c r="B45" s="60"/>
-      <c r="C45" s="229"/>
-      <c r="D45" s="229"/>
-      <c r="E45" s="229"/>
-      <c r="F45" s="229"/>
-      <c r="G45" s="229"/>
-      <c r="H45" s="230"/>
-      <c r="I45" s="231"/>
-      <c r="J45" s="231"/>
-      <c r="K45" s="231"/>
-      <c r="L45" s="231"/>
-      <c r="M45" s="232"/>
-      <c r="N45" s="233"/>
-      <c r="O45" s="234"/>
-      <c r="P45" s="235"/>
+      <c r="C45" s="249"/>
+      <c r="D45" s="249"/>
+      <c r="E45" s="249"/>
+      <c r="F45" s="249"/>
+      <c r="G45" s="249"/>
+      <c r="H45" s="257"/>
+      <c r="I45" s="258"/>
+      <c r="J45" s="258"/>
+      <c r="K45" s="258"/>
+      <c r="L45" s="258"/>
+      <c r="M45" s="259"/>
+      <c r="N45" s="250"/>
+      <c r="O45" s="251"/>
+      <c r="P45" s="252"/>
       <c r="Q45" s="60"/>
-      <c r="R45" s="236"/>
-      <c r="S45" s="236"/>
+      <c r="R45" s="253"/>
+      <c r="S45" s="253"/>
     </row>
     <row r="46" spans="1:19" ht="30" customHeight="1">
       <c r="A46" s="60"/>
       <c r="B46" s="60"/>
-      <c r="C46" s="229"/>
-      <c r="D46" s="229"/>
-      <c r="E46" s="229"/>
-      <c r="F46" s="229"/>
-      <c r="G46" s="229"/>
-      <c r="H46" s="230"/>
-      <c r="I46" s="231"/>
-      <c r="J46" s="231"/>
-      <c r="K46" s="231"/>
-      <c r="L46" s="231"/>
-      <c r="M46" s="232"/>
-      <c r="N46" s="233"/>
-      <c r="O46" s="234"/>
-      <c r="P46" s="235"/>
+      <c r="C46" s="249"/>
+      <c r="D46" s="249"/>
+      <c r="E46" s="249"/>
+      <c r="F46" s="249"/>
+      <c r="G46" s="249"/>
+      <c r="H46" s="257"/>
+      <c r="I46" s="258"/>
+      <c r="J46" s="258"/>
+      <c r="K46" s="258"/>
+      <c r="L46" s="258"/>
+      <c r="M46" s="259"/>
+      <c r="N46" s="250"/>
+      <c r="O46" s="251"/>
+      <c r="P46" s="252"/>
       <c r="Q46" s="60"/>
-      <c r="R46" s="236"/>
-      <c r="S46" s="236"/>
+      <c r="R46" s="253"/>
+      <c r="S46" s="253"/>
     </row>
     <row r="47" spans="1:19" ht="30" customHeight="1">
       <c r="A47" s="60"/>
       <c r="B47" s="60"/>
-      <c r="C47" s="229"/>
-      <c r="D47" s="229"/>
-      <c r="E47" s="229"/>
-      <c r="F47" s="229"/>
-      <c r="G47" s="229"/>
-      <c r="H47" s="230"/>
-      <c r="I47" s="231"/>
-      <c r="J47" s="231"/>
-      <c r="K47" s="231"/>
-      <c r="L47" s="231"/>
-      <c r="M47" s="232"/>
-      <c r="N47" s="233"/>
-      <c r="O47" s="234"/>
-      <c r="P47" s="235"/>
+      <c r="C47" s="249"/>
+      <c r="D47" s="249"/>
+      <c r="E47" s="249"/>
+      <c r="F47" s="249"/>
+      <c r="G47" s="249"/>
+      <c r="H47" s="257"/>
+      <c r="I47" s="258"/>
+      <c r="J47" s="258"/>
+      <c r="K47" s="258"/>
+      <c r="L47" s="258"/>
+      <c r="M47" s="259"/>
+      <c r="N47" s="250"/>
+      <c r="O47" s="251"/>
+      <c r="P47" s="252"/>
       <c r="Q47" s="60"/>
-      <c r="R47" s="236"/>
-      <c r="S47" s="236"/>
+      <c r="R47" s="253"/>
+      <c r="S47" s="253"/>
     </row>
     <row r="48" spans="1:19" ht="30" customHeight="1">
       <c r="A48" s="60"/>
       <c r="B48" s="60"/>
-      <c r="C48" s="229"/>
-      <c r="D48" s="229"/>
-      <c r="E48" s="229"/>
-      <c r="F48" s="229"/>
-      <c r="G48" s="229"/>
-      <c r="H48" s="230"/>
-      <c r="I48" s="231"/>
-      <c r="J48" s="231"/>
-      <c r="K48" s="231"/>
-      <c r="L48" s="231"/>
-      <c r="M48" s="232"/>
-      <c r="N48" s="233"/>
-      <c r="O48" s="234"/>
-      <c r="P48" s="235"/>
+      <c r="C48" s="249"/>
+      <c r="D48" s="249"/>
+      <c r="E48" s="249"/>
+      <c r="F48" s="249"/>
+      <c r="G48" s="249"/>
+      <c r="H48" s="257"/>
+      <c r="I48" s="258"/>
+      <c r="J48" s="258"/>
+      <c r="K48" s="258"/>
+      <c r="L48" s="258"/>
+      <c r="M48" s="259"/>
+      <c r="N48" s="250"/>
+      <c r="O48" s="251"/>
+      <c r="P48" s="252"/>
       <c r="Q48" s="60"/>
-      <c r="R48" s="236"/>
-      <c r="S48" s="236"/>
+      <c r="R48" s="253"/>
+      <c r="S48" s="253"/>
     </row>
     <row r="49" spans="1:19" ht="30" customHeight="1">
       <c r="A49" s="60"/>
       <c r="B49" s="60"/>
-      <c r="C49" s="229"/>
-      <c r="D49" s="229"/>
-      <c r="E49" s="229"/>
-      <c r="F49" s="229"/>
-      <c r="G49" s="229"/>
-      <c r="H49" s="230"/>
-      <c r="I49" s="231"/>
-      <c r="J49" s="231"/>
-      <c r="K49" s="231"/>
-      <c r="L49" s="231"/>
-      <c r="M49" s="232"/>
-      <c r="N49" s="233"/>
-      <c r="O49" s="234"/>
-      <c r="P49" s="235"/>
+      <c r="C49" s="249"/>
+      <c r="D49" s="249"/>
+      <c r="E49" s="249"/>
+      <c r="F49" s="249"/>
+      <c r="G49" s="249"/>
+      <c r="H49" s="257"/>
+      <c r="I49" s="258"/>
+      <c r="J49" s="258"/>
+      <c r="K49" s="258"/>
+      <c r="L49" s="258"/>
+      <c r="M49" s="259"/>
+      <c r="N49" s="250"/>
+      <c r="O49" s="251"/>
+      <c r="P49" s="252"/>
       <c r="Q49" s="60"/>
-      <c r="R49" s="236"/>
-      <c r="S49" s="236"/>
+      <c r="R49" s="253"/>
+      <c r="S49" s="253"/>
     </row>
     <row r="50" spans="1:19" ht="30" customHeight="1">
       <c r="A50" s="60"/>
       <c r="B50" s="60"/>
-      <c r="C50" s="229"/>
-      <c r="D50" s="229"/>
-      <c r="E50" s="229"/>
-      <c r="F50" s="229"/>
-      <c r="G50" s="229"/>
-      <c r="H50" s="230"/>
-      <c r="I50" s="231"/>
-      <c r="J50" s="231"/>
-      <c r="K50" s="231"/>
-      <c r="L50" s="231"/>
-      <c r="M50" s="232"/>
-      <c r="N50" s="233"/>
-      <c r="O50" s="234"/>
-      <c r="P50" s="235"/>
+      <c r="C50" s="249"/>
+      <c r="D50" s="249"/>
+      <c r="E50" s="249"/>
+      <c r="F50" s="249"/>
+      <c r="G50" s="249"/>
+      <c r="H50" s="257"/>
+      <c r="I50" s="258"/>
+      <c r="J50" s="258"/>
+      <c r="K50" s="258"/>
+      <c r="L50" s="258"/>
+      <c r="M50" s="259"/>
+      <c r="N50" s="250"/>
+      <c r="O50" s="251"/>
+      <c r="P50" s="252"/>
       <c r="Q50" s="60"/>
-      <c r="R50" s="236"/>
-      <c r="S50" s="236"/>
+      <c r="R50" s="253"/>
+      <c r="S50" s="253"/>
     </row>
     <row r="51" spans="1:19" ht="30" customHeight="1">
       <c r="A51" s="60"/>
       <c r="B51" s="60"/>
-      <c r="C51" s="229"/>
-      <c r="D51" s="229"/>
-      <c r="E51" s="229"/>
-      <c r="F51" s="229"/>
-      <c r="G51" s="229"/>
-      <c r="H51" s="230"/>
-      <c r="I51" s="231"/>
-      <c r="J51" s="231"/>
-      <c r="K51" s="231"/>
-      <c r="L51" s="231"/>
-      <c r="M51" s="232"/>
-      <c r="N51" s="233"/>
-      <c r="O51" s="234"/>
-      <c r="P51" s="235"/>
+      <c r="C51" s="249"/>
+      <c r="D51" s="249"/>
+      <c r="E51" s="249"/>
+      <c r="F51" s="249"/>
+      <c r="G51" s="249"/>
+      <c r="H51" s="257"/>
+      <c r="I51" s="258"/>
+      <c r="J51" s="258"/>
+      <c r="K51" s="258"/>
+      <c r="L51" s="258"/>
+      <c r="M51" s="259"/>
+      <c r="N51" s="250"/>
+      <c r="O51" s="251"/>
+      <c r="P51" s="252"/>
       <c r="Q51" s="60"/>
-      <c r="R51" s="236"/>
-      <c r="S51" s="236"/>
+      <c r="R51" s="253"/>
+      <c r="S51" s="253"/>
     </row>
     <row r="52" spans="1:19" ht="30" customHeight="1">
       <c r="A52" s="60"/>
       <c r="B52" s="60"/>
-      <c r="C52" s="229"/>
-      <c r="D52" s="229"/>
-      <c r="E52" s="229"/>
-      <c r="F52" s="229"/>
-      <c r="G52" s="229"/>
-      <c r="H52" s="230"/>
-      <c r="I52" s="231"/>
-      <c r="J52" s="231"/>
-      <c r="K52" s="231"/>
-      <c r="L52" s="231"/>
-      <c r="M52" s="232"/>
-      <c r="N52" s="233"/>
-      <c r="O52" s="234"/>
-      <c r="P52" s="235"/>
+      <c r="C52" s="249"/>
+      <c r="D52" s="249"/>
+      <c r="E52" s="249"/>
+      <c r="F52" s="249"/>
+      <c r="G52" s="249"/>
+      <c r="H52" s="257"/>
+      <c r="I52" s="258"/>
+      <c r="J52" s="258"/>
+      <c r="K52" s="258"/>
+      <c r="L52" s="258"/>
+      <c r="M52" s="259"/>
+      <c r="N52" s="250"/>
+      <c r="O52" s="251"/>
+      <c r="P52" s="252"/>
       <c r="Q52" s="60"/>
-      <c r="R52" s="236"/>
-      <c r="S52" s="236"/>
+      <c r="R52" s="253"/>
+      <c r="S52" s="253"/>
     </row>
   </sheetData>
   <mergeCells count="205">
+    <mergeCell ref="C52:G52"/>
+    <mergeCell ref="H52:M52"/>
+    <mergeCell ref="N52:P52"/>
+    <mergeCell ref="R52:S52"/>
+    <mergeCell ref="C50:G50"/>
+    <mergeCell ref="H50:M50"/>
+    <mergeCell ref="N50:P50"/>
+    <mergeCell ref="R50:S50"/>
+    <mergeCell ref="C51:G51"/>
+    <mergeCell ref="H51:M51"/>
+    <mergeCell ref="N51:P51"/>
+    <mergeCell ref="R51:S51"/>
+    <mergeCell ref="C48:G48"/>
+    <mergeCell ref="H48:M48"/>
+    <mergeCell ref="N48:P48"/>
+    <mergeCell ref="R48:S48"/>
+    <mergeCell ref="C49:G49"/>
+    <mergeCell ref="H49:M49"/>
+    <mergeCell ref="N49:P49"/>
+    <mergeCell ref="R49:S49"/>
+    <mergeCell ref="C46:G46"/>
+    <mergeCell ref="H46:M46"/>
+    <mergeCell ref="N46:P46"/>
+    <mergeCell ref="R46:S46"/>
+    <mergeCell ref="C47:G47"/>
+    <mergeCell ref="H47:M47"/>
+    <mergeCell ref="N47:P47"/>
+    <mergeCell ref="R47:S47"/>
+    <mergeCell ref="C44:G44"/>
+    <mergeCell ref="H44:M44"/>
+    <mergeCell ref="N44:P44"/>
+    <mergeCell ref="R44:S44"/>
+    <mergeCell ref="C45:G45"/>
+    <mergeCell ref="H45:M45"/>
+    <mergeCell ref="N45:P45"/>
+    <mergeCell ref="R45:S45"/>
+    <mergeCell ref="C42:G42"/>
+    <mergeCell ref="H42:M42"/>
+    <mergeCell ref="N42:P42"/>
+    <mergeCell ref="R42:S42"/>
+    <mergeCell ref="C43:G43"/>
+    <mergeCell ref="H43:M43"/>
+    <mergeCell ref="N43:P43"/>
+    <mergeCell ref="R43:S43"/>
+    <mergeCell ref="C40:G40"/>
+    <mergeCell ref="H40:M40"/>
+    <mergeCell ref="N40:P40"/>
+    <mergeCell ref="R40:S40"/>
+    <mergeCell ref="C41:G41"/>
+    <mergeCell ref="H41:M41"/>
+    <mergeCell ref="N41:P41"/>
+    <mergeCell ref="R41:S41"/>
+    <mergeCell ref="C38:G38"/>
+    <mergeCell ref="H38:M38"/>
+    <mergeCell ref="N38:P38"/>
+    <mergeCell ref="R38:S38"/>
+    <mergeCell ref="C39:G39"/>
+    <mergeCell ref="H39:M39"/>
+    <mergeCell ref="N39:P39"/>
+    <mergeCell ref="R39:S39"/>
+    <mergeCell ref="C36:G36"/>
+    <mergeCell ref="H36:M36"/>
+    <mergeCell ref="N36:P36"/>
+    <mergeCell ref="R36:S36"/>
+    <mergeCell ref="C37:G37"/>
+    <mergeCell ref="H37:M37"/>
+    <mergeCell ref="N37:P37"/>
+    <mergeCell ref="R37:S37"/>
+    <mergeCell ref="C34:G34"/>
+    <mergeCell ref="H34:M34"/>
+    <mergeCell ref="N34:P34"/>
+    <mergeCell ref="R34:S34"/>
+    <mergeCell ref="C35:G35"/>
+    <mergeCell ref="H35:M35"/>
+    <mergeCell ref="N35:P35"/>
+    <mergeCell ref="R35:S35"/>
+    <mergeCell ref="C32:G32"/>
+    <mergeCell ref="H32:M32"/>
+    <mergeCell ref="N32:P32"/>
+    <mergeCell ref="R32:S32"/>
+    <mergeCell ref="C33:G33"/>
+    <mergeCell ref="H33:M33"/>
+    <mergeCell ref="N33:P33"/>
+    <mergeCell ref="R33:S33"/>
+    <mergeCell ref="C30:G30"/>
+    <mergeCell ref="H30:M30"/>
+    <mergeCell ref="N30:P30"/>
+    <mergeCell ref="R30:S30"/>
+    <mergeCell ref="C31:G31"/>
+    <mergeCell ref="H31:M31"/>
+    <mergeCell ref="N31:P31"/>
+    <mergeCell ref="R31:S31"/>
+    <mergeCell ref="C28:G28"/>
+    <mergeCell ref="H28:M28"/>
+    <mergeCell ref="N28:P28"/>
+    <mergeCell ref="R28:S28"/>
+    <mergeCell ref="C29:G29"/>
+    <mergeCell ref="H29:M29"/>
+    <mergeCell ref="N29:P29"/>
+    <mergeCell ref="R29:S29"/>
+    <mergeCell ref="C26:G26"/>
+    <mergeCell ref="H26:M26"/>
+    <mergeCell ref="N26:P26"/>
+    <mergeCell ref="R26:S26"/>
+    <mergeCell ref="C27:G27"/>
+    <mergeCell ref="H27:M27"/>
+    <mergeCell ref="N27:P27"/>
+    <mergeCell ref="R27:S27"/>
+    <mergeCell ref="C24:G24"/>
+    <mergeCell ref="H24:M24"/>
+    <mergeCell ref="N24:P24"/>
+    <mergeCell ref="R24:S24"/>
+    <mergeCell ref="C25:G25"/>
+    <mergeCell ref="H25:M25"/>
+    <mergeCell ref="N25:P25"/>
+    <mergeCell ref="R25:S25"/>
+    <mergeCell ref="C22:G22"/>
+    <mergeCell ref="H22:M22"/>
+    <mergeCell ref="N22:P22"/>
+    <mergeCell ref="R22:S22"/>
+    <mergeCell ref="C23:G23"/>
+    <mergeCell ref="H23:M23"/>
+    <mergeCell ref="N23:P23"/>
+    <mergeCell ref="R23:S23"/>
+    <mergeCell ref="C20:G20"/>
+    <mergeCell ref="H20:M20"/>
+    <mergeCell ref="N20:P20"/>
+    <mergeCell ref="R20:S20"/>
+    <mergeCell ref="C21:G21"/>
+    <mergeCell ref="H21:M21"/>
+    <mergeCell ref="N21:P21"/>
+    <mergeCell ref="R21:S21"/>
+    <mergeCell ref="C18:G18"/>
+    <mergeCell ref="H18:M18"/>
+    <mergeCell ref="N18:P18"/>
+    <mergeCell ref="R18:S18"/>
+    <mergeCell ref="C19:G19"/>
+    <mergeCell ref="H19:M19"/>
+    <mergeCell ref="N19:P19"/>
+    <mergeCell ref="R19:S19"/>
+    <mergeCell ref="C16:G16"/>
+    <mergeCell ref="H16:M16"/>
+    <mergeCell ref="N16:P16"/>
+    <mergeCell ref="R16:S16"/>
+    <mergeCell ref="C17:G17"/>
+    <mergeCell ref="H17:M17"/>
+    <mergeCell ref="N17:P17"/>
+    <mergeCell ref="R17:S17"/>
+    <mergeCell ref="C14:G14"/>
+    <mergeCell ref="H14:M14"/>
+    <mergeCell ref="N14:P14"/>
+    <mergeCell ref="R14:S14"/>
+    <mergeCell ref="C15:G15"/>
+    <mergeCell ref="H15:M15"/>
+    <mergeCell ref="N15:P15"/>
+    <mergeCell ref="R15:S15"/>
+    <mergeCell ref="C12:G12"/>
+    <mergeCell ref="H12:M12"/>
+    <mergeCell ref="N12:P12"/>
+    <mergeCell ref="R12:S12"/>
+    <mergeCell ref="C13:G13"/>
+    <mergeCell ref="H13:M13"/>
+    <mergeCell ref="N13:P13"/>
+    <mergeCell ref="R13:S13"/>
+    <mergeCell ref="C10:G10"/>
+    <mergeCell ref="H10:M10"/>
+    <mergeCell ref="N10:P10"/>
+    <mergeCell ref="R10:S10"/>
+    <mergeCell ref="C11:G11"/>
+    <mergeCell ref="H11:M11"/>
+    <mergeCell ref="N11:P11"/>
+    <mergeCell ref="R11:S11"/>
+    <mergeCell ref="C8:G8"/>
+    <mergeCell ref="H8:M8"/>
+    <mergeCell ref="N8:P8"/>
+    <mergeCell ref="R8:S8"/>
+    <mergeCell ref="C9:G9"/>
+    <mergeCell ref="H9:M9"/>
+    <mergeCell ref="N9:P9"/>
+    <mergeCell ref="R9:S9"/>
+    <mergeCell ref="C6:G6"/>
+    <mergeCell ref="H6:M6"/>
+    <mergeCell ref="N6:P6"/>
+    <mergeCell ref="R6:S6"/>
+    <mergeCell ref="C7:G7"/>
+    <mergeCell ref="H7:M7"/>
+    <mergeCell ref="N7:P7"/>
+    <mergeCell ref="R7:S7"/>
     <mergeCell ref="C4:G4"/>
     <mergeCell ref="H4:M4"/>
     <mergeCell ref="N4:P4"/>
@@ -21962,194 +22070,6 @@
     <mergeCell ref="F2:M2"/>
     <mergeCell ref="O2:P2"/>
     <mergeCell ref="R2:S2"/>
-    <mergeCell ref="C8:G8"/>
-    <mergeCell ref="H8:M8"/>
-    <mergeCell ref="N8:P8"/>
-    <mergeCell ref="R8:S8"/>
-    <mergeCell ref="C9:G9"/>
-    <mergeCell ref="H9:M9"/>
-    <mergeCell ref="N9:P9"/>
-    <mergeCell ref="R9:S9"/>
-    <mergeCell ref="C6:G6"/>
-    <mergeCell ref="H6:M6"/>
-    <mergeCell ref="N6:P6"/>
-    <mergeCell ref="R6:S6"/>
-    <mergeCell ref="C7:G7"/>
-    <mergeCell ref="H7:M7"/>
-    <mergeCell ref="N7:P7"/>
-    <mergeCell ref="R7:S7"/>
-    <mergeCell ref="C12:G12"/>
-    <mergeCell ref="H12:M12"/>
-    <mergeCell ref="N12:P12"/>
-    <mergeCell ref="R12:S12"/>
-    <mergeCell ref="C13:G13"/>
-    <mergeCell ref="H13:M13"/>
-    <mergeCell ref="N13:P13"/>
-    <mergeCell ref="R13:S13"/>
-    <mergeCell ref="C10:G10"/>
-    <mergeCell ref="H10:M10"/>
-    <mergeCell ref="N10:P10"/>
-    <mergeCell ref="R10:S10"/>
-    <mergeCell ref="C11:G11"/>
-    <mergeCell ref="H11:M11"/>
-    <mergeCell ref="N11:P11"/>
-    <mergeCell ref="R11:S11"/>
-    <mergeCell ref="C16:G16"/>
-    <mergeCell ref="H16:M16"/>
-    <mergeCell ref="N16:P16"/>
-    <mergeCell ref="R16:S16"/>
-    <mergeCell ref="C17:G17"/>
-    <mergeCell ref="H17:M17"/>
-    <mergeCell ref="N17:P17"/>
-    <mergeCell ref="R17:S17"/>
-    <mergeCell ref="C14:G14"/>
-    <mergeCell ref="H14:M14"/>
-    <mergeCell ref="N14:P14"/>
-    <mergeCell ref="R14:S14"/>
-    <mergeCell ref="C15:G15"/>
-    <mergeCell ref="H15:M15"/>
-    <mergeCell ref="N15:P15"/>
-    <mergeCell ref="R15:S15"/>
-    <mergeCell ref="C20:G20"/>
-    <mergeCell ref="H20:M20"/>
-    <mergeCell ref="N20:P20"/>
-    <mergeCell ref="R20:S20"/>
-    <mergeCell ref="C21:G21"/>
-    <mergeCell ref="H21:M21"/>
-    <mergeCell ref="N21:P21"/>
-    <mergeCell ref="R21:S21"/>
-    <mergeCell ref="C18:G18"/>
-    <mergeCell ref="H18:M18"/>
-    <mergeCell ref="N18:P18"/>
-    <mergeCell ref="R18:S18"/>
-    <mergeCell ref="C19:G19"/>
-    <mergeCell ref="H19:M19"/>
-    <mergeCell ref="N19:P19"/>
-    <mergeCell ref="R19:S19"/>
-    <mergeCell ref="C24:G24"/>
-    <mergeCell ref="H24:M24"/>
-    <mergeCell ref="N24:P24"/>
-    <mergeCell ref="R24:S24"/>
-    <mergeCell ref="C25:G25"/>
-    <mergeCell ref="H25:M25"/>
-    <mergeCell ref="N25:P25"/>
-    <mergeCell ref="R25:S25"/>
-    <mergeCell ref="C22:G22"/>
-    <mergeCell ref="H22:M22"/>
-    <mergeCell ref="N22:P22"/>
-    <mergeCell ref="R22:S22"/>
-    <mergeCell ref="C23:G23"/>
-    <mergeCell ref="H23:M23"/>
-    <mergeCell ref="N23:P23"/>
-    <mergeCell ref="R23:S23"/>
-    <mergeCell ref="C28:G28"/>
-    <mergeCell ref="H28:M28"/>
-    <mergeCell ref="N28:P28"/>
-    <mergeCell ref="R28:S28"/>
-    <mergeCell ref="C29:G29"/>
-    <mergeCell ref="H29:M29"/>
-    <mergeCell ref="N29:P29"/>
-    <mergeCell ref="R29:S29"/>
-    <mergeCell ref="C26:G26"/>
-    <mergeCell ref="H26:M26"/>
-    <mergeCell ref="N26:P26"/>
-    <mergeCell ref="R26:S26"/>
-    <mergeCell ref="C27:G27"/>
-    <mergeCell ref="H27:M27"/>
-    <mergeCell ref="N27:P27"/>
-    <mergeCell ref="R27:S27"/>
-    <mergeCell ref="C32:G32"/>
-    <mergeCell ref="H32:M32"/>
-    <mergeCell ref="N32:P32"/>
-    <mergeCell ref="R32:S32"/>
-    <mergeCell ref="C33:G33"/>
-    <mergeCell ref="H33:M33"/>
-    <mergeCell ref="N33:P33"/>
-    <mergeCell ref="R33:S33"/>
-    <mergeCell ref="C30:G30"/>
-    <mergeCell ref="H30:M30"/>
-    <mergeCell ref="N30:P30"/>
-    <mergeCell ref="R30:S30"/>
-    <mergeCell ref="C31:G31"/>
-    <mergeCell ref="H31:M31"/>
-    <mergeCell ref="N31:P31"/>
-    <mergeCell ref="R31:S31"/>
-    <mergeCell ref="C36:G36"/>
-    <mergeCell ref="H36:M36"/>
-    <mergeCell ref="N36:P36"/>
-    <mergeCell ref="R36:S36"/>
-    <mergeCell ref="C37:G37"/>
-    <mergeCell ref="H37:M37"/>
-    <mergeCell ref="N37:P37"/>
-    <mergeCell ref="R37:S37"/>
-    <mergeCell ref="C34:G34"/>
-    <mergeCell ref="H34:M34"/>
-    <mergeCell ref="N34:P34"/>
-    <mergeCell ref="R34:S34"/>
-    <mergeCell ref="C35:G35"/>
-    <mergeCell ref="H35:M35"/>
-    <mergeCell ref="N35:P35"/>
-    <mergeCell ref="R35:S35"/>
-    <mergeCell ref="C40:G40"/>
-    <mergeCell ref="H40:M40"/>
-    <mergeCell ref="N40:P40"/>
-    <mergeCell ref="R40:S40"/>
-    <mergeCell ref="C41:G41"/>
-    <mergeCell ref="H41:M41"/>
-    <mergeCell ref="N41:P41"/>
-    <mergeCell ref="R41:S41"/>
-    <mergeCell ref="C38:G38"/>
-    <mergeCell ref="H38:M38"/>
-    <mergeCell ref="N38:P38"/>
-    <mergeCell ref="R38:S38"/>
-    <mergeCell ref="C39:G39"/>
-    <mergeCell ref="H39:M39"/>
-    <mergeCell ref="N39:P39"/>
-    <mergeCell ref="R39:S39"/>
-    <mergeCell ref="C44:G44"/>
-    <mergeCell ref="H44:M44"/>
-    <mergeCell ref="N44:P44"/>
-    <mergeCell ref="R44:S44"/>
-    <mergeCell ref="C45:G45"/>
-    <mergeCell ref="H45:M45"/>
-    <mergeCell ref="N45:P45"/>
-    <mergeCell ref="R45:S45"/>
-    <mergeCell ref="C42:G42"/>
-    <mergeCell ref="H42:M42"/>
-    <mergeCell ref="N42:P42"/>
-    <mergeCell ref="R42:S42"/>
-    <mergeCell ref="C43:G43"/>
-    <mergeCell ref="H43:M43"/>
-    <mergeCell ref="N43:P43"/>
-    <mergeCell ref="R43:S43"/>
-    <mergeCell ref="C48:G48"/>
-    <mergeCell ref="H48:M48"/>
-    <mergeCell ref="N48:P48"/>
-    <mergeCell ref="R48:S48"/>
-    <mergeCell ref="C49:G49"/>
-    <mergeCell ref="H49:M49"/>
-    <mergeCell ref="N49:P49"/>
-    <mergeCell ref="R49:S49"/>
-    <mergeCell ref="C46:G46"/>
-    <mergeCell ref="H46:M46"/>
-    <mergeCell ref="N46:P46"/>
-    <mergeCell ref="R46:S46"/>
-    <mergeCell ref="C47:G47"/>
-    <mergeCell ref="H47:M47"/>
-    <mergeCell ref="N47:P47"/>
-    <mergeCell ref="R47:S47"/>
-    <mergeCell ref="C52:G52"/>
-    <mergeCell ref="H52:M52"/>
-    <mergeCell ref="N52:P52"/>
-    <mergeCell ref="R52:S52"/>
-    <mergeCell ref="C50:G50"/>
-    <mergeCell ref="H50:M50"/>
-    <mergeCell ref="N50:P50"/>
-    <mergeCell ref="R50:S50"/>
-    <mergeCell ref="C51:G51"/>
-    <mergeCell ref="H51:M51"/>
-    <mergeCell ref="N51:P51"/>
-    <mergeCell ref="R51:S51"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.31496062992125984" bottom="0.27559055118110237" header="0.35433070866141736" footer="0.15748031496062992"/>
